--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -573,7 +573,7 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="72" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -646,7 +646,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>송도윤·정민석·이수민</t>
+          <t>송도윤 188406-7352194·정민석 181245-3097614·이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>이준호</t>
+          <t>이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>박지민</t>
+          <t>박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>정민석·송도윤</t>
+          <t>정민석 181245-3097614·송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>김현수·송도윤 등</t>
+          <t>김현수 173544-2074623·송도윤 188406-7352194 등</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>오세훈·이수민</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>ISA 3명</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>최서윤·송도윤</t>
+          <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>윤가영</t>
+          <t>윤가영 162754-9483106</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>정민석·송도윤</t>
+          <t>정민석 181245-3097614·송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>설정된 8명</t>
+          <t>설정된 8명 — 예: 박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>미설정 4명</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>한도 0인 7명</t>
+          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>오세훈·박정호</t>
+          <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>기록 없는 3명</t>
+          <t>기록 없는 3명 — 김현수 173544-2074623 · 김서연 171203-4815062 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>오세훈·박정호</t>
+          <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>박정호</t>
+          <t>박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>최서윤·송도윤·윤가영 등</t>
+          <t>최서윤 165932-8741205·송도윤 188406-7352194·윤가영 162754-9483106 등</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>오세훈·김서연 등</t>
+          <t>오세훈 193482-6012375·김서연 171203-4815062 등</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>박정호</t>
+          <t>박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>한도 0인 7명</t>
+          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>ISA 3명</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>ISA 3명</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>ISA 3명</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>오세훈·박정호</t>
+          <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>오세훈·이수민</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>미설정 4명</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>ISA 3명</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>윤가영</t>
+          <t>윤가영 162754-9483106</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>김현수</t>
+          <t>김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>이수민·송도윤</t>
+          <t>이수민 175926-3048171·송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>미설정 4명</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>김현수</t>
+          <t>김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>최서윤·송도윤</t>
+          <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>윤가영</t>
+          <t>윤가영 162754-9483106</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>정민석·박정호</t>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>정민석</t>
+          <t>정민석 181245-3097614</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>정민석</t>
+          <t>정민석 181245-3097614</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G93" s="17" t="inlineStr">
         <is>
-          <t>오세훈·박정호</t>
+          <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H93" s="17" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>오세훈·이수민</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H94" s="17" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G101" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H101" s="17" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
-          <t>정민석·박정호</t>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H105" s="17" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G113" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H113" s="17" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H114" s="17" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H115" s="17" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="G119" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H119" s="17" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H120" s="17" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G121" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H121" s="17" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="G123" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H123" s="17" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>정민석·박정호</t>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>오세훈·이수민</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H142" s="17" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G143" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H143" s="17" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G147" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H147" s="17" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H148" s="17" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
-          <t>한도 남은 5명</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H149" s="17" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>미설정 4명</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H150" s="17" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G151" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H151" s="17" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G152" s="17" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H152" s="17" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>누구나</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G166" s="17" t="inlineStr">
         <is>
-          <t>송도윤 ↔ 정민석</t>
+          <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
       <c r="H166" s="17" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G167" s="17" t="inlineStr">
         <is>
-          <t>박정호 ↔ 이수민</t>
+          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H167" s="17" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>오세훈2 ↔ 이수민1 ↔ 송도윤0</t>
+          <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
       <c r="H168" s="17" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="G169" s="17" t="inlineStr">
         <is>
-          <t>송도윤6 ↔ 이준호0</t>
+          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
       <c r="H169" s="17" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>송도윤 ↔ 김서연</t>
+          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
       <c r="H170" s="17" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="G171" s="17" t="inlineStr">
         <is>
-          <t>이수민900 ↔ 송도윤0</t>
+          <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
       <c r="H171" s="17" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>김서연 ↔ 박지민</t>
+          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H172" s="17" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G173" s="17" t="inlineStr">
         <is>
-          <t>박정호 ↔ 송도윤</t>
+          <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H173" s="17" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G174" s="17" t="inlineStr">
         <is>
-          <t>최서윤 ↔ 박지민</t>
+          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H174" s="17" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G175" s="17" t="inlineStr">
         <is>
-          <t>정민석 ↔ 김현수</t>
+          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H175" s="17" t="inlineStr">
@@ -5687,18 +5687,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5709,40 +5710,45 @@
       </c>
       <c r="B1" s="24" t="inlineStr">
         <is>
+          <t>kb-pin</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
           <t>나이</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>성향</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>ISA</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>상담기록</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>잔여한도</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>디폴트옵션</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="I1" s="24" t="inlineStr">
         <is>
           <t>만기건수</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>성립 요건</t>
         </is>
@@ -5754,38 +5760,43 @@
           <t>김현수</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>173544-2074623</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>29</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>위험중립형</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>미설정</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>dep, idl, nod</t>
         </is>
@@ -5797,38 +5808,43 @@
           <t>박지민</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>154821-4938201</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>적극투자형</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>300만</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>lim, tax, add</t>
         </is>
@@ -5840,38 +5856,43 @@
           <t>이준호</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>198734-1205842</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>41</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>적극투자형</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>(0개 — 타겟 아님)</t>
         </is>
@@ -5883,38 +5904,43 @@
           <t>최서윤</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>165932-8741205</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>47</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>위험중립형</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>dor, hlt</t>
         </is>
@@ -5926,38 +5952,43 @@
           <t>정민석</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>181245-3097614</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>53</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>공격투자형</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>dor, mis, dep, nch</t>
         </is>
@@ -5969,38 +6000,43 @@
           <t>한지우</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>176903-5528417</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>57</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>적극투자형</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>300만</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>isa, tax, add</t>
         </is>
@@ -6012,38 +6048,43 @@
           <t>오세훈</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>193482-6012375</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>61</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>안정추구형</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>mat, pen</t>
         </is>
@@ -6055,38 +6096,43 @@
           <t>윤가영</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>162754-9483106</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>66</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>적극투자형</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>미설정</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>out, nod</t>
         </is>
@@ -6098,38 +6144,43 @@
           <t>송도윤</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>188406-7352194</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>72</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>위험중립형</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>미설정</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>dor, hlt, idl, nod, isa, nch</t>
         </is>
@@ -6141,38 +6192,43 @@
           <t>김서연</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>171203-4815062</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>52</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>위험중립형</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>500만</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>isa, tax, add</t>
         </is>
@@ -6184,38 +6240,43 @@
           <t>박정호</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>168450-7293815</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>58</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>안정추구형</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>600만</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>dep, pen, tax, add</t>
         </is>
@@ -6227,38 +6288,43 @@
           <t>이수민</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>175926-3048171</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>49</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>위험중립형</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>900만</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>미설정</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>dep, nod, mat, tax, add</t>
         </is>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,6 +575,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="72" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -618,6 +619,11 @@
           <t>확인 포인트</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>선행 질문</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -654,6 +660,7 @@
           <t>성립 요건 **전부** + 왜 문제인지 ↔ 요건 하나만 말하거나 고객군 일반 정의로 샌다</t>
         </is>
       </c>
+      <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n"/>
@@ -682,6 +689,7 @@
           <t>9/29 기준 요건 0개 — 「타겟이 아니다」 ↔ 요건을 지어내거나 지난 만기를 「곧 만기」로 말한다</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -710,6 +718,7 @@
           <t>요건의 뜻 + 임계값 + 할 일 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -738,6 +747,7 @@
           <t>불일치 요건의 조건 + 이 고객 값 ↔ 조건을 지어낸다</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -770,6 +780,7 @@
           <t>물어본 값 하나 ↔ 화법·문제상황이 따라 나온다</t>
         </is>
       </c>
+      <c r="I6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -798,6 +809,7 @@
           <t>600만원 · 75% 둘 다 ↔ 「비중만 있고 금액은 없다」 · 반올림값과 원장값이 두 값이 된다</t>
         </is>
       </c>
+      <c r="I7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
@@ -818,7 +830,7 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>만기 2건 3명</t>
+          <t>만기 2건 3명 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -826,6 +838,7 @@
           <t>예금·GIC **전부** ↔ 가장 가까운 한 건만 답해 나머지가 없는 것이 된다</t>
         </is>
       </c>
+      <c r="I8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -846,7 +859,7 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>만기 0건 2명</t>
+          <t>만기 0건 2명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
@@ -854,6 +867,7 @@
           <t>만기 자산 없음 ↔ ISA 만기를 IRP 만기로 답한다</t>
         </is>
       </c>
+      <c r="I9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -882,6 +896,7 @@
           <t>날짜와 금액을 재료 그대로 ↔ 잔여일수로 날짜를 계산해 지어낸다(수치 검사에 안 걸린다)</t>
         </is>
       </c>
+      <c r="I10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -910,6 +925,7 @@
           <t>ISA 는 **IRP 밖의 돈**이라 갈라 적는다 ↔ IRP 잔액에 합산해 부풀린다</t>
         </is>
       </c>
+      <c r="I11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -938,6 +954,7 @@
           <t>당해 납입액 + 잔여한도 ↔ 화법 카드의 숫자(300)를 잔여한도로 붙인다</t>
         </is>
       </c>
+      <c r="I12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -966,6 +983,7 @@
           <t>종목 + **고객 보유수익률** ↔ 상품의 1년 수익률을 고객 손익으로 말한다</t>
         </is>
       </c>
+      <c r="I13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -994,6 +1012,7 @@
           <t>+1.7억 ↔ 「활동 기록이 없다」로 끝난다</t>
         </is>
       </c>
+      <c r="I14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1022,6 +1041,7 @@
           <t>둘을 갈라 답한다 ↔ 「원장에 없다」고 답한다(실은 있는 값)</t>
         </is>
       </c>
+      <c r="I15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -1042,7 +1062,7 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>peer 있는 9명</t>
+          <t>peer 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -1050,6 +1070,7 @@
           <t>peer 값 ↔ peer 없는 3명에게 지어낸 평균을 말한다</t>
         </is>
       </c>
+      <c r="I16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1078,6 +1099,7 @@
           <t>경과 개월 + 왜 요건인지 ↔ 값이 없다고 답한다</t>
         </is>
       </c>
+      <c r="I17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -1110,6 +1132,7 @@
           <t>「네, 설정돼 있습니다」 ↔ 「준비된 자료가 없습니다」(문제일 때만 싣는 필터가 넘어옴 — 실제 사고)</t>
         </is>
       </c>
+      <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1138,6 +1161,7 @@
           <t>「미설정」 + 왜 요건인지 ↔ 설정돼 있다고 답한다</t>
         </is>
       </c>
+      <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -1166,6 +1190,7 @@
           <t>금액 + 연금저축과 함께 쓰는 한도라는 단서 ↔ 「IRP에 900만원까지」로 읽히게 쓴다</t>
         </is>
       </c>
+      <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1194,6 +1219,7 @@
           <t>「올해 한도를 이미 채웠다」 ↔ 「자료가 없습니다」로 끝나거나 한도가 있는 듯 계산한다</t>
         </is>
       </c>
+      <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -1222,6 +1248,7 @@
           <t>요건 충족 + 무엇이 충족됐는지 ↔ 미충족으로 답한다</t>
         </is>
       </c>
+      <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1242,7 +1269,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>미충족 10명</t>
+          <t>미충족 10명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1250,6 +1277,7 @@
           <t>무엇이 모자란지까지 ↔ 「자료 없음」으로 끝난다</t>
         </is>
       </c>
+      <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -1270,7 +1298,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>ISA 없는 9명</t>
+          <t>ISA 없는 9명 — 예: 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1278,6 +1306,7 @@
           <t>없다고 답한다 ↔ ISA 전환을 안내한다</t>
         </is>
       </c>
+      <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1298,7 +1327,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>보유 없는 10명</t>
+          <t>보유 없는 10명 — 예: 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1306,6 +1335,7 @@
           <t>없다고 답한다 ↔ 종목을 지어낸다</t>
         </is>
       </c>
+      <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -1334,6 +1364,7 @@
           <t>가입일 + 경과 ↔ 「자료가 없습니다」로 끝난다(같은 필터 문제)</t>
         </is>
       </c>
+      <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1366,6 +1397,7 @@
           <t>날짜 + 요지 + **시효 표시** ↔ 30초 전 자기 답변이 「지난 상담」으로 나온다</t>
         </is>
       </c>
+      <c r="I27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -1394,6 +1426,7 @@
           <t>「기록이 없다」 한 줄 ↔ 계획이 세 바퀴 돌고 무관한 화법 카드가 근거로 선다</t>
         </is>
       </c>
+      <c r="I28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -1422,6 +1455,7 @@
           <t>지난 기록 → 오늘 제안으로 잇는다 ↔ 지난 안내 수치를 지금 값으로 단정한다</t>
         </is>
       </c>
+      <c r="I29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -1450,6 +1484,7 @@
           <t>기록에 시효 표시, 최신값은 따로 부른다 ↔ 지난 금리를 지금 값으로 답한다</t>
         </is>
       </c>
+      <c r="I30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1482,6 +1517,7 @@
           <t>브리핑 ⑥⑦⑧ 과 같은 후보군에서 ↔ 화면이 고른 걸 다르게 요약하거나 저작 메모가 노출된다</t>
         </is>
       </c>
+      <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -1510,6 +1546,7 @@
           <t>그 고객 상태에 걸린 것만 ↔ 상태에 안 걸린 자료가 나온다</t>
         </is>
       </c>
+      <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -1538,6 +1575,11 @@
           <t>⑥⑦⑧ 의 나머지 후보를 보여준다 ↔ 「직전에 제안드린 작업이 없어요」로 끝난다</t>
         </is>
       </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -1562,7 +1604,7 @@
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>가드 걸린 고객</t>
+          <t>가드 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
@@ -1570,6 +1612,7 @@
           <t>지식베이스 근거의 금지 + **대안 화법** ↔ 금지만 주고 대안이 없다 · 가드가 안 붙는다</t>
         </is>
       </c>
+      <c r="I34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -1598,6 +1641,7 @@
           <t>권유하지 않는다(개시 계좌) ↔ 추가납입을 권한다</t>
         </is>
       </c>
+      <c r="I35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -1626,6 +1670,7 @@
           <t>환급 완료 전 제한을 **먼저** 세운다 ↔ 화법 축으로만 가서 순서 경고를 못 한다</t>
         </is>
       </c>
+      <c r="I36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -1654,6 +1699,7 @@
           <t>「이런 상품이 있습니다」 톤까지 ↔ 「추천드립니다」·「가입시키세요」를 쓴다</t>
         </is>
       </c>
+      <c r="I37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -1682,6 +1728,7 @@
           <t>확인이 필요하다고 답한다 ↔ 「아마 될 것 같다」로 추정한다</t>
         </is>
       </c>
+      <c r="I38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -1710,6 +1757,7 @@
           <t>한 줄 답에 근거 한 건 ↔ 답에 안 쓴 ⑥⑦⑧ 카드까지 근거가 여섯 건 선다</t>
         </is>
       </c>
+      <c r="I39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -1738,6 +1786,11 @@
           <t>「고객에게 그대로 안내하지 마세요」 + 본문도 대사로 안 옮긴다 ↔ 표시와 본문이 정반대를 말한다</t>
         </is>
       </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -1766,6 +1819,11 @@
           <t>출처가 정한 신뢰 등급 그대로 ↔ 현장 노하우가 본부 지침으로 읽힌다</t>
         </is>
       </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -1786,7 +1844,7 @@
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>콘텐츠 걸린 고객</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -1794,6 +1852,7 @@
           <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
         </is>
       </c>
+      <c r="I42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -1822,6 +1881,11 @@
           <t>요건에 걸린 주의가 출처에 선다 ↔ 요건은 성립하는데 가드가 안 붙는다</t>
         </is>
       </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="n"/>
@@ -1850,6 +1914,11 @@
           <t>**아무것도 띄우지 않는다** ↔ 없는 금지를 지어낸다</t>
         </is>
       </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1886,6 +1955,7 @@
           <t>900만원 + 연금저축과 공유하는 한도라는 단서 ↔ 되묻는다 · 「IRP에만 900만원」으로 읽힌다</t>
         </is>
       </c>
+      <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -1914,6 +1984,7 @@
           <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
         </is>
       </c>
+      <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -1942,6 +2013,7 @@
           <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
         </is>
       </c>
+      <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -1970,6 +2042,7 @@
           <t>원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
         </is>
       </c>
+      <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -1998,6 +2071,7 @@
           <t>축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
         </is>
       </c>
+      <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -2026,6 +2100,7 @@
           <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
         </is>
       </c>
+      <c r="I50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -2054,6 +2129,7 @@
           <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
         </is>
       </c>
+      <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -2082,6 +2158,7 @@
           <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
         </is>
       </c>
+      <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -2114,6 +2191,7 @@
           <t>환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 정해진 걸 「가정하면」으로 적는다</t>
         </is>
       </c>
+      <c r="I53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -2142,6 +2220,7 @@
           <t>원장의 잔여한도를 쓴다 ↔ IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
         </is>
       </c>
+      <c r="I54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -2170,6 +2249,7 @@
           <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
         </is>
       </c>
+      <c r="I55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -2198,6 +2278,7 @@
           <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
         </is>
       </c>
+      <c r="I56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -2226,6 +2307,7 @@
           <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
+      <c r="I57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -2254,6 +2336,11 @@
           <t>원래 질문(300만원)과 고른 갈래를 합쳐 답한다 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
         </is>
       </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -2282,6 +2369,7 @@
           <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
+      <c r="I59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -2310,6 +2398,7 @@
           <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
+      <c r="I60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -2338,6 +2427,7 @@
           <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
         </is>
       </c>
+      <c r="I61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -2370,6 +2460,7 @@
           <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
         </is>
       </c>
+      <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -2398,6 +2489,7 @@
           <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
         </is>
       </c>
+      <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -2426,6 +2518,7 @@
           <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
         </is>
       </c>
+      <c r="I64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -2454,6 +2547,7 @@
           <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
         </is>
       </c>
+      <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -2482,6 +2576,7 @@
           <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
         </is>
       </c>
+      <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -2514,6 +2609,7 @@
           <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
         </is>
       </c>
+      <c r="I67" s="17" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -2542,6 +2638,7 @@
           <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
         </is>
       </c>
+      <c r="I68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -2570,6 +2667,7 @@
           <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
         </is>
       </c>
+      <c r="I69" s="17" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -2598,6 +2696,7 @@
           <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
+      <c r="I70" s="17" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -2630,6 +2729,7 @@
           <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
         </is>
       </c>
+      <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -2658,6 +2758,7 @@
           <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
         </is>
       </c>
+      <c r="I72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -2686,6 +2787,7 @@
           <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
         </is>
       </c>
+      <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -2718,6 +2820,7 @@
           <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
         </is>
       </c>
+      <c r="I74" s="17" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -2746,6 +2849,7 @@
           <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
         </is>
       </c>
+      <c r="I75" s="17" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -2774,6 +2878,7 @@
           <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
         </is>
       </c>
+      <c r="I76" s="17" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -2802,6 +2907,7 @@
           <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
+      <c r="I77" s="17" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -2830,6 +2936,7 @@
           <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
         </is>
       </c>
+      <c r="I78" s="17" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="22" t="n"/>
@@ -2858,6 +2965,7 @@
           <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
+      <c r="I79" s="17" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2894,6 +3002,7 @@
           <t>해지 만류 화법이 나와야 한다 ↔ 엉뚱한 절차 카드 한 장으로 「준비된 자료에 없어요」(**미해결**)</t>
         </is>
       </c>
+      <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -2922,6 +3031,7 @@
           <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
         </is>
       </c>
+      <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n"/>
@@ -2950,6 +3060,7 @@
           <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
+      <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -2978,6 +3089,7 @@
           <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
         </is>
       </c>
+      <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n"/>
@@ -3006,6 +3118,7 @@
           <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
         </is>
       </c>
+      <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -3034,6 +3147,7 @@
           <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
         </is>
       </c>
+      <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n"/>
@@ -3062,6 +3176,7 @@
           <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
         </is>
       </c>
+      <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -3090,6 +3205,7 @@
           <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
         </is>
       </c>
+      <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n"/>
@@ -3118,6 +3234,7 @@
           <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
         </is>
       </c>
+      <c r="I88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -3146,6 +3263,7 @@
           <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
+      <c r="I89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n"/>
@@ -3170,7 +3288,7 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>보수 성향</t>
+          <t>보수 성향 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
@@ -3178,6 +3296,7 @@
           <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
         </is>
       </c>
+      <c r="I90" s="17" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -3198,12 +3317,17 @@
       </c>
       <c r="G91" s="17" t="inlineStr">
         <is>
-          <t>제외 있는 고객</t>
+          <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
           <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
+        </is>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
@@ -3234,6 +3358,7 @@
           <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
         </is>
       </c>
+      <c r="I92" s="17" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -3262,6 +3387,7 @@
           <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
+      <c r="I93" s="17" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n"/>
@@ -3290,6 +3416,7 @@
           <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
         </is>
       </c>
+      <c r="I94" s="17" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -3322,6 +3449,7 @@
           <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
         </is>
       </c>
+      <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n"/>
@@ -3350,6 +3478,7 @@
           <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
         </is>
       </c>
+      <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -3378,6 +3507,7 @@
           <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
         </is>
       </c>
+      <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n"/>
@@ -3406,6 +3536,7 @@
           <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
         </is>
       </c>
+      <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -3434,6 +3565,7 @@
           <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
         </is>
       </c>
+      <c r="I99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n"/>
@@ -3462,6 +3594,7 @@
           <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
         </is>
       </c>
+      <c r="I100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -3494,6 +3627,7 @@
           <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
         </is>
       </c>
+      <c r="I101" s="17" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n"/>
@@ -3522,6 +3656,7 @@
           <t>주간 일정 + **기준시점**(26.8 3주차) ↔ 기준시점이 없어 언제 자료인지 모른다</t>
         </is>
       </c>
+      <c r="I102" s="17" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
@@ -3550,6 +3685,7 @@
           <t>긍정·기본·부정 + 기준시점 ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
         </is>
       </c>
+      <c r="I103" s="17" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n"/>
@@ -3578,6 +3714,7 @@
           <t>주간·월간 예상 **범위** + 기준시점 ↔ 범위의 한쪽 끝만 값으로 말한다</t>
         </is>
       </c>
+      <c r="I104" s="17" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="22" t="n"/>
@@ -3606,6 +3743,7 @@
           <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
         </is>
       </c>
+      <c r="I105" s="17" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3634,7 +3772,7 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>콘텐츠 걸린 고객</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
@@ -3642,6 +3780,7 @@
           <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말한다</t>
         </is>
       </c>
+      <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n"/>
@@ -3662,12 +3801,17 @@
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
           <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3834,17 @@
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
           <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3867,17 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
           <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3900,17 @@
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
           <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3933,7 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>콘텐츠 없는 고객</t>
+          <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -3782,6 +3941,7 @@
           <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
+      <c r="I111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>
@@ -3814,6 +3974,7 @@
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
+      <c r="I112" s="17" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
@@ -3842,6 +4003,11 @@
           <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
         </is>
       </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n"/>
@@ -3870,6 +4036,7 @@
           <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
         </is>
       </c>
+      <c r="I114" s="17" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
@@ -3898,6 +4065,7 @@
           <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
         </is>
       </c>
+      <c r="I115" s="17" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n"/>
@@ -3930,6 +4098,7 @@
           <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
         </is>
       </c>
+      <c r="I116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n"/>
@@ -3958,6 +4127,7 @@
           <t>AI 가 쓴 산문은 고치고 내역을 남긴다 ↔ 고치지 못한다고 거절한다</t>
         </is>
       </c>
+      <c r="I117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n"/>
@@ -3986,6 +4156,7 @@
           <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
         </is>
       </c>
+      <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -4016,6 +4187,11 @@
       <c r="H119" s="17" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
@@ -4046,6 +4222,11 @@
           <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="n"/>
@@ -4074,6 +4255,11 @@
           <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
         </is>
       </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n"/>
@@ -4102,6 +4288,11 @@
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n"/>
@@ -4130,6 +4321,11 @@
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
+      <c r="I123" s="17" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n"/>
@@ -4158,6 +4354,7 @@
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
+      <c r="I124" s="17" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n"/>
@@ -4190,6 +4387,7 @@
           <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
         </is>
       </c>
+      <c r="I125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="8" t="n"/>
@@ -4218,6 +4416,7 @@
           <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
         </is>
       </c>
+      <c r="I126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="n"/>
@@ -4246,6 +4445,7 @@
           <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
         </is>
       </c>
+      <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n"/>
@@ -4278,6 +4478,7 @@
           <t>이름 + 순번 + 선정 요건(고객 안 열린 자리) ↔ 「고객을 먼저 열어달라」 · 브리핑과 다른 순서</t>
         </is>
       </c>
+      <c r="I128" s="17" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="22" t="n"/>
@@ -4306,6 +4507,7 @@
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
+      <c r="I129" s="17" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4342,6 +4544,7 @@
           <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
         </is>
       </c>
+      <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n"/>
@@ -4370,6 +4573,11 @@
           <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
         </is>
       </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="n"/>
@@ -4398,6 +4606,7 @@
           <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
         </is>
       </c>
+      <c r="I132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n"/>
@@ -4426,6 +4635,7 @@
           <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
         </is>
       </c>
+      <c r="I133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="8" t="n"/>
@@ -4454,6 +4664,11 @@
           <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
         </is>
       </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 만기 언제고 금액은 얼마야?</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n"/>
@@ -4482,6 +4697,11 @@
           <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
         </is>
       </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="n"/>
@@ -4510,6 +4730,11 @@
           <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
         </is>
       </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>실물이전 어떻게 처리해?</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n"/>
@@ -4538,6 +4763,11 @@
           <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
         </is>
       </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>실물이전 어떻게 처리해?</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="n"/>
@@ -4566,6 +4796,11 @@
           <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
         </is>
       </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n"/>
@@ -4594,6 +4829,11 @@
           <t>직원이 말한 값은 되받아 적을 수 있다 ↔ 이전 턴 수치를 인용하면 폐기된다(**미해결**)</t>
         </is>
       </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n"/>
@@ -4622,6 +4862,7 @@
           <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
         </is>
       </c>
+      <c r="I140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n"/>
@@ -4650,6 +4891,11 @@
           <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
         </is>
       </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n"/>
@@ -4682,6 +4928,7 @@
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
+      <c r="I142" s="17" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n"/>
@@ -4710,6 +4957,7 @@
           <t>고객이 한 말 → 화법 도구 ↔ 고객 상태 도구로 가서 관련 없는 카드 한 장(**미해결**)</t>
         </is>
       </c>
+      <c r="I143" s="17" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n"/>
@@ -4738,6 +4986,7 @@
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
+      <c r="I144" s="17" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n"/>
@@ -4766,6 +5015,7 @@
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
+      <c r="I145" s="17" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="8" t="n"/>
@@ -4786,7 +5036,7 @@
       </c>
       <c r="G146" s="17" t="inlineStr">
         <is>
-          <t>콘텐츠 걸린 고객</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H146" s="17" t="inlineStr">
@@ -4794,6 +5044,7 @@
           <t>안내 콘텐츠로 간다 ↔ 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
+      <c r="I146" s="17" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n"/>
@@ -4822,6 +5073,11 @@
           <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
         </is>
       </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n"/>
@@ -4850,6 +5106,7 @@
           <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
+      <c r="I148" s="17" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="n"/>
@@ -4878,6 +5135,7 @@
           <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
+      <c r="I149" s="17" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="8" t="n"/>
@@ -4906,6 +5164,7 @@
           <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
         </is>
       </c>
+      <c r="I150" s="17" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n"/>
@@ -4934,6 +5193,11 @@
           <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n"/>
@@ -4962,6 +5226,7 @@
           <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
+      <c r="I152" s="17" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n"/>
@@ -4990,6 +5255,7 @@
           <t>타겟 목록 ↔ 「고객 화면을 먼저 열어달라」고 답한다</t>
         </is>
       </c>
+      <c r="I153" s="17" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="n"/>
@@ -5022,6 +5288,7 @@
           <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
         </is>
       </c>
+      <c r="I154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="n"/>
@@ -5050,6 +5317,7 @@
           <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
         </is>
       </c>
+      <c r="I155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="8" t="n"/>
@@ -5078,6 +5346,7 @@
           <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
         </is>
       </c>
+      <c r="I156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="n"/>
@@ -5106,6 +5375,7 @@
           <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
+      <c r="I157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="n"/>
@@ -5134,6 +5404,7 @@
           <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
+      <c r="I158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="n"/>
@@ -5162,6 +5433,11 @@
           <t>「확인하지 못했습니다」 + 원인 ↔ 「자료를 찾지 못했습니다」로 나간다(있는 자료를 없다고)</t>
         </is>
       </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="8" t="n"/>
@@ -5190,6 +5466,11 @@
           <t>「확인하지 못했다」 ↔ 「기록이 없습니다」로 답한다</t>
         </is>
       </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="n"/>
@@ -5218,6 +5499,11 @@
           <t>「LLM 연결이 안 됐다」 + 원인 ↔ 「자료가 없습니다」로 답한다</t>
         </is>
       </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="8" t="n"/>
@@ -5246,6 +5532,11 @@
           <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
         </is>
       </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="n"/>
@@ -5274,6 +5565,11 @@
           <t>일부만 인용해도 통과 ↔ 여섯 개를 맞게 인용한 답이 폐기되고 원문 덤프</t>
         </is>
       </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="8" t="n"/>
@@ -5302,6 +5598,11 @@
           <t>기간 표기를 풀어 써도 통과 ↔ 숫자가 맨숫자로 남아 폐기된다</t>
         </is>
       </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n"/>
@@ -5330,6 +5631,11 @@
           <t>표시도 인용 허용 ↔ 「2025.03.31 기준」이 자료 밖 날짜로 폐기된다</t>
         </is>
       </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="8" t="n"/>
@@ -5362,6 +5668,7 @@
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
         </is>
       </c>
+      <c r="I166" s="17" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="n"/>
@@ -5390,6 +5697,7 @@
           <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
+      <c r="I167" s="17" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="n"/>
@@ -5418,6 +5726,7 @@
           <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
         </is>
       </c>
+      <c r="I168" s="17" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="n"/>
@@ -5446,6 +5755,7 @@
           <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
+      <c r="I169" s="17" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="n"/>
@@ -5474,6 +5784,7 @@
           <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
+      <c r="I170" s="17" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="n"/>
@@ -5502,6 +5813,7 @@
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
+      <c r="I171" s="17" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="n"/>
@@ -5530,6 +5842,7 @@
           <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
+      <c r="I172" s="17" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="n"/>
@@ -5558,6 +5871,7 @@
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
+      <c r="I173" s="17" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="8" t="n"/>
@@ -5586,6 +5900,7 @@
           <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
+      <c r="I174" s="17" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="n"/>
@@ -5614,6 +5929,7 @@
           <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
+      <c r="I175" s="17" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="22" t="n"/>
@@ -5634,7 +5950,7 @@
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>콘텐츠 있음 ↔ 없음</t>
+          <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H176" s="17" t="inlineStr">
@@ -5642,6 +5958,7 @@
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
+      <c r="I176" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>성립 요건 **전부** + 왜 문제인지 ↔ 요건 하나만 말하거나 고객군 일반 정의로 샌다</t>
+          <t>〔송도윤·정민석·이수민〕 성립 요건 **전부** + 왜 문제인지 ↔ 요건 하나만 말하거나 고객군 일반 정의로 샌다</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>9/29 기준 요건 0개 — 「타겟이 아니다」 ↔ 요건을 지어내거나 지난 만기를 「곧 만기」로 말한다</t>
+          <t>〔이준호〕 9/29 기준 요건 0개 — 「타겟이 아니다」 ↔ 요건을 지어내거나 지난 만기를 「곧 만기」로 말한다</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>「네, 설정돼 있습니다」 ↔ 「준비된 자료가 없습니다」(문제일 때만 싣는 필터가 넘어옴 — 실제 사고)</t>
+          <t>〔설정된 8명〕 「네, 설정돼 있습니다」 ↔ 「준비된 자료가 없습니다」(문제일 때만 싣는 필터가 넘어옴 — 실제 사고)</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>「미설정」 + 왜 요건인지 ↔ 설정돼 있다고 답한다</t>
+          <t>〔미설정 4명〕 「미설정」 + 왜 요건인지 ↔ 설정돼 있다고 답한다</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>요건 충족 + 무엇이 충족됐는지 ↔ 미충족으로 답한다</t>
+          <t>〔오세훈 · 박정호〕 요건 충족 + 무엇이 충족됐는지 ↔ 미충족으로 답한다</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>무엇이 모자란지까지 ↔ 「자료 없음」으로 끝난다</t>
+          <t>〔미충족 10명〕 무엇이 모자란지까지 ↔ 「자료 없음」으로 끝난다</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>날짜 + 요지 + **시효 표시** ↔ 30초 전 자기 답변이 「지난 상담」으로 나온다</t>
+          <t>〔기록 있는 9명〕 날짜 + 요지 + **시효 표시** ↔ 30초 전 자기 답변이 「지난 상담」으로 나온다</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>「기록이 없다」 한 줄 ↔ 계획이 세 바퀴 돌고 무관한 화법 카드가 근거로 선다</t>
+          <t>〔기록 없는 3명〕 「기록이 없다」 한 줄 ↔ 계획이 세 바퀴 돌고 무관한 화법 카드가 근거로 선다</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
+          <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
+          <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말한다</t>
+          <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>이름 + 순번 + 선정 요건(고객 안 열린 자리) ↔ 「고객을 먼저 열어달라」 · 브리핑과 다른 순서</t>
+          <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr"/>
@@ -4938,23 +4938,23 @@
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
+          <t>국고채 금리 어때?</t>
         </is>
       </c>
       <c r="E143" s="17" t="inlineStr"/>
-      <c r="F143" s="20" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G143" s="17" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H143" s="17" t="inlineStr">
         <is>
-          <t>고객이 한 말 → 화법 도구 ↔ 고객 상태 도구로 가서 관련 없는 카드 한 장(**미해결**)</t>
+          <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
       <c r="I143" s="17" t="inlineStr"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>국고채 금리 어때?</t>
+          <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
       <c r="E144" s="17" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H144" s="17" t="inlineStr">
         <is>
-          <t>시황만 ↔ 추천펀드가 따라 나온다</t>
+          <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
       <c r="I144" s="17" t="inlineStr"/>
@@ -4996,26 +4996,30 @@
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>8월 추천펀드 뭐야?</t>
+          <t>대화 내용 요약해줘</t>
         </is>
       </c>
       <c r="E145" s="17" t="inlineStr"/>
-      <c r="F145" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F145" s="20" t="inlineStr">
+        <is>
+          <t>○ 예비 · 시연본 리허설</t>
         </is>
       </c>
       <c r="G145" s="17" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H145" s="17" t="inlineStr">
         <is>
-          <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
-        </is>
-      </c>
-      <c r="I145" s="17" t="inlineStr"/>
+          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
+        </is>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="n"/>
@@ -5025,23 +5029,23 @@
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>이 고객한테 안내할 만한 세미나 있어?</t>
+          <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
       <c r="E146" s="17" t="inlineStr"/>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 대본 리허설</t>
         </is>
       </c>
       <c r="G146" s="17" t="inlineStr">
         <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H146" s="17" t="inlineStr">
         <is>
-          <t>안내 콘텐츠로 간다 ↔ 상품 자료로 가서 재료 0건</t>
+          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
       <c r="I146" s="17" t="inlineStr"/>
@@ -5054,30 +5058,26 @@
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>대화 내용 요약해줘</t>
+          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
       <c r="E147" s="17" t="inlineStr"/>
-      <c r="F147" s="20" t="inlineStr">
-        <is>
-          <t>○ 예비 · 시연본 리허설</t>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G147" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H147" s="17" t="inlineStr">
         <is>
-          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
-        </is>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
+          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
+        </is>
+      </c>
+      <c r="I147" s="17" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n"/>
@@ -5087,23 +5087,23 @@
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>지난번엔 무슨 얘기 했지?</t>
+          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
       <c r="E148" s="17" t="inlineStr"/>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>○ 예비 · 대본 리허설</t>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H148" s="17" t="inlineStr">
         <is>
-          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
+          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
         </is>
       </c>
       <c r="I148" s="17" t="inlineStr"/>
@@ -5116,176 +5116,176 @@
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
+          <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
       <c r="E149" s="17" t="inlineStr"/>
-      <c r="F149" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F149" s="20" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H149" s="17" t="inlineStr">
         <is>
-          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
-        </is>
-      </c>
-      <c r="I149" s="17" t="inlineStr"/>
+          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="n"/>
-      <c r="B150" s="9" t="n"/>
+      <c r="B150" s="12" t="n"/>
       <c r="C150" s="15" t="n">
         <v>149</v>
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
+          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
         </is>
       </c>
       <c r="E150" s="17" t="inlineStr"/>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H150" s="17" t="inlineStr">
         <is>
-          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
+          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
       <c r="I150" s="17" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n"/>
-      <c r="B151" s="9" t="n"/>
-      <c r="C151" s="15" t="n">
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>25. 실패·경계 처리</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>좀 더 짧게 줄여줘</t>
-        </is>
-      </c>
-      <c r="E151" s="17" t="inlineStr"/>
-      <c r="F151" s="20" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G151" s="17" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H151" s="17" t="inlineStr">
-        <is>
-          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
-        </is>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr"/>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n"/>
       <c r="B152" s="9" t="n"/>
-      <c r="C152" s="15" t="n">
+      <c r="C152" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
-        </is>
-      </c>
-      <c r="E152" s="17" t="inlineStr"/>
-      <c r="F152" s="20" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G152" s="17" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H152" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
-        </is>
-      </c>
-      <c r="I152" s="17" t="inlineStr"/>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>이 고객 평가금액 얼마야?</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr"/>
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n"/>
-      <c r="B153" s="12" t="n"/>
-      <c r="C153" s="15" t="n">
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="D153" s="16" t="inlineStr">
-        <is>
-          <t>오늘 누구부터 봐야 해?</t>
-        </is>
-      </c>
-      <c r="E153" s="17" t="inlineStr"/>
-      <c r="F153" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G153" s="17" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>IRP 중도인출 사유가 뭐야?</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr"/>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H153" s="17" t="inlineStr">
-        <is>
-          <t>타겟 목록 ↔ 「고객 화면을 먼저 열어달라」고 답한다</t>
-        </is>
-      </c>
-      <c r="I153" s="17" t="inlineStr"/>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="n"/>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>25. 실패·경계 처리</t>
-        </is>
-      </c>
+      <c r="B154" s="9" t="n"/>
       <c r="C154" s="4" t="n">
         <v>153</v>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
+          <t>이 고객은 왜 타겟이 됐지?</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="10" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
+          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
       <c r="I154" s="6" t="inlineStr"/>
@@ -5298,23 +5298,23 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>이 고객 평가금액 얼마야?</t>
+          <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr"/>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
+          <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
       <c r="I155" s="6" t="inlineStr"/>
@@ -5327,26 +5327,30 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>IRP 중도인출 사유가 뭐야?</t>
+          <t>(도구가 죽는 상황)</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="11" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F156" s="13" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>장애</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
-        </is>
-      </c>
-      <c r="I156" s="6" t="inlineStr"/>
+          <t>「확인하지 못했습니다」 + 원인 ↔ 「자료를 찾지 못했습니다」로 나간다(있는 자료를 없다고)</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="n"/>
@@ -5356,26 +5360,30 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>이 고객은 왜 타겟이 됐지?</t>
+          <t>(상담기록 저장소를 못 읽는 상황)</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr"/>
-      <c r="F157" s="11" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F157" s="13" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>장애</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
-        </is>
-      </c>
-      <c r="I157" s="6" t="inlineStr"/>
+          <t>「확인하지 못했다」 ↔ 「기록이 없습니다」로 답한다</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="8" t="n"/>
@@ -5385,7 +5393,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>이 고객 전반적으로 다 정리해서 알려줘</t>
+          <t>(LLM 미연결 상황)</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr"/>
@@ -5396,15 +5404,19 @@
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>장애</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
-        </is>
-      </c>
-      <c r="I158" s="6" t="inlineStr"/>
+          <t>「LLM 연결이 안 됐다」 + 원인 ↔ 「자료가 없습니다」로 답한다</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>[장애 상황 — 손으로 재현한다]</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="n"/>
@@ -5414,7 +5426,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>(도구가 죽는 상황)</t>
+          <t>(고객 연 직후 첫 질문)</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr"/>
@@ -5425,17 +5437,17 @@
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>장애</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>「확인하지 못했습니다」 + 원인 ↔ 「자료를 찾지 못했습니다」로 나간다(있는 자료를 없다고)</t>
+          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
@@ -5447,28 +5459,28 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>(상담기록 저장소를 못 읽는 상황)</t>
+          <t>(화면번호 여러 개가 나오는 절차 질문)</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="13" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>장애</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>「확인하지 못했다」 ↔ 「기록이 없습니다」로 답한다</t>
+          <t>일부만 인용해도 통과 ↔ 여섯 개를 맞게 인용한 답이 폐기되고 원문 덤프</t>
         </is>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
@@ -5480,56 +5492,56 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>(LLM 미연결 상황)</t>
+          <t>(기준시점이 기간으로 적힌 카드를 쓰는 질문)</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="13" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+      <c r="F161" s="23" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>장애</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>「LLM 연결이 안 됐다」 + 원인 ↔ 「자료가 없습니다」로 답한다</t>
+          <t>기간 표기를 풀어 써도 통과 ↔ 숫자가 맨숫자로 남아 폐기된다</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="8" t="n"/>
-      <c r="B162" s="9" t="n"/>
+      <c r="B162" s="12" t="n"/>
       <c r="C162" s="4" t="n">
         <v>161</v>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>(고객 연 직후 첫 질문)</t>
+          <t>(기준시점이 표시에만 있는 카드를 쓰는 질문)</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="13" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+      <c r="F162" s="23" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 대본 리허설</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
+          <t>표시도 인용 허용 ↔ 「2025.03.31 기준」이 자료 밖 날짜로 폐기된다</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
@@ -5540,132 +5552,120 @@
     </row>
     <row r="163">
       <c r="A163" s="8" t="n"/>
-      <c r="B163" s="9" t="n"/>
-      <c r="C163" s="4" t="n">
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>26. 고객별 대조</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="n">
         <v>162</v>
       </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>(화면번호 여러 개가 나오는 절차 질문)</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr"/>
-      <c r="F163" s="23" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>일부만 인용해도 통과 ↔ 여섯 개를 맞게 인용한 답이 폐기되고 원문 덤프</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 권할 수 있어?</t>
+        </is>
+      </c>
+      <c r="E163" s="17" t="inlineStr"/>
+      <c r="F163" s="19" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G163" s="17" t="inlineStr">
+        <is>
+          <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
+        </is>
+      </c>
+      <c r="H163" s="17" t="inlineStr">
+        <is>
+          <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
+        </is>
+      </c>
+      <c r="I163" s="17" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="n"/>
       <c r="B164" s="9" t="n"/>
-      <c r="C164" s="4" t="n">
+      <c r="C164" s="15" t="n">
         <v>163</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
-        <is>
-          <t>(기준시점이 기간으로 적힌 카드를 쓰는 질문)</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr"/>
-      <c r="F164" s="23" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>기간 표기를 풀어 써도 통과 ↔ 숫자가 맨숫자로 남아 폐기된다</t>
-        </is>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>이 고객 디폴트옵션 설정돼 있어?</t>
+        </is>
+      </c>
+      <c r="E164" s="17" t="inlineStr"/>
+      <c r="F164" s="21" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G164" s="17" t="inlineStr">
+        <is>
+          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H164" s="17" t="inlineStr">
+        <is>
+          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
+        </is>
+      </c>
+      <c r="I164" s="17" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n"/>
-      <c r="B165" s="12" t="n"/>
-      <c r="C165" s="4" t="n">
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="15" t="n">
         <v>164</v>
       </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>(기준시점이 표시에만 있는 카드를 쓰는 질문)</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr"/>
-      <c r="F165" s="23" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 대본 리허설</t>
-        </is>
-      </c>
-      <c r="G165" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>표시도 인용 허용 ↔ 「2025.03.31 기준」이 자료 밖 날짜로 폐기된다</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t>이 고객 만기 뭐뭐 있어?</t>
+        </is>
+      </c>
+      <c r="E165" s="17" t="inlineStr"/>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G165" s="17" t="inlineStr">
+        <is>
+          <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H165" s="17" t="inlineStr">
+        <is>
+          <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
+        </is>
+      </c>
+      <c r="I165" s="17" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="n"/>
-      <c r="B166" s="14" t="inlineStr">
-        <is>
-          <t>26. 고객별 대조</t>
-        </is>
-      </c>
+      <c r="B166" s="9" t="n"/>
       <c r="C166" s="15" t="n">
         <v>165</v>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>이 고객한테 뭘 권할 수 있어?</t>
+          <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
       <c r="E166" s="17" t="inlineStr"/>
-      <c r="F166" s="19" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G166" s="17" t="inlineStr">
         <is>
-          <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
+          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
       <c r="H166" s="17" t="inlineStr">
         <is>
-          <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
+          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
       <c r="I166" s="17" t="inlineStr"/>
@@ -5678,23 +5678,23 @@
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>이 고객 디폴트옵션 설정돼 있어?</t>
+          <t>지난 상담에서 무슨 얘기 했지?</t>
         </is>
       </c>
       <c r="E167" s="17" t="inlineStr"/>
-      <c r="F167" s="21" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G167" s="17" t="inlineStr">
         <is>
-          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
+          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
       <c r="H167" s="17" t="inlineStr">
         <is>
-          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
+          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
       <c r="I167" s="17" t="inlineStr"/>
@@ -5707,23 +5707,23 @@
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>이 고객 만기 뭐뭐 있어?</t>
+          <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
       <c r="E168" s="17" t="inlineStr"/>
-      <c r="F168" s="21" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+          <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
       <c r="H168" s="17" t="inlineStr">
         <is>
-          <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
+          <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
       <c r="I168" s="17" t="inlineStr"/>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>이 고객 왜 관리 대상이야?</t>
+          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
         </is>
       </c>
       <c r="E169" s="17" t="inlineStr"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="G169" s="17" t="inlineStr">
         <is>
-          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
+          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H169" s="17" t="inlineStr">
         <is>
-          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
+          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
       <c r="I169" s="17" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>지난 상담에서 무슨 얘기 했지?</t>
+          <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
       <c r="E170" s="17" t="inlineStr"/>
@@ -5776,12 +5776,12 @@
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
+          <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H170" s="17" t="inlineStr">
         <is>
-          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
+          <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
       <c r="I170" s="17" t="inlineStr"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
-          <t>300만원 더 넣으면 얼마 돌려받아?</t>
+          <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
       <c r="E171" s="17" t="inlineStr"/>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="G171" s="17" t="inlineStr">
         <is>
-          <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H171" s="17" t="inlineStr">
         <is>
-          <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
+          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
       <c r="I171" s="17" t="inlineStr"/>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D172" s="16" t="inlineStr">
         <is>
-          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
+          <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
       <c r="E172" s="17" t="inlineStr"/>
@@ -5834,25 +5834,25 @@
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
+          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H172" s="17" t="inlineStr">
         <is>
-          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
+          <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
       <c r="I172" s="17" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="8" t="n"/>
-      <c r="B173" s="9" t="n"/>
+      <c r="A173" s="22" t="n"/>
+      <c r="B173" s="12" t="n"/>
       <c r="C173" s="15" t="n">
         <v>172</v>
       </c>
       <c r="D173" s="16" t="inlineStr">
         <is>
-          <t>이 고객 연금개시 할 수 있어?</t>
+          <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
       <c r="E173" s="17" t="inlineStr"/>
@@ -5863,117 +5863,27 @@
       </c>
       <c r="G173" s="17" t="inlineStr">
         <is>
-          <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
+          <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H173" s="17" t="inlineStr">
         <is>
-          <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
+          <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
       <c r="I173" s="17" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="n"/>
-      <c r="B174" s="9" t="n"/>
-      <c r="C174" s="15" t="n">
-        <v>173</v>
-      </c>
-      <c r="D174" s="16" t="inlineStr">
-        <is>
-          <t>판매중단된 펀드 뭐 들고 있어?</t>
-        </is>
-      </c>
-      <c r="E174" s="17" t="inlineStr"/>
-      <c r="F174" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G174" s="17" t="inlineStr">
-        <is>
-          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
-        </is>
-      </c>
-      <c r="H174" s="17" t="inlineStr">
-        <is>
-          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I174" s="17" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="n"/>
-      <c r="B175" s="9" t="n"/>
-      <c r="C175" s="15" t="n">
-        <v>174</v>
-      </c>
-      <c r="D175" s="16" t="inlineStr">
-        <is>
-          <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
-        </is>
-      </c>
-      <c r="E175" s="17" t="inlineStr"/>
-      <c r="F175" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G175" s="17" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
-        </is>
-      </c>
-      <c r="H175" s="17" t="inlineStr">
-        <is>
-          <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
-        </is>
-      </c>
-      <c r="I175" s="17" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="22" t="n"/>
-      <c r="B176" s="12" t="n"/>
-      <c r="C176" s="15" t="n">
-        <v>175</v>
-      </c>
-      <c r="D176" s="16" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 세미나 있어?</t>
-        </is>
-      </c>
-      <c r="E176" s="17" t="inlineStr"/>
-      <c r="F176" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G176" s="17" t="inlineStr">
-        <is>
-          <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
-        </is>
-      </c>
-      <c r="H176" s="17" t="inlineStr">
-        <is>
-          <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
-        </is>
-      </c>
-      <c r="I176" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="B45:B52"/>
-    <mergeCell ref="B142:B153"/>
     <mergeCell ref="A45:A79"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B106:B111"/>
-    <mergeCell ref="B154:B165"/>
-    <mergeCell ref="B166:B176"/>
     <mergeCell ref="B53:B61"/>
     <mergeCell ref="B67:B70"/>
-    <mergeCell ref="A130:A176"/>
     <mergeCell ref="B34:B44"/>
+    <mergeCell ref="B142:B150"/>
     <mergeCell ref="A80:A105"/>
     <mergeCell ref="B125:B127"/>
     <mergeCell ref="B130:B141"/>
@@ -5985,7 +5895,10 @@
     <mergeCell ref="B90:B94"/>
     <mergeCell ref="B119:B124"/>
     <mergeCell ref="B71:B73"/>
+    <mergeCell ref="B151:B162"/>
+    <mergeCell ref="A130:A173"/>
     <mergeCell ref="B116:B118"/>
+    <mergeCell ref="B163:B173"/>
     <mergeCell ref="B101:B105"/>
     <mergeCell ref="B74:B79"/>
     <mergeCell ref="B18:B26"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,7 +150,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,13 +160,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -189,6 +192,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -668,13 +674,9 @@
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -697,13 +699,13 @@
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>위험자산 한도 초과라는데 뭐가 문제고 뭘 해야 하는 거야?</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -722,17 +724,17 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
-      <c r="B5" s="12" t="n"/>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>이 고객 성향이랑 실제 운용이 안 맞는다는 게 무슨 말이야?</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -751,355 +753,355 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>물어본 값 하나 ↔ 화법·문제상황이 따라 나온다</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr"/>
+      <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>고유계정대 얼마야? 금액이랑 비중 둘 다 알려줘</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>김현수 173544-2074623·송도윤 188406-7352194 등</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>600만원 · 75% 둘 다 ↔ 「비중만 있고 금액은 없다」 · 반올림값과 원장값이 두 값이 된다</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>만기 2건 3명 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>예금·GIC **전부** ↔ 가장 가까운 한 건만 답해 나머지가 없는 것이 된다</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 언제야?</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>만기 0건 2명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>만기 자산 없음 ↔ ISA 만기를 IRP 만기로 답한다</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 언제고 금액은 얼마야?</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>날짜와 금액을 재료 그대로 ↔ 잔여일수로 날짜를 계산해 지어낸다(수치 검사에 안 걸린다)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>이 고객 ISA 만기가 언제고 얼마짜리야?</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>ISA 는 **IRP 밖의 돈**이라 갈라 적는다 ↔ IRP 잔액에 합산해 부풀린다</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>올해 얼마 넣었고 잔여한도는 얼마 남았어?</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>당해 납입액 + 잔여한도 ↔ 화법 카드의 숫자(300)를 잔여한도로 붙인다</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr"/>
+      <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>판매중단된 펀드 뭐 들고 있고 지금 손실이 얼마나 나 있어?</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>종목 + **고객 보유수익률** ↔ 상품의 1년 수익률을 고객 손익으로 말한다</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr"/>
+      <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>최근 한 달 사이에 고유계정대가 얼마나 늘었어?</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>+1.7억 ↔ 「활동 기록이 없다」로 끝난다</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>이 고객 퇴직급여랑 개인부담금이 각각 얼마야?</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>둘을 갈라 답한다 ↔ 「원장에 없다」고 답한다(실은 있는 값)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>같은 또래 평균이랑 비교하면 이 고객은 어떤 편이야?</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr"/>
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>peer 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>peer 값 ↔ peer 없는 3명에게 지어낸 평균을 말한다</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="15" t="n">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>운용변경 안 한 지 얼마나 됐어?</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr"/>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>경과 개월 + 왜 요건인지 ↔ 값이 없다고 답한다</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr"/>
+      <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -1117,7 +1119,7 @@
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -1140,13 +1142,9 @@
       <c r="C19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>이 고객 디폴트옵션 설정돼 있어?</t>
-        </is>
-      </c>
+      <c r="D19" s="10" t="n"/>
       <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -1169,13 +1167,13 @@
       <c r="C20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>이 고객 세액공제 잔여한도 얼마 남았어?</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -1198,7 +1196,7 @@
       <c r="C21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>이 고객 세액공제 더 받을 수 있어?</t>
         </is>
@@ -1233,7 +1231,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -1256,13 +1254,9 @@
       <c r="C23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>이 고객 연금개시 할 수 있는 상태야?</t>
-        </is>
-      </c>
+      <c r="D23" s="10" t="n"/>
       <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -1285,13 +1279,13 @@
       <c r="C24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>이 고객 ISA 만기자금 갖고 있어?</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -1314,13 +1308,13 @@
       <c r="C25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>이 고객 판매중단 상품 들고 있는 거 있어?</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -1339,17 +1333,17 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
-      <c r="B26" s="12" t="n"/>
+      <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>이 고객 계좌 가입일이 언제고 몇 년 됐어?</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -1368,123 +1362,119 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>지난 상담에서 무슨 얘기 했는지 알려줘</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>〔기록 있는 9명〕 날짜 + 요지 + **시효 표시** ↔ 30초 전 자기 답변이 「지난 상담」으로 나온다</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr"/>
+      <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
       <c r="B28" s="9" t="n"/>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>지난 상담에서 무슨 얘기 했는지 알려줘</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr"/>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="18" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>기록 없는 3명 — 김현수 173544-2074623 · 김서연 171203-4815062 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>〔기록 없는 3명〕 「기록이 없다」 한 줄 ↔ 계획이 세 바퀴 돌고 무관한 화법 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr"/>
+      <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>지난 상담 내용 참고해서 오늘 뭐라고 말하면 좋을지 알려줘</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr"/>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>지난 기록 → 오늘 제안으로 잇는다 ↔ 지난 안내 수치를 지금 값으로 단정한다</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr"/>
+      <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="15" t="n">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>그때 안내한 금리가 지금도 맞는 거야?</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr"/>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr"/>
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>기록에 시효 표시, 최신값은 따로 부른다 ↔ 지난 금리를 지금 값으로 답한다</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr"/>
+      <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1496,13 +1486,13 @@
       <c r="C31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>이 고객 상담 들어가기 전에 뭘 준비해두면 좋을까?</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -1525,13 +1515,13 @@
       <c r="C32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>이 고객 상태에 걸린 참고자료 뭐뭐 있어?</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -1550,17 +1540,17 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
-      <c r="B33" s="12" t="n"/>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>(화법 제안 뒤) 네, 보여줘</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
@@ -1583,210 +1573,210 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
         </is>
       </c>
-      <c r="C34" s="15" t="n">
+      <c r="C34" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 하면 안 되는 게 뭐야?</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr"/>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본 리허설</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>가드 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>지식베이스 근거의 금지 + **대안 화법** ↔ 금지만 주고 대안이 없다 · 가드가 안 붙는다</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr"/>
+      <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>이 고객 세액공제 더 받게 추가납입 권해도 돼?</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr"/>
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>권유하지 않는다(개시 계좌) ↔ 추가납입을 권한다</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr"/>
+      <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="15" t="n">
+      <c r="C36" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>이 고객 연금개시 요건도 충족했던데, 개시까지 같이 진행하면 걸리는 거 없어?</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr"/>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>환급 완료 전 제한을 **먼저** 세운다 ↔ 화법 축으로만 가서 순서 경고를 못 한다</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr"/>
+      <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
-      <c r="C37" s="15" t="n">
+      <c r="C37" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 어떤 펀드 넣어주면 되는지 딱 집어줘</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr"/>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr"/>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>「이런 상품이 있습니다」 톤까지 ↔ 「추천드립니다」·「가입시키세요」를 쓴다</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr"/>
+      <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
       <c r="B38" s="9" t="n"/>
-      <c r="C38" s="15" t="n">
+      <c r="C38" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>이 고객 재취업할 것 같아?</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr"/>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr"/>
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>확인이 필요하다고 답한다 ↔ 「아마 될 것 같다」로 추정한다</t>
         </is>
       </c>
-      <c r="I38" s="17" t="inlineStr"/>
+      <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
-      <c r="C39" s="15" t="n">
+      <c r="C39" s="16" t="n">
         <v>38</v>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>이 고객 디폴트옵션 등록됐어?</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr"/>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr"/>
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>한 줄 답에 근거 한 건 ↔ 답에 안 쓴 ⑥⑦⑧ 카드까지 근거가 여섯 건 선다</t>
         </is>
       </c>
-      <c r="I39" s="17" t="inlineStr"/>
+      <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
       <c r="B40" s="9" t="n"/>
-      <c r="C40" s="15" t="n">
+      <c r="C40" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>(내부용 카드가 걸리는 질문)</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr"/>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr"/>
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>「고객에게 그대로 안내하지 마세요」 + 본문도 대사로 안 옮긴다 ↔ 표시와 본문이 정반대를 말한다</t>
         </is>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
@@ -1795,31 +1785,31 @@
     <row r="41">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
-      <c r="C41" s="15" t="n">
+      <c r="C41" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>(현장 노하우 카드가 걸리는 질문)</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr"/>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr"/>
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>출처가 정한 신뢰 등급 그대로 ↔ 현장 노하우가 본부 지침으로 읽힌다</t>
         </is>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
@@ -1828,93 +1818,93 @@
     <row r="42">
       <c r="A42" s="8" t="n"/>
       <c r="B42" s="9" t="n"/>
-      <c r="C42" s="15" t="n">
+      <c r="C42" s="16" t="n">
         <v>41</v>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>(더미 자산 문구로) 이 문구 발송 화면에 넣어줘</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr"/>
-      <c r="F42" s="18" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr"/>
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
         </is>
       </c>
-      <c r="I42" s="17" t="inlineStr"/>
+      <c r="I42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
-      <c r="C43" s="15" t="n">
+      <c r="C43" s="16" t="n">
         <v>42</v>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>(가드 재료가 있는 요건 고객에게 아무 상담 질문)</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr"/>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="E43" s="18" t="inlineStr"/>
+      <c r="F43" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205·송도윤 188406-7352194·윤가영 162754-9483106 등</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>요건에 걸린 주의가 출처에 선다 ↔ 요건은 성립하는데 가드가 안 붙는다</t>
         </is>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="15" t="n">
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>(가드 재료가 없는 요건 고객에게 아무 상담 질문)</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr"/>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375·김서연 171203-4815062 등</t>
         </is>
       </c>
-      <c r="H44" s="17" t="inlineStr">
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>**아무것도 띄우지 않는다** ↔ 없는 금지를 지어낸다</t>
         </is>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
@@ -1934,12 +1924,22 @@
       <c r="C45" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>IRP 세액공제 한도가 얼마야?</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>IRP를 포함한 세액공제 한도는 연간 납입액 최대 900만원이에요. 2026년 6월 기준 자료에 따르면, 연금저축만으로는 한도가 연 600만원이지만 IRP를 포함하면 900만원까지 확대돼요.
+총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 고객님은 16.5%, 초과하는 고객님은 13.2%(지방소득세 포함)의 공제율이 적용돼요. 이에 따라 900만원을 모두 채우면 각각 1,485,000원과 1,188,000원을 환급받을 수 있어요.
+다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못할 수 있다는 점을 유의해서 안내해 주세요.
+── 참고한 자료
+· 본부 공식 자료
+── 이어서 물어보실 수 있어요
+· 고객이 앱에서 직접 할 수 있어?</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -1963,7 +1963,7 @@
       <c r="C46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
         </is>
@@ -1992,13 +1992,13 @@
       <c r="C47" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
         </is>
@@ -2050,13 +2050,9 @@
       <c r="C49" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>수수료 얼마야?</t>
-        </is>
-      </c>
+      <c r="D49" s="10" t="n"/>
       <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
@@ -2079,7 +2075,7 @@
       <c r="C50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>타행 IRP 수수료는 우리보다 싼가?</t>
         </is>
@@ -2108,13 +2104,19 @@
       <c r="C51" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>퇴직금을 통장으로 받은 걸 IRP에 다시 넣으면 세액공제도 받을 수 있어?</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>고객의 총급여 수준이 어떻게 되나요?
+· 5,500만원 이하
+· 5,500만원 초과</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -2133,17 +2135,17 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
-      <c r="B52" s="12" t="n"/>
+      <c r="B52" s="10" t="n"/>
       <c r="C52" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -2162,181 +2164,228 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
         </is>
       </c>
-      <c r="C53" s="15" t="n">
+      <c r="C53" s="16" t="n">
         <v>52</v>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr"/>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>총급여 구간을 선택해 주세요.
+· 5,500만원 이하
+· 5,500만원 초과</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="H53" s="17" t="inlineStr">
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 정해진 걸 「가정하면」으로 적는다</t>
         </is>
       </c>
-      <c r="I53" s="17" t="inlineStr"/>
+      <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
       <c r="B54" s="9" t="n"/>
-      <c r="C54" s="15" t="n">
+      <c r="C54" s="16" t="n">
         <v>53</v>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr"/>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>총급여 구간이 어떻게 되나요?
+· 5,500만원 이하
+· 5,500만원 초과</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="G54" s="18" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="H54" s="17" t="inlineStr">
+      <c r="H54" s="18" t="inlineStr">
         <is>
           <t>원장의 잔여한도를 쓴다 ↔ IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
         </is>
       </c>
-      <c r="I54" s="17" t="inlineStr"/>
+      <c r="I54" s="18" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
-      <c r="C55" s="15" t="n">
+      <c r="C55" s="16" t="n">
         <v>54</v>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr"/>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객이 개인형IRP 계좌에 현금을 추가로 300만원 더 납입하는 경우라면, 세액공제 잔여한도가 0원이라 추가 공제 대상이 없어 올해 세액공제로 돌아오는 환급액은 늘어나지 않아요. 세액공제 한도 900만원은 연금저축 납입분까지 합산하여 이미 채워져 있기 때문이에요. 다만 연 납입한도 1,800만원까지는 납입 자체를 할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H55" s="17" t="inlineStr">
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
         </is>
       </c>
-      <c r="I55" s="17" t="inlineStr"/>
+      <c r="I55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
       <c r="B56" s="9" t="n"/>
-      <c r="C56" s="15" t="n">
+      <c r="C56" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr"/>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>● ISA
+총급여 구간이 어떻게 되나요?
+· 5,500만원 이하
+· 5,500만원 초과
+● ISA
+지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
+응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 15, model: ge…)
+● ISA
+송도윤 고객이 ISA 만기자금 중 일부인 8,000만원을 개인형IRP 계좌로 전환할 때는 늘어나는 추가 공제 대상과 총급여 구간에 따른 환급액을 바탕으로 안내하는 게 핵심이에요. 현재 이 고객의 개인형IRP 계좌 세액공제 잔여한도가 0원이므로 현금을 그냥 더 납입하는 경우에는 추가 공제 대상이 없지만, ISA 만기자금을 전환하면 전환액의 10%가 세액공제 대상에 더해져서 공제 한도가 900만원에서 최대 1,200만원으로 늘어나요. ISA 만기자금 8,000만원을 전환할 때 추가 공제 대상은 300만원 한도에 닿아 300만원이 되며, 총급여 5,500만원 이하인 경우 16.5% 공제율을 적용하면 495,000원의 환급이 늘어나고, 총급여 5,500만원 초과인 경우 13.2% 공제율을 적용하면 396,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안의 선택지처럼 견주지 않도록 유의하세요.</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H56" s="17" t="inlineStr">
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
         </is>
       </c>
-      <c r="I56" s="17" t="inlineStr"/>
+      <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
-      <c r="C57" s="15" t="n">
+      <c r="C57" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr"/>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>● ISA
+ISA 만기자금 8천만원을 개인형IRP 계좌로 전환할 때의 세액공제 환급액은 총급여 구간에 따라 다르게 안내해야 해요. 이 고객의 총급여 구간은 원장에 없으므로 단말에서 먼저 확인해야 하며, 5,500만원 이하인 경우 전환액 8천만원에 대해 추가 공제 대상 300만원이 적용되어 495,000원의 환급액이 늘어나고, 총급여 5,500만원 초과인 경우 추가 공제 대상 300만원이 적용되어 396,000원의 환급액이 늘어나요. ISA 만기자금 전환은 기존 현금 납입과 별개로 공제 대상 한도 자체가 늘어나는 몫이므로 둘을 같은 한도 안에서 저울질하지 않으며, 만기일로부터 60일 이내에 전환해야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● ISA
+ISA 만기자금 전환 시 세액공제 혜택 안내는 고객의 총급여 구간에 따라 다르게 적용되므로, 단말에서 총급여 구간을 먼저 확인한 뒤 해당 금액으로 안내해 드려야 해요. 이 고객의 개인형IRP 계좌로 8,000만원을 전환하는 경우 ISA 만기자금 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 늘어나요. 총급여 5,500만원 이하 구간(16.5%)이 확인되면 전환액 8,000만원에 대해 추가 공제 대상 300만원으로 늘어나는 환급액 495,000원을 안내하고, 총급여 5,500만원 초과 구간(13.2%)이 확인되면 늘어나는 환급액 396,000원을 안내해 주세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요.
+● ISA
+ISA 만기자금 8천만원을 개인형IRP 계좌로 전환하면 공제 대상 한도가 늘어나 추가 환급을 받을 수 있어요. 이 고객의 개인형IRP 계좌 추가 납입액 8,000만원을 ISA 만기자금으로 전환하는 경우, 전환액의 10%인 300만원이 추가 공제 대상 상한에 닿아 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어나요. 총급여가 5,500만원 이하(16.5%)라면 늘어나는 환급은 495,000원이고, 5,500만원 초과(13.2%)라면 396,000원이 돼요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않아야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 바탕으로 설명해 주세요.</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H57" s="17" t="inlineStr">
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
-      <c r="I57" s="17" t="inlineStr"/>
+      <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
       <c r="B58" s="9" t="n"/>
-      <c r="C58" s="15" t="n">
+      <c r="C58" s="16" t="n">
         <v>57</v>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr"/>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>● ISA
+총급여 5,500만원 초과 구간의 고객에게는 ISA 만기자금을 개인형IRP 계좌로 전환할 때의 추가 공제와 환급 예상액을 안내하는 게 핵심이에요. 앞서 말씀드린 현금 추가 납입의 경우와 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 방식이며, 8,000만원을 전부 전환하는 경우 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 초과 기준 396,000원의 환급이 늘어나요. 다만 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● ISA
+총급여 5,500만원 초과 구간에서는 개인형IRP 계좌 추가 납입과 ISA 만기자금 전환 각각의 경우에 따라 환급 예상액이 다르게 산출된다. 현금을 더 납입하는 경우 당해 납입액 600만원에 세액공제 한도 900만원, 잔여한도 300만원인 상태에서 추가 납입액 8,000만원을 넣으면 공제 대상이 600만원에서 900만원으로 늘어나고, 13.2% 공제율을 적용하여 환급 예상 792,000원에서 1,188,000원으로 늘어나며 늘어나는 금액은 396,000원이다. ISA 만기자금을 전환하는 경우 8,000만원을 타행에서 전환하면 전환액의 10%가 상한 300만원까지 세액공제 대상에 더해져 추가 공제 대상이 300만원이 되고, 13.2% 공제율을 적용하여 이 전환으로 늘어나는 환급은 396,000원이다. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이다.
+● ISA
+총급여가 5,500만원을 초과하는 고객에게는 ISA 만기자금 1억 2,000만원을 개인형IRP 계좌로 전환할 때 추가 공제 대상 300만원에 적용 공제율 13.2%를 곱해 환급액 396,000원이 늘어난다는 점을 안내하는 게 핵심이에요. 앞서 말씀드린 대로 이 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요. 전환액 1억 2,000만원 중 일부만 옮기는 경우라면 전환액의 10%가 세액공제 대상에 더해진다는 점을 감안해 주셔야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않도록 유의해 주세요.</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H58" s="17" t="inlineStr">
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>원래 질문(300만원)과 고른 갈래를 합쳐 답한다 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
         </is>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
@@ -2345,89 +2394,102 @@
     <row r="59">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
-      <c r="C59" s="15" t="n">
+      <c r="C59" s="16" t="n">
         <v>58</v>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr"/>
-      <c r="F59" s="20" t="inlineStr">
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>오늘 날짜는 2026년 9월 29일 월요일이고 올해 연말까지는 93일 남았어요. 연말정산 세액공제를 받으려면 올해 12월 31일까지 납입을 완료해야 해요.</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H59" s="17" t="inlineStr">
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
-      <c r="I59" s="17" t="inlineStr"/>
+      <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
       <c r="B60" s="9" t="n"/>
-      <c r="C60" s="15" t="n">
+      <c r="C60" s="16" t="n">
         <v>59</v>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>이 고객 잔액은 언제 기준 값이야?</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr"/>
-      <c r="F60" s="18" t="inlineStr">
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>원장에 기준시점 값이 따로 나와 있지 않아서 해당 항목의 기준 날짜는 확인할 수 없어요. 단말 화면에 표시된 현재 원장 값을 그대로 활용해 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
-      <c r="I60" s="17" t="inlineStr"/>
+      <c r="I60" s="18" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="15" t="n">
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>300 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr"/>
-      <c r="F61" s="18" t="inlineStr">
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 납입하는 경우에는 총급여 5,500만원 이하(16.5%)일 때 환급액 495,000원, 총급여 5,500만원 초과(13.2%)일 때 환급액 396,000원을 적용할 수 있어요. 
+이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로, ISA 만기자금 전환액의 10%가 세액공제 대상에 더해져 추가 공제 대상 300만원 상한 안에서 산출된 것이에요. 전환금은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 전환할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
         </is>
       </c>
-      <c r="I61" s="17" t="inlineStr"/>
+      <c r="I61" s="18" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -2439,7 +2501,7 @@
       <c r="C62" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
         </is>
@@ -2468,13 +2530,19 @@
       <c r="C63" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>어떤 처리 채널로 진행하시나요?
+· 비대면
+· 전문 송수신(일반)</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -2497,13 +2565,13 @@
       <c r="C64" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
@@ -2526,13 +2594,13 @@
       <c r="C65" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -2551,17 +2619,17 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
-      <c r="B66" s="12" t="n"/>
+      <c r="B66" s="10" t="n"/>
       <c r="C66" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -2580,123 +2648,123 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
         </is>
       </c>
-      <c r="C67" s="15" t="n">
+      <c r="C67" s="16" t="n">
         <v>66</v>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr"/>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="E67" s="18" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H67" s="17" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
         </is>
       </c>
-      <c r="I67" s="17" t="inlineStr"/>
+      <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
       <c r="B68" s="9" t="n"/>
-      <c r="C68" s="15" t="n">
+      <c r="C68" s="16" t="n">
         <v>67</v>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr"/>
-      <c r="F68" s="20" t="inlineStr">
+      <c r="E68" s="18" t="inlineStr"/>
+      <c r="F68" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
+      <c r="G68" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
         </is>
       </c>
-      <c r="I68" s="17" t="inlineStr"/>
+      <c r="I68" s="18" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
-      <c r="C69" s="15" t="n">
+      <c r="C69" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
         </is>
       </c>
-      <c r="E69" s="17" t="inlineStr"/>
-      <c r="F69" s="18" t="inlineStr">
+      <c r="E69" s="18" t="inlineStr"/>
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="G69" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="H69" s="18" t="inlineStr">
         <is>
           <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
         </is>
       </c>
-      <c r="I69" s="17" t="inlineStr"/>
+      <c r="I69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="15" t="n">
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="16" t="n">
         <v>69</v>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr"/>
-      <c r="F70" s="18" t="inlineStr">
+      <c r="E70" s="18" t="inlineStr"/>
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
+      <c r="G70" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="H70" s="18" t="inlineStr">
         <is>
           <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
-      <c r="I70" s="17" t="inlineStr"/>
+      <c r="I70" s="18" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -2708,7 +2776,7 @@
       <c r="C71" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
         </is>
@@ -2737,13 +2805,13 @@
       <c r="C72" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
-      <c r="F72" s="13" t="inlineStr">
+      <c r="F72" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -2762,17 +2830,17 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
-      <c r="B73" s="12" t="n"/>
+      <c r="B73" s="10" t="n"/>
       <c r="C73" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="11" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -2791,181 +2859,181 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
         </is>
       </c>
-      <c r="C74" s="15" t="n">
+      <c r="C74" s="16" t="n">
         <v>73</v>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr"/>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="E74" s="18" t="inlineStr"/>
+      <c r="F74" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr"/>
+      <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
-      <c r="C75" s="15" t="n">
+      <c r="C75" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr"/>
-      <c r="F75" s="21" t="inlineStr">
+      <c r="E75" s="18" t="inlineStr"/>
+      <c r="F75" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
+      <c r="G75" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H75" s="17" t="inlineStr">
+      <c r="H75" s="18" t="inlineStr">
         <is>
           <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
         </is>
       </c>
-      <c r="I75" s="17" t="inlineStr"/>
+      <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
       <c r="B76" s="9" t="n"/>
-      <c r="C76" s="15" t="n">
+      <c r="C76" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr"/>
-      <c r="F76" s="20" t="inlineStr">
+      <c r="E76" s="18" t="inlineStr"/>
+      <c r="F76" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G76" s="17" t="inlineStr">
+      <c r="G76" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H76" s="17" t="inlineStr">
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr"/>
+      <c r="I76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
-      <c r="C77" s="15" t="n">
+      <c r="C77" s="16" t="n">
         <v>76</v>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr"/>
-      <c r="F77" s="18" t="inlineStr">
+      <c r="E77" s="18" t="inlineStr"/>
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G77" s="17" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
-      <c r="I77" s="17" t="inlineStr"/>
+      <c r="I77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
       <c r="B78" s="9" t="n"/>
-      <c r="C78" s="15" t="n">
+      <c r="C78" s="16" t="n">
         <v>77</v>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
         </is>
       </c>
-      <c r="E78" s="17" t="inlineStr"/>
-      <c r="F78" s="18" t="inlineStr">
+      <c r="E78" s="18" t="inlineStr"/>
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr">
+      <c r="G78" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
         </is>
       </c>
-      <c r="I78" s="17" t="inlineStr"/>
+      <c r="I78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="n"/>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="15" t="n">
+      <c r="A79" s="24" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
         </is>
       </c>
-      <c r="E79" s="17" t="inlineStr"/>
-      <c r="F79" s="18" t="inlineStr">
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G79" s="17" t="inlineStr">
+      <c r="G79" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H79" s="17" t="inlineStr">
+      <c r="H79" s="18" t="inlineStr">
         <is>
           <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
-      <c r="I79" s="17" t="inlineStr"/>
+      <c r="I79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2981,7 +3049,7 @@
       <c r="C80" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
         </is>
@@ -3010,7 +3078,7 @@
       <c r="C81" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -3039,7 +3107,7 @@
       <c r="C82" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
         </is>
@@ -3068,13 +3136,13 @@
       <c r="C83" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="13" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3097,13 +3165,13 @@
       <c r="C84" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
         </is>
@@ -3126,13 +3194,13 @@
       <c r="C85" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr"/>
-      <c r="F85" s="11" t="inlineStr">
+      <c r="F85" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -3155,13 +3223,13 @@
       <c r="C86" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
-      <c r="F86" s="11" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -3184,13 +3252,13 @@
       <c r="C87" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr"/>
-      <c r="F87" s="11" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -3213,13 +3281,13 @@
       <c r="C88" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr"/>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
@@ -3238,17 +3306,17 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
-      <c r="B89" s="12" t="n"/>
+      <c r="B89" s="10" t="n"/>
       <c r="C89" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="11" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
@@ -3267,65 +3335,65 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n"/>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B90" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
         </is>
       </c>
-      <c r="C90" s="15" t="n">
+      <c r="C90" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
-      <c r="E90" s="17" t="inlineStr"/>
-      <c r="F90" s="19" t="inlineStr">
+      <c r="E90" s="18" t="inlineStr"/>
+      <c r="F90" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
+      <c r="G90" s="18" t="inlineStr">
         <is>
           <t>보수 성향 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H90" s="17" t="inlineStr">
+      <c r="H90" s="18" t="inlineStr">
         <is>
           <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
         </is>
       </c>
-      <c r="I90" s="17" t="inlineStr"/>
+      <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
-      <c r="C91" s="15" t="n">
+      <c r="C91" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>왜 이 상품은 목록에서 빠진 거야?</t>
         </is>
       </c>
-      <c r="E91" s="17" t="inlineStr"/>
-      <c r="F91" s="21" t="inlineStr">
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G91" s="17" t="inlineStr">
+      <c r="G91" s="18" t="inlineStr">
         <is>
           <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H91" s="17" t="inlineStr">
+      <c r="H91" s="18" t="inlineStr">
         <is>
           <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
         </is>
       </c>
-      <c r="I91" s="17" t="inlineStr">
+      <c r="I91" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
@@ -3334,89 +3402,89 @@
     <row r="92">
       <c r="A92" s="8" t="n"/>
       <c r="B92" s="9" t="n"/>
-      <c r="C92" s="15" t="n">
+      <c r="C92" s="16" t="n">
         <v>91</v>
       </c>
-      <c r="D92" s="16" t="inlineStr">
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>이 고객한테는 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr"/>
-      <c r="F92" s="20" t="inlineStr">
+      <c r="E92" s="18" t="inlineStr"/>
+      <c r="F92" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본 리허설</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
+      <c r="G92" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H92" s="17" t="inlineStr">
+      <c r="H92" s="18" t="inlineStr">
         <is>
           <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
         </is>
       </c>
-      <c r="I92" s="17" t="inlineStr"/>
+      <c r="I92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
-      <c r="C93" s="15" t="n">
+      <c r="C93" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
         </is>
       </c>
-      <c r="E93" s="17" t="inlineStr"/>
-      <c r="F93" s="18" t="inlineStr">
+      <c r="E93" s="18" t="inlineStr"/>
+      <c r="F93" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G93" s="17" t="inlineStr">
+      <c r="G93" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H93" s="17" t="inlineStr">
+      <c r="H93" s="18" t="inlineStr">
         <is>
           <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
-      <c r="I93" s="17" t="inlineStr"/>
+      <c r="I93" s="18" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n"/>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="15" t="n">
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="16" t="n">
         <v>93</v>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
         </is>
       </c>
-      <c r="E94" s="17" t="inlineStr"/>
-      <c r="F94" s="20" t="inlineStr">
+      <c r="E94" s="18" t="inlineStr"/>
+      <c r="F94" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G94" s="17" t="inlineStr">
+      <c r="G94" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H94" s="17" t="inlineStr">
+      <c r="H94" s="18" t="inlineStr">
         <is>
           <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
         </is>
       </c>
-      <c r="I94" s="17" t="inlineStr"/>
+      <c r="I94" s="18" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -3428,13 +3496,13 @@
       <c r="C95" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -3457,13 +3525,13 @@
       <c r="C96" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -3486,7 +3554,7 @@
       <c r="C97" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
         </is>
@@ -3515,13 +3583,13 @@
       <c r="C98" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr"/>
-      <c r="F98" s="13" t="inlineStr">
+      <c r="F98" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3544,13 +3612,13 @@
       <c r="C99" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr"/>
-      <c r="F99" s="13" t="inlineStr">
+      <c r="F99" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3569,17 +3637,17 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n"/>
-      <c r="B100" s="12" t="n"/>
+      <c r="B100" s="10" t="n"/>
       <c r="C100" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="12" t="inlineStr">
         <is>
           <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F100" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3598,152 +3666,177 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
         </is>
       </c>
-      <c r="C101" s="15" t="n">
+      <c r="C101" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="D101" s="16" t="inlineStr">
+      <c r="D101" s="17" t="inlineStr">
         <is>
           <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
         </is>
       </c>
-      <c r="E101" s="17" t="inlineStr"/>
-      <c r="F101" s="21" t="inlineStr">
+      <c r="E101" s="18" t="inlineStr"/>
+      <c r="F101" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G101" s="17" t="inlineStr">
+      <c r="G101" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H101" s="17" t="inlineStr">
+      <c r="H101" s="18" t="inlineStr">
         <is>
           <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="I101" s="17" t="inlineStr"/>
+      <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n"/>
       <c r="B102" s="9" t="n"/>
-      <c r="C102" s="15" t="n">
+      <c r="C102" s="16" t="n">
         <v>101</v>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="17" t="inlineStr">
         <is>
           <t>이번 주 금융시장에 영향 줄 만한 일정 뭐 있어?</t>
         </is>
       </c>
-      <c r="E102" s="17" t="inlineStr"/>
-      <c r="F102" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G102" s="17" t="inlineStr">
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>2026년 8월 3주차(2026년 8월 14일 종가 기준) 금융시장에 영향을 줄 수 있는 주요 일정은 국가별로 지정되어 있어요.
+- 17일 월요일 — 1~20일 수출/입
+- 18일 화요일(미국) — S&amp;P 제조업 및 서비스업 PMI
+- 20일 목요일(미국) — FOMC 의사록 공개
+- 21일 금요일(한국/미국) — 수출입물가 및 산업생산
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="F102" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H102" s="17" t="inlineStr">
-        <is>
-          <t>주간 일정 + **기준시점**(26.8 3주차) ↔ 기준시점이 없어 언제 자료인지 모른다</t>
-        </is>
-      </c>
-      <c r="I102" s="17" t="inlineStr"/>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「이번 주」에 8월 3주차 일정이 나온다(시효 표시는 붙는다). 봐야 할 것은 기준시점이 빠지지 않는가</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
       <c r="B103" s="9" t="n"/>
-      <c r="C103" s="15" t="n">
+      <c r="C103" s="16" t="n">
         <v>102</v>
       </c>
-      <c r="D103" s="16" t="inlineStr">
+      <c r="D103" s="17" t="inlineStr">
         <is>
           <t>이번 달 FOMC 어떻게 보고 있는지 시나리오별로 알려줘</t>
         </is>
       </c>
-      <c r="E103" s="17" t="inlineStr"/>
-      <c r="F103" s="18" t="inlineStr">
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>2026년 9월 자료 기준으로 9월 미국 FOMC는 기준금리를 동결할 가능성이 가장 높은 기본 시나리오로 보고 있어요.
+당시 기준으로 연준의 9월 기준금리 동결 가능성은 시장에 이미 선반영되었고, 포워드 가이던스를 주지 않으려는 워시 의장의 태도로 인해 시장 영향력은 제한적일 것으로 보았어요. 기본 시나리오에서는 미국초단기 국채 ETF신탁 같은 미국초단기채 상품을 고려해 볼 수 있어요.
+만약 기준금리 동결과 함께 향후 인하 가능성을 시사하는 긍정적 시나리오로 진행된다면 연내 금리 인하 기대감이 살아나며 단기물 중심의 미 국채가 강세를 보일 수 있어요. 이때는 미국10년국채선물 ETF신탁 같은 미국중단기채 상품이 대안이 될 수 있고, 미국 재정적자 확대 우려가 있는 미국장기채는 단기 상승 시 리밸런싱을 고려하는 대응이 필요해요.
+반대로 기준금리 인상과 함께 강한 긴축 기조 지속 가능성을 시사하는 부정적 시나리오가 나오면, 단기물 중심으로 미국 국채금리가 추가 상승할 수 있어요. 이 경우에는 NH-Amundi USD 초단기채(UH), 우리 미국 단기채 공모주(H), 미국초단기 국채 ETF신탁처럼 달러 상승에 대비할 수 있는 미국초단기채 상품을 살펴볼 수 있어요.
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="F103" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G103" s="17" t="inlineStr">
+      <c r="G103" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H103" s="17" t="inlineStr">
-        <is>
-          <t>긍정·기본·부정 + 기준시점 ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I103" s="17" t="inlineStr"/>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>긍정·기본·부정 + 기준시점(26.09 — 시연일과 같은 달) ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n"/>
       <c r="B104" s="9" t="n"/>
-      <c r="C104" s="15" t="n">
+      <c r="C104" s="16" t="n">
         <v>103</v>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D104" s="17" t="inlineStr">
         <is>
           <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
         </is>
       </c>
-      <c r="E104" s="17" t="inlineStr"/>
-      <c r="F104" s="18" t="inlineStr">
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 2 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
+응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gem…)</t>
+        </is>
+      </c>
+      <c r="F104" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="n"/>
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr"/>
+      <c r="F105" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H104" s="17" t="inlineStr">
-        <is>
-          <t>주간·월간 예상 **범위** + 기준시점 ↔ 범위의 한쪽 끝만 값으로 말한다</t>
-        </is>
-      </c>
-      <c r="I104" s="17" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="22" t="n"/>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
-        </is>
-      </c>
-      <c r="E105" s="17" t="inlineStr"/>
-      <c r="F105" s="18" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G105" s="17" t="inlineStr">
+      <c r="G105" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H105" s="17" t="inlineStr">
+      <c r="H105" s="18" t="inlineStr">
         <is>
           <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
         </is>
       </c>
-      <c r="I105" s="17" t="inlineStr"/>
+      <c r="I105" s="18" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3759,7 +3852,7 @@
       <c r="C106" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="12" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
@@ -3788,13 +3881,13 @@
       <c r="C107" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>왜 이 이벤트를 고른 거야?</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr"/>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -3821,7 +3914,7 @@
       <c r="C108" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
         <is>
           <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
         </is>
@@ -3854,13 +3947,13 @@
       <c r="C109" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
         <is>
           <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="13" t="inlineStr">
+      <c r="F109" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3887,13 +3980,13 @@
       <c r="C110" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
-      <c r="F110" s="13" t="inlineStr">
+      <c r="F110" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3916,17 +4009,17 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n"/>
-      <c r="B111" s="12" t="n"/>
+      <c r="B111" s="10" t="n"/>
       <c r="C111" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr"/>
-      <c r="F111" s="13" t="inlineStr">
+      <c r="F111" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -3945,65 +4038,65 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B112" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
         </is>
       </c>
-      <c r="C112" s="15" t="n">
+      <c r="C112" s="16" t="n">
         <v>111</v>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
-      <c r="E112" s="17" t="inlineStr"/>
-      <c r="F112" s="19" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr"/>
+      <c r="F112" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr">
+      <c r="G112" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H112" s="17" t="inlineStr">
+      <c r="H112" s="18" t="inlineStr">
         <is>
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="I112" s="17" t="inlineStr"/>
+      <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
       <c r="B113" s="9" t="n"/>
-      <c r="C113" s="15" t="n">
+      <c r="C113" s="16" t="n">
         <v>112</v>
       </c>
-      <c r="D113" s="16" t="inlineStr">
+      <c r="D113" s="17" t="inlineStr">
         <is>
           <t>(쪽지 초안 뒤) 응, 보내줘</t>
         </is>
       </c>
-      <c r="E113" s="17" t="inlineStr"/>
-      <c r="F113" s="19" t="inlineStr">
+      <c r="E113" s="18" t="inlineStr"/>
+      <c r="F113" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
         </is>
       </c>
-      <c r="G113" s="17" t="inlineStr">
+      <c r="G113" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H113" s="17" t="inlineStr">
+      <c r="H113" s="18" t="inlineStr">
         <is>
           <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
         </is>
       </c>
-      <c r="I113" s="17" t="inlineStr">
+      <c r="I113" s="18" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
@@ -4012,60 +4105,60 @@
     <row r="114">
       <c r="A114" s="8" t="n"/>
       <c r="B114" s="9" t="n"/>
-      <c r="C114" s="15" t="n">
+      <c r="C114" s="16" t="n">
         <v>113</v>
       </c>
-      <c r="D114" s="16" t="inlineStr">
+      <c r="D114" s="17" t="inlineStr">
         <is>
           <t>지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr"/>
-      <c r="F114" s="18" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr"/>
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G114" s="17" t="inlineStr">
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H114" s="17" t="inlineStr">
+      <c r="H114" s="18" t="inlineStr">
         <is>
           <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
         </is>
       </c>
-      <c r="I114" s="17" t="inlineStr"/>
+      <c r="I114" s="18" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="15" t="n">
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="16" t="n">
         <v>114</v>
       </c>
-      <c r="D115" s="16" t="inlineStr">
+      <c r="D115" s="17" t="inlineStr">
         <is>
           <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E115" s="17" t="inlineStr"/>
-      <c r="F115" s="18" t="inlineStr">
+      <c r="E115" s="18" t="inlineStr"/>
+      <c r="F115" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G115" s="17" t="inlineStr">
+      <c r="G115" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H115" s="17" t="inlineStr">
+      <c r="H115" s="18" t="inlineStr">
         <is>
           <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
         </is>
       </c>
-      <c r="I115" s="17" t="inlineStr"/>
+      <c r="I115" s="18" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n"/>
@@ -4077,13 +4170,13 @@
       <c r="C116" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -4106,15 +4199,15 @@
       <c r="C117" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr">
         <is>
           <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -4124,24 +4217,24 @@
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>AI 가 쓴 산문은 고치고 내역을 남긴다 ↔ 고치지 못한다고 거절한다</t>
+          <t>**시연 금지 — 재적용 루프 미구현.** 감사로그에만 남고 화면은 안 바뀌는데 「반영할게요」라고 답한다(correction.py 머리말)</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n"/>
-      <c r="B118" s="12" t="n"/>
+      <c r="B118" s="10" t="n"/>
       <c r="C118" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="12" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔줘</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F118" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4160,36 +4253,36 @@
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
-      <c r="B119" s="14" t="inlineStr">
+      <c r="B119" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
         </is>
       </c>
-      <c r="C119" s="15" t="n">
+      <c r="C119" s="16" t="n">
         <v>118</v>
       </c>
-      <c r="D119" s="16" t="inlineStr">
+      <c r="D119" s="17" t="inlineStr">
         <is>
           <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E119" s="17" t="inlineStr"/>
-      <c r="F119" s="19" t="inlineStr">
+      <c r="E119" s="18" t="inlineStr"/>
+      <c r="F119" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G119" s="17" t="inlineStr">
+      <c r="G119" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H119" s="17" t="inlineStr">
+      <c r="H119" s="18" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I119" s="17" t="inlineStr">
+      <c r="I119" s="18" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -4198,31 +4291,31 @@
     <row r="120">
       <c r="A120" s="8" t="n"/>
       <c r="B120" s="9" t="n"/>
-      <c r="C120" s="15" t="n">
+      <c r="C120" s="16" t="n">
         <v>119</v>
       </c>
-      <c r="D120" s="16" t="inlineStr">
+      <c r="D120" s="17" t="inlineStr">
         <is>
           <t>그 중 두 번째 상품만 자세히 설명해줘</t>
         </is>
       </c>
-      <c r="E120" s="17" t="inlineStr"/>
-      <c r="F120" s="19" t="inlineStr">
+      <c r="E120" s="18" t="inlineStr"/>
+      <c r="F120" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G120" s="17" t="inlineStr">
+      <c r="G120" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H120" s="17" t="inlineStr">
+      <c r="H120" s="18" t="inlineStr">
         <is>
           <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
-      <c r="I120" s="17" t="inlineStr">
+      <c r="I120" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
@@ -4231,31 +4324,31 @@
     <row r="121">
       <c r="A121" s="8" t="n"/>
       <c r="B121" s="9" t="n"/>
-      <c r="C121" s="15" t="n">
+      <c r="C121" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="D121" s="16" t="inlineStr">
+      <c r="D121" s="17" t="inlineStr">
         <is>
           <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
         </is>
       </c>
-      <c r="E121" s="17" t="inlineStr"/>
-      <c r="F121" s="18" t="inlineStr">
+      <c r="E121" s="18" t="inlineStr"/>
+      <c r="F121" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G121" s="17" t="inlineStr">
+      <c r="G121" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H121" s="17" t="inlineStr">
+      <c r="H121" s="18" t="inlineStr">
         <is>
           <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
         </is>
       </c>
-      <c r="I121" s="17" t="inlineStr">
+      <c r="I121" s="18" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -4264,31 +4357,31 @@
     <row r="122">
       <c r="A122" s="8" t="n"/>
       <c r="B122" s="9" t="n"/>
-      <c r="C122" s="15" t="n">
+      <c r="C122" s="16" t="n">
         <v>121</v>
       </c>
-      <c r="D122" s="16" t="inlineStr">
+      <c r="D122" s="17" t="inlineStr">
         <is>
           <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
-      <c r="E122" s="17" t="inlineStr"/>
-      <c r="F122" s="18" t="inlineStr">
+      <c r="E122" s="18" t="inlineStr"/>
+      <c r="F122" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G122" s="17" t="inlineStr">
+      <c r="G122" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H122" s="17" t="inlineStr">
+      <c r="H122" s="18" t="inlineStr">
         <is>
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
-      <c r="I122" s="17" t="inlineStr">
+      <c r="I122" s="18" t="inlineStr">
         <is>
           <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -4297,31 +4390,31 @@
     <row r="123">
       <c r="A123" s="8" t="n"/>
       <c r="B123" s="9" t="n"/>
-      <c r="C123" s="15" t="n">
+      <c r="C123" s="16" t="n">
         <v>122</v>
       </c>
-      <c r="D123" s="16" t="inlineStr">
+      <c r="D123" s="17" t="inlineStr">
         <is>
           <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
-      <c r="E123" s="17" t="inlineStr"/>
-      <c r="F123" s="18" t="inlineStr">
+      <c r="E123" s="18" t="inlineStr"/>
+      <c r="F123" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G123" s="17" t="inlineStr">
+      <c r="G123" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H123" s="17" t="inlineStr">
+      <c r="H123" s="18" t="inlineStr">
         <is>
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
-      <c r="I123" s="17" t="inlineStr">
+      <c r="I123" s="18" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -4329,32 +4422,32 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n"/>
-      <c r="B124" s="12" t="n"/>
-      <c r="C124" s="15" t="n">
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="16" t="n">
         <v>123</v>
       </c>
-      <c r="D124" s="16" t="inlineStr">
+      <c r="D124" s="17" t="inlineStr">
         <is>
           <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E124" s="17" t="inlineStr"/>
-      <c r="F124" s="18" t="inlineStr">
+      <c r="E124" s="18" t="inlineStr"/>
+      <c r="F124" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G124" s="17" t="inlineStr">
+      <c r="G124" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H124" s="17" t="inlineStr">
+      <c r="H124" s="18" t="inlineStr">
         <is>
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
-      <c r="I124" s="17" t="inlineStr"/>
+      <c r="I124" s="18" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n"/>
@@ -4366,13 +4459,13 @@
       <c r="C125" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="12" t="inlineStr">
         <is>
           <t>너 뭐 할 수 있는지 알려줘</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -4395,13 +4488,13 @@
       <c r="C126" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="12" t="inlineStr">
         <is>
           <t>너 이전 대화 기억해?</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
-      <c r="F126" s="13" t="inlineStr">
+      <c r="F126" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4420,17 +4513,17 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n"/>
-      <c r="B127" s="12" t="n"/>
+      <c r="B127" s="10" t="n"/>
       <c r="C127" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="12" t="inlineStr">
         <is>
           <t>고객한테 문자 직접 보내줄 수 있어?</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="13" t="inlineStr">
+      <c r="F127" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4449,65 +4542,65 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n"/>
-      <c r="B128" s="14" t="inlineStr">
+      <c r="B128" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
         </is>
       </c>
-      <c r="C128" s="15" t="n">
+      <c r="C128" s="16" t="n">
         <v>127</v>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D128" s="17" t="inlineStr">
         <is>
           <t>오늘 누구부터 봐야 해?</t>
         </is>
       </c>
-      <c r="E128" s="17" t="inlineStr"/>
-      <c r="F128" s="18" t="inlineStr">
+      <c r="E128" s="18" t="inlineStr"/>
+      <c r="F128" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G128" s="17" t="inlineStr">
+      <c r="G128" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H128" s="17" t="inlineStr">
+      <c r="H128" s="18" t="inlineStr">
         <is>
           <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
         </is>
       </c>
-      <c r="I128" s="17" t="inlineStr"/>
+      <c r="I128" s="18" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="22" t="n"/>
-      <c r="B129" s="12" t="n"/>
-      <c r="C129" s="15" t="n">
+      <c r="A129" s="24" t="n"/>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="16" t="n">
         <v>128</v>
       </c>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="D129" s="17" t="inlineStr">
         <is>
           <t>타겟 목록에 고객번호도 같이 넣어줘</t>
         </is>
       </c>
-      <c r="E129" s="17" t="inlineStr"/>
-      <c r="F129" s="18" t="inlineStr">
+      <c r="E129" s="18" t="inlineStr"/>
+      <c r="F129" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G129" s="17" t="inlineStr">
+      <c r="G129" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H129" s="17" t="inlineStr">
+      <c r="H129" s="18" t="inlineStr">
         <is>
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
-      <c r="I129" s="17" t="inlineStr"/>
+      <c r="I129" s="18" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4523,7 +4616,7 @@
       <c r="C130" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="12" t="inlineStr">
         <is>
           <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
         </is>
@@ -4552,7 +4645,7 @@
       <c r="C131" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D131" s="12" t="inlineStr">
         <is>
           <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
         </is>
@@ -4585,13 +4678,13 @@
       <c r="C132" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="12" t="inlineStr">
         <is>
           <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
-      <c r="F132" s="11" t="inlineStr">
+      <c r="F132" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
@@ -4614,13 +4707,13 @@
       <c r="C133" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="12" t="inlineStr">
         <is>
           <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr"/>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="F133" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
@@ -4643,13 +4736,13 @@
       <c r="C134" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="12" t="inlineStr">
         <is>
           <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="11" t="inlineStr">
+      <c r="F134" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
@@ -4676,13 +4769,13 @@
       <c r="C135" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D135" s="12" t="inlineStr">
         <is>
           <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr"/>
-      <c r="F135" s="13" t="inlineStr">
+      <c r="F135" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4709,13 +4802,13 @@
       <c r="C136" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="12" t="inlineStr">
         <is>
           <t>(되묻기 뒤) 2번째꺼</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="F136" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
         </is>
@@ -4742,13 +4835,13 @@
       <c r="C137" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D137" s="12" t="inlineStr">
         <is>
           <t>(되묻기 뒤) 잘 모르겠는데</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr"/>
-      <c r="F137" s="13" t="inlineStr">
+      <c r="F137" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4775,13 +4868,13 @@
       <c r="C138" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D138" s="12" t="inlineStr">
         <is>
           <t>(제안 뒤) 아니, 됐어</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
-      <c r="F138" s="13" t="inlineStr">
+      <c r="F138" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4808,13 +4901,13 @@
       <c r="C139" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="12" t="inlineStr">
         <is>
           <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr"/>
-      <c r="F139" s="13" t="inlineStr">
+      <c r="F139" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -4841,13 +4934,13 @@
       <c r="C140" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D140" s="12" t="inlineStr">
         <is>
           <t>(첫 턴) 네</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="13" t="inlineStr">
+      <c r="F140" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -4866,17 +4959,17 @@
     </row>
     <row r="141">
       <c r="A141" s="8" t="n"/>
-      <c r="B141" s="12" t="n"/>
+      <c r="B141" s="10" t="n"/>
       <c r="C141" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D141" s="12" t="inlineStr">
         <is>
           <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr"/>
-      <c r="F141" s="13" t="inlineStr">
+      <c r="F141" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -4899,123 +4992,123 @@
     </row>
     <row r="142">
       <c r="A142" s="8" t="n"/>
-      <c r="B142" s="14" t="inlineStr">
+      <c r="B142" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
         </is>
       </c>
-      <c r="C142" s="15" t="n">
+      <c r="C142" s="16" t="n">
         <v>141</v>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 무슨 상품 추천해주지?</t>
         </is>
       </c>
-      <c r="E142" s="17" t="inlineStr"/>
-      <c r="F142" s="19" t="inlineStr">
+      <c r="E142" s="18" t="inlineStr"/>
+      <c r="F142" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G142" s="17" t="inlineStr">
+      <c r="G142" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H142" s="17" t="inlineStr">
+      <c r="H142" s="18" t="inlineStr">
         <is>
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
-      <c r="I142" s="17" t="inlineStr"/>
+      <c r="I142" s="18" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n"/>
       <c r="B143" s="9" t="n"/>
-      <c r="C143" s="15" t="n">
+      <c r="C143" s="16" t="n">
         <v>142</v>
       </c>
-      <c r="D143" s="16" t="inlineStr">
+      <c r="D143" s="17" t="inlineStr">
         <is>
           <t>국고채 금리 어때?</t>
         </is>
       </c>
-      <c r="E143" s="17" t="inlineStr"/>
-      <c r="F143" s="18" t="inlineStr">
+      <c r="E143" s="18" t="inlineStr"/>
+      <c r="F143" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G143" s="17" t="inlineStr">
+      <c r="G143" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H143" s="17" t="inlineStr">
+      <c r="H143" s="18" t="inlineStr">
         <is>
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I143" s="17" t="inlineStr"/>
+      <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n"/>
       <c r="B144" s="9" t="n"/>
-      <c r="C144" s="15" t="n">
+      <c r="C144" s="16" t="n">
         <v>143</v>
       </c>
-      <c r="D144" s="16" t="inlineStr">
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
-      <c r="E144" s="17" t="inlineStr"/>
-      <c r="F144" s="18" t="inlineStr">
+      <c r="E144" s="18" t="inlineStr"/>
+      <c r="F144" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G144" s="17" t="inlineStr">
+      <c r="G144" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H144" s="17" t="inlineStr">
+      <c r="H144" s="18" t="inlineStr">
         <is>
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I144" s="17" t="inlineStr"/>
+      <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n"/>
       <c r="B145" s="9" t="n"/>
-      <c r="C145" s="15" t="n">
+      <c r="C145" s="16" t="n">
         <v>144</v>
       </c>
-      <c r="D145" s="16" t="inlineStr">
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>대화 내용 요약해줘</t>
         </is>
       </c>
-      <c r="E145" s="17" t="inlineStr"/>
-      <c r="F145" s="20" t="inlineStr">
+      <c r="E145" s="18" t="inlineStr"/>
+      <c r="F145" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
         </is>
       </c>
-      <c r="G145" s="17" t="inlineStr">
+      <c r="G145" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H145" s="17" t="inlineStr">
+      <c r="H145" s="18" t="inlineStr">
         <is>
           <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
         </is>
       </c>
-      <c r="I145" s="17" t="inlineStr">
+      <c r="I145" s="18" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -5024,118 +5117,118 @@
     <row r="146">
       <c r="A146" s="8" t="n"/>
       <c r="B146" s="9" t="n"/>
-      <c r="C146" s="15" t="n">
+      <c r="C146" s="16" t="n">
         <v>145</v>
       </c>
-      <c r="D146" s="16" t="inlineStr">
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E146" s="17" t="inlineStr"/>
-      <c r="F146" s="20" t="inlineStr">
+      <c r="E146" s="18" t="inlineStr"/>
+      <c r="F146" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본 리허설</t>
         </is>
       </c>
-      <c r="G146" s="17" t="inlineStr">
+      <c r="G146" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H146" s="17" t="inlineStr">
+      <c r="H146" s="18" t="inlineStr">
         <is>
           <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
-      <c r="I146" s="17" t="inlineStr"/>
+      <c r="I146" s="18" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n"/>
       <c r="B147" s="9" t="n"/>
-      <c r="C147" s="15" t="n">
+      <c r="C147" s="16" t="n">
         <v>146</v>
       </c>
-      <c r="D147" s="16" t="inlineStr">
+      <c r="D147" s="17" t="inlineStr">
         <is>
           <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E147" s="17" t="inlineStr"/>
-      <c r="F147" s="18" t="inlineStr">
+      <c r="E147" s="18" t="inlineStr"/>
+      <c r="F147" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G147" s="17" t="inlineStr">
+      <c r="G147" s="18" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="H147" s="17" t="inlineStr">
+      <c r="H147" s="18" t="inlineStr">
         <is>
           <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
-      <c r="I147" s="17" t="inlineStr"/>
+      <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n"/>
       <c r="B148" s="9" t="n"/>
-      <c r="C148" s="15" t="n">
+      <c r="C148" s="16" t="n">
         <v>147</v>
       </c>
-      <c r="D148" s="16" t="inlineStr">
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
-      <c r="E148" s="17" t="inlineStr"/>
-      <c r="F148" s="20" t="inlineStr">
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G148" s="17" t="inlineStr">
+      <c r="G148" s="18" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H148" s="17" t="inlineStr">
+      <c r="H148" s="18" t="inlineStr">
         <is>
           <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="I148" s="17" t="inlineStr"/>
+      <c r="I148" s="18" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="n"/>
       <c r="B149" s="9" t="n"/>
-      <c r="C149" s="15" t="n">
+      <c r="C149" s="16" t="n">
         <v>148</v>
       </c>
-      <c r="D149" s="16" t="inlineStr">
+      <c r="D149" s="17" t="inlineStr">
         <is>
           <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E149" s="17" t="inlineStr"/>
-      <c r="F149" s="20" t="inlineStr">
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G149" s="17" t="inlineStr">
+      <c r="G149" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H149" s="17" t="inlineStr">
+      <c r="H149" s="18" t="inlineStr">
         <is>
           <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I149" s="17" t="inlineStr">
+      <c r="I149" s="18" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -5143,32 +5236,32 @@
     </row>
     <row r="150">
       <c r="A150" s="8" t="n"/>
-      <c r="B150" s="12" t="n"/>
-      <c r="C150" s="15" t="n">
+      <c r="B150" s="10" t="n"/>
+      <c r="C150" s="16" t="n">
         <v>149</v>
       </c>
-      <c r="D150" s="16" t="inlineStr">
+      <c r="D150" s="17" t="inlineStr">
         <is>
           <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
         </is>
       </c>
-      <c r="E150" s="17" t="inlineStr"/>
-      <c r="F150" s="20" t="inlineStr">
+      <c r="E150" s="18" t="inlineStr"/>
+      <c r="F150" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G150" s="17" t="inlineStr">
+      <c r="G150" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H150" s="17" t="inlineStr">
+      <c r="H150" s="18" t="inlineStr">
         <is>
           <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
-      <c r="I150" s="17" t="inlineStr"/>
+      <c r="I150" s="18" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n"/>
@@ -5180,13 +5273,13 @@
       <c r="C151" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D151" s="12" t="inlineStr">
         <is>
           <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr"/>
-      <c r="F151" s="10" t="inlineStr">
+      <c r="F151" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
@@ -5209,13 +5302,13 @@
       <c r="C152" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
         <is>
           <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F152" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
@@ -5238,13 +5331,13 @@
       <c r="C153" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="12" t="inlineStr">
         <is>
           <t>IRP 중도인출 사유가 뭐야?</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="11" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
@@ -5267,13 +5360,13 @@
       <c r="C154" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D154" s="12" t="inlineStr">
         <is>
           <t>이 고객은 왜 타겟이 됐지?</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="11" t="inlineStr">
+      <c r="F154" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
@@ -5296,13 +5389,13 @@
       <c r="C155" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr"/>
-      <c r="F155" s="13" t="inlineStr">
+      <c r="F155" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -5325,13 +5418,13 @@
       <c r="C156" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="D156" s="12" t="inlineStr">
         <is>
           <t>(도구가 죽는 상황)</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="13" t="inlineStr">
+      <c r="F156" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -5358,13 +5451,13 @@
       <c r="C157" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>(상담기록 저장소를 못 읽는 상황)</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr"/>
-      <c r="F157" s="13" t="inlineStr">
+      <c r="F157" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -5391,13 +5484,13 @@
       <c r="C158" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>(LLM 미연결 상황)</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="13" t="inlineStr">
+      <c r="F158" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -5424,13 +5517,13 @@
       <c r="C159" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>(고객 연 직후 첫 질문)</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr"/>
-      <c r="F159" s="13" t="inlineStr">
+      <c r="F159" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
@@ -5457,13 +5550,13 @@
       <c r="C160" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>(화면번호 여러 개가 나오는 절차 질문)</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="F160" s="25" t="inlineStr">
         <is>
           <t>– 디버깅용 · 라이브러리 리허설</t>
         </is>
@@ -5490,13 +5583,13 @@
       <c r="C161" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="D161" s="12" t="inlineStr">
         <is>
           <t>(기준시점이 기간으로 적힌 카드를 쓰는 질문)</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="23" t="inlineStr">
+      <c r="F161" s="25" t="inlineStr">
         <is>
           <t>– 디버깅용 · 라이브러리 리허설</t>
         </is>
@@ -5519,17 +5612,17 @@
     </row>
     <row r="162">
       <c r="A162" s="8" t="n"/>
-      <c r="B162" s="12" t="n"/>
+      <c r="B162" s="10" t="n"/>
       <c r="C162" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="D162" s="5" t="inlineStr">
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>(기준시점이 표시에만 있는 카드를 쓰는 질문)</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="23" t="inlineStr">
+      <c r="F162" s="25" t="inlineStr">
         <is>
           <t>– 디버깅용 · 대본 리허설</t>
         </is>
@@ -5552,336 +5645,339 @@
     </row>
     <row r="163">
       <c r="A163" s="8" t="n"/>
-      <c r="B163" s="14" t="inlineStr">
+      <c r="B163" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
         </is>
       </c>
-      <c r="C163" s="15" t="n">
+      <c r="C163" s="16" t="n">
         <v>162</v>
       </c>
-      <c r="D163" s="16" t="inlineStr">
+      <c r="D163" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E163" s="17" t="inlineStr"/>
-      <c r="F163" s="19" t="inlineStr">
+      <c r="E163" s="18" t="inlineStr"/>
+      <c r="F163" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
         </is>
       </c>
-      <c r="G163" s="17" t="inlineStr">
+      <c r="G163" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H163" s="17" t="inlineStr">
+      <c r="H163" s="18" t="inlineStr">
         <is>
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
         </is>
       </c>
-      <c r="I163" s="17" t="inlineStr"/>
+      <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="n"/>
       <c r="B164" s="9" t="n"/>
-      <c r="C164" s="15" t="n">
+      <c r="C164" s="16" t="n">
         <v>163</v>
       </c>
-      <c r="D164" s="16" t="inlineStr">
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>이 고객 디폴트옵션 설정돼 있어?</t>
         </is>
       </c>
-      <c r="E164" s="17" t="inlineStr"/>
-      <c r="F164" s="21" t="inlineStr">
+      <c r="E164" s="18" t="inlineStr"/>
+      <c r="F164" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G164" s="17" t="inlineStr">
+      <c r="G164" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H164" s="17" t="inlineStr">
+      <c r="H164" s="18" t="inlineStr">
         <is>
           <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
-      <c r="I164" s="17" t="inlineStr"/>
+      <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n"/>
       <c r="B165" s="9" t="n"/>
-      <c r="C165" s="15" t="n">
+      <c r="C165" s="16" t="n">
         <v>164</v>
       </c>
-      <c r="D165" s="16" t="inlineStr">
+      <c r="D165" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E165" s="17" t="inlineStr"/>
-      <c r="F165" s="21" t="inlineStr">
+      <c r="E165" s="18" t="inlineStr"/>
+      <c r="F165" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G165" s="17" t="inlineStr">
+      <c r="G165" s="18" t="inlineStr">
         <is>
           <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H165" s="17" t="inlineStr">
+      <c r="H165" s="18" t="inlineStr">
         <is>
           <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
         </is>
       </c>
-      <c r="I165" s="17" t="inlineStr"/>
+      <c r="I165" s="18" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="n"/>
       <c r="B166" s="9" t="n"/>
-      <c r="C166" s="15" t="n">
+      <c r="C166" s="16" t="n">
         <v>165</v>
       </c>
-      <c r="D166" s="16" t="inlineStr">
+      <c r="D166" s="17" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E166" s="17" t="inlineStr"/>
-      <c r="F166" s="18" t="inlineStr">
+      <c r="E166" s="18" t="inlineStr"/>
+      <c r="F166" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G166" s="17" t="inlineStr">
+      <c r="G166" s="18" t="inlineStr">
         <is>
           <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
-      <c r="H166" s="17" t="inlineStr">
+      <c r="H166" s="18" t="inlineStr">
         <is>
           <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
-      <c r="I166" s="17" t="inlineStr"/>
+      <c r="I166" s="18" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="n"/>
       <c r="B167" s="9" t="n"/>
-      <c r="C167" s="15" t="n">
+      <c r="C167" s="16" t="n">
         <v>166</v>
       </c>
-      <c r="D167" s="16" t="inlineStr">
+      <c r="D167" s="17" t="inlineStr">
         <is>
           <t>지난 상담에서 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E167" s="17" t="inlineStr"/>
-      <c r="F167" s="18" t="inlineStr">
+      <c r="E167" s="18" t="inlineStr"/>
+      <c r="F167" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G167" s="17" t="inlineStr">
+      <c r="G167" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
-      <c r="H167" s="17" t="inlineStr">
+      <c r="H167" s="18" t="inlineStr">
         <is>
           <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="I167" s="17" t="inlineStr"/>
+      <c r="I167" s="18" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="n"/>
       <c r="B168" s="9" t="n"/>
-      <c r="C168" s="15" t="n">
+      <c r="C168" s="16" t="n">
         <v>167</v>
       </c>
-      <c r="D168" s="16" t="inlineStr">
+      <c r="D168" s="17" t="inlineStr">
         <is>
           <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E168" s="17" t="inlineStr"/>
-      <c r="F168" s="18" t="inlineStr">
+      <c r="E168" s="18" t="inlineStr"/>
+      <c r="F168" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G168" s="17" t="inlineStr">
+      <c r="G168" s="18" t="inlineStr">
         <is>
           <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H168" s="17" t="inlineStr">
+      <c r="H168" s="18" t="inlineStr">
         <is>
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
-      <c r="I168" s="17" t="inlineStr"/>
+      <c r="I168" s="18" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="n"/>
       <c r="B169" s="9" t="n"/>
-      <c r="C169" s="15" t="n">
+      <c r="C169" s="16" t="n">
         <v>168</v>
       </c>
-      <c r="D169" s="16" t="inlineStr">
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E169" s="17" t="inlineStr"/>
-      <c r="F169" s="18" t="inlineStr">
+      <c r="E169" s="18" t="inlineStr"/>
+      <c r="F169" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G169" s="17" t="inlineStr">
+      <c r="G169" s="18" t="inlineStr">
         <is>
           <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H169" s="17" t="inlineStr">
+      <c r="H169" s="18" t="inlineStr">
         <is>
           <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
-      <c r="I169" s="17" t="inlineStr"/>
+      <c r="I169" s="18" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="n"/>
       <c r="B170" s="9" t="n"/>
-      <c r="C170" s="15" t="n">
+      <c r="C170" s="16" t="n">
         <v>169</v>
       </c>
-      <c r="D170" s="16" t="inlineStr">
+      <c r="D170" s="17" t="inlineStr">
         <is>
           <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
-      <c r="E170" s="17" t="inlineStr"/>
-      <c r="F170" s="18" t="inlineStr">
+      <c r="E170" s="18" t="inlineStr"/>
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G170" s="17" t="inlineStr">
+      <c r="G170" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H170" s="17" t="inlineStr">
+      <c r="H170" s="18" t="inlineStr">
         <is>
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
-      <c r="I170" s="17" t="inlineStr"/>
+      <c r="I170" s="18" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="n"/>
       <c r="B171" s="9" t="n"/>
-      <c r="C171" s="15" t="n">
+      <c r="C171" s="16" t="n">
         <v>170</v>
       </c>
-      <c r="D171" s="16" t="inlineStr">
+      <c r="D171" s="17" t="inlineStr">
         <is>
           <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
-      <c r="E171" s="17" t="inlineStr"/>
-      <c r="F171" s="18" t="inlineStr">
+      <c r="E171" s="18" t="inlineStr"/>
+      <c r="F171" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G171" s="17" t="inlineStr">
+      <c r="G171" s="18" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H171" s="17" t="inlineStr">
+      <c r="H171" s="18" t="inlineStr">
         <is>
           <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
-      <c r="I171" s="17" t="inlineStr"/>
+      <c r="I171" s="18" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="n"/>
       <c r="B172" s="9" t="n"/>
-      <c r="C172" s="15" t="n">
+      <c r="C172" s="16" t="n">
         <v>171</v>
       </c>
-      <c r="D172" s="16" t="inlineStr">
+      <c r="D172" s="17" t="inlineStr">
         <is>
           <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E172" s="17" t="inlineStr"/>
-      <c r="F172" s="18" t="inlineStr">
+      <c r="E172" s="18" t="inlineStr"/>
+      <c r="F172" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G172" s="17" t="inlineStr">
+      <c r="G172" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H172" s="17" t="inlineStr">
+      <c r="H172" s="18" t="inlineStr">
         <is>
           <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
-      <c r="I172" s="17" t="inlineStr"/>
+      <c r="I172" s="18" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="22" t="n"/>
-      <c r="B173" s="12" t="n"/>
-      <c r="C173" s="15" t="n">
+      <c r="A173" s="24" t="n"/>
+      <c r="B173" s="10" t="n"/>
+      <c r="C173" s="16" t="n">
         <v>172</v>
       </c>
-      <c r="D173" s="16" t="inlineStr">
+      <c r="D173" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E173" s="17" t="inlineStr"/>
-      <c r="F173" s="18" t="inlineStr">
+      <c r="E173" s="18" t="inlineStr"/>
+      <c r="F173" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G173" s="17" t="inlineStr">
+      <c r="G173" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H173" s="17" t="inlineStr">
+      <c r="H173" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I173" s="17" t="inlineStr"/>
+      <c r="I173" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="36">
     <mergeCell ref="B45:B52"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="A45:A79"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B106:B111"/>
     <mergeCell ref="B53:B61"/>
     <mergeCell ref="B67:B70"/>
+    <mergeCell ref="D48:D49"/>
     <mergeCell ref="B34:B44"/>
     <mergeCell ref="B142:B150"/>
     <mergeCell ref="A80:A105"/>
@@ -5891,6 +5987,7 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="A106:A129"/>
     <mergeCell ref="B62:B66"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="B112:B115"/>
     <mergeCell ref="B90:B94"/>
     <mergeCell ref="B119:B124"/>
@@ -5906,6 +6003,7 @@
     <mergeCell ref="B95:B100"/>
     <mergeCell ref="B6:B17"/>
     <mergeCell ref="B80:B89"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5933,52 +6031,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>고객</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>kb-pin</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>나이</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>성향</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>ISA</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>상담기록</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>잔여한도</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>디폴트옵션</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>만기건수</t>
         </is>
       </c>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>성립 요건</t>
         </is>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -650,7 +650,16 @@
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>● 송도윤
+송도윤 고객님이 관리 대상으로 뜬 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 있으나, 358일간 접촉 이력이 없어 장기 미접촉 상태에 있기 때문이에요. 또한 판매중단된 KB 퇴직연금 배당(주식) 상품을 보유하고 있고, 고유계정대인 현금성자산을 방치 중이며, 디폴트옵션이 미설정 상태예요. 그 밖에 운용변경이 12개월 이상 없었고, ISA 만기자금을 보유하고 있으며, 당해 납입액이 0원인 상태예요.
+● 송도윤
+공격투자형 성향이신 정민석 고객님은 221일간 장기 미접촉 상태가 이어지고 있으며, 투자성향과 포트폴리오 간의 불일치가 발생하여 관리 대상으로 선정되었어요. 세부적으로는 현재 위험자산 비중이 0%로 원리금보장 및 현금성 자산이 100%를 차지하고 있으며, 12개월 이상 운용변경이 없는 상태입니다. 이로 인해 전체 운용수익률은 3.1%에 머물러 동연령대 평균 수익률(7.5%) 및 상위 1% 평균 수익률(20.3%)과 큰 격차를 보이고 있어요.
+● 송도윤
+현재 평가금액 8,000만원 중 원리금보장형과 고유계정대가 100%를 차지하여 위험자산 비중이 0%로 편중되어 있고, 오는 2026년 10월 17일에 7,000만원 규모의 예금 만기가 도래할 예정이기 때문에 관리 대상으로 선정되었어요. 또한 원리금보장상품 편중(80% 이상), 디폴트옵션 미설정, 만기예금 보유, 세액공제 활용 가능, 추가입금 여력 보유 항목이 성립 요건에 해당해요.</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -669,7 +678,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n"/>
+      <c r="A3" s="9" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -694,7 +703,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -723,7 +732,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -752,7 +761,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -785,7 +794,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -814,7 +823,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -843,7 +852,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -872,7 +881,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -901,7 +910,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -930,7 +939,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -959,7 +968,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -988,7 +997,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1017,7 +1026,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1046,7 +1055,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1075,7 +1084,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1104,7 +1113,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1137,7 +1146,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1162,7 +1171,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1191,7 +1200,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1220,7 +1229,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1249,7 +1258,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1274,7 +1283,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1303,7 +1312,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1332,7 +1341,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1361,7 +1370,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
+      <c r="A27" s="9" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1394,7 +1403,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1419,7 +1428,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
+      <c r="A29" s="9" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1448,7 +1457,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="9" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1477,7 +1486,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1510,7 +1519,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
+      <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1539,7 +1548,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
+      <c r="A33" s="9" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1572,7 +1581,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
+      <c r="A34" s="9" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1605,7 +1614,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1634,7 +1643,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
+      <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1663,7 +1672,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
+      <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1692,7 +1701,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
+      <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1721,7 +1730,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
+      <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1750,7 +1759,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n"/>
+      <c r="A40" s="9" t="n"/>
       <c r="B40" s="9" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -1783,7 +1792,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n"/>
+      <c r="A41" s="9" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="16" t="n">
         <v>40</v>
@@ -1816,7 +1825,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n"/>
+      <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="16" t="n">
         <v>41</v>
@@ -1845,7 +1854,7 @@
       <c r="I42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="16" t="n">
         <v>42</v>
@@ -1878,7 +1887,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="n"/>
+      <c r="A44" s="10" t="n"/>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="16" t="n">
         <v>43</v>
@@ -1958,7 +1967,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
+      <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -1987,7 +1996,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n"/>
+      <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2016,7 +2025,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
+      <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2045,7 +2054,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="4" t="n">
         <v>48</v>
@@ -2070,7 +2079,7 @@
       <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
+      <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="4" t="n">
         <v>49</v>
@@ -2099,7 +2108,7 @@
       <c r="I50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
+      <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="4" t="n">
         <v>50</v>
@@ -2134,7 +2143,7 @@
       <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
+      <c r="A52" s="9" t="n"/>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="4" t="n">
         <v>51</v>
@@ -2163,7 +2172,7 @@
       <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
+      <c r="A53" s="9" t="n"/>
       <c r="B53" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2202,7 +2211,7 @@
       <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
+      <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="16" t="n">
         <v>53</v>
@@ -2237,7 +2246,7 @@
       <c r="I54" s="18" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
+      <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="16" t="n">
         <v>54</v>
@@ -2270,7 +2279,7 @@
       <c r="I55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
+      <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2312,7 +2321,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2350,7 +2359,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
+      <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2392,7 +2401,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
+      <c r="A59" s="9" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="16" t="n">
         <v>58</v>
@@ -2425,7 +2434,7 @@
       <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="16" t="n">
         <v>59</v>
@@ -2458,7 +2467,7 @@
       <c r="I60" s="18" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
+      <c r="A61" s="9" t="n"/>
       <c r="B61" s="10" t="n"/>
       <c r="C61" s="16" t="n">
         <v>60</v>
@@ -2492,7 +2501,7 @@
       <c r="I61" s="18" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
+      <c r="A62" s="9" t="n"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2525,7 +2534,7 @@
       <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
+      <c r="A63" s="9" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="4" t="n">
         <v>62</v>
@@ -2560,7 +2569,7 @@
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
+      <c r="A64" s="9" t="n"/>
       <c r="B64" s="9" t="n"/>
       <c r="C64" s="4" t="n">
         <v>63</v>
@@ -2589,7 +2598,7 @@
       <c r="I64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
+      <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="4" t="n">
         <v>64</v>
@@ -2618,7 +2627,7 @@
       <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="9" t="n"/>
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="4" t="n">
         <v>65</v>
@@ -2647,7 +2656,7 @@
       <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
+      <c r="A67" s="9" t="n"/>
       <c r="B67" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -2680,7 +2689,7 @@
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
+      <c r="A68" s="9" t="n"/>
       <c r="B68" s="9" t="n"/>
       <c r="C68" s="16" t="n">
         <v>67</v>
@@ -2709,7 +2718,7 @@
       <c r="I68" s="18" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
+      <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="16" t="n">
         <v>68</v>
@@ -2738,7 +2747,7 @@
       <c r="I69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
+      <c r="A70" s="9" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="16" t="n">
         <v>69</v>
@@ -2767,7 +2776,7 @@
       <c r="I70" s="18" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="9" t="n"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -2800,7 +2809,7 @@
       <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
+      <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="4" t="n">
         <v>71</v>
@@ -2829,7 +2838,7 @@
       <c r="I72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="9" t="n"/>
       <c r="B73" s="10" t="n"/>
       <c r="C73" s="4" t="n">
         <v>72</v>
@@ -2858,7 +2867,7 @@
       <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
+      <c r="A74" s="9" t="n"/>
       <c r="B74" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -2891,7 +2900,7 @@
       <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="16" t="n">
         <v>74</v>
@@ -2920,7 +2929,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n"/>
+      <c r="A76" s="9" t="n"/>
       <c r="B76" s="9" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -2949,7 +2958,7 @@
       <c r="I76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n"/>
+      <c r="A77" s="9" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="16" t="n">
         <v>76</v>
@@ -2978,7 +2987,7 @@
       <c r="I77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n"/>
+      <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="16" t="n">
         <v>77</v>
@@ -3007,7 +3016,7 @@
       <c r="I78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="n"/>
+      <c r="A79" s="10" t="n"/>
       <c r="B79" s="10" t="n"/>
       <c r="C79" s="16" t="n">
         <v>78</v>
@@ -3073,7 +3082,7 @@
       <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
+      <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="4" t="n">
         <v>80</v>
@@ -3102,7 +3111,7 @@
       <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="9" t="n"/>
       <c r="C82" s="4" t="n">
         <v>81</v>
@@ -3131,7 +3140,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
+      <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3160,7 +3169,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
+      <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3189,7 +3198,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3218,7 +3227,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
+      <c r="A86" s="9" t="n"/>
       <c r="B86" s="9" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3247,7 +3256,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
+      <c r="A87" s="9" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="4" t="n">
         <v>86</v>
@@ -3276,7 +3285,7 @@
       <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
+      <c r="A88" s="9" t="n"/>
       <c r="B88" s="9" t="n"/>
       <c r="C88" s="4" t="n">
         <v>87</v>
@@ -3305,7 +3314,7 @@
       <c r="I88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
+      <c r="A89" s="9" t="n"/>
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="4" t="n">
         <v>88</v>
@@ -3334,7 +3343,7 @@
       <c r="I89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
+      <c r="A90" s="9" t="n"/>
       <c r="B90" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -3367,7 +3376,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
+      <c r="A91" s="9" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3400,7 +3409,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
+      <c r="A92" s="9" t="n"/>
       <c r="B92" s="9" t="n"/>
       <c r="C92" s="16" t="n">
         <v>91</v>
@@ -3429,7 +3438,7 @@
       <c r="I92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n"/>
+      <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="16" t="n">
         <v>92</v>
@@ -3458,7 +3467,7 @@
       <c r="I93" s="18" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
+      <c r="A94" s="9" t="n"/>
       <c r="B94" s="10" t="n"/>
       <c r="C94" s="16" t="n">
         <v>93</v>
@@ -3487,7 +3496,7 @@
       <c r="I94" s="18" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
+      <c r="A95" s="9" t="n"/>
       <c r="B95" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -3520,7 +3529,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n"/>
+      <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -3549,7 +3558,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
+      <c r="A97" s="9" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -3578,7 +3587,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
+      <c r="A98" s="9" t="n"/>
       <c r="B98" s="9" t="n"/>
       <c r="C98" s="4" t="n">
         <v>97</v>
@@ -3607,7 +3616,7 @@
       <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
+      <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="4" t="n">
         <v>98</v>
@@ -3636,7 +3645,7 @@
       <c r="I99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n"/>
+      <c r="A100" s="9" t="n"/>
       <c r="B100" s="10" t="n"/>
       <c r="C100" s="4" t="n">
         <v>99</v>
@@ -3665,7 +3674,7 @@
       <c r="I100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
+      <c r="A101" s="9" t="n"/>
       <c r="B101" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -3698,7 +3707,7 @@
       <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n"/>
+      <c r="A102" s="9" t="n"/>
       <c r="B102" s="9" t="n"/>
       <c r="C102" s="16" t="n">
         <v>101</v>
@@ -3737,7 +3746,7 @@
       <c r="I102" s="18" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="n"/>
+      <c r="A103" s="9" t="n"/>
       <c r="B103" s="9" t="n"/>
       <c r="C103" s="16" t="n">
         <v>102</v>
@@ -3775,7 +3784,7 @@
       <c r="I103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="n"/>
+      <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="16" t="n">
         <v>103</v>
@@ -3810,7 +3819,7 @@
       <c r="I104" s="18" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="n"/>
+      <c r="A105" s="10" t="n"/>
       <c r="B105" s="10" t="n"/>
       <c r="C105" s="16" t="n">
         <v>104</v>
@@ -3876,7 +3885,7 @@
       <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n"/>
+      <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -3909,7 +3918,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
+      <c r="A108" s="9" t="n"/>
       <c r="B108" s="9" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -3942,7 +3951,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n"/>
+      <c r="A109" s="9" t="n"/>
       <c r="B109" s="9" t="n"/>
       <c r="C109" s="4" t="n">
         <v>108</v>
@@ -3975,7 +3984,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
+      <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="n"/>
       <c r="C110" s="4" t="n">
         <v>109</v>
@@ -4008,7 +4017,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
+      <c r="A111" s="9" t="n"/>
       <c r="B111" s="10" t="n"/>
       <c r="C111" s="4" t="n">
         <v>110</v>
@@ -4037,7 +4046,7 @@
       <c r="I111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
+      <c r="A112" s="9" t="n"/>
       <c r="B112" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
@@ -4070,7 +4079,7 @@
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
+      <c r="A113" s="9" t="n"/>
       <c r="B113" s="9" t="n"/>
       <c r="C113" s="16" t="n">
         <v>112</v>
@@ -4103,7 +4112,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
+      <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="16" t="n">
         <v>113</v>
@@ -4132,7 +4141,7 @@
       <c r="I114" s="18" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
+      <c r="A115" s="9" t="n"/>
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="16" t="n">
         <v>114</v>
@@ -4161,7 +4170,7 @@
       <c r="I115" s="18" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
+      <c r="A116" s="9" t="n"/>
       <c r="B116" s="3" t="inlineStr">
         <is>
           <t>19. 브리핑 수정</t>
@@ -4194,7 +4203,7 @@
       <c r="I116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
+      <c r="A117" s="9" t="n"/>
       <c r="B117" s="9" t="n"/>
       <c r="C117" s="4" t="n">
         <v>116</v>
@@ -4223,7 +4232,7 @@
       <c r="I117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="n"/>
+      <c r="A118" s="9" t="n"/>
       <c r="B118" s="10" t="n"/>
       <c r="C118" s="4" t="n">
         <v>117</v>
@@ -4252,7 +4261,7 @@
       <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
+      <c r="A119" s="9" t="n"/>
       <c r="B119" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
@@ -4289,7 +4298,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
+      <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="16" t="n">
         <v>119</v>
@@ -4322,7 +4331,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
+      <c r="A121" s="9" t="n"/>
       <c r="B121" s="9" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
@@ -4355,7 +4364,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
+      <c r="A122" s="9" t="n"/>
       <c r="B122" s="9" t="n"/>
       <c r="C122" s="16" t="n">
         <v>121</v>
@@ -4388,7 +4397,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
+      <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="16" t="n">
         <v>122</v>
@@ -4421,7 +4430,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
+      <c r="A124" s="9" t="n"/>
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="16" t="n">
         <v>123</v>
@@ -4450,7 +4459,7 @@
       <c r="I124" s="18" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
+      <c r="A125" s="9" t="n"/>
       <c r="B125" s="3" t="inlineStr">
         <is>
           <t>21. 에이전트 능력 안내</t>
@@ -4483,7 +4492,7 @@
       <c r="I125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="n"/>
+      <c r="A126" s="9" t="n"/>
       <c r="B126" s="9" t="n"/>
       <c r="C126" s="4" t="n">
         <v>125</v>
@@ -4512,7 +4521,7 @@
       <c r="I126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="n"/>
+      <c r="A127" s="9" t="n"/>
       <c r="B127" s="10" t="n"/>
       <c r="C127" s="4" t="n">
         <v>126</v>
@@ -4541,7 +4550,7 @@
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
+      <c r="A128" s="9" t="n"/>
       <c r="B128" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
@@ -4574,7 +4583,7 @@
       <c r="I128" s="18" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="24" t="n"/>
+      <c r="A129" s="10" t="n"/>
       <c r="B129" s="10" t="n"/>
       <c r="C129" s="16" t="n">
         <v>128</v>
@@ -4640,7 +4649,7 @@
       <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
+      <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -4673,7 +4682,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
+      <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -4702,7 +4711,7 @@
       <c r="I132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
+      <c r="A133" s="9" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -4731,7 +4740,7 @@
       <c r="I133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
+      <c r="A134" s="9" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -4764,7 +4773,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
+      <c r="A135" s="9" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -4797,7 +4806,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
+      <c r="A136" s="9" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -4830,7 +4839,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
+      <c r="A137" s="9" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -4863,7 +4872,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
+      <c r="A138" s="9" t="n"/>
       <c r="B138" s="9" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -4896,7 +4905,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
+      <c r="A139" s="9" t="n"/>
       <c r="B139" s="9" t="n"/>
       <c r="C139" s="4" t="n">
         <v>138</v>
@@ -4929,7 +4938,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
+      <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="4" t="n">
         <v>139</v>
@@ -4958,7 +4967,7 @@
       <c r="I140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="n"/>
+      <c r="A141" s="9" t="n"/>
       <c r="B141" s="10" t="n"/>
       <c r="C141" s="4" t="n">
         <v>140</v>
@@ -4991,7 +5000,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="n"/>
+      <c r="A142" s="9" t="n"/>
       <c r="B142" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
@@ -5024,7 +5033,7 @@
       <c r="I142" s="18" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
+      <c r="A143" s="9" t="n"/>
       <c r="B143" s="9" t="n"/>
       <c r="C143" s="16" t="n">
         <v>142</v>
@@ -5053,7 +5062,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
+      <c r="A144" s="9" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -5082,7 +5091,7 @@
       <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
+      <c r="A145" s="9" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -5115,7 +5124,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
+      <c r="A146" s="9" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -5144,7 +5153,7 @@
       <c r="I146" s="18" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
+      <c r="A147" s="9" t="n"/>
       <c r="B147" s="9" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -5173,7 +5182,7 @@
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="n"/>
+      <c r="A148" s="9" t="n"/>
       <c r="B148" s="9" t="n"/>
       <c r="C148" s="16" t="n">
         <v>147</v>
@@ -5202,7 +5211,7 @@
       <c r="I148" s="18" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="n"/>
+      <c r="A149" s="9" t="n"/>
       <c r="B149" s="9" t="n"/>
       <c r="C149" s="16" t="n">
         <v>148</v>
@@ -5235,7 +5244,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="n"/>
+      <c r="A150" s="9" t="n"/>
       <c r="B150" s="10" t="n"/>
       <c r="C150" s="16" t="n">
         <v>149</v>
@@ -5264,7 +5273,7 @@
       <c r="I150" s="18" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="n"/>
+      <c r="A151" s="9" t="n"/>
       <c r="B151" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -5297,7 +5306,7 @@
       <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="n"/>
+      <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -5326,7 +5335,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="n"/>
+      <c r="A153" s="9" t="n"/>
       <c r="B153" s="9" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -5355,7 +5364,7 @@
       <c r="I153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="n"/>
+      <c r="A154" s="9" t="n"/>
       <c r="B154" s="9" t="n"/>
       <c r="C154" s="4" t="n">
         <v>153</v>
@@ -5384,7 +5393,7 @@
       <c r="I154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="n"/>
+      <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="4" t="n">
         <v>154</v>
@@ -5413,7 +5422,7 @@
       <c r="I155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="n"/>
+      <c r="A156" s="9" t="n"/>
       <c r="B156" s="9" t="n"/>
       <c r="C156" s="4" t="n">
         <v>155</v>
@@ -5446,7 +5455,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="n"/>
+      <c r="A157" s="9" t="n"/>
       <c r="B157" s="9" t="n"/>
       <c r="C157" s="4" t="n">
         <v>156</v>
@@ -5479,7 +5488,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="n"/>
+      <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="4" t="n">
         <v>157</v>
@@ -5512,7 +5521,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="n"/>
+      <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="4" t="n">
         <v>158</v>
@@ -5545,7 +5554,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="n"/>
+      <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="4" t="n">
         <v>159</v>
@@ -5578,7 +5587,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="n"/>
+      <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="4" t="n">
         <v>160</v>
@@ -5611,7 +5620,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="n"/>
+      <c r="A162" s="9" t="n"/>
       <c r="B162" s="10" t="n"/>
       <c r="C162" s="4" t="n">
         <v>161</v>
@@ -5644,7 +5653,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="n"/>
+      <c r="A163" s="9" t="n"/>
       <c r="B163" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -5677,7 +5686,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="n"/>
+      <c r="A164" s="9" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -5706,7 +5715,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="8" t="n"/>
+      <c r="A165" s="9" t="n"/>
       <c r="B165" s="9" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -5735,7 +5744,7 @@
       <c r="I165" s="18" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="8" t="n"/>
+      <c r="A166" s="9" t="n"/>
       <c r="B166" s="9" t="n"/>
       <c r="C166" s="16" t="n">
         <v>165</v>
@@ -5764,7 +5773,7 @@
       <c r="I166" s="18" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="8" t="n"/>
+      <c r="A167" s="9" t="n"/>
       <c r="B167" s="9" t="n"/>
       <c r="C167" s="16" t="n">
         <v>166</v>
@@ -5793,7 +5802,7 @@
       <c r="I167" s="18" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="8" t="n"/>
+      <c r="A168" s="9" t="n"/>
       <c r="B168" s="9" t="n"/>
       <c r="C168" s="16" t="n">
         <v>167</v>
@@ -5822,7 +5831,7 @@
       <c r="I168" s="18" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="8" t="n"/>
+      <c r="A169" s="9" t="n"/>
       <c r="B169" s="9" t="n"/>
       <c r="C169" s="16" t="n">
         <v>168</v>
@@ -5851,7 +5860,7 @@
       <c r="I169" s="18" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="8" t="n"/>
+      <c r="A170" s="9" t="n"/>
       <c r="B170" s="9" t="n"/>
       <c r="C170" s="16" t="n">
         <v>169</v>
@@ -5880,7 +5889,7 @@
       <c r="I170" s="18" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="8" t="n"/>
+      <c r="A171" s="9" t="n"/>
       <c r="B171" s="9" t="n"/>
       <c r="C171" s="16" t="n">
         <v>170</v>
@@ -5909,7 +5918,7 @@
       <c r="I171" s="18" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="8" t="n"/>
+      <c r="A172" s="9" t="n"/>
       <c r="B172" s="9" t="n"/>
       <c r="C172" s="16" t="n">
         <v>171</v>
@@ -5938,7 +5947,7 @@
       <c r="I172" s="18" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="24" t="n"/>
+      <c r="A173" s="10" t="n"/>
       <c r="B173" s="10" t="n"/>
       <c r="C173" s="16" t="n">
         <v>172</v>
@@ -5979,8 +5988,8 @@
     <mergeCell ref="B67:B70"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A80:A105"/>
     <mergeCell ref="B142:B150"/>
-    <mergeCell ref="A80:A105"/>
     <mergeCell ref="B125:B127"/>
     <mergeCell ref="B130:B141"/>
     <mergeCell ref="B128:B129"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -201,9 +201,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -570,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +681,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="10" t="n"/>
-      <c r="E3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>이준호 고객님이 관리 대상으로 뜬 이유는 평가금액 1억 2,500만원, 운용수익률 13.7%로 동연령 평균 수익률 12.1%를 상회하고 있으나, 2026년 9월 10일 만기가 경과한 예금 4,050만원이 포함되어 있어 체계적인 포트폴리오 재점검이 필요하기 때문이에요.</t>
+        </is>
+      </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -713,7 +714,11 @@
           <t>위험자산 한도 초과라는데 뭐가 문제고 뭘 해야 하는 거야?</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>박지민 고객님은 적극투자형 성향이지만 위험자산 비중이 75%로 DC·개인형IRP 투자한도인 70%를 초과하여 컴플라이언스 위반 점검 대상이 되었습니다. 이 규정 사항은 고객의 투자성향과 무관하게 한도 내로 조정해야 하므로 다른 위험자산 조정 전략에 흡수시키지 않고 우선적으로 해소해야 합니다. 위험자산 한도를 초과한 계좌를 해소하는 방법은 초과 금액을 정기예금 등 안전자산으로 교체매매하거나, 추가입금 후 안전자산으로 운용지시하여 분모를 늘려 비율을 해소하는 두 가지 방법이 있습니다.</t>
+        </is>
+      </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -742,7 +747,17 @@
           <t>이 고객 성향이랑 실제 운용이 안 맞는다는 게 무슨 말이야?</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>● 정민석
+공격투자형 성향이신 정민석 고객님은 현재 위험자산 비중이 0%로, 원리금보장·현금성 자산이 100%를 차지하며 성향과 포트폴리오 간의 불일치가 발생하고 있습니다.
+이로 인해 전체 운용수익률은 3.1%에 머물러 동연령대 평균 수익률(7.5%) 및 상위 1% 평균 수익률(20.3%)과 큰 격차를 보이고 있습니다.
+또한 12개월 이상 운용변경이 없고 6개월 이상 장기 미접촉 상태가 지속되면서 관리가 필요한 상황입니다.
+● 정민석
+송도윤 고객님의 성향과 실제 운용이 맞지 않는다고 보는 이유는 위험중립형 성향이신데도 고유계정대 2억 8,000만원이 현금성자산으로 방치되어 있기 때문이에요. 또한 12개월 이상 운용변경이 없고 디폴트옵션도 설정되지 않은 상태이며, 판매중단 상태인 KB 퇴직연금 배당 (주식) 상품을 보유하고 계세요. 
+고객에게 안내할 때는 고유계정대라는 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰도록 하세요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지는 말고, 운용 여건의 차이를 중심으로 설명해야 해요.</t>
+        </is>
+      </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -775,7 +790,11 @@
           <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 평가금액은 5억 2,000만원이에요. 자료에 따르면 이 고객은 평가금액 5억 2,000만원의 대규모 자산을 보유하고 계시며, 운용수익률 32.6%를 기록하고 있어요.</t>
+        </is>
+      </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -804,7 +823,14 @@
           <t>고유계정대 얼마야? 금액이랑 비중 둘 다 알려줘</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>● 김현수
+고유계정대 금액은 600만 원이고 비중은 75.0%예요. 고객에게 안내할 때는 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 주세요.
+● 김현수
+송도윤 고객님의 고유계정대는 2억 8,000만원이며, 자산군별 비중은 53.8%예요. 고객에게 안내할 때는 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 주세요.</t>
+        </is>
+      </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -833,7 +859,11 @@
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>이 고객의 만기 예정 자산은 2026년 10월 9일에 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품과, 2027년 1-10에 도래하는 3,550만원 규모의 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 상품이 있어요. 만기 1개월 전 원리금보장상품을 보유하고 있어 정기예금 자동 재예치 제도가 폐지됨에 따라 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로 만기 전 운용 방향 확정이 필요해요.</t>
+        </is>
+      </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -862,7 +892,11 @@
           <t>이 고객 만기 언제야?</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 만기 일자는 2026년 9월 20일인 1억 2,000만원 규모의 당행 ISA 만기자금이 있다. 해당 자금은 만기가 경과한 상태이다.</t>
+        </is>
+      </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1759,14 +1793,14 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="9" t="n"/>
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>(내부용 카드가 걸리는 질문)</t>
+          <t>(더미 자산 문구로) 이 문구 발송 화면에 넣어줘</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr"/>
@@ -1777,168 +1811,36 @@
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>「고객에게 그대로 안내하지 마세요」 + 본문도 대사로 안 옮긴다 ↔ 표시와 본문이 정반대를 말한다</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+          <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="16" t="n">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ. 상담 중 — 지식 질의응답(주 기능)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>7. 제도·수치 확인</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>(현장 노하우 카드가 걸리는 질문)</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr"/>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H41" s="18" t="inlineStr">
-        <is>
-          <t>출처가 정한 신뢰 등급 그대로 ↔ 현장 노하우가 본부 지침으로 읽힌다</t>
-        </is>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>(더미 자산 문구로) 이 문구 발송 화면에 넣어줘</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr"/>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H42" s="18" t="inlineStr">
-        <is>
-          <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>(가드 재료가 있는 요건 고객에게 아무 상담 질문)</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr"/>
-      <c r="F43" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>최서윤 165932-8741205·송도윤 188406-7352194·윤가영 162754-9483106 등</t>
-        </is>
-      </c>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>요건에 걸린 주의가 출처에 선다 ↔ 요건은 성립하는데 가드가 안 붙는다</t>
-        </is>
-      </c>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>(가드 재료가 없는 요건 고객에게 아무 상담 질문)</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr"/>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375·김서연 171203-4815062 등</t>
-        </is>
-      </c>
-      <c r="H44" s="18" t="inlineStr">
-        <is>
-          <t>**아무것도 띄우지 않는다** ↔ 없는 금지를 지어낸다</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Ⅱ. 상담 중 — 지식 질의응답(주 기능)</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>7. 제도·수치 확인</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>IRP 세액공제 한도가 얼마야?</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>IRP를 포함한 세액공제 한도는 연간 납입액 최대 900만원이에요. 2026년 6월 기준 자료에 따르면, 연금저축만으로는 한도가 연 600만원이지만 IRP를 포함하면 900만원까지 확대돼요.
 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 고객님은 16.5%, 초과하는 고객님은 13.2%(지방소득세 포함)의 공제율이 적용돼요. 이에 따라 900만원을 모두 채우면 각각 1,485,000원과 1,188,000원을 환급받을 수 있어요.
@@ -1949,11 +1851,123 @@
 · 고객이 앱에서 직접 할 수 있어?</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
         </is>
       </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>900만원 + 연금저축과 공유하는 한도라는 단서 ↔ 되묻는다 · 「IRP에만 900만원」으로 읽힌다</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>수수료 얼마야?</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 대본 리허설</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
+        </is>
+      </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
@@ -1961,7 +1975,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>900만원 + 연금저축과 공유하는 한도라는 단서 ↔ 되묻는다 · 「IRP에만 900만원」으로 읽힌다</t>
+          <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
@@ -1974,13 +1988,13 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
+          <t>타행 IRP 수수료는 우리보다 싼가?</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 대본 리허설</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -1990,7 +2004,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
+          <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr"/>
@@ -2003,209 +2017,207 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr"/>
+          <t>퇴직금을 통장으로 받은 걸 IRP에 다시 넣으면 세액공제도 받을 수 있어?</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>고객의 총급여 수준이 어떻게 되나요?
+· 5,500만원 이하
+· 5,500만원 초과</t>
+        </is>
+      </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
+          <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="9" t="n"/>
+      <c r="B48" s="10" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>수수료 얼마야?</t>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
+          <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n"/>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="4" t="n">
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>8. 세액공제 계산</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr"/>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>타행 IRP 수수료는 우리보다 싼가?</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본 리허설</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr"/>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>퇴직금을 통장으로 받은 걸 IRP에 다시 넣으면 세액공제도 받을 수 있어?</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>고객의 총급여 수준이 어떻게 되나요?
-· 5,500만원 이하
-· 5,500만원 초과</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr"/>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="4" t="n">
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="16" t="n">
         <v>51</v>
       </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr"/>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr"/>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>8. 세액공제 계산</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="n"/>
       <c r="C53" s="16" t="n">
         <v>52</v>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>총급여 구간을 선택해 주세요.
-· 5,500만원 이하
-· 5,500만원 초과</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 정해진 걸 「가정하면」으로 적는다</t>
+          <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr"/>
@@ -2218,32 +2230,30 @@
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>총급여 구간이 어떻게 되나요?
-· 5,500만원 이하
-· 5,500만원 초과</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>(총급여 구간 되묻기 뒤) 초과야</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>원장의 잔여한도를 쓴다 ↔ IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
-        </is>
-      </c>
-      <c r="I54" s="18" t="inlineStr"/>
+          <t>원래 질문(300만원)과 고른 갈래를 합쳐 13.2% 로 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="inlineStr">
+        <is>
+          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n"/>
@@ -2253,30 +2263,30 @@
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>송도윤 고객이 개인형IRP 계좌에 현금을 추가로 300만원 더 납입하는 경우라면, 세액공제 잔여한도가 0원이라 추가 공제 대상이 없어 올해 세액공제로 돌아오는 환급액은 늘어나지 않아요. 세액공제 한도 900만원은 연금저축 납입분까지 합산하여 이미 채워져 있기 때문이에요. 다만 연 납입한도 1,800만원까지는 납입 자체를 할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr"/>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr"/>
+          <t>같은 자리에서 **16.5%** 로 갈린다(300만원이면 495,000원) ↔ 13.2% 로 답하거나 원장 구간이 이긴다고 직원 말을 무시한다</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
@@ -2286,36 +2296,23 @@
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="inlineStr">
-        <is>
-          <t>● ISA
-총급여 구간이 어떻게 되나요?
-· 5,500만원 이하
-· 5,500만원 초과
-● ISA
-지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
-응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 15, model: ge…)
-● ISA
-송도윤 고객이 ISA 만기자금 중 일부인 8,000만원을 개인형IRP 계좌로 전환할 때는 늘어나는 추가 공제 대상과 총급여 구간에 따른 환급액을 바탕으로 안내하는 게 핵심이에요. 현재 이 고객의 개인형IRP 계좌 세액공제 잔여한도가 0원이므로 현금을 그냥 더 납입하는 경우에는 추가 공제 대상이 없지만, ISA 만기자금을 전환하면 전환액의 10%가 세액공제 대상에 더해져서 공제 한도가 900만원에서 최대 1,200만원으로 늘어나요. ISA 만기자금 8,000만원을 전환할 때 추가 공제 대상은 300만원 한도에 닿아 300만원이 되며, 총급여 5,500만원 이하인 경우 16.5% 공제율을 적용하면 495,000원의 환급이 늘어나고, 총급여 5,500만원 초과인 경우 13.2% 공제율을 적용하면 396,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안의 선택지처럼 견주지 않도록 유의하세요.</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
+          <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr"/>
@@ -2328,352 +2325,317 @@
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
-        </is>
-      </c>
-      <c r="E57" s="18" t="inlineStr">
-        <is>
-          <t>● ISA
-ISA 만기자금 8천만원을 개인형IRP 계좌로 전환할 때의 세액공제 환급액은 총급여 구간에 따라 다르게 안내해야 해요. 이 고객의 총급여 구간은 원장에 없으므로 단말에서 먼저 확인해야 하며, 5,500만원 이하인 경우 전환액 8천만원에 대해 추가 공제 대상 300만원이 적용되어 495,000원의 환급액이 늘어나고, 총급여 5,500만원 초과인 경우 추가 공제 대상 300만원이 적용되어 396,000원의 환급액이 늘어나요. ISA 만기자금 전환은 기존 현금 납입과 별개로 공제 대상 한도 자체가 늘어나는 몫이므로 둘을 같은 한도 안에서 저울질하지 않으며, 만기일로부터 60일 이내에 전환해야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● ISA
-ISA 만기자금 전환 시 세액공제 혜택 안내는 고객의 총급여 구간에 따라 다르게 적용되므로, 단말에서 총급여 구간을 먼저 확인한 뒤 해당 금액으로 안내해 드려야 해요. 이 고객의 개인형IRP 계좌로 8,000만원을 전환하는 경우 ISA 만기자금 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 늘어나요. 총급여 5,500만원 이하 구간(16.5%)이 확인되면 전환액 8,000만원에 대해 추가 공제 대상 300만원으로 늘어나는 환급액 495,000원을 안내하고, 총급여 5,500만원 초과 구간(13.2%)이 확인되면 늘어나는 환급액 396,000원을 안내해 주세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요.
-● ISA
-ISA 만기자금 8천만원을 개인형IRP 계좌로 전환하면 공제 대상 한도가 늘어나 추가 환급을 받을 수 있어요. 이 고객의 개인형IRP 계좌 추가 납입액 8,000만원을 ISA 만기자금으로 전환하는 경우, 전환액의 10%인 300만원이 추가 공제 대상 상한에 닿아 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어나요. 총급여가 5,500만원 이하(16.5%)라면 늘어나는 환급은 495,000원이고, 5,500만원 초과(13.2%)라면 396,000원이 돼요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않아야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 바탕으로 설명해 주세요.</t>
-        </is>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>이 고객 잔액은 언제 기준 값이야?</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
         <is>
-          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
+          <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n"/>
-      <c r="B58" s="9" t="n"/>
+      <c r="B58" s="10" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>(총급여 구간 되묻기 뒤) 초과야</t>
-        </is>
-      </c>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>● ISA
-총급여 5,500만원 초과 구간의 고객에게는 ISA 만기자금을 개인형IRP 계좌로 전환할 때의 추가 공제와 환급 예상액을 안내하는 게 핵심이에요. 앞서 말씀드린 현금 추가 납입의 경우와 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 방식이며, 8,000만원을 전부 전환하는 경우 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 초과 기준 396,000원의 환급이 늘어나요. 다만 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● ISA
-총급여 5,500만원 초과 구간에서는 개인형IRP 계좌 추가 납입과 ISA 만기자금 전환 각각의 경우에 따라 환급 예상액이 다르게 산출된다. 현금을 더 납입하는 경우 당해 납입액 600만원에 세액공제 한도 900만원, 잔여한도 300만원인 상태에서 추가 납입액 8,000만원을 넣으면 공제 대상이 600만원에서 900만원으로 늘어나고, 13.2% 공제율을 적용하여 환급 예상 792,000원에서 1,188,000원으로 늘어나며 늘어나는 금액은 396,000원이다. ISA 만기자금을 전환하는 경우 8,000만원을 타행에서 전환하면 전환액의 10%가 상한 300만원까지 세액공제 대상에 더해져 추가 공제 대상이 300만원이 되고, 13.2% 공제율을 적용하여 이 전환으로 늘어나는 환급은 396,000원이다. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이다.
-● ISA
-총급여가 5,500만원을 초과하는 고객에게는 ISA 만기자금 1억 2,000만원을 개인형IRP 계좌로 전환할 때 추가 공제 대상 300만원에 적용 공제율 13.2%를 곱해 환급액 396,000원이 늘어난다는 점을 안내하는 게 핵심이에요. 앞서 말씀드린 대로 이 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요. 전환액 1억 2,000만원 중 일부만 옮기는 경우라면 전환액의 10%가 세액공제 대상에 더해진다는 점을 감안해 주셔야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않도록 유의해 주세요.</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>300 넣으면 얼마 받아?</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G58" s="18" t="inlineStr">
         <is>
-          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
-          <t>원래 질문(300만원)과 고른 갈래를 합쳐 답한다 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
-        </is>
-      </c>
-      <c r="I58" s="18" t="inlineStr">
-        <is>
-          <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
-        </is>
-      </c>
+          <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n"/>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="16" t="n">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>9. 업무 처리 절차</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
-        </is>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>오늘 날짜는 2026년 9월 29일 월요일이고 올해 연말까지는 93일 남았어요. 연말정산 세액공제를 받으려면 올해 12월 31일까지 납입을 완료해야 해요.</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
-        <is>
-          <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · QA 리허설</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
-      <c r="C60" s="16" t="n">
+      <c r="C60" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 잔액은 언제 기준 값이야?</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>원장에 기준시점 값이 따로 나와 있지 않아서 해당 항목의 기준 날짜는 확인할 수 없어요. 단말 화면에 표시된 현재 원장 값을 그대로 활용해 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G60" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
-        <is>
-          <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>300 넣으면 얼마 받아?</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 납입하는 경우에는 총급여 5,500만원 이하(16.5%)일 때 환급액 495,000원, 총급여 5,500만원 초과(13.2%)일 때 환급액 396,000원을 적용할 수 있어요. 
-이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로, ISA 만기자금 전환액의 10%가 세액공제 대상에 더해져 추가 공제 대상 300만원 상한 안에서 산출된 것이에요. 전환금은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 전환할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G61" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>9. 업무 처리 절차</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="9" t="n"/>
-      <c r="C63" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>어떤 처리 채널로 진행하시나요?
 · 비대면
 · 전문 송수신(일반)</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
         </is>
       </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
+        </is>
+      </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
+          <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n"/>
-      <c r="B64" s="9" t="n"/>
-      <c r="C64" s="4" t="n">
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>10. 단말 화면번호</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
         <v>63</v>
       </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr"/>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr"/>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr"/>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="n"/>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="16" t="n">
         <v>64</v>
       </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr"/>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr"/>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr"/>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="4" t="n">
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="16" t="n">
         <v>65</v>
       </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr"/>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr"/>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n"/>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>10. 단말 화면번호</t>
-        </is>
-      </c>
+      <c r="B67" s="10" t="n"/>
       <c r="C67" s="16" t="n">
         <v>66</v>
       </c>
       <c r="D67" s="17" t="inlineStr">
         <is>
-          <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
+          <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr"/>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
@@ -2683,218 +2645,218 @@
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
+          <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n"/>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="16" t="n">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>11. 비대면 채널 경로</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
-        </is>
-      </c>
-      <c r="E68" s="18" t="inlineStr"/>
-      <c r="F68" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
-        <is>
-          <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H68" s="18" t="inlineStr">
-        <is>
-          <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr"/>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
-      <c r="C69" s="16" t="n">
+      <c r="C69" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr"/>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n"/>
       <c r="B70" s="10" t="n"/>
-      <c r="C70" s="16" t="n">
+      <c r="C70" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="D70" s="17" t="inlineStr">
-        <is>
-          <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
-        </is>
-      </c>
-      <c r="E70" s="18" t="inlineStr"/>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G70" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr"/>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>윤가영 162754-9483106</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n"/>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>11. 비대면 채널 경로</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="n">
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>12. 고객군·관리 기준</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr"/>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · QA 리허설</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>김현수 173544-2074623</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="16" t="n">
         <v>71</v>
       </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr"/>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr"/>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr"/>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n"/>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="4" t="n">
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr"/>
+      <c r="F73" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>윤가영 162754-9483106</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr"/>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n"/>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>12. 고객군·관리 기준</t>
-        </is>
-      </c>
+      <c r="B74" s="9" t="n"/>
       <c r="C74" s="16" t="n">
         <v>73</v>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
+          <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr"/>
-      <c r="F74" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · QA 리허설</t>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>김현수 173544-2074623</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
+          <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr"/>
@@ -2907,13 +2869,13 @@
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
+          <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -2923,26 +2885,26 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
+          <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="9" t="n"/>
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
+          <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr"/>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
@@ -2952,131 +2914,131 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
+          <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="9" t="n"/>
-      <c r="C77" s="16" t="n">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Ⅲ. 상담 중 — 무엇을 어떻게 말하나</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>13. 상담 화법·반론 대응</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="inlineStr"/>
-      <c r="F77" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="inlineStr"/>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>해지 만류 화법이 나와야 한다 ↔ 엉뚱한 절차 카드 한 장으로 「준비된 자료에 없어요」(**미해결**)</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
-      <c r="C78" s="16" t="n">
+      <c r="C78" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr"/>
-      <c r="F78" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G78" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H78" s="18" t="inlineStr">
-        <is>
-          <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
-        </is>
-      </c>
-      <c r="I78" s="18" t="inlineStr"/>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>이수민 175926-3048171·송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n"/>
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="16" t="n">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="D79" s="17" t="inlineStr">
-        <is>
-          <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="inlineStr"/>
-      <c r="F79" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G79" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H79" s="18" t="inlineStr">
-        <is>
-          <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
-        </is>
-      </c>
-      <c r="I79" s="18" t="inlineStr"/>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Ⅲ. 상담 중 — 무엇을 어떻게 말하나</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>13. 상담 화법·반론 대응</t>
-        </is>
-      </c>
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
       <c r="C80" s="4" t="n">
         <v>79</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
+          <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>해지 만류 화법이 나와야 한다 ↔ 엉뚱한 절차 카드 한 장으로 「준비된 자료에 없어요」(**미해결**)</t>
+          <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr"/>
@@ -3089,23 +3051,23 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+          <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 시연본 리허설</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>이수민 175926-3048171·송도윤 188406-7352194</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
+          <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -3118,23 +3080,23 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
+          <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
+          <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr"/>
@@ -3147,23 +3109,23 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
+          <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
+          <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr"/>
@@ -3176,23 +3138,23 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
+          <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+          <t>윤가영 162754-9483106</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
+          <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr"/>
@@ -3205,325 +3167,325 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
+          <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr"/>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>김현수 173544-2074623</t>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
+          <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="n"/>
-      <c r="B86" s="9" t="n"/>
+      <c r="B86" s="10" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
+          <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
+          <t>정민석 181245-3097614</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
+          <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n"/>
-      <c r="B87" s="9" t="n"/>
-      <c r="C87" s="4" t="n">
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>14. 적합성 범위 안내</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr"/>
-      <c r="F87" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>윤가영 162754-9483106</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr"/>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr"/>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>보수 성향 — 예: 오세훈 193482-6012375</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n"/>
       <c r="B88" s="9" t="n"/>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr"/>
-      <c r="F88" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614·박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr"/>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>왜 이 상품은 목록에서 빠진 거야?</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr"/>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n"/>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="4" t="n">
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr"/>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테는 뭘 권할 수 있어?</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr"/>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 대본 리허설</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr"/>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n"/>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>14. 적합성 범위 안내</t>
-        </is>
-      </c>
+      <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+          <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr"/>
-      <c r="F90" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F90" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>보수 성향 — 예: 오세훈 193482-6012375</t>
+          <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
+          <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n"/>
-      <c r="B91" s="9" t="n"/>
+      <c r="B91" s="10" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
       </c>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>왜 이 상품은 목록에서 빠진 거야?</t>
+          <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
-        </is>
-      </c>
-      <c r="I91" s="18" t="inlineStr">
-        <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
-        </is>
-      </c>
+          <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="9" t="n"/>
-      <c r="B92" s="9" t="n"/>
-      <c r="C92" s="16" t="n">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>15. 퇴직연금 운용 상품</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="D92" s="17" t="inlineStr">
-        <is>
-          <t>이 고객한테는 뭘 권할 수 있어?</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="inlineStr"/>
-      <c r="F92" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 대본 리허설</t>
-        </is>
-      </c>
-      <c r="G92" s="18" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614</t>
-        </is>
-      </c>
-      <c r="H92" s="18" t="inlineStr">
-        <is>
-          <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
-        </is>
-      </c>
-      <c r="I92" s="18" t="inlineStr"/>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
-      <c r="C93" s="16" t="n">
+      <c r="C93" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="D93" s="17" t="inlineStr">
-        <is>
-          <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="inlineStr"/>
-      <c r="F93" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G93" s="18" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375·박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H93" s="18" t="inlineStr">
-        <is>
-          <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
-        </is>
-      </c>
-      <c r="I93" s="18" t="inlineStr"/>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="n"/>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="16" t="n">
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="D94" s="17" t="inlineStr">
-        <is>
-          <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="inlineStr"/>
-      <c r="F94" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G94" s="18" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H94" s="18" t="inlineStr">
-        <is>
-          <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
-        </is>
-      </c>
-      <c r="I94" s="18" t="inlineStr"/>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n"/>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>15. 퇴직연금 운용 상품</t>
-        </is>
-      </c>
+      <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
+          <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
+          <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr"/>
@@ -3536,13 +3498,13 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
+          <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -3552,26 +3514,26 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
+          <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="n"/>
-      <c r="B97" s="9" t="n"/>
+      <c r="B97" s="10" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
+          <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -3581,143 +3543,56 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
+          <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="n"/>
-      <c r="B98" s="9" t="n"/>
-      <c r="C98" s="4" t="n">
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>16. 시황 — 상담에 쓰는 만큼</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="n">
         <v>97</v>
       </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr"/>
-      <c r="F98" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
-        </is>
-      </c>
-      <c r="I98" s="6" t="inlineStr"/>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr"/>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
-      <c r="C99" s="4" t="n">
+      <c r="C99" s="16" t="n">
         <v>98</v>
       </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr"/>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="n"/>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
-        <is>
-          <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr"/>
-      <c r="F100" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>16. 시황 — 상담에 쓰는 만큼</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D101" s="17" t="inlineStr">
-        <is>
-          <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
-        </is>
-      </c>
-      <c r="E101" s="18" t="inlineStr"/>
-      <c r="F101" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G101" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H101" s="18" t="inlineStr">
-        <is>
-          <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
-        </is>
-      </c>
-      <c r="I101" s="18" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="n"/>
-      <c r="B102" s="9" t="n"/>
-      <c r="C102" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="D102" s="17" t="inlineStr">
+      <c r="D99" s="17" t="inlineStr">
         <is>
           <t>이번 주 금융시장에 영향 줄 만한 일정 뭐 있어?</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr">
+      <c r="E99" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차(2026년 8월 14일 종가 기준) 금융시장에 영향을 줄 수 있는 주요 일정은 국가별로 지정되어 있어요.
 - 17일 월요일 — 1~20일 수출/입
@@ -3728,35 +3603,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F102" s="19" t="inlineStr">
+      <c r="F99" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G102" s="18" t="inlineStr">
+      <c r="G99" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H102" s="18" t="inlineStr">
+      <c r="H99" s="18" t="inlineStr">
         <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「이번 주」에 8월 3주차 일정이 나온다(시효 표시는 붙는다). 봐야 할 것은 기준시점이 빠지지 않는가</t>
         </is>
       </c>
-      <c r="I102" s="18" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="n"/>
-      <c r="B103" s="9" t="n"/>
-      <c r="C103" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="D103" s="17" t="inlineStr">
+      <c r="I99" s="18" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>이번 달 FOMC 어떻게 보고 있는지 시나리오별로 알려줘</t>
         </is>
       </c>
-      <c r="E103" s="18" t="inlineStr">
+      <c r="E100" s="18" t="inlineStr">
         <is>
           <t>2026년 9월 자료 기준으로 9월 미국 FOMC는 기준금리를 동결할 가능성이 가장 높은 기본 시나리오로 보고 있어요.
 당시 기준으로 연준의 9월 기준금리 동결 가능성은 시장에 이미 선반영되었고, 포워드 가이던스를 주지 않으려는 워시 의장의 태도로 인해 시장 영향력은 제한적일 것으로 보았어요. 기본 시나리오에서는 미국초단기 국채 ETF신탁 같은 미국초단기채 상품을 고려해 볼 수 있어요.
@@ -3766,123 +3641,222 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F103" s="19" t="inlineStr">
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G103" s="18" t="inlineStr">
+      <c r="G100" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H103" s="18" t="inlineStr">
+      <c r="H100" s="18" t="inlineStr">
         <is>
           <t>긍정·기본·부정 + 기준시점(26.09 — 시연일과 같은 달) ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
         </is>
       </c>
-      <c r="I103" s="18" t="inlineStr"/>
+      <c r="I100" s="18" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 2 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
+응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gem…)</t>
+        </is>
+      </c>
+      <c r="F101" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
+        </is>
+      </c>
+      <c r="I101" s="18" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n"/>
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="16" t="n">
+        <v>101</v>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr"/>
+      <c r="F102" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Ⅳ. 상담 후 · 그 밖</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>17. 안내 콘텐츠·발송</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
-      <c r="C104" s="16" t="n">
+      <c r="C104" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="D104" s="17" t="inlineStr">
-        <is>
-          <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
-        </is>
-      </c>
-      <c r="E104" s="18" t="inlineStr">
-        <is>
-          <t>지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 2 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
-응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gem…)</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G104" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H104" s="18" t="inlineStr">
-        <is>
-          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
-        </is>
-      </c>
-      <c r="I104" s="18" t="inlineStr"/>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>왜 이 이벤트를 고른 거야?</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="n"/>
-      <c r="B105" s="10" t="n"/>
-      <c r="C105" s="16" t="n">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="D105" s="17" t="inlineStr">
-        <is>
-          <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
-        </is>
-      </c>
-      <c r="E105" s="18" t="inlineStr"/>
-      <c r="F105" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G105" s="18" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614·박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H105" s="18" t="inlineStr">
-        <is>
-          <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I105" s="18" t="inlineStr"/>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Ⅳ. 상담 후 · 그 밖</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>17. 안내 콘텐츠·발송</t>
-        </is>
-      </c>
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
+          <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="n"/>
@@ -3892,13 +3866,13 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>왜 이 이벤트를 고른 거야?</t>
+          <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -3908,7 +3882,7 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
+          <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -3919,151 +3893,143 @@
     </row>
     <row r="108">
       <c r="A108" s="9" t="n"/>
-      <c r="B108" s="9" t="n"/>
+      <c r="B108" s="10" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
+          <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+          <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
+          <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="n"/>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="4" t="n">
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>18. 이번 상담 요약·쪽지</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr"/>
-      <c r="F109" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr"/>
+      <c r="F109" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="n"/>
-      <c r="C110" s="4" t="n">
+      <c r="C110" s="16" t="n">
         <v>109</v>
       </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr"/>
-      <c r="F110" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
-        </is>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>(쪽지 초안 뒤) 응, 보내줘</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr"/>
+      <c r="F110" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본 리허설</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="inlineStr">
+        <is>
+          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
+        </is>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="n"/>
-      <c r="B111" s="10" t="n"/>
-      <c r="C111" s="4" t="n">
+      <c r="B111" s="9" t="n"/>
+      <c r="C111" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 세미나 있어?</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr"/>
-      <c r="F111" s="14" t="inlineStr">
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>지금까지 얘기한 거 정리해줘</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr"/>
+      <c r="F111" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
-        </is>
-      </c>
-      <c r="H111" s="6" t="inlineStr">
-        <is>
-          <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
-        </is>
-      </c>
-      <c r="I111" s="6" t="inlineStr"/>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="9" t="n"/>
-      <c r="B112" s="15" t="inlineStr">
-        <is>
-          <t>18. 이번 상담 요약·쪽지</t>
-        </is>
-      </c>
+      <c r="B112" s="10" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t>대화 내용 요약해서 쪽지로 보내줘</t>
+          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
       <c r="E112" s="18" t="inlineStr"/>
-      <c r="F112" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
@@ -4073,212 +4039,220 @@
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
-          <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
+          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
         </is>
       </c>
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="9" t="n"/>
-      <c r="B113" s="9" t="n"/>
-      <c r="C113" s="16" t="n">
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>19. 브리핑 수정</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="D113" s="17" t="inlineStr">
-        <is>
-          <t>(쪽지 초안 뒤) 응, 보내줘</t>
-        </is>
-      </c>
-      <c r="E113" s="18" t="inlineStr"/>
-      <c r="F113" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
-        </is>
-      </c>
-      <c r="G113" s="18" t="inlineStr">
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr"/>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H113" s="18" t="inlineStr">
-        <is>
-          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
-        </is>
-      </c>
-      <c r="I113" s="18" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
-        </is>
-      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
-      <c r="C114" s="16" t="n">
+      <c r="C114" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="D114" s="17" t="inlineStr">
-        <is>
-          <t>지금까지 얘기한 거 정리해줘</t>
-        </is>
-      </c>
-      <c r="E114" s="18" t="inlineStr"/>
-      <c r="F114" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G114" s="18" t="inlineStr">
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr"/>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H114" s="18" t="inlineStr">
-        <is>
-          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
-        </is>
-      </c>
-      <c r="I114" s="18" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>**시연 금지 — 재적용 루프 미구현.** 감사로그에만 남고 화면은 안 바뀌는데 「반영할게요」라고 답한다(correction.py 머리말)</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="n"/>
       <c r="B115" s="10" t="n"/>
-      <c r="C115" s="16" t="n">
+      <c r="C115" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="D115" s="17" t="inlineStr">
-        <is>
-          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
-        </is>
-      </c>
-      <c r="E115" s="18" t="inlineStr"/>
-      <c r="F115" s="19" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>추천 상품을 다른 걸로 바꿔줘</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr"/>
+      <c r="F115" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G115" s="18" t="inlineStr">
+      <c r="G115" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H115" s="18" t="inlineStr">
-        <is>
-          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
-        </is>
-      </c>
-      <c r="I115" s="18" t="inlineStr"/>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="n"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>19. 브리핑 수정</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="n">
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>20. 답변 다듬기·되짚기</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="n">
         <v>115</v>
       </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr"/>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr"/>
+      <c r="F116" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
-        </is>
-      </c>
-      <c r="I116" s="6" t="inlineStr"/>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="n"/>
       <c r="B117" s="9" t="n"/>
-      <c r="C117" s="4" t="n">
+      <c r="C117" s="16" t="n">
         <v>116</v>
       </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr"/>
-      <c r="F117" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>그 중 두 번째 상품만 자세히 설명해줘</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr"/>
+      <c r="F117" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>**시연 금지 — 재적용 루프 미구현.** 감사로그에만 남고 화면은 안 바뀌는데 「반영할게요」라고 답한다(correction.py 머리말)</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="inlineStr"/>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="n"/>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="4" t="n">
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="16" t="n">
         <v>117</v>
       </c>
-      <c r="D118" s="12" t="inlineStr">
-        <is>
-          <t>추천 상품을 다른 걸로 바꿔줘</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr"/>
-      <c r="F118" s="14" t="inlineStr">
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr"/>
+      <c r="F118" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
+      <c r="G118" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr"/>
+      <c r="H118" s="18" t="inlineStr">
+        <is>
+          <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="n"/>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>20. 답변 다듬기·되짚기</t>
-        </is>
-      </c>
+      <c r="B119" s="9" t="n"/>
       <c r="C119" s="16" t="n">
         <v>118</v>
       </c>
       <c r="D119" s="17" t="inlineStr">
         <is>
-          <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
+          <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr"/>
-      <c r="F119" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G119" s="18" t="inlineStr">
@@ -4288,12 +4262,12 @@
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+          <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+          <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
@@ -4305,13 +4279,13 @@
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t>그 중 두 번째 상품만 자세히 설명해줘</t>
+          <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
       <c r="E120" s="18" t="inlineStr"/>
-      <c r="F120" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
@@ -4321,30 +4295,30 @@
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
+          <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr">
         <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n"/>
-      <c r="B121" s="9" t="n"/>
+      <c r="B121" s="10" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
       </c>
       <c r="D121" s="17" t="inlineStr">
         <is>
-          <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
+          <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr"/>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
@@ -4354,187 +4328,187 @@
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
-        </is>
-      </c>
-      <c r="I121" s="18" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+          <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="n"/>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="16" t="n">
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>21. 에이전트 능력 안내</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t>아까 수수료 설명한 거 요약해줘</t>
-        </is>
-      </c>
-      <c r="E122" s="18" t="inlineStr"/>
-      <c r="F122" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G122" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H122" s="18" t="inlineStr">
-        <is>
-          <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
-        </is>
-      </c>
-      <c r="I122" s="18" t="inlineStr">
-        <is>
-          <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>너 뭐 할 수 있는지 알려줘</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr"/>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
-      <c r="C123" s="16" t="n">
+      <c r="C123" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="D123" s="17" t="inlineStr">
-        <is>
-          <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
-        </is>
-      </c>
-      <c r="E123" s="18" t="inlineStr"/>
-      <c r="F123" s="19" t="inlineStr">
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>너 이전 대화 기억해?</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr"/>
+      <c r="F123" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G123" s="18" t="inlineStr">
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H123" s="18" t="inlineStr">
-        <is>
-          <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
-        </is>
-      </c>
-      <c r="I123" s="18" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="9" t="n"/>
       <c r="B124" s="10" t="n"/>
-      <c r="C124" s="16" t="n">
+      <c r="C124" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="D124" s="17" t="inlineStr">
-        <is>
-          <t>(첫 턴) 좀 더 짧게 줄여줘</t>
-        </is>
-      </c>
-      <c r="E124" s="18" t="inlineStr"/>
-      <c r="F124" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G124" s="18" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>고객한테 문자 직접 보내줄 수 있어?</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr"/>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H124" s="18" t="inlineStr">
-        <is>
-          <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
-        </is>
-      </c>
-      <c r="I124" s="18" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="9" t="n"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>21. 에이전트 능력 안내</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>22. 오늘의 타겟 목록</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="n">
         <v>124</v>
       </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>너 뭐 할 수 있는지 알려줘</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr"/>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>오늘 누구부터 봐야 해?</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr"/>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H125" s="6" t="inlineStr">
-        <is>
-          <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
-        </is>
-      </c>
-      <c r="I125" s="6" t="inlineStr"/>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="n"/>
-      <c r="B126" s="9" t="n"/>
-      <c r="C126" s="4" t="n">
+      <c r="A126" s="10" t="n"/>
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="16" t="n">
         <v>125</v>
       </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>너 이전 대화 기억해?</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr"/>
-      <c r="F126" s="14" t="inlineStr">
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>타겟 목록에 고객번호도 같이 넣어줘</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr"/>
+      <c r="F126" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
-        </is>
-      </c>
-      <c r="I126" s="6" t="inlineStr"/>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
+          <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
+        </is>
+      </c>
+      <c r="I126" s="18" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="n"/>
-      <c r="B127" s="10" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ⅴ. 품질 — 시연엔 안 올려도 보는 것</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>23. 복합·연쇄 턴</t>
+        </is>
+      </c>
       <c r="C127" s="4" t="n">
         <v>126</v>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>고객한테 문자 직접 보내줄 수 있어?</t>
+          <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
-      <c r="F127" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 대본 리허설</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -4544,106 +4518,98 @@
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
+          <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="n"/>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>22. 오늘의 타겟 목록</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="n">
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="D128" s="17" t="inlineStr">
-        <is>
-          <t>오늘 누구부터 봐야 해?</t>
-        </is>
-      </c>
-      <c r="E128" s="18" t="inlineStr"/>
-      <c r="F128" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G128" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H128" s="18" t="inlineStr">
-        <is>
-          <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
-        </is>
-      </c>
-      <c r="I128" s="18" t="inlineStr"/>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr"/>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="10" t="n"/>
-      <c r="B129" s="10" t="n"/>
-      <c r="C129" s="16" t="n">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="D129" s="17" t="inlineStr">
-        <is>
-          <t>타겟 목록에 고객번호도 같이 넣어줘</t>
-        </is>
-      </c>
-      <c r="E129" s="18" t="inlineStr"/>
-      <c r="F129" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G129" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H129" s="18" t="inlineStr">
-        <is>
-          <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
-        </is>
-      </c>
-      <c r="I129" s="18" t="inlineStr"/>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr"/>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Ⅴ. 품질 — 시연엔 안 올려도 보는 것</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>23. 복합·연쇄 턴</t>
-        </is>
-      </c>
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
+          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr"/>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+      <c r="F130" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
+          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr"/>
@@ -4656,28 +4622,28 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
+          <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
+          <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+          <t>이 고객 만기 언제고 금액은 얼마야?</t>
         </is>
       </c>
     </row>
@@ -4689,26 +4655,30 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
+          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
-      <c r="F132" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>정민석 181245-3097614·박정호 168450-7293815</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
-        </is>
-      </c>
-      <c r="I132" s="6" t="inlineStr"/>
+          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="n"/>
@@ -4718,26 +4688,30 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
+          <t>(되묻기 뒤) 2번째꺼</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr"/>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · 라이브러리 리허설</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr"/>
+          <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>실물이전 어떻게 처리해?</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="n"/>
@@ -4747,28 +4721,28 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
+          <t>(되묻기 뒤) 잘 모르겠는데</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
-      <c r="F134" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F134" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
+          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>이 고객 만기 언제고 금액은 얼마야?</t>
+          <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4754,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
+          <t>(제안 뒤) 아니, 됐어</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr"/>
@@ -4796,12 +4770,12 @@
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
+          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
@@ -4813,13 +4787,13 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>(되묻기 뒤) 2번째꺼</t>
+          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
-      <c r="F136" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -4829,12 +4803,12 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
+          <t>직원이 말한 값은 되받아 적을 수 있다 ↔ 이전 턴 수치를 인용하면 폐기된다(**미해결**)</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>실물이전 어떻게 처리해?</t>
+          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
     </row>
@@ -4846,40 +4820,36 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>(되묻기 뒤) 잘 모르겠는데</t>
+          <t>(첫 턴) 네</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr"/>
       <c r="F137" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>실물이전 어떻게 처리해?</t>
-        </is>
-      </c>
+          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="9" t="n"/>
-      <c r="B138" s="9" t="n"/>
+      <c r="B138" s="10" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>(제안 뒤) 아니, 됐어</t>
+          <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
@@ -4895,142 +4865,138 @@
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
+          <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+          <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="9" t="n"/>
-      <c r="B139" s="9" t="n"/>
-      <c r="C139" s="4" t="n">
+      <c r="B139" s="15" t="inlineStr">
+        <is>
+          <t>24. 도구 경계 혼동</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="n">
         <v>138</v>
       </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr"/>
-      <c r="F139" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="inlineStr">
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테 무슨 상품 추천해주지?</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr"/>
+      <c r="F139" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스 리허설</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>직원이 말한 값은 되받아 적을 수 있다 ↔ 이전 턴 수치를 인용하면 폐기된다(**미해결**)</t>
-        </is>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
-        </is>
-      </c>
+      <c r="H139" s="18" t="inlineStr">
+        <is>
+          <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
+        </is>
+      </c>
+      <c r="I139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
-      <c r="C140" s="4" t="n">
+      <c r="C140" s="16" t="n">
         <v>139</v>
       </c>
-      <c r="D140" s="12" t="inlineStr">
-        <is>
-          <t>(첫 턴) 네</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>국고채 금리 어때?</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr"/>
+      <c r="F140" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
-        </is>
-      </c>
-      <c r="I140" s="6" t="inlineStr"/>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>시황만 ↔ 추천펀드가 따라 나온다</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="9" t="n"/>
-      <c r="B141" s="10" t="n"/>
-      <c r="C141" s="4" t="n">
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr"/>
-      <c r="F141" s="14" t="inlineStr">
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>8월 추천펀드 뭐야?</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr"/>
+      <c r="F141" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
-        </is>
-      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
+        </is>
+      </c>
+      <c r="I141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="n"/>
-      <c r="B142" s="15" t="inlineStr">
-        <is>
-          <t>24. 도구 경계 혼동</t>
-        </is>
-      </c>
+      <c r="B142" s="9" t="n"/>
       <c r="C142" s="16" t="n">
         <v>141</v>
       </c>
       <c r="D142" s="17" t="inlineStr">
         <is>
-          <t>이 고객한테 무슨 상품 추천해주지?</t>
+          <t>대화 내용 요약해줘</t>
         </is>
       </c>
       <c r="E142" s="18" t="inlineStr"/>
-      <c r="F142" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+      <c r="F142" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 시연본 리허설</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H142" s="18" t="inlineStr">
         <is>
-          <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
-        </is>
-      </c>
-      <c r="I142" s="18" t="inlineStr"/>
+          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="n"/>
@@ -5040,23 +5006,23 @@
       </c>
       <c r="D143" s="17" t="inlineStr">
         <is>
-          <t>국고채 금리 어때?</t>
+          <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
       <c r="E143" s="18" t="inlineStr"/>
-      <c r="F143" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 대본 리허설</t>
         </is>
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H143" s="18" t="inlineStr">
         <is>
-          <t>시황만 ↔ 추천펀드가 따라 나온다</t>
+          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
       <c r="I143" s="18" t="inlineStr"/>
@@ -5069,7 +5035,7 @@
       </c>
       <c r="D144" s="17" t="inlineStr">
         <is>
-          <t>8월 추천펀드 뭐야?</t>
+          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
       <c r="E144" s="18" t="inlineStr"/>
@@ -5080,12 +5046,12 @@
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H144" s="18" t="inlineStr">
         <is>
-          <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
+          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
       <c r="I144" s="18" t="inlineStr"/>
@@ -5098,30 +5064,26 @@
       </c>
       <c r="D145" s="17" t="inlineStr">
         <is>
-          <t>대화 내용 요약해줘</t>
+          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
       <c r="E145" s="18" t="inlineStr"/>
       <c r="F145" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · QA 리허설</t>
         </is>
       </c>
       <c r="G145" s="18" t="inlineStr">
         <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H145" s="18" t="inlineStr">
         <is>
-          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
-        </is>
-      </c>
-      <c r="I145" s="18" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
+          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="n"/>
@@ -5131,176 +5093,176 @@
       </c>
       <c r="D146" s="17" t="inlineStr">
         <is>
-          <t>지난번엔 무슨 얘기 했지?</t>
+          <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
       <c r="E146" s="18" t="inlineStr"/>
       <c r="F146" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 대본 리허설</t>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
         <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H146" s="18" t="inlineStr">
         <is>
-          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
-        </is>
-      </c>
-      <c r="I146" s="18" t="inlineStr"/>
+          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="n"/>
-      <c r="B147" s="9" t="n"/>
+      <c r="B147" s="10" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
       </c>
       <c r="D147" s="17" t="inlineStr">
         <is>
-          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
+          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
         </is>
       </c>
       <c r="E147" s="18" t="inlineStr"/>
-      <c r="F147" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H147" s="18" t="inlineStr">
         <is>
-          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
+          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="9" t="n"/>
-      <c r="B148" s="9" t="n"/>
-      <c r="C148" s="16" t="n">
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>25. 실패·경계 처리</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
         <v>147</v>
       </c>
-      <c r="D148" s="17" t="inlineStr">
-        <is>
-          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
-        </is>
-      </c>
-      <c r="E148" s="18" t="inlineStr"/>
-      <c r="F148" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA 리허설</t>
-        </is>
-      </c>
-      <c r="G148" s="18" t="inlineStr">
-        <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H148" s="18" t="inlineStr">
-        <is>
-          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
-        </is>
-      </c>
-      <c r="I148" s="18" t="inlineStr"/>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr"/>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="9" t="n"/>
       <c r="B149" s="9" t="n"/>
-      <c r="C149" s="16" t="n">
+      <c r="C149" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="D149" s="17" t="inlineStr">
-        <is>
-          <t>좀 더 짧게 줄여줘</t>
-        </is>
-      </c>
-      <c r="E149" s="18" t="inlineStr"/>
-      <c r="F149" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G149" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H149" s="18" t="inlineStr">
-        <is>
-          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
-        </is>
-      </c>
-      <c r="I149" s="18" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>이 고객 평가금액 얼마야?</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr"/>
+      <c r="F149" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="9" t="n"/>
-      <c r="B150" s="10" t="n"/>
-      <c r="C150" s="16" t="n">
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="D150" s="17" t="inlineStr">
-        <is>
-          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
-        </is>
-      </c>
-      <c r="E150" s="18" t="inlineStr"/>
-      <c r="F150" s="21" t="inlineStr">
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>IRP 중도인출 사유가 뭐야?</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr"/>
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
-      <c r="G150" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H150" s="18" t="inlineStr">
-        <is>
-          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
-        </is>
-      </c>
-      <c r="I150" s="18" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="9" t="n"/>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>25. 실패·경계 처리</t>
-        </is>
-      </c>
+      <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
+          <t>이 고객은 왜 타겟이 됐지?</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr"/>
-      <c r="F151" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스 리허설</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
+          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr"/>
@@ -5313,374 +5275,350 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>이 고객 평가금액 얼마야?</t>
+          <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
+          <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="n"/>
-      <c r="B153" s="9" t="n"/>
+      <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>IRP 중도인출 사유가 뭐야?</t>
+          <t>(고객 연 직후 첫 질문)</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
+      <c r="F153" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
-        </is>
-      </c>
-      <c r="I153" s="6" t="inlineStr"/>
+          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="9" t="n"/>
-      <c r="B154" s="9" t="n"/>
-      <c r="C154" s="4" t="n">
+      <c r="B154" s="15" t="inlineStr">
+        <is>
+          <t>26. 고객별 대조</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="n">
         <v>153</v>
       </c>
-      <c r="D154" s="12" t="inlineStr">
-        <is>
-          <t>이 고객은 왜 타겟이 됐지?</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스 리허설</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
-        </is>
-      </c>
-      <c r="I154" s="6" t="inlineStr"/>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 권할 수 있어?</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr"/>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리 리허설</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
-      <c r="C155" s="4" t="n">
+      <c r="C155" s="16" t="n">
         <v>154</v>
       </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>이 고객 전반적으로 다 정리해서 알려줘</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr"/>
-      <c r="F155" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G155" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
-        </is>
-      </c>
-      <c r="I155" s="6" t="inlineStr"/>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 디폴트옵션 설정돼 있어?</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr"/>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr">
+        <is>
+          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="n"/>
       <c r="B156" s="9" t="n"/>
-      <c r="C156" s="4" t="n">
+      <c r="C156" s="16" t="n">
         <v>155</v>
       </c>
-      <c r="D156" s="12" t="inlineStr">
-        <is>
-          <t>(도구가 죽는 상황)</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
-          <t>장애</t>
-        </is>
-      </c>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>「확인하지 못했습니다」 + 원인 ↔ 「자료를 찾지 못했습니다」로 나간다(있는 자료를 없다고)</t>
-        </is>
-      </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
-        </is>
-      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 만기 뭐뭐 있어?</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr"/>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="9" t="n"/>
       <c r="B157" s="9" t="n"/>
-      <c r="C157" s="4" t="n">
+      <c r="C157" s="16" t="n">
         <v>156</v>
       </c>
-      <c r="D157" s="12" t="inlineStr">
-        <is>
-          <t>(상담기록 저장소를 못 읽는 상황)</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr"/>
-      <c r="F157" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>장애</t>
-        </is>
-      </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>「확인하지 못했다」 ↔ 「기록이 없습니다」로 답한다</t>
-        </is>
-      </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
-        </is>
-      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상이야?</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr"/>
+      <c r="F157" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr">
+        <is>
+          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
-      <c r="C158" s="4" t="n">
+      <c r="C158" s="16" t="n">
         <v>157</v>
       </c>
-      <c r="D158" s="12" t="inlineStr">
-        <is>
-          <t>(LLM 미연결 상황)</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>장애</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>「LLM 연결이 안 됐다」 + 원인 ↔ 「자료가 없습니다」로 답한다</t>
-        </is>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>[장애 상황 — 손으로 재현한다]</t>
-        </is>
-      </c>
+      <c r="D158" s="17" t="inlineStr">
+        <is>
+          <t>지난 상담에서 무슨 얘기 했지?</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr"/>
+      <c r="F158" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr">
+        <is>
+          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
+        </is>
+      </c>
+      <c r="I158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
-      <c r="C159" s="4" t="n">
+      <c r="C159" s="16" t="n">
         <v>158</v>
       </c>
-      <c r="D159" s="12" t="inlineStr">
-        <is>
-          <t>(고객 연 직후 첫 질문)</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr"/>
-      <c r="F159" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H159" s="6" t="inlineStr">
-        <is>
-          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
-        </is>
-      </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>300만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr"/>
+      <c r="F159" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="inlineStr">
+        <is>
+          <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
+        </is>
+      </c>
+      <c r="I159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
-      <c r="C160" s="4" t="n">
+      <c r="C160" s="16" t="n">
         <v>159</v>
       </c>
-      <c r="D160" s="12" t="inlineStr">
-        <is>
-          <t>(화면번호 여러 개가 나오는 절차 질문)</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr"/>
-      <c r="F160" s="25" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>일부만 인용해도 통과 ↔ 여섯 개를 맞게 인용한 답이 폐기되고 원문 덤프</t>
-        </is>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr"/>
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>박지민16 154821-4938201.5 ↔ 한지우13 176903-5528417.2</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="inlineStr">
+        <is>
+          <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
+        </is>
+      </c>
+      <c r="I160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
-      <c r="C161" s="4" t="n">
+      <c r="C161" s="16" t="n">
         <v>160</v>
       </c>
-      <c r="D161" s="12" t="inlineStr">
-        <is>
-          <t>(기준시점이 기간으로 적힌 카드를 쓰는 질문)</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="25" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 라이브러리 리허설</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>기간 표기를 풀어 써도 통과 ↔ 숫자가 맨숫자로 남아 폐기된다</t>
-        </is>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr"/>
+      <c r="F161" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="inlineStr">
+        <is>
+          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
+        </is>
+      </c>
+      <c r="I161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="n"/>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="4" t="n">
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="16" t="n">
         <v>161</v>
       </c>
-      <c r="D162" s="12" t="inlineStr">
-        <is>
-          <t>(기준시점이 표시에만 있는 카드를 쓰는 질문)</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="25" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 대본 리허설</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>표시도 인용 허용 ↔ 「2025.03.31 기준」이 자료 밖 날짜로 폐기된다</t>
-        </is>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="D162" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 연금개시 할 수 있어?</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr"/>
+      <c r="F162" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="inlineStr">
+        <is>
+          <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
+        </is>
+      </c>
+      <c r="I162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="9" t="n"/>
-      <c r="B163" s="15" t="inlineStr">
-        <is>
-          <t>26. 고객별 대조</t>
-        </is>
-      </c>
+      <c r="B163" s="9" t="n"/>
       <c r="C163" s="16" t="n">
         <v>162</v>
       </c>
       <c r="D163" s="17" t="inlineStr">
         <is>
-          <t>이 고객한테 뭘 권할 수 있어?</t>
+          <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
       <c r="E163" s="18" t="inlineStr"/>
-      <c r="F163" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+      <c r="F163" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G163" s="18" t="inlineStr">
         <is>
-          <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
+          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
       <c r="H163" s="18" t="inlineStr">
         <is>
-          <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
+          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
       <c r="I163" s="18" t="inlineStr"/>
@@ -5693,325 +5631,93 @@
       </c>
       <c r="D164" s="17" t="inlineStr">
         <is>
-          <t>이 고객 디폴트옵션 설정돼 있어?</t>
+          <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
       <c r="E164" s="18" t="inlineStr"/>
-      <c r="F164" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G164" s="18" t="inlineStr">
         <is>
-          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
+          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H164" s="18" t="inlineStr">
         <is>
-          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
+          <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n"/>
-      <c r="B165" s="9" t="n"/>
+      <c r="A165" s="10" t="n"/>
+      <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
       </c>
       <c r="D165" s="17" t="inlineStr">
         <is>
-          <t>이 고객 만기 뭐뭐 있어?</t>
+          <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
       <c r="E165" s="18" t="inlineStr"/>
-      <c r="F165" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+      <c r="F165" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 안 해본 질문</t>
         </is>
       </c>
       <c r="G165" s="18" t="inlineStr">
         <is>
-          <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
+          <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
       <c r="H165" s="18" t="inlineStr">
         <is>
-          <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
+          <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
       <c r="I165" s="18" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="9" t="n"/>
-      <c r="B166" s="9" t="n"/>
-      <c r="C166" s="16" t="n">
-        <v>165</v>
-      </c>
-      <c r="D166" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상이야?</t>
-        </is>
-      </c>
-      <c r="E166" s="18" t="inlineStr"/>
-      <c r="F166" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G166" s="18" t="inlineStr">
-        <is>
-          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
-        </is>
-      </c>
-      <c r="H166" s="18" t="inlineStr">
-        <is>
-          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I166" s="18" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="n"/>
-      <c r="B167" s="9" t="n"/>
-      <c r="C167" s="16" t="n">
-        <v>166</v>
-      </c>
-      <c r="D167" s="17" t="inlineStr">
-        <is>
-          <t>지난 상담에서 무슨 얘기 했지?</t>
-        </is>
-      </c>
-      <c r="E167" s="18" t="inlineStr"/>
-      <c r="F167" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G167" s="18" t="inlineStr">
-        <is>
-          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
-        </is>
-      </c>
-      <c r="H167" s="18" t="inlineStr">
-        <is>
-          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
-        </is>
-      </c>
-      <c r="I167" s="18" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="9" t="n"/>
-      <c r="B168" s="9" t="n"/>
-      <c r="C168" s="16" t="n">
-        <v>167</v>
-      </c>
-      <c r="D168" s="17" t="inlineStr">
-        <is>
-          <t>300만원 더 넣으면 얼마 돌려받아?</t>
-        </is>
-      </c>
-      <c r="E168" s="18" t="inlineStr"/>
-      <c r="F168" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G168" s="18" t="inlineStr">
-        <is>
-          <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H168" s="18" t="inlineStr">
-        <is>
-          <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
-        </is>
-      </c>
-      <c r="I168" s="18" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="9" t="n"/>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="D169" s="17" t="inlineStr">
-        <is>
-          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E169" s="18" t="inlineStr"/>
-      <c r="F169" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G169" s="18" t="inlineStr">
-        <is>
-          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
-        </is>
-      </c>
-      <c r="H169" s="18" t="inlineStr">
-        <is>
-          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
-        </is>
-      </c>
-      <c r="I169" s="18" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="9" t="n"/>
-      <c r="B170" s="9" t="n"/>
-      <c r="C170" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="D170" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 연금개시 할 수 있어?</t>
-        </is>
-      </c>
-      <c r="E170" s="18" t="inlineStr"/>
-      <c r="F170" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G170" s="18" t="inlineStr">
-        <is>
-          <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H170" s="18" t="inlineStr">
-        <is>
-          <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
-        </is>
-      </c>
-      <c r="I170" s="18" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="9" t="n"/>
-      <c r="B171" s="9" t="n"/>
-      <c r="C171" s="16" t="n">
-        <v>170</v>
-      </c>
-      <c r="D171" s="17" t="inlineStr">
-        <is>
-          <t>판매중단된 펀드 뭐 들고 있어?</t>
-        </is>
-      </c>
-      <c r="E171" s="18" t="inlineStr"/>
-      <c r="F171" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G171" s="18" t="inlineStr">
-        <is>
-          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
-        </is>
-      </c>
-      <c r="H171" s="18" t="inlineStr">
-        <is>
-          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I171" s="18" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="9" t="n"/>
-      <c r="B172" s="9" t="n"/>
-      <c r="C172" s="16" t="n">
-        <v>171</v>
-      </c>
-      <c r="D172" s="17" t="inlineStr">
-        <is>
-          <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
-        </is>
-      </c>
-      <c r="E172" s="18" t="inlineStr"/>
-      <c r="F172" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G172" s="18" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
-        </is>
-      </c>
-      <c r="H172" s="18" t="inlineStr">
-        <is>
-          <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
-        </is>
-      </c>
-      <c r="I172" s="18" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="10" t="n"/>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="16" t="n">
-        <v>172</v>
-      </c>
-      <c r="D173" s="17" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 세미나 있어?</t>
-        </is>
-      </c>
-      <c r="E173" s="18" t="inlineStr"/>
-      <c r="F173" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 안 해본 질문</t>
-        </is>
-      </c>
-      <c r="G173" s="18" t="inlineStr">
-        <is>
-          <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
-        </is>
-      </c>
-      <c r="H173" s="18" t="inlineStr">
-        <is>
-          <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
-        </is>
-      </c>
-      <c r="I173" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="B127:B138"/>
+    <mergeCell ref="A127:A165"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A45:A79"/>
+    <mergeCell ref="B109:B112"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A103:A126"/>
+    <mergeCell ref="B34:B40"/>
+    <mergeCell ref="B41:B48"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A80:A105"/>
-    <mergeCell ref="B142:B150"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B130:B141"/>
-    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="B154:B165"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="B139:B147"/>
+    <mergeCell ref="B59:B63"/>
     <mergeCell ref="B31:B33"/>
-    <mergeCell ref="A106:A129"/>
-    <mergeCell ref="B62:B66"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B90:B94"/>
-    <mergeCell ref="B119:B124"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="B151:B162"/>
-    <mergeCell ref="A130:A173"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B163:B173"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="B77:B86"/>
+    <mergeCell ref="B116:B121"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="A2:A40"/>
+    <mergeCell ref="A41:A76"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B92:B97"/>
     <mergeCell ref="B18:B26"/>
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B95:B100"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="A77:A102"/>
+    <mergeCell ref="B98:B102"/>
+    <mergeCell ref="B125:B126"/>
     <mergeCell ref="B6:B17"/>
-    <mergeCell ref="B80:B89"/>
+    <mergeCell ref="B49:B58"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6040,52 +5746,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>고객</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>kb-pin</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>나이</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>성향</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>ISA</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>상담기록</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>잔여한도</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>디폴트옵션</t>
         </is>
       </c>
-      <c r="I1" s="26" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>만기건수</t>
         </is>
       </c>
-      <c r="J1" s="26" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>성립 요건</t>
         </is>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -651,9 +651,9 @@
         <is>
           <t>● 송도윤
 송도윤 고객님이 관리 대상으로 뜬 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 있으나, 358일간 접촉 이력이 없어 장기 미접촉 상태에 있기 때문이에요. 또한 판매중단된 KB 퇴직연금 배당(주식) 상품을 보유하고 있고, 고유계정대인 현금성자산을 방치 중이며, 디폴트옵션이 미설정 상태예요. 그 밖에 운용변경이 12개월 이상 없었고, ISA 만기자금을 보유하고 있으며, 당해 납입액이 0원인 상태예요.
-● 송도윤
+● 정민석
 공격투자형 성향이신 정민석 고객님은 221일간 장기 미접촉 상태가 이어지고 있으며, 투자성향과 포트폴리오 간의 불일치가 발생하여 관리 대상으로 선정되었어요. 세부적으로는 현재 위험자산 비중이 0%로 원리금보장 및 현금성 자산이 100%를 차지하고 있으며, 12개월 이상 운용변경이 없는 상태입니다. 이로 인해 전체 운용수익률은 3.1%에 머물러 동연령대 평균 수익률(7.5%) 및 상위 1% 평균 수익률(20.3%)과 큰 격차를 보이고 있어요.
-● 송도윤
+● 이수민
 현재 평가금액 8,000만원 중 원리금보장형과 고유계정대가 100%를 차지하여 위험자산 비중이 0%로 편중되어 있고, 오는 2026년 10월 17일에 7,000만원 규모의 예금 만기가 도래할 예정이기 때문에 관리 대상으로 선정되었어요. 또한 원리금보장상품 편중(80% 이상), 디폴트옵션 미설정, 만기예금 보유, 세액공제 활용 가능, 추가입금 여력 보유 항목이 성립 요건에 해당해요.</t>
         </is>
       </c>
@@ -753,7 +753,7 @@
 공격투자형 성향이신 정민석 고객님은 현재 위험자산 비중이 0%로, 원리금보장·현금성 자산이 100%를 차지하며 성향과 포트폴리오 간의 불일치가 발생하고 있습니다.
 이로 인해 전체 운용수익률은 3.1%에 머물러 동연령대 평균 수익률(7.5%) 및 상위 1% 평균 수익률(20.3%)과 큰 격차를 보이고 있습니다.
 또한 12개월 이상 운용변경이 없고 6개월 이상 장기 미접촉 상태가 지속되면서 관리가 필요한 상황입니다.
-● 정민석
+● 송도윤
 송도윤 고객님의 성향과 실제 운용이 맞지 않는다고 보는 이유는 위험중립형 성향이신데도 고유계정대 2억 8,000만원이 현금성자산으로 방치되어 있기 때문이에요. 또한 12개월 이상 운용변경이 없고 디폴트옵션도 설정되지 않은 상태이며, 판매중단 상태인 KB 퇴직연금 배당 (주식) 상품을 보유하고 계세요. 
 고객에게 안내할 때는 고유계정대라는 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰도록 하세요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지는 말고, 운용 여건의 차이를 중심으로 설명해야 해요.</t>
         </is>
@@ -827,7 +827,7 @@
         <is>
           <t>● 김현수
 고유계정대 금액은 600만 원이고 비중은 75.0%예요. 고객에게 안내할 때는 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 주세요.
-● 김현수
+● 송도윤
 송도윤 고객님의 고유계정대는 2억 8,000만원이며, 자산군별 비중은 53.8%예요. 고객에게 안내할 때는 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 주세요.</t>
         </is>
       </c>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
 (LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 2 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
 응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gem…)</t>
         </is>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -925,7 +925,14 @@
           <t>이 고객 만기 언제고 금액은 얼마야?</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>● 오세훈
+만기 예정인 예금은 2026년 10월 9일 도래하는 7,040만 원의 SBI저축은행 퇴직연금 정기예금 1년 건이 있고, GIC는 2027년 1월 10일에 3,550만 원 규모로 만기가 도래해요.
+● 이수민
+이수민 고객님의 만기일은 2026년 10월 17일이며, 해당 예금 금액은 7,000만원이다. 만기가 18일 앞으로 다가온 상태이니 만기 전 운용 방향을 확정할 수 있도록 안내해야 한다.</t>
+        </is>
+      </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -954,7 +961,16 @@
           <t>이 고객 ISA 만기가 언제고 얼마짜리야?</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+김서연 고객의 타행 ISA 만기자금은 2026년 9월 30일 만기인 8,000만원이에요.
+● 한지우
+한지우 고객님의 ISA 만기일은 2026년 9월 5일이고, 금액은 8,000만원이에요. 이 자금은 타행 ISA 만기자금이며 만기가 경과한 지 24일이 되었어요.
+● 송도윤
+송도윤 고객님의 ISA 만기 자금은 2026년 9월 20일에 만기가 경과한 1억 2,000만원이에요. IRP 외부 계좌로 보유 중인 자금으로, 만기 경과 9일째인 상태예요.</t>
+        </is>
+      </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -5731,7 +5747,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -999,7 +999,11 @@
           <t>올해 얼마 넣었고 잔여한도는 얼마 남았어?</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr"/>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>당해 납입액은 0원이고 세액공제 잔여한도는 900만원이 남았어요. 연 납입한도 1,800만원 중 당해 납입액이 없어 1,800만원의 납입 여력이 있는 상태예요. 세액공제 한도 900만원에 미달하는 고객인 만큼, 세액공제 잔여한도 900만원을 확인한 뒤 자동이체 금액 증액을 제안하거나 여유자금 발생 시점의 추가입금으로 예약을 남기는 순서로 설계해 보세요.</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1028,7 +1032,16 @@
           <t>판매중단된 펀드 뭐 들고 있고 지금 손실이 얼마나 나 있어?</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr"/>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>● 최서윤
+판매중단된 상품으로는 KB 코리아밸류업액티브 (주식)를 보유하고 있고, 해당 상품의 수익률은 -38.7%예요. 전체 운용수익률은 -9.4%를 기록하고 있어요.
+● 송도윤
+송도윤 고객님이 보유 중이신 판매중단 펀드는 수익률 정보와 함께 다음과 같아요.
+- KB 퇴직연금 배당 (주식) — 수익률 60.0%
+참고로 이 고객은 사용자부담금(퇴직급여) 5억 2,000만원 전액이 고유계정대(현금성자산)로 2억 8,000만원, 수익증권 1억 2,400만원, ETF 1억 1,600만원으로 구성되어 있어요. 판매중단 펀드인 KB 퇴직연금 배당 (주식) 외에 RISE 미국나스닥100 ETF(수익률 65.7%), 하나 파이팅 코리아 (주식)(수익률 46.7%)도 함께 보유 중이에요.</t>
+        </is>
+      </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -1057,7 +1070,13 @@
           <t>최근 한 달 사이에 고유계정대가 얼마나 늘었어?</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: fact:고유계정대 최근 한 달 증가액
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1086,7 +1105,11 @@
           <t>이 고객 퇴직급여랑 개인부담금이 각각 얼마야?</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 퇴직급여와 개인부담금은 사용자부담금(퇴직급여) 5억 2,000만원, 가입자부담금(개인부담금) 0원이에요.</t>
+        </is>
+      </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1115,7 +1138,12 @@
           <t>같은 또래 평균이랑 비교하면 이 고객은 어떤 편이야?</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr"/>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님은 72세 연령대 평균 수익률과 비교했을 때 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 크게 상회하고 계세요. 
+비교그룹 운용현황은 [06-12-631] 고객포털에서, 추천 포트폴리오는 WiseNet에서 준비해 상담 근거자료를 만들어 활용할 수 있어요. 수익률 하위 고객에게 "같은 연령대는 이렇게 운용한다"는 비교 상담을 하려면 [06-12-631] 퇴직연금 고객포털의 '퇴직연금 컨설팅'에서 비교그룹 상품운용현황을 조회하면 돼요. 제안할 상품은 KB-WiseNet/Info-zone의 실적배당상품 메뉴인 펀드정보와 추천펀드 및 포트폴리오에서 준비할 수 있어요. 단말의 고객 현황과 WiseNet의 제안 상품, 고객포털의 비교군까지 3개 소스를 상담 전에 묶는 구조로 준비해 보세요.</t>
+        </is>
+      </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1144,7 +1172,14 @@
           <t>운용변경 안 한 지 얼마나 됐어?</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr"/>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>● 정민석
+운용변경 이력이 없는 기간은 12개월 이상이에요. 221일간 접촉 이력이 없고 최근 12개월 이상 운용변경 이력이 없는 상태예요.
+● 송도윤
+송도윤 고객이 운용변경을 하지 않은 기간은 12개월 이상이에요. 358일간 접촉 이력이 없으며 최근 운용지시는 2025년 7월 18일에 이루어졌어요. 장기간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으니, 유선 접촉을 통해 관계를 회복해야 해요. 만일 현금성자산(고유계정대)을 방치 중인 상황이라면 운용지시나 리밸런싱을 안내할 수 있어요.</t>
+        </is>
+      </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1177,7 +1212,11 @@
           <t>이 고객 디폴트옵션 설정돼 있어?</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>박정호 고객님은 디폴트옵션 설정이 되어 있어요. IRP 안에서 이미 디폴트옵션이 등록되어 있는 고객이므로, 만약 보유상품을 변경하시거나 사전지정운용제도를 다시 등록하실 경우에는 사전지정운용제도 등록 및 변경과 기존 매도 후 신규 매수로 이어지는 2단계 거래가 필요하다는 점을 안내해 드릴 수 있어요.</t>
+        </is>
+      </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -1202,7 +1241,12 @@
         <v>18</v>
       </c>
       <c r="D19" s="10" t="n"/>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>디폴트옵션은 현재 설정되어 있지 않아요.
+이수민 고객님은 현재 원리금보장·현금성 자산이 100%를 차지하고 있으며, 7,000만원 규모의 정기예금 만기가 2026년 10월 17일(D-18) 도래를 앞두고 있어요. 만기 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태이므로, 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 디폴트옵션 사전지정 등록 또는 만기 예약변경을 권유해 보세요.</t>
+        </is>
+      </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1231,7 +1275,11 @@
           <t>이 고객 세액공제 잔여한도 얼마 남았어?</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>이수민 고객의 세액공제 잔여한도는 900만원이에요. 세액공제 한도 900만원에 미달하여 납입하고 있는 상태이므로, 당행과 타행의 합산 잔여한도를 먼저 확인하고 자동이체 금액 증액을 제안해 보세요. 거절할 경우 여유자금 발생 시점의 추가입금으로 예약을 남기는 순서로 설계해 주시면 돼요.</t>
+        </is>
+      </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1260,7 +1308,11 @@
           <t>이 고객 세액공제 더 받을 수 있어?</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객이 세액공제를 더 받을 수 있는지 묻는 질문에는 총급여 구간에 따른 세액공제 환급액 기준으로 안내드리면 돼요. 현재 이 고객의 개인형IRP 계좌 추가 납입분은 세액공제 잔여한도가 0원이어서 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않아요. 다만 ISA 만기자금을 개인형IRP로 전환하는 경우라면 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 늘어나요. 총급여 5,500만원 이하인 경우 16.5% 공제율을 적용하면 전환액 1억 2,000만원 전액을 전환할 때 추가 공제 대상 300만원에 대해 495,000원의 환급액이 늘어나요. 총급여 5,500만원 초과인 경우 13.2% 공제율을 적용하면 추가 공제 대상 300만원에 대해 396,000원의 환급액이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않아요.</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -1289,7 +1341,14 @@
           <t>이 고객 연금개시 할 수 있는 상태야?</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>● 오세훈
+연금개시 요건을 충족했으나 아직 개시하지 않은 상태예요. 2018년 2월 19일에 IRP에 가입해 가입 후 8.6년이 경과했고 연령도 만 61세로 요건을 모두 채웠어요. 연금개시를 진행할 때는 세액 미공제 한도 등록 후 연금지급 등록의 2단계로 처리하며, 개시 전에 세금우대 조회로 이전 가능한 상품이 있는지 먼저 확인해야 해요.
+● 박정호
+박정호 고객님은 연금개시 요건을 충족했으나 아직 연금개시를 하지 않은 상태예요. 연금개시를 미루는 고객에게는 "고객님. 지금은 퇴직금을 꺼내 쓰시기보다, 자산을 늘려나가야 하는 시기입니다. IRP 안에서 운용수익에 대해선 과세가 되지 않는 만큼 계속 운용하면서 복리효과를 더 누리시는 게 좋습니다"라고 예상 반론 대응을 활용해 안내해 보세요.</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1314,7 +1373,11 @@
         <v>22</v>
       </c>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님은 아직 연금개시요건을 충족하지 못해 연금개시를 할 수 있는 상태가 아니에요. 현재 연금개시가 미개시 상태로 등록되어 있으니 이 점을 먼저 확인하고 안내해 주세요.</t>
+        </is>
+      </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1343,7 +1406,11 @@
           <t>이 고객 ISA 만기자금 갖고 있어?</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>박지민 고객님은 ISA 만기자금 보유 내역이 없어요.</t>
+        </is>
+      </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1372,7 +1439,11 @@
           <t>이 고객 판매중단 상품 들고 있는 거 있어?</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>판매중단 보유상품은 없어요.</t>
+        </is>
+      </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1401,7 +1472,11 @@
           <t>이 고객 계좌 가입일이 언제고 몇 년 됐어?</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 IRP 가입일은 2023년 10월 2일이며, 가입 후 3.0년이 지났어요.</t>
+        </is>
+      </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1434,7 +1509,11 @@
           <t>지난 상담에서 무슨 얘기 했는지 알려줘</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr"/>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서 고객은 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 밝혔어요. 지난 기록인 만큼 지금의 상황과는 다를 수 있으니 참고해서 상담을 진행해 주세요.</t>
+        </is>
+      </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -1459,7 +1538,16 @@
         <v>27</v>
       </c>
       <c r="D28" s="10" t="n"/>
-      <c r="E28" s="18" t="inlineStr"/>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>● 김현수
+이 고객과의 지난 상담 기록은 아직 등록된 내용이 없어요. 기록이 없는 상태이므로 별도의 지난 상담 이력을 안내해 드릴 수 있는 내용은 아직 준비된 자료가 없어요.
+● 김서연
+이 고객과의 지난 상담 기록은 0건으로, 확인되는 이전 상담 이력이 없어요. 지금 진행 중인 이번 상담을 제외하고는 쌓인 기록이 없어서 안내해 드릴 내용이 없어요.
+● 이수민
+고객과의 지난 상담 기록은 아직 등록된 내용이 없어요. 시스템상 이 고객에 대한 이전 상담 이력이 0건으로 조회되니 이 점 참고해서 이번 상담을 진행하면 돼요.</t>
+        </is>
+      </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -1488,7 +1576,11 @@
           <t>지난 상담 내용 참고해서 오늘 뭐라고 말하면 좋을지 알려줘</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr"/>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶어 하셨어요. 그때 나눈 이야기인 만큼 오늘 대화에서는 지금 고객의 자산 상황이나 투자 의향이 그때와 같은지 단말에서 먼저 확인해 보고 말씀을 이어가야 해요.</t>
+        </is>
+      </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -1517,7 +1609,11 @@
           <t>그때 안내한 금리가 지금도 맞는 거야?</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr"/>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>원리금보장상품 금리는 매월 변경되므로 어떤 자료의 수치도 고정 팩트로 쓸 수 없다. 상담 전 [04-12-17A] New퇴직연금상품조회와 월별 특별제공상품 자료에서 당월 상품·금리·잔여한도를 확인하는 것이 유일하게 정확한 안내다. "일반은행 → 저축은행/GIC 갈아타기로 금리 상향"이라는 논리 구조만 시점 무관하게 유효하다. 기준시점 상시. 이 내용은 고객에게 그대로 안내하지는 마세요.</t>
+        </is>
+      </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1550,7 +1646,11 @@
           <t>이 고객 상담 들어가기 전에 뭘 준비해두면 좋을까?</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님과의 상담을 시작하기 전에 단말에서 확인된 고객 현황과 제안 근거 자료를 미리 준비해 두어야 해요. 비교그룹 운용현황은 고객포털에서, 추천 포트폴리오는 WiseNet에서 준비해 상담 근거자료를 만드세요. 구체적으로는 단말에서 확인한 고객 현황과 WiseNet의 제안 상품, 그리고 고객포털의 비교군 정보를 사전에 묶어두는 것이 필요해요. 관리 사각지대 고객이자 장기간 접촉 이력이 없는 상태이므로, 유선 접촉을 통해 관계를 회복해야 해요.</t>
+        </is>
+      </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -1579,7 +1679,11 @@
           <t>이 고객 상태에 걸린 참고자료 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 상태에 걸려 있는 참고 자료는 대기 현금성자산 보유 고객(금액 기준), 디폴트옵션 미지정(미동의) 고객(만기 조건 없는 전수 대상), 성과저조(환매추천) 펀드 보유 고객, 관리 사각지대 고객(무권유 비대면 신규 / 전담직원 관리 미비), 전년 납입 있었으나 당해 미납인 고객(납입 중단 신호), ISA 만기(예정)·만기해지 자금 보유 고객까지 총 6건이에요. 자료에 따르면 358일간 접촉 이력이 없어 관리 사각지대 및 장기 미접촉 상태에 해당하며, 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 계시고 고유계정대 2억 8,000만원의 현금성자산을 보유 중인 점 등이 함께 확인돼요.</t>
+        </is>
+      </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1608,7 +1712,12 @@
           <t>(화법 제안 뒤) 네, 보여줘</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>보유하신 퇴직연금 DC, 기업형 IRP, 개인형 IRP 계좌에 운용지시가 안 된 현금성자산이 000만원 있는데 알고 계신가요? 하고 물어볼 수 있도록 현금성자산 운용지시와 리밸런싱을 권유하는 첫 번째 화법을 활용할 수 있어요. 고객이 어떻게 하면 되냐고 물어보면 은행에 내점하실 필요 없이, 스타뱅킹에서 운용지시를 하실 수 있습니다. 고객님, 스타뱅킹이나 인터넷뱅킹은 사용하고 계시죠? 라고 안내해 드릴 수 있어요. 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.
+만기 1개월 내 원리금보장상품을 보유하고 디폴트옵션에 등록하지 않은 고객이라면 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 사전지정 등록을 권유하는 두 번째 화법을 쓸 수 있어요. 사용계획이 있는 자금인지 먼저 확인하고 접근하는 것이 중요해요.</t>
+        </is>
+      </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
@@ -1645,7 +1754,20 @@
           <t>이 고객한테 하면 안 되는 게 뭐야?</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr"/>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>위험중립형 성향인 이 고객에게는 보통위험 등급까지만 안내할 수 있어요. 안내할 수 있는 상품은 다음 8종뿐이에요.
+- KB 글로벌채권인덱스 C-P — 보통위험
+- KB 국내채권형 C-P — 낮은위험
+- KB 안정형 MP — 낮은위험
+- KB 중립형 MP — 보통위험
+- KB GIC 확정금리 — 매우낮은위험
+- KB ELB 지수연계 — 낮은위험
+- KB 정기예금(1년) — 매우낮은위험
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험
+다소높은위험 등급인 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP와 높은위험 등급인 KB 글로벌리츠 ETF는 상품 위험등급이 고객의 허용 상한인 보통위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이지 투자권유가 아니라는 점을 유의해야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -1796,7 +1796,15 @@
           <t>이 고객 세액공제 더 받게 추가납입 권해도 돼?</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr"/>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>● 오세훈
+세액공제 추가납입은 권할 수 없어요. 이 고객의 세액공제 잔여한도가 0원이기 때문이에요.
+● 박정호
+이 고객에게는 남은 세액공제 한도 활용을 위해 추가 납입을 제안하는 것이 핵심이에요. 2026년 3월 자료 기준으로 총급여 5,500만원 초과 기준 공제율은 13.2%가 적용되며, 세액공제 잔여한도는 600만원까지 남아 있어 추가 절세 혜택을 챙길 수 있습니다. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못할 수 있으니 유의해야 합니다.
+전년도 세액공제 한도 미소진 사실을 확인해 알려주고 자동이체 금액 증액을 제안할 때는 이렇게 말씀해 보세요. "세액공제 한도 납입 — 전년도 세액공제 한도 미소진 사실을 확인해 알려주고 자동이체 금액 증액을 제안한다." 거절 시에도 여지를 남기는 짧은 클로징이 원문에 같이 붙어 있습니다.</t>
+        </is>
+      </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -1825,7 +1833,11 @@
           <t>이 고객 연금개시 요건도 충족했던데, 개시까지 같이 진행하면 걸리는 거 없어?</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr"/>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>박정호 고객님은 연금개시 요건을 충족하고 있으나 연금개시가 미개시 상태인 고객으로, 연금개시 진행 시 만 55세 아직 멀었어요 같은 반론이 나올 수 있음에 유의해야 한다. 연금개시를 안내할 때는 "고객님. 지금은 퇴직금을 꺼내 쓰시기보다, 자산을 늘려나가야 하는 시기입니다. IRP 안에서 운용수익에 대해선 과세가 되지 않는 만큼 계속 운용하면서 복리효과를 더 누리시는 게 좋습니다."라는 대응 논리를 활용할 수 있다. 사용계획 있는 자금은 먼저 걸러내야 하며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 한다.</t>
+        </is>
+      </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -1854,7 +1866,20 @@
           <t>이 고객한테 어떤 펀드 넣어주면 되는지 딱 집어줘</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr"/>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>위험중립형 고객에게는 적합성 허용 상한인 보통위험 등급 이하의 상품만 안내할 수 있으며, 이 고객의 성향에 맞는 상품을 정해서 권유하는 대신 단말에서 확인 가능한 상품 목록을 바탕으로 안내해 드려야 해요. 현재 고객의 적합성 허용 상한은 보통위험이며, 이에 따라 안내할 수 있는 상품과 안내할 수 없는 상품이 구분돼요.
+- KB 글로벌채권인덱스 C-P — 채권형, 보통위험, 최근 1년 4.8%
+- KB 국내채권형 C-P — 채권형, 낮은위험, 최근 1년 3.8%
+- KB 안정형 MP — MP, 낮은위험, 최근 1년 3.9%
+- KB 중립형 MP — MP, 보통위험, 최근 1년 5.1%
+- KB GIC 확정금리 — GIC, 매우낮은위험, 최근 1년 3.65%
+- KB ELB 지수연계 — ELB, 낮은위험, 최근 1년 4.1%
+- KB 정기예금(1년) — 예금, 매우낮은위험, 최근 1년 3.1%
+- KB 원리금보장 안정 포트폴리오 — MP, 매우낮은위험, 최근 1년 3.3%
+안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 안내 대상에서 제외돼요. 이 안내는 적합성 확인 결과에 따른 것이며 특정 상품에 대한 투자권유를 의미하지 않아요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -1883,7 +1908,11 @@
           <t>이 고객 재취업할 것 같아?</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr"/>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 재취업 여부나 고용 상태에 대해서는 현재 보유하신 자료에 확인되는 내용이 없어요. 재취업 관련 사항은 아직 준비된 자료가 없어요.</t>
+        </is>
+      </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1912,7 +1941,12 @@
           <t>이 고객 디폴트옵션 등록됐어?</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr"/>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님은 디폴트옵션이 미설정 상태예요. 
+디폴트옵션 미지정 고객에게는 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 이렇게 말해 보세요. "여기서의 위험은 '데인저러스'가 아니고 '리스크'입니다. 리스크가 곧 변동성이거든요"라고 설명하며 용어에 대한 부담을 없애고, 연금사업자가 자기 이름을 걸고 운용하므로 관리에 신경 쓴다는 점을 함께 안내해 주세요. 고유계정대 2억 8,000만원을 보유하고 계시므로, 현금성자산 운용지시나 리밸런싱을 권유할 때 디폴트옵션 가입을 함께 유도하는 방향으로 활용할 수 있어요.</t>
+        </is>
+      </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -1941,7 +1975,11 @@
           <t>(더미 자산 문구로) 이 문구 발송 화면에 넣어줘</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr"/>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>어떤 문구를 보낼지 큰따옴표로 감싸서 알려주시겠어요? (예: "..." 로 LMS 보내줘)</t>
+        </is>
+      </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -2017,7 +2055,11 @@
           <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>고객이 중도해지나 중도인출 시 적용되는 세금을 물을 때에는 2026년 6월 기준 자료를 바탕으로 정확한 과세 방식을 짚어주어야 해요. 중도인출은 일시금 수령과 동일하게 기타소득세 16.5%(지방소득세 포함) 가 부과되고, 중도해지 시에도 세액공제 받은 납입원금·운용수익에 기타소득세 16.5%만 분리과세된다. 이 부담은 납입 시 세액공제(16.5%)와 크거나 같아, 공제받은 고객이 중도인출하면 혜택이 상쇄된다. 연금수령한도 초과 인출분도 소득원천별(퇴직소득세·기타소득세)로 과세된다. 기준시점 2026.06 (KBthink 01 일치) 내용을 안내해 드려요. 과세 대상은 세액공제 받은 원금과 운용수익에 한정되며, 세액공제를 받지 않은 과세제외분은 제외된다는 점을 함께 확인해 주세요.</t>
+        </is>
+      </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -2046,7 +2088,11 @@
           <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>IRP 중도인출은 법정 사유에 한해 가능하다. 2026년 6월 기준으로 무주택자 주택구입(매매계약 체결일~소유권 이전 등기 접수일 후 1개월 이내 신청), 무주택자 전세금·임차보증금(계약 체결일~잔금 지급일 후 1개월 이내, 하나의 사업장 근무 중 1회 한정), 본인·배우자·부양가족의 6개월 이상 요양(연간 임금총액의 12.5% 초과 의료비 부담 시), 자연재난·특별재난지역 사회재난 피해, 5년 이내 개인회생절차 개시 결정, 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 최대 90%까지 일부 인출할 수 있으며 횟수 제한은 없다. 다만 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다.</t>
+        </is>
+      </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
@@ -2075,7 +2121,11 @@
           <t>수수료 얼마야?</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>사용자부담금 대면 계좌 기준으로 안내드리면, 2026년 3월 기준 개인형IRP 수수료율은 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%가 적용돼요. 단일 수치로 안내하면 오답이 될 수 있으므로 단말에서 부담금 종류와 채널, 금액 구간을 먼저 확인하고 안내해 주세요.</t>
+        </is>
+      </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본 리허설</t>
@@ -2100,7 +2150,13 @@
         <v>44</v>
       </c>
       <c r="D45" s="10" t="n"/>
-      <c r="E45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>어느 부담금인가요?
+· 사용자부담금
+· 가입자부담금</t>
+        </is>
+      </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
@@ -2129,7 +2185,13 @@
           <t>타행 IRP 수수료는 우리보다 싼가?</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: fact:타행 IRP 수수료 · pitch:타행 IRP 수수료는 우리보다 싼가
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본 리허설</t>
@@ -2193,7 +2255,12 @@
           <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>총급여 5,500만원 이하 공제율 16.5%, 적금 이율 3.50% 가정, 이자소득세 15.4% 원천징수 전이라는 전제를 함께 짚어주면서 세액공제 환급액을 적금 이자와 같은 단위로 환산하는 방식을 활용하는 것이 좋아요. 
+"월 75만원 적립 = 적금 월 790만원" 비유를 사용해 세액공제 환급액을 적금 이자와 같은 단위로 환산하면 적금보다 10배 이상 차이 난다는 점을 쉽게 체감시킬 수 있어요.</t>
+        </is>
+      </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -2226,7 +2293,11 @@
           <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
         </is>
       </c>
-      <c r="E49" s="18" t="n"/>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>이수민 고객의 총급여 구간이 확인되지 않아 두 가지 경우를 모두 살펴봐야 하니, 단말에서 총급여 구간을 먼저 확인한 뒤에 안내해 주세요. 개인형IRP 계좌 추가 납입액 300만원을 넣을 때, 총급여 5,500만원 이하로 적용 공제율 16.5%가 확인되면 환급 예상액은 0원에서 495,000원으로 늘어나며 늘어나는 금액은 495,000원이에요. 총급여 5,500만원 초과로 적용 공제율 13.2%가 확인되면 환급 예상액은 0원에서 396,000원으로 늘어나며 늘어나는 금액은 396,000원이에요. 이 고객의 잔여한도는 연금저축 납입분까지 합산한 값으로 900만원이 남아 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2255,7 +2326,11 @@
           <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E50" s="18" t="n"/>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
+        </is>
+      </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2284,7 +2359,14 @@
           <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E51" s="18" t="n"/>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>현금을 더 납입하는 경우를 기준으로 안내드리면, 이 고객의 개인형IRP 계좌 추가 납입액 300만원에 대해 더 돌려받는 환급액은 없다. 
+이 고객은 당해 납입액이 0원이고 세액공제 한도 900만원과 잔여한도가 0원이라 추가 공제 대상이 없기 때문이다. 
+세액공제 잔여한도가 0원이라 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않으며, 세액공제 한도 900만원은 연금저축과 함께 쓴다. 단, 납입 자체는 연 납입한도 1,800만원까지 가능하다. 
+단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -2313,7 +2395,33 @@
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E52" s="18" t="n"/>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+김서연 고객에게는 8천만원 전부에 부담을 느낄 때 ISA 만기자금 전환액을 일부로 조정했을 때의 세액공제 적용 구조를 안내하는 게 핵심이에요. 개인형IRP 계좌 추가 납입 자료와 달리 ISA 만기자금을 전환하는 경우는 전환금의 10%가 세액공제 대상에 더해지며 300만원의 상한이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상인 8,000만원 전환 시 상한인 300만원이 적용돼요. 총급여 5,500만원 이하 구간인 16.5% 적용 시 전환액 8,000만원 기준으로 늘어나는 환급액은 495,000원이며, 총급여 5,500만원 초과 구간인 13.2% 적용 시 늘어나는 환급액은 396,000원이에요. 이 고객의 총급여 구간은 원장에 확인되지 않으므로 단말에서 소득 구간을 먼저 확인한 뒤 해당되는 환급 예상액을 안내해 주세요.
+● 한지우
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 8,000만원
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 이하(16.5%): 환급 예상 990,000원 → 1,485,000원 (늘어나는 금액 495,000원)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 송도윤
+송도윤 고객이 ISA 만기자금 8,000만원 중 일부만 IRP 계좌로 전환할 때의 세액공제 효과를 안내할 때는, 현금을 추가로 납입하는 경우와 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 별개의 축이라는 점을 짚어 주어야 해요. 현재 이 고객의 개인형IRP 계좌 추가 납입분은 세액공제 잔여한도가 0원이지만, ISA 만기자금 전환은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지며 상한은 300만원이므로, 8,000만원을 전환하면 상한인 300만원의 추가 공제 대상이 만들어져요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간에 따라 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 495,000원이고, 총급여 5,500만원 초과(13.2%)인 경우 늘어나는 환급액은 396,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않으며, 고객의 총급여 구간이 확인되지 않았으므로 두 경우를 모두 안내해 주세요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
+        </is>
+      </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -2342,7 +2450,16 @@
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E53" s="18" t="n"/>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+ISA 만기자금을 개인형IRP 계좌로 전환할 때는 현금을 더 납입하는 경우와 다른 한도가 적용되니 두 축을 구분해서 안내해야 해요. 고객의 정확한 총급여 구간이 원장에 확인되지 않아 두 가지 경우를 모두 고려해야 하므로, 총급여 5,500만원 이하(16.5%)라면 전환으로 늘어나는 환급 예상액은 495,000원이고, 총급여 5,500만원 초과(13.2%)라면 늘어나는 환급 예상액은 396,000원이에요. 이 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 개인형IRP 계좌에 넣을 수 있으며, 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 기존 900만원에서 최대 1,200만원으로 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않으며, 타행 ISA 만기일인 2026년 9월 30일로부터 60일 이내에 전환해야 해요.
+● 한지우
+ISA 만기자금 8,000만원을 개인형IRP 계좌로 전환할 때 받는 세액공제는 고객의 총급여 구간에 따라 달라지며, 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 적용돼요. 총급여 5,500만원 이하(16.5%)라면 이 전환으로 늘어나는 환급금은 495,000원이고, 총급여 5,500만원 초과(13.2%)라면 늘어나는 환급금은 396,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이며, 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 송도윤
+ISA 만기자금 8,000만원을 개인형IRP로 전환하는 고객에게는 총급여 5,500만원 이하(16.5%) 기준으로 환급액을 안내하는 게 핵심이에요. 송도윤 고객의 개인형IRP 계좌는 당해 납입액이 0원이고 세액공제 잔여한도도 0원이지만, ISA 만기자금 전환은 기존 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 다른 축이에요. 만기일로부터 60일 이내에 전환하면 전환금의 10%가 세액공제 대상에 더해지며 상한은 300만원이에요. 8,000만원을 전환하면 상한인 300만원이 추가 공제 대상이 되고, 총급여 5,500만원 이하 적용 시 이 전환으로 늘어나는 환급액은 495,000원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요.</t>
+        </is>
+      </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2488,7 +2488,30 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="n"/>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+총급여 5,500만원 초과 구간인 김서연 고객에게는 ISA 만기자금 8,000만원 중 일부인 3,000만원을 개인형IRP 계좌로 전환할 때의 환급액을 안내해 주는 게 핵심이에요. 3,000만원을 전환하면 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어나고, 적용 공제율 13.2% 기준 환급액 396,000원이 추가로 발생해요. 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상 전환 시 상한인 300만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+총급여가 5,500만원 초과인 고객에게는 ISA 만기자금 중 3,000만원 이상을 개인형IRP로 전환할 때 추가 공제 대상이 300만원으로 상한에 도달하며, 이 경우 늘어나는 환급 예상액은 396,000원이에요. 앞서 말씀드린 현금을 더 납입하는 경우와는 다른 축으로 별개로 더해지는 몫이므로, 만기자금 8,000만원 중 일부만 옮기는 경우에도 전환액의 10%에 해당하는 금액이 세액공제 대상에 더해져서 전환액 1,000만원이면 100만원, 2,000만원이면 200만원, 3,000만원 이상이면 300만원의 공제 대상 한도가 추가로 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않은 부분은 아직 준비된 자료가 없어요.
+● 송도윤
+■ 세액공제 환급 예상액 — 송도윤 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 0원 · 세액공제 한도 900만원 · 잔여한도 0원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 0원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 세액공제 잔여한도가 0원이라 **추가 공제 대상이 없다** — 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않는다 (세액공제 한도 900만원은 연금저축과 함께 쓴다. 납입 자체는 연 납입한도 1,800만원까지 가능하다)
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 1억 2,000만원 · 만기 2026-09-20 (만기 9일 경과 · 전환 기한 51일 남음) · 당행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 1억 2,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 1억 2,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
+        </is>
+      </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2521,7 +2544,50 @@
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr"/>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 400만원 · 세액공제 한도 900만원 · 잔여한도 500만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 500만원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 공제 대상 400만원 → 900만원 (잔여한도 500만원까지)
+· 총급여 5,500만원 이하(16.5%): 환급 예상 660,000원 → 1,485,000원 (늘어나는 금액 825,000원)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 528,000원 → 1,188,000원 (늘어나는 금액 660,000원)
+· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-30 (D-1) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 한지우
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 300만원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 이하(16.5%): 환급 예상 990,000원 → 1,485,000원 (늘어나는 금액 495,000원)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 송도윤
+세액공제 환급 예상액을 안내할 때 5,500만원 이하 소득 구간에서는 개인형IRP 계좌로 1억 2,000만원을 ISA 만기자금으로 전환할 때 추가 공제 대상 300만원이 적용되어 495,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 현금을 더 납입하는 경우와 달리 이 전환 금액은 서로 다른 한도로 별개로 더해지는 몫이에요.</t>
+        </is>
+      </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -2554,7 +2620,11 @@
           <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
         </is>
       </c>
-      <c r="E56" s="18" t="n"/>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>오늘 날짜는 2026년 9월 29일 월요일이고 2026년 연말까지는 오늘을 세지 않고 93일 남았어요. 세액공제를 받으려면 올해 12월 31일까지 납입해야 해요.</t>
+        </is>
+      </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2583,7 +2653,11 @@
           <t>이 고객 잔액은 언제 기준 값이야?</t>
         </is>
       </c>
-      <c r="E57" s="18" t="n"/>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>해당 고객의 잔액 기준 시점에 대한 자료는 아직 준비된 자료가 없어요.</t>
+        </is>
+      </c>
       <c r="F57" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -2612,7 +2686,11 @@
           <t>300 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E58" s="18" t="n"/>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 넣으면 적용받는 공제율에 따라 환급액이 달라져요. 총급여 5,500만원 이하인 경우 16.5%를 적용하여 개인형IRP 계좌 추가 납입으로 495,000원의 환급을 받게 되고, 총급여 5,500만원 초과인 경우 13.2%를 적용하여 개인형IRP 계좌 추가 납입으로 396,000원의 환급을 받게 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -2645,7 +2723,14 @@
           <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>● 오세훈
+연금 개시 신청 업무는 2단계로 처리해야 하니 [06-12-622] 세액 미공제 한도 등록을 먼저 거친 뒤 [02-12-221] 연금지급 등록을 진행하는 게 핵심이에요. 첫 단계의 준비서류는 연금보험료 등 소득·세액 공제 확인서이며 서류가 없을 때는 국민지갑에서 발급할 수 있어요. 본격적인 개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 먼저 확인해야 하며 연금개시 후에는 이전이 불가능해요. 또한 처리 중에 자동이체 금액이 입금되고 있거나 보유상품변경이 진행 중이면 거래가 불가하니 이 점을 주의해 주세요.
+● 박정호
+연금 개시를 신청하는 고객에게는 2단계로 처리하는 것이 핵심이에요. 먼저 [06-12-622] 세액 미공제 한도 등록을 진행하고, 이어서 [02-12-221] 연금지급 등록을 처리해요. 세액 미공제 한도 등록 시에는 「연금보험료 등 소득·세액 공제 확인서」를 준비해야 하며, 서류가 없다면 국민지갑에서 발급할 수 있어요. 연금개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 꼭 확인해야 해요. 아울러 처리 중 자동이체 금액이 입금 중이거나 보유상품변경이 진행 중이면 거래가 불가하다는 점을 미리 안내드릴게요.</t>
+        </is>
+      </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>
@@ -2709,7 +2794,11 @@
           <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>과세이연 등록을 처리할 때는 과세이연정보(통산정보) 등록·조회와 과세이연계좌신고서 출력을 할 수 있는 [04-12-648] 과세이연정보관리 화면을 활용하면 돼요. 이어서 [01-12-213] 입금/입금예약 화면에서 거래구분을 과세이연/계약이전입금으로 선택해 입금을 진행하면 과세이연 등록 절차를 처리할 수 있어요.</t>
+        </is>
+      </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2827,7 +2827,18 @@
           <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>● 오세훈
+[실행 실패] LLM 다운 — 만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 
+처리는 두 갈래로 나누어 디폴트옵션 사전지정 등록과 만기 예약변경으로 안내하며, 처리 화면은 [75-08-110]을 활용해요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 방치되면 현금성자산에 머물게 되므로 사전 조치가 필요해요. 
+상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거쳐야 하며, 저축은행 상품은 만기 안내가 특히 중요해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 할 수 있어요. 
+접촉 가능 구간은 만기 1개월 전부터 만기 후 4주까지이며, 만기 후 6주(4+2주 구조)가 지나기 전에 대응해야 해요. 옵트인은 대기 기간 없이 즉시 처리할 수 있어요.
+● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2856,7 +2867,12 @@
           <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2889,7 +2905,12 @@
           <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr"/>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2939,7 +2939,19 @@
           <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
         </is>
       </c>
-      <c r="E65" s="18" t="inlineStr"/>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 한지우
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
@@ -2968,7 +2980,12 @@
           <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr"/>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3014,7 +3014,12 @@
           <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr"/>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -3047,7 +3052,12 @@
           <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -3076,7 +3086,12 @@
           <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -3105,7 +3120,12 @@
           <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -3138,7 +3158,12 @@
           <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr"/>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3192,7 +3192,12 @@
           <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr"/>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -3221,7 +3226,12 @@
           <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr"/>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -3250,7 +3260,12 @@
           <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr"/>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -3279,7 +3294,12 @@
           <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr"/>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3328,7 +3328,12 @@
           <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr"/>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -3365,7 +3370,12 @@
           <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr"/>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -3394,7 +3404,16 @@
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3442,7 +3442,12 @@
           <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr"/>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -3471,7 +3476,12 @@
           <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -3500,7 +3510,12 @@
           <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr"/>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
@@ -3529,7 +3544,12 @@
           <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr"/>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3578,7 +3578,16 @@
           <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>● 최서윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -3607,7 +3616,12 @@
           <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3650,7 +3650,16 @@
           <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr"/>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>● 정민석
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
@@ -3679,7 +3688,12 @@
           <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>
@@ -3712,7 +3726,12 @@
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
-      <c r="E87" s="18" t="inlineStr"/>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -3741,7 +3760,12 @@
           <t>왜 이 상품은 목록에서 빠진 거야?</t>
         </is>
       </c>
-      <c r="E88" s="18" t="inlineStr"/>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3798,7 +3798,12 @@
           <t>이 고객한테는 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E89" s="18" t="inlineStr"/>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본 리허설</t>
@@ -3827,7 +3832,16 @@
           <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
         </is>
       </c>
-      <c r="E90" s="18" t="inlineStr"/>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>● 오세훈
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3870,7 +3870,16 @@
           <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
         </is>
       </c>
-      <c r="E91" s="18" t="inlineStr"/>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>● 오세훈
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -3903,7 +3912,12 @@
           <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr"/>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -3932,7 +3946,12 @@
           <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr"/>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -3961,7 +3980,12 @@
           <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4014,7 +4014,12 @@
           <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr"/>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4043,7 +4048,12 @@
           <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr"/>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4072,7 +4082,12 @@
           <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr"/>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4105,7 +4120,12 @@
           <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
         </is>
       </c>
-      <c r="E98" s="18" t="inlineStr"/>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4234,8 +4234,7 @@
       <c r="E101" s="18" t="inlineStr">
         <is>
           <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 5회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 2 · 간격 0.2초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_INTERVAL_SEC 를 늘립니다.)
-응답: { "error": { "code": 429, "message": "You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gem…)</t>
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
@@ -4266,7 +4265,16 @@
           <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr"/>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>● 정민석
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4303,7 +4311,12 @@
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4345,7 +4345,12 @@
           <t>왜 이 이벤트를 고른 거야?</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr"/>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -4378,7 +4383,12 @@
           <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4421,7 +4421,12 @@
           <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4454,7 +4459,12 @@
           <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F107" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4487,7 +4497,12 @@
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4520,7 +4535,12 @@
           <t>대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
-      <c r="E109" s="18" t="inlineStr"/>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F109" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4569,7 +4569,12 @@
           <t>(쪽지 초안 뒤) 응, 보내줘</t>
         </is>
       </c>
-      <c r="E110" s="18" t="inlineStr"/>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -4602,7 +4607,12 @@
           <t>지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr"/>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F111" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4641,7 +4641,12 @@
           <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr"/>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4674,7 +4679,12 @@
           <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr"/>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -4703,7 +4713,12 @@
           <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr"/>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -4732,7 +4747,12 @@
           <t>추천 상품을 다른 걸로 바꿔줘</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr"/>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F115" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4785,7 +4785,12 @@
           <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E116" s="18" t="inlineStr"/>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F116" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -4818,7 +4823,12 @@
           <t>그 중 두 번째 상품만 자세히 설명해줘</t>
         </is>
       </c>
-      <c r="E117" s="18" t="inlineStr"/>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4861,7 +4861,12 @@
           <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
         </is>
       </c>
-      <c r="E118" s="18" t="inlineStr"/>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4894,7 +4899,12 @@
           <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
-      <c r="E119" s="18" t="inlineStr"/>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F119" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4937,7 +4937,12 @@
           <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
-      <c r="E120" s="18" t="inlineStr"/>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4970,7 +4975,12 @@
           <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E121" s="18" t="inlineStr"/>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -5003,7 +5013,12 @@
           <t>너 뭐 할 수 있는지 알려줘</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr"/>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5047,7 +5047,12 @@
           <t>너 이전 대화 기억해?</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr"/>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F123" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5076,7 +5081,12 @@
           <t>고객한테 문자 직접 보내줄 수 있어?</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr"/>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5109,7 +5119,12 @@
           <t>오늘 누구부터 봐야 해?</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr"/>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F125" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5138,7 +5153,12 @@
           <t>타겟 목록에 고객번호도 같이 넣어줘</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr"/>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5175,7 +5195,12 @@
           <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr"/>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5229,7 +5229,12 @@
           <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr"/>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -5262,7 +5267,16 @@
           <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr"/>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>● 정민석
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5305,7 +5305,12 @@
           <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr"/>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5339,7 +5339,16 @@
           <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr"/>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>● 오세훈
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
@@ -5372,7 +5381,12 @@
           <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr"/>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5405,7 +5419,12 @@
           <t>(되묻기 뒤) 2번째꺼</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr"/>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5457,7 +5457,12 @@
           <t>(되묻기 뒤) 잘 모르겠는데</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr"/>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5490,7 +5495,12 @@
           <t>(제안 뒤) 아니, 됐어</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr"/>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F135" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5533,7 +5533,12 @@
           <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr"/>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -5566,7 +5571,12 @@
           <t>(첫 턴) 네</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr"/>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F137" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -5632,7 +5642,12 @@
           <t>이 고객한테 무슨 상품 추천해주지?</t>
         </is>
       </c>
-      <c r="E139" s="18" t="inlineStr"/>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스 리허설</t>
@@ -5661,7 +5676,12 @@
           <t>국고채 금리 어때?</t>
         </is>
       </c>
-      <c r="E140" s="18" t="inlineStr"/>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F140" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5710,7 +5710,12 @@
           <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
-      <c r="E141" s="18" t="inlineStr"/>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F141" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5739,7 +5744,12 @@
           <t>대화 내용 요약해줘</t>
         </is>
       </c>
-      <c r="E142" s="18" t="inlineStr"/>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F142" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본 리허설</t>
@@ -5772,7 +5782,12 @@
           <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E143" s="18" t="inlineStr"/>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F143" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5816,7 +5816,12 @@
           <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E144" s="18" t="inlineStr"/>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F144" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -5845,7 +5850,12 @@
           <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
-      <c r="E145" s="18" t="inlineStr"/>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F145" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -5874,7 +5884,12 @@
           <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E146" s="18" t="inlineStr"/>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F146" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5922,7 +5922,12 @@
           <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
         </is>
       </c>
-      <c r="E147" s="18" t="inlineStr"/>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F147" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
@@ -5955,7 +5960,12 @@
           <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr"/>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -5984,7 +5994,12 @@
           <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr"/>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F149" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6013,7 +6028,12 @@
           <t>IRP 중도인출 사유가 뭐야?</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr"/>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F150" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>
@@ -6042,7 +6062,12 @@
           <t>이 고객은 왜 타겟이 됐지?</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr"/>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6096,7 +6096,12 @@
           <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr"/>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 안 해본 질문</t>
@@ -6162,7 +6167,16 @@
           <t>이 고객한테 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E154" s="18" t="inlineStr"/>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 정민석
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6205,7 +6205,16 @@
           <t>이 고객 디폴트옵션 설정돼 있어?</t>
         </is>
       </c>
-      <c r="E155" s="18" t="inlineStr"/>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>
@@ -6234,7 +6243,19 @@
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E156" s="18" t="inlineStr"/>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>● 오세훈
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6284,7 +6284,16 @@
           <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E157" s="18" t="inlineStr"/>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이준호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F157" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6313,7 +6322,16 @@
           <t>지난 상담에서 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E158" s="18" t="inlineStr"/>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 김서연
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F158" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6360,7 +6360,16 @@
           <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E159" s="18" t="inlineStr"/>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>● 이수민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F159" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6389,7 +6398,16 @@
           <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
         </is>
       </c>
-      <c r="E160" s="18" t="inlineStr"/>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>● 박지민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 한지우
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6436,7 +6436,16 @@
           <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E161" s="18" t="inlineStr"/>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박지민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F161" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6465,7 +6474,16 @@
           <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
-      <c r="E162" s="18" t="inlineStr"/>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>● 박정호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F162" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6494,7 +6512,16 @@
           <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
-      <c r="E163" s="18" t="inlineStr"/>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>● 최서윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 박지민
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F163" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6550,7 +6550,16 @@
           <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E164" s="18" t="inlineStr"/>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>● 정민석
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 김현수
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F164" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6579,7 +6588,16 @@
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E165" s="18" t="inlineStr"/>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>● 송도윤
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+● 이준호
+[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+        </is>
+      </c>
       <c r="F165" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>이수민 고객의 총급여 구간이 확인되지 않아 두 가지 경우를 모두 살펴봐야 하니, 단말에서 총급여 구간을 먼저 확인한 뒤에 안내해 주세요. 개인형IRP 계좌 추가 납입액 300만원을 넣을 때, 총급여 5,500만원 이하로 적용 공제율 16.5%가 확인되면 환급 예상액은 0원에서 495,000원으로 늘어나며 늘어나는 금액은 495,000원이에요. 총급여 5,500만원 초과로 적용 공제율 13.2%가 확인되면 환급 예상액은 0원에서 396,000원으로 늘어나며 늘어나는 금액은 396,000원이에요. 이 고객의 잔여한도는 연금저축 납입분까지 합산한 값으로 900만원이 남아 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+          <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -2395,33 +2395,7 @@
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-김서연 고객에게는 8천만원 전부에 부담을 느낄 때 ISA 만기자금 전환액을 일부로 조정했을 때의 세액공제 적용 구조를 안내하는 게 핵심이에요. 개인형IRP 계좌 추가 납입 자료와 달리 ISA 만기자금을 전환하는 경우는 전환금의 10%가 세액공제 대상에 더해지며 300만원의 상한이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상인 8,000만원 전환 시 상한인 300만원이 적용돼요. 총급여 5,500만원 이하 구간인 16.5% 적용 시 전환액 8,000만원 기준으로 늘어나는 환급액은 495,000원이며, 총급여 5,500만원 초과 구간인 13.2% 적용 시 늘어나는 환급액은 396,000원이에요. 이 고객의 총급여 구간은 원장에 확인되지 않으므로 단말에서 소득 구간을 먼저 확인한 뒤 해당되는 환급 예상액을 안내해 주세요.
-● 한지우
-■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
-· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
-· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
-· 계산에 쓴 추가 납입액 8,000만원
-· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
-· 총급여 5,500만원 이하(16.5%): 환급 예상 990,000원 → 1,485,000원 (늘어나는 금액 495,000원)
-· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
-· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
-■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
-· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
-· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
-· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
-· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
-· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
-· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원
-· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
-· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
-· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
-● 송도윤
-송도윤 고객이 ISA 만기자금 8,000만원 중 일부만 IRP 계좌로 전환할 때의 세액공제 효과를 안내할 때는, 현금을 추가로 납입하는 경우와 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 별개의 축이라는 점을 짚어 주어야 해요. 현재 이 고객의 개인형IRP 계좌 추가 납입분은 세액공제 잔여한도가 0원이지만, ISA 만기자금 전환은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지며 상한은 300만원이므로, 8,000만원을 전환하면 상한인 300만원의 추가 공제 대상이 만들어져요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간에 따라 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 495,000원이고, 총급여 5,500만원 초과(13.2%)인 경우 늘어나는 환급액은 396,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않으며, 고객의 총급여 구간이 확인되지 않았으므로 두 경우를 모두 안내해 주세요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
-        </is>
-      </c>
+      <c r="E52" s="18" t="n"/>
       <c r="F52" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -2450,16 +2424,7 @@
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-ISA 만기자금을 개인형IRP 계좌로 전환할 때는 현금을 더 납입하는 경우와 다른 한도가 적용되니 두 축을 구분해서 안내해야 해요. 고객의 정확한 총급여 구간이 원장에 확인되지 않아 두 가지 경우를 모두 고려해야 하므로, 총급여 5,500만원 이하(16.5%)라면 전환으로 늘어나는 환급 예상액은 495,000원이고, 총급여 5,500만원 초과(13.2%)라면 늘어나는 환급 예상액은 396,000원이에요. 이 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 개인형IRP 계좌에 넣을 수 있으며, 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 기존 900만원에서 최대 1,200만원으로 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 같은 한도 안에서 저울질하지 않으며, 타행 ISA 만기일인 2026년 9월 30일로부터 60일 이내에 전환해야 해요.
-● 한지우
-ISA 만기자금 8,000만원을 개인형IRP 계좌로 전환할 때 받는 세액공제는 고객의 총급여 구간에 따라 달라지며, 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 적용돼요. 총급여 5,500만원 이하(16.5%)라면 이 전환으로 늘어나는 환급금은 495,000원이고, 총급여 5,500만원 초과(13.2%)라면 늘어나는 환급금은 396,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이며, 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 송도윤
-ISA 만기자금 8,000만원을 개인형IRP로 전환하는 고객에게는 총급여 5,500만원 이하(16.5%) 기준으로 환급액을 안내하는 게 핵심이에요. 송도윤 고객의 개인형IRP 계좌는 당해 납입액이 0원이고 세액공제 잔여한도도 0원이지만, ISA 만기자금 전환은 기존 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 다른 축이에요. 만기일로부터 60일 이내에 전환하면 전환금의 10%가 세액공제 대상에 더해지며 상한은 300만원이에요. 8,000만원을 전환하면 상한인 300만원이 추가 공제 대상이 되고, 총급여 5,500만원 이하 적용 시 이 전환으로 늘어나는 환급액은 495,000원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요.</t>
-        </is>
-      </c>
+      <c r="E53" s="18" t="n"/>
       <c r="F53" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2488,30 +2453,7 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-총급여 5,500만원 초과 구간인 김서연 고객에게는 ISA 만기자금 8,000만원 중 일부인 3,000만원을 개인형IRP 계좌로 전환할 때의 환급액을 안내해 주는 게 핵심이에요. 3,000만원을 전환하면 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어나고, 적용 공제율 13.2% 기준 환급액 396,000원이 추가로 발생해요. 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상 전환 시 상한인 300만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 한지우
-총급여가 5,500만원 초과인 고객에게는 ISA 만기자금 중 3,000만원 이상을 개인형IRP로 전환할 때 추가 공제 대상이 300만원으로 상한에 도달하며, 이 경우 늘어나는 환급 예상액은 396,000원이에요. 앞서 말씀드린 현금을 더 납입하는 경우와는 다른 축으로 별개로 더해지는 몫이므로, 만기자금 8,000만원 중 일부만 옮기는 경우에도 전환액의 10%에 해당하는 금액이 세액공제 대상에 더해져서 전환액 1,000만원이면 100만원, 2,000만원이면 200만원, 3,000만원 이상이면 300만원의 공제 대상 한도가 추가로 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않은 부분은 아직 준비된 자료가 없어요.
-● 송도윤
-■ 세액공제 환급 예상액 — 송도윤 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
-· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
-· 당해 납입액 0원 · 세액공제 한도 900만원 · 잔여한도 0원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
-· 계산에 쓴 추가 납입액 0원 (질문에 금액이 없어 잔여한도로 계산했다)
-· 세액공제 잔여한도가 0원이라 **추가 공제 대상이 없다** — 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않는다 (세액공제 한도 900만원은 연금저축과 함께 쓴다. 납입 자체는 연 납입한도 1,800만원까지 가능하다)
-■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
-· ISA 만기자금 1억 2,000만원 · 만기 2026-09-20 (만기 9일 경과 · 전환 기한 51일 남음) · 당행 — 만기일로부터 60일 이내에 전환한다
-· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
-· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
-· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
-· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 1억 2,000만원 → 300만원(상한)
-· 계산에 쓴 전환액 1억 2,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
-· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
-· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
-· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
-        </is>
-      </c>
+      <c r="E54" s="18" t="n"/>
       <c r="F54" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2544,50 +2486,7 @@
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
-· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
-· 당해 납입액 400만원 · 세액공제 한도 900만원 · 잔여한도 500만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
-· 계산에 쓴 추가 납입액 500만원 (질문에 금액이 없어 잔여한도로 계산했다)
-· 공제 대상 400만원 → 900만원 (잔여한도 500만원까지)
-· 총급여 5,500만원 이하(16.5%): 환급 예상 660,000원 → 1,485,000원 (늘어나는 금액 825,000원)
-· 총급여 5,500만원 초과(13.2%): 환급 예상 528,000원 → 1,188,000원 (늘어나는 금액 660,000원)
-· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
-■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
-· ISA 만기자금 8,000만원 · 만기 2026-09-30 (D-1) · 타행 — 만기일로부터 60일 이내에 전환한다
-· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
-· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
-· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
-· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
-· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
-· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
-· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
-· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
-● 한지우
-■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
-· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
-· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
-· 계산에 쓴 추가 납입액 300만원 (질문에 금액이 없어 잔여한도로 계산했다)
-· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
-· 총급여 5,500만원 이하(16.5%): 환급 예상 990,000원 → 1,485,000원 (늘어나는 금액 495,000원)
-· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
-· 이 고객의 총급여 구간은 원장에 없어 두 경우를 다 실었다 — 어느 구간인지 확인하면 하나로 좁혀진다
-■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
-· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
-· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
-· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
-· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
-· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
-· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
-· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
-· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
-· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
-● 송도윤
-세액공제 환급 예상액을 안내할 때 5,500만원 이하 소득 구간에서는 개인형IRP 계좌로 1억 2,000만원을 ISA 만기자금으로 전환할 때 추가 공제 대상 300만원이 적용되어 495,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 현금을 더 납입하는 경우와 달리 이 전환 금액은 서로 다른 한도로 별개로 더해지는 몫이에요.</t>
-        </is>
-      </c>
+      <c r="E55" s="18" t="n"/>
       <c r="F55" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6665,7 +6564,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2395,7 +2395,49 @@
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E52" s="18" t="n"/>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 400만원 · 세액공제 한도 900만원 · 잔여한도 500만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 8,000만원
+· 공제 대상 400만원 → 900만원 (잔여한도 500만원까지)
+· 총급여 5,500만원 이하(16.5%): 환급 예상 660,000원 → 1,485,000원 (늘어나는 금액 825,000원)
+· 공제율은 **원장의 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-30 (D-1) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 한지우
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 8,000만원
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 공제율은 **원장의 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 송도윤
+송도윤 고객이 ISA 만기자금을 개인형IRP 계좌로 8천만원 중 일부만 전환할 때는 전환액에 따라 추가 공제 대상이 늘어나는 구조로 안내해야 해요. 
+이 고객의 ISA 만기자금 1억 2,000만원 중 일부를 개인형IRP 계좌로 전환할 때, 전환액의 10%가 세액공제 대상에 더해지며 상한은 300만원이에요. 자료에 따르면 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상 전환 시 상한인 300만원이 추가로 더해져요. 
+단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 
+총급여 5,500만원 이하(16.5%) 적용 시, 8천만원 전액을 전환하면 추가 공제 대상 300만원에 대해 최대 495,000원의 환급액이 늘어나게 돼요. 8천만원보다 적은 일부 금액을 옮기더라도 3,000만원까지는 전환액의 10%가 추가 공제 대상에 더해지는 방식으로 계산되니 이 점을 참고해 안내해 보세요.</t>
+        </is>
+      </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본 리허설</t>
@@ -2424,7 +2466,31 @@
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E53" s="18" t="n"/>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+ISA 만기자금을 8천만원 전부 전환할 때 세액공제 환급 예상액을 묻는 질문에는 개인형IRP 계좌 추가 납입인 현금 납입과 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 축으로 다루는 게 핵심이에요. 
+김서연 고객의 ISA 만기자금 8천만원을 타행에서 전환할 때는 만기일로부터 60일 이내에 처리해야 하며, 전환금은 연 납입한도 1,800만원과 무관하게 전부 또는 일부를 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이므로, 8천만원을 전환하면 300만원이 추가 공제 대상이 돼요. 총급여 5,500만원 이하(16.5%) 기준일 때 이 전환으로 늘어나는 환급 예상액은 495,000원이며, 이는 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요. 
+단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+ISA 만기자금 8,000만원을 개인형IRP 계좌로 전환하면 세액공제 대상 한도가 늘어나 환급액을 더 받을 수 있어요. 한지우 고객의 총급여 5,500만원 초과(13.2%) 기준으로 전환액 8,000만원에 대해 추가 공제 대상 300만원이 적용되어 396,000원의 환급액이 늘어나요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 송도윤
+■ 세액공제 환급 예상액 — 송도윤 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 0원 · 세액공제 한도 900만원 · 잔여한도 0원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 8,000만원
+· 세액공제 잔여한도가 0원이라 **추가 공제 대상이 없다** — 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않는다 (세액공제 한도 900만원은 연금저축과 함께 쓴다. 납입 자체는 연 납입한도 1,800만원까지 가능하다)
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 1억 2,000만원 · 만기 2026-09-20 (만기 9일 경과 · 전환 기한 51일 남음) · 당행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 1억 2,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원
+· 총급여 5,500만원 이하(16.5%): 이 전환으로 늘어나는 환급 495,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
+        </is>
+      </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA 리허설</t>
@@ -2453,7 +2519,31 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="n"/>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+이전 대화에서 나눈 ISA 만기자금 8,000만원 전액 전환 기준의 추가 공제와 달리, 일부 금액만 전환하는 경우라면 전환액에 따라 추가 공제 대상이 달라져요. 1,000만원을 전환하면 100만원이, 2,000만원을 전환하면 200만원이, 3,000만원 이상을 전환하면 상한인 300만원이 세액공제 대상에 더해져요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 300만원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 공제율은 **원장의 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
+● 송도윤
+송도윤 고객의 총급여가 5,500만원 초과 구간인 경우라면 ISA 만기자금 1억 2,000만원 중 일부인 1,000만원, 2,000만원, 3,000만원을 개인형IRP 계좌로 전환할 때 각각 추가 공제 대상 100만원, 200만원, 300만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 5,500만원 초과 구간의 적용 공제율 등 세부 세액공제율 자료는 아직 준비된 자료가 없어요.</t>
+        </is>
+      </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2486,7 +2576,16 @@
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="n"/>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+김서연 고객의 개인형IRP 계좌 추가 납입과 관련하여 총급여 5,500만원 이하 구간을 확인하였으므로 16.5%의 공제율을 적용하여 환급 예상액을 안내하는 게 핵심이에요. 앞서 말씀드린 현금을 더 납입하는 경우, 잔여한도 500만원을 추가 납입하면 총급여 5,500만원 이하(16.5%) 기준으로 1,485,000원의 환급 예상액을 받으실 수 있어요. 이는 기존 당해 납입액 400만원에 따른 660,000원에서 825,000원이 늘어나는 금액이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+총급여 5,500만원 이하 구간 기준으로 안내해 드려야 해요. 앞서 말씀드린 ISA 만기자금 8,000만원 중 일부를 개인형IRP 계좌로 전환할 때 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상 전환 시 상한인 300만원이 되어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 송도윤
+총급여 5,500만원 이하인 송도윤 고객이 ISA 만기자금 1억 2,000만원 중 일부인 3,000만원을 개인형IRP 계좌로 전환할 때 예상되는 세액공제 환급액은 495,000원이에요. 이 금액은 총급여 5,500만원 이하 적용 공제율 16.5%와 추가 공제 대상 300만원이 반영된 결과예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 대로 전환금은 연 납입한도 1,800만원과 무관하며, 현금을 더 납입하는 경우와는 다른 한도로 별개로 더해지는 몫이에요.</t>
+        </is>
+      </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -2729,13 +2828,9 @@
       <c r="E62" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
-[실행 실패] LLM 다운 — 만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 
-처리는 두 갈래로 나누어 디폴트옵션 사전지정 등록과 만기 예약변경으로 안내하며, 처리 화면은 [75-08-110]을 활용해요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 방치되면 현금성자산에 머물게 되므로 사전 조치가 필요해요. 
-상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거쳐야 하며, 저축은행 상품은 만기 안내가 특히 중요해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 할 수 있어요. 
-접촉 가능 구간은 만기 1개월 전부터 만기 후 4주까지이며, 만기 후 6주(4+2주 구조)가 지나기 전에 대응해야 해요. 옵트인은 대기 기간 없이 즉시 처리할 수 있어요.
+만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거친 뒤, [75-08-110] 화면을 통해 예약변경 거래를 처리하면 돼요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 현금성자산에 머무르므로, 저축은행 상품처럼 만기 안내와 예약변경이 중요해요. 특히 만기 후 6주(만기일부터 4주간 지시 없으면 안내 후 2주 뒤 적용)의 유예 구조가 있으나 만기 4주 시점에 본부 안내가 나가기 때문에, 접촉 가능 구간인 만기 1개월 전부터 만기 후 4주 사이에 서둘러 대응해야 해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 하는 방식을 활용할 수 있어요.
 ● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+만기상품 예약변경은 먼저 사용계획이 있는 자금인지 확인하고 처리하는 게 핵심이에요. 정기예금은 만기에 자동 재예치되지 않아 방치되면 현금성자산에 머물게 되니 [75-08-110] 화면에서 만기상품 예약변경으로 처리해야 해요. 처리 순서는 익월 금리가 월 단위로 확정되므로 익월 금리 확인을 선행한 뒤 만기 1개월 전부터 예약변경을 걸고, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하는 방식이에요. 주의할 점은 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 먼저 걸러내야 하며, 디폴트옵션 미등록 고객은 사전지정 등록과 만기 예약변경을 함께 처리해야 한다는 점이에요.</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
@@ -2768,8 +2863,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>디폴트옵션 등록 절차와 화면번호는 [75-08-110] 화면을 통해 처리해요. 원리금보장상품 만기가 다가오는데 디폴트옵션 미등록인 고객은 별도 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 디폴트옵션 사전지정 등록과 만기 예약변경으로 나누어 처리할 수 있어요. 만기 예약거래는 만기 한 달 전부터 가능하며, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하면 돼요. 처리는 디폴트옵션(저위험이상) 사전지정 등록과 만기 예약변경 두 갈래로 진행돼요.</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -2806,8 +2900,7 @@
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>IRP 계좌 해지 업무는 [02-12-220] 퇴직연금 지급 화면에서 진행해요. 해당 화면은 해지, 계좌이체, 미지급금 출금, 지연보상금 지급을 처리하는 화면이에요. 단일 자료에만 등장하는 내용이라 다른 화면 번호는 안내되지 않으니 참고해 주세요.</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
@@ -6564,7 +6657,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2934,14 +2934,11 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>● 김서연
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+ISA 만기자금 입금은 입금/입금예약·입금명부 등록 화면인 [01-12-213]번 화면에서 처리하면 돼요. 이 화면은 지급, 과세이연, 연금 관련 업무를 처리하는 곳이며 거래구분에서 ISA 만기자금 입금을 선택할 수 있어요. [01-12-213] 관련 내용은 현재 준비된 자료를 바탕으로 안내해 드렸어요.
 ● 한지우
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+ISA 만기자금 입금은 입금·입금예약·입금명부 등록을 처리하는 01-12-213 화면에서 처리해요. 해당 화면에서는 거래구분을 과세이연·계약이전입금이나 ISA 만기자금 입금으로 선택해 진행할 수 있어요. [01-12-213] ISA 만기자금 입금 거래구분을 선택하면 입금가능금액을 자동으로 조회할 수 있다는 점을 함께 참고해서 안내해 주세요.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+ISA 만기자금 입금은 [01-12-213] 입금/입금예약 화면에서 처리하면 돼요. 이 화면은 입금, 입금예약, 그리고 입금명부 등록을 처리하는 화면이에요. 거래구분을 선택할 때 ISA 만기자금 입금을 고르면 입금가능금액을 자동으로 조회할 수 있어요. 그 외에 과세이연이나 계약이전입금 거래구분도 이 화면에서 함께 다루고 있어요.</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
@@ -2974,8 +2971,7 @@
       </c>
       <c r="E66" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>포트폴리오 운용현황 조회를 위한 화면번호는 06-12-604이며, 해당 화면은 연금 로보어드바이저 운용현황 조회를 처리하는 화면이에요. AI투자일임 및 케이봇쌤과 관련된 거래를 확인할 때 활용할 수 있어요. [06-12-604]</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
@@ -3008,8 +3004,9 @@
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: screen:타행 계좌 잔액 조회 화면
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
       <c r="F67" s="19" t="inlineStr">
@@ -3046,8 +3043,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>고객이 스타뱅킹에서 직접 추가납입할 때는 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로로 안내해 드려요. 인터넷뱅킹을 이용할 때는 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로로 들어가서 진행할 수 있어요. 이용 시간 예외로 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지 가능하니 이 시간대에 처리하도록 미리 짚어드릴게요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -3080,8 +3076,8 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>개인형IRP 연금수령 신청은 KB스타뱅킹의 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 수령관리 &gt; 연금 수령관리 – 개인형IRP 연금수령 신청 경로와 인터넷뱅킹의 KB퇴직연금 &gt; 개인고객 &gt; 연금수령신청/조회 &gt; 개인형IRP 연금수령 신청 경로를 통해 고객이 직접 진행할 수 있어요. 
+이용 가능한 채널은 개인형IRP에 한하며, ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -3114,8 +3110,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>우리 IRP에서도 ETF 매매를 할 수 있으니 고객이 직접 진행할 때 안내할 경로를 짚어드릴게요. KB스타뱅킹을 이용하는 경우 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, ETF 매매하기 순으로 이동하면 되고, 인터넷뱅킹을 이용하는 경우 KB퇴직연금, 개인고객, 퇴직연금 ETF, ETF 매매하기 경로로 접근하면 돼요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -3152,8 +3147,7 @@
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>적립금이 1천만원 미만이더라도 이 고객은 원리금보장·현금성 자산 비중이 90%로 편중되어 있고 디폴트옵션이 미설정되어 있어 관리 대상에 해당해요. 현재 고유계정대와 예금을 포함한 원리금보장·현금성 자산 비중이 높고 키움 더드림 단기채 수익률이 -6.4%를 기록하면서 전체 운용수익률이 -1.8%에 머물러 있는 상태예요. 이는 동연령 평균 수익률 10.2%와 비교해 저조한 수준이며, 위험자산 한도 70% 중 위험자산 비중이 0%로 나타나 포트폴리오 조정이 필요한 상태예요.</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -3186,8 +3180,7 @@
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>운용지시 없이 대기 중인 현금성자산(가용고유대 − 디폴트옵션 실행대기자금) 보유 고객. 단, 임계값이 자료마다 다름: | 기준 | 출처·시기 | 용도 | |---|---|---| | 7,500만원 이상 (PB센터 관리고객 제외) | 오늘의할일 스크립트, 2023~24 추정 | TM 콜 대상 | | 100만원 이상 | 수익률 KPI 시나리오, 2021 | 매월 안내 LMS 자동발송 | | 보유비율 50% 이상 | Series 1, 2026.05 → 세그먼트 1 | 이탈위험 선별 | 과 디폴트옵션 미동의 &amp; 현금성 대기자산 10만원 이상 보유 고객 실행: 주 1회 카카오톡 + 매월 스타알림으로 등록 동의·교체매매 안내 (2023년 디폴트옵션 시행기 방식)에 따라 선정되는 대기 현금성자산 보유 고객은 운용지시 없이 대기 중인 상태여서 사실상 무수익 방치 상태로 보기 때문에 관리 대상으로 삼는 것이에요. 현금성자산은 금액이 클수록 수익률 개선 효과와 이탈 방지 효과가 커서 TM 등 고비용 채널의 우선 대상이 되며, 특히 디폴트옵션 등록 전에는 고유계정대 자금이 계속 현금성 대기자산으로 남기 때문에 디폴트옵션 동의와 교체매매를 세트로 진행하는 것이 핵심이에요.</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
@@ -3220,8 +3213,12 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이탈 위험 고객은 현금성자산이나 정기예금 편중 고객과 계약이전 신청 고객을 기준으로 선정해요.
+현금성자산·정기예금 편중 고객은 고유계정대(현금성자산) 보유 비율 50% 이상, 또는 고유계정대 + 시중은행 정기예금만으로 100% 운용 중 대상 기준선: 총 적립금 1천만원 이상 (본부 타깃리스트 제공 기준)에 해당하는 고객을 골라내요. 이 조건에 해당하는 고객은 이탈위험도가 일반 고객의 1.3배 수준으로 높아서 본부가 리밸런싱 관리 최우선 세그먼트로 지정했어요. 다만 원문 임계값은 '고유계정대 보유비율 50% 이상 또는 고유대+시중은행 정기예금 100%, 적립금 1천만원 이상'. 코드 판정(customer.conditions dep)은 룰베이스 TG-202 의 '원리금보장 합산 80% 이상'이라 모집단이 다르다는 점을 참고해 주세요.
+다른 기준으로 타사로 계약이전(전출) 신청이 접수되어 알림이 발생한 고객 조건 조회형이 아니라 알림 수신 시점에 발동하는 이벤트형 세그먼트 (사후관리 중 시급성 최상)에 해당하는 고객도 있어요. 이들은 사후관리 중 시급성이 최상인 이탈 진행 중 고객으로, 이탈 사유를 들어보면 지킬 수 있는 고객이 생각보다 많기 때문에 영업점 직접 방어 대상으로 지정되어 있어요.
+── 빠뜨리면 안 되는 표시
+· 현금성자산·정기예금 편중 고객 (이탈 고위험)
+  원문 임계값은 '고유계정대 보유비율 50% 이상 또는 고유대+시중은행 정기예금 100%, 적립금 1천만원 이상'. 코드 판정(customer.conditions dep)은 룰베이스 TG-202 의 '원리금보장 합산 80% 이상'이라 모집단이 다르다.</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
@@ -3254,8 +3251,10 @@
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>어떤 목적의 대상 선정 기준인가요?
+· TM 콜 대상
+· 매월 안내 LMS 자동발송
+· 이탈위험 선별</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -3288,8 +3287,7 @@
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>오늘 우선 관리해야 할 대상은 총 11명이며, 각 고객의 현황에 따른 선정 요건 순서대로 확인해야 해요. 윤가영 고객은 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월에 해당해요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월이며, 최서윤 고객은 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원이 확인되며, 이수민 고객은 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원이 선정 요 이에요. 박정호 고객은 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원이며, 김현수는 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시이며, 김서연 고객은 ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원이에요. 한지우 고객은 ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
@@ -3322,8 +3320,7 @@
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>만기 안내 전화할 때는 본부 공식 지침은 아니지만 영업점 현장에서 관찰된 방식을 활용할 수 있어요. 비율 대신 원 단위 금액으로 제시하는 것이 반복되는 성공 패턴이며, 계산이 상담의 성패를 가른다는 점을 참고해 보세요. 중도해지이율이 수수료율 합계보다 낮으면 원금에서 차감 지급된다는 점이나 지급까지 3영업일이 소요된다는 사실, 그리고 중도인출 신청액이 세전이라는 점을 미리 안내하지 않으면 민원으로 돌아올 수 있으니 사전에 고지하는 것이 중요해요. 만기 안내 전화 과정에서 수수료로 원금이 깨질 수 있는 부분이나 현금화 지연 가능성 같은 필수 고지 사항을 빠뜨리지 않도록 유의하세요.</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -3364,8 +3361,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>손실만 나고 해지하겠다는 고객에게는 보유 포트폴리오 유형으로 화법을 분기하여, 저희가 세심하게 관리를 해드렸어야 했는데 죄송합니다라고 먼저 관리 미흡을 사과하고 그 자리에서 매도와 재추천이라는 액션을 약속하는 방식으로 접근해야 해요. 본부 교육 영상에서는 공시 순위를 앞세우지 않고 이처럼 사과와 원인 규명에 이어 즉시 리밸런싱을 3단으로 밟아나가는 방식을 권하고 있어요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속해서는 안 되며, 근거는 수익률 예측이 아니라 운용 여건의 차이에 두어야 해요. 또한 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 미리 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 상담 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -3399,11 +3395,9 @@
       <c r="E78" s="6" t="inlineStr">
         <is>
           <t>● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+"예금만 해서 관리 필요 없어요"라는 고객에게는 금리 갈아타기가 곧 관리라는 논리로 접근하는 게 핵심이에요. 예금과 같은 원리금보장상품도 꾸준한 관리가 필요한 대상이라는 점을 짚어주고, 매월 금리가 가장 좋은 상품을 제공하고 있다는 점을 설명해 주세요. 고객에게는 이렇게 안내해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다." 이미 안정적으로 잘 운용하고 있다는 점을 먼저 인정한 뒤, 같은 안전성인 예금자보호 테두리 안에서 금리를 올려주는 제안으로 자연스럽게 대화를 이어가면 됩니다.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+예금만으로도 충분하지 않냐고 묻는 고객에게는 예금 같은 원리금보장상품도 매월 금리가 유리한 상품으로 갈아타는 과정이 곧 관리라는 점을 짚어주는 것이 핵심이에요. 당행은 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있다는 점을 설명해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내하시면 돼요. 이 과정에서 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 '고유계정대' 같은 용어 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 표현을 사용해 주세요. 아울러 연금지급 대기나 교체매매 등으로 사용 계획이 있는 자금인지 먼저 확인하고 접근하시는 것이 안전해요.</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -3436,8 +3430,10 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>IRP 중도인출 가능 여부를 묻는 고객에게는 무주택자의 주택 구입이나 전세금 및 임차보증금이 필요한 경우 등 법적 요건을 충족하면 언제든 중도인출이 가능하다고 안내하는 것이 핵심이에요. 55세까지 아예 못 뺀다는 고객의 우려를 법정 사유로 먼저 해소해야 해요. 
+그후 고객이 자유로운 입출금을 원하며 가입을 망설일 때는 무조건 돈 전부를 넣으라는 것이 아니라고 요구 수준을 낮추어 짚어 주세요. 한 가지 음식만 먹으면 영양이 부족하듯 자산을 골고루 나누어 안정성과 수익성, 절세 효과를 균형 있게 챙겨야 한다는 점을 설명하는 것이 효과적이에요. 해지에 대한 우려로 큰 혜택을 놓치는 것은 아쉽다는 점을 강조하면서 다음 대사를 활용해 보세요. 
+"IRP는 만 55세 이후를 준비하는 계좌이지만, 무주택이신 분이 주택을 구입하시거나, 전세금/임차보증금이 필요한 경우 등 법적 요건을 충족하시면 언제든 중도인출이 가능합니다."
+"그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -3470,8 +3466,13 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>증권사 수수료 무료 발언으로 이탈을 우려하는 고객에게는 면제 조건을 먼저 제시한 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 
+만 55세 이후 연금개시를 하시면 수수료가 0원이 되며, 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되므로 이 조건을 먼저 짚어주세요. 
+고객이 퇴직금이 5천만원이 안된다고 할 때를 대비해 "국민은행도 만 55세 이후 연금개시를 하시면 수수료가 0원입니다^^ 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제됩니다."라고 안내해 보세요.
+수수료가 일부 발생하더라도 IRP는 수수료만 보고 결정하기엔 아까운 계좌라는 점을 설명하며, 증권사는 직접 투자하고 직접 관리해야 하는 반면 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능하다는 점을 강조해요. 
+실제로 안내할 때는 "네, 수수료가 일부 발생합니다. 그런데 고객님. IRP는 수수료만 보고 결정하기엔 아까운 계좌입니다. 증권사는 고객님이 장기간 직접 투자하고 직접 관리하셔야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능합니다."라고 말씀해 주세요.
+마지막으로 IRP 수수료는 적립금 규모와 가입 방식에 따라 다르며 우리 고객님 조건에서는 오히려 국민은행이 더 저렴한 경우가 많으므로, 고객님 상황과 적립금 기준으로 한번 같이 비교해드릴게요라고 덧붙여 주시면 돼요.
+대화 중 "IRP 수수료는 적립금 규모와 가입 방식에 따라 다릅니다. 우리 고객님 조건에서는 오히려 국민은행이 더 저렴한 경우가 많습니다. 실제로 고객님 상황과 적립금 기준으로 한번 같이 비교해드릴게요."라는 멘트를 활용해 고객의 상황을 구체적으로 비교해 보면서 대응을 이어가세요.</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -3505,8 +3505,9 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>디폴트옵션에 거부반응을 보이는 고객에게는 전량 전환을 밀지 않고 일부만 먼저 전환하고 되돌릴 수 있다는 가역성을 제시하는 게 핵심이에요. 
+전부 바꾸지 않고 일부만 먼저 운용해 보고 원할 때 되돌릴 수 있다는 점을 안내해 심리적 부담을 낮추는 방식으로 접근해야 해요. 
+이용하려는 자금이 연금지급 대기나 교체매매 중에 있는 등 사용계획이 있는 자금이라면 먼저 걸러내야 하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -3539,8 +3540,9 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: pitch:금액도 얼마 안 되는데 그냥 두면 안 되나요 · playbook:금액도 얼마 안 되는데 그냥 두면 안 되나요
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
@@ -3574,11 +3576,11 @@
       <c r="E83" s="6" t="inlineStr">
         <is>
           <t>● 최서윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+성과저조나 판매중단 펀드를 보유한 고객이 손실 중인 상태에서 교체를 망설일 때는 고객의 속상한 심정을 먼저 인정하는 공감의 자세로 접근해야 해요. 
+보유하신 계좌의 해당 상품이 현재 성과가 좋지 않고 신규 판매가 중단된 상태라는 점을 설명하면서, 이런 경우 운용사의 관리가 소홀해질 수 있어 향후 수익률 개선이 상대적으로 어려울 수 있다는 점을 짚어주는 것이 중요해요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 예측이 아니라 운용 여건의 차이를 근거로 설명해야 해요. 
+고객에게 안내할 때는 "많이 속상하시겠지만, 고객님 안정적인 퇴직연금 자산관리를 위해 최근 수익률 등을 비교해 보시고 상대적으로 성과가 우수한 상품으로 변경해 보시는 건 어떠신가요?"라고 말씀해 보세요.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+성과저조·판매중단 펀드 보유 고객이 손실 상황에서 불만을 제기할 때는 감정 공감을 먼저 건네며 접근하는 것이 핵심이에요. "속상하시겠지만"이라는 감정 인정을 반드시 앞세우고, 판매중단 사유와 그 결과로 운용사 관심도가 하락해 향후 수익률 개선이 어려울 수 있다는 점을 설명한 뒤 교체를 권해야 해요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되고, 수익률 예측이 아니라 운용 여건의 차이를 근거로 다가가야 해요. 고객에게는 "많이 속상하시겠지만, 고객님 안정적인 퇴직연금 자산관리를 위해 최근 수익률 등을 비교해 보시고 상대적으로 성과가 우수한 상품으로 변경해 보시는 건 어떠신가요?"라고 안내해 보세요. 상담 과정에서 사용계획이 있는 자금이라면 먼저 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 해요.</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -3611,8 +3613,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>증권사가 ETF 종류가 훨씬 많다는 고객에게는 고객의 반론을 먼저 인정하면서 10~20년 장기 운용을 해야 하는 연금자산에서는 상품의 개수보다 어떤 상품을 선택해서 운용하느냐가 더 중요하다는 점으로 설명을 이끌어가는 게 핵심이에요. 증권사는 8~900개의 다양한 테마형, 섹터형 ETF를 제공하고 있지만, 선택의 폭이 넓어지면 트렌드에 맞춰 관리해야 하고 그에 따른 피로도와 결정장애가 생기기 마련이라는 점을 짚어주세요. 퇴직연금은 중장기 안정적인 성과를 추구해야 하는 장기자산이므로, 국민은행은 이런 자산의 특성과 시장상황 등을 고려해 엄선한 ETF만을 선별 제공하고 있다는 점을 안내할 수 있어요. 현재 당행에서 판매 중인 ETF는 총 193종(국내 90종, 해외 103종)으로 계속 늘려가고 있으며, 고객님의 선택 폭을 넓히기 위해 중복테마 및 거래가 활발하지 않은 ETF를 제외하고 상품 라인업을 최대 400개까지 확대할 예정이라는 사실을 함께 활용해 보세요.</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
@@ -3646,11 +3647,14 @@
       <c r="E85" s="6" t="inlineStr">
         <is>
           <t>● 정민석
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+예금만 하겠다는 고객에게는 원리금보장상품도 관리가 필요하다는 점을 짚어주고 같은 안전성 안에서 금리를 올려주는 제안으로 접근하는 게 핵심이에요. 
+우선 고객이 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 현재 보유 중인 정기예금 금리와 GIC·저축은행 정기예금 금리를 숫자 대 숫자로 나란히 비교해 주는 방식을 활용할 수 있어요. 
+상담을 진행할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요. 
+또한 보험사 공시이율은 2~3% 수준이지만 이를 IRP로 이전하셔서 원리금보장상품 GIC 3~5년제로 가입하시면 4.5% 이상의 금리를 가져가실 수 있다는 점을 함께 짚어드릴 수 있어요. 
+다만 사용 계획이 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내야 하고, 공격투자형이면서 스스로 초저위험을 선택한 고객은 원리금보장 100% 대상에서 제외해 이중 접촉을 방지해야 한다는 점을 유의해 주세요.
 ● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+예금만 하겠다는 고객에게는 원리금보장상품도 관리가 중요하다는 점을 짚어주고 금리 갈아타기로 대응하는 것이 핵심이에요. 예금 같은 원리금보장상품도 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 GIC 같은 고금리 상품을 비대면으로 손쉽게 거래할 수 있다는 점을 활용해 사후관리에서는 금리 갈아타기가 곧 관리라는 논리로 접근해요. 현금성자산이나 시중은행 정기예금 100%인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가요. 현재 보유 중인 정기예금 금리와 GIC 및 저축은행 정기예금 금리를 숫자 대 숫자로 나란히 제시하는 방식으로 대응해요. 고객에게는 이렇게 안내해 보세요.
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -3683,8 +3687,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>원금 손실을 우려하는 고객에게는 연금 자산의 투자 성격과 기간을 들어 위험의 의미를 다시 정의하며 접근하는 것이 핵심이에요. 먼저 주식이 위험하다는 고객의 의견을 수용하면서, 여기서 말하는 위험이 손실이 아니라 기간이 길어질수록 줄어드는 변동성임을 짚어주세요. 당장 1~2년 뒤에 쓸 돈이 아니라 은퇴 후 30년을 운용해야 할 자산이라는 점을 설명하고, 연금이야말로 기간이 길어 30년이면 손실 확률이 0%에 수렴하는 특성을 지닌다는 점을 안내할 수 있어요. 또한 '위험'이라는 단어가 주는 부담감을 줄이기 위해 30년이라는 장기 투자 기간과 소규모 납입금의 특성을 들어 오히려 연금투자가 변동성을 감당할 수 있는 자금 성격임을 설명하는 방식을 활용해 보세요. 다만 사용 계획이 있는 자금이나 연금지급 대기 및 교체매매 중인 자금은 먼저 걸러내야 하며, 고객에게 생소할 수 있는 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F86" s="13" t="inlineStr">
@@ -3721,8 +3724,15 @@
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이 고객에게는 적합성 확인 결과 허용된 상품 범위 안에서만 상품을 안내해야 해요. 현재 고객의 투자성향은 안정추구형이며, 적합성 허용 상한은 낮은위험으로 이 등급까지의 상품만 안내할 수 있어요. 
+안내할 수 있는 상품은 다음과 같아요.
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+반면 KB 글로벌채권인덱스 C-P, KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 중립형 MP, KB 성장형 MP, KB 글로벌리츠 ETF는 상품 위험등급이 허용 상한인 낮은위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
@@ -3755,8 +3765,14 @@
       </c>
       <c r="E88" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이 고객에게 안내할 수 없는 상품이 목록에서 빠진 이유는 고객의 투자성향이 안정추구형이라 위험등급 허용 상한이 낮은위험으로 정해져 있기 때문이에요. 앞서 말씀드린 안내할 수 없는 상품들은 상품 자체의 위험등급이 고객의 허용 상한보다 높아 제외되었으며, 구체적인 내용은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 중립형 MP —상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험 &gt; 허용 상한 낮은위험
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
@@ -3793,8 +3809,20 @@
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>공격투자형인 이 고객에게는 높은위험 등급까지의 상품만 안내할 수 있고, 허용 상한이 높은위험이라 카탈로그 전부가 범위 안이다. 다만 무엇을 권유할지는 직원이 판단해야 하므로, 안내할 수 있는 상품 목록을 확인하고 적합성 확인 결과이지 투자권유가 아니라는 점을 염두에 두어야 해요. 안내할 수 없는 상품은 없어요. 안내할 수 있는 상품 12종은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 온국민TDF2035 C-P — 다소높은위험 · 최근 1년 6.2% · TDF
+- KB 온국민TDF2040 C-P — 다소높은위험 · 최근 1년 6.6% · TDF
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB 중립형 MP — 보통위험 · 최근 1년 5.1% · MP
+- KB 성장형 MP — 다소높은위험 · 최근 1년 6.4% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 글로벌리츠 ETF — 높은위험 · 최근 1년 7.5% · ETF
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
@@ -3828,11 +3856,30 @@
       <c r="E90" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+이 고객의 투자성향과 위험등급 상한을 고려할 때 주식형 펀드는 안내할 수 없어요. 현재 고객의 투자성향은 안정추구형이고 적합성 허용 상한은 낮은위험이라서, 이 등급보다 높은 상품은 가입 대상이 아니에요. 따라서 위험등급이 보통위험 이상인 주식형 펀드는 안내가 제한돼요. 지금 고객에게 안내할 수 있는 상품은 위험등급이 낮은위험과 매우낮은위험에 해당하는 다음의 6종이에요.
+- KB 국내채권형 C-P — 낮은위험
+- KB 안정형 MP — 낮은위험
+- KB GIC 확정금리 — 매우낮은위험
+- KB ELB 지수연계 — 낮은위험
+- KB 정기예금(1년) — 매우낮은위험
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험
+반면 허용 상한을 초과하여 안내할 수 없는 상품과 그 사유는 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 중립형 MP — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험 &gt; 허용 상한 낮은위험
+이 내용은 적합성 확인 결과이며 투자권유가 아니에요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.
 ● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+안정추구형인 이 고객에게는 주식형 펀드를 바로 안내할 수 없어요. 이 고객의 적합성 허용 상한은 낮은위험이라서, 그보다 위험도가 높은 주식형 펀드는 가입 대상이 아니에요. 지금 고객에게 안내할 수 있는 상품은 위험등급이 낮은 상품들로 한정되어 있어요. 단말에서 확인된 허용 상한인 낮은위험 이하의 상품들만 골라서 다음과 같이 보여드릴 수 있어요.
+- KB 국내채권형 C-P — 낮은위험
+- KB 안정형 MP — 낮은위험
+- KB GIC 확정금리 — 매우낮은위험
+- KB ELB 지수연계 — 낮은위험
+- KB 정기예금(1년) — 매우낮은위험
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험
+반면에 글로벌채권인덱스 C-P, 온국민TDF2035 C-P, 온국민TDF2040 C-P, 중립형 MP, 성장형 MP, 글로벌리츠 ETF 같은 상품들은 상품 위험등급이 보통위험에서 높은위험까지로 고객의 허용 상한인 낮은위험을 초과하기 때문에 안내할 수 없어요. 이는 어디까지나 적합성 확인 결과에 따른 안내이며 특정 상품에 대한 투자권유가 아니라는 점을 염두에 두셔야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
@@ -3866,11 +3913,33 @@
       <c r="E91" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+안정추구형인 이 고객에게는 적합성 허용 상한이 낮은위험으로 설정되어 있어 그에 맞는 상품만 안내할 수 있어요. 
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. 안내할 수 있는 상품은 다음과 같아요.
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+이 고객의 허용 상한이 낮은위험이므로 위험등급이 그보다 높은 다음 상품들은 안내할 수 없어요.
+- KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 중립형 MP — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험 &gt; 허용 상한 낮은위험
+위 내용은 어디까지나 적합성 확인 결과에 따른 안내 범위이며, 실제 상품 안내 시에는 투자권유가 아님을 유의해야 해요.
 ● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+위험중립형인 이 고객에게 안내할 수 있는 위험등급 상한은 보통위험이며, 안내할 수 있는 상품은 총 8종이에요.
+- KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB 중립형 MP — 보통위험 · 최근 1년 5.1% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+이외에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험보다 높아 안내할 수 없으며, KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이라 안내할 수 없어요. 이 안내는 적합성 확인 결과이며 투자권유가 아니라는 점을 염두에 두시고, 사용계획이 있는 자금이라면 먼저 걸러내어 현금성자산이나 운용지시가 되지 않는 자산으로 다루어 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
@@ -3907,8 +3976,17 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>고객이 문의한 TDF 추천 연도 및 위험자산 비중 정보는 현재 준비된 자료가 없어 안내하기 어려워요. 대신 현재 등록된 투자성향을 기준으로 안내할 수 있는 상품 범위와 적합성 확인 결과를 짚어 드릴게요. 이 고객은 위험중립형 성향으로 위험등급 보통위험까지 허용되므로, 해당 등급 이내의 상품만 안내할 수 있어요. 
+안내할 수 있는 상품은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB 중립형 MP — 보통위험 · 최근 1년 5.1% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+반면에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하며, KB 글로벌리츠 ETF는 높은위험으로 역시 허용 상한을 초과하여 목록에 포함되지 않아요. 이 목록은 고객의 적합성 확인 결과에 따른 안내 가능 범위이며 특정 상품의 가입을 권유하는 것이 아니니 유의해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
@@ -3941,8 +4019,49 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>8월 퇴직연금 추천펀드(디폴트옵션)에 올라와 있는 상품은 위험도별로 구분되어 있으며, 2026년 8월 기준(수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준)으로 안내할 수 있다. 시장 변동과 상품 개편에 따라 빠르게 달라질 수 있으므로 인용 전 기준시점을 확인해야 한다. 
+초저위험 지켜드림 포트폴리오는 비중 100이며 1년 수익률 2.13%로 구성되어 있다. 편입상품은 다음과 같다.
+- 지켜드림 — 신한은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 35, 금리 3.40%)
+- 지켜드림 — 기업은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 35, 금리 3.25%)
+- 지켜드림 — 하나은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 30, 금리 3.32%)
+저위험 알파드림 포트폴리오는 비중 100이며 1년 수익률 4.23%이다. 편입상품은 다음과 같다.
+- 알파드림 — 수협은행 노후보장 정기예금 디폴트옵션용(3년) (비중 70, 금리 3.27%)
+- 알파드림 — 키움키워드림적격TDF2030 (비중 20)
+- 알파드림 — 삼성글로벌EMP적격TDF2035 (비중 10)
+저위험 알파드림 II 포트폴리오는 비중 100이며 1년 수익률 8.56%이다. 편입상품은 다음과 같다.
+- 알파드림 II — 기업은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 50, 금리 3.25%)
+- 알파드림 II — KB다이나믹적격TDF2030 (비중 40)
+- 알파드림 II — NH하나로적격TDF2035 (비중 10)
+저위험 알파드림 III 포트폴리오는 비중 100이며 1년 수익률 5.86%이다. 편입상품은 다음과 같다.
+- 알파드림 III — 농협은행 디폴트옵션 퇴직연금 정기예금(3년) (비중 35, 금리 3.40%)
+- 알파드림 III — DB손해보험 퇴직연금 디폴트옵션 이율보증형보험(3년) (비중 35, 금리 4.41%)
+- 알파드림 III — KB온국민적격TDF2035(H) (비중 30)
+중위험 뿔려드림 포트폴리오는 비중 100이며 1년 수익률 13.95%이다. 편입상품은 다음과 같다.
+- 뿔려드림 — 하나은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 30, 금리 3.32%)
+- 뿔려드림 — KB다이나믹적격TDF2040 (비중 50)
+- 뿔려드림 — 한화Lifeplus적격TDF2040 (비중 20)
+중위험 뿔려드림 II 포트폴리오는 비중 100이며 1년 수익률 15.04%이다. 편입상품은 다음과 같다.
+- 뿔려드림 II — 미래에셋평생소득 TIF (비중 70)
+- 뿔려드림 II — 키움불리온글로벌멀티에셋EMP(UH) (비중 20)
+- 뿔려드림 II — IBK플레인바닐라EMP (비중 10)
+중위험 뿔려드림 III 포트폴리오는 비중 100이며 1년 수익률 10.59%이다. 편입상품은 다음과 같다.
+- 뿔려드림 III — KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) (비중 20, 금리 4.25%)
+- 뿔려드림 III — KB드림스타자산배분안정형 (비중 80)
+고위험 모두드림 포트폴리오는 비중 100이며 1년 수익률 20.63%이다. 편입상품은 다음과 같다.
+- 모두드림 — KB온국민적격TDF2055(UH) (비중 60)
+- 모두드림 — 한국투자적격TDF알아서2050(UH) (비중 20)
+- 모두드림 — 한화Lifeplus적격TDF2045 (비중 20)
+고위험 모두드림 II 포트폴리오는 비중 100이며 1년 수익률 19.19%이다. 편입상품은 다음과 같다.
+- 모두드림 II — KB다이나믹적격TDF2050 (비중 50)
+- 모두드림 II — 한국투자적격TDF알아서2055(UH) (비중 40)
+- 모두드림 II — 미래에셋전략배분적격TDF2050 (비중 10)
+고위험 모두드림 III 포트폴리오는 비중 100이며 1년 수익률 15.19%이다. 편입상품은 다음과 같다.
+- 모두드림 III — 미래에셋디폴트전략배분성장형 (비중 100)
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기
+── 빠뜨리면 안 되는 표시
+· 8월 퇴직연금 추천펀드(디폴트옵션)
+  ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+  ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -3975,8 +4094,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>수익률 비교 질문을 하는 고객에게는 금융감독원 공시와 디폴트옵션 실적을 근거로 제시하면서 장기적인 관점의 관리를 약속하는 방식으로 접근해야 해요. 다른 은행과 비교하는 고객에게는 단기 성과보다 장기 관리가 중요하다는 점을 짚어주는 것이 핵심이에요. IRP 실적배당형 부문 전 구간 1위와 디폴트옵션 수익률 순위를 안내할 수 있도록 "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀드려 보세요. 또한 디폴트옵션 고위험 포트폴리오의 실적을 바탕으로 "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요.</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -4009,8 +4127,46 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>디폴트옵션 포트폴리오의 구성상품과 비중, 금리 정보는 2026년 8월 기준(수익률은 2026년 7월 30일, 원리금보장 금리는 2026년 8월 기준)으로 안내할 수 있는 상품들이 있다. 위험도별 포트폴리오의 구체적인 구성과 비중, 금리는 다음과 같이 확인된다.
+초저위험 '지켜드림' 포트폴리오
+- 신한은행 퇴직연금 디폴트옵션 정기예금(3년) — 비중 35%, 금리 3.40%
+- 기업은행 퇴직연금 디폴트옵션 정기예금(3년) — 비중 35%, 금리 3.25%
+- 하나은행 퇴직연금 디폴트옵션 정기예금(3년) — 비중 30%, 금리 3.32%
+저위험 '알파드림' 포트폴리오
+- 수협은행 노후보장 정기예금 디폴트옵션용(3년) — 비중 70%, 금리 3.27%
+- 키움키워드림적격TDF2030 — 비중 20%
+- 삼성글로벌EMP적격TDF2035 — 비중 10%
+저위험 '알파드림 II' 포트폴리오
+- 기업은행 퇴직연금 디폴트옵션 정기예금(3년) — 비중 50%, 금리 3.25%
+- KB다이나믹적격TDF2030 — 비중 40%
+- NH하나로적격TDF2035 — 비중 10%
+저위험 '알파드림 III' 포트폴리오
+- 농협은행 디폴트옵션 퇴직연금 정기예금(3년) — 비중 35%, 금리 3.40%
+- DB손해보험 퇴직연금 디폴트옵션 이율보증형보험(3년) — 비중 35%, 금리 4.41%
+- KB온국민적격TDF2035(H) — 비중 30%
+중위험 '뿔려드림' 포트폴리오
+- 하나은행 퇴직연금 디폴트옵션 정기예금(3년) — 비중 30%, 금리 3.32%
+- KB다이나믹적격TDF2040 — 비중 50%
+- 한화Lifeplus적격TDF2040 — 비중 20%
+중위험 '뿔려드림 II' 포트폴리오
+- 미래에셋평생소득 TIF — 비중 70%
+- 키움불리온글로벌멀티에셋EMP(UH) — 비중 20%
+- IBK플레인바닐라EMP — 비중 10%
+중위험 '뿔려드림 III' 포트폴리오
+- KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) — 비중 20%, 금리 4.25%
+- KB드림스타자산배분안정형 — 비중 80%
+고위험 '모두드림' 포트폴리오
+- KB온국민적격TDF2055(UH) — 비중 60%
+- 한국투자적격TDF알아서2050(UH) — 비중 20%
+- 한화Lifeplus적격TDF2045 — 비중 20%
+고위험 '모두드림 II' 포트폴리오
+- KB다이나믹적격TDF2050 — 비중 50%
+- 한국투자적격TDF알아서2055(UH) — 비중 40%
+- 미래에셋전략배분적격TDF2050 — 비중 10%
+고위험 '모두드림 III' 포트폴리오
+- 미래에셋디폴트전략배분성장형 — 비중 100%
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F95" s="14" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4199,8 +4199,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>직원이 물어본 TDF 수익률 및 위험등급에 대해서는 현재 준비된 자료가 없어요. 다만 2026년 3월에 작성된 연금사업본부 연금컨설팅부 자료를 기준으로 2025년 10월 기준 당행 라인업의 개념과 선택 공식에 관한 내용은 확인할 수 있어요. TDF는 은퇴 시점에 맞춰 주식→채권 비중을 자동 조정하는 자산배분 펀드다(전략 명칭 글라이드 패스). 상품명 숫자 = 목표 은퇴연도, 5년 단위 빈티지. 선택 공식 출생연도 + 예상 은퇴연령 = Target Date(예: 1990+60=2050). 당행 라인업 총 18종(2025.10 기준). 환헤지 여부로 H(헤지) / UH(언헤지) 상품이 구분된다 — H는 환율 변동 영향 축소, UH는 환차익·환차손 반영. 관련 내용은 기준시점 2025.10 (KBthink 04) 기준으로 안내해 드릴 수 있어요.</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
@@ -4233,8 +4232,51 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>■ 투자성향별 포트폴리오  (상품 · 퇴직연금 펀드 8월 포트폴리오)
+· 기준시점: 2026.08
+### ① 안정형
+- **자산배분** : 국내채권 100%
+- **기대수익 2.4% / 변동성 3.0%**
+| 구분 | 상품명 | 투자비중 | 상품특징 |
+|---|---|---|---|
+| 국내채권 | 한화 내일받는 단기국공채 (합성총보수 연0.1977%) | 30% | 무위험 채권 및 특수채, 우량채에 투자하며, 채권잔존만기를 6개월 수준으로 유지하여 채권가격 변동위험 최소화 |
+| 국내채권 | 유진 챔피언 단기채 (합성총보수 연0.3290%) | 30% | 잔존만기가 짧은 전단채 및 기업어음에 주로 투자하여 금리변동 리스크 관리 |
+| 국내채권 | KB 스타 단기국공채 (총보수 연0.2430%) | 40% | 단기 국채, 지방채, 특수채 및 우량 회사채에 투자하여 안정적인 수익 추구 |
+### ② 안정추구형
+- **자산배분** : 국내채권 80% / 해외채권 20%
+- **기대수익 2.4% / 변동성 3.6%**
+| 구분 | 상품명 | 투자비중 | 상품특징 |
+|---|---|---|---|
+| 국내채권 | 키움 더드림 단기채 (합성총보수 연0.2990%) | 80% | 국내 단기채권 및 CP 등에 60% 이상을 투자하여 안정적인 이자수익 추구 |
+| 해외채권 | KB 글로벌 단기채(H) (합성총보수 연0.6960%) | 10% | 전세계 달러표시 단기채권에 투자하여 안정적 수익추구 |
+| 해외채권 | AB글로벌고수익 (합성총보수 연1.3670%) | 10% | 미국 및 이머징국가 기업발행 하이일드채권에 주로 투자하여 초과 수익 추구 |
+### ③ 위험중립형
+- **자산배분** : 국내채권 60% / 해외채권 15% / 해외혼합 25%
+- **기대수익 5.4% / 변동성 4.9%**
+| 구분 | 상품명 | 투자비중 | 상품특징 |
+|---|---|---|---|
+| 국내채권 | 하나 파워e단기채 (합성총보수 연0.1834%) | 60% | 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구 |
+| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 15% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
+| 해외혼합 | 삼성EMP 리얼리턴(UH) (합성총보수 연1.1215%) | 25% | 국내외 주식, 채권, 대체자산 등 다양한 자산 관련 ETF에 투자 |
+### ④ 적극투자형
+- **자산배분(도넛 표기)** : 국내채권 30% / 해외채권 10% / 해외주식 60% ⟨판독불확실⟩
+- **기대수익 10.3% / 변동성 9.7%**
+| 구분 | 상품명 | 투자비중 | 상품특징 |
+|---|---|---|---|
+| 국내채권 | NH-Amundi 하나로단기채 (합성총보수 연0.2939%) | 35% | 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구 |
+| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 5% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
+| 해외주식 | 신한누버거버먼 미국가치주(H) (합성총보수 연1.6100%) | 60% | 미국가치주 등에 주로 투자하는 누버거버먼 미국 라지캡밸류펀드에 투자하는 주식형펀드 |
+&gt; *※ 도넛 차트 표기(국내채권 30 / 해외채권 10)와 구성상품 표의 비중(국내채권 35 / 해외채권 5)이 원문상 상이하게 표기되어 있어 그대로 옮김.*
+### ⑤ 공격투자형
+- **자산배분** : 국내채권 25% / 해외채권 5% / 해외주식 70%
+- **기대수익 11.7% / 변동성 11.2%**
+| 구분 | 상품명 | 투자비중 | 상품특징 |
+|---|---|---|---|
+| 국내채권 | 교보악사Tomorrow 장기우량K-1 (총보수 연0.3300%) | 25% | 국공채, 통안채, 공사채, 은행채, 우량회사채 등 안정성이 높은 채권을 투자대상자산으로 하여 자본이득과 안정적인 이자 수익 추구 |
+| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 5% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
+| 해외주식 | 삼성글로벌 배당성장주(H) (합성총보수 연1.4213%) | 70% | 지속적으로 배당이 증가하는 선진국 중심의 배당성장주 및 밸류에이션 매력이 높은 고배당기업에 투자 |
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 기준 표기입니다.
+· 출처 퇴직연금 펀드 8월 포트폴리오 (2026-08)</t>
         </is>
       </c>
       <c r="F97" s="14" t="inlineStr">
@@ -4271,8 +4313,7 @@
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>시장 불안을 이유로 실적배당형 상품 전환을 고민하는 고객에게는 연금의 자금 성격과 운용 기간의 특성을 활용해 접근하는 것이 핵심이에요. 연금은 일반 투자와 달리 30년 이상이라는 장기 기간을 가지며 투입되는 규모도 상대적으로 작아 마이너스 50%를 맞아도 실제 체감하는 타격이 크지 않다는 점을 짚어주세요. 일반 투자는 금액이 크고 기간이 짧아 저변동성이 맞지만, 연금은 오히려 변동성을 지향해도 된다는 논리로 고객의 통념을 전환해 줄 수 있어요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 연금지급 대기나 교체매매 중으로 사용계획이 있는 자금은 먼저 걸러내야 해요. 또한 고객에게 설명할 때는 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 시장 상황에 대한 불안을 해소할 때는 우리나라 사람들이 실거주 부동산을 30~50년씩 보유하는 것처럼 30년 이상의 기간에는 이미 익숙하다는 점을 함께 안내해 주세요.</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
@@ -4382,8 +4423,7 @@
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
@@ -4417,11 +4457,12 @@
       <c r="E102" s="18" t="inlineStr">
         <is>
           <t>● 정민석
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+질문하신 고객의 원리금보장 상품 유지 여부를 판단할 때 시장 상황과 자금의 성격을 함께 고려해야 해요. 2026년 8월 3주차 기준으로 미국 증시는 소비자물가 예상 부합과 생산자물가 예상 하회, 연준 금리 인상 우려 완화 속에 AI 반도체 및 기술주 중심의 상승세로 S&amp;P500지수가 사상 최고치를 경신했으나, 미국-이란 긴장으로 인한 국제유가 상승, 미국 재정 적자 우려, 하이퍼스케일러들의 AI 인프라 투자 자금 채권시장 조달에 따른 미국 국채 금리 상승 등이 증시 상승세를 제약하는 요인으로 작용하고 있습니다. 2026년 9월 기준으로는 미국 FOMC와 일본 BOJ 등 주요 경제 이벤트와 점도표 변화, 엔 캐리 청산 우려 등 변동성 확대 요인이 있으므로 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. 또한 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라진니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.
+── 빠뜨리면 안 되는 표시
+· 「Insight to Solution」 월간 주요 이벤트 &amp; 투자전략 — 2026년 9월
+  ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.
 ● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+요즘 시황 근거로 원리금보장 자산을 그대로 두어도 되는지 판단할 때는 2026년 8월 3주차와 2026년 9월 자료에서 다루는 시장 상황과 기준시점을 확인해야 해요. 미국 7월 소비자물가가 예상에 부합하고 생산자물가는 예상을 하회하여 연준 금리 인상 우려가 완화된 반면, 미·이런 긴장에 따른 국제유가 상승과 미국 국채 금리 상승 요인이 함께 작용하고 있어요. 또한 9월에는 기준금리 동결 후 데이터 의존 입장을 반복할 것으로 예상되는 미국 FOMC와 기준금리 인상이 예상되는 일본 BOJ 금융정책결정회의 등 중요 이벤트가 예정되어 있어요. 미국 재정적자 확대와 장기국채 수요 감소를 감안해 장기금리 하락은 비중 축소 기회로 활용할 수 있으며, BOJ의 기준금리 인상과 엔 캐리 청산 우려가 있으나 인상이 예상된 이벤트라 2024년 8월과 같은 증시 폭락 가능성은 낮다고 판단하고 있어요. 다만 사용계획이 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내어 판단해야 해요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
@@ -4462,8 +4503,9 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객에게 안내할 만한 이벤트와 세미나는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있고 디폴트옵션이 미설정된 상태이므로 잠자는 IRP 자금 깨우기 운용 이벤트와 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나를 안내하는 것이 핵심이에요.
+잠자는 IRP 자금 깨우기 운용 이벤트는 12/30까지 KB스타뱅킹에서 진행되며, 고객이 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 상태이므로 참고하시기 좋고 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX를 활용할 수 있어요.
+퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나는 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 온라인 세미나로, 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어 추천하며 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX로 안내할 수 있어요.</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4496,8 +4538,11 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객에게 잠자는 IRP 자금 깨우기 운용 이벤트를 안내하는 이유는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 성립 요건을 충족하기 때문이에요. 고객이 최종 운용변경 이후 장기간 운용되지 않은 자금을 보유하고 있어 운용상품을 선택하거나 변경할 수 있도록 이벤트를 권유할 수 있어요. 안내 시 참고할 발송 문구는 다음과 같아요.
+(광고) 송도윤 고객님, KB국민은행입니다.
+KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요.
+▶ https://obank.kbstar.com/demo/event/irp-004
+무료수신거부 080-XXX-XXXX</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -4534,8 +4579,11 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기
+화면이 열리면 이 문구를 넣어 주세요 — "(광고) 송도윤 고객님, KB국민은행입니다.
+KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요.
+▶ https://obank.kbstar.com/demo/event/irp-004
+무료수신거부 080-XXX-XXXX"</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -4572,8 +4620,9 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이 고객에게 안내할 이벤트와 세미나의 발송 문구는 자료에 있는 문구를 그대로 활용하는 게 핵심이에요. 
+잠자는 IRP 자금 깨우기 운용 이벤트 발송 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX"를 그대로 사용해 주세요.
+온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -4610,8 +4659,17 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 말씀드린 2건 외에 잠재적 안내 후보로 열려 있는 이벤트 3건과 세미나 4건이 더 있어요.
+이벤트 3건은 다음과 같아요.
+- ISA 만기자금, IRP로 이어가는 절세 이벤트 — 12/25까지
+- IRP 추가입금하고 절세혜택 챙기기 이벤트 — 11/25까지
+- 다른 금융기관 IRP, KB로 이전하고 혜택받기 — 12/11까지
+세미나 4건은 다음과 같아요.
+- 연금개시 전 꼭 알아야 할 IRP 수령 방법 — 11/3(화) 17시
+- 예금만으로 괜찮을까? 퇴직연금 자산배분 전략 — 11/10(화) 17시
+- 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 — 11/12(목) 17시
+- 금리 변화기, 퇴직연금 예금 만기 이후 운용 전략 — 11/17(화) 17시
+고객에게 안내할 때는 사용계획이 있는 자금인지 먼저 확인하고 활용할 수 있는 방법을 살펴보세요. 세부적인 발송 문구나 링크가 필요한 항목이 있다면 이어서 말씀해 드릴게요.</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
@@ -4648,8 +4706,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>현재 이 고객의 요건에 맞는 세미나는 아직 준비된 자료가 없어요. 다만 열려 있는 콘텐츠 중 날짜가 가까운 세미나로는 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 세미나가 11/12(목) 17시에 KB국민은행 WM투자부 주관으로 예정되어 있어요. 이 세미나는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋은 내용이에요. 안내할 때 참고할 수 있는 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요.</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -4686,8 +4743,8 @@
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이번 상담에서 아직 오간 대화가 없습니다.
+— 쪽지를 보낼 받는 사람을 알 수 없어요 — 로그인 사번이 넘어오지 않았습니다. «사번 3902172한테 보내줘»처럼 사번을 알려주시면 그 앞으로 보낼게요.</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4777,8 +4777,7 @@
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2519,31 +2519,7 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-이전 대화에서 나눈 ISA 만기자금 8,000만원 전액 전환 기준의 추가 공제와 달리, 일부 금액만 전환하는 경우라면 전환액에 따라 추가 공제 대상이 달라져요. 1,000만원을 전환하면 100만원이, 2,000만원을 전환하면 200만원이, 3,000만원 이상을 전환하면 상한인 300만원이 세액공제 대상에 더해져요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 한지우
-■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
-· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
-· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
-· 계산에 쓴 추가 납입액 300만원 (질문에 금액이 없어 잔여한도로 계산했다)
-· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
-· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
-· 공제율은 **원장의 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
-■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
-· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
-· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
-· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 전환금 전액이 공제 대상이 되는 것이 아니다
-· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
-· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
-· 계산에 쓴 전환액 8,000만원 → 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
-· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
-· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
-● 송도윤
-송도윤 고객의 총급여가 5,500만원 초과 구간인 경우라면 ISA 만기자금 1억 2,000만원 중 일부인 1,000만원, 2,000만원, 3,000만원을 개인형IRP 계좌로 전환할 때 각각 추가 공제 대상 100만원, 200만원, 300만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 5,500만원 초과 구간의 적용 공제율 등 세부 세액공제율 자료는 아직 준비된 자료가 없어요.</t>
-        </is>
-      </c>
+      <c r="E54" s="18" t="n"/>
       <c r="F54" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2576,16 +2552,7 @@
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>● 김서연
-김서연 고객의 개인형IRP 계좌 추가 납입과 관련하여 총급여 5,500만원 이하 구간을 확인하였으므로 16.5%의 공제율을 적용하여 환급 예상액을 안내하는 게 핵심이에요. 앞서 말씀드린 현금을 더 납입하는 경우, 잔여한도 500만원을 추가 납입하면 총급여 5,500만원 이하(16.5%) 기준으로 1,485,000원의 환급 예상액을 받으실 수 있어요. 이는 기존 당해 납입액 400만원에 따른 660,000원에서 825,000원이 늘어나는 금액이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 한지우
-총급여 5,500만원 이하 구간 기준으로 안내해 드려야 해요. 앞서 말씀드린 ISA 만기자금 8,000만원 중 일부를 개인형IRP 계좌로 전환할 때 전환액별 추가 공제 대상은 1,000만원 전환 시 100만원, 2,000만원 전환 시 200만원, 3,000만원 이상 전환 시 상한인 300만원이 되어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 송도윤
-총급여 5,500만원 이하인 송도윤 고객이 ISA 만기자금 1억 2,000만원 중 일부인 3,000만원을 개인형IRP 계좌로 전환할 때 예상되는 세액공제 환급액은 495,000원이에요. 이 금액은 총급여 5,500만원 이하 적용 공제율 16.5%와 추가 공제 대상 300만원이 반영된 결과예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 대로 전환금은 연 납입한도 1,800만원과 무관하며, 현금을 더 납입하는 경우와는 다른 한도로 별개로 더해지는 몫이에요.</t>
-        </is>
-      </c>
+      <c r="E55" s="18" t="n"/>
       <c r="F55" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -6870,7 +6837,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2519,7 +2519,21 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="n"/>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+총급여 5,500만원 초과 구간인 고객에게는 ISA 만기자금 중 일부를 개인형IRP 계좌로 전환할 때의 세액공제 효과를 금액별로 짚어주는 게 핵심이에요. 앞서 말씀드린 8,000만원 전액 전환 시의 추가 공제 대상 300만원과 늘어나는 환급액 396,000원 외에, 질문하신 일부 금액 전환 시에는 전환액 1,000만원일 때 추가 공제 대상 100만원과 전환액 2,000만원일 때 추가 공제 대상 200만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액들은 현금을 더 납입하는 경우와 별개로 더해지는 몫이니, 두 한도를 같은 안에서 저울질하지 않고 각각 안내해 주세요.
+● 한지우
+ISA 만기자금 중 일부를 IRP 계좌로 전환할 때는 전환액의 10%가 세액공제 대상에 더해져 공제 한도가 최대 1,200만원까지 늘어나요. 
+고객이 8천만원 중 일부만 전환하는 경우, 전환액별로 추가되는 공제 대상 금액은 다음과 같이 달라져요.
+- 1,000만원 전환 — 추가 공제 대상 100만원
+- 2,000만원 전환 — 추가 공제 대상 200만원
+- 3,000만원 이상 전환 — 추가 공제 대상 300만원(상한)
+총급여가 5,500만원을 초과해 13.2%의 공제율이 적용되는 경우, 전환액 3,000만원 이상을 넣으면 늘어나는 환급액은 396,000원이 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 현금 추가 납입분과 ISA 전환분은 서로 다른 한도이므로 같은 한도 안에서 저울질하지 않도록 안내해 주세요.
+● 송도윤
+총급여 5,500만원 초과 구간인 송도윤 고객에게는 ISA 만기자금 1억 2,000만원 중 일부인 1억 2,000만원을 개인형IRP 계좌로 전환할 때 추가 공제 대상 300만원과 적용 공제율 13.2%를 반영한 환급 예상액 396,000원을 안내하는 것이 핵심이에요. 앞서 말씀드린 현금을 더 납입하는 경우와는 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않아야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리 리허설</t>
@@ -2552,7 +2566,17 @@
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="n"/>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+김서연 고객의 총급여가 5,500만원 이하인 경우라면 개인형IRP 계좌 추가 납입과 ISA 만기자금 전환 각각에 따른 세액공제 금액을 나누어 짚어 주는 게 핵심이에요. 현금을 추가 납입할 때는 500만원을 개인형IRP 계좌에 넣으면 총급여 5,500만원 이하 기준 16.5%가 적용되어 825,000원이 늘어난 1,485,000원의 환급을 예상할 수 있어요. ISA 만기자금 8,000만원 중 일부인 1,000만원을 전환할 때는 100만원이 추가 공제 대상이 되고, 2,000만원을 전환하면 200만원, 3,000만원 이상을 전환하면 상한인 300만원이 추가 공제 대상이 되어 총급여 5,500만원 이하 기준 16.5%를 적용하면 495,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+총급여가 5,500만원 이하인 고객에게는 개인형IRP 계좌로 ISA 만기자금을 일부 전환할 때 전환액에 따라 추가 공제 대상이 달라진다는 점을 짚어주는 게 핵심이에요. 앞서 말씀드린 대로 전환액의 10%가 세액공제 대상에 더해지며 상한은 300만원이에요. 전환액별 추가 공제 대상은 1,000만원이면 100만원, 2,000만원이면 200만원, 3,000만원 이상이면 상한인 300만원이 적용되어요. 총급여 5,500만원 이하 구간에서는 16.5%의 공제율이 적용되어 전환액 3,000만원 이상일 때 늘어나는 환급액은 495,000원이 되어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 송도윤
+송도윤 고객의 총급여가 5,500만원 이하로 확인된 경우, ISA 만기자금 1억 2,000만원 중 일부인 3,000만원을 개인형IRP 계좌로 전환하면 추가 공제 대상 300만원이 더해져 총급여 5,500만원 이하 기준 적용 공제율 16.5%로 계산된 495,000원의 환급액을 받게 돼요.
+만기자금 전환은 기존 현금 추가 납입과 별개의 한도로 운영되는 몫이라 서로 다른 한도 안에서 저울질하지 않고 더해지는 구조예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 안 해본 질문</t>
@@ -4781,8 +4805,7 @@
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이번 상담에서 오간 대화 기록이 없어요.</t>
         </is>
       </c>
       <c r="F111" s="19" t="inlineStr">
@@ -4815,8 +4838,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
@@ -4853,8 +4875,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -4887,8 +4908,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -4921,8 +4941,18 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>추천 상품을 다른 걸로 바꿔 달라는 요청에 대해서는 직접적인 변경 사유나 추가 상품을 안내해 드릴 자료가 아직 준비된 사유가 없어요. 다만 현재 등록된 투자성향 기준으로는 안내할 수 있는 위험등급 상한이 보통위험까지예요. 
+이 고객은 위험중립형 성향이라 보통위험 등급까지만 상품을 안내할 수 있어서, 현재 기준으로 안내 가능한 상품 목록은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB 중립형 MP — 보통위험 · 최근 1년 5.1% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+반면 KB 온국민TDF2035 C-P는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험보다 높아 안내할 수 없으며, KB 온국민TDF2040 C-P 역시 다소높은위험 등급이라 목록에서 제외돼요. KB 성장형 MP도 다소높은위험 등급이라 안내 대상이 아니며, KB 글로벌리츠 ETF는 높은위험 등급이어서 역시 안내할 수 없어요. 
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
@@ -4959,8 +4989,10 @@
       </c>
       <c r="E116" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 내용을 바탕으로 고객에게 바로 전달할 수 있는 핵심 대사만 짧게 줄여서 정리해 드릴게요. 
+연금지급 대기 자금이나 교체매매 중인 자금이 아닌지 먼저 확인한 뒤에 이렇게 안내해 보세요.
+"예금과 같은 원리금보장상품도 관리가 중요하며, 매월 금리가 좋은 상품을 지속적으로 제공하고 있으니 GIC 같은 고금리 상품을 비대면으로 거래해 보세요."
+이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정해 약속하지 않도록 주의하고, 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용하여 고객이 쉽게 이해할 수 있도록 설명해 주세요.</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -4997,8 +5029,9 @@
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 상품 중 두 번째 상품인 KB 국내채권형 C-P에 대해 자세히 설명해 드릴게요.
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -5035,8 +5068,7 @@
       </c>
       <c r="E118" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
@@ -5073,8 +5105,15 @@
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 개인형IRP 수수료는 부담금 종류와 채널 및 구간에 따라 차등 적용되니 단말에서 먼저 확인한 뒤 안내해 주세요. 상세 수수료율은 다음과 같이 대면 및 비대면 채널별 구간에 따라 적용돼요.
+- 사용자부담금(퇴직금) 대면 5천만원 미만 — 0.45%
+- 사용자부담금(퇴직금) 대면 5천만원 이상 — 0.38%
+- 사용자부담금(퇴직금) 비대면 5천만원 미만 — 0.20%
+- 사용자부담금(퇴직금) 비대면 5천만원 이상 — 면제
+- 가입자부담금 대면 1억원 미만 — 0.28%
+- 가입자부담금 대면 1억원 이상 — 0.25%
+- 가입자부담금 비대면 1억원 미만 — 0.23%
+- 가입자부담금 비대면 1억원 이상 — 0.21%</t>
         </is>
       </c>
       <c r="F119" s="19" t="inlineStr">
@@ -5111,8 +5150,9 @@
       </c>
       <c r="E120" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>예금만으로 자산을 보유해 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 자산관리라는 논리로 접근하는 게 핵심이에요. 앞서 안내드린 내용에 수수료 관련 내용은 자료에 없어 추가하지 못했어요. 이미 안전하게 잘 운용하고 계신 점을 먼저 인정한 뒤, 원리금보장 상품도 매월 최고금리 상품 제공과 비대면 거래를 통해 꾸준히 관리해야 한다는 점을 짚어주세요. 
+고객에게는 이렇게 말씀해 보세요.
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
@@ -5149,8 +5189,7 @@
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이번 상담에서 오간 대화 기록은 없습니다.</t>
         </is>
       </c>
       <c r="F121" s="19" t="inlineStr">
@@ -6837,7 +6876,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -5226,8 +5226,22 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>■ 제가 도와드릴 수 있는 것
+IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
+· 신규 제안 — 다양한 고객에게 IRP를 처음 권할 때
+· 거절 대응 — 관리·수익률 불만, 제도·투자 거부, 증권사 비교, 해지·망설임 같은 반응이 나왔을 때
+· 운용관리 업무 가이드 — 예: 기존 고객 정기 관리의 타이밍 → 만기 1개월 전 안내 등 4원칙
+· 관리 대상 정의 — 어떤 고객군을 왜 관리하는지 (86건)
+· 관리 방법론 — 이런 상황이면 무엇을 제안하는지 (131건)
+· 업무 처리 절차 — 처리 순서·주의 (74건)
+· 단말 화면번호 — 무슨 업무가 몇 번 화면인지 (87건)
+· 비대면 채널 경로 — 고객이 앱·웹에서 직접 하는 메뉴 (56건)
+· 현장의 목소리 — 영업점이 실제로 하는 방식 (10건)
+· 제도·상품 팩트 — 한도·요건·수수료 같은 확정 수치 (64건)
+■ 활용 팁
+"사업자 고객인데 수수료 부담된다고 하시네요" 처럼 실제 상황을 그대로 말씀해 주시면 바로 화법을 찾아드려요.
+고객이 한 말을 그대로 옮겨 주셔도 됩니다("증권사가 수수료 무료라던데요") — 그 말에 어떻게 답하면 되는지 짚어드려요.
+"세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
@@ -5260,8 +5274,24 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>■ 제가 도와드릴 수 있는 것
+IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
+· 신규 제안 — 다양한 고객에게 IRP를 처음 권할 때
+· 거절 대응 — 관리·수익률 불만, 제도·투자 거부, 증권사 비교, 해지·망설임 같은 반응이 나왔을 때
+· 운용관리 업무 가이드 — 예: 기존 고객 정기 관리의 타이밍 → 만기 1개월 전 안내 등 4원칙
+· 관리 대상 정의 — 어떤 고객군을 왜 관리하는지 (86건)
+· 관리 방법론 — 이런 상황이면 무엇을 제안하는지 (131건)
+· 업무 처리 절차 — 처리 순서·주의 (74건)
+· 단말 화면번호 — 무슨 업무가 몇 번 화면인지 (87건)
+· 비대면 채널 경로 — 고객이 앱·웹에서 직접 하는 메뉴 (56건)
+· 현장의 목소리 — 영업점이 실제로 하는 방식 (10건)
+· 제도·상품 팩트 — 한도·요건·수수료 같은 확정 수치 (64건)
+· 지난 상담 기록 — 이 고객과 언제 무슨 얘기를 했는지
+· 이번 상담 요약 — 지금까지 나눈 대화를 정리하고, 원하시면 쪽지로 보내기
+■ 활용 팁
+"사업자 고객인데 수수료 부담된다고 하시네요" 처럼 실제 상황을 그대로 말씀해 주시면 바로 화법을 찾아드려요.
+고객이 한 말을 그대로 옮겨 주셔도 됩니다("증권사가 수수료 무료라던데요") — 그 말에 어떻게 답하면 되는지 짚어드려요.
+"세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
       <c r="F123" s="14" t="inlineStr">
@@ -5294,8 +5324,24 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>■ 제가 도와드릴 수 있는 것
+IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
+· 신규 제안 — 다양한 고객에게 IRP를 처음 권할 때
+· 거절 대응 — 관리·수익률 불만, 제도·투자 거부, 증권사 비교, 해지·망설임 같은 반응이 나왔을 때
+· 운용관리 업무 가이드 — 예: 기존 고객 정기 관리의 타이밍 → 만기 1개월 전 안내 등 4원칙
+· 관리 대상 정의 — 어떤 고객군을 왜 관리하는지 (86건)
+· 관리 방법론 — 이런 상황이면 무엇을 제안하는지 (131건)
+· 업무 처리 절차 — 처리 순서·주의 (74건)
+· 단말 화면번호 — 무슨 업무가 몇 번 화면인지 (87건)
+· 비대면 채널 경로 — 고객이 앱·웹에서 직접 하는 메뉴 (56건)
+· 현장의 목소리 — 영업점이 실제로 하는 방식 (10건)
+· 제도·상품 팩트 — 한도·요건·수수료 같은 확정 수치 (64건)
+· 지난 상담 기록 — 이 고객과 언제 무슨 얘기를 했는지
+· 이번 상담 요약 — 지금까지 나눈 대화를 정리하고, 원하시면 쪽지로 보내기
+■ 활용 팁
+"사업자 고객인데 수수료 부담된다고 하시네요" 처럼 실제 상황을 그대로 말씀해 주시면 바로 화법을 찾아드려요.
+고객이 한 말을 그대로 옮겨 주셔도 됩니다("증권사가 수수료 무료라던데요") — 그 말에 어떻게 답하면 되는지 짚어드려요.
+"세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
       <c r="F124" s="14" t="inlineStr">
@@ -5332,8 +5378,7 @@
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
       <c r="F125" s="19" t="inlineStr">
@@ -5366,8 +5411,18 @@
       </c>
       <c r="E126" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>요청하신 타겟 목록의 고객번호는 현재 자료에 없어요. 2026년 9월 29일 기준 타겟 목록에 있는 고객들의 선정 사유와 순서를 안내해 드릴게요.
+- 윤가영 — 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원, 디폴트옵션 미설정
+- 송도윤 — 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월
+- 정민석 — 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월
+- 최서윤 — 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건
+- 박지민 — 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원
+- 이수민 — 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원
+- 박정호 — 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원
+- 김현수 — 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정
+- 오세훈 — 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시
+- 김서연 — ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원
+- 한지우 — ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원</t>
         </is>
       </c>
       <c r="F126" s="19" t="inlineStr">
@@ -5408,8 +5463,10 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>증권사 수수료 무료를 이유로 이탈하려는 고객에게는 면제 조건을 먼저 짚어준 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 증권사의 수수료 면제가 고객을 모아 펀드 판매로 수익을 내는 전략이라는 점과 장기할인 소멸 및 수시인출 면제 구조를 염두에 두고 대응 논리를 펼치세요. 만 55세 이후 연금개시 시 수수료가 0원이 되며 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되는 조건을 먼저 확인해 주세요. 
+고객에게는 "국민은행도 만 55세 이후 연금개시를 하시면 수수료가 0원입니다^^ 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제됩니다"라고 안내해 보세요. 
+조건에 해당하지 않아 수수료가 일부 발생하는 경우라면 수수료보다 전문가 관리로 프레임을 옮겨야 해요. 증권사는 고객이 장기간 직접 투자하고 직접 관리해야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능하기 때문이에요. 이 경우에는 "네, 수수료가 일부 발생합니다. 그런데 고객님. IRP는 수수료만 보고 결정하기엔 아까운 계좌입니다. 증권사는 고객님이 장기간 직접 투자하고 직접 관리하셔야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능합니다"라고 말씀해 보세요. 
+아울러 당행 구체적인 수수료율이나 우리 수수료가 얼마인지에 대한 상세한 수치는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -5442,8 +5499,7 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -5481,11 +5537,12 @@
       <c r="E129" s="6" t="inlineStr">
         <is>
           <t>● 정민석
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+현재 보유하신 자산이 모두 원리금보장상품으로만 운용 중인 고객에게는 정기예금 대신 디폴트옵션 저위험 이상으로 운용해 보시는 방법을 제안해 볼 수 있어요. 다만 해당 고객이 이미 디폴트옵션 초저위험을 등록해 보유하고 계신 상태라면 사전지정운용제도 등록 및 변경과 보유상품 변경인 기존 매도 및 신규 매수의 2단계 거래가 필요하다는 점을 반드시 함께 안내해 드려야 해요. 또한 고객에게 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 쉽게 설명해 주시는 것이 좋아요. 사용 계획이 있는 자금이나 반대 케이스에 해당하는지 먼저 확인하고 접근하는 점도 잊지 마세요.
 ● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+원리금보장상품 100% 운용 고객에게는 적립금 300만원 이상인 경우 정기예금 대신 디폴트옵션 저위험 이상으로 운용을 제안할 수 있어요. 
+상담을 진행할 때 사용계획 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내야 한다는 점을 유념해 주세요. 
+또한 고객에게 안내할 때는 생소한 '고유계정대'라는 표현 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요. 
+이미 디폴트옵션 초저위험을 등록·보유한 고객이라면 사전지정운용제도 등록 및 변경과 보유상품 변경(기존 매도 후 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요.</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
@@ -5518,8 +5575,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
       <c r="F130" s="13" t="inlineStr">
@@ -5553,11 +5609,10 @@
       <c r="E131" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 안내하는 것이 핵심이에요. 1개월 내 만기도래 원리금보장상품을 보유하고 디폴트옵션이 미등록된 상태라면 이러한 제도 변경 내용을 짚어주면서 디폴트옵션 사전지정 등록이나 만기 예약변경을 권유하는 방법을 활용할 수 있어요.
 ● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+앞서 말씀드린 2026년 10월 17일 만기를 앞둔 7,000만원 규모의 예금은 만기 때 별도의 재예치 지시가 없으면 현금성자산으로 대기하게 돼요. 
+정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 만기 전 운용 방향을 확정해야 해요. 만기 임박 + 디폴트옵션 미등록 고객에게는 "정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기 자금이 현금성자산으로 상환되니 디폴트옵션 사전지정 등록이나 만기 예약을 하시는 것이 좋아요"라고 안내해 보세요.</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
@@ -5594,8 +5649,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
         </is>
       </c>
       <c r="F132" s="14" t="inlineStr">
@@ -5632,8 +5686,11 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>■ [06-AD-080] 개인형IRP 계좌이체 전입/전출  (계약이전)
+· 무슨 화면인지: 계좌이체 전입/전출 조회, 전출취소(해제), 이전 진행상황 수시 조회 → 관련 지식항목 33·34
+· 근거 신뢰도: 여러 자료에서 교차확인(○ (3건))
+· 비고: 전입 기능도 같은 번호(1부는 전출만 기재였음). 기업형 DB/DC는 [06-AD-090]
+· 출처 퇴직연금 주요거래 화면번호 안내 (KB StarLearn 직원교육)</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
@@ -5670,8 +5727,9 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>어느 방향으로 이전하는 건가요?
+· 전출
+· 전입</t>
         </is>
       </c>
       <c r="F134" s="14" t="inlineStr">
@@ -5708,8 +5766,7 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
         </is>
       </c>
       <c r="F135" s="14" t="inlineStr">
@@ -5746,8 +5803,7 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
         </is>
       </c>
       <c r="F136" s="14" t="inlineStr">
@@ -5784,8 +5840,7 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
         </is>
       </c>
       <c r="F137" s="14" t="inlineStr">
@@ -5855,8 +5910,16 @@
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>투자성향이 위험중립형인 이 고객에게는 적합성 허용 상한이 보통위험까지이므로, 그에 맞는 상품들을 확인하고 안내해 드리는 것이 핵심이에요. 이 고객의 적합성 허용 상한은 보통위험이며, 안내할 수 있는 상품 목록은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험, 최근 1년 4.8%, 채권형
+- KB 국내채권형 C-P — 낮은위험, 최근 1년 3.8%, 채권형
+- KB 안정형 MP — 낮은위험, 최근 1년 3.9%, MP
+- KB 중립형 MP — 보통위험, 최근 1년 5.1%, MP
+- KB GIC 확정금리 — 매우낮은위험, 최근 1년 3.65%, GIC
+- KB ELB 지수연계 — 낮은위험, 최근 1년 4.1%, ELB
+- KB 정기예금(1년) — 매우낮은위험, 최근 1년 3.1%, 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험, 최근 1년 3.3%, MP
+안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 허용 상한을 초과하여 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -5889,8 +5952,33 @@
       </c>
       <c r="E140" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>2026년 8월 3주차 기준 국고채 금리는 국고채3년물과 국고채10년물의 변동 추이를 살펴보아야 해요. 2026년 8월 14일 종가 기준으로 국고채3년물은 3.795, 국고채10년물은 4.31로 나타나 있어요. 
+- KOSPI — 6977.94 (+11.5%)
+- KOSPI200 — 1098.18 (+12.7%)
+- KOSDAQ — 864.65 (+8.2%)
+- KOSDAQ150 — 1495.95 (+9.3%)
+- S&amp;P500 — 7785.76 (+0.4%)
+- 나스닥 — 26729.16 (+0.1%)
+- 다우존스 — 53732.41 (-0.6%)
+- NIKKEI225 — 68713.8 (+4.7%)
+- Eurostoxx50 — 6539.59 (+0.2%)
+- 독일 DAX — 26440.31 (+0.5%)
+- 국제유가(WTI) — 82.4 (+5.4%)
+- 금(Gold) — 4376.4 (+0.8%)
+- CSI300 — 4665.88 (-0.6%)
+- 상해종합 — 3927.176 (-0.3%)
+- 인도SENSEX — 78009.25 (-0.6%)
+- HSI — 25116.85 (-2.1%)
+- HSCEI — 8340.83 (-2.2%)
+- 베트남VN30 — 1876.81 (-1.8%)
+- 달러인덱스 — 99.667 (+0.1%)
+- 원/달러 — 1415.68 (+0.6%)
+- 국고채3년물 — 3.795 (+5bp)
+- 국고채10년물 — 4.31 (+9bp)
+- 미국채2년물 — 4.1691 (-3bp)
+- 미국채10년물 — 4.6922 (+5bp)
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F140" s="19" t="inlineStr">
@@ -5923,8 +6011,20 @@
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션)로는 위험도에 따라 초저위험 지켜드림, 저위험 알파드림·알파드림 II·알파드림 III, 중위험 뿔려드림·뿔려드림 II·뿔려드림 III, 고위험 모두드림·모두드림 II·모두드림 III 같은 상품들이 있어요. 2026년 8월 기준(수익률은 2026년 7월 30일 기준, 원리금보장 금리는 2026년 8월 기준)으로 각 포트폴리오의 구성과 1년 수익률을 살펴보면 다음과 같아요.
+- 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성, 1년 수익률 미표시
+- 알파드림 — 저위험, 수협은행 노후보장 정기예금 디폴트옵션용(3년) 외 TDF 구성, 1년 수익률 4.23%
+- 알파드림 II — 저위험, 기업은행 정기예금(3년) 및 TDF 구성, 1년 수익률 8.56%
+- 알파드림 III — 저위험, 농협은행 정기예금(3년)·DB손해보험 이율보증형보험(3년) 및 TDF 구성, 1년 수익률 5.86%
+- 뿔려드림 — 중위험, 하나은행 정기예금(3년) 및 TDF 구성, 1년 수익률 13.95%
+- 뿔려드림 II — 중위험, 미래에셋평생소득 TIF 및 EMP 펀드 구성, 1년 수익률 15.04%
+- 뿔려드림 III — 중위험, KB라이프생명 이율보증형보험(3년) 및 KB드림스타자산배분안정형 구성, 1년 수익률 10.59%
+- 모두드림 — 고위험, TDF 100 투자 포트폴리오, 1년 수익률 20.63%
+- 모두드림 II — 고위험, 액티브 TDF 100 구성, 1년 수익률 19.19%
+- 모두드림 III — 고위험, 미래에셋디폴트전략배분성장형(BF) 100 구성, 1년 수익률 15.19%
+포트폴리오 수익률은 일단위 재투자를 가정한 수익률로 산정되며, 원리금 보장상품은 매월 공시되는 금리로 반영되므로 고객의 실제 수익률과 상이할 수 있어요. 저위험 알파드림에 포함된 수협은행 노후보장 정기예금 디폴트옵션용(3년)은 안정자산 포트폴리오 구성상품 교체(리밸런싱)가 시행된 적이 있어요. 
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F141" s="19" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6057,8 +6057,7 @@
       </c>
       <c r="E142" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
         </is>
       </c>
       <c r="F142" s="21" t="inlineStr">
@@ -6095,8 +6094,7 @@
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
         </is>
       </c>
       <c r="F143" s="21" t="inlineStr">
@@ -6129,8 +6127,8 @@
       </c>
       <c r="E144" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
+자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
         </is>
       </c>
       <c r="F144" s="19" t="inlineStr">
@@ -6163,8 +6161,7 @@
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
       <c r="F145" s="21" t="inlineStr">
@@ -6197,8 +6194,7 @@
       </c>
       <c r="E146" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
       <c r="F146" s="21" t="inlineStr">
@@ -6235,8 +6231,7 @@
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
         </is>
       </c>
       <c r="F147" s="21" t="inlineStr">
@@ -6273,8 +6268,9 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: market:퇴직연금과 부동산 투자 비교 시황 및 자산배분 전략 · fact:퇴직연금과 부동산 투자 비교 · pitch:퇴직연금과 부동산 투자 비교 시 고객 설득 화법
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -6307,8 +6303,9 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
+찾아본 곳: fact:고객 평가금액
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
       <c r="F149" s="14" t="inlineStr">
@@ -6341,8 +6338,7 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
         </is>
       </c>
       <c r="F150" s="13" t="inlineStr">
@@ -6375,8 +6371,7 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
         </is>
       </c>
       <c r="F151" s="13" t="inlineStr">
@@ -6409,8 +6404,12 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+          <t>송도윤 고객님은 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 크게 상회하고 있지만, 6개월 이상 장기 미접촉 상태인 관리 사각지대 고객이에요. 현재 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식을 보유하고 계시며, 고유계정대 2억 8,000만원의 현금성자산이 방치되어 있고, 디폴트옵션 미설정 및 ISA 만기자금 1억 2,000만원을 보유하고 계셔요.
+- 고유계정대 — 2억 8,000만원 (수익률 0.0%)
+- RISE 미국나스닥100 ETF — 1억 1,600만원 (수익률 65.7%)
+- KB 퇴직연금 배당 (주식) — 8,000만원 (수익률 60.0%, ⚠판매중단)
+- 하나 파이팅 코리아 (주식) — 4,400만원 (수익률 46.7%)
+장기간 접촉 이력이 없어 타사 비교에 노출될 가능성이 있으므로, 유선 접촉을 통해 관계를 회복해야 합니다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 사용계획이 있는 자금은 먼저 걸러내며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F152" s="14" t="inlineStr">
@@ -6481,11 +6480,43 @@
       <c r="E154" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+■ 제가 도와드릴 수 있는 것
+IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
+· 신규 제안 — 다양한 고객에게 IRP를 처음 권할 때
+· 거절 대응 — 관리·수익률 불만, 제도·투자 거부, 증권사 비교, 해지·망설임 같은 반응이 나왔을 때
+· 운용관리 업무 가이드 — 예: 기존 고객 정기 관리의 타이밍 → 만기 1개월 전 안내 등 4원칙
+· 관리 대상 정의 — 어떤 고객군을 왜 관리하는지 (86건)
+· 관리 방법론 — 이런 상황이면 무엇을 제안하는지 (131건)
+· 업무 처리 절차 — 처리 순서·주의 (74건)
+· 단말 화면번호 — 무슨 업무가 몇 번 화면인지 (87건)
+· 비대면 채널 경로 — 고객이 앱·웹에서 직접 하는 메뉴 (56건)
+· 현장의 목소리 — 영업점이 실제로 하는 방식 (10건)
+· 제도·상품 팩트 — 한도·요건·수수료 같은 확정 수치 (64건)
+· 지난 상담 기록 — 이 고객과 언제 무슨 얘기를 했는지
+· 이번 상담 요약 — 지금까지 나눈 대화를 정리하고, 원하시면 쪽지로 보내기
+■ 활용 팁
+"사업자 고객인데 수수료 부담된다고 하시네요" 처럼 실제 상황을 그대로 말씀해 주시면 바로 화법을 찾아드려요.
+고객이 한 말을 그대로 옮겨 주셔도 됩니다("증권사가 수수료 무료라던데요") — 그 말에 어떻게 답하면 되는지 짚어드려요.
+"세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.
 ● 정민석
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+■ 제가 도와드릴 수 있는 것
+IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
+· 신규 제안 — 다양한 고객에게 IRP를 처음 권할 때
+· 거절 대응 — 관리·수익률 불만, 제도·투자 거부, 증권사 비교, 해지·망설임 같은 반응이 나왔을 때
+· 운용관리 업무 가이드 — 예: 기존 고객 정기 관리의 타이밍 → 만기 1개월 전 안내 등 4원칙
+· 관리 대상 정의 — 어떤 고객군을 왜 관리하는지 (86건)
+· 관리 방법론 — 이런 상황이면 무엇을 제안하는지 (131건)
+· 업무 처리 절차 — 처리 순서·주의 (74건)
+· 단말 화면번호 — 무슨 업무가 몇 번 화면인지 (87건)
+· 비대면 채널 경로 — 고객이 앱·웹에서 직접 하는 메뉴 (56건)
+· 현장의 목소리 — 영업점이 실제로 하는 방식 (10건)
+· 제도·상품 팩트 — 한도·요건·수수료 같은 확정 수치 (64건)
+· 지난 상담 기록 — 이 고객과 언제 무슨 얘기를 했는지
+· 이번 상담 요약 — 지금까지 나눈 대화를 정리하고, 원하시면 쪽지로 보내기
+■ 활용 팁
+"사업자 고객인데 수수료 부담된다고 하시네요" 처럼 실제 상황을 그대로 말씀해 주시면 바로 화법을 찾아드려요.
+고객이 한 말을 그대로 옮겨 주셔도 됩니다("증권사가 수수료 무료라던데요") — 그 말에 어떻게 답하면 되는지 짚어드려요.
+"세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -6519,11 +6550,9 @@
       <c r="E155" s="18" t="inlineStr">
         <is>
           <t>● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+박정호 고객님은 현재 디폴트옵션 설정이 되어 있어요. 다만 이미 디폴트옵션(초저위험)을 등록·보유한 고객은 ⓐ 사전지정운용제도 등록/변경 → ⓑ 보유상품 변경(기존 매도 + 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요. 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 «현재 보유중이신 디폴트옵션(초저위험)은 정기예금만으로 구성되어 있습니다»라고 짚어 주세요.
 ● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
@@ -6557,14 +6586,12 @@
       <c r="E156" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+만기 도래 항목을 묻는 질문에 대해, 현재 2026년 10월 9일에 만기가 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품이 있어요. 그리고 2027년 1-10에 만기가 도래하는 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 3,550만원 상품이 있습니다.
 ● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+이수민 고객의 만기 예정 자산은 2026년 10월 17일에 도래하는 7,000만원 규모의 기업은행 퇴직연금 정기예금 1년 상품이 있습니다. 
+해당 정기예금의 금리와 수익률은 모두 2.90%이며, 만기 D-18을 앞두고 있어 재예치 지시가 없으면 현금성자산(연 2.52%)으로 대기하게 되므로 만기 전 운용 방향 확정이 필요합니다.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+송도윤 고객님의 만기 내역은 2026년 9월 20일에 만기가 경과한 ISA 만기자금(IRP 외부) 1억 2,000만원이 있어요. 원장에 등록된 만기 항목은 해당 건이 전부이며, 다른 만기 건은 자료에 없어요.</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
@@ -6598,11 +6625,9 @@
       <c r="E157" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 및 환매추천 펀드인 KB 퇴직연금 배당 (주식)을 보유하고 계시고, 미운용 현금성자산이 있으며, 디폴트옵션이 미설정 상태이고, ISA 만기자금 보유와 운용변경이 12개월 이상 없었기 때문이에요. 추가로 관리 사각지대 고객이자 당해 납입이 없는 고객에 해당하며, 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시고 운용수익률은 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 계세요. 다만 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있는 상태예요.
 ● 이준호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
         </is>
       </c>
       <c r="F157" s="19" t="inlineStr">
@@ -6636,11 +6661,9 @@
       <c r="E158" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담 기록에 따르면, 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 있어요.
 ● 김서연
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
         </is>
       </c>
       <c r="F158" s="19" t="inlineStr">
@@ -6674,11 +6697,10 @@
       <c r="E159" s="18" t="inlineStr">
         <is>
           <t>● 이수민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+이수민 고객에게 개인형IRP 계좌에 300만원을 추가 납입할 때 예상되는 세액공제 환급액을 안내할 때는 총급여 구간과 세액공제 한도를 함께 짚어주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 한도 및 잔여한도가 900만원이므로, 300만원을 추가 납입하면 총급여 5,500만원 이하 기준 16.5%의 공제율을 적용하여 495,000원의 환급을 예상할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 이를 바탕으로 안내해 보세요.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+세액공제 잔여한도가 이미 0원인 고객에게 현금을 추가로 납입하는 경우라면 환급액이 늘어나지 않으니 주의해야 해요. 이 고객의 세액공제 한도 900만원은 연금저축 납입분까지 합산된 값으로 잔여한도가 남아있지 않기 때문이에요. 
+다만 ISA 만기자금을 개인형IRP 계좌로 전환하는 경우라면 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 별개의 축이에요. 300만원을 ISA 만기자금에서 개인형IRP로 전환할 때 적용되는 공제율에 따라 추가 공제 대상과 환급액이 달라질 수 있어요. 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 49,500원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않았으니 단말에서 고객의 총급여 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
       <c r="F159" s="19" t="inlineStr">
@@ -6712,11 +6734,9 @@
       <c r="E160" s="18" t="inlineStr">
         <is>
           <t>● 박지민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+고객의 소득 수준이나 종합소득금액 값이 자료에 나와 있지 않아 해당 고객의 세액공제율을 바로 확정해 말씀드리기는 어려워요. 2026년 6월 기준 자료에 따르면, 공제율은 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 경우 16.5%, 이를 초과하는 경우 13.2%가 적용돼요. 여기서 5,500만원 '이상'이 아니라 '초과'가 정확한 경계 표현이며, 5,500만원 정확히 일치하는 금액은 16.5% 구간에 해당한다는 점을 참고해 주세요. 단말에서 고객의 소득 조건을 먼저 확인하신 뒤에 안내를 이어가셔야 해요.
 ● 한지우
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -6770,11 +6770,9 @@
       <c r="E161" s="18" t="inlineStr">
         <is>
           <t>● 김서연
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+ISA 만기자금을 IRP로 옮겨 세액공제 혜택을 확인하는 고객에게는 만기금액의 전환에 따른 추가 공제 구조를 짚어 드리는 게 핵심이에요. 개인형IRP 계좌로 8,000만원을 전환할 때 이 금액은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이라, 8,000만원을 전환하면 추가 공제 대상은 300만원이 돼요. 총급여 5,500만원 이하 16.5% 기준으로 이 전환으로 늘어나는 환급 예상액은 495,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로 서로 다른 한도예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
 ● 박지민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
       <c r="F161" s="19" t="inlineStr">
@@ -6808,11 +6806,10 @@
       <c r="E162" s="18" t="inlineStr">
         <is>
           <t>● 박정호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+박정호 고객님은 연금개시 요건을 충족하였으나 아직 연금개시를 하지 않은 상태예요. 
+만 55세가 아직 멀었다며 연금개시를 망설이는 반론이 예상될 때는 "고객님. 지금은 퇴직금을 꺼내 쓰시기보다, 자산을 늘려나가야 하는 시기입니다. IRP 안에서 운용수익에 대해선 과세가 되지 않는 만큼 계속 운용하면서 복리효과를 더 누리시는 게 좋습니다."라고 안내해 보세요.
 ● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+송도윤 고객님은 연금개시요건을 충족하지 않아 현재 연금개시를 하실 수 없어요. 자료에 따르면 연금개시 상태는 미개시이며 연금개시요건도 충족되지 않은 상태로 확인돼요.</t>
         </is>
       </c>
       <c r="F162" s="19" t="inlineStr">
@@ -6846,11 +6843,9 @@
       <c r="E163" s="18" t="inlineStr">
         <is>
           <t>● 최서윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+최서윤 고객이 보유하고 있는 판매중단 상품은 KB 코리아밸류업액티브(주식)이다. 해당 상품은 920만원 규모로 보유 중이며 수익률은 -38.7%를 기록하고 있다. 판매중단 상품을 보유하고 있어 관리 공백이 우려되는 상황이므로, 보유 포트폴리오를 점검하고 매도 및 재추천 등의 액션을 안내하는 방향으로 접근해야 한다.
 ● 박지민
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+판매중단된 보유상품은 없어요.</t>
         </is>
       </c>
       <c r="F163" s="19" t="inlineStr">
@@ -6884,11 +6879,9 @@
       <c r="E164" s="18" t="inlineStr">
         <is>
           <t>● 정민석
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+현재 보유한 자산이 예금 위주인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가는 게 핵심이에요. 원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 입증해야 하므로, 금리 갈아타기가 곧 관리라는 논리로 대응해 보세요. 다만 사용계획이 있는 자금은 먼저 걸러내고, 고객에게 생소한 고유계정대 같은 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 고객이 예금만 해서 관리가 필요 없다고 반응할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
 ● 김현수
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+예금만 보유하고 있어 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 점을 짚어주는 게 핵심이에요. 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 같은 안전성 안에서 금리를 올려주는 제안으로 들어가야 해요. 고객이 사용계획이 있는 자금인지 먼저 확인하고, 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
       <c r="F164" s="19" t="inlineStr">
@@ -6922,11 +6915,9 @@
       <c r="E165" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)
+송도윤 고객에게는 지금 안내할 수 있는 세미나로 11/5(목) 16시에 진행되는 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 온라인 세미나가 있어요. 이 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어, 미운용 자금 및 디폴트옵션 제도를 다루는 해당 세미나를 안내합니다. 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX를 활용하시면 돼요. 고객에게 안내하실 때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 사용계획이 있는 자금이라면 먼저 걸러내고 접근하시는 게 핵심이에요. 참고로 다른 세미나 후보 4건인 연금개시 전 꼭 알아야 할 IRP 수령 방법, 예금만으로 괜찮을까? 퇴직연금 자산배분 전략, 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기, 금리 변화기, 퇴직연금 예금 만기 이후 운용 전략에 대해서는 아직 상세 안내 자료가 없어요.
 ● 이준호
-[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 4.5초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_IN…)</t>
+이 고객에게는 지금 요건에 맞는 안내 대상 세미나가 없어요. 다만 현재 열려 있는 세미나 중 날짜가 가장 가까운 것은 11/12(목) 17시에 KB국민은행 WM투자부에서 주관하는 «내 투자성향에 맞는 포트폴리오 찾기»예요. 이 콘텐츠는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋으나 이 고객의 요건과는 무관해요. 안내 시 참고할 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요. 다른 이벤트나 세미나 관련해서 다른 후보 콘텐츠들에 대한 상세 요건은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
       <c r="F165" s="19" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
+      <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -688,7 +688,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
+      <c r="A5" s="8" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="8" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -797,7 +797,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G7" s="18" t="inlineStr">
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
+      <c r="A17" s="8" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
+      <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
+      <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
+      <c r="A24" s="8" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
+      <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="8" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
+      <c r="A27" s="8" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
+      <c r="A28" s="8" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
+      <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
+      <c r="A30" s="8" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
+      <c r="A31" s="8" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
+      <c r="A32" s="8" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n"/>
+      <c r="A33" s="8" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
+      <c r="A34" s="8" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n"/>
+      <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
+      <c r="A36" s="8" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
+      <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr">
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="8" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
+      <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
@@ -1965,7 +1965,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
+      <c r="A40" s="24" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G40" s="18" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -2045,7 +2045,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
+      <c r="A42" s="8" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2078,7 +2078,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
+      <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2111,7 +2111,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2144,7 +2144,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
+      <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -2175,7 +2175,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
+      <c r="A46" s="8" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
+      <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2245,7 +2245,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
+      <c r="A48" s="8" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -2279,7 +2279,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n"/>
+      <c r="A49" s="8" t="n"/>
       <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G49" s="18" t="inlineStr">
@@ -2316,7 +2316,7 @@
       <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="8" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="16" t="n">
         <v>49</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G50" s="18" t="inlineStr">
@@ -2349,7 +2349,7 @@
       <c r="I50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n"/>
+      <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="16" t="n">
         <v>50</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G51" s="18" t="inlineStr">
@@ -2385,7 +2385,7 @@
       <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
+      <c r="A52" s="8" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="16" t="n">
         <v>51</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G52" s="18" t="inlineStr">
@@ -2456,7 +2456,7 @@
       <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n"/>
+      <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="16" t="n">
         <v>52</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
@@ -2509,7 +2509,7 @@
       <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n"/>
+      <c r="A54" s="8" t="n"/>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="16" t="n">
         <v>53</v>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G54" s="18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n"/>
+      <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="16" t="n">
         <v>54</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
+      <c r="A56" s="8" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n"/>
+      <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F57" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
@@ -2665,7 +2665,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
+      <c r="A58" s="8" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G58" s="18" t="inlineStr">
@@ -2698,7 +2698,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
+      <c r="A59" s="8" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
+      <c r="A60" s="8" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="4" t="n">
         <v>59</v>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -2773,7 +2773,7 @@
       <c r="I60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n"/>
+      <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="4" t="n">
         <v>60</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       <c r="I61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
+      <c r="A62" s="8" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="4" t="n">
         <v>61</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -2842,7 +2842,7 @@
       <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="n"/>
+      <c r="A63" s="8" t="n"/>
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="4" t="n">
         <v>62</v>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
+      <c r="A64" s="8" t="n"/>
       <c r="B64" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
@@ -2912,7 +2912,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n"/>
+      <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="16" t="n">
         <v>64</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G65" s="18" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
+      <c r="A66" s="8" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="16" t="n">
         <v>65</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -2983,7 +2983,7 @@
       <c r="I66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
+      <c r="A67" s="8" t="n"/>
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="16" t="n">
         <v>66</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
@@ -3018,7 +3018,7 @@
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
+      <c r="A68" s="8" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n"/>
+      <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -3089,7 +3089,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
+      <c r="A70" s="8" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3122,7 +3122,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n"/>
+      <c r="A71" s="8" t="n"/>
       <c r="B71" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · QA 리허설</t>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G71" s="18" t="inlineStr">
@@ -3159,7 +3159,7 @@
       <c r="I71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
+      <c r="A72" s="8" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="16" t="n">
         <v>71</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G72" s="18" t="inlineStr">
@@ -3192,7 +3192,7 @@
       <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n"/>
+      <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="16" t="n">
         <v>72</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
@@ -3230,7 +3230,7 @@
       <c r="I73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
+      <c r="A74" s="8" t="n"/>
       <c r="B74" s="9" t="n"/>
       <c r="C74" s="16" t="n">
         <v>73</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n"/>
+      <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="16" t="n">
         <v>74</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -3299,7 +3299,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n"/>
+      <c r="A76" s="24" t="n"/>
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -3367,13 +3367,13 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>해지 만류 화법이 나와야 한다 ↔ 엉뚱한 절차 카드 한 장으로 「준비된 자료에 없어요」(**미해결**)</t>
+          <t>해지 만류 화법 — 사과 → 원인 규명 → 리밸런싱 3단 + 고객에게 할 대사 ↔ 절차 카드 한 장으로 「준비된 자료에 없어요」(gap 35 재현)</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n"/>
+      <c r="A78" s="8" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="4" t="n">
         <v>77</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -3409,7 +3409,7 @@
       <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n"/>
+      <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="4" t="n">
         <v>78</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3445,7 +3445,7 @@
       <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n"/>
+      <c r="A80" s="8" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="4" t="n">
         <v>79</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3484,7 +3484,7 @@
       <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n"/>
+      <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="4" t="n">
         <v>80</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -3519,7 +3519,7 @@
       <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n"/>
+      <c r="A82" s="8" t="n"/>
       <c r="B82" s="9" t="n"/>
       <c r="C82" s="4" t="n">
         <v>81</v>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -3554,7 +3554,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n"/>
+      <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -3592,7 +3592,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
+      <c r="A84" s="8" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="n"/>
+      <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -3666,7 +3666,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
+      <c r="A86" s="8" t="n"/>
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -3699,7 +3699,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="n"/>
+      <c r="A87" s="8" t="n"/>
       <c r="B87" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G87" s="18" t="inlineStr">
@@ -3744,7 +3744,7 @@
       <c r="I87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n"/>
+      <c r="A88" s="8" t="n"/>
       <c r="B88" s="9" t="n"/>
       <c r="C88" s="16" t="n">
         <v>87</v>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n"/>
+      <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 대본 리허설</t>
+          <t>○ 예비 · 대본</t>
         </is>
       </c>
       <c r="G89" s="18" t="inlineStr">
@@ -3834,7 +3834,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n"/>
+      <c r="A90" s="8" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
@@ -3891,7 +3891,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n"/>
+      <c r="A91" s="8" t="n"/>
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
@@ -3951,7 +3951,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n"/>
+      <c r="A92" s="8" t="n"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -3998,7 +3998,7 @@
       <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="n"/>
+      <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="4" t="n">
         <v>92</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -4073,7 +4073,7 @@
       <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="n"/>
+      <c r="A94" s="8" t="n"/>
       <c r="B94" s="9" t="n"/>
       <c r="C94" s="4" t="n">
         <v>93</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4106,7 +4106,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n"/>
+      <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -4178,7 +4178,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="n"/>
+      <c r="A96" s="8" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4211,7 +4211,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="n"/>
+      <c r="A97" s="8" t="n"/>
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -4288,7 +4288,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n"/>
+      <c r="A98" s="8" t="n"/>
       <c r="B98" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
@@ -4325,7 +4325,7 @@
       <c r="I98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n"/>
+      <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="16" t="n">
         <v>98</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="F99" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G99" s="18" t="inlineStr">
@@ -4364,7 +4364,7 @@
       <c r="I99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n"/>
+      <c r="A100" s="8" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="16" t="n">
         <v>99</v>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
@@ -4402,7 +4402,7 @@
       <c r="I100" s="18" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="n"/>
+      <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="16" t="n">
         <v>100</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F101" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G101" s="18" t="inlineStr">
@@ -4435,7 +4435,7 @@
       <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n"/>
+      <c r="A102" s="24" t="n"/>
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="16" t="n">
         <v>101</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -4517,7 +4517,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n"/>
+      <c r="A104" s="8" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n"/>
+      <c r="A105" s="8" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n"/>
+      <c r="A106" s="8" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="n"/>
+      <c r="A107" s="8" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="F107" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="n"/>
+      <c r="A108" s="8" t="n"/>
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -4718,7 +4718,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="n"/>
+      <c r="A109" s="8" t="n"/>
       <c r="B109" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F109" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G109" s="18" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="I109" s="18" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n"/>
+      <c r="A110" s="8" t="n"/>
       <c r="B110" s="9" t="n"/>
       <c r="C110" s="16" t="n">
         <v>109</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 시연본 리허설</t>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="n"/>
+      <c r="A111" s="8" t="n"/>
       <c r="B111" s="9" t="n"/>
       <c r="C111" s="16" t="n">
         <v>110</v>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F111" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G111" s="18" t="inlineStr">
@@ -4826,7 +4826,7 @@
       <c r="I111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n"/>
+      <c r="A112" s="8" t="n"/>
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
@@ -4859,7 +4859,7 @@
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n"/>
+      <c r="A113" s="8" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>19. 브리핑 수정</t>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
@@ -4896,7 +4896,7 @@
       <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n"/>
+      <c r="A114" s="8" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="4" t="n">
         <v>113</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -4923,13 +4923,13 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>**시연 금지 — 재적용 루프 미구현.** 감사로그에만 남고 화면은 안 바뀌는데 「반영할게요」라고 답한다(correction.py 머리말)</t>
+          <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n"/>
+      <c r="A115" s="8" t="n"/>
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="4" t="n">
         <v>114</v>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="F115" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
@@ -4973,7 +4973,7 @@
       <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n"/>
+      <c r="A116" s="8" t="n"/>
       <c r="B116" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F116" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="n"/>
+      <c r="A117" s="8" t="n"/>
       <c r="B117" s="9" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G117" s="18" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="n"/>
+      <c r="A118" s="8" t="n"/>
       <c r="B118" s="9" t="n"/>
       <c r="C118" s="16" t="n">
         <v>117</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n"/>
+      <c r="A119" s="8" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="16" t="n">
         <v>118</v>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F119" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G119" s="18" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="n"/>
+      <c r="A120" s="8" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="16" t="n">
         <v>119</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="n"/>
+      <c r="A121" s="8" t="n"/>
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
@@ -5210,7 +5210,7 @@
       <c r="I121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="n"/>
+      <c r="A122" s="8" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>21. 에이전트 능력 안내</t>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5262,7 +5262,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n"/>
+      <c r="A123" s="8" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F123" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
@@ -5312,7 +5312,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="n"/>
+      <c r="A124" s="8" t="n"/>
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="4" t="n">
         <v>123</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="n"/>
+      <c r="A125" s="8" t="n"/>
       <c r="B125" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F125" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G125" s="18" t="inlineStr">
@@ -5399,7 +5399,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n"/>
+      <c r="A126" s="24" t="n"/>
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G126" s="18" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 대본 리허설</t>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -5487,7 +5487,7 @@
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="n"/>
+      <c r="A128" s="8" t="n"/>
       <c r="B128" s="9" t="n"/>
       <c r="C128" s="4" t="n">
         <v>127</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="n"/>
+      <c r="A129" s="8" t="n"/>
       <c r="B129" s="9" t="n"/>
       <c r="C129" s="4" t="n">
         <v>128</v>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
@@ -5563,7 +5563,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="n"/>
+      <c r="A130" s="8" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5596,7 +5596,7 @@
       <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="n"/>
+      <c r="A131" s="8" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="n"/>
+      <c r="A132" s="8" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="n"/>
+      <c r="A133" s="8" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 라이브러리 리허설</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="n"/>
+      <c r="A134" s="8" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n"/>
+      <c r="A135" s="8" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="F135" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="n"/>
+      <c r="A136" s="8" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>직원이 말한 값은 되받아 적을 수 있다 ↔ 이전 턴 수치를 인용하면 폐기된다(**미해결**)</t>
+          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="n"/>
+      <c r="A137" s="8" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F137" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
@@ -5861,7 +5861,7 @@
       <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="n"/>
+      <c r="A138" s="8" t="n"/>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5874,7 +5874,7 @@
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="n"/>
+      <c r="A139" s="8" t="n"/>
       <c r="B139" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 케이스 리허설</t>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G139" s="18" t="inlineStr">
@@ -5940,7 +5940,7 @@
       <c r="I139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="n"/>
+      <c r="A140" s="8" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="16" t="n">
         <v>139</v>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F140" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G140" s="18" t="inlineStr">
@@ -5999,7 +5999,7 @@
       <c r="I140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="n"/>
+      <c r="A141" s="8" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="16" t="n">
         <v>140</v>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F141" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G141" s="18" t="inlineStr">
@@ -6045,7 +6045,7 @@
       <c r="I141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="n"/>
+      <c r="A142" s="8" t="n"/>
       <c r="B142" s="9" t="n"/>
       <c r="C142" s="16" t="n">
         <v>141</v>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F142" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 시연본 리허설</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="n"/>
+      <c r="A143" s="8" t="n"/>
       <c r="B143" s="9" t="n"/>
       <c r="C143" s="16" t="n">
         <v>142</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="F143" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 대본 리허설</t>
+          <t>○ 예비 · 대본</t>
         </is>
       </c>
       <c r="G143" s="18" t="inlineStr">
@@ -6115,7 +6115,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="n"/>
+      <c r="A144" s="8" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="F144" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G144" s="18" t="inlineStr">
@@ -6149,7 +6149,7 @@
       <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="n"/>
+      <c r="A145" s="8" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="F145" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA 리허설</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G145" s="18" t="inlineStr">
@@ -6182,7 +6182,7 @@
       <c r="I145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="n"/>
+      <c r="A146" s="8" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="F146" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n"/>
+      <c r="A147" s="8" t="n"/>
       <c r="B147" s="10" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="F147" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G147" s="18" t="inlineStr">
@@ -6252,7 +6252,7 @@
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="n"/>
+      <c r="A148" s="8" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6291,7 +6291,7 @@
       <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="n"/>
+      <c r="A149" s="8" t="n"/>
       <c r="B149" s="9" t="n"/>
       <c r="C149" s="4" t="n">
         <v>148</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F149" s="14" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
@@ -6326,7 +6326,7 @@
       <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="n"/>
+      <c r="A150" s="8" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="F150" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6359,7 +6359,7 @@
       <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="n"/>
+      <c r="A151" s="8" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스 리허설</t>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
@@ -6392,7 +6392,7 @@
       <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="n"/>
+      <c r="A152" s="8" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6430,7 +6430,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="n"/>
+      <c r="A153" s="8" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6443,7 +6443,7 @@
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 안 해본 질문</t>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="n"/>
+      <c r="A154" s="8" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 라이브러리 리허설</t>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
@@ -6537,7 +6537,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="n"/>
+      <c r="A155" s="8" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G155" s="18" t="inlineStr">
@@ -6573,7 +6573,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="9" t="n"/>
+      <c r="A156" s="8" t="n"/>
       <c r="B156" s="9" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G156" s="18" t="inlineStr">
@@ -6612,7 +6612,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="n"/>
+      <c r="A157" s="8" t="n"/>
       <c r="B157" s="9" t="n"/>
       <c r="C157" s="16" t="n">
         <v>156</v>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F157" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G157" s="18" t="inlineStr">
@@ -6648,7 +6648,7 @@
       <c r="I157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="n"/>
+      <c r="A158" s="8" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="16" t="n">
         <v>157</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="F158" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G158" s="18" t="inlineStr">
@@ -6684,7 +6684,7 @@
       <c r="I158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="n"/>
+      <c r="A159" s="8" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="16" t="n">
         <v>158</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="F159" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G159" s="18" t="inlineStr">
@@ -6721,7 +6721,7 @@
       <c r="I159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="n"/>
+      <c r="A160" s="8" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="16" t="n">
         <v>159</v>
@@ -6741,12 +6741,12 @@
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>◎ 1순위 · 안 해본 질문</t>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G160" s="18" t="inlineStr">
         <is>
-          <t>박지민16 154821-4938201.5 ↔ 한지우13 176903-5528417.2</t>
+          <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
         </is>
       </c>
       <c r="H160" s="18" t="inlineStr">
@@ -6757,7 +6757,7 @@
       <c r="I160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="n"/>
+      <c r="A161" s="8" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="16" t="n">
         <v>160</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="F161" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G161" s="18" t="inlineStr">
@@ -6793,7 +6793,7 @@
       <c r="I161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="n"/>
+      <c r="A162" s="8" t="n"/>
       <c r="B162" s="9" t="n"/>
       <c r="C162" s="16" t="n">
         <v>161</v>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="F162" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G162" s="18" t="inlineStr">
@@ -6830,7 +6830,7 @@
       <c r="I162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n"/>
+      <c r="A163" s="8" t="n"/>
       <c r="B163" s="9" t="n"/>
       <c r="C163" s="16" t="n">
         <v>162</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F163" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G163" s="18" t="inlineStr">
@@ -6866,7 +6866,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="n"/>
+      <c r="A164" s="8" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="F164" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G164" s="18" t="inlineStr">
@@ -6902,7 +6902,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="10" t="n"/>
+      <c r="A165" s="24" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F165" s="19" t="inlineStr">
         <is>
-          <t>○ 예비 · 안 해본 질문</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G165" s="18" t="inlineStr">
@@ -6940,8 +6940,8 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B127:B138"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="A127:A165"/>
-    <mergeCell ref="D27:D28"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B68:B70"/>
@@ -6987,7 +6987,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -4753,7 +4753,11 @@
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="I109" s="18" t="inlineStr"/>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n"/>
@@ -4823,7 +4827,11 @@
           <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
         </is>
       </c>
-      <c r="I111" s="18" t="inlineStr"/>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n"/>
+      <c r="A3" s="9" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
+      <c r="A27" s="9" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
+      <c r="A29" s="9" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="9" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
+      <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
+      <c r="A33" s="9" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
+      <c r="A34" s="9" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
+      <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
+      <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
+      <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
+      <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1965,7 +1965,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
+      <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -2045,7 +2045,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n"/>
+      <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2078,7 +2078,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2111,7 +2111,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n"/>
+      <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2144,7 +2144,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
+      <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2175,7 +2175,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
+      <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2210,7 +2210,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n"/>
+      <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2245,7 +2245,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
+      <c r="A48" s="9" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2279,7 +2279,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2316,7 +2316,7 @@
       <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
+      <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="16" t="n">
         <v>49</v>
@@ -2349,7 +2349,7 @@
       <c r="I50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
+      <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="16" t="n">
         <v>50</v>
@@ -2385,7 +2385,7 @@
       <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
+      <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="16" t="n">
         <v>51</v>
@@ -2456,7 +2456,7 @@
       <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
+      <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="16" t="n">
         <v>52</v>
@@ -2509,7 +2509,7 @@
       <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
+      <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="16" t="n">
         <v>53</v>
@@ -2556,7 +2556,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
+      <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="16" t="n">
         <v>54</v>
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
+      <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2632,7 +2632,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2665,7 +2665,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
+      <c r="A58" s="9" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2698,7 +2698,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
+      <c r="A59" s="9" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2738,7 +2738,7 @@
       <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="4" t="n">
         <v>59</v>
@@ -2773,7 +2773,7 @@
       <c r="I60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
+      <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="4" t="n">
         <v>60</v>
@@ -2806,7 +2806,7 @@
       <c r="I61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
+      <c r="A62" s="9" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="4" t="n">
         <v>61</v>
@@ -2842,7 +2842,7 @@
       <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
+      <c r="A63" s="9" t="n"/>
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="4" t="n">
         <v>62</v>
@@ -2875,7 +2875,7 @@
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
+      <c r="A64" s="9" t="n"/>
       <c r="B64" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -2912,7 +2912,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
+      <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="16" t="n">
         <v>64</v>
@@ -2950,7 +2950,7 @@
       <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="9" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="16" t="n">
         <v>65</v>
@@ -2983,7 +2983,7 @@
       <c r="I66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
+      <c r="A67" s="9" t="n"/>
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="16" t="n">
         <v>66</v>
@@ -3018,7 +3018,7 @@
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
+      <c r="A68" s="9" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3055,7 +3055,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
+      <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3089,7 +3089,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
+      <c r="A70" s="9" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3122,7 +3122,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="9" t="n"/>
       <c r="B71" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3159,7 +3159,7 @@
       <c r="I71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
+      <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="16" t="n">
         <v>71</v>
@@ -3192,7 +3192,7 @@
       <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="9" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="16" t="n">
         <v>72</v>
@@ -3230,7 +3230,7 @@
       <c r="I73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
+      <c r="A74" s="9" t="n"/>
       <c r="B74" s="9" t="n"/>
       <c r="C74" s="16" t="n">
         <v>73</v>
@@ -3266,7 +3266,7 @@
       <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="16" t="n">
         <v>74</v>
@@ -3299,7 +3299,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="n"/>
+      <c r="A76" s="10" t="n"/>
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3373,7 +3373,7 @@
       <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n"/>
+      <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="4" t="n">
         <v>77</v>
@@ -3409,7 +3409,7 @@
       <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
+      <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="4" t="n">
         <v>78</v>
@@ -3445,7 +3445,7 @@
       <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
+      <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="4" t="n">
         <v>79</v>
@@ -3484,7 +3484,7 @@
       <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
+      <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="4" t="n">
         <v>80</v>
@@ -3519,7 +3519,7 @@
       <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="9" t="n"/>
       <c r="C82" s="4" t="n">
         <v>81</v>
@@ -3554,7 +3554,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
+      <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3592,7 +3592,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
+      <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3625,7 +3625,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3666,7 +3666,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
+      <c r="A86" s="9" t="n"/>
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3699,7 +3699,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
+      <c r="A87" s="9" t="n"/>
       <c r="B87" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -3744,7 +3744,7 @@
       <c r="I87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
+      <c r="A88" s="9" t="n"/>
       <c r="B88" s="9" t="n"/>
       <c r="C88" s="16" t="n">
         <v>87</v>
@@ -3788,7 +3788,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
+      <c r="A89" s="9" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3834,7 +3834,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
+      <c r="A90" s="9" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3891,7 +3891,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
+      <c r="A91" s="9" t="n"/>
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3951,7 +3951,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
+      <c r="A92" s="9" t="n"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -3998,7 +3998,7 @@
       <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n"/>
+      <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="4" t="n">
         <v>92</v>
@@ -4073,7 +4073,7 @@
       <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
+      <c r="A94" s="9" t="n"/>
       <c r="B94" s="9" t="n"/>
       <c r="C94" s="4" t="n">
         <v>93</v>
@@ -4106,7 +4106,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
+      <c r="A95" s="9" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -4178,7 +4178,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n"/>
+      <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4211,7 +4211,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
+      <c r="A97" s="9" t="n"/>
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4288,7 +4288,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
+      <c r="A98" s="9" t="n"/>
       <c r="B98" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -4325,7 +4325,7 @@
       <c r="I98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
+      <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="16" t="n">
         <v>98</v>
@@ -4364,7 +4364,7 @@
       <c r="I99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n"/>
+      <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="16" t="n">
         <v>99</v>
@@ -4402,7 +4402,7 @@
       <c r="I100" s="18" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
+      <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="16" t="n">
         <v>100</v>
@@ -4435,7 +4435,7 @@
       <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="n"/>
+      <c r="A102" s="10" t="n"/>
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="16" t="n">
         <v>101</v>
@@ -4517,7 +4517,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="n"/>
+      <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4558,7 +4558,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="n"/>
+      <c r="A105" s="9" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4599,7 +4599,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="n"/>
+      <c r="A106" s="9" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4638,7 +4638,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n"/>
+      <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4685,7 +4685,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
+      <c r="A108" s="9" t="n"/>
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4718,7 +4718,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n"/>
+      <c r="A109" s="9" t="n"/>
       <c r="B109" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
@@ -4734,8 +4734,8 @@
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>이번 상담에서 아직 오간 대화가 없습니다.
-— 쪽지를 보낼 받는 사람을 알 수 없어요 — 로그인 사번이 넘어오지 않았습니다. «사번 3902172한테 보내줘»처럼 사번을 알려주시면 그 앞으로 보낼게요.</t>
+          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
+(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 12.0초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_I…)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
+      <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="n"/>
       <c r="C110" s="16" t="n">
         <v>109</v>
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
+      <c r="A111" s="9" t="n"/>
       <c r="B111" s="9" t="n"/>
       <c r="C111" s="16" t="n">
         <v>110</v>
@@ -4834,7 +4834,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
+      <c r="A112" s="9" t="n"/>
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4867,7 +4867,7 @@
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
+      <c r="A113" s="9" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>19. 브리핑 수정</t>
@@ -4904,7 +4904,7 @@
       <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
+      <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="4" t="n">
         <v>113</v>
@@ -4937,7 +4937,7 @@
       <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
+      <c r="A115" s="9" t="n"/>
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="4" t="n">
         <v>114</v>
@@ -4981,7 +4981,7 @@
       <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
+      <c r="A116" s="9" t="n"/>
       <c r="B116" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
@@ -5025,7 +5025,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
+      <c r="A117" s="9" t="n"/>
       <c r="B117" s="9" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -5064,7 +5064,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="n"/>
+      <c r="A118" s="9" t="n"/>
       <c r="B118" s="9" t="n"/>
       <c r="C118" s="16" t="n">
         <v>117</v>
@@ -5101,7 +5101,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
+      <c r="A119" s="9" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="16" t="n">
         <v>118</v>
@@ -5146,7 +5146,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
+      <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="16" t="n">
         <v>119</v>
@@ -5185,7 +5185,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
+      <c r="A121" s="9" t="n"/>
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
@@ -5218,7 +5218,7 @@
       <c r="I121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
+      <c r="A122" s="9" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>21. 에이전트 능력 안내</t>
@@ -5270,7 +5270,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
+      <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5320,7 +5320,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
+      <c r="A124" s="9" t="n"/>
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="4" t="n">
         <v>123</v>
@@ -5370,7 +5370,7 @@
       <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
+      <c r="A125" s="9" t="n"/>
       <c r="B125" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
@@ -5407,7 +5407,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="24" t="n"/>
+      <c r="A126" s="10" t="n"/>
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5495,7 +5495,7 @@
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
+      <c r="A128" s="9" t="n"/>
       <c r="B128" s="9" t="n"/>
       <c r="C128" s="4" t="n">
         <v>127</v>
@@ -5532,7 +5532,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="n"/>
+      <c r="A129" s="9" t="n"/>
       <c r="B129" s="9" t="n"/>
       <c r="C129" s="4" t="n">
         <v>128</v>
@@ -5571,7 +5571,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="n"/>
+      <c r="A130" s="9" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5604,7 +5604,7 @@
       <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
+      <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5645,7 +5645,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
+      <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5682,7 +5682,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
+      <c r="A133" s="9" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5723,7 +5723,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
+      <c r="A134" s="9" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5762,7 +5762,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
+      <c r="A135" s="9" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5799,7 +5799,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
+      <c r="A136" s="9" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
+      <c r="A137" s="9" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5869,7 +5869,7 @@
       <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
+      <c r="A138" s="9" t="n"/>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5902,7 +5902,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
+      <c r="A139" s="9" t="n"/>
       <c r="B139" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
@@ -5948,7 +5948,7 @@
       <c r="I139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
+      <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="16" t="n">
         <v>139</v>
@@ -6007,7 +6007,7 @@
       <c r="I140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="n"/>
+      <c r="A141" s="9" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="16" t="n">
         <v>140</v>
@@ -6053,7 +6053,7 @@
       <c r="I141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="n"/>
+      <c r="A142" s="9" t="n"/>
       <c r="B142" s="9" t="n"/>
       <c r="C142" s="16" t="n">
         <v>141</v>
@@ -6090,7 +6090,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
+      <c r="A143" s="9" t="n"/>
       <c r="B143" s="9" t="n"/>
       <c r="C143" s="16" t="n">
         <v>142</v>
@@ -6123,7 +6123,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
+      <c r="A144" s="9" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -6157,7 +6157,7 @@
       <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
+      <c r="A145" s="9" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -6190,7 +6190,7 @@
       <c r="I145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
+      <c r="A146" s="9" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6227,7 +6227,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
+      <c r="A147" s="9" t="n"/>
       <c r="B147" s="10" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6260,7 +6260,7 @@
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="n"/>
+      <c r="A148" s="9" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -6299,7 +6299,7 @@
       <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="n"/>
+      <c r="A149" s="9" t="n"/>
       <c r="B149" s="9" t="n"/>
       <c r="C149" s="4" t="n">
         <v>148</v>
@@ -6334,7 +6334,7 @@
       <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="n"/>
+      <c r="A150" s="9" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6367,7 +6367,7 @@
       <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="n"/>
+      <c r="A151" s="9" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6400,7 +6400,7 @@
       <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="n"/>
+      <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6438,7 +6438,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="n"/>
+      <c r="A153" s="9" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6471,7 +6471,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="n"/>
+      <c r="A154" s="9" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -6545,7 +6545,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="n"/>
+      <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6581,7 +6581,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="n"/>
+      <c r="A156" s="9" t="n"/>
       <c r="B156" s="9" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6620,7 +6620,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="n"/>
+      <c r="A157" s="9" t="n"/>
       <c r="B157" s="9" t="n"/>
       <c r="C157" s="16" t="n">
         <v>156</v>
@@ -6656,7 +6656,7 @@
       <c r="I157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="n"/>
+      <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="16" t="n">
         <v>157</v>
@@ -6692,7 +6692,7 @@
       <c r="I158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="n"/>
+      <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="16" t="n">
         <v>158</v>
@@ -6729,7 +6729,7 @@
       <c r="I159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="n"/>
+      <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="16" t="n">
         <v>159</v>
@@ -6765,7 +6765,7 @@
       <c r="I160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="n"/>
+      <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="16" t="n">
         <v>160</v>
@@ -6801,7 +6801,7 @@
       <c r="I161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="n"/>
+      <c r="A162" s="9" t="n"/>
       <c r="B162" s="9" t="n"/>
       <c r="C162" s="16" t="n">
         <v>161</v>
@@ -6838,7 +6838,7 @@
       <c r="I162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="n"/>
+      <c r="A163" s="9" t="n"/>
       <c r="B163" s="9" t="n"/>
       <c r="C163" s="16" t="n">
         <v>162</v>
@@ -6874,7 +6874,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="n"/>
+      <c r="A164" s="9" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6910,7 +6910,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="24" t="n"/>
+      <c r="A165" s="10" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6948,8 +6948,8 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B127:B138"/>
+    <mergeCell ref="A127:A165"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A127:A165"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B68:B70"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
+      <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
+      <c r="A5" s="8" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="8" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
+      <c r="A17" s="8" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
+      <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
+      <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
+      <c r="A24" s="8" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
+      <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="8" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
+      <c r="A27" s="8" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
+      <c r="A28" s="8" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
+      <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
+      <c r="A30" s="8" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
+      <c r="A31" s="8" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
+      <c r="A32" s="8" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n"/>
+      <c r="A33" s="8" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
+      <c r="A34" s="8" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n"/>
+      <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
+      <c r="A36" s="8" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
+      <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="8" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
+      <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1965,21 +1965,17 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
+      <c r="A40" s="24" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>(더미 자산 문구로) 이 문구 발송 화면에 넣어줘</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>어떤 문구를 보낼지 큰따옴표로 감싸서 알려주시겠어요? (예: "..." 로 LMS 보내줘)</t>
-        </is>
-      </c>
+          <t>(더미 문구로 LMS 요청한 뒤) 응, 열어줘</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr"/>
       <c r="F40" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -1995,7 +1991,11 @@
           <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr"/>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>"[KB국민은행] 고객님의 개인형IRP 운용 상태를 점검해 안내드릴 예정입니다. 자세한 내용은 https://obank.kbstar.com/pending/irp-checkup-draft 에서 확인해 주세요." 로 LMS 보내줘</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
+      <c r="A42" s="8" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2078,7 +2078,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
+      <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2111,7 +2111,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2144,7 +2144,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
+      <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2175,7 +2175,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
+      <c r="A46" s="8" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2210,7 +2210,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
+      <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2245,7 +2245,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
+      <c r="A48" s="8" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2279,7 +2279,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n"/>
+      <c r="A49" s="8" t="n"/>
       <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2316,7 +2316,7 @@
       <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="8" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="16" t="n">
         <v>49</v>
@@ -2349,7 +2349,7 @@
       <c r="I50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n"/>
+      <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="16" t="n">
         <v>50</v>
@@ -2385,7 +2385,7 @@
       <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
+      <c r="A52" s="8" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="16" t="n">
         <v>51</v>
@@ -2456,7 +2456,7 @@
       <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n"/>
+      <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="16" t="n">
         <v>52</v>
@@ -2509,7 +2509,7 @@
       <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n"/>
+      <c r="A54" s="8" t="n"/>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="16" t="n">
         <v>53</v>
@@ -2556,7 +2556,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n"/>
+      <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="16" t="n">
         <v>54</v>
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
+      <c r="A56" s="8" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2632,7 +2632,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n"/>
+      <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2665,7 +2665,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
+      <c r="A58" s="8" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2698,7 +2698,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
+      <c r="A59" s="8" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2738,7 +2738,7 @@
       <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
+      <c r="A60" s="8" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="4" t="n">
         <v>59</v>
@@ -2773,7 +2773,7 @@
       <c r="I60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n"/>
+      <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="4" t="n">
         <v>60</v>
@@ -2806,7 +2806,7 @@
       <c r="I61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
+      <c r="A62" s="8" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="4" t="n">
         <v>61</v>
@@ -2842,7 +2842,7 @@
       <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="n"/>
+      <c r="A63" s="8" t="n"/>
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="4" t="n">
         <v>62</v>
@@ -2875,7 +2875,7 @@
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
+      <c r="A64" s="8" t="n"/>
       <c r="B64" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -2912,7 +2912,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n"/>
+      <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="16" t="n">
         <v>64</v>
@@ -2950,7 +2950,7 @@
       <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
+      <c r="A66" s="8" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="16" t="n">
         <v>65</v>
@@ -2983,7 +2983,7 @@
       <c r="I66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
+      <c r="A67" s="8" t="n"/>
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="16" t="n">
         <v>66</v>
@@ -3018,7 +3018,7 @@
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
+      <c r="A68" s="8" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3055,7 +3055,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n"/>
+      <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3089,7 +3089,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
+      <c r="A70" s="8" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3122,7 +3122,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n"/>
+      <c r="A71" s="8" t="n"/>
       <c r="B71" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3159,7 +3159,7 @@
       <c r="I71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
+      <c r="A72" s="8" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="16" t="n">
         <v>71</v>
@@ -3192,7 +3192,7 @@
       <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n"/>
+      <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="16" t="n">
         <v>72</v>
@@ -3230,7 +3230,7 @@
       <c r="I73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
+      <c r="A74" s="8" t="n"/>
       <c r="B74" s="9" t="n"/>
       <c r="C74" s="16" t="n">
         <v>73</v>
@@ -3266,7 +3266,7 @@
       <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n"/>
+      <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="16" t="n">
         <v>74</v>
@@ -3299,7 +3299,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n"/>
+      <c r="A76" s="24" t="n"/>
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3373,7 +3373,7 @@
       <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n"/>
+      <c r="A78" s="8" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="4" t="n">
         <v>77</v>
@@ -3409,7 +3409,7 @@
       <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n"/>
+      <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="4" t="n">
         <v>78</v>
@@ -3445,7 +3445,7 @@
       <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n"/>
+      <c r="A80" s="8" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="4" t="n">
         <v>79</v>
@@ -3484,7 +3484,7 @@
       <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n"/>
+      <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="4" t="n">
         <v>80</v>
@@ -3519,7 +3519,7 @@
       <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n"/>
+      <c r="A82" s="8" t="n"/>
       <c r="B82" s="9" t="n"/>
       <c r="C82" s="4" t="n">
         <v>81</v>
@@ -3554,7 +3554,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n"/>
+      <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3592,7 +3592,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
+      <c r="A84" s="8" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3625,7 +3625,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="n"/>
+      <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3666,7 +3666,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
+      <c r="A86" s="8" t="n"/>
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3699,7 +3699,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="n"/>
+      <c r="A87" s="8" t="n"/>
       <c r="B87" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -3744,7 +3744,7 @@
       <c r="I87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n"/>
+      <c r="A88" s="8" t="n"/>
       <c r="B88" s="9" t="n"/>
       <c r="C88" s="16" t="n">
         <v>87</v>
@@ -3788,7 +3788,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n"/>
+      <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3834,7 +3834,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n"/>
+      <c r="A90" s="8" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3891,7 +3891,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n"/>
+      <c r="A91" s="8" t="n"/>
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3951,7 +3951,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n"/>
+      <c r="A92" s="8" t="n"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -3998,7 +3998,7 @@
       <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="n"/>
+      <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="4" t="n">
         <v>92</v>
@@ -4073,7 +4073,7 @@
       <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="n"/>
+      <c r="A94" s="8" t="n"/>
       <c r="B94" s="9" t="n"/>
       <c r="C94" s="4" t="n">
         <v>93</v>
@@ -4106,7 +4106,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n"/>
+      <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -4178,7 +4178,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="n"/>
+      <c r="A96" s="8" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4211,7 +4211,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="n"/>
+      <c r="A97" s="8" t="n"/>
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4288,7 +4288,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n"/>
+      <c r="A98" s="8" t="n"/>
       <c r="B98" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -4325,7 +4325,7 @@
       <c r="I98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n"/>
+      <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="16" t="n">
         <v>98</v>
@@ -4364,7 +4364,7 @@
       <c r="I99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n"/>
+      <c r="A100" s="8" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="16" t="n">
         <v>99</v>
@@ -4402,7 +4402,7 @@
       <c r="I100" s="18" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="n"/>
+      <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="16" t="n">
         <v>100</v>
@@ -4435,7 +4435,7 @@
       <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n"/>
+      <c r="A102" s="24" t="n"/>
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="16" t="n">
         <v>101</v>
@@ -4517,7 +4517,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n"/>
+      <c r="A104" s="8" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4558,7 +4558,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="n"/>
+      <c r="A105" s="8" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4599,7 +4599,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n"/>
+      <c r="A106" s="8" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4638,7 +4638,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="n"/>
+      <c r="A107" s="8" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4685,7 +4685,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="n"/>
+      <c r="A108" s="8" t="n"/>
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4718,7 +4718,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="n"/>
+      <c r="A109" s="8" t="n"/>
       <c r="B109" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
@@ -4760,7 +4760,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n"/>
+      <c r="A110" s="8" t="n"/>
       <c r="B110" s="9" t="n"/>
       <c r="C110" s="16" t="n">
         <v>109</v>
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="n"/>
+      <c r="A111" s="8" t="n"/>
       <c r="B111" s="9" t="n"/>
       <c r="C111" s="16" t="n">
         <v>110</v>
@@ -4834,7 +4834,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n"/>
+      <c r="A112" s="8" t="n"/>
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4867,7 +4867,7 @@
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n"/>
+      <c r="A113" s="8" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>19. 브리핑 수정</t>
@@ -4904,7 +4904,7 @@
       <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n"/>
+      <c r="A114" s="8" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="4" t="n">
         <v>113</v>
@@ -4937,7 +4937,7 @@
       <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n"/>
+      <c r="A115" s="8" t="n"/>
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="4" t="n">
         <v>114</v>
@@ -4981,7 +4981,7 @@
       <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n"/>
+      <c r="A116" s="8" t="n"/>
       <c r="B116" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
@@ -5025,7 +5025,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="n"/>
+      <c r="A117" s="8" t="n"/>
       <c r="B117" s="9" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -5064,7 +5064,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="n"/>
+      <c r="A118" s="8" t="n"/>
       <c r="B118" s="9" t="n"/>
       <c r="C118" s="16" t="n">
         <v>117</v>
@@ -5101,7 +5101,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n"/>
+      <c r="A119" s="8" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="16" t="n">
         <v>118</v>
@@ -5146,7 +5146,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="n"/>
+      <c r="A120" s="8" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="16" t="n">
         <v>119</v>
@@ -5185,7 +5185,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="n"/>
+      <c r="A121" s="8" t="n"/>
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
@@ -5218,7 +5218,7 @@
       <c r="I121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="n"/>
+      <c r="A122" s="8" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>21. 에이전트 능력 안내</t>
@@ -5270,7 +5270,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n"/>
+      <c r="A123" s="8" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5320,7 +5320,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="n"/>
+      <c r="A124" s="8" t="n"/>
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="4" t="n">
         <v>123</v>
@@ -5370,7 +5370,7 @@
       <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="n"/>
+      <c r="A125" s="8" t="n"/>
       <c r="B125" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
@@ -5407,7 +5407,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n"/>
+      <c r="A126" s="24" t="n"/>
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5495,7 +5495,7 @@
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="n"/>
+      <c r="A128" s="8" t="n"/>
       <c r="B128" s="9" t="n"/>
       <c r="C128" s="4" t="n">
         <v>127</v>
@@ -5532,7 +5532,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="n"/>
+      <c r="A129" s="8" t="n"/>
       <c r="B129" s="9" t="n"/>
       <c r="C129" s="4" t="n">
         <v>128</v>
@@ -5571,7 +5571,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="n"/>
+      <c r="A130" s="8" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5604,7 +5604,7 @@
       <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="n"/>
+      <c r="A131" s="8" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5645,7 +5645,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="n"/>
+      <c r="A132" s="8" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5682,7 +5682,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="n"/>
+      <c r="A133" s="8" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5723,7 +5723,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="n"/>
+      <c r="A134" s="8" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5762,7 +5762,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n"/>
+      <c r="A135" s="8" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5799,7 +5799,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="n"/>
+      <c r="A136" s="8" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="n"/>
+      <c r="A137" s="8" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5869,7 +5869,7 @@
       <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="n"/>
+      <c r="A138" s="8" t="n"/>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5902,7 +5902,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="n"/>
+      <c r="A139" s="8" t="n"/>
       <c r="B139" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
@@ -5948,7 +5948,7 @@
       <c r="I139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="n"/>
+      <c r="A140" s="8" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="16" t="n">
         <v>139</v>
@@ -6007,7 +6007,7 @@
       <c r="I140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="n"/>
+      <c r="A141" s="8" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="16" t="n">
         <v>140</v>
@@ -6053,7 +6053,7 @@
       <c r="I141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="n"/>
+      <c r="A142" s="8" t="n"/>
       <c r="B142" s="9" t="n"/>
       <c r="C142" s="16" t="n">
         <v>141</v>
@@ -6090,7 +6090,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="n"/>
+      <c r="A143" s="8" t="n"/>
       <c r="B143" s="9" t="n"/>
       <c r="C143" s="16" t="n">
         <v>142</v>
@@ -6123,7 +6123,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="n"/>
+      <c r="A144" s="8" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -6157,7 +6157,7 @@
       <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="n"/>
+      <c r="A145" s="8" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -6190,7 +6190,7 @@
       <c r="I145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="n"/>
+      <c r="A146" s="8" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6227,7 +6227,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n"/>
+      <c r="A147" s="8" t="n"/>
       <c r="B147" s="10" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6260,7 +6260,7 @@
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="n"/>
+      <c r="A148" s="8" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -6299,7 +6299,7 @@
       <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="n"/>
+      <c r="A149" s="8" t="n"/>
       <c r="B149" s="9" t="n"/>
       <c r="C149" s="4" t="n">
         <v>148</v>
@@ -6334,7 +6334,7 @@
       <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="n"/>
+      <c r="A150" s="8" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6367,7 +6367,7 @@
       <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="n"/>
+      <c r="A151" s="8" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6400,7 +6400,7 @@
       <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="n"/>
+      <c r="A152" s="8" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6438,7 +6438,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="n"/>
+      <c r="A153" s="8" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6471,7 +6471,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="n"/>
+      <c r="A154" s="8" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -6545,7 +6545,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="n"/>
+      <c r="A155" s="8" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6581,7 +6581,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="9" t="n"/>
+      <c r="A156" s="8" t="n"/>
       <c r="B156" s="9" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6620,7 +6620,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="n"/>
+      <c r="A157" s="8" t="n"/>
       <c r="B157" s="9" t="n"/>
       <c r="C157" s="16" t="n">
         <v>156</v>
@@ -6656,7 +6656,7 @@
       <c r="I157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="n"/>
+      <c r="A158" s="8" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="16" t="n">
         <v>157</v>
@@ -6692,7 +6692,7 @@
       <c r="I158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="n"/>
+      <c r="A159" s="8" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="16" t="n">
         <v>158</v>
@@ -6729,7 +6729,7 @@
       <c r="I159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="n"/>
+      <c r="A160" s="8" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="16" t="n">
         <v>159</v>
@@ -6765,7 +6765,7 @@
       <c r="I160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="n"/>
+      <c r="A161" s="8" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="16" t="n">
         <v>160</v>
@@ -6801,7 +6801,7 @@
       <c r="I161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="n"/>
+      <c r="A162" s="8" t="n"/>
       <c r="B162" s="9" t="n"/>
       <c r="C162" s="16" t="n">
         <v>161</v>
@@ -6838,7 +6838,7 @@
       <c r="I162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n"/>
+      <c r="A163" s="8" t="n"/>
       <c r="B163" s="9" t="n"/>
       <c r="C163" s="16" t="n">
         <v>162</v>
@@ -6874,7 +6874,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="n"/>
+      <c r="A164" s="8" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6910,7 +6910,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="10" t="n"/>
+      <c r="A165" s="24" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6948,8 +6948,8 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B127:B138"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="A127:A165"/>
-    <mergeCell ref="D27:D28"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B68:B70"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -568,7 +568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I165"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n"/>
+      <c r="A3" s="9" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1072,8 +1072,8 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: fact:고유계정대 최근 한 달 증가액
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 제도·상품 수치 「고유계정대 최근 한 달 증가액」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>송도윤 고객님의 IRP 가입일은 2023년 10월 2일이며, 가입 후 3.0년이 지났어요.</t>
+          <t>그 고객의 IRP 가입일은 2023년 10월 2일이고, 가입 후 2년 11개월이 지났어요.</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
+      <c r="A27" s="9" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
+      <c r="A29" s="9" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="9" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
+      <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
+      <c r="A33" s="9" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
+      <c r="A34" s="9" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
+      <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
+      <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
+      <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
+      <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1965,7 +1965,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
+      <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -1975,7 +1975,11 @@
           <t>(더미 문구로 LMS 요청한 뒤) 응, 열어줘</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr"/>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>연계하지 않았어요. 더미 콘텐츠는 발송 화면에 채울 수 없습니다 — 실제 콘텐츠로 교체한 뒤(자산의 dummy 표시 제거) 다시 시도하세요</t>
+        </is>
+      </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -2045,7 +2049,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n"/>
+      <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2078,7 +2082,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2111,7 +2115,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n"/>
+      <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2144,7 +2148,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
+      <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2175,7 +2179,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
+      <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2210,7 +2214,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n"/>
+      <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2245,7 +2249,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
+      <c r="A48" s="9" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2279,7 +2283,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2316,7 +2320,7 @@
       <c r="I49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
+      <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="16" t="n">
         <v>49</v>
@@ -2349,7 +2353,7 @@
       <c r="I50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
+      <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="16" t="n">
         <v>50</v>
@@ -2385,7 +2389,7 @@
       <c r="I51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
+      <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="16" t="n">
         <v>51</v>
@@ -2456,7 +2460,7 @@
       <c r="I52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
+      <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="16" t="n">
         <v>52</v>
@@ -2509,7 +2513,7 @@
       <c r="I53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
+      <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="16" t="n">
         <v>53</v>
@@ -2556,7 +2560,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
+      <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="16" t="n">
         <v>54</v>
@@ -2599,7 +2603,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
+      <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2632,7 +2636,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2665,7 +2669,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
+      <c r="A58" s="9" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2698,7 +2702,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
+      <c r="A59" s="9" t="n"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2738,7 +2742,7 @@
       <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="4" t="n">
         <v>59</v>
@@ -2773,7 +2777,7 @@
       <c r="I60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
+      <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="4" t="n">
         <v>60</v>
@@ -2806,7 +2810,7 @@
       <c r="I61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
+      <c r="A62" s="9" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="4" t="n">
         <v>61</v>
@@ -2842,7 +2846,7 @@
       <c r="I62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
+      <c r="A63" s="9" t="n"/>
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="4" t="n">
         <v>62</v>
@@ -2875,7 +2879,7 @@
       <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
+      <c r="A64" s="9" t="n"/>
       <c r="B64" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -2912,7 +2916,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
+      <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="16" t="n">
         <v>64</v>
@@ -2950,7 +2954,7 @@
       <c r="I65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="9" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="16" t="n">
         <v>65</v>
@@ -2983,7 +2987,7 @@
       <c r="I66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
+      <c r="A67" s="9" t="n"/>
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="16" t="n">
         <v>66</v>
@@ -3018,7 +3022,7 @@
       <c r="I67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
+      <c r="A68" s="9" t="n"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3055,7 +3059,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
+      <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3089,7 +3093,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
+      <c r="A70" s="9" t="n"/>
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3122,7 +3126,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="9" t="n"/>
       <c r="B71" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3159,7 +3163,7 @@
       <c r="I71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
+      <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="16" t="n">
         <v>71</v>
@@ -3192,7 +3196,7 @@
       <c r="I72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="9" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="16" t="n">
         <v>72</v>
@@ -3230,7 +3234,7 @@
       <c r="I73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
+      <c r="A74" s="9" t="n"/>
       <c r="B74" s="9" t="n"/>
       <c r="C74" s="16" t="n">
         <v>73</v>
@@ -3266,7 +3270,7 @@
       <c r="I74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="16" t="n">
         <v>74</v>
@@ -3299,7 +3303,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="n"/>
+      <c r="A76" s="10" t="n"/>
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3373,7 +3377,7 @@
       <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n"/>
+      <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="4" t="n">
         <v>77</v>
@@ -3409,7 +3413,7 @@
       <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
+      <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="4" t="n">
         <v>78</v>
@@ -3445,7 +3449,7 @@
       <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
+      <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="4" t="n">
         <v>79</v>
@@ -3484,7 +3488,7 @@
       <c r="I80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
+      <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="4" t="n">
         <v>80</v>
@@ -3519,7 +3523,7 @@
       <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="9" t="n"/>
       <c r="C82" s="4" t="n">
         <v>81</v>
@@ -3554,7 +3558,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
+      <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3592,7 +3596,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
+      <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3625,7 +3629,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3666,7 +3670,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
+      <c r="A86" s="9" t="n"/>
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3699,7 +3703,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
+      <c r="A87" s="9" t="n"/>
       <c r="B87" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -3744,7 +3748,7 @@
       <c r="I87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
+      <c r="A88" s="9" t="n"/>
       <c r="B88" s="9" t="n"/>
       <c r="C88" s="16" t="n">
         <v>87</v>
@@ -3788,7 +3792,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
+      <c r="A89" s="9" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3834,7 +3838,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
+      <c r="A90" s="9" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3891,7 +3895,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
+      <c r="A91" s="9" t="n"/>
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3951,7 +3955,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
+      <c r="A92" s="9" t="n"/>
       <c r="B92" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -3998,7 +4002,7 @@
       <c r="I92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n"/>
+      <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="4" t="n">
         <v>92</v>
@@ -4073,7 +4077,7 @@
       <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
+      <c r="A94" s="9" t="n"/>
       <c r="B94" s="9" t="n"/>
       <c r="C94" s="4" t="n">
         <v>93</v>
@@ -4106,7 +4110,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
+      <c r="A95" s="9" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -4178,7 +4182,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n"/>
+      <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4211,7 +4215,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
+      <c r="A97" s="9" t="n"/>
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4288,7 +4292,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
+      <c r="A98" s="9" t="n"/>
       <c r="B98" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -4325,7 +4329,7 @@
       <c r="I98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
+      <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="16" t="n">
         <v>98</v>
@@ -4364,7 +4368,7 @@
       <c r="I99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n"/>
+      <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="16" t="n">
         <v>99</v>
@@ -4402,7 +4406,7 @@
       <c r="I100" s="18" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
+      <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="16" t="n">
         <v>100</v>
@@ -4435,7 +4439,7 @@
       <c r="I101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="n"/>
+      <c r="A102" s="10" t="n"/>
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="16" t="n">
         <v>101</v>
@@ -4517,7 +4521,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="n"/>
+      <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4558,7 +4562,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="n"/>
+      <c r="A105" s="9" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4599,7 +4603,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="n"/>
+      <c r="A106" s="9" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4638,7 +4642,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n"/>
+      <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4685,7 +4689,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
+      <c r="A108" s="9" t="n"/>
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4718,7 +4722,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n"/>
+      <c r="A109" s="9" t="n"/>
       <c r="B109" s="15" t="inlineStr">
         <is>
           <t>18. 이번 상담 요약·쪽지</t>
@@ -4760,7 +4764,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
+      <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="n"/>
       <c r="C110" s="16" t="n">
         <v>109</v>
@@ -4797,7 +4801,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
+      <c r="A111" s="9" t="n"/>
       <c r="B111" s="9" t="n"/>
       <c r="C111" s="16" t="n">
         <v>110</v>
@@ -4834,7 +4838,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
+      <c r="A112" s="9" t="n"/>
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4867,7 +4871,7 @@
       <c r="I112" s="18" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
+      <c r="A113" s="9" t="n"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
           <t>19. 브리핑 수정</t>
@@ -4904,7 +4908,7 @@
       <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
+      <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="4" t="n">
         <v>113</v>
@@ -4937,7 +4941,7 @@
       <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
+      <c r="A115" s="9" t="n"/>
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="4" t="n">
         <v>114</v>
@@ -4981,7 +4985,7 @@
       <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
+      <c r="A116" s="9" t="n"/>
       <c r="B116" s="15" t="inlineStr">
         <is>
           <t>20. 답변 다듬기·되짚기</t>
@@ -5025,7 +5029,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
+      <c r="A117" s="9" t="n"/>
       <c r="B117" s="9" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -5064,7 +5068,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="n"/>
+      <c r="A118" s="9" t="n"/>
       <c r="B118" s="9" t="n"/>
       <c r="C118" s="16" t="n">
         <v>117</v>
@@ -5101,7 +5105,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
+      <c r="A119" s="9" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="16" t="n">
         <v>118</v>
@@ -5146,7 +5150,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
+      <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="16" t="n">
         <v>119</v>
@@ -5185,7 +5189,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
+      <c r="A121" s="9" t="n"/>
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="16" t="n">
         <v>120</v>
@@ -5218,7 +5222,7 @@
       <c r="I121" s="18" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
+      <c r="A122" s="9" t="n"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>21. 에이전트 능력 안내</t>
@@ -5270,7 +5274,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
+      <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5320,7 +5324,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
+      <c r="A124" s="9" t="n"/>
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="4" t="n">
         <v>123</v>
@@ -5370,7 +5374,7 @@
       <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
+      <c r="A125" s="9" t="n"/>
       <c r="B125" s="15" t="inlineStr">
         <is>
           <t>22. 오늘의 타겟 목록</t>
@@ -5407,7 +5411,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="24" t="n"/>
+      <c r="A126" s="10" t="n"/>
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5495,7 +5499,7 @@
       <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
+      <c r="A128" s="9" t="n"/>
       <c r="B128" s="9" t="n"/>
       <c r="C128" s="4" t="n">
         <v>127</v>
@@ -5532,7 +5536,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="n"/>
+      <c r="A129" s="9" t="n"/>
       <c r="B129" s="9" t="n"/>
       <c r="C129" s="4" t="n">
         <v>128</v>
@@ -5571,7 +5575,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="n"/>
+      <c r="A130" s="9" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5604,7 +5608,7 @@
       <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
+      <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5645,7 +5649,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
+      <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5682,7 +5686,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
+      <c r="A133" s="9" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5723,7 +5727,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
+      <c r="A134" s="9" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5762,7 +5766,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
+      <c r="A135" s="9" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5799,7 +5803,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
+      <c r="A136" s="9" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5836,7 +5840,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
+      <c r="A137" s="9" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5869,7 +5873,7 @@
       <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
+      <c r="A138" s="9" t="n"/>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5902,7 +5906,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
+      <c r="A139" s="9" t="n"/>
       <c r="B139" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
@@ -5948,7 +5952,7 @@
       <c r="I139" s="18" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
+      <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="16" t="n">
         <v>139</v>
@@ -6007,7 +6011,7 @@
       <c r="I140" s="18" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="n"/>
+      <c r="A141" s="9" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="16" t="n">
         <v>140</v>
@@ -6053,7 +6057,7 @@
       <c r="I141" s="18" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="n"/>
+      <c r="A142" s="9" t="n"/>
       <c r="B142" s="9" t="n"/>
       <c r="C142" s="16" t="n">
         <v>141</v>
@@ -6090,7 +6094,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
+      <c r="A143" s="9" t="n"/>
       <c r="B143" s="9" t="n"/>
       <c r="C143" s="16" t="n">
         <v>142</v>
@@ -6123,7 +6127,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
+      <c r="A144" s="9" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -6157,7 +6161,7 @@
       <c r="I144" s="18" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
+      <c r="A145" s="9" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -6190,7 +6194,7 @@
       <c r="I145" s="18" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
+      <c r="A146" s="9" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6227,7 +6231,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
+      <c r="A147" s="9" t="n"/>
       <c r="B147" s="10" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6260,7 +6264,7 @@
       <c r="I147" s="18" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="n"/>
+      <c r="A148" s="9" t="n"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -6299,7 +6303,7 @@
       <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="n"/>
+      <c r="A149" s="9" t="n"/>
       <c r="B149" s="9" t="n"/>
       <c r="C149" s="4" t="n">
         <v>148</v>
@@ -6334,7 +6338,7 @@
       <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="n"/>
+      <c r="A150" s="9" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6367,7 +6371,7 @@
       <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="n"/>
+      <c r="A151" s="9" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6400,7 +6404,7 @@
       <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="n"/>
+      <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6438,7 +6442,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="n"/>
+      <c r="A153" s="9" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6471,7 +6475,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="n"/>
+      <c r="A154" s="9" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -6545,7 +6549,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="n"/>
+      <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6581,7 +6585,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="n"/>
+      <c r="A156" s="9" t="n"/>
       <c r="B156" s="9" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6620,7 +6624,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="n"/>
+      <c r="A157" s="9" t="n"/>
       <c r="B157" s="9" t="n"/>
       <c r="C157" s="16" t="n">
         <v>156</v>
@@ -6656,7 +6660,7 @@
       <c r="I157" s="18" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="n"/>
+      <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="16" t="n">
         <v>157</v>
@@ -6692,7 +6696,7 @@
       <c r="I158" s="18" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="n"/>
+      <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="16" t="n">
         <v>158</v>
@@ -6729,7 +6733,7 @@
       <c r="I159" s="18" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="n"/>
+      <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="16" t="n">
         <v>159</v>
@@ -6765,7 +6769,7 @@
       <c r="I160" s="18" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="n"/>
+      <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="16" t="n">
         <v>160</v>
@@ -6801,7 +6805,7 @@
       <c r="I161" s="18" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="n"/>
+      <c r="A162" s="9" t="n"/>
       <c r="B162" s="9" t="n"/>
       <c r="C162" s="16" t="n">
         <v>161</v>
@@ -6838,7 +6842,7 @@
       <c r="I162" s="18" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="n"/>
+      <c r="A163" s="9" t="n"/>
       <c r="B163" s="9" t="n"/>
       <c r="C163" s="16" t="n">
         <v>162</v>
@@ -6874,7 +6878,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="n"/>
+      <c r="A164" s="9" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6910,7 +6914,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="24" t="n"/>
+      <c r="A165" s="10" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6948,8 +6952,8 @@
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B127:B138"/>
+    <mergeCell ref="A127:A165"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A127:A165"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B68:B70"/>
@@ -6995,7 +6999,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2191,9 +2191,8 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: fact:타행 IRP 수수료 · pitch:타행 IRP 수수료는 우리보다 싼가
-다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+          <t>타행 IRP 수수료는 제가 가진 자료로는 확인이 어려워요. 다만 당행의 개인형IRP 수수료율에 대한 안내는 드릴 수 있으니 참고해 주세요. 
+2026년 3월 기준 개인형IRP 수수료율은 부담금 종류와 채널, 구간에 따라 다르게 적용돼요. 사용자부담금(퇴직금)은 대면 채널에서 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%이며, 비대면 채널에서는 5천만원 미만인 경우 0.20%, 5천만원 이상인 경우 면제로 적용돼요. 가입자부담금은 대면 채널에서 1억원 미만인 경우 0.28%, 1억원 이상인 경우 0.25%이고, 비대면 채널에서는 1억원 미만인 경우 0.23%, 1억원 이상인 경우 0.21%로 적용되니 안내해 드릴 때 이 점을 함께 확인해 주세요.</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2999,8 +2998,8 @@
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: screen:타행 계좌 잔액 조회 화면
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 단말 화면번호 「타행 계좌 잔액 조회」 · 업무 처리 절차 「타행 계좌 잔액 조회 업무 처리 순서」 · 단말 화면번호 「타행 계좌 잔액 조회 화면번호」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
@@ -3175,7 +3174,7 @@
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>운용지시 없이 대기 중인 현금성자산(가용고유대 − 디폴트옵션 실행대기자금) 보유 고객. 단, 임계값이 자료마다 다름: | 기준 | 출처·시기 | 용도 | |---|---|---| | 7,500만원 이상 (PB센터 관리고객 제외) | 오늘의할일 스크립트, 2023~24 추정 | TM 콜 대상 | | 100만원 이상 | 수익률 KPI 시나리오, 2021 | 매월 안내 LMS 자동발송 | | 보유비율 50% 이상 | Series 1, 2026.05 → 세그먼트 1 | 이탈위험 선별 | 과 디폴트옵션 미동의 &amp; 현금성 대기자산 10만원 이상 보유 고객 실행: 주 1회 카카오톡 + 매월 스타알림으로 등록 동의·교체매매 안내 (2023년 디폴트옵션 시행기 방식)에 따라 선정되는 대기 현금성자산 보유 고객은 운용지시 없이 대기 중인 상태여서 사실상 무수익 방치 상태로 보기 때문에 관리 대상으로 삼는 것이에요. 현금성자산은 금액이 클수록 수익률 개선 효과와 이탈 방지 효과가 커서 TM 등 고비용 채널의 우선 대상이 되며, 특히 디폴트옵션 등록 전에는 고유계정대 자금이 계속 현금성 대기자산으로 남기 때문에 디폴트옵션 동의와 교체매매를 세트로 진행하는 것이 핵심이에요.</t>
+          <t>현금성자산이 많다고 해서 무조건 방치 자금으로 볼 수는 없어요. 현금성자산이 일정기간(1개월 이상) 금액변동 없이 유지 중이고 [04-12-644] 퇴직연금 거래내역조회 시 입금 사유가 '교체매매'나 '연금지급' 사유가 아닌 경우 미운용중인 자산이 있다고 안내해 보세요. 연금지급이나 교체매매 대기 중인 정상 자금일 수도 있으므로, 고객에게 접촉하기 전에 사용계획 자금인지 방치 자금인지 먼저 가르는 것이 판단 기준이에요. 상담 용어: "고유계정대" 대신 "현금성자산", "운용지시가 되지 않는 자산" 사용 (고객에게 생소한 용어 금지).</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
@@ -3208,12 +3207,9 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>이탈 위험 고객은 현금성자산이나 정기예금 편중 고객과 계약이전 신청 고객을 기준으로 선정해요.
-현금성자산·정기예금 편중 고객은 고유계정대(현금성자산) 보유 비율 50% 이상, 또는 고유계정대 + 시중은행 정기예금만으로 100% 운용 중 대상 기준선: 총 적립금 1천만원 이상 (본부 타깃리스트 제공 기준)에 해당하는 고객을 골라내요. 이 조건에 해당하는 고객은 이탈위험도가 일반 고객의 1.3배 수준으로 높아서 본부가 리밸런싱 관리 최우선 세그먼트로 지정했어요. 다만 원문 임계값은 '고유계정대 보유비율 50% 이상 또는 고유대+시중은행 정기예금 100%, 적립금 1천만원 이상'. 코드 판정(customer.conditions dep)은 룰베이스 TG-202 의 '원리금보장 합산 80% 이상'이라 모집단이 다르다는 점을 참고해 주세요.
-다른 기준으로 타사로 계약이전(전출) 신청이 접수되어 알림이 발생한 고객 조건 조회형이 아니라 알림 수신 시점에 발동하는 이벤트형 세그먼트 (사후관리 중 시급성 최상)에 해당하는 고객도 있어요. 이들은 사후관리 중 시급성이 최상인 이탈 진행 중 고객으로, 이탈 사유를 들어보면 지킬 수 있는 고객이 생각보다 많기 때문에 영업점 직접 방어 대상으로 지정되어 있어요.
-── 빠뜨리면 안 되는 표시
-· 현금성자산·정기예금 편중 고객 (이탈 고위험)
-  원문 임계값은 '고유계정대 보유비율 50% 이상 또는 고유대+시중은행 정기예금 100%, 적립금 1천만원 이상'. 코드 판정(customer.conditions dep)은 룰베이스 TG-202 의 '원리금보장 합산 80% 이상'이라 모집단이 다르다.</t>
+          <t>어떤 이탈 위험 유형을 기준으로 보시겠습니까?
+· 자산 편중형
+· 투자 목적형</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
@@ -3535,9 +3531,9 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: pitch:금액도 얼마 안 되는데 그냥 두면 안 되나요 · playbook:금액도 얼마 안 되는데 그냥 두면 안 되나요
-다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+          <t>현금성자산 방치 고객이 금액이 적다는 이유로 운용을 미루려 할 때는, 사용계획이 있는 자금인지 먼저 확인하고 수익률 관점에서의 기회비용을 짚어주는 게 핵심이에요. 
+고유계정대 같은 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰고, 연금지급 대기나 교체매매 등 사용계획이 있는 자금인지 먼저 걸러내야 해요. 그런 자금이 아니라면 현재 미운용 중인 자산은 금리가 낮아 방치할수록 손해라는 점을 자연스럽게 설명해 보세요. 
+고객에게는 "고객님, 금액이 작아 보이셔도 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준이라서요. 금리가 높은 저축은행 정기예금이나 펀드 같은 상품으로 운용하시면 향후에 수령하시는 퇴직연금 금액이 달라지니 지금 재정비하시는 게 좋아요"라고 안내해 드릴 수 있어요.</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
@@ -4227,51 +4223,12 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>■ 투자성향별 포트폴리오  (상품 · 퇴직연금 펀드 8월 포트폴리오)
-· 기준시점: 2026.08
-### ① 안정형
-- **자산배분** : 국내채권 100%
-- **기대수익 2.4% / 변동성 3.0%**
-| 구분 | 상품명 | 투자비중 | 상품특징 |
-|---|---|---|---|
-| 국내채권 | 한화 내일받는 단기국공채 (합성총보수 연0.1977%) | 30% | 무위험 채권 및 특수채, 우량채에 투자하며, 채권잔존만기를 6개월 수준으로 유지하여 채권가격 변동위험 최소화 |
-| 국내채권 | 유진 챔피언 단기채 (합성총보수 연0.3290%) | 30% | 잔존만기가 짧은 전단채 및 기업어음에 주로 투자하여 금리변동 리스크 관리 |
-| 국내채권 | KB 스타 단기국공채 (총보수 연0.2430%) | 40% | 단기 국채, 지방채, 특수채 및 우량 회사채에 투자하여 안정적인 수익 추구 |
-### ② 안정추구형
-- **자산배분** : 국내채권 80% / 해외채권 20%
-- **기대수익 2.4% / 변동성 3.6%**
-| 구분 | 상품명 | 투자비중 | 상품특징 |
-|---|---|---|---|
-| 국내채권 | 키움 더드림 단기채 (합성총보수 연0.2990%) | 80% | 국내 단기채권 및 CP 등에 60% 이상을 투자하여 안정적인 이자수익 추구 |
-| 해외채권 | KB 글로벌 단기채(H) (합성총보수 연0.6960%) | 10% | 전세계 달러표시 단기채권에 투자하여 안정적 수익추구 |
-| 해외채권 | AB글로벌고수익 (합성총보수 연1.3670%) | 10% | 미국 및 이머징국가 기업발행 하이일드채권에 주로 투자하여 초과 수익 추구 |
-### ③ 위험중립형
-- **자산배분** : 국내채권 60% / 해외채권 15% / 해외혼합 25%
-- **기대수익 5.4% / 변동성 4.9%**
-| 구분 | 상품명 | 투자비중 | 상품특징 |
-|---|---|---|---|
-| 국내채권 | 하나 파워e단기채 (합성총보수 연0.1834%) | 60% | 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구 |
-| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 15% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
-| 해외혼합 | 삼성EMP 리얼리턴(UH) (합성총보수 연1.1215%) | 25% | 국내외 주식, 채권, 대체자산 등 다양한 자산 관련 ETF에 투자 |
-### ④ 적극투자형
-- **자산배분(도넛 표기)** : 국내채권 30% / 해외채권 10% / 해외주식 60% ⟨판독불확실⟩
-- **기대수익 10.3% / 변동성 9.7%**
-| 구분 | 상품명 | 투자비중 | 상품특징 |
-|---|---|---|---|
-| 국내채권 | NH-Amundi 하나로단기채 (합성총보수 연0.2939%) | 35% | 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구 |
-| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 5% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
-| 해외주식 | 신한누버거버먼 미국가치주(H) (합성총보수 연1.6100%) | 60% | 미국가치주 등에 주로 투자하는 누버거버먼 미국 라지캡밸류펀드에 투자하는 주식형펀드 |
-&gt; *※ 도넛 차트 표기(국내채권 30 / 해외채권 10)와 구성상품 표의 비중(국내채권 35 / 해외채권 5)이 원문상 상이하게 표기되어 있어 그대로 옮김.*
-### ⑤ 공격투자형
-- **자산배분** : 국내채권 25% / 해외채권 5% / 해외주식 70%
-- **기대수익 11.7% / 변동성 11.2%**
-| 구분 | 상품명 | 투자비중 | 상품특징 |
-|---|---|---|---|
-| 국내채권 | 교보악사Tomorrow 장기우량K-1 (총보수 연0.3300%) | 25% | 국공채, 통안채, 공사채, 은행채, 우량회사채 등 안정성이 높은 채권을 투자대상자산으로 하여 자본이득과 안정적인 이자 수익 추구 |
-| 해외채권 | 우리미국 단기채공모주(H) (합성총보수 연1.2171%) | 5% | 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자 |
-| 해외주식 | 삼성글로벌 배당성장주(H) (합성총보수 연1.4213%) | 70% | 지속적으로 배당이 증가하는 선진국 중심의 배당성장주 및 밸류에이션 매력이 높은 고배당기업에 투자 |
+          <t>위험중립형 포트폴리오는 2026년 8월 기준 국내채권 60%, 해외채권 15%, 해외혼합 25%의 자산배분으로 구성되어 있어요. 이 유형의 기대수익은 5.4%, 변동성은 4.9%로 산정되어 있으며, 활용할 수 있는 상품은 다음과 같아요.
+- 하나 파워e단기채 (합성총보수 연0.1834%) — 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구
+- 우리미국 단기채공모주(H) (합성총보수 연1.2171%) — 미국 공모주와 미국 채권에 주로 투자하며 일부자산은 한국 포함 글로벌 공모주에 선별 투자
+- 삼성EMP 리얼리턴(UH) (합성총보수 연1.1215%) — 국내외 주식, 채권, 대체자산 등 다양한 자산 관련 ETF에 투자
 ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 기준 표기입니다.
-· 출처 퇴직연금 펀드 8월 포트폴리오 (2026-08)</t>
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
       <c r="F97" s="14" t="inlineStr">
@@ -4738,8 +4695,12 @@
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>[실행 실패] LLM 다운 — 지금은 답변을 만들 수 없어요 — LLM 호출이 실패했습니다. 지식베이스에 자료가 없다는 뜻이 아니니, 잠시 후 다시 시도해주세요.
-(LLMError: HTTP 429 — 6회 시도 후에도 실패. 속도 제한. 호출 간격을 두거나 쿼터를 확인하십시오. (동시 1 · 간격 12.0초 — LLM_MAX_CONCURRENCY 를 낮추거나 LLM_MIN_I…)</t>
+          <t>[제목] 송도윤 고객 관리 대상 사유 및 대응 방향
+송도윤 고객은 최근 358일간 접촉 이력이 없어 타사 비교 견적 노출 가능성이 있습니다.
+고유계정대 2억 8,000만원이 미운용 현금성자산으로 방치되어 있으며, 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있습니다.
+디폴트옵션 미설정 상태이며 ISA 만기자금 1억 2,000만원이 유입되었고 12개월 이상 운용변경이 없는 상태로 관리 대상으로 선정되었습니다.
+현금성자산 방치 건은 정기예금이나 디폴트옵션 초저위험 상품으로의 운용지시 및 리밸런싱을 권유하고, 디폴트옵션은 일부만 먼저 전환하는 방식으로 안내합니다.
+(아래에 이 고객의 연령·투자성향·평가금액·수익률·연금개시·세액공제 잔여한도·관리 사유 표가 붙습니다)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -4776,7 +4737,7 @@
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -4813,7 +4774,7 @@
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>이번 상담에서 오간 대화 기록이 없어요.</t>
+          <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
         </is>
       </c>
       <c r="F111" s="19" t="inlineStr">
@@ -6280,8 +6241,8 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: market:퇴직연금과 부동산 투자 비교 시황 및 자산배분 전략 · fact:퇴직연금과 부동산 투자 비교 · pitch:퇴직연금과 부동산 투자 비교 시 고객 설득 화법
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 상담 화법 「퇴직연금과 부동산 투자 비교 설명 및 설득 화법」 · 시황 자료 「퇴직연금과 부동산 투자 시장 현황 및 비교」 · 운용 상품 자료 「퇴직연금과 부동산 투자 비교」 · 관리 방법론 「퇴직연금과 부동산 투자 비교 판단 기준 및 장단점」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
@@ -6315,8 +6276,8 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>그 질문에 쓸 근거를 지식베이스에서 찾지 못했습니다. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있습니다.
-찾아본 곳: fact:고객 평가금액
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 제도·상품 수치 「고객 평가금액」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>(더미 문구로 LMS 요청한 뒤) 응, 열어줘</t>
+          <t>(문구를 인용해 LMS 요청한 뒤) 응, 열어줘</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
+          <t>발송 화면 딥링크 + 그 문구를 그대로 건넨다 ↔ 문구를 되묻거나 「연계하지 않았다」로 끝난다</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -567,18 +567,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="72" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="20" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="34" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="72" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="I13" s="18" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27" s="9" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I27" s="18" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" hidden="1">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="I37" s="18" t="inlineStr"/>
     </row>
-    <row r="38">
+    <row r="38" hidden="1">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
@@ -2249,7 +2249,7 @@
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="10" t="n"/>
+      <c r="B48" s="9" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
       </c>
@@ -2283,86 +2283,292 @@
     </row>
     <row r="49">
       <c r="A49" s="9" t="n"/>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>8. 세액공제 계산</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H49" s="18" t="inlineStr">
-        <is>
-          <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr"/>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>연간 납입한도가 얼마고 연금저축이랑 어떻게 나눠 쓰는 거야?</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>2026년 3월부터 적용되는 개인형IRP의 연간 납입한도는 연금저축과 DC형 및 기업형IRP의 개인부담금을 모두 합산하여 1,800만원이에요. IRP 단독이 아니라 타행과 타사의 연금저축 납입액까지 포함되므로 실제 납입 여력은 [06-12-151] 화면의 개인부담금 연합회 한도 조회로 확인하고 안내해 드려야 해요. 세액공제 한도의 경우 연금저축만 보유하면 연 600만원이지만 개인형IRP를 포함하면 연 900만원까지 확대되므로, 연금저축만 가진 고객이라면 개인형IRP로 300만원의 추가 공제 여력을 활용하실 수 있어요. 세액공제 한도 900만원과 전체 납입한도 1,800만원은 혼동하기 쉬우니 구분해서 살펴볼 필요가 있어요.</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>1,800만원 + 연금저축·DC 개인부담금 합산 ↔ IRP 단독 한도로 답한다</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
-        <is>
-          <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr"/>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>900만원 넘게 넣으면 그 초과분은 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>2026년 3월 기준으로 세액공제 한도인 900만원을 초과해 납입한 금액은 세제 혜택과 인출 시 유리한 구조로 활용할 수 있어요. 900만원 초과분은 운용 기간 동안 과세이연 혜택을 받을 수 있고, 세액공제를 받지 않은 가입자부담금은 연금수령 시 과세제외로 인출할 수 있어요. 또한 올해 초과 납입분을 내년 세액공제분으로 이월 신청하는 이연 공제도 활용할 수 있어요. 다만 세액공제를 받지 않은 금액이 과세제외로 인출되려면 미공제 금액 등록이 선행되어야 하니 단말에서 이 부분을 먼저 챙겨 보셔야 해요. 이연 공제의 구체적인 실무 절차나 서류에 대해서는 제가 가진 자료로는 확인이 어려워요. 고객에게는 "세액공제 한도인 900만원을 초과해서 납입하시는 금액도 운용 기간 동안 과세이연 혜택을 받으실 수 있고, 공제받지 않은 금액은 나중에 연금으로 받으실 때 세금을 내지 않고 먼저 인출하실 수 있어요. 또한 올해 초과 납입하신 분량은 내년 세액공제분으로 이월해서 신청하실 수도 있습니다"라고 안내해 보세요.</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>과세이연 + 인출 시 과세제외 + 이연 공제 신청 ↔ 「공제 안 된다」로만 끝낸다</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>위험자산 70% 한도가 뭐고 넘으면 어떻게 해?</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>위험자산 70% 한도는 근로자퇴직급여보장법 시행령에 따라 주식형이나 주식혼합형 펀드 같은 위험자산을 평가금액의 70% 이내에서만 운용할 수 있는 규정이에요. 2026년 6월 기준 자료를 보면 전액 주식형 펀드로만 운용하는 것은 불가능하며, DB형의 경우에는 사용자별 전체 적립금 기준 70% 이내로 제한돼요. 만약 한도를 초과하더라도 별도의 페널티는 없고, 초과된 금액을 정기예금 같은 안전자산으로 교체매매하거나 추가입금을 한 뒤 안전자산으로 운용지시를 내려 해소하면 돼요. 세부적인 위반 현황은 확인 화면 04-12-354의 컴플라이언스 위반점검 현황조회에서 조회구분을 위험자산투자한도위반으로 설정해 확인할 수 있어요. 주식형 ETF의 포함 여부와 관련해서는 영업점 핫팁과 본부 자료의 언급이 달라 법령이나 감독규정 확인 전까지 확정해 안내하기 어려우니 이 점은 참고해 주세요.</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>한도 범위 + 초과 시 조치 + 확인 화면 ↔ 조치를 빼고 한도만 말한다</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>TDF나 디폴트옵션은 70% 한도 예외라던데 맞아?</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>TDF나 디폴트옵션은 금감원장이 정한 기준을 충족할 때 위험자산 70% 한도의 예외로 적립금의 100%까지 운용할 수 있어요. 2026년 3~7월 자료를 기준으로 보면, 당행 퇴직연금에서 운용 가능한 TDF는 전부 적격 TDF에 해당해요. 다만 채권형이나 채권혼합형 ETF 100% 예외 같은 범위는 본부 자료에 없어서 지금 확인해 드리기 어려워요.</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>적격TDF·디폴트옵션 100% 운용 가능 ↔ 채권형 ETF 의 ⚠ 까지 단정한다</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>디폴트옵션이 뭔지 고객한테 설명하려는데 위험등급이랑 적용되는 경우 알려줘</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>디폴트옵션 설명 및 적용되는 경우에 대해서는 제가 가진 자료로는 확인이 어려워요. 대신 참고하실 수 있도록 2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션) 목록과 포트폴리오 현황을 안내해 드릴게요.
+- 지켜드림 — 초저위험 / 시중은행 정기예금 중심 포트폴리오 (포트폴리오 1년 수익률 2.13%)
+- 알파드림 — 저위험 / 정기예금 70, TDF 30 포트폴리오 (포트폴리오 1년 수익률 4.23%)
+- 알파드림 II — 저위험 / 정기예금 50, TDF 50 포트폴리오 (포트폴리오 1년 수익률 8.56%)
+- 알파드림 III — 저위험 / 정기예금·보험사 GIC 70, TDF 30 포트폴리오 (포트폴리오 1년 수익률 5.86%)
+- 뿔려드림 — 중위험 / 정기예금 30, TDF 70 포트폴리오 (포트폴리오 1년 수익률 13.95%)
+- 뿔려드림 II — 중위험 / TIF와 EMP 자산배분형 포트폴리오 (포트폴리오 1년 수익률 15.04%)
+- 뿔려드림 III — 중위험 / 이율보증형보험 20, 자산배분안정형 80 포트폴리오 (포트폴리오 1년 수익률 10.59%)
+- 모두드림 — 고위험 / TDF 100 투자 포트폴리오 (포트폴리오 1년 수익률 20.63%)
+- 모두드림 II — 고위험 / 액티브 TDF 100 포트폴리오 (포트폴리오 1년 수익률 19.19%)
+- 모두드림 III — 고위험 / 자산배분형 BF (BF 1년 수익률 15.19%)
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>정의 + 위험등급 4단계 + 적용 3케이스 ↔ 등급만 나열한다</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>IRP에서 살 수 있는 상품이 뭐뭐야?</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>3분류·5종 정의 ↔ 상품명을 나열해 권유처럼 읽힌다(§8)</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>8. 세액공제 계산</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E57" s="18" t="inlineStr">
         <is>
           <t>현금을 더 납입하는 경우를 기준으로 안내드리면, 이 고객의 개인형IRP 계좌 추가 납입액 300만원에 대해 더 돌려받는 환급액은 없다. 
 이 고객은 당해 납입액이 0원이고 세액공제 한도 900만원과 잔여한도가 0원이라 추가 공제 대상이 없기 때문이다. 
@@ -2370,35 +2576,35 @@
 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G51" s="18" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
         </is>
       </c>
-      <c r="I51" s="18" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E58" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
@@ -2441,35 +2647,35 @@
 총급여 5,500만원 이하(16.5%) 적용 시, 8천만원 전액을 전환하면 추가 공제 대상 300만원에 대해 최대 495,000원의 환급액이 늘어나게 돼요. 8천만원보다 적은 일부 금액을 옮기더라도 3,000만원까지는 전환액의 10%가 추가 공제 대상에 더해지는 방식으로 계산되니 이 점을 참고해 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F58" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
         </is>
       </c>
-      <c r="I52" s="18" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="n"/>
-      <c r="B53" s="9" t="n"/>
-      <c r="C53" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금을 8천만원 전부 전환할 때 세액공제 환급 예상액을 묻는 질문에는 개인형IRP 계좌 추가 납입인 현금 납입과 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 축으로 다루는 게 핵심이에요. 
@@ -2494,35 +2700,35 @@
 · 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="F59" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G53" s="18" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
-      <c r="I53" s="18" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
+      <c r="E60" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 총급여 5,500만원 초과 구간인 고객에게는 ISA 만기자금 중 일부를 개인형IRP 계좌로 전환할 때의 세액공제 효과를 금액별로 짚어주는 게 핵심이에요. 앞서 말씀드린 8,000만원 전액 전환 시의 추가 공제 대상 300만원과 늘어나는 환급액 396,000원 외에, 질문하신 일부 금액 전환 시에는 전환액 1,000만원일 때 추가 공제 대상 100만원과 전환액 2,000만원일 때 추가 공제 대상 200만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액들은 현금을 더 납입하는 경우와 별개로 더해지는 몫이니, 두 한도를 같은 안에서 저울질하지 않고 각각 안내해 주세요.
@@ -2537,39 +2743,39 @@
 총급여 5,500만원 초과 구간인 송도윤 고객에게는 ISA 만기자금 1억 2,000만원 중 일부인 1억 2,000만원을 개인형IRP 계좌로 전환할 때 추가 공제 대상 300만원과 적용 공제율 13.2%를 반영한 환급 예상액 396,000원을 안내하는 것이 핵심이에요. 앞서 말씀드린 현금을 더 납입하는 경우와는 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않아야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H54" s="18" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>원래 질문(300만원)과 고른 갈래를 합쳐 13.2% 로 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
         </is>
       </c>
-      <c r="I54" s="18" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E61" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 김서연 고객의 총급여가 5,500만원 이하인 경우라면 개인형IRP 계좌 추가 납입과 ISA 만기자금 전환 각각에 따른 세액공제 금액을 나누어 짚어 주는 게 핵심이에요. 현금을 추가 납입할 때는 500만원을 개인형IRP 계좌에 넣으면 총급여 5,500만원 이하 기준 16.5%가 적용되어 825,000원이 늘어난 1,485,000원의 환급을 예상할 수 있어요. ISA 만기자금 8,000만원 중 일부인 1,000만원을 전환할 때는 100만원이 추가 공제 대상이 되고, 2,000만원을 전환하면 200만원, 3,000만원 이상을 전환하면 상한인 300만원이 추가 공제 대상이 되어 총급여 5,500만원 이하 기준 16.5%를 적용하면 495,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
@@ -2580,142 +2786,142 @@
 만기자금 전환은 기존 현금 추가 납입과 별개의 한도로 운영되는 몫이라 서로 다른 한도 안에서 저울질하지 않고 더해지는 구조예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>같은 자리에서 **16.5%** 로 갈린다(300만원이면 495,000원) ↔ 13.2% 로 답하거나 원장 구간이 이긴다고 직원 말을 무시한다</t>
         </is>
       </c>
-      <c r="I55" s="18" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="n"/>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E62" s="18" t="inlineStr">
         <is>
           <t>오늘 날짜는 2026년 9월 29일 월요일이고 2026년 연말까지는 오늘을 세지 않고 93일 남았어요. 세액공제를 받으려면 올해 12월 31일까지 납입해야 해요.</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="F62" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G56" s="18" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
-      <c r="I56" s="18" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr"/>
+    </row>
+    <row r="63" hidden="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="16" t="n">
+        <v>62</v>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>이 고객 잔액은 언제 기준 값이야?</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E63" s="18" t="inlineStr">
         <is>
           <t>해당 고객의 잔액 기준 시점에 대한 자료는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G57" s="18" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>300 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 넣으면 적용받는 공제율에 따라 환급액이 달라져요. 총급여 5,500만원 이하인 경우 16.5%를 적용하여 개인형IRP 계좌 추가 납입으로 495,000원의 환급을 받게 되고, 총급여 5,500만원 초과인 경우 13.2%를 적용하여 개인형IRP 계좌 추가 납입으로 396,000원의 환급을 받게 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G58" s="18" t="inlineStr">
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
         </is>
       </c>
-      <c r="C59" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="C65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
 연금 개시 신청 업무는 2단계로 처리해야 하니 [06-12-622] 세액 미공제 한도 등록을 먼저 거친 뒤 [02-12-221] 연금지급 등록을 진행하는 게 핵심이에요. 첫 단계의 준비서류는 연금보험료 등 소득·세액 공제 확인서이며 서류가 없을 때는 국민지갑에서 발급할 수 있어요. 본격적인 개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 먼저 확인해야 하며 연금개시 후에는 이전이 불가능해요. 또한 처리 중에 자동이체 금액이 입금되고 있거나 보유상품변경이 진행 중이면 거래가 불가하니 이 점을 주의해 주세요.
@@ -2723,103 +2929,103 @@
 연금 개시를 신청하는 고객에게는 2단계로 처리하는 것이 핵심이에요. 먼저 [06-12-622] 세액 미공제 한도 등록을 진행하고, 이어서 [02-12-221] 연금지급 등록을 처리해요. 세액 미공제 한도 등록 시에는 「연금보험료 등 소득·세액 공제 확인서」를 준비해야 하며, 서류가 없다면 국민지갑에서 발급할 수 있어요. 연금개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 꼭 확인해야 해요. 아울러 처리 중 자동이체 금액이 입금 중이거나 보유상품변경이 진행 중이면 거래가 불가하다는 점을 미리 안내드릴게요.</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>어떤 처리 채널로 진행하시나요?
 · 비대면
 · 전문 송수신(일반)</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>과세이연 등록을 처리할 때는 과세이연정보(통산정보) 등록·조회와 과세이연계좌신고서 출력을 할 수 있는 [04-12-648] 과세이연정보관리 화면을 활용하면 돼요. 이어서 [01-12-213] 입금/입금예약 화면에서 거래구분을 과세이연/계약이전입금으로 선택해 입금을 진행하면 과세이연 등록 절차를 처리할 수 있어요.</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
 만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거친 뒤, [75-08-110] 화면을 통해 예약변경 거래를 처리하면 돼요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 현금성자산에 머무르므로, 저축은행 상품처럼 만기 안내와 예약변경이 중요해요. 특히 만기 후 6주(만기일부터 4주간 지시 없으면 안내 후 2주 뒤 적용)의 유예 구조가 있으나 만기 4주 시점에 본부 안내가 나가기 때문에, 접촉 가능 구간인 만기 1개월 전부터 만기 후 4주 사이에 서둘러 대응해야 해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 하는 방식을 활용할 수 있어요.
@@ -2827,105 +3033,250 @@
 만기상품 예약변경은 먼저 사용계획이 있는 자금인지 확인하고 처리하는 게 핵심이에요. 정기예금은 만기에 자동 재예치되지 않아 방치되면 현금성자산에 머물게 되니 [75-08-110] 화면에서 만기상품 예약변경으로 처리해야 해요. 처리 순서는 익월 금리가 월 단위로 확정되므로 익월 금리 확인을 선행한 뒤 만기 1개월 전부터 예약변경을 걸고, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하는 방식이에요. 주의할 점은 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 먼저 걸러내야 하며, 디폴트옵션 미등록 고객은 사전지정 등록과 만기 예약변경을 함께 처리해야 한다는 점이에요.</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 절차와 화면번호는 [75-08-110] 화면을 통해 처리해요. 원리금보장상품 만기가 다가오는데 디폴트옵션 미등록인 고객은 별도 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 디폴트옵션 사전지정 등록과 만기 예약변경으로 나누어 처리할 수 있어요. 만기 예약거래는 만기 한 달 전부터 가능하며, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하면 돼요. 처리는 디폴트옵션(저위험이상) 사전지정 등록과 만기 예약변경 두 갈래로 진행돼요.</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>추가납입 권유하기 전에 뭘 먼저 확인하고 들어가야 해?</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>입금이력·한도에 더해 **연금개시 여부**를 먼저 ↔ 연금개시 확인이 빠진다(§8 관리대장)</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>수수료 불만 들었는데 상담 전에 뭘 준비해야 해?</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>[04-12-613] 수수료 예상조회로 현재·전환 후를 숫자로 ↔ 화법만 주고 준비를 뺀다</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>정기예금 중도해지하면 손실이 얼마인지 어떻게 확인해?</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>계산기로 사전 산출 + 매도 우선순위 4단계 ↔ 「해지하면 손해」로만 끝낸다</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>퇴직소득세는 어떻게 계산해?</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>[02-12-221] 「계산」 3단계 + 지방소득세 10% 별도 ↔ 별도분을 뺀다</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>타사 연금 납입정보는 어떻게 확인해?</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>전자증명서 출력 또는 집중조회(동의서 징구 필수) ↔ 동의서 징구를 뺀다</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
         </is>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="C75" s="16" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr">
+      <c r="E75" s="18" t="inlineStr">
         <is>
           <t>IRP 계좌 해지 업무는 [02-12-220] 퇴직연금 지급 화면에서 진행해요. 해당 화면은 해지, 계좌이체, 미지급금 출금, 지연보상금 지급을 처리하는 화면이에요. 단일 자료에만 등장하는 내용이라 다른 화면 번호는 안내되지 않으니 참고해 주세요.</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F75" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G64" s="18" t="inlineStr">
+      <c r="G75" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="H75" s="18" t="inlineStr">
         <is>
           <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="n"/>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="16" t="n">
-        <v>64</v>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="I75" s="18" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
         </is>
       </c>
-      <c r="E65" s="18" t="inlineStr">
+      <c r="E76" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금 입금은 입금/입금예약·입금명부 등록 화면인 [01-12-213]번 화면에서 처리하면 돼요. 이 화면은 지급, 과세이연, 연금 관련 업무를 처리하는 곳이며 거래구분에서 ISA 만기자금 입금을 선택할 수 있어요. [01-12-213] 관련 내용은 현재 준비된 자료를 바탕으로 안내해 드렸어요.
@@ -2935,312 +3286,486 @@
 ISA 만기자금 입금은 [01-12-213] 입금/입금예약 화면에서 처리하면 돼요. 이 화면은 입금, 입금예약, 그리고 입금명부 등록을 처리하는 화면이에요. 거래구분을 선택할 때 ISA 만기자금 입금을 고르면 입금가능금액을 자동으로 조회할 수 있어요. 그 외에 과세이연이나 계약이전입금 거래구분도 이 화면에서 함께 다루고 있어요.</t>
         </is>
       </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="F76" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G65" s="18" t="inlineStr">
+      <c r="G76" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
         </is>
       </c>
-      <c r="I65" s="18" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="I76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
+      <c r="E77" s="18" t="inlineStr">
         <is>
           <t>포트폴리오 운용현황 조회를 위한 화면번호는 06-12-604이며, 해당 화면은 연금 로보어드바이저 운용현황 조회를 처리하는 화면이에요. AI투자일임 및 케이봇쌤과 관련된 거래를 확인할 때 활용할 수 있어요. [06-12-604]</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G66" s="18" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="I77" s="18" t="inlineStr"/>
+    </row>
+    <row r="78" hidden="1">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E78" s="18" t="inlineStr">
         <is>
           <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
 찾아본 곳: 단말 화면번호 「타행 계좌 잔액 조회」 · 업무 처리 절차 「타행 계좌 잔액 조회 업무 처리 순서」 · 단말 화면번호 「타행 계좌 잔액 조회 화면번호」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="G78" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
-      <c r="I67" s="18" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="I78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>적립금이랑 수익률 조회는 몇 번 화면이야?</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>[04-12-642] + 그 화면이 무엇을 하는 화면인지 ↔ 번호만 던진다</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>수수료 예상조회 화면번호 알려줘</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr"/>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>[04-12-613] ↔ 수수료율표(제도 수치)로 답해 화면번호를 안 준다</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>고객 거래내역은 어느 화면에서 봐?</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr"/>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>거래내역 조회 화면번호 ↔ 적립금 조회 화면을 준다</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
         </is>
       </c>
-      <c r="C68" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="C82" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>고객이 스타뱅킹에서 직접 추가납입할 때는 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로로 안내해 드려요. 인터넷뱅킹을 이용할 때는 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로로 들어가서 진행할 수 있어요. 이용 시간 예외로 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지 가능하니 이 시간대에 처리하도록 미리 짚어드릴게요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="n"/>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>개인형IRP 연금수령 신청은 KB스타뱅킹의 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 수령관리 &gt; 연금 수령관리 – 개인형IRP 연금수령 신청 경로와 인터넷뱅킹의 KB퇴직연금 &gt; 개인고객 &gt; 연금수령신청/조회 &gt; 개인형IRP 연금수령 신청 경로를 통해 고객이 직접 진행할 수 있어요. 
 이용 가능한 채널은 개인형IRP에 한하며, ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="n"/>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>우리 IRP에서도 ETF 매매를 할 수 있으니 고객이 직접 진행할 때 안내할 경로를 짚어드릴게요. KB스타뱅킹을 이용하는 경우 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, ETF 매매하기 순으로 이동하면 되고, 인터넷뱅킹을 이용하는 경우 KB퇴직연금, 개인고객, 퇴직연금 ETF, ETF 매매하기 경로로 접근하면 돼요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F70" s="13" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="n"/>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>고객이 앱에서 자기 수익률이랑 보유상품 보려면 어느 메뉴야?</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>채널별 메뉴 경로 ↔ 직원 단말 화면번호를 알려준다(셋을 가른 이유 — §3)</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>운용상품 찾기 경로 + 그 채널에서 되는지 ↔ 상품 목록을 늘어놓는다</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>고객이 추가입금 예약을 직접 걸 수 있어?</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>부담금입금/예약 경로 ↔ 직원이 단말에서 하는 절차를 고객에게 시킨다</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
         </is>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="C88" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
+      <c r="E88" s="18" t="inlineStr">
         <is>
           <t>적립금이 1천만원 미만이더라도 이 고객은 원리금보장·현금성 자산 비중이 90%로 편중되어 있고 디폴트옵션이 미설정되어 있어 관리 대상에 해당해요. 현재 고유계정대와 예금을 포함한 원리금보장·현금성 자산 비중이 높고 키움 더드림 단기채 수익률이 -6.4%를 기록하면서 전체 운용수익률이 -1.8%에 머물러 있는 상태예요. 이는 동연령 평균 수익률 10.2%와 비교해 저조한 수준이며, 위험자산 한도 70% 중 위험자산 비중이 0%로 나타나 포트폴리오 조정이 필요한 상태예요.</t>
         </is>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F88" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="G71" s="18" t="inlineStr">
+      <c r="G88" s="18" t="inlineStr">
         <is>
           <t>김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H71" s="18" t="inlineStr">
+      <c r="H88" s="18" t="inlineStr">
         <is>
           <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
         </is>
       </c>
-      <c r="I71" s="18" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="n"/>
-      <c r="B72" s="9" t="n"/>
-      <c r="C72" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="I88" s="18" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E89" s="18" t="inlineStr">
         <is>
           <t>현금성자산이 많다고 해서 무조건 방치 자금으로 볼 수는 없어요. 현금성자산이 일정기간(1개월 이상) 금액변동 없이 유지 중이고 [04-12-644] 퇴직연금 거래내역조회 시 입금 사유가 '교체매매'나 '연금지급' 사유가 아닌 경우 미운용중인 자산이 있다고 안내해 보세요. 연금지급이나 교체매매 대기 중인 정상 자금일 수도 있으므로, 고객에게 접촉하기 전에 사용계획 자금인지 방치 자금인지 먼저 가르는 것이 판단 기준이에요. 상담 용어: "고유계정대" 대신 "현금성자산", "운용지시가 되지 않는 자산" 사용 (고객에게 생소한 용어 금지).</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="F89" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G72" s="18" t="inlineStr">
+      <c r="G89" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H72" s="18" t="inlineStr">
+      <c r="H89" s="18" t="inlineStr">
         <is>
           <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
         </is>
       </c>
-      <c r="I72" s="18" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="I89" s="18" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr">
+      <c r="E90" s="18" t="inlineStr">
         <is>
           <t>어떤 이탈 위험 유형을 기준으로 보시겠습니까?
 · 자산 편중형
 · 투자 목적형</t>
         </is>
       </c>
-      <c r="F73" s="21" t="inlineStr">
+      <c r="F90" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G73" s="18" t="inlineStr">
+      <c r="G90" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H73" s="18" t="inlineStr">
+      <c r="H90" s="18" t="inlineStr">
         <is>
           <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
         </is>
       </c>
-      <c r="I73" s="18" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="I90" s="18" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E91" s="18" t="inlineStr">
         <is>
           <t>어떤 목적의 대상 선정 기준인가요?
 · TM 콜 대상
@@ -3248,142 +3773,142 @@
 · 이탈위험 선별</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="F91" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G74" s="18" t="inlineStr">
+      <c r="G91" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="H91" s="18" t="inlineStr">
         <is>
           <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
-      <c r="I74" s="18" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="I91" s="18" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="E92" s="18" t="inlineStr">
         <is>
           <t>오늘 우선 관리해야 할 대상은 총 11명이며, 각 고객의 현황에 따른 선정 요건 순서대로 확인해야 해요. 윤가영 고객은 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월에 해당해요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월이며, 최서윤 고객은 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원이 확인되며, 이수민 고객은 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원이 선정 요 이에요. 박정호 고객은 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원이며, 김현수는 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시이며, 김서연 고객은 ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원이에요. 한지우 고객은 ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
-      <c r="F75" s="19" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G75" s="18" t="inlineStr">
+      <c r="G92" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H75" s="18" t="inlineStr">
+      <c r="H92" s="18" t="inlineStr">
         <is>
           <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
         </is>
       </c>
-      <c r="I75" s="18" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="I92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E93" s="18" t="inlineStr">
         <is>
           <t>만기 안내 전화할 때는 본부 공식 지침은 아니지만 영업점 현장에서 관찰된 방식을 활용할 수 있어요. 비율 대신 원 단위 금액으로 제시하는 것이 반복되는 성공 패턴이며, 계산이 상담의 성패를 가른다는 점을 참고해 보세요. 중도해지이율이 수수료율 합계보다 낮으면 원금에서 차감 지급된다는 점이나 지급까지 3영업일이 소요된다는 사실, 그리고 중도인출 신청액이 세전이라는 점을 미리 안내하지 않으면 민원으로 돌아올 수 있으니 사전에 고지하는 것이 중요해요. 만기 안내 전화 과정에서 수수료로 원금이 깨질 수 있는 부분이나 현금화 지연 가능성 같은 필수 고지 사항을 빠뜨리지 않도록 유의하세요.</t>
         </is>
       </c>
-      <c r="F76" s="19" t="inlineStr">
+      <c r="F93" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
+      <c r="G93" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H93" s="18" t="inlineStr">
         <is>
           <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
-      <c r="I76" s="18" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Ⅲ. 상담 중 — 무엇을 어떻게 말하나</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="I93" s="18" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Ⅲ. 상담 중 — 말하기와 이어지는 대화</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>13. 상담 화법·반론 대응</t>
         </is>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="C94" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>손실만 나고 해지하겠다는 고객에게는 보유 포트폴리오 유형으로 화법을 분기하여, 저희가 세심하게 관리를 해드렸어야 했는데 죄송합니다라고 먼저 관리 미흡을 사과하고 그 자리에서 매도와 재추천이라는 액션을 약속하는 방식으로 접근해야 해요. 본부 교육 영상에서는 공시 순위를 앞세우지 않고 이처럼 사과와 원인 규명에 이어 즉시 리밸런싱을 3단으로 밟아나가는 방식을 권하고 있어요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속해서는 안 되며, 근거는 수익률 예측이 아니라 운용 여건의 차이에 두어야 해요. 또한 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 미리 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 상담 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>해지 만류 화법 — 사과 → 원인 규명 → 리밸런싱 3단 + 고객에게 할 대사 ↔ 절차 카드 한 장으로 「준비된 자료에 없어요」(gap 35 재현)</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="n"/>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>● 이수민
 "예금만 해서 관리 필요 없어요"라는 고객에게는 금리 갈아타기가 곧 관리라는 논리로 접근하는 게 핵심이에요. 예금과 같은 원리금보장상품도 꾸준한 관리가 필요한 대상이라는 점을 짚어주고, 매월 금리가 가장 좋은 상품을 제공하고 있다는 점을 설명해 주세요. 고객에게는 이렇게 안내해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다." 이미 안정적으로 잘 운용하고 있다는 점을 먼저 인정한 뒤, 같은 안전성인 예금자보호 테두리 안에서 금리를 올려주는 제안으로 자연스럽게 대화를 이어가면 됩니다.
@@ -3391,35 +3916,35 @@
 예금만으로도 충분하지 않냐고 묻는 고객에게는 예금 같은 원리금보장상품도 매월 금리가 유리한 상품으로 갈아타는 과정이 곧 관리라는 점을 짚어주는 것이 핵심이에요. 당행은 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있다는 점을 설명해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내하시면 돼요. 이 과정에서 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 '고유계정대' 같은 용어 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 표현을 사용해 주세요. 아울러 연금지급 대기나 교체매매 등으로 사용 계획이 있는 자금인지 먼저 확인하고 접근하시는 것이 안전해요.</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>이수민 175926-3048171·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="n"/>
-      <c r="B79" s="9" t="n"/>
-      <c r="C79" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="I95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>IRP 중도인출 가능 여부를 묻는 고객에게는 무주택자의 주택 구입이나 전세금 및 임차보증금이 필요한 경우 등 법적 요건을 충족하면 언제든 중도인출이 가능하다고 안내하는 것이 핵심이에요. 55세까지 아예 못 뺀다는 고객의 우려를 법정 사유로 먼저 해소해야 해요. 
 그후 고객이 자유로운 입출금을 원하며 가입을 망설일 때는 무조건 돈 전부를 넣으라는 것이 아니라고 요구 수준을 낮추어 짚어 주세요. 한 가지 음식만 먹으면 영양이 부족하듯 자산을 골고루 나누어 안정성과 수익성, 절세 효과를 균형 있게 챙겨야 한다는 점을 설명하는 것이 효과적이에요. 해지에 대한 우려로 큰 혜택을 놓치는 것은 아쉽다는 점을 강조하면서 다음 대사를 활용해 보세요. 
@@ -3427,35 +3952,35 @@
 "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="n"/>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>증권사 수수료 무료 발언으로 이탈을 우려하는 고객에게는 면제 조건을 먼저 제시한 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 
 만 55세 이후 연금개시를 하시면 수수료가 0원이 되며, 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되므로 이 조건을 먼저 짚어주세요. 
@@ -3466,105 +3991,105 @@
 대화 중 "IRP 수수료는 적립금 규모와 가입 방식에 따라 다릅니다. 우리 고객님 조건에서는 오히려 국민은행이 더 저렴한 경우가 많습니다. 실제로 고객님 상황과 적립금 기준으로 한번 같이 비교해드릴게요."라는 멘트를 활용해 고객의 상황을 구체적으로 비교해 보면서 대응을 이어가세요.</t>
         </is>
       </c>
-      <c r="F80" s="14" t="inlineStr">
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="n"/>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>디폴트옵션에 거부반응을 보이는 고객에게는 전량 전환을 밀지 않고 일부만 먼저 전환하고 되돌릴 수 있다는 가역성을 제시하는 게 핵심이에요. 
 전부 바꾸지 않고 일부만 먼저 운용해 보고 원할 때 되돌릴 수 있다는 점을 안내해 심리적 부담을 낮추는 방식으로 접근해야 해요. 
 이용하려는 자금이 연금지급 대기나 교체매매 중에 있는 등 사용계획이 있는 자금이라면 먼저 걸러내야 하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr">
+      <c r="F98" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="n"/>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="I98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n"/>
+      <c r="C99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>현금성자산 방치 고객이 금액이 적다는 이유로 운용을 미루려 할 때는, 사용계획이 있는 자금인지 먼저 확인하고 수익률 관점에서의 기회비용을 짚어주는 게 핵심이에요. 
 고유계정대 같은 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰고, 연금지급 대기나 교체매매 등 사용계획이 있는 자금인지 먼저 걸러내야 해요. 그런 자금이 아니라면 현재 미운용 중인 자산은 금리가 낮아 방치할수록 손해라는 점을 자연스럽게 설명해 보세요. 
 고객에게는 "고객님, 금액이 작아 보이셔도 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준이라서요. 금리가 높은 저축은행 정기예금이나 펀드 같은 상품으로 운용하시면 향후에 수령하시는 퇴직연금 금액이 달라지니 지금 재정비하시는 게 좋아요"라고 안내해 드릴 수 있어요.</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F99" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="n"/>
-      <c r="B83" s="9" t="n"/>
-      <c r="C83" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="I99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
         <is>
           <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>● 최서윤
 성과저조나 판매중단 펀드를 보유한 고객이 손실 중인 상태에서 교체를 망설일 때는 고객의 속상한 심정을 먼저 인정하는 공감의 자세로 접근해야 해요. 
@@ -3574,68 +4099,68 @@
 성과저조·판매중단 펀드 보유 고객이 손실 상황에서 불만을 제기할 때는 감정 공감을 먼저 건네며 접근하는 것이 핵심이에요. "속상하시겠지만"이라는 감정 인정을 반드시 앞세우고, 판매중단 사유와 그 결과로 운용사 관심도가 하락해 향후 수익률 개선이 어려울 수 있다는 점을 설명한 뒤 교체를 권해야 해요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되고, 수익률 예측이 아니라 운용 여건의 차이를 근거로 다가가야 해요. 고객에게는 "많이 속상하시겠지만, 고객님 안정적인 퇴직연금 자산관리를 위해 최근 수익률 등을 비교해 보시고 상대적으로 성과가 우수한 상품으로 변경해 보시는 건 어떠신가요?"라고 안내해 보세요. 상담 과정에서 사용계획이 있는 자금이라면 먼저 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 해요.</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
+      <c r="F100" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="n"/>
-      <c r="B84" s="9" t="n"/>
-      <c r="C84" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
         <is>
           <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>증권사가 ETF 종류가 훨씬 많다는 고객에게는 고객의 반론을 먼저 인정하면서 10~20년 장기 운용을 해야 하는 연금자산에서는 상품의 개수보다 어떤 상품을 선택해서 운용하느냐가 더 중요하다는 점으로 설명을 이끌어가는 게 핵심이에요. 증권사는 8~900개의 다양한 테마형, 섹터형 ETF를 제공하고 있지만, 선택의 폭이 넓어지면 트렌드에 맞춰 관리해야 하고 그에 따른 피로도와 결정장애가 생기기 마련이라는 점을 짚어주세요. 퇴직연금은 중장기 안정적인 성과를 추구해야 하는 장기자산이므로, 국민은행은 이런 자산의 특성과 시장상황 등을 고려해 엄선한 ETF만을 선별 제공하고 있다는 점을 안내할 수 있어요. 현재 당행에서 판매 중인 ETF는 총 193종(국내 90종, 해외 103종)으로 계속 늘려가고 있으며, 고객님의 선택 폭을 넓히기 위해 중복테마 및 거래가 활발하지 않은 ETF를 제외하고 상품 라인업을 최대 400개까지 확대할 예정이라는 사실을 함께 활용해 보세요.</t>
         </is>
       </c>
-      <c r="F84" s="13" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="n"/>
-      <c r="B85" s="9" t="n"/>
-      <c r="C85" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="I101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>● 정민석
 예금만 하겠다는 고객에게는 원리금보장상품도 관리가 필요하다는 점을 짚어주고 같은 안전성 안에서 금리를 올려주는 제안으로 접근하는 게 핵심이에요. 
@@ -3648,72 +4173,275 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="F102" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="n"/>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="I102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
         <is>
           <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>원금 손실을 우려하는 고객에게는 연금 자산의 투자 성격과 기간을 들어 위험의 의미를 다시 정의하며 접근하는 것이 핵심이에요. 먼저 주식이 위험하다는 고객의 의견을 수용하면서, 여기서 말하는 위험이 손실이 아니라 기간이 길어질수록 줄어드는 변동성임을 짚어주세요. 당장 1~2년 뒤에 쓸 돈이 아니라 은퇴 후 30년을 운용해야 할 자산이라는 점을 설명하고, 연금이야말로 기간이 길어 30년이면 손실 확률이 0%에 수렴하는 특성을 지닌다는 점을 안내할 수 있어요. 또한 '위험'이라는 단어가 주는 부담감을 줄이기 위해 30년이라는 장기 투자 기간과 소규모 납입금의 특성을 들어 오히려 연금투자가 변동성을 감당할 수 있는 자금 성격임을 설명하는 방식을 활용해 보세요. 다만 사용 계획이 있는 자금이나 연금지급 대기 및 교체매매 중인 자금은 먼저 걸러내야 하며, 고객에게 생소할 수 있는 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F86" s="13" t="inlineStr">
+      <c r="F103" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="n"/>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '생각 좀 해볼게요' 하고 미루는데 뭐라고 하지?</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>시간의 정당성 인정 + 자가확인 경로 ↔ 재촉하거나 그냥 끝낸다</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '지금 쓸 돈도 없어요' 하는데 뭐라고 해?</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>자유납입으로 부담 제거 ↔ 한도를 채우라고 밀어붙인다</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '나중에 돈 못 빼는 거 아니에요?' 하는데 뭐라고 설명하지?</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>법정 사유 + 균형 비유 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '회사에서 알아서 해주는 거 아니냐'고 하는데?</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>「가입보다 관리」로 논점 이동 ↔ 제도 설명만 하고 할 말이 없다</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '직접 관리하기 귀찮다'고 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>자동화 3종(자동이체·자동매수·디폴트옵션) ↔ 디폴트옵션 하나만 말한다</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>고객이 '수익률은 다른 은행이 더 좋던데요' 하면 뭐라고 답해?</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr"/>
+      <c r="F109" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>공시 근거 + 장기 관리 약속 ↔ 근거 없이 우리가 낫다고 말한다</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>중립적 용건 오프너 ↔ 바로 상품 권유로 들어간다</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
         </is>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="C111" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
-      <c r="E87" s="18" t="inlineStr">
+      <c r="E111" s="18" t="inlineStr">
         <is>
           <t>이 고객에게는 적합성 확인 결과 허용된 상품 범위 안에서만 상품을 안내해야 해요. 현재 고객의 투자성향은 안정추구형이며, 적합성 허용 상한은 낮은위험으로 이 등급까지의 상품만 안내할 수 있어요. 
 안내할 수 있는 상품은 다음과 같아요.
@@ -3726,35 +4454,35 @@
 반면 KB 글로벌채권인덱스 C-P, KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 중립형 MP, KB 성장형 MP, KB 글로벌리츠 ETF는 상품 위험등급이 허용 상한인 낮은위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F87" s="20" t="inlineStr">
+      <c r="F111" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G87" s="18" t="inlineStr">
+      <c r="G111" s="18" t="inlineStr">
         <is>
           <t>보수 성향 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H87" s="18" t="inlineStr">
+      <c r="H111" s="18" t="inlineStr">
         <is>
           <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
         </is>
       </c>
-      <c r="I87" s="18" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="n"/>
-      <c r="B88" s="9" t="n"/>
-      <c r="C88" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="I111" s="18" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="16" t="n">
+        <v>111</v>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>왜 이 상품은 목록에서 빠진 거야?</t>
         </is>
       </c>
-      <c r="E88" s="18" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr">
         <is>
           <t>이 고객에게 안내할 수 없는 상품이 목록에서 빠진 이유는 고객의 투자성향이 안정추구형이라 위험등급 허용 상한이 낮은위험으로 정해져 있기 때문이에요. 앞서 말씀드린 안내할 수 없는 상품들은 상품 자체의 위험등급이 고객의 허용 상한보다 높아 제외되었으며, 구체적인 내용은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
@@ -3766,39 +4494,39 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F88" s="23" t="inlineStr">
+      <c r="F112" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G88" s="18" t="inlineStr">
+      <c r="G112" s="18" t="inlineStr">
         <is>
           <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H88" s="18" t="inlineStr">
+      <c r="H112" s="18" t="inlineStr">
         <is>
           <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
         </is>
       </c>
-      <c r="I88" s="18" t="inlineStr">
+      <c r="I112" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="9" t="n"/>
-      <c r="B89" s="9" t="n"/>
-      <c r="C89" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="D89" s="17" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="16" t="n">
+        <v>112</v>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
         <is>
           <t>이 고객한테는 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E89" s="18" t="inlineStr">
+      <c r="E113" s="18" t="inlineStr">
         <is>
           <t>공격투자형인 이 고객에게는 높은위험 등급까지의 상품만 안내할 수 있고, 허용 상한이 높은위험이라 카탈로그 전부가 범위 안이다. 다만 무엇을 권유할지는 직원이 판단해야 하므로, 안내할 수 있는 상품 목록을 확인하고 적합성 확인 결과이지 투자권유가 아니라는 점을 염두에 두어야 해요. 안내할 수 없는 상품은 없어요. 안내할 수 있는 상품 12종은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
@@ -3816,35 +4544,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F89" s="21" t="inlineStr">
+      <c r="F113" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본</t>
         </is>
       </c>
-      <c r="G89" s="18" t="inlineStr">
+      <c r="G113" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H89" s="18" t="inlineStr">
+      <c r="H113" s="18" t="inlineStr">
         <is>
           <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
         </is>
       </c>
-      <c r="I89" s="18" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="n"/>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="D90" s="17" t="inlineStr">
+      <c r="I113" s="18" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="16" t="n">
+        <v>113</v>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
         <is>
           <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
         </is>
       </c>
-      <c r="E90" s="18" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 이 고객의 투자성향과 위험등급 상한을 고려할 때 주식형 펀드는 안내할 수 없어요. 현재 고객의 투자성향은 안정추구형이고 적합성 허용 상한은 낮은위험이라서, 이 등급보다 높은 상품은 가입 대상이 아니에요. 따라서 위험등급이 보통위험 이상인 주식형 펀드는 안내가 제한돼요. 지금 고객에게 안내할 수 있는 상품은 위험등급이 낮은위험과 매우낮은위험에 해당하는 다음의 6종이에요.
@@ -3873,35 +4601,35 @@
 반면에 글로벌채권인덱스 C-P, 온국민TDF2035 C-P, 온국민TDF2040 C-P, 중립형 MP, 성장형 MP, 글로벌리츠 ETF 같은 상품들은 상품 위험등급이 보통위험에서 높은위험까지로 고객의 허용 상한인 낮은위험을 초과하기 때문에 안내할 수 없어요. 이는 어디까지나 적합성 확인 결과에 따른 안내이며 특정 상품에 대한 투자권유가 아니라는 점을 염두에 두셔야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F90" s="19" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G90" s="18" t="inlineStr">
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H90" s="18" t="inlineStr">
+      <c r="H114" s="18" t="inlineStr">
         <is>
           <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
-      <c r="I90" s="18" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="n"/>
-      <c r="B91" s="10" t="n"/>
-      <c r="C91" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="D91" s="17" t="inlineStr">
+      <c r="I114" s="18" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
         <is>
           <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
         </is>
       </c>
-      <c r="E91" s="18" t="inlineStr">
+      <c r="E115" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 안정추구형인 이 고객에게는 적합성 허용 상한이 낮은위험으로 설정되어 있어 그에 맞는 상품만 안내할 수 있어요. 
@@ -3933,39 +4661,97 @@
 이외에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험보다 높아 안내할 수 없으며, KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이라 안내할 수 없어요. 이 안내는 적합성 확인 결과이며 투자권유가 아니라는 점을 염두에 두시고, 사용계획이 있는 자금이라면 먼저 걸러내어 현금성자산이나 운용지시가 되지 않는 자산으로 다루어 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F91" s="21" t="inlineStr">
+      <c r="F115" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G91" s="18" t="inlineStr">
+      <c r="G115" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H91" s="18" t="inlineStr">
+      <c r="H115" s="18" t="inlineStr">
         <is>
           <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
         </is>
       </c>
-      <c r="I91" s="18" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="I115" s="18" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="16" t="n">
+        <v>115</v>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 성향으로 안내 못 하는 건 뭐고 왜 그런 거야?</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr"/>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>제외된 상품 + 사유 ↔ 「없다」로 끝내거나 사유를 지어낸다(§5 — 0건일 때 침묵하지 않는다)</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>이 고객 위험등급 상한이 어디까지야?</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr"/>
+      <c r="F117" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>허용 위험등급 상한 + 투자권유가 아니라는 표시 ↔ 상한만 던진다</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr"/>
+    </row>
+    <row r="118" hidden="1">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="C118" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
         <is>
           <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>고객이 문의한 TDF 추천 연도 및 위험자산 비중 정보는 현재 준비된 자료가 없어 안내하기 어려워요. 대신 현재 등록된 투자성향을 기준으로 안내할 수 있는 상품 범위와 적합성 확인 결과를 짚어 드릴게요. 이 고객은 위험중립형 성향으로 위험등급 보통위험까지 허용되므로, 해당 등급 이내의 상품만 안내할 수 있어요. 
 안내할 수 있는 상품은 다음과 같아요.
@@ -3980,35 +4766,35 @@
 반면에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하며, KB 글로벌리츠 ETF는 높은위험으로 역시 허용 상한을 초과하여 목록에 포함되지 않아요. 이 목록은 고객의 적합성 확인 결과에 따른 안내 가능 범위이며 특정 상품의 가입을 권유하는 것이 아니니 유의해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G118" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="n"/>
-      <c r="B93" s="9" t="n"/>
-      <c r="C93" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="I118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="9" t="n"/>
+      <c r="C119" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>8월 퇴직연금 추천펀드(디폴트옵션)에 올라와 있는 상품은 위험도별로 구분되어 있으며, 2026년 8월 기준(수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준)으로 안내할 수 있다. 시장 변동과 상품 개편에 따라 빠르게 달라질 수 있으므로 인용 전 기준시점을 확인해야 한다. 
 초저위험 지켜드림 포트폴리오는 비중 100이며 1년 수익률 2.13%로 구성되어 있다. 편입상품은 다음과 같다.
@@ -4055,68 +4841,68 @@
   ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F93" s="11" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G119" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H119" s="6" t="inlineStr">
         <is>
           <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="n"/>
-      <c r="B94" s="9" t="n"/>
-      <c r="C94" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="I119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>수익률 비교 질문을 하는 고객에게는 금융감독원 공시와 디폴트옵션 실적을 근거로 제시하면서 장기적인 관점의 관리를 약속하는 방식으로 접근해야 해요. 다른 은행과 비교하는 고객에게는 단기 성과보다 장기 관리가 중요하다는 점을 짚어주는 것이 핵심이에요. IRP 실적배당형 부문 전 구간 1위와 디폴트옵션 수익률 순위를 안내할 수 있도록 "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀드려 보세요. 또한 디폴트옵션 고위험 포트폴리오의 실적을 바탕으로 "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G120" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H120" s="6" t="inlineStr">
         <is>
           <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="n"/>
-      <c r="B95" s="9" t="n"/>
-      <c r="C95" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="I120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>디폴트옵션 포트폴리오의 구성상품과 비중, 금리 정보는 2026년 8월 기준(수익률은 2026년 7월 30일, 원리금보장 금리는 2026년 8월 기준)으로 안내할 수 있는 상품들이 있다. 위험도별 포트폴리오의 구체적인 구성과 비중, 금리는 다음과 같이 확인된다.
 초저위험 '지켜드림' 포트폴리오
@@ -4160,68 +4946,68 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F95" s="14" t="inlineStr">
+      <c r="F121" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G121" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H121" s="6" t="inlineStr">
         <is>
           <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="9" t="n"/>
-      <c r="C96" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="I121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" hidden="1">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
         <is>
           <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>직원이 물어본 TDF 수익률 및 위험등급에 대해서는 현재 준비된 자료가 없어요. 다만 2026년 3월에 작성된 연금사업본부 연금컨설팅부 자료를 기준으로 2025년 10월 기준 당행 라인업의 개념과 선택 공식에 관한 내용은 확인할 수 있어요. TDF는 은퇴 시점에 맞춰 주식→채권 비중을 자동 조정하는 자산배분 펀드다(전략 명칭 글라이드 패스). 상품명 숫자 = 목표 은퇴연도, 5년 단위 빈티지. 선택 공식 출생연도 + 예상 은퇴연령 = Target Date(예: 1990+60=2050). 당행 라인업 총 18종(2025.10 기준). 환헤지 여부로 H(헤지) / UH(언헤지) 상품이 구분된다 — H는 환율 변동 영향 축소, UH는 환차익·환차손 반영. 관련 내용은 기준시점 2025.10 (KBthink 04) 기준으로 안내해 드릴 수 있어요.</t>
         </is>
       </c>
-      <c r="F96" s="14" t="inlineStr">
+      <c r="F122" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="n"/>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
         <is>
           <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>위험중립형 포트폴리오는 2026년 8월 기준 국내채권 60%, 해외채권 15%, 해외혼합 25%의 자산배분으로 구성되어 있어요. 이 유형의 기대수익은 5.4%, 변동성은 4.9%로 산정되어 있으며, 활용할 수 있는 상품은 다음과 같아요.
 - 하나 파워e단기채 (합성총보수 연0.1834%) — 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구
@@ -4231,72 +5017,72 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F97" s="14" t="inlineStr">
+      <c r="F123" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="n"/>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="I123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
         </is>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="C124" s="16" t="n">
+        <v>123</v>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
         <is>
           <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
         </is>
       </c>
-      <c r="E98" s="18" t="inlineStr">
+      <c r="E124" s="18" t="inlineStr">
         <is>
           <t>시장 불안을 이유로 실적배당형 상품 전환을 고민하는 고객에게는 연금의 자금 성격과 운용 기간의 특성을 활용해 접근하는 것이 핵심이에요. 연금은 일반 투자와 달리 30년 이상이라는 장기 기간을 가지며 투입되는 규모도 상대적으로 작아 마이너스 50%를 맞아도 실제 체감하는 타격이 크지 않다는 점을 짚어주세요. 일반 투자는 금액이 크고 기간이 짧아 저변동성이 맞지만, 연금은 오히려 변동성을 지향해도 된다는 논리로 고객의 통념을 전환해 줄 수 있어요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 연금지급 대기나 교체매매 중으로 사용계획이 있는 자금은 먼저 걸러내야 해요. 또한 고객에게 설명할 때는 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 시장 상황에 대한 불안을 해소할 때는 우리나라 사람들이 실거주 부동산을 30~50년씩 보유하는 것처럼 30년 이상의 기간에는 이미 익숙하다는 점을 함께 안내해 주세요.</t>
         </is>
       </c>
-      <c r="F98" s="23" t="inlineStr">
+      <c r="F124" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G98" s="18" t="inlineStr">
+      <c r="G124" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H98" s="18" t="inlineStr">
+      <c r="H124" s="18" t="inlineStr">
         <is>
           <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="I98" s="18" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="n"/>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="D99" s="17" t="inlineStr">
+      <c r="I124" s="18" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="9" t="n"/>
+      <c r="C125" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
         <is>
           <t>이번 주 금융시장에 영향 줄 만한 일정 뭐 있어?</t>
         </is>
       </c>
-      <c r="E99" s="18" t="inlineStr">
+      <c r="E125" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차(2026년 8월 14일 종가 기준) 금융시장에 영향을 줄 수 있는 주요 일정은 국가별로 지정되어 있어요.
 - 17일 월요일 — 1~20일 수출/입
@@ -4307,35 +5093,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F99" s="19" t="inlineStr">
+      <c r="F125" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G99" s="18" t="inlineStr">
+      <c r="G125" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H99" s="18" t="inlineStr">
+      <c r="H125" s="18" t="inlineStr">
         <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「이번 주」에 8월 3주차 일정이 나온다(시효 표시는 붙는다). 봐야 할 것은 기준시점이 빠지지 않는가</t>
         </is>
       </c>
-      <c r="I99" s="18" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="n"/>
-      <c r="B100" s="9" t="n"/>
-      <c r="C100" s="16" t="n">
-        <v>99</v>
-      </c>
-      <c r="D100" s="17" t="inlineStr">
+      <c r="I125" s="18" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
         <is>
           <t>이번 달 FOMC 어떻게 보고 있는지 시나리오별로 알려줘</t>
         </is>
       </c>
-      <c r="E100" s="18" t="inlineStr">
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>2026년 9월 자료 기준으로 9월 미국 FOMC는 기준금리를 동결할 가능성이 가장 높은 기본 시나리오로 보고 있어요.
 당시 기준으로 연준의 9월 기준금리 동결 가능성은 시장에 이미 선반영되었고, 포워드 가이던스를 주지 않으려는 워시 의장의 태도로 인해 시장 영향력은 제한적일 것으로 보았어요. 기본 시나리오에서는 미국초단기 국채 ETF신탁 같은 미국초단기채 상품을 고려해 볼 수 있어요.
@@ -4345,68 +5131,68 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F100" s="19" t="inlineStr">
+      <c r="F126" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G100" s="18" t="inlineStr">
+      <c r="G126" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H100" s="18" t="inlineStr">
+      <c r="H126" s="18" t="inlineStr">
         <is>
           <t>긍정·기본·부정 + 기준시점(26.09 — 시연일과 같은 달) ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
         </is>
       </c>
-      <c r="I100" s="18" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="9" t="n"/>
-      <c r="C101" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D101" s="17" t="inlineStr">
+      <c r="I126" s="18" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
         <is>
           <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
         </is>
       </c>
-      <c r="E101" s="18" t="inlineStr">
+      <c r="E127" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F101" s="19" t="inlineStr">
+      <c r="F127" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G101" s="18" t="inlineStr">
+      <c r="G127" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H101" s="18" t="inlineStr">
+      <c r="H127" s="18" t="inlineStr">
         <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
         </is>
       </c>
-      <c r="I101" s="18" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="n"/>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="D102" s="17" t="inlineStr">
+      <c r="I127" s="18" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="16" t="n">
+        <v>127</v>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
         <is>
           <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr">
+      <c r="E128" s="18" t="inlineStr">
         <is>
           <t>● 정민석
 질문하신 고객의 원리금보장 상품 유지 여부를 판단할 때 시장 상황과 자금의 성격을 함께 고려해야 해요. 2026년 8월 3주차 기준으로 미국 증시는 소비자물가 예상 부합과 생산자물가 예상 하회, 연준 금리 인상 우려 완화 속에 AI 반도체 및 기술주 중심의 상승세로 S&amp;P500지수가 사상 최고치를 경신했으나, 미국-이란 긴장으로 인한 국제유가 상승, 미국 재정 적자 우려, 하이퍼스케일러들의 AI 인프라 투자 자금 채권시장 조달에 따른 미국 국채 금리 상승 등이 증시 상승세를 제약하는 요인으로 작용하고 있습니다. 2026년 9월 기준으로는 미국 FOMC와 일본 BOJ 등 주요 경제 이벤트와 점도표 변화, 엔 캐리 청산 우려 등 변동성 확대 요인이 있으므로 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. 또한 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라진니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.
@@ -4417,78 +5203,525 @@
 요즘 시황 근거로 원리금보장 자산을 그대로 두어도 되는지 판단할 때는 2026년 8월 3주차와 2026년 9월 자료에서 다루는 시장 상황과 기준시점을 확인해야 해요. 미국 7월 소비자물가가 예상에 부합하고 생산자물가는 예상을 하회하여 연준 금리 인상 우려가 완화된 반면, 미·이런 긴장에 따른 국제유가 상승과 미국 국채 금리 상승 요인이 함께 작용하고 있어요. 또한 9월에는 기준금리 동결 후 데이터 의존 입장을 반복할 것으로 예상되는 미국 FOMC와 기준금리 인상이 예상되는 일본 BOJ 금융정책결정회의 등 중요 이벤트가 예정되어 있어요. 미국 재정적자 확대와 장기국채 수요 감소를 감안해 장기금리 하락은 비중 축소 기회로 활용할 수 있으며, BOJ의 기준금리 인상과 엔 캐리 청산 우려가 있으나 인상이 예상된 이벤트라 2024년 8월과 같은 증시 폭락 가능성은 낮다고 판단하고 있어요. 다만 사용계획이 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내어 판단해야 해요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F102" s="19" t="inlineStr">
+      <c r="F128" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G102" s="18" t="inlineStr">
+      <c r="G128" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H102" s="18" t="inlineStr">
+      <c r="H128" s="18" t="inlineStr">
         <is>
           <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
         </is>
       </c>
-      <c r="I102" s="18" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I128" s="18" t="inlineStr"/>
+    </row>
+    <row r="129" hidden="1">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>17. 복합·연쇄 턴</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>증권사 수수료 무료를 이유로 이탈하려는 고객에게는 면제 조건을 먼저 짚어준 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 증권사의 수수료 면제가 고객을 모아 펀드 판매로 수익을 내는 전략이라는 점과 장기할인 소멸 및 수시인출 면제 구조를 염두에 두고 대응 논리를 펼치세요. 만 55세 이후 연금개시 시 수수료가 0원이 되며 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되는 조건을 먼저 확인해 주세요. 
+고객에게는 "국민은행도 만 55세 이후 연금개시를 하시면 수수료가 0원입니다^^ 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제됩니다"라고 안내해 보세요. 
+조건에 해당하지 않아 수수료가 일부 발생하는 경우라면 수수료보다 전문가 관리로 프레임을 옮겨야 해요. 증권사는 고객이 장기간 직접 투자하고 직접 관리해야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능하기 때문이에요. 이 경우에는 "네, 수수료가 일부 발생합니다. 그런데 고객님. IRP는 수수료만 보고 결정하기엔 아까운 계좌입니다. 증권사는 고객님이 장기간 직접 투자하고 직접 관리하셔야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능합니다"라고 말씀해 보세요. 
+아울러 당행 구체적인 수수료율이나 우리 수수료가 얼마인지에 대한 상세한 수치는 아직 준비된 자료가 없어요.</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 대본</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>● 정민석
+현재 보유하신 자산이 모두 원리금보장상품으로만 운용 중인 고객에게는 정기예금 대신 디폴트옵션 저위험 이상으로 운용해 보시는 방법을 제안해 볼 수 있어요. 다만 해당 고객이 이미 디폴트옵션 초저위험을 등록해 보유하고 계신 상태라면 사전지정운용제도 등록 및 변경과 보유상품 변경인 기존 매도 및 신규 매수의 2단계 거래가 필요하다는 점을 반드시 함께 안내해 드려야 해요. 또한 고객에게 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 쉽게 설명해 주시는 것이 좋아요. 사용 계획이 있는 자금이나 반대 케이스에 해당하는지 먼저 확인하고 접근하는 점도 잊지 마세요.
+● 박정호
+원리금보장상품 100% 운용 고객에게는 적립금 300만원 이상인 경우 정기예금 대신 디폴트옵션 저위험 이상으로 운용을 제안할 수 있어요. 
+상담을 진행할 때 사용계획 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내야 한다는 점을 유념해 주세요. 
+또한 고객에게 안내할 때는 생소한 '고유계정대'라는 표현 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요. 
+이미 디폴트옵션 초저위험을 등록·보유한 고객이라면 사전지정운용제도 등록 및 변경과 보유상품 변경(기존 매도 후 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요.</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>정민석 181245-3097614·박정호 168450-7293815</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>● 오세훈
+정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 안내하는 것이 핵심이에요. 1개월 내 만기도래 원리금보장상품을 보유하고 디폴트옵션이 미등록된 상태라면 이러한 제도 변경 내용을 짚어주면서 디폴트옵션 사전지정 등록이나 만기 예약변경을 권유하는 방법을 활용할 수 있어요.
+● 이수민
+앞서 말씀드린 2026년 10월 17일 만기를 앞둔 7,000만원 규모의 예금은 만기 때 별도의 재예치 지시가 없으면 현금성자산으로 대기하게 돼요. 
+정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 만기 전 운용 방향을 확정해야 해요. 만기 임박 + 디폴트옵션 미등록 고객에게는 "정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기 자금이 현금성자산으로 상환되니 디폴트옵션 사전지정 등록이나 만기 예약을 하시는 것이 좋아요"라고 안내해 보세요.</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 만기 언제고 금액은 얼마야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="n"/>
+      <c r="B135" s="9" t="n"/>
+      <c r="C135" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>(되묻기 뒤) 2번째꺼</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>■ [06-AD-080] 개인형IRP 계좌이체 전입/전출  (계약이전)
+· 무슨 화면인지: 계좌이체 전입/전출 조회, 전출취소(해제), 이전 진행상황 수시 조회 → 관련 지식항목 33·34
+· 근거 신뢰도: 여러 자료에서 교차확인(○ (3건))
+· 비고: 전입 기능도 같은 번호(1부는 전출만 기재였음). 기업형 DB/DC는 [06-AD-090]
+· 출처 퇴직연금 주요거래 화면번호 안내 (KB StarLearn 직원교육)</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 라이브러리</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>실물이전 어떻게 처리해?</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>(되묻기 뒤) 잘 모르겠는데</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>어느 방향으로 이전하는 건가요?
+· 전출
+· 전입</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>실물이전 어떻게 처리해?</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="9" t="n"/>
+      <c r="C137" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>(제안 뒤) 아니, 됐어</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="n"/>
+      <c r="B139" s="9" t="n"/>
+      <c r="C139" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>(첫 턴) 네</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr"/>
+    </row>
+    <row r="140" hidden="1">
+      <c r="A140" s="10" t="n"/>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr"/>
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Ⅳ. 상담 후 · 그 밖</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>17. 안내 콘텐츠·발송</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>18. 안내 콘텐츠·발송</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E141" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 안내할 만한 이벤트와 세미나는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있고 디폴트옵션이 미설정된 상태이므로 잠자는 IRP 자금 깨우기 운용 이벤트와 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나를 안내하는 것이 핵심이에요.
 잠자는 IRP 자금 깨우기 운용 이벤트는 12/30까지 KB스타뱅킹에서 진행되며, 고객이 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 상태이므로 참고하시기 좋고 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX를 활용할 수 있어요.
 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나는 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 온라인 세미나로, 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어 추천하며 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX로 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="F141" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="G141" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H103" s="6" t="inlineStr">
+      <c r="H141" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
-      <c r="I103" s="6" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="n"/>
-      <c r="B104" s="9" t="n"/>
-      <c r="C104" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
+      <c r="I141" s="18" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
         <is>
           <t>왜 이 이벤트를 고른 거야?</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E142" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 잠자는 IRP 자금 깨우기 운용 이벤트를 안내하는 이유는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 성립 요건을 충족하기 때문이에요. 고객이 최종 운용변경 이후 장기간 운용되지 않은 자금을 보유하고 있어 운용상품을 선택하거나 변경할 수 있도록 이벤트를 권유할 수 있어요. 안내 시 참고할 발송 문구는 다음과 같아요.
 (광고) 송도윤 고객님, KB국민은행입니다.
@@ -4497,39 +5730,39 @@
 무료수신거부 080-XXX-XXXX</t>
         </is>
       </c>
-      <c r="F104" s="11" t="inlineStr">
+      <c r="F142" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="G142" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H142" s="18" t="inlineStr">
         <is>
           <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
+      <c r="I142" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="D105" s="12" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="9" t="n"/>
+      <c r="B143" s="9" t="n"/>
+      <c r="C143" s="16" t="n">
+        <v>142</v>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
         <is>
           <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E143" s="18" t="inlineStr">
         <is>
           <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기
 화면이 열리면 이 문구를 넣어 주세요 — "(광고) 송도윤 고객님, KB국민은행입니다.
@@ -4538,78 +5771,78 @@
 무료수신거부 080-XXX-XXXX"</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F143" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="G143" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="H143" s="18" t="inlineStr">
         <is>
           <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I143" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="n"/>
-      <c r="B106" s="9" t="n"/>
-      <c r="C106" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D106" s="12" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="16" t="n">
+        <v>143</v>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E144" s="18" t="inlineStr">
         <is>
           <t>이 고객에게 안내할 이벤트와 세미나의 발송 문구는 자료에 있는 문구를 그대로 활용하는 게 핵심이에요. 
 잠자는 IRP 자금 깨우기 운용 이벤트 발송 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX"를 그대로 사용해 주세요.
 온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
         </is>
       </c>
-      <c r="F106" s="14" t="inlineStr">
+      <c r="F144" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="G144" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H144" s="18" t="inlineStr">
         <is>
           <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I144" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="9" t="n"/>
-      <c r="B107" s="9" t="n"/>
-      <c r="C107" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="16" t="n">
+        <v>144</v>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E145" s="18" t="inlineStr">
         <is>
           <t>앞서 말씀드린 2건 외에 잠재적 안내 후보로 열려 있는 이벤트 3건과 세미나 4건이 더 있어요.
 이벤트 3건은 다음과 같아요.
@@ -4624,76 +5857,76 @@
 고객에게 안내할 때는 사용계획이 있는 자금인지 먼저 확인하고 활용할 수 있는 방법을 살펴보세요. 세부적인 발송 문구나 링크가 필요한 항목이 있다면 이어서 말씀해 드릴게요.</t>
         </is>
       </c>
-      <c r="F107" s="14" t="inlineStr">
+      <c r="F145" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="G145" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="H145" s="18" t="inlineStr">
         <is>
           <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I145" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="n"/>
-      <c r="B108" s="10" t="n"/>
-      <c r="C108" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="D108" s="12" t="inlineStr">
+    <row r="146" hidden="1">
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E146" s="18" t="inlineStr">
         <is>
           <t>현재 이 고객의 요건에 맞는 세미나는 아직 준비된 자료가 없어요. 다만 열려 있는 콘텐츠 중 날짜가 가까운 세미나로는 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 세미나가 11/12(목) 17시에 KB국민은행 WM투자부 주관으로 예정되어 있어요. 이 세미나는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋은 내용이에요. 안내할 때 참고할 수 있는 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요.</t>
         </is>
       </c>
-      <c r="F108" s="14" t="inlineStr">
+      <c r="F146" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G146" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H146" s="18" t="inlineStr">
         <is>
           <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="n"/>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>18. 이번 상담 요약·쪽지</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="n">
-        <v>108</v>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
+      <c r="I146" s="18" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="n"/>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>19. 이번 상담 요약·쪽지</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
         <is>
           <t>대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
-      <c r="E109" s="18" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>[제목] 송도윤 고객 관리 대상 사유 및 대응 방향
 송도윤 고객은 최근 358일간 접촉 이력이 없어 타사 비교 견적 노출 가능성이 있습니다.
@@ -4703,216 +5936,216 @@
 (아래에 이 고객의 연령·투자성향·평가금액·수익률·연금개시·세액공제 잔여한도·관리 사유 표가 붙습니다)</t>
         </is>
       </c>
-      <c r="F109" s="20" t="inlineStr">
+      <c r="F147" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G109" s="18" t="inlineStr">
+      <c r="G147" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H109" s="18" t="inlineStr">
+      <c r="H147" s="6" t="inlineStr">
         <is>
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="I109" s="18" t="inlineStr">
+      <c r="I147" s="6" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="n"/>
-      <c r="B110" s="9" t="n"/>
-      <c r="C110" s="16" t="n">
-        <v>109</v>
-      </c>
-      <c r="D110" s="17" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
         <is>
           <t>(쪽지 초안 뒤) 응, 보내줘</t>
         </is>
       </c>
-      <c r="E110" s="18" t="inlineStr">
+      <c r="E148" s="6" t="inlineStr">
         <is>
           <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
         </is>
       </c>
-      <c r="F110" s="20" t="inlineStr">
+      <c r="F148" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G110" s="18" t="inlineStr">
+      <c r="G148" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H110" s="18" t="inlineStr">
+      <c r="H148" s="6" t="inlineStr">
         <is>
           <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
         </is>
       </c>
-      <c r="I110" s="18" t="inlineStr">
+      <c r="I148" s="6" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="9" t="n"/>
-      <c r="B111" s="9" t="n"/>
-      <c r="C111" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="D111" s="17" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="9" t="n"/>
+      <c r="C149" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
         <is>
           <t>지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
         </is>
       </c>
-      <c r="F111" s="19" t="inlineStr">
+      <c r="F149" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G111" s="18" t="inlineStr">
+      <c r="G149" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H111" s="18" t="inlineStr">
+      <c r="H149" s="6" t="inlineStr">
         <is>
           <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
         </is>
       </c>
-      <c r="I111" s="18" t="inlineStr">
+      <c r="I149" s="6" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="9" t="n"/>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="D112" s="17" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="9" t="n"/>
+      <c r="B150" s="10" t="n"/>
+      <c r="C150" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
         </is>
       </c>
-      <c r="F112" s="19" t="inlineStr">
+      <c r="F150" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G112" s="18" t="inlineStr">
+      <c r="G150" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H112" s="18" t="inlineStr">
+      <c r="H150" s="6" t="inlineStr">
         <is>
           <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
         </is>
       </c>
-      <c r="I112" s="18" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="n"/>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>19. 브리핑 수정</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
+      <c r="I150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="n"/>
+      <c r="B151" s="15" t="inlineStr">
+        <is>
+          <t>20. 브리핑 수정</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
         <is>
           <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E151" s="18" t="inlineStr">
         <is>
           <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="F151" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G151" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H113" s="6" t="inlineStr">
+      <c r="H151" s="18" t="inlineStr">
         <is>
           <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="n"/>
-      <c r="B114" s="9" t="n"/>
-      <c r="C114" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="I151" s="18" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="16" t="n">
+        <v>151</v>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
         <is>
           <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E152" s="18" t="inlineStr">
         <is>
           <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
         </is>
       </c>
-      <c r="F114" s="14" t="inlineStr">
+      <c r="F152" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr">
+      <c r="G152" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H114" s="6" t="inlineStr">
+      <c r="H152" s="18" t="inlineStr">
         <is>
           <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="n"/>
-      <c r="B115" s="10" t="n"/>
-      <c r="C115" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
+      <c r="I152" s="18" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="n"/>
+      <c r="B153" s="10" t="n"/>
+      <c r="C153" s="16" t="n">
+        <v>152</v>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔줘</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E153" s="18" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔 달라는 요청에 대해서는 직접적인 변경 사유나 추가 상품을 안내해 드릴 자료가 아직 준비된 사유가 없어요. 다만 현재 등록된 투자성향 기준으로는 안내할 수 있는 위험등급 상한이 보통위험까지예요. 
 이 고객은 위험중립형 성향이라 보통위험 등급까지만 상품을 안내할 수 있어서, 현재 기준으로 안내 가능한 상품 목록은 다음과 같아요.
@@ -4928,39 +6161,39 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F115" s="14" t="inlineStr">
+      <c r="F153" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G115" s="6" t="inlineStr">
+      <c r="G153" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H115" s="6" t="inlineStr">
+      <c r="H153" s="18" t="inlineStr">
         <is>
           <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
         </is>
       </c>
-      <c r="I115" s="6" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="n"/>
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t>20. 답변 다듬기·되짚기</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="D116" s="17" t="inlineStr">
+      <c r="I153" s="18" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="n"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>21. 답변 다듬기·되짚기</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
         <is>
           <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E116" s="18" t="inlineStr">
+      <c r="E154" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 내용을 바탕으로 고객에게 바로 전달할 수 있는 핵심 대사만 짧게 줄여서 정리해 드릴게요. 
 연금지급 대기 자금이나 교체매매 중인 자금이 아닌지 먼저 확인한 뒤에 이렇게 안내해 보세요.
@@ -4968,115 +6201,115 @@
 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정해 약속하지 않도록 주의하고, 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용하여 고객이 쉽게 이해할 수 있도록 설명해 주세요.</t>
         </is>
       </c>
-      <c r="F116" s="20" t="inlineStr">
+      <c r="F154" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G116" s="18" t="inlineStr">
+      <c r="G154" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H116" s="18" t="inlineStr">
+      <c r="H154" s="6" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I116" s="18" t="inlineStr">
+      <c r="I154" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="9" t="n"/>
-      <c r="B117" s="9" t="n"/>
-      <c r="C117" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="D117" s="17" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="9" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>그 중 두 번째 상품만 자세히 설명해줘</t>
         </is>
       </c>
-      <c r="E117" s="18" t="inlineStr">
+      <c r="E155" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 상품 중 두 번째 상품인 KB 국내채권형 C-P에 대해 자세히 설명해 드릴게요.
 - KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
 위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
         </is>
       </c>
-      <c r="F117" s="20" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G117" s="18" t="inlineStr">
+      <c r="G155" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H117" s="18" t="inlineStr">
+      <c r="H155" s="6" t="inlineStr">
         <is>
           <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
-      <c r="I117" s="18" t="inlineStr">
+      <c r="I155" s="6" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="9" t="n"/>
-      <c r="B118" s="9" t="n"/>
-      <c r="C118" s="16" t="n">
-        <v>117</v>
-      </c>
-      <c r="D118" s="17" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="9" t="n"/>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="D156" s="12" t="inlineStr">
         <is>
           <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
         </is>
       </c>
-      <c r="E118" s="18" t="inlineStr">
+      <c r="E156" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
         </is>
       </c>
-      <c r="F118" s="19" t="inlineStr">
+      <c r="F156" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G118" s="18" t="inlineStr">
+      <c r="G156" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H118" s="18" t="inlineStr">
+      <c r="H156" s="6" t="inlineStr">
         <is>
           <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
         </is>
       </c>
-      <c r="I118" s="18" t="inlineStr">
+      <c r="I156" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="n"/>
-      <c r="B119" s="9" t="n"/>
-      <c r="C119" s="16" t="n">
-        <v>118</v>
-      </c>
-      <c r="D119" s="17" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="9" t="n"/>
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
-      <c r="E119" s="18" t="inlineStr">
+      <c r="E157" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 개인형IRP 수수료는 부담금 종류와 채널 및 구간에 따라 차등 적용되니 단말에서 먼저 확인한 뒤 안내해 주세요. 상세 수수료율은 다음과 같이 대면 및 비대면 채널별 구간에 따라 적용돼요.
 - 사용자부담금(퇴직금) 대면 5천만원 미만 — 0.45%
@@ -5089,115 +6322,115 @@
 - 가입자부담금 비대면 1억원 이상 — 0.21%</t>
         </is>
       </c>
-      <c r="F119" s="19" t="inlineStr">
+      <c r="F157" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G119" s="18" t="inlineStr">
+      <c r="G157" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H119" s="18" t="inlineStr">
+      <c r="H157" s="6" t="inlineStr">
         <is>
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
-      <c r="I119" s="18" t="inlineStr">
+      <c r="I157" s="6" t="inlineStr">
         <is>
           <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="9" t="n"/>
-      <c r="B120" s="9" t="n"/>
-      <c r="C120" s="16" t="n">
-        <v>119</v>
-      </c>
-      <c r="D120" s="17" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
-      <c r="E120" s="18" t="inlineStr">
+      <c r="E158" s="6" t="inlineStr">
         <is>
           <t>예금만으로 자산을 보유해 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 자산관리라는 논리로 접근하는 게 핵심이에요. 앞서 안내드린 내용에 수수료 관련 내용은 자료에 없어 추가하지 못했어요. 이미 안전하게 잘 운용하고 계신 점을 먼저 인정한 뒤, 원리금보장 상품도 매월 최고금리 상품 제공과 비대면 거래를 통해 꾸준히 관리해야 한다는 점을 짚어주세요. 
 고객에게는 이렇게 말씀해 보세요.
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="F120" s="19" t="inlineStr">
+      <c r="F158" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G120" s="18" t="inlineStr">
+      <c r="G158" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H120" s="18" t="inlineStr">
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
-      <c r="I120" s="18" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="9" t="n"/>
-      <c r="B121" s="10" t="n"/>
-      <c r="C121" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="D121" s="17" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="9" t="n"/>
+      <c r="B159" s="10" t="n"/>
+      <c r="C159" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E121" s="18" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>이번 상담에서 오간 대화 기록은 없습니다.</t>
         </is>
       </c>
-      <c r="F121" s="19" t="inlineStr">
+      <c r="F159" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G121" s="18" t="inlineStr">
+      <c r="G159" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H121" s="18" t="inlineStr">
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
-      <c r="I121" s="18" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="n"/>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>21. 에이전트 능력 안내</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
+      <c r="I159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="n"/>
+      <c r="B160" s="15" t="inlineStr">
+        <is>
+          <t>22. 에이전트 능력 안내</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="n">
+        <v>159</v>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
         <is>
           <t>너 뭐 할 수 있는지 알려줘</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E160" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -5217,35 +6450,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F160" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="G160" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="H160" s="18" t="inlineStr">
         <is>
           <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="n"/>
-      <c r="B123" s="9" t="n"/>
-      <c r="C123" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
+      <c r="I160" s="18" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="16" t="n">
+        <v>160</v>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
         <is>
           <t>너 이전 대화 기억해?</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E161" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -5267,35 +6500,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F123" s="14" t="inlineStr">
+      <c r="F161" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G161" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H161" s="18" t="inlineStr">
         <is>
           <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="n"/>
-      <c r="B124" s="10" t="n"/>
-      <c r="C124" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="D124" s="12" t="inlineStr">
+      <c r="I161" s="18" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="10" t="n"/>
+      <c r="C162" s="16" t="n">
+        <v>161</v>
+      </c>
+      <c r="D162" s="17" t="inlineStr">
         <is>
           <t>고객한테 문자 직접 보내줄 수 있어?</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E162" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -5317,72 +6550,72 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F124" s="14" t="inlineStr">
+      <c r="F162" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G162" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H162" s="18" t="inlineStr">
         <is>
           <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="n"/>
-      <c r="B125" s="15" t="inlineStr">
-        <is>
-          <t>22. 오늘의 타겟 목록</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="D125" s="17" t="inlineStr">
+      <c r="I162" s="18" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="n"/>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>23. 오늘의 타겟 목록</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>오늘 누구부터 봐야 해?</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
-      <c r="F125" s="19" t="inlineStr">
+      <c r="F163" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G125" s="18" t="inlineStr">
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H125" s="18" t="inlineStr">
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
         </is>
       </c>
-      <c r="I125" s="18" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="n"/>
-      <c r="B126" s="10" t="n"/>
-      <c r="C126" s="16" t="n">
-        <v>125</v>
-      </c>
-      <c r="D126" s="17" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="n"/>
+      <c r="B164" s="10" t="n"/>
+      <c r="C164" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
         <is>
           <t>타겟 목록에 고객번호도 같이 넣어줘</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr">
+      <c r="E164" s="6" t="inlineStr">
         <is>
           <t>요청하신 타겟 목록의 고객번호는 현재 자료에 없어요. 2026년 9월 29일 기준 타겟 목록에 있는 고객들의 선정 사유와 순서를 안내해 드릴게요.
 - 윤가영 — 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원, 디폴트옵션 미설정
@@ -5398,490 +6631,43 @@
 - 한지우 — ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원</t>
         </is>
       </c>
-      <c r="F126" s="19" t="inlineStr">
+      <c r="F164" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G126" s="18" t="inlineStr">
+      <c r="G164" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H126" s="18" t="inlineStr">
+      <c r="H164" s="6" t="inlineStr">
         <is>
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
-      <c r="I126" s="18" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I164" s="6" t="inlineStr"/>
+    </row>
+    <row r="165" hidden="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Ⅴ. 품질 — 시연엔 안 올려도 보는 것</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>23. 복합·연쇄 턴</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>증권사 수수료 무료를 이유로 이탈하려는 고객에게는 면제 조건을 먼저 짚어준 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 증권사의 수수료 면제가 고객을 모아 펀드 판매로 수익을 내는 전략이라는 점과 장기할인 소멸 및 수시인출 면제 구조를 염두에 두고 대응 논리를 펼치세요. 만 55세 이후 연금개시 시 수수료가 0원이 되며 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되는 조건을 먼저 확인해 주세요. 
-고객에게는 "국민은행도 만 55세 이후 연금개시를 하시면 수수료가 0원입니다^^ 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제됩니다"라고 안내해 보세요. 
-조건에 해당하지 않아 수수료가 일부 발생하는 경우라면 수수료보다 전문가 관리로 프레임을 옮겨야 해요. 증권사는 고객이 장기간 직접 투자하고 직접 관리해야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능하기 때문이에요. 이 경우에는 "네, 수수료가 일부 발생합니다. 그런데 고객님. IRP는 수수료만 보고 결정하기엔 아까운 계좌입니다. 증권사는 고객님이 장기간 직접 투자하고 직접 관리하셔야 하는 반면, 국민은행은 가까운 영업점 어디에서든 포트폴리오 점검 및 리밸런싱 상담이 가능합니다"라고 말씀해 보세요. 
-아울러 당행 구체적인 수수료율이나 우리 수수료가 얼마인지에 대한 상세한 수치는 아직 준비된 자료가 없어요.</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="n"/>
-      <c r="B128" s="9" t="n"/>
-      <c r="C128" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
-        </is>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="n"/>
-      <c r="B129" s="9" t="n"/>
-      <c r="C129" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>● 정민석
-현재 보유하신 자산이 모두 원리금보장상품으로만 운용 중인 고객에게는 정기예금 대신 디폴트옵션 저위험 이상으로 운용해 보시는 방법을 제안해 볼 수 있어요. 다만 해당 고객이 이미 디폴트옵션 초저위험을 등록해 보유하고 계신 상태라면 사전지정운용제도 등록 및 변경과 보유상품 변경인 기존 매도 및 신규 매수의 2단계 거래가 필요하다는 점을 반드시 함께 안내해 드려야 해요. 또한 고객에게 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 쉽게 설명해 주시는 것이 좋아요. 사용 계획이 있는 자금이나 반대 케이스에 해당하는지 먼저 확인하고 접근하는 점도 잊지 마세요.
-● 박정호
-원리금보장상품 100% 운용 고객에게는 적립금 300만원 이상인 경우 정기예금 대신 디폴트옵션 저위험 이상으로 운용을 제안할 수 있어요. 
-상담을 진행할 때 사용계획 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내야 한다는 점을 유념해 주세요. 
-또한 고객에게 안내할 때는 생소한 '고유계정대'라는 표현 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요. 
-이미 디폴트옵션 초저위험을 등록·보유한 고객이라면 사전지정운용제도 등록 및 변경과 보유상품 변경(기존 매도 후 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요.</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614·박정호 168450-7293815</t>
-        </is>
-      </c>
-      <c r="H129" s="6" t="inlineStr">
-        <is>
-          <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
-        </is>
-      </c>
-      <c r="I129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="n"/>
-      <c r="B130" s="9" t="n"/>
-      <c r="C130" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F130" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
-        </is>
-      </c>
-      <c r="I130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="n"/>
-      <c r="B131" s="9" t="n"/>
-      <c r="C131" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>● 오세훈
-정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 안내하는 것이 핵심이에요. 1개월 내 만기도래 원리금보장상품을 보유하고 디폴트옵션이 미등록된 상태라면 이러한 제도 변경 내용을 짚어주면서 디폴트옵션 사전지정 등록이나 만기 예약변경을 권유하는 방법을 활용할 수 있어요.
-● 이수민
-앞서 말씀드린 2026년 10월 17일 만기를 앞둔 7,000만원 규모의 예금은 만기 때 별도의 재예치 지시가 없으면 현금성자산으로 대기하게 돼요. 
-정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 만기 전 운용 방향을 확정해야 해요. 만기 임박 + 디폴트옵션 미등록 고객에게는 "정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기 자금이 현금성자산으로 상환되니 디폴트옵션 사전지정 등록이나 만기 예약을 하시는 것이 좋아요"라고 안내해 보세요.</t>
-        </is>
-      </c>
-      <c r="F131" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
-        </is>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>이 고객 만기 언제고 금액은 얼마야?</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="n"/>
-      <c r="B132" s="9" t="n"/>
-      <c r="C132" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F132" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
-        </is>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9" t="n"/>
-      <c r="B133" s="9" t="n"/>
-      <c r="C133" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>(되묻기 뒤) 2번째꺼</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>■ [06-AD-080] 개인형IRP 계좌이체 전입/전출  (계약이전)
-· 무슨 화면인지: 계좌이체 전입/전출 조회, 전출취소(해제), 이전 진행상황 수시 조회 → 관련 지식항목 33·34
-· 근거 신뢰도: 여러 자료에서 교차확인(○ (3건))
-· 비고: 전입 기능도 같은 번호(1부는 전출만 기재였음). 기업형 DB/DC는 [06-AD-090]
-· 출처 퇴직연금 주요거래 화면번호 안내 (KB StarLearn 직원교육)</t>
-        </is>
-      </c>
-      <c r="F133" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>실물이전 어떻게 처리해?</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="9" t="n"/>
-      <c r="B134" s="9" t="n"/>
-      <c r="C134" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="D134" s="12" t="inlineStr">
-        <is>
-          <t>(되묻기 뒤) 잘 모르겠는데</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>어느 방향으로 이전하는 건가요?
-· 전출
-· 전입</t>
-        </is>
-      </c>
-      <c r="F134" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
-        </is>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>실물이전 어떻게 처리해?</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="n"/>
-      <c r="B135" s="9" t="n"/>
-      <c r="C135" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>(제안 뒤) 아니, 됐어</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
-        </is>
-      </c>
-      <c r="F135" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
-        </is>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="n"/>
-      <c r="B136" s="9" t="n"/>
-      <c r="C136" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="D136" s="12" t="inlineStr">
-        <is>
-          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F136" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
-        </is>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="n"/>
-      <c r="B137" s="9" t="n"/>
-      <c r="C137" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="D137" s="12" t="inlineStr">
-        <is>
-          <t>(첫 턴) 네</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
-        </is>
-      </c>
-      <c r="F137" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="9" t="n"/>
-      <c r="B138" s="10" t="n"/>
-      <c r="C138" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="D138" s="12" t="inlineStr">
-        <is>
-          <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr"/>
-      <c r="F138" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="9" t="n"/>
-      <c r="B139" s="15" t="inlineStr">
+      <c r="B165" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
         </is>
       </c>
-      <c r="C139" s="16" t="n">
-        <v>138</v>
-      </c>
-      <c r="D139" s="17" t="inlineStr">
+      <c r="C165" s="16" t="n">
+        <v>164</v>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 무슨 상품 추천해주지?</t>
         </is>
       </c>
-      <c r="E139" s="18" t="inlineStr">
+      <c r="E165" s="18" t="inlineStr">
         <is>
           <t>투자성향이 위험중립형인 이 고객에게는 적합성 허용 상한이 보통위험까지이므로, 그에 맞는 상품들을 확인하고 안내해 드리는 것이 핵심이에요. 이 고객의 적합성 허용 상한은 보통위험이며, 안내할 수 있는 상품 목록은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 보통위험, 최근 1년 4.8%, 채권형
@@ -5895,35 +6681,35 @@
 안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 허용 상한을 초과하여 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F139" s="20" t="inlineStr">
+      <c r="F165" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G139" s="18" t="inlineStr">
+      <c r="G165" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H139" s="18" t="inlineStr">
+      <c r="H165" s="18" t="inlineStr">
         <is>
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
-      <c r="I139" s="18" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="n"/>
-      <c r="B140" s="9" t="n"/>
-      <c r="C140" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="D140" s="17" t="inlineStr">
+      <c r="I165" s="18" t="inlineStr"/>
+    </row>
+    <row r="166" hidden="1">
+      <c r="A166" s="9" t="n"/>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D166" s="17" t="inlineStr">
         <is>
           <t>국고채 금리 어때?</t>
         </is>
       </c>
-      <c r="E140" s="18" t="inlineStr">
+      <c r="E166" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차 기준 국고채 금리는 국고채3년물과 국고채10년물의 변동 추이를 살펴보아야 해요. 2026년 8월 14일 종가 기준으로 국고채3년물은 3.795, 국고채10년물은 4.31로 나타나 있어요. 
 - KOSPI — 6977.94 (+11.5%)
@@ -5954,35 +6740,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F140" s="19" t="inlineStr">
+      <c r="F166" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G140" s="18" t="inlineStr">
+      <c r="G166" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H140" s="18" t="inlineStr">
+      <c r="H166" s="18" t="inlineStr">
         <is>
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I140" s="18" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="n"/>
-      <c r="B141" s="9" t="n"/>
-      <c r="C141" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="D141" s="17" t="inlineStr">
+      <c r="I166" s="18" t="inlineStr"/>
+    </row>
+    <row r="167" hidden="1">
+      <c r="A167" s="9" t="n"/>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="16" t="n">
+        <v>166</v>
+      </c>
+      <c r="D167" s="17" t="inlineStr">
         <is>
           <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
-      <c r="E141" s="18" t="inlineStr">
+      <c r="E167" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션)로는 위험도에 따라 초저위험 지켜드림, 저위험 알파드림·알파드림 II·알파드림 III, 중위험 뿔려드림·뿔려드림 II·뿔려드림 III, 고위험 모두드림·모두드림 II·모두드림 III 같은 상품들이 있어요. 2026년 8월 기준(수익률은 2026년 7월 30일 기준, 원리금보장 금리는 2026년 8월 기준)으로 각 포트폴리오의 구성과 1년 수익률을 살펴보면 다음과 같아요.
 - 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성, 1년 수익률 미표시
@@ -6000,382 +6786,382 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F141" s="19" t="inlineStr">
+      <c r="F167" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G141" s="18" t="inlineStr">
+      <c r="G167" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H141" s="18" t="inlineStr">
+      <c r="H167" s="18" t="inlineStr">
         <is>
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I141" s="18" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="n"/>
-      <c r="B142" s="9" t="n"/>
-      <c r="C142" s="16" t="n">
-        <v>141</v>
-      </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="I167" s="18" t="inlineStr"/>
+    </row>
+    <row r="168" hidden="1">
+      <c r="A168" s="9" t="n"/>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="16" t="n">
+        <v>167</v>
+      </c>
+      <c r="D168" s="17" t="inlineStr">
         <is>
           <t>대화 내용 요약해줘</t>
         </is>
       </c>
-      <c r="E142" s="18" t="inlineStr">
+      <c r="E168" s="18" t="inlineStr">
         <is>
           <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
         </is>
       </c>
-      <c r="F142" s="21" t="inlineStr">
+      <c r="F168" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본</t>
         </is>
       </c>
-      <c r="G142" s="18" t="inlineStr">
+      <c r="G168" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H142" s="18" t="inlineStr">
+      <c r="H168" s="18" t="inlineStr">
         <is>
           <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
         </is>
       </c>
-      <c r="I142" s="18" t="inlineStr">
+      <c r="I168" s="18" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="9" t="n"/>
-      <c r="B143" s="9" t="n"/>
-      <c r="C143" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="D143" s="17" t="inlineStr">
+    <row r="169" hidden="1">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="16" t="n">
+        <v>168</v>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E143" s="18" t="inlineStr">
+      <c r="E169" s="18" t="inlineStr">
         <is>
           <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
         </is>
       </c>
-      <c r="F143" s="21" t="inlineStr">
+      <c r="F169" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본</t>
         </is>
       </c>
-      <c r="G143" s="18" t="inlineStr">
+      <c r="G169" s="18" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H143" s="18" t="inlineStr">
+      <c r="H169" s="18" t="inlineStr">
         <is>
           <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
-      <c r="I143" s="18" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="9" t="n"/>
-      <c r="B144" s="9" t="n"/>
-      <c r="C144" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="I169" s="18" t="inlineStr"/>
+    </row>
+    <row r="170" hidden="1">
+      <c r="A170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="16" t="n">
+        <v>169</v>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
         <is>
           <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
-      <c r="E144" s="18" t="inlineStr">
+      <c r="E170" s="18" t="inlineStr">
         <is>
           <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
 자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
         </is>
       </c>
-      <c r="F144" s="19" t="inlineStr">
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G144" s="18" t="inlineStr">
+      <c r="G170" s="18" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="H144" s="18" t="inlineStr">
+      <c r="H170" s="18" t="inlineStr">
         <is>
           <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
-      <c r="I144" s="18" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="n"/>
-      <c r="B145" s="9" t="n"/>
-      <c r="C145" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="D145" s="17" t="inlineStr">
+      <c r="I170" s="18" t="inlineStr"/>
+    </row>
+    <row r="171" hidden="1">
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="16" t="n">
+        <v>170</v>
+      </c>
+      <c r="D171" s="17" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
-      <c r="E145" s="18" t="inlineStr">
+      <c r="E171" s="18" t="inlineStr">
         <is>
           <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F145" s="21" t="inlineStr">
+      <c r="F171" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G145" s="18" t="inlineStr">
+      <c r="G171" s="18" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H145" s="18" t="inlineStr">
+      <c r="H171" s="18" t="inlineStr">
         <is>
           <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="I145" s="18" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="n"/>
-      <c r="B146" s="9" t="n"/>
-      <c r="C146" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="D146" s="17" t="inlineStr">
+      <c r="I171" s="18" t="inlineStr"/>
+    </row>
+    <row r="172" hidden="1">
+      <c r="A172" s="9" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="16" t="n">
+        <v>171</v>
+      </c>
+      <c r="D172" s="17" t="inlineStr">
         <is>
           <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E146" s="18" t="inlineStr">
+      <c r="E172" s="18" t="inlineStr">
         <is>
           <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F146" s="21" t="inlineStr">
+      <c r="F172" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G146" s="18" t="inlineStr">
+      <c r="G172" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H146" s="18" t="inlineStr">
+      <c r="H172" s="18" t="inlineStr">
         <is>
           <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I146" s="18" t="inlineStr">
+      <c r="I172" s="18" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="9" t="n"/>
-      <c r="B147" s="10" t="n"/>
-      <c r="C147" s="16" t="n">
-        <v>146</v>
-      </c>
-      <c r="D147" s="17" t="inlineStr">
+    <row r="173" hidden="1">
+      <c r="A173" s="9" t="n"/>
+      <c r="B173" s="10" t="n"/>
+      <c r="C173" s="16" t="n">
+        <v>172</v>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
         <is>
           <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
         </is>
       </c>
-      <c r="E147" s="18" t="inlineStr">
+      <c r="E173" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
+      <c r="F173" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G147" s="18" t="inlineStr">
+      <c r="G173" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H147" s="18" t="inlineStr">
+      <c r="H173" s="18" t="inlineStr">
         <is>
           <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
-      <c r="I147" s="18" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="n"/>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="I173" s="18" t="inlineStr"/>
+    </row>
+    <row r="174" hidden="1">
+      <c r="A174" s="9" t="n"/>
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="D148" s="12" t="inlineStr">
+      <c r="C174" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
         <is>
           <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E174" s="6" t="inlineStr">
         <is>
           <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
 찾아본 곳: 상담 화법 「퇴직연금과 부동산 투자 비교 설명 및 설득 화법」 · 시황 자료 「퇴직연금과 부동산 투자 시장 현황 및 비교」 · 운용 상품 자료 「퇴직연금과 부동산 투자 비교」 · 관리 방법론 「퇴직연금과 부동산 투자 비교 판단 기준 및 장단점」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="F148" s="11" t="inlineStr">
+      <c r="F174" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G148" s="6" t="inlineStr">
+      <c r="G174" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="H174" s="6" t="inlineStr">
         <is>
           <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
         </is>
       </c>
-      <c r="I148" s="6" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="n"/>
-      <c r="B149" s="9" t="n"/>
-      <c r="C149" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="D149" s="12" t="inlineStr">
+      <c r="I174" s="6" t="inlineStr"/>
+    </row>
+    <row r="175" hidden="1">
+      <c r="A175" s="9" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E175" s="6" t="inlineStr">
         <is>
           <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
 찾아본 곳: 제도·상품 수치 「고객 평가금액」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="F149" s="14" t="inlineStr">
+      <c r="F175" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G149" s="6" t="inlineStr">
+      <c r="G175" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H149" s="6" t="inlineStr">
+      <c r="H175" s="6" t="inlineStr">
         <is>
           <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
         </is>
       </c>
-      <c r="I149" s="6" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="9" t="n"/>
-      <c r="B150" s="9" t="n"/>
-      <c r="C150" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="D150" s="12" t="inlineStr">
+      <c r="I175" s="6" t="inlineStr"/>
+    </row>
+    <row r="176" hidden="1">
+      <c r="A176" s="9" t="n"/>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
         <is>
           <t>IRP 중도인출 사유가 뭐야?</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E176" s="6" t="inlineStr">
         <is>
           <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
         </is>
       </c>
-      <c r="F150" s="13" t="inlineStr">
+      <c r="F176" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G150" s="6" t="inlineStr">
+      <c r="G176" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H150" s="6" t="inlineStr">
+      <c r="H176" s="6" t="inlineStr">
         <is>
           <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
         </is>
       </c>
-      <c r="I150" s="6" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="n"/>
-      <c r="B151" s="9" t="n"/>
-      <c r="C151" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="I176" s="6" t="inlineStr"/>
+    </row>
+    <row r="177" hidden="1">
+      <c r="A177" s="9" t="n"/>
+      <c r="B177" s="9" t="n"/>
+      <c r="C177" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>이 고객은 왜 타겟이 됐지?</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr">
         <is>
           <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
         </is>
       </c>
-      <c r="F151" s="13" t="inlineStr">
+      <c r="F177" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G151" s="6" t="inlineStr">
+      <c r="G177" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H151" s="6" t="inlineStr">
+      <c r="H177" s="6" t="inlineStr">
         <is>
           <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
-      <c r="I151" s="6" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="n"/>
-      <c r="B152" s="9" t="n"/>
-      <c r="C152" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="D152" s="12" t="inlineStr">
+      <c r="I177" s="6" t="inlineStr"/>
+    </row>
+    <row r="178" hidden="1">
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
         <is>
           <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E178" s="6" t="inlineStr">
         <is>
           <t>송도윤 고객님은 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 크게 상회하고 있지만, 6개월 이상 장기 미접촉 상태인 관리 사각지대 고객이에요. 현재 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식을 보유하고 계시며, 고유계정대 2억 8,000만원의 현금성자산이 방치되어 있고, 디폴트옵션 미설정 및 ISA 만기자금 1억 2,000만원을 보유하고 계셔요.
 - 고유계정대 — 2억 8,000만원 (수익률 0.0%)
@@ -6385,72 +7171,72 @@
 장기간 접촉 이력이 없어 타사 비교에 노출될 가능성이 있으므로, 유선 접촉을 통해 관계를 회복해야 합니다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 사용계획이 있는 자금은 먼저 걸러내며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F152" s="14" t="inlineStr">
+      <c r="F178" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G152" s="6" t="inlineStr">
+      <c r="G178" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H152" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
-      <c r="I152" s="6" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="n"/>
-      <c r="B153" s="10" t="n"/>
-      <c r="C153" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="D153" s="12" t="inlineStr">
+      <c r="I178" s="6" t="inlineStr"/>
+    </row>
+    <row r="179" hidden="1">
+      <c r="A179" s="9" t="n"/>
+      <c r="B179" s="10" t="n"/>
+      <c r="C179" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
         <is>
           <t>(고객 연 직후 첫 질문)</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="14" t="inlineStr">
+      <c r="E179" s="6" t="inlineStr"/>
+      <c r="F179" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G153" s="6" t="inlineStr">
+      <c r="G179" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H153" s="6" t="inlineStr">
+      <c r="H179" s="6" t="inlineStr">
         <is>
           <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
         </is>
       </c>
-      <c r="I153" s="6" t="inlineStr">
+      <c r="I179" s="6" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="9" t="n"/>
-      <c r="B154" s="15" t="inlineStr">
+    <row r="180" hidden="1">
+      <c r="A180" s="9" t="n"/>
+      <c r="B180" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
         </is>
       </c>
-      <c r="C154" s="16" t="n">
-        <v>153</v>
-      </c>
-      <c r="D154" s="17" t="inlineStr">
+      <c r="C180" s="16" t="n">
+        <v>179</v>
+      </c>
+      <c r="D180" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E154" s="18" t="inlineStr">
+      <c r="E180" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 ■ 제가 도와드릴 수 있는 것
@@ -6492,35 +7278,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F154" s="20" t="inlineStr">
+      <c r="F180" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="G154" s="18" t="inlineStr">
+      <c r="G180" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H154" s="18" t="inlineStr">
+      <c r="H180" s="18" t="inlineStr">
         <is>
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
         </is>
       </c>
-      <c r="I154" s="18" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="n"/>
-      <c r="B155" s="9" t="n"/>
-      <c r="C155" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="D155" s="17" t="inlineStr">
+      <c r="I180" s="18" t="inlineStr"/>
+    </row>
+    <row r="181" hidden="1">
+      <c r="A181" s="9" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="D181" s="17" t="inlineStr">
         <is>
           <t>이 고객 디폴트옵션 설정돼 있어?</t>
         </is>
       </c>
-      <c r="E155" s="18" t="inlineStr">
+      <c r="E181" s="18" t="inlineStr">
         <is>
           <t>● 박정호
 박정호 고객님은 현재 디폴트옵션 설정이 되어 있어요. 다만 이미 디폴트옵션(초저위험)을 등록·보유한 고객은 ⓐ 사전지정운용제도 등록/변경 → ⓑ 보유상품 변경(기존 매도 + 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요. 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 «현재 보유중이신 디폴트옵션(초저위험)은 정기예금만으로 구성되어 있습니다»라고 짚어 주세요.
@@ -6528,35 +7314,35 @@
 이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
         </is>
       </c>
-      <c r="F155" s="23" t="inlineStr">
+      <c r="F181" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G155" s="18" t="inlineStr">
+      <c r="G181" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H155" s="18" t="inlineStr">
+      <c r="H181" s="18" t="inlineStr">
         <is>
           <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
-      <c r="I155" s="18" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="9" t="n"/>
-      <c r="B156" s="9" t="n"/>
-      <c r="C156" s="16" t="n">
-        <v>155</v>
-      </c>
-      <c r="D156" s="17" t="inlineStr">
+      <c r="I181" s="18" t="inlineStr"/>
+    </row>
+    <row r="182" hidden="1">
+      <c r="A182" s="9" t="n"/>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="16" t="n">
+        <v>181</v>
+      </c>
+      <c r="D182" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E156" s="18" t="inlineStr">
+      <c r="E182" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 만기 도래 항목을 묻는 질문에 대해, 현재 2026년 10월 9일에 만기가 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품이 있어요. 그리고 2027년 1-10에 만기가 도래하는 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 3,550만원 상품이 있습니다.
@@ -6567,35 +7353,35 @@
 송도윤 고객님의 만기 내역은 2026년 9월 20일에 만기가 경과한 ISA 만기자금(IRP 외부) 1억 2,000만원이 있어요. 원장에 등록된 만기 항목은 해당 건이 전부이며, 다른 만기 건은 자료에 없어요.</t>
         </is>
       </c>
-      <c r="F156" s="23" t="inlineStr">
+      <c r="F182" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G156" s="18" t="inlineStr">
+      <c r="G182" s="18" t="inlineStr">
         <is>
           <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H156" s="18" t="inlineStr">
+      <c r="H182" s="18" t="inlineStr">
         <is>
           <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
         </is>
       </c>
-      <c r="I156" s="18" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="9" t="n"/>
-      <c r="B157" s="9" t="n"/>
-      <c r="C157" s="16" t="n">
-        <v>156</v>
-      </c>
-      <c r="D157" s="17" t="inlineStr">
+      <c r="I182" s="18" t="inlineStr"/>
+    </row>
+    <row r="183" hidden="1">
+      <c r="A183" s="9" t="n"/>
+      <c r="B183" s="9" t="n"/>
+      <c r="C183" s="16" t="n">
+        <v>182</v>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E157" s="18" t="inlineStr">
+      <c r="E183" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 및 환매추천 펀드인 KB 퇴직연금 배당 (주식)을 보유하고 계시고, 미운용 현금성자산이 있으며, 디폴트옵션이 미설정 상태이고, ISA 만기자금 보유와 운용변경이 12개월 이상 없었기 때문이에요. 추가로 관리 사각지대 고객이자 당해 납입이 없는 고객에 해당하며, 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시고 운용수익률은 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 계세요. 다만 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있는 상태예요.
@@ -6603,35 +7389,35 @@
 적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
         </is>
       </c>
-      <c r="F157" s="19" t="inlineStr">
+      <c r="F183" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G157" s="18" t="inlineStr">
+      <c r="G183" s="18" t="inlineStr">
         <is>
           <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
-      <c r="H157" s="18" t="inlineStr">
+      <c r="H183" s="18" t="inlineStr">
         <is>
           <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
-      <c r="I157" s="18" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="n"/>
-      <c r="B158" s="9" t="n"/>
-      <c r="C158" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="D158" s="17" t="inlineStr">
+      <c r="I183" s="18" t="inlineStr"/>
+    </row>
+    <row r="184" hidden="1">
+      <c r="A184" s="9" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="16" t="n">
+        <v>183</v>
+      </c>
+      <c r="D184" s="17" t="inlineStr">
         <is>
           <t>지난 상담에서 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E158" s="18" t="inlineStr">
+      <c r="E184" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 ※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담 기록에 따르면, 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 있어요.
@@ -6639,35 +7425,35 @@
 고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
         </is>
       </c>
-      <c r="F158" s="19" t="inlineStr">
+      <c r="F184" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G158" s="18" t="inlineStr">
+      <c r="G184" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
-      <c r="H158" s="18" t="inlineStr">
+      <c r="H184" s="18" t="inlineStr">
         <is>
           <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="I158" s="18" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="n"/>
-      <c r="B159" s="9" t="n"/>
-      <c r="C159" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="D159" s="17" t="inlineStr">
+      <c r="I184" s="18" t="inlineStr"/>
+    </row>
+    <row r="185" hidden="1">
+      <c r="A185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="16" t="n">
+        <v>184</v>
+      </c>
+      <c r="D185" s="17" t="inlineStr">
         <is>
           <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E159" s="18" t="inlineStr">
+      <c r="E185" s="18" t="inlineStr">
         <is>
           <t>● 이수민
 이수민 고객에게 개인형IRP 계좌에 300만원을 추가 납입할 때 예상되는 세액공제 환급액을 안내할 때는 총급여 구간과 세액공제 한도를 함께 짚어주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 한도 및 잔여한도가 900만원이므로, 300만원을 추가 납입하면 총급여 5,500만원 이하 기준 16.5%의 공제율을 적용하여 495,000원의 환급을 예상할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 이를 바탕으로 안내해 보세요.
@@ -6676,35 +7462,35 @@
 다만 ISA 만기자금을 개인형IRP 계좌로 전환하는 경우라면 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 별개의 축이에요. 300만원을 ISA 만기자금에서 개인형IRP로 전환할 때 적용되는 공제율에 따라 추가 공제 대상과 환급액이 달라질 수 있어요. 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 49,500원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않았으니 단말에서 고객의 총급여 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="F159" s="19" t="inlineStr">
+      <c r="F185" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G159" s="18" t="inlineStr">
+      <c r="G185" s="18" t="inlineStr">
         <is>
           <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H159" s="18" t="inlineStr">
+      <c r="H185" s="18" t="inlineStr">
         <is>
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
-      <c r="I159" s="18" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="n"/>
-      <c r="B160" s="9" t="n"/>
-      <c r="C160" s="16" t="n">
-        <v>159</v>
-      </c>
-      <c r="D160" s="17" t="inlineStr">
+      <c r="I185" s="18" t="inlineStr"/>
+    </row>
+    <row r="186" hidden="1">
+      <c r="A186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="16" t="n">
+        <v>185</v>
+      </c>
+      <c r="D186" s="17" t="inlineStr">
         <is>
           <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
         </is>
       </c>
-      <c r="E160" s="18" t="inlineStr">
+      <c r="E186" s="18" t="inlineStr">
         <is>
           <t>● 박지민
 고객의 소득 수준이나 종합소득금액 값이 자료에 나와 있지 않아 해당 고객의 세액공제율을 바로 확정해 말씀드리기는 어려워요. 2026년 6월 기준 자료에 따르면, 공제율은 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 경우 16.5%, 이를 초과하는 경우 13.2%가 적용돼요. 여기서 5,500만원 '이상'이 아니라 '초과'가 정확한 경계 표현이며, 5,500만원 정확히 일치하는 금액은 16.5% 구간에 해당한다는 점을 참고해 주세요. 단말에서 고객의 소득 조건을 먼저 확인하신 뒤에 안내를 이어가셔야 해요.
@@ -6712,35 +7498,35 @@
 총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
         </is>
       </c>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="F186" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G160" s="18" t="inlineStr">
+      <c r="G186" s="18" t="inlineStr">
         <is>
           <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
         </is>
       </c>
-      <c r="H160" s="18" t="inlineStr">
+      <c r="H186" s="18" t="inlineStr">
         <is>
           <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
         </is>
       </c>
-      <c r="I160" s="18" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="n"/>
-      <c r="B161" s="9" t="n"/>
-      <c r="C161" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="D161" s="17" t="inlineStr">
+      <c r="I186" s="18" t="inlineStr"/>
+    </row>
+    <row r="187" hidden="1">
+      <c r="A187" s="9" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="16" t="n">
+        <v>186</v>
+      </c>
+      <c r="D187" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E161" s="18" t="inlineStr">
+      <c r="E187" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금을 IRP로 옮겨 세액공제 혜택을 확인하는 고객에게는 만기금액의 전환에 따른 추가 공제 구조를 짚어 드리는 게 핵심이에요. 개인형IRP 계좌로 8,000만원을 전환할 때 이 금액은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이라, 8,000만원을 전환하면 추가 공제 대상은 300만원이 돼요. 총급여 5,500만원 이하 16.5% 기준으로 이 전환으로 늘어나는 환급 예상액은 495,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로 서로 다른 한도예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
@@ -6748,35 +7534,35 @@
 ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F161" s="19" t="inlineStr">
+      <c r="F187" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G161" s="18" t="inlineStr">
+      <c r="G187" s="18" t="inlineStr">
         <is>
           <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H161" s="18" t="inlineStr">
+      <c r="H187" s="18" t="inlineStr">
         <is>
           <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
-      <c r="I161" s="18" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="n"/>
-      <c r="B162" s="9" t="n"/>
-      <c r="C162" s="16" t="n">
-        <v>161</v>
-      </c>
-      <c r="D162" s="17" t="inlineStr">
+      <c r="I187" s="18" t="inlineStr"/>
+    </row>
+    <row r="188" hidden="1">
+      <c r="A188" s="9" t="n"/>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="D188" s="17" t="inlineStr">
         <is>
           <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
-      <c r="E162" s="18" t="inlineStr">
+      <c r="E188" s="18" t="inlineStr">
         <is>
           <t>● 박정호
 박정호 고객님은 연금개시 요건을 충족하였으나 아직 연금개시를 하지 않은 상태예요. 
@@ -6785,35 +7571,35 @@
 송도윤 고객님은 연금개시요건을 충족하지 않아 현재 연금개시를 하실 수 없어요. 자료에 따르면 연금개시 상태는 미개시이며 연금개시요건도 충족되지 않은 상태로 확인돼요.</t>
         </is>
       </c>
-      <c r="F162" s="19" t="inlineStr">
+      <c r="F188" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G162" s="18" t="inlineStr">
+      <c r="G188" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H162" s="18" t="inlineStr">
+      <c r="H188" s="18" t="inlineStr">
         <is>
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
-      <c r="I162" s="18" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="9" t="n"/>
-      <c r="C163" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="D163" s="17" t="inlineStr">
+      <c r="I188" s="18" t="inlineStr"/>
+    </row>
+    <row r="189" hidden="1">
+      <c r="A189" s="9" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
         <is>
           <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
-      <c r="E163" s="18" t="inlineStr">
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>● 최서윤
 최서윤 고객이 보유하고 있는 판매중단 상품은 KB 코리아밸류업액티브(주식)이다. 해당 상품은 920만원 규모로 보유 중이며 수익률은 -38.7%를 기록하고 있다. 판매중단 상품을 보유하고 있어 관리 공백이 우려되는 상황이므로, 보유 포트폴리오를 점검하고 매도 및 재추천 등의 액션을 안내하는 방향으로 접근해야 한다.
@@ -6821,35 +7607,35 @@
 판매중단된 보유상품은 없어요.</t>
         </is>
       </c>
-      <c r="F163" s="19" t="inlineStr">
+      <c r="F189" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G163" s="18" t="inlineStr">
+      <c r="G189" s="18" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H163" s="18" t="inlineStr">
+      <c r="H189" s="18" t="inlineStr">
         <is>
           <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
-      <c r="I163" s="18" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="9" t="n"/>
-      <c r="B164" s="9" t="n"/>
-      <c r="C164" s="16" t="n">
-        <v>163</v>
-      </c>
-      <c r="D164" s="17" t="inlineStr">
+      <c r="I189" s="18" t="inlineStr"/>
+    </row>
+    <row r="190" hidden="1">
+      <c r="A190" s="9" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="D190" s="17" t="inlineStr">
         <is>
           <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E164" s="18" t="inlineStr">
+      <c r="E190" s="18" t="inlineStr">
         <is>
           <t>● 정민석
 현재 보유한 자산이 예금 위주인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가는 게 핵심이에요. 원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 입증해야 하므로, 금리 갈아타기가 곧 관리라는 논리로 대응해 보세요. 다만 사용계획이 있는 자금은 먼저 걸러내고, 고객에게 생소한 고유계정대 같은 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 고객이 예금만 해서 관리가 필요 없다고 반응할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
@@ -6857,35 +7643,35 @@
 예금만 보유하고 있어 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 점을 짚어주는 게 핵심이에요. 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 같은 안전성 안에서 금리를 올려주는 제안으로 들어가야 해요. 고객이 사용계획이 있는 자금인지 먼저 확인하고, 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F164" s="19" t="inlineStr">
+      <c r="F190" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G164" s="18" t="inlineStr">
+      <c r="G190" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H164" s="18" t="inlineStr">
+      <c r="H190" s="18" t="inlineStr">
         <is>
           <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
-      <c r="I164" s="18" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="10" t="n"/>
-      <c r="B165" s="10" t="n"/>
-      <c r="C165" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="I190" s="18" t="inlineStr"/>
+    </row>
+    <row r="191" hidden="1">
+      <c r="A191" s="10" t="n"/>
+      <c r="B191" s="10" t="n"/>
+      <c r="C191" s="16" t="n">
+        <v>190</v>
+      </c>
+      <c r="D191" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E165" s="18" t="inlineStr">
+      <c r="E191" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 송도윤 고객에게는 지금 안내할 수 있는 세미나로 11/5(목) 16시에 진행되는 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 온라인 세미나가 있어요. 이 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어, 미운용 자금 및 디폴트옵션 제도를 다루는 해당 세미나를 안내합니다. 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX를 활용하시면 돼요. 고객에게 안내하실 때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 사용계획이 있는 자금이라면 먼저 걸러내고 접근하시는 게 핵심이에요. 참고로 다른 세미나 후보 4건인 연금개시 전 꼭 알아야 할 IRP 수령 방법, 예금만으로 괜찮을까? 퇴직연금 자산배분 전략, 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기, 금리 변화기, 퇴직연금 예금 만기 이후 운용 전략에 대해서는 아직 상세 안내 자료가 없어요.
@@ -6893,60 +7679,60 @@
 이 고객에게는 지금 요건에 맞는 안내 대상 세미나가 없어요. 다만 현재 열려 있는 세미나 중 날짜가 가장 가까운 것은 11/12(목) 17시에 KB국민은행 WM투자부에서 주관하는 «내 투자성향에 맞는 포트폴리오 찾기»예요. 이 콘텐츠는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋으나 이 고객의 요건과는 무관해요. 안내 시 참고할 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요. 다른 이벤트나 세미나 관련해서 다른 후보 콘텐츠들에 대한 상세 요건은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F165" s="19" t="inlineStr">
+      <c r="F191" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G165" s="18" t="inlineStr">
+      <c r="G191" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H165" s="18" t="inlineStr">
+      <c r="H191" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I165" s="18" t="inlineStr"/>
+      <c r="I191" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B127:B138"/>
-    <mergeCell ref="A127:A165"/>
+    <mergeCell ref="B141:B146"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B109:B112"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A103:A126"/>
     <mergeCell ref="B34:B40"/>
-    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="B129:B140"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="B154:B165"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B148:B153"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="B139:B147"/>
-    <mergeCell ref="B59:B63"/>
+    <mergeCell ref="A165:A191"/>
+    <mergeCell ref="B124:B128"/>
+    <mergeCell ref="A41:A93"/>
+    <mergeCell ref="B147:B150"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="B160:B162"/>
     <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B180:B191"/>
+    <mergeCell ref="A94:A140"/>
+    <mergeCell ref="A141:A164"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="B75:B81"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B77:B86"/>
-    <mergeCell ref="B116:B121"/>
-    <mergeCell ref="B103:B108"/>
     <mergeCell ref="A2:A40"/>
-    <mergeCell ref="A41:A76"/>
+    <mergeCell ref="B174:B179"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B118:B123"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="B18:B26"/>
+    <mergeCell ref="B65:B74"/>
+    <mergeCell ref="B165:B173"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B6:B17"/>
+    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B94:B110"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B92:B97"/>
-    <mergeCell ref="B18:B26"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="A77:A102"/>
-    <mergeCell ref="B98:B102"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B6:B17"/>
-    <mergeCell ref="B49:B58"/>
+    <mergeCell ref="B154:B159"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -2469,7 +2469,24 @@
           <t>IRP에서 살 수 있는 상품이 뭐뭐야?</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>그 부분은 제가 가진 자료로는 확인이 어려워요. 다만 2026년 8월 기준으로 IRP 등 퇴직연금에서 참고할 수 있는 디폴트옵션 추천펀드와 포트폴리오 자료는 다음과 같이 확인할 수 있어요.
+- 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성된 원리금보장형 포트폴리오
+- 알파드림 — 저위험, 수협은행 노후보장 정기예금 70 및 TDF 30으로 구성된 포트폴리오
+- 알파드림 II — 저위험, 기업은행 정기예금 50 및 TDF 50으로 구성된 포트폴리오
+- 알파드림 III — 저위험, 농협은행 정기예금 및 DB손해보험 이율보증형보험 70과 TDF 30으로 구성된 포트폴리오
+- 뿔려드림 — 중위험, 하나은행 정기예금 30 및 TDF 70으로 구성된 포트폴리오
+- 뿔려드림 II — 중위험, 미래에셋평생소득 TIF 등 EMP 자산배분형 펀드 포트폴리오
+- 뿔려드림 III — 중위험, KB라이프생명 이율보증형보험 20 및 KB드림스타자산배분안정형 80으로 구성된 포트폴리오
+- 모두드림 — 고위험, TDF 100으로 구성된 포트폴리오
+- 모두드림 II — 고위험, 액티브 TDF 100으로 구성된 포트폴리오
+- 모두드림 III — 고위험, 미래에셋디폴트전략배분성장형 자산배분형 BF 포트폴리오
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 기준 표기입니다.</t>
+        </is>
+      </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3094,7 +3111,11 @@
           <t>추가납입 권유하기 전에 뭘 먼저 확인하고 들어가야 해?</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>추가납입을 권유하기 전에, 이 고객의 당해 납입액이 0원이며 예상 세액공제액과 세액공제 잔여한도가 모두 0원으로 확인되는지 단말에서 먼저 살펴봐야 해요. 추가납입 여력을 살피는 과정에서는 사용계획이 있는 자금인지 확인하는 단계를 먼저 거쳐야 한다는 점을 염두에 두시면 좋아요.</t>
+        </is>
+      </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -3123,7 +3144,12 @@
           <t>수수료 불만 들었는데 상담 전에 뭘 준비해야 해?</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>그 부분은 제가 가진 자료로는 수수료 불만에 대한 구체적인 대응 지침을 확인하기 어려워요. 대신 현재 고객님은 고유계정대 금리가 더 높다던데요 같은 반론이나 디폴트옵션 거부 반응에 대비한 대응 논리를 활용하실 수 있어요. 
+상담을 준비하실 때는 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 설명하는 방향으로 준비해 보세요. 또한 사용계획이 있는 자금인지 먼저 확인하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주시는 것이 좋아요.</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -3152,7 +3178,11 @@
           <t>정기예금 중도해지하면 손실이 얼마인지 어떻게 확인해?</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>정기예금 중도해지 예상 손실금액은 「정기예금 중도해지 &amp; 리밸런싱 계산기」를 통해 산출할 수 있어요. 진입 경로는 1번 Info-zone의 연금(퇴직연금) 안 계산기 메뉴를 이용하시거나 [04-12-642] 화면 하단의 연계메뉴에서 바로 클릭하시면 돼요. 계산할 때는 예상이율을 현재 보유상품 이율로 변경한 뒤 조회해야 하며, 그 결과는 참고용이라는 점을 미리 안내해 드릴게요.</t>
+        </is>
+      </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -567,8 +567,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I194"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2004,7 +2004,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ. 상담 중 — 지식 질의응답(주 기능)</t>
+          <t>Ⅱ. 상담 중 — 지식 질의응답</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr"/>
     </row>
-    <row r="53">
+    <row r="53" hidden="1">
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="4" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr"/>
     </row>
-    <row r="54">
+    <row r="54" hidden="1">
       <c r="A54" s="9" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="4" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr"/>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71" s="9" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="4" t="n">
@@ -3211,7 +3211,11 @@
           <t>퇴직소득세는 어떻게 계산해?</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr"/>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>퇴직소득세는 개인형IRP 연금지급 화면인 [02-12-221]에서 입사일자, 중간정산특례 적용 여부, 퇴직일자, 퇴직금액을 입력해 계산하는 것이 핵심이에요. 2026년 기준시점으로, 해당 화면에 나오는 표시 금액은 순수 퇴직소득세이므로 지방소득세 10%를 별도로 더해 고객 안내 총 세액은 표시액의 1.1배로 계산해야 해요. 중간정산특례 적용 여부에 따른 세금 차이도 함께 비교할 수 있으니 참고해 주세요. 근속연수가 짧을수록, 퇴직급여가 많을수록 퇴직소득세가 커진다. 본부 제시 매트릭스(발췌) — 1억·5년 1,036만원(10%) / 1억·10년 426만원(4%) / 2억·10년 1,966만원(10%) / 2억·20년 773만원(4%) / 5억·10년 9,781만원(20%). 원문 각주가 "실제 부과 세액은 다소 상이할 수 있음"을 명시하므로 확정 세액으로 안내하지 말고, 정확한 세액은 홈택스 모의계산 또는 [02-12-221] 시뮬레이션(F46)으로 계산한다. 기준시점 2026</t>
+        </is>
+      </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3240,7 +3244,11 @@
           <t>타사 연금 납입정보는 어떻게 확인해?</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>타사 연금 납입정보를 파악할 때 활용할 수 있는 두 가지 경로를 안내해 드릴게요. 먼저 고객이 스타뱅킹에서 생활제휴, 국민지갑, 전자증명서 순으로 이동해 「연금보험료 등 소득·세액공제 확인서」를 전송하면, 직원은 [06-7E-001] 화면에서 문서열람번호로 출력할 수 있어요. 또는 [06-10-182] 화면의 연금납입정보 집중 조회 및 정정청구등록(해제) 메뉴를 통해 연금납입정보 현황을 직접 조회하는 방법도 있어요. 이 두 번째 조회 경로를 이용하실 때는 금융거래정보제공요청동의서를 반드시 징구해야 하니 유의해 주세요.</t>
+        </is>
+      </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3412,7 +3420,11 @@
           <t>적립금이랑 수익률 조회는 몇 번 화면이야?</t>
         </is>
       </c>
-      <c r="E79" s="18" t="inlineStr"/>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>적립금과 수익률을 조회하실 때는 [04-12-642] 화면을 활용하시면 돼요. 해당 화면은 전일자 보유상품, 평가금액, 수익률 조회 및 고유계정대 이자조회를 하실 수 있는 화면이에요.</t>
+        </is>
+      </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -3441,7 +3453,11 @@
           <t>수수료 예상조회 화면번호 알려줘</t>
         </is>
       </c>
-      <c r="E80" s="18" t="inlineStr"/>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>문의하신 수수료 예상조회 화면번호는 [04-12-613]이에요. 해당 화면은 수수료 미납이나 납입 내역 및 예상 조회를 할 수 있고 계좌별 수수료 정보를 확인할 수 있는 화면이에요. 업무에 참고해 주세요.</t>
+        </is>
+      </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3470,7 +3486,11 @@
           <t>고객 거래내역은 어느 화면에서 봐?</t>
         </is>
       </c>
-      <c r="E81" s="18" t="inlineStr"/>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>고객 거래내역은 [04-12-644] 화면에서 확인하실 수 있어요. 해당 화면은 현금성자산 유입사유, 부담금입금내역, 입금내역 등을 조회할 수 있는 거래내역 조회 화면이에요.</t>
+        </is>
+      </c>
       <c r="F81" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3603,7 +3623,11 @@
           <t>고객이 앱에서 자기 수익률이랑 보유상품 보려면 어느 메뉴야?</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr"/>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>고객이 앱이나 인터넷으로 직접 수익률과 보유상품을 확인하실 수 있도록 안내할 때는 KB스타뱅킹과 인터넷뱅킹 경로를 활용해 주시면 좋아요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 나의 퇴직연금 순으로 이동해 보유상품 수익률을 점검하실 수 있어요. 인터넷뱅킹을 이용하신다면 KB퇴직연금의 개인고객 메뉴에서 My퇴직연금의 수익률과 평가금액조회 항목을 통해 확인하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -3632,7 +3656,14 @@
           <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>어떤 운용상품 종류의 조회 방법을 찾으시는가요?
+· 운용상품 전체 (운용상품 찾기)
+· ETF 상품
+· 디폴트옵션 상품</t>
+        </is>
+      </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3661,7 +3692,11 @@
           <t>고객이 추가입금 예약을 직접 걸 수 있어?</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr"/>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>고객이 추가입금 예약을 직접 진행하실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 짚어드릴 수 있어요. KB스타뱅킹을 이용하신다면 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로를 통해 진행하실 수 있고, 인터넷뱅킹을 이용하신다면 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로를 통해 처리하실 수 있어요. 다만 이용 시간의 경우 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지만 가능하니 이 점을 미리 안내해 드리는 것이 좋아요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -3963,7 +3998,7 @@
       </c>
       <c r="I95" s="6" t="inlineStr"/>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
@@ -4073,7 +4108,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr"/>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="4" t="n">
@@ -4108,7 +4143,7 @@
       </c>
       <c r="I99" s="6" t="inlineStr"/>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="4" t="n">
@@ -4146,7 +4181,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr"/>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="4" t="n">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="I101" s="6" t="inlineStr"/>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="9" t="n"/>
       <c r="C102" s="4" t="n">
@@ -4220,7 +4255,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr"/>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" s="9" t="n"/>
       <c r="B103" s="9" t="n"/>
       <c r="C103" s="4" t="n">
@@ -4253,7 +4288,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr"/>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
@@ -4264,7 +4299,11 @@
           <t>고객이 '생각 좀 해볼게요' 하고 미루는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr"/>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>고객이 망설일 때는 즉답을 압박하지 않고 생각할 시간의 정당성을 먼저 인정해 주는 방식으로 접근해야 해요. 당장 결정을 재촉하기보다 고객이 스스로 상품 정보를 찾아볼 수 있도록 안내하는 것이 좋아요. "아무래도 많이 운용해보신 상품이 아니라 생각하실 시간이 필요하실 거에요. 궁금한 점 있으시면 언제든지 연락 주시고, 인터넷뱅킹 또는 스타뱅킹을 통해서도 관련상품에 대한 정보를 찾아보실 수 있으니 참고해주세요"라고 안내해 드려 보세요.</t>
+        </is>
+      </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -4282,7 +4321,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr"/>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" s="9" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
@@ -4293,7 +4332,12 @@
           <t>고객이 '지금 쓸 돈도 없어요' 하는데 뭐라고 해?</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>지금 쓸 돈이 없다고 말씀하시는 고객에게는 IRP가 매달 의무적으로 일정 금액을 납입해야 하는 상품이 아니라는 점을 안내하여 부담을 덜어드리는 것이 핵심이에요. 여유가 있는 달에만 넣고 부담되는 달에는 쉬어가면서 원할 때만 입금하면 된다는 점을 설명하면서 큰 금액보다는 '시작하는 습관'을 강조하는 방식으로 접근할 수 있어요. 
+상담 과정에서 고객이 적금을 따로 가입하겠다고 말씀하신다면 "IRP는 매달 무조건 일정 금액을 입금해야하는 상품이 아닙니다. 여유가 있는 달에 넣고, 부담되는 달에는 쉬어가면서 원할때만 입금하시면 됩니다."라고 안내해 보세요. 이어지는 대응으로는 "적금은 만기이자에 이자소득세가 차감되는 반면, IRP는 예금, 펀드 등 운용수익에 대해 세금을 하나도 차감하지 않아요. 또 연말정산, 종합소득세 신고때 세액공제까지 된답니다."라는 내용을 활용하실 수 있어요.</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -4311,7 +4355,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr"/>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106" s="9" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
@@ -4322,7 +4366,11 @@
           <t>고객이 '나중에 돈 못 빼는 거 아니에요?' 하는데 뭐라고 설명하지?</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>IRP 가입 시 중도인출에 대한 우려를 표하는 고객에게는 법적 요건을 충족하면 언제든 인출이 가능하다는 점을 설명하고, 자산을 균형 있게 나누어 운용하는 방식을 안내하는 것이 좋아요. IRP는 노후 대비를 위한 계좌이지만 무주택자의 주택 구입이나 전세금 및 임차보증금 마련 등 법정 사유가 있을 때 중도인출이 가능하므로, 고객이 가진 자금 유동성에 대한 불안을 먼저 덜어줄 수 있어요. 또한 고객의 전체 자산을 전부 IRP에 넣으라는 것이 아니라는 점을 짚어 주면서, "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."라고 말씀해 보세요. IRP의 절세 혜택과 안정성을 함께 챙길 수 있도록 유도하는 화법이에요.</t>
+        </is>
+      </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -4340,7 +4388,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr"/>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
@@ -4351,7 +4399,13 @@
           <t>고객이 '회사에서 알아서 해주는 거 아니냐'고 하는데?</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>그 부분은 제가 가진 자료로는 확인이 어려워요. 다만 바쁜 일상 속에서 직접 관리해야 하는 번거로움을 느끼는 고객에게는 자동화 기능을 통해 부담을 덜어드리는 방식을 활용할 수 있어요. 
+「충분히 그렇게 느끼실 수 있습니다. 바쁜 일상에서 운용 중인 상품을 관리해야 하는 일은 보통 일이 아니죠. 정기적으로 보험료 납입하시는 것처럼 IRP로 자동이체와 자동매수 설정을 해놓으시면 편하게 관리 가능합니다.」
+「그 부분은 전혀 걱정하지 않으셔도 됩니다. 기존 상품이 만기가 도래해도 알아서 상품이 매수되는 디폴트옵션 설정도 도와드릴게요. 한번 설정해놓으시면 기존 연금보험처럼 신경 쓰실 필요 없이 알아서 운용될 거에요.」</t>
+        </is>
+      </c>
       <c r="F107" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -4369,7 +4423,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr"/>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" s="9" t="n"/>
       <c r="B108" s="9" t="n"/>
       <c r="C108" s="4" t="n">
@@ -4380,7 +4434,15 @@
           <t>고객이 '직접 관리하기 귀찮다'고 하는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>직접 관리하기 귀찮다는 고객에게는 전문가의 추천이나 자동화된 운용 방식을 제안하여 선택의 부담을 덜어주는 방향으로 접근하는 것이 핵심이에요.
+펀드 선택에 어려움을 겪는 고객에게는 전문가들로 구성된 상품선정 및 자산배분 회의를 거쳐 매월 추천 펀드와 포트폴리오를 제공하고 있다는 점을 안내할 수 있어요. 
+이때 활용할 수 있는 화법은 다음과 같아요.
+"국민은행에서는 전문가들로 구성된 상품선정 및 자산배분 회의를 통해 매월 고객님들께 개별펀드와 포트폴리오상품을 추천해드리고 있어요. 그중에 고객님의 투자성향과 관심분야 등에 맞는 상품을 골라 운용해 보시는건 어떠실까요?"
+직접 운용이 어려운 고객에게는 디폴트옵션이나 TDF 외의 제3 선택지로 AI투자일임 서비스를 안내해 드릴 수 있어요. KB국민은행 개인형IRP 보유 고객은 제휴 투자일임사 3곳인 디셈버앤컴퍼니, 미래에셋자산운용, 한국투자신탁운용의 로보어드바이저에 운용을 맡길 수 있어요. 다만 이 서비스를 안내하실 때는 1인 1계좌 제한, 연금 수령을 시작한 고객·미성년자·외국인 제외, 전 운용사 합산 연 900만원의 투자 한도, 퇴직연금 수수료 외 별도 일임 보수 발생, 원금 비보장 등의 제약 사항을 함께 확인해 주셔야 해요. 아울러 운용 중에는 타기관 이전, 연금 지급, 중도인출, 해지가 제한되며 일임계약 해지 후에만 가능하다는 점과 투자성향이 안정형이면 진행이 어려울 수 있다는 점도 미리 짚어드릴 필요가 있어요.</t>
+        </is>
+      </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -4398,7 +4460,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr"/>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" s="9" t="n"/>
       <c r="B109" s="9" t="n"/>
       <c r="C109" s="4" t="n">
@@ -4409,7 +4471,14 @@
           <t>고객이 '수익률은 다른 은행이 더 좋던데요' 하면 뭐라고 답해?</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr"/>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>고객이 수익률 불만을 제기할 때는 2026년 1분기 금융감독원 발표 공시 자료를 근거로 내세워 단기 성과 중심의 비교에서 장기 관리의 중요성으로 설명을 유도하는 게 핵심이에요. 
+수익률 반론에는 금융감독원 공시를 바탕으로 당행의 성과를 객관적으로 짚어드려야 하니, "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀해 보세요. 
+이어서 퇴직연금 디폴트옵션 고위험 포트폴리오의 구체적인 성과를 들어 설명의 설득력을 높여야 하니, "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요. 
+다만 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하거나 예측하는 표현은 쓰지 않도록 주의가 필요해요. 사용 계획이 있는 자금인 경우 사전에 걸러내야 한다는 점도 함께 염두에 두고 상담을 진행해 보세요. 그 외에 추가로 확인이 필요한 사항은 제가 가진 자료로는 확인이 어려워요.</t>
+        </is>
+      </c>
       <c r="F109" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -4438,7 +4507,13 @@
           <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr"/>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>상담 목적과 오프너 유형 중 어떤 방식을 원하시나요?
+· 중립적 용건으로 열기 (수익률 관리 해피콜)
+· 침묵을 유도하는 질문으로 열기 (IRP 수익률)</t>
+        </is>
+      </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -4719,7 +4794,16 @@
           <t>이 고객 성향으로 안내 못 하는 건 뭐고 왜 그런 거야?</t>
         </is>
       </c>
-      <c r="E116" s="18" t="inlineStr"/>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>위험중립형 성향인 이 고객에게 안내할 수 있는 상품 위험등급 상한은 보통위험이에요. 안내할 수 없는 상품들은 모두 허용 상한을 초과하여 다음의 상품들이 해당돼요.
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험
+이 안내는 고객의 투자성향에 따른 적합성 확인 결과이며 특정 상품에 대한 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -4748,7 +4832,26 @@
           <t>이 고객 위험등급 상한이 어디까지야?</t>
         </is>
       </c>
-      <c r="E117" s="18" t="inlineStr"/>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>이 고객에게 안내할 수 있는 투자성향 허용 상한은 보통위험까지예요. 적합성 확인 결과 이 등급까지의 상품만 안내할 수 있으니 참고해 주세요. 
+안내할 수 있는 상품은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB 중립형 MP — 보통위험 · 최근 1년 5.1% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+안내할 수 없는 상품은 허용 상한을 초과하여 다음의 위험등급으로 구성되어 있어요.
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험
+이 안내는 적합성 확인 결과이며 투자권유가 아니에요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
       <c r="F117" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -5565,32 +5668,34 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>(제안 뒤) 아니, 됐어</t>
+          <t>(채널 되묻기 뒤) ETF 상품</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
-        </is>
-      </c>
-      <c r="F137" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>어느 채널에서 조회하는 경로를 안내해 드릴까요?
+· KB스타뱅킹
+· 인터넷뱅킹</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
+          <t>고른 갈래의 채널 경로만 ↔ 세 갈래를 다 쏟거나 되묻기를 또 한다</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+          <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
         </is>
       </c>
     </row>
@@ -5602,17 +5707,13 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F138" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>(오프너 되묻기 뒤) 중립적 용건으로 열기</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr"/>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -5622,12 +5723,12 @@
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
+          <t>고른 오프너의 첫 마디 대사 ↔ 고르지 않은 쪽을 답하거나 일반론으로 돌아간다</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
+          <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
         </is>
       </c>
     </row>
@@ -5639,119 +5740,193 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>(첫 턴) 네</t>
+          <t>(제안 뒤) 아니, 됐어</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
         </is>
       </c>
       <c r="F139" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
-        </is>
-      </c>
-      <c r="I139" s="6" t="inlineStr"/>
-    </row>
-    <row r="140" hidden="1">
-      <c r="A140" s="10" t="n"/>
-      <c r="B140" s="10" t="n"/>
+          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="9" t="n"/>
       <c r="C140" s="4" t="n">
         <v>139</v>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
+          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="n"/>
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>(첫 턴) 네</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr"/>
+    </row>
+    <row r="142" hidden="1">
+      <c r="A142" s="10" t="n"/>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
           <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="14" t="inlineStr">
+      <c r="E142" s="6" t="inlineStr"/>
+      <c r="F142" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr">
+      <c r="G142" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="H142" s="6" t="inlineStr">
         <is>
           <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
+      <c r="I142" s="6" t="inlineStr">
         <is>
           <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Ⅳ. 상담 후 · 그 밖</t>
         </is>
       </c>
-      <c r="B141" s="15" t="inlineStr">
+      <c r="B143" s="15" t="inlineStr">
         <is>
           <t>18. 안내 콘텐츠·발송</t>
         </is>
       </c>
-      <c r="C141" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="D141" s="17" t="inlineStr">
+      <c r="C143" s="16" t="n">
+        <v>142</v>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
-      <c r="E141" s="18" t="inlineStr">
+      <c r="E143" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 안내할 만한 이벤트와 세미나는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있고 디폴트옵션이 미설정된 상태이므로 잠자는 IRP 자금 깨우기 운용 이벤트와 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나를 안내하는 것이 핵심이에요.
 잠자는 IRP 자금 깨우기 운용 이벤트는 12/30까지 KB스타뱅킹에서 진행되며, 고객이 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 상태이므로 참고하시기 좋고 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX를 활용할 수 있어요.
 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나는 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 온라인 세미나로, 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어 추천하며 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX로 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="F141" s="20" t="inlineStr">
+      <c r="F143" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G141" s="18" t="inlineStr">
+      <c r="G143" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H141" s="18" t="inlineStr">
+      <c r="H143" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
-      <c r="I141" s="18" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="n"/>
-      <c r="B142" s="9" t="n"/>
-      <c r="C142" s="16" t="n">
-        <v>141</v>
-      </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="I143" s="18" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="16" t="n">
+        <v>143</v>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>왜 이 이벤트를 고른 거야?</t>
         </is>
       </c>
-      <c r="E142" s="18" t="inlineStr">
+      <c r="E144" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 잠자는 IRP 자금 깨우기 운용 이벤트를 안내하는 이유는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 성립 요건을 충족하기 때문이에요. 고객이 최종 운용변경 이후 장기간 운용되지 않은 자금을 보유하고 있어 운용상품을 선택하거나 변경할 수 있도록 이벤트를 권유할 수 있어요. 안내 시 참고할 발송 문구는 다음과 같아요.
 (광고) 송도윤 고객님, KB국민은행입니다.
@@ -5760,39 +5935,39 @@
 무료수신거부 080-XXX-XXXX</t>
         </is>
       </c>
-      <c r="F142" s="23" t="inlineStr">
+      <c r="F144" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G142" s="18" t="inlineStr">
+      <c r="G144" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H142" s="18" t="inlineStr">
+      <c r="H144" s="18" t="inlineStr">
         <is>
           <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
         </is>
       </c>
-      <c r="I142" s="18" t="inlineStr">
+      <c r="I144" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="9" t="n"/>
-      <c r="B143" s="9" t="n"/>
-      <c r="C143" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="D143" s="17" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="16" t="n">
+        <v>144</v>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
         </is>
       </c>
-      <c r="E143" s="18" t="inlineStr">
+      <c r="E145" s="18" t="inlineStr">
         <is>
           <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기
 화면이 열리면 이 문구를 넣어 주세요 — "(광고) 송도윤 고객님, KB국민은행입니다.
@@ -5801,78 +5976,78 @@
 무료수신거부 080-XXX-XXXX"</t>
         </is>
       </c>
-      <c r="F143" s="20" t="inlineStr">
+      <c r="F145" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G143" s="18" t="inlineStr">
+      <c r="G145" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H143" s="18" t="inlineStr">
+      <c r="H145" s="18" t="inlineStr">
         <is>
           <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
         </is>
       </c>
-      <c r="I143" s="18" t="inlineStr">
+      <c r="I145" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="9" t="n"/>
-      <c r="B144" s="9" t="n"/>
-      <c r="C144" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
         </is>
       </c>
-      <c r="E144" s="18" t="inlineStr">
+      <c r="E146" s="18" t="inlineStr">
         <is>
           <t>이 고객에게 안내할 이벤트와 세미나의 발송 문구는 자료에 있는 문구를 그대로 활용하는 게 핵심이에요. 
 잠자는 IRP 자금 깨우기 운용 이벤트 발송 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX"를 그대로 사용해 주세요.
 온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
         </is>
       </c>
-      <c r="F144" s="19" t="inlineStr">
+      <c r="F146" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G144" s="18" t="inlineStr">
+      <c r="G146" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H144" s="18" t="inlineStr">
+      <c r="H146" s="18" t="inlineStr">
         <is>
           <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
         </is>
       </c>
-      <c r="I144" s="18" t="inlineStr">
+      <c r="I146" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="9" t="n"/>
-      <c r="B145" s="9" t="n"/>
-      <c r="C145" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="D145" s="17" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="9" t="n"/>
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="16" t="n">
+        <v>146</v>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
         <is>
           <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
-      <c r="E145" s="18" t="inlineStr">
+      <c r="E147" s="18" t="inlineStr">
         <is>
           <t>앞서 말씀드린 2건 외에 잠재적 안내 후보로 열려 있는 이벤트 3건과 세미나 4건이 더 있어요.
 이벤트 3건은 다음과 같아요.
@@ -5887,76 +6062,76 @@
 고객에게 안내할 때는 사용계획이 있는 자금인지 먼저 확인하고 활용할 수 있는 방법을 살펴보세요. 세부적인 발송 문구나 링크가 필요한 항목이 있다면 이어서 말씀해 드릴게요.</t>
         </is>
       </c>
-      <c r="F145" s="19" t="inlineStr">
+      <c r="F147" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G145" s="18" t="inlineStr">
+      <c r="G147" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H145" s="18" t="inlineStr">
+      <c r="H147" s="18" t="inlineStr">
         <is>
           <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
         </is>
       </c>
-      <c r="I145" s="18" t="inlineStr">
+      <c r="I147" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="146" hidden="1">
-      <c r="A146" s="9" t="n"/>
-      <c r="B146" s="10" t="n"/>
-      <c r="C146" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="D146" s="17" t="inlineStr">
+    <row r="148" hidden="1">
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="10" t="n"/>
+      <c r="C148" s="16" t="n">
+        <v>147</v>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E146" s="18" t="inlineStr">
+      <c r="E148" s="18" t="inlineStr">
         <is>
           <t>현재 이 고객의 요건에 맞는 세미나는 아직 준비된 자료가 없어요. 다만 열려 있는 콘텐츠 중 날짜가 가까운 세미나로는 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 세미나가 11/12(목) 17시에 KB국민은행 WM투자부 주관으로 예정되어 있어요. 이 세미나는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋은 내용이에요. 안내할 때 참고할 수 있는 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요.</t>
         </is>
       </c>
-      <c r="F146" s="19" t="inlineStr">
+      <c r="F148" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G146" s="18" t="inlineStr">
+      <c r="G148" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H146" s="18" t="inlineStr">
+      <c r="H148" s="18" t="inlineStr">
         <is>
           <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I146" s="18" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="9" t="n"/>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="I148" s="18" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
         </is>
       </c>
-      <c r="C147" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="C149" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
         <is>
           <t>대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>[제목] 송도윤 고객 관리 대상 사유 및 대응 방향
 송도윤 고객은 최근 358일간 접촉 이력이 없어 타사 비교 견적 노출 가능성이 있습니다.
@@ -5966,120 +6141,46 @@
 (아래에 이 고객의 연령·투자성향·평가금액·수익률·연금개시·세액공제 잔여한도·관리 사유 표가 붙습니다)</t>
         </is>
       </c>
-      <c r="F147" s="7" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G147" s="6" t="inlineStr">
+      <c r="G149" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H147" s="6" t="inlineStr">
+      <c r="H149" s="6" t="inlineStr">
         <is>
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="I147" s="6" t="inlineStr">
+      <c r="I149" s="6" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="9" t="n"/>
-      <c r="B148" s="9" t="n"/>
-      <c r="C148" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="D148" s="12" t="inlineStr">
-        <is>
-          <t>(쪽지 초안 뒤) 응, 보내줘</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H148" s="6" t="inlineStr">
-        <is>
-          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
-        </is>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="n"/>
-      <c r="B149" s="9" t="n"/>
-      <c r="C149" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="D149" s="12" t="inlineStr">
-        <is>
-          <t>지금까지 얘기한 거 정리해줘</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
-        </is>
-      </c>
-      <c r="F149" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
-        </is>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
+    <row r="150" hidden="1">
       <c r="A150" s="9" t="n"/>
-      <c r="B150" s="10" t="n"/>
+      <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
+          <t>(쪽지 초안 뒤) 응, 보내줘</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
-        </is>
-      </c>
-      <c r="F150" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6089,93 +6190,200 @@
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
-        </is>
-      </c>
-      <c r="I150" s="6" t="inlineStr"/>
+          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="9" t="n"/>
-      <c r="B151" s="15" t="inlineStr">
-        <is>
-          <t>20. 브리핑 수정</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="n">
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D151" s="17" t="inlineStr">
-        <is>
-          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
-        </is>
-      </c>
-      <c r="E151" s="18" t="inlineStr">
-        <is>
-          <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="F151" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
-        </is>
-      </c>
-      <c r="G151" s="18" t="inlineStr">
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>지금까지 얘기한 거 정리해줘</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
+        </is>
+      </c>
+      <c r="F151" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H151" s="18" t="inlineStr">
-        <is>
-          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
-        </is>
-      </c>
-      <c r="I151" s="18" t="inlineStr"/>
-    </row>
-    <row r="152">
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" hidden="1">
       <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
-      <c r="C152" s="16" t="n">
+      <c r="C152" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="D152" s="17" t="inlineStr">
-        <is>
-          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
-        </is>
-      </c>
-      <c r="E152" s="18" t="inlineStr">
-        <is>
-          <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="F152" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
-        </is>
-      </c>
-      <c r="G152" s="18" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
+        </is>
+      </c>
+      <c r="F152" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H152" s="18" t="inlineStr">
-        <is>
-          <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
-        </is>
-      </c>
-      <c r="I152" s="18" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="n"/>
       <c r="B153" s="10" t="n"/>
-      <c r="C153" s="16" t="n">
+      <c r="C153" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="D153" s="17" t="inlineStr">
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>(쪽지 초안 뒤) 응, 사번 3902172한테 보내줘</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr"/>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>받는 사람이 본인이 아니라 그 사번으로 바뀌고 화면에 밝힌다 ↔ 사번을 금액으로 읽어 본인에게 보낸다 · 사번을 못 읽었는데 「보냈다」고 답한다</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" hidden="1">
+      <c r="A154" s="9" t="n"/>
+      <c r="B154" s="15" t="inlineStr">
+        <is>
+          <t>20. 브리핑 수정</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="n">
+        <v>153</v>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F154" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr"/>
+    </row>
+    <row r="155" hidden="1">
+      <c r="A155" s="9" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="16" t="n">
+        <v>154</v>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F155" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr">
+        <is>
+          <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr"/>
+    </row>
+    <row r="156" hidden="1">
+      <c r="A156" s="9" t="n"/>
+      <c r="B156" s="10" t="n"/>
+      <c r="C156" s="16" t="n">
+        <v>155</v>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔줘</t>
         </is>
       </c>
-      <c r="E153" s="18" t="inlineStr">
+      <c r="E156" s="18" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔 달라는 요청에 대해서는 직접적인 변경 사유나 추가 상품을 안내해 드릴 자료가 아직 준비된 사유가 없어요. 다만 현재 등록된 투자성향 기준으로는 안내할 수 있는 위험등급 상한이 보통위험까지예요. 
 이 고객은 위험중립형 성향이라 보통위험 등급까지만 상품을 안내할 수 있어서, 현재 기준으로 안내 가능한 상품 목록은 다음과 같아요.
@@ -6191,39 +6399,39 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F153" s="19" t="inlineStr">
+      <c r="F156" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G153" s="18" t="inlineStr">
+      <c r="G156" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H153" s="18" t="inlineStr">
+      <c r="H156" s="18" t="inlineStr">
         <is>
           <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
         </is>
       </c>
-      <c r="I153" s="18" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="n"/>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="I156" s="18" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="n"/>
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
         </is>
       </c>
-      <c r="C154" s="4" t="n">
-        <v>153</v>
-      </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="C157" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E157" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 내용을 바탕으로 고객에게 바로 전달할 수 있는 핵심 대사만 짧게 줄여서 정리해 드릴게요. 
 연금지급 대기 자금이나 교체매매 중인 자금이 아닌지 먼저 확인한 뒤에 이렇게 안내해 보세요.
@@ -6231,115 +6439,115 @@
 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정해 약속하지 않도록 주의하고, 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용하여 고객이 쉽게 이해할 수 있도록 설명해 주세요.</t>
         </is>
       </c>
-      <c r="F154" s="7" t="inlineStr">
+      <c r="F157" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G154" s="6" t="inlineStr">
+      <c r="G157" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H154" s="6" t="inlineStr">
+      <c r="H157" s="6" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I154" s="6" t="inlineStr">
+      <c r="I157" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="9" t="n"/>
-      <c r="B155" s="9" t="n"/>
-      <c r="C155" s="4" t="n">
-        <v>154</v>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>그 중 두 번째 상품만 자세히 설명해줘</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E158" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 상품 중 두 번째 상품인 KB 국내채권형 C-P에 대해 자세히 설명해 드릴게요.
 - KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
 위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
         </is>
       </c>
-      <c r="F155" s="7" t="inlineStr">
+      <c r="F158" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G155" s="6" t="inlineStr">
+      <c r="G158" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H155" s="6" t="inlineStr">
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
-      <c r="I155" s="6" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="9" t="n"/>
-      <c r="B156" s="9" t="n"/>
-      <c r="C156" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="D156" s="12" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="9" t="n"/>
+      <c r="B159" s="9" t="n"/>
+      <c r="C159" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
         </is>
       </c>
-      <c r="F156" s="14" t="inlineStr">
+      <c r="F159" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G156" s="6" t="inlineStr">
+      <c r="G159" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H156" s="6" t="inlineStr">
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
         </is>
       </c>
-      <c r="I156" s="6" t="inlineStr">
+      <c r="I159" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="9" t="n"/>
-      <c r="B157" s="9" t="n"/>
-      <c r="C157" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="9" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E160" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 개인형IRP 수수료는 부담금 종류와 채널 및 구간에 따라 차등 적용되니 단말에서 먼저 확인한 뒤 안내해 주세요. 상세 수수료율은 다음과 같이 대면 및 비대면 채널별 구간에 따라 적용돼요.
 - 사용자부담금(퇴직금) 대면 5천만원 미만 — 0.45%
@@ -6352,115 +6560,115 @@
 - 가입자부담금 비대면 1억원 이상 — 0.21%</t>
         </is>
       </c>
-      <c r="F157" s="14" t="inlineStr">
+      <c r="F160" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G157" s="6" t="inlineStr">
+      <c r="G160" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H157" s="6" t="inlineStr">
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
-      <c r="I157" s="6" t="inlineStr">
+      <c r="I160" s="6" t="inlineStr">
         <is>
           <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="9" t="n"/>
-      <c r="B158" s="9" t="n"/>
-      <c r="C158" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="D158" s="12" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
         <is>
           <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E161" s="6" t="inlineStr">
         <is>
           <t>예금만으로 자산을 보유해 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 자산관리라는 논리로 접근하는 게 핵심이에요. 앞서 안내드린 내용에 수수료 관련 내용은 자료에 없어 추가하지 못했어요. 이미 안전하게 잘 운용하고 계신 점을 먼저 인정한 뒤, 원리금보장 상품도 매월 최고금리 상품 제공과 비대면 거래를 통해 꾸준히 관리해야 한다는 점을 짚어주세요. 
 고객에게는 이렇게 말씀해 보세요.
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="F158" s="14" t="inlineStr">
+      <c r="F161" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G158" s="6" t="inlineStr">
+      <c r="G161" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H158" s="6" t="inlineStr">
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
-      <c r="I158" s="6" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="9" t="n"/>
-      <c r="B159" s="10" t="n"/>
-      <c r="C159" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="D159" s="12" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="10" t="n"/>
+      <c r="C162" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E162" s="6" t="inlineStr">
         <is>
           <t>이번 상담에서 오간 대화 기록은 없습니다.</t>
         </is>
       </c>
-      <c r="F159" s="14" t="inlineStr">
+      <c r="F162" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
+      <c r="G162" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="n"/>
-      <c r="B160" s="15" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="n"/>
+      <c r="B163" s="15" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
         </is>
       </c>
-      <c r="C160" s="16" t="n">
-        <v>159</v>
-      </c>
-      <c r="D160" s="17" t="inlineStr">
+      <c r="C163" s="16" t="n">
+        <v>162</v>
+      </c>
+      <c r="D163" s="17" t="inlineStr">
         <is>
           <t>너 뭐 할 수 있는지 알려줘</t>
         </is>
       </c>
-      <c r="E160" s="18" t="inlineStr">
+      <c r="E163" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6480,35 +6688,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="F163" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G160" s="18" t="inlineStr">
+      <c r="G163" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H160" s="18" t="inlineStr">
+      <c r="H163" s="18" t="inlineStr">
         <is>
           <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
         </is>
       </c>
-      <c r="I160" s="18" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="n"/>
-      <c r="B161" s="9" t="n"/>
-      <c r="C161" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="D161" s="17" t="inlineStr">
+      <c r="I163" s="18" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="16" t="n">
+        <v>163</v>
+      </c>
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>너 이전 대화 기억해?</t>
         </is>
       </c>
-      <c r="E161" s="18" t="inlineStr">
+      <c r="E164" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6530,35 +6738,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F161" s="19" t="inlineStr">
+      <c r="F164" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G161" s="18" t="inlineStr">
+      <c r="G164" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H161" s="18" t="inlineStr">
+      <c r="H164" s="18" t="inlineStr">
         <is>
           <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
         </is>
       </c>
-      <c r="I161" s="18" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="n"/>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="16" t="n">
-        <v>161</v>
-      </c>
-      <c r="D162" s="17" t="inlineStr">
+      <c r="I164" s="18" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="n"/>
+      <c r="B165" s="10" t="n"/>
+      <c r="C165" s="16" t="n">
+        <v>164</v>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
         <is>
           <t>고객한테 문자 직접 보내줄 수 있어?</t>
         </is>
       </c>
-      <c r="E162" s="18" t="inlineStr">
+      <c r="E165" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6580,72 +6788,72 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F162" s="19" t="inlineStr">
+      <c r="F165" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G162" s="18" t="inlineStr">
+      <c r="G165" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H162" s="18" t="inlineStr">
+      <c r="H165" s="18" t="inlineStr">
         <is>
           <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
         </is>
       </c>
-      <c r="I162" s="18" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="I165" s="18" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="n"/>
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>23. 오늘의 타겟 목록</t>
         </is>
       </c>
-      <c r="C163" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
+      <c r="C166" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
         <is>
           <t>오늘 누구부터 봐야 해?</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E166" s="6" t="inlineStr">
         <is>
           <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
-      <c r="F163" s="14" t="inlineStr">
+      <c r="F166" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G163" s="6" t="inlineStr">
+      <c r="G166" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H163" s="6" t="inlineStr">
+      <c r="H166" s="6" t="inlineStr">
         <is>
           <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
         </is>
       </c>
-      <c r="I163" s="6" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="n"/>
-      <c r="B164" s="10" t="n"/>
-      <c r="C164" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="D164" s="12" t="inlineStr">
+      <c r="I166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="n"/>
+      <c r="B167" s="10" t="n"/>
+      <c r="C167" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
         <is>
           <t>타겟 목록에 고객번호도 같이 넣어줘</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E167" s="6" t="inlineStr">
         <is>
           <t>요청하신 타겟 목록의 고객번호는 현재 자료에 없어요. 2026년 9월 29일 기준 타겟 목록에 있는 고객들의 선정 사유와 순서를 안내해 드릴게요.
 - 윤가영 — 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원, 디폴트옵션 미설정
@@ -6661,43 +6869,43 @@
 - 한지우 — ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원</t>
         </is>
       </c>
-      <c r="F164" s="14" t="inlineStr">
+      <c r="F167" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G164" s="6" t="inlineStr">
+      <c r="G167" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H164" s="6" t="inlineStr">
+      <c r="H167" s="6" t="inlineStr">
         <is>
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
-      <c r="I164" s="6" t="inlineStr"/>
-    </row>
-    <row r="165" hidden="1">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168" hidden="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Ⅴ. 품질 — 시연엔 안 올려도 보는 것</t>
         </is>
       </c>
-      <c r="B165" s="15" t="inlineStr">
+      <c r="B168" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
         </is>
       </c>
-      <c r="C165" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="C168" s="16" t="n">
+        <v>167</v>
+      </c>
+      <c r="D168" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 무슨 상품 추천해주지?</t>
         </is>
       </c>
-      <c r="E165" s="18" t="inlineStr">
+      <c r="E168" s="18" t="inlineStr">
         <is>
           <t>투자성향이 위험중립형인 이 고객에게는 적합성 허용 상한이 보통위험까지이므로, 그에 맞는 상품들을 확인하고 안내해 드리는 것이 핵심이에요. 이 고객의 적합성 허용 상한은 보통위험이며, 안내할 수 있는 상품 목록은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 보통위험, 최근 1년 4.8%, 채권형
@@ -6711,35 +6919,35 @@
 안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 허용 상한을 초과하여 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F165" s="20" t="inlineStr">
+      <c r="F168" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G165" s="18" t="inlineStr">
+      <c r="G168" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H165" s="18" t="inlineStr">
+      <c r="H168" s="18" t="inlineStr">
         <is>
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
-      <c r="I165" s="18" t="inlineStr"/>
-    </row>
-    <row r="166" hidden="1">
-      <c r="A166" s="9" t="n"/>
-      <c r="B166" s="9" t="n"/>
-      <c r="C166" s="16" t="n">
-        <v>165</v>
-      </c>
-      <c r="D166" s="17" t="inlineStr">
+      <c r="I168" s="18" t="inlineStr"/>
+    </row>
+    <row r="169" hidden="1">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="16" t="n">
+        <v>168</v>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>국고채 금리 어때?</t>
         </is>
       </c>
-      <c r="E166" s="18" t="inlineStr">
+      <c r="E169" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차 기준 국고채 금리는 국고채3년물과 국고채10년물의 변동 추이를 살펴보아야 해요. 2026년 8월 14일 종가 기준으로 국고채3년물은 3.795, 국고채10년물은 4.31로 나타나 있어요. 
 - KOSPI — 6977.94 (+11.5%)
@@ -6770,35 +6978,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F166" s="19" t="inlineStr">
+      <c r="F169" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G166" s="18" t="inlineStr">
+      <c r="G169" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H166" s="18" t="inlineStr">
+      <c r="H169" s="18" t="inlineStr">
         <is>
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I166" s="18" t="inlineStr"/>
-    </row>
-    <row r="167" hidden="1">
-      <c r="A167" s="9" t="n"/>
-      <c r="B167" s="9" t="n"/>
-      <c r="C167" s="16" t="n">
-        <v>166</v>
-      </c>
-      <c r="D167" s="17" t="inlineStr">
+      <c r="I169" s="18" t="inlineStr"/>
+    </row>
+    <row r="170" hidden="1">
+      <c r="A170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="16" t="n">
+        <v>169</v>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
         <is>
           <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
-      <c r="E167" s="18" t="inlineStr">
+      <c r="E170" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션)로는 위험도에 따라 초저위험 지켜드림, 저위험 알파드림·알파드림 II·알파드림 III, 중위험 뿔려드림·뿔려드림 II·뿔려드림 III, 고위험 모두드림·모두드림 II·모두드림 III 같은 상품들이 있어요. 2026년 8월 기준(수익률은 2026년 7월 30일 기준, 원리금보장 금리는 2026년 8월 기준)으로 각 포트폴리오의 구성과 1년 수익률을 살펴보면 다음과 같아요.
 - 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성, 1년 수익률 미표시
@@ -6816,123 +7024,19 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F167" s="19" t="inlineStr">
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G167" s="18" t="inlineStr">
+      <c r="G170" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H167" s="18" t="inlineStr">
+      <c r="H170" s="18" t="inlineStr">
         <is>
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
-        </is>
-      </c>
-      <c r="I167" s="18" t="inlineStr"/>
-    </row>
-    <row r="168" hidden="1">
-      <c r="A168" s="9" t="n"/>
-      <c r="B168" s="9" t="n"/>
-      <c r="C168" s="16" t="n">
-        <v>167</v>
-      </c>
-      <c r="D168" s="17" t="inlineStr">
-        <is>
-          <t>대화 내용 요약해줘</t>
-        </is>
-      </c>
-      <c r="E168" s="18" t="inlineStr">
-        <is>
-          <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
-        </is>
-      </c>
-      <c r="F168" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 시연본</t>
-        </is>
-      </c>
-      <c r="G168" s="18" t="inlineStr">
-        <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H168" s="18" t="inlineStr">
-        <is>
-          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
-        </is>
-      </c>
-      <c r="I168" s="18" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" hidden="1">
-      <c r="A169" s="9" t="n"/>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="D169" s="17" t="inlineStr">
-        <is>
-          <t>지난번엔 무슨 얘기 했지?</t>
-        </is>
-      </c>
-      <c r="E169" s="18" t="inlineStr">
-        <is>
-          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
-        </is>
-      </c>
-      <c r="F169" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 대본</t>
-        </is>
-      </c>
-      <c r="G169" s="18" t="inlineStr">
-        <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H169" s="18" t="inlineStr">
-        <is>
-          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
-        </is>
-      </c>
-      <c r="I169" s="18" t="inlineStr"/>
-    </row>
-    <row r="170" hidden="1">
-      <c r="A170" s="9" t="n"/>
-      <c r="B170" s="9" t="n"/>
-      <c r="C170" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="D170" s="17" t="inlineStr">
-        <is>
-          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
-        </is>
-      </c>
-      <c r="E170" s="18" t="inlineStr">
-        <is>
-          <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
-자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
-        </is>
-      </c>
-      <c r="F170" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G170" s="18" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H170" s="18" t="inlineStr">
-        <is>
-          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
       <c r="I170" s="18" t="inlineStr"/>
@@ -6945,30 +7049,34 @@
       </c>
       <c r="D171" s="17" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
+          <t>대화 내용 요약해줘</t>
         </is>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
+          <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
         </is>
       </c>
       <c r="F171" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · QA</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G171" s="18" t="inlineStr">
         <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H171" s="18" t="inlineStr">
         <is>
-          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
-        </is>
-      </c>
-      <c r="I171" s="18" t="inlineStr"/>
+          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
+        </is>
+      </c>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="172" hidden="1">
       <c r="A172" s="9" t="n"/>
@@ -6978,204 +7086,203 @@
       </c>
       <c r="D172" s="17" t="inlineStr">
         <is>
-          <t>좀 더 짧게 줄여줘</t>
+          <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
       <c r="E172" s="18" t="inlineStr">
         <is>
-          <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
+          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
         </is>
       </c>
       <c r="F172" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스</t>
+          <t>○ 예비 · 대본</t>
         </is>
       </c>
       <c r="G172" s="18" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H172" s="18" t="inlineStr">
         <is>
-          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
-        </is>
-      </c>
-      <c r="I172" s="18" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
+        </is>
+      </c>
+      <c r="I172" s="18" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
       <c r="A173" s="9" t="n"/>
-      <c r="B173" s="10" t="n"/>
+      <c r="B173" s="9" t="n"/>
       <c r="C173" s="16" t="n">
         <v>172</v>
       </c>
       <c r="D173" s="17" t="inlineStr">
         <is>
-          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
+          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
-        </is>
-      </c>
-      <c r="F173" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
+          <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
+자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
+        </is>
+      </c>
+      <c r="F173" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G173" s="18" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H173" s="18" t="inlineStr">
         <is>
-          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
+          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
       <c r="I173" s="18" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
       <c r="A174" s="9" t="n"/>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="16" t="n">
+        <v>173</v>
+      </c>
+      <c r="D174" s="17" t="inlineStr">
+        <is>
+          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
+        </is>
+      </c>
+      <c r="F174" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr">
+        <is>
+          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
+        </is>
+      </c>
+      <c r="I174" s="18" t="inlineStr"/>
+    </row>
+    <row r="175" hidden="1">
+      <c r="A175" s="9" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="16" t="n">
+        <v>174</v>
+      </c>
+      <c r="D175" s="17" t="inlineStr">
+        <is>
+          <t>좀 더 짧게 줄여줘</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="inlineStr">
+        <is>
+          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" hidden="1">
+      <c r="A176" s="9" t="n"/>
+      <c r="B176" s="10" t="n"/>
+      <c r="C176" s="16" t="n">
+        <v>175</v>
+      </c>
+      <c r="D176" s="17" t="inlineStr">
+        <is>
+          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
+        </is>
+      </c>
+      <c r="F176" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
+        </is>
+      </c>
+      <c r="I176" s="18" t="inlineStr"/>
+    </row>
+    <row r="177" hidden="1">
+      <c r="A177" s="9" t="n"/>
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
         </is>
       </c>
-      <c r="C174" s="4" t="n">
-        <v>173</v>
-      </c>
-      <c r="D174" s="12" t="inlineStr">
+      <c r="C177" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr">
         <is>
           <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
 찾아본 곳: 상담 화법 「퇴직연금과 부동산 투자 비교 설명 및 설득 화법」 · 시황 자료 「퇴직연금과 부동산 투자 시장 현황 및 비교」 · 운용 상품 자료 「퇴직연금과 부동산 투자 비교」 · 관리 방법론 「퇴직연금과 부동산 투자 비교 판단 기준 및 장단점」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="F174" s="11" t="inlineStr">
+      <c r="F177" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G174" s="6" t="inlineStr">
+      <c r="G177" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="H177" s="6" t="inlineStr">
         <is>
           <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
-        </is>
-      </c>
-      <c r="I174" s="6" t="inlineStr"/>
-    </row>
-    <row r="175" hidden="1">
-      <c r="A175" s="9" t="n"/>
-      <c r="B175" s="9" t="n"/>
-      <c r="C175" s="4" t="n">
-        <v>174</v>
-      </c>
-      <c r="D175" s="12" t="inlineStr">
-        <is>
-          <t>이 고객 평가금액 얼마야?</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
-찾아본 곳: 제도·상품 수치 「고객 평가금액」
-다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
-        </is>
-      </c>
-      <c r="F175" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G175" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H175" s="6" t="inlineStr">
-        <is>
-          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
-        </is>
-      </c>
-      <c r="I175" s="6" t="inlineStr"/>
-    </row>
-    <row r="176" hidden="1">
-      <c r="A176" s="9" t="n"/>
-      <c r="B176" s="9" t="n"/>
-      <c r="C176" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="D176" s="12" t="inlineStr">
-        <is>
-          <t>IRP 중도인출 사유가 뭐야?</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
-        </is>
-      </c>
-      <c r="F176" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H176" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
-        </is>
-      </c>
-      <c r="I176" s="6" t="inlineStr"/>
-    </row>
-    <row r="177" hidden="1">
-      <c r="A177" s="9" t="n"/>
-      <c r="B177" s="9" t="n"/>
-      <c r="C177" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="D177" s="12" t="inlineStr">
-        <is>
-          <t>이 고객은 왜 타겟이 됐지?</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
-        </is>
-      </c>
-      <c r="F177" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H177" s="6" t="inlineStr">
-        <is>
-          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
       <c r="I177" s="6" t="inlineStr"/>
@@ -7188,10 +7295,111 @@
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
+          <t>이 고객 평가금액 얼마야?</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 제도·상품 수치 「고객 평가금액」
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+        </is>
+      </c>
+      <c r="F178" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr"/>
+    </row>
+    <row r="179" hidden="1">
+      <c r="A179" s="9" t="n"/>
+      <c r="B179" s="9" t="n"/>
+      <c r="C179" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>IRP 중도인출 사유가 뭐야?</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
+        </is>
+      </c>
+      <c r="F179" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180" hidden="1">
+      <c r="A180" s="9" t="n"/>
+      <c r="B180" s="9" t="n"/>
+      <c r="C180" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>이 고객은 왜 타겟이 됐지?</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
+        </is>
+      </c>
+      <c r="F180" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr"/>
+    </row>
+    <row r="181" hidden="1">
+      <c r="A181" s="9" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
           <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr">
         <is>
           <t>송도윤 고객님은 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 크게 상회하고 있지만, 6개월 이상 장기 미접촉 상태인 관리 사각지대 고객이에요. 현재 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식을 보유하고 계시며, 고유계정대 2억 8,000만원의 현금성자산이 방치되어 있고, 디폴트옵션 미설정 및 ISA 만기자금 1억 2,000만원을 보유하고 계셔요.
 - 고유계정대 — 2억 8,000만원 (수익률 0.0%)
@@ -7201,72 +7409,72 @@
 장기간 접촉 이력이 없어 타사 비교에 노출될 가능성이 있으므로, 유선 접촉을 통해 관계를 회복해야 합니다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 사용계획이 있는 자금은 먼저 걸러내며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F178" s="14" t="inlineStr">
+      <c r="F181" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G178" s="6" t="inlineStr">
+      <c r="G181" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="H181" s="6" t="inlineStr">
         <is>
           <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
-      <c r="I178" s="6" t="inlineStr"/>
-    </row>
-    <row r="179" hidden="1">
-      <c r="A179" s="9" t="n"/>
-      <c r="B179" s="10" t="n"/>
-      <c r="C179" s="4" t="n">
-        <v>178</v>
-      </c>
-      <c r="D179" s="12" t="inlineStr">
+      <c r="I181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182" hidden="1">
+      <c r="A182" s="9" t="n"/>
+      <c r="B182" s="10" t="n"/>
+      <c r="C182" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
         <is>
           <t>(고객 연 직후 첫 질문)</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr"/>
-      <c r="F179" s="14" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr"/>
+      <c r="F182" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G179" s="6" t="inlineStr">
+      <c r="G182" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
         </is>
       </c>
-      <c r="I179" s="6" t="inlineStr">
+      <c r="I182" s="6" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
       </c>
     </row>
-    <row r="180" hidden="1">
-      <c r="A180" s="9" t="n"/>
-      <c r="B180" s="15" t="inlineStr">
+    <row r="183" hidden="1">
+      <c r="A183" s="9" t="n"/>
+      <c r="B183" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
         </is>
       </c>
-      <c r="C180" s="16" t="n">
-        <v>179</v>
-      </c>
-      <c r="D180" s="17" t="inlineStr">
+      <c r="C183" s="16" t="n">
+        <v>182</v>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E180" s="18" t="inlineStr">
+      <c r="E183" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 ■ 제가 도와드릴 수 있는 것
@@ -7308,35 +7516,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F180" s="20" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="G180" s="18" t="inlineStr">
+      <c r="G183" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H180" s="18" t="inlineStr">
+      <c r="H183" s="18" t="inlineStr">
         <is>
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
         </is>
       </c>
-      <c r="I180" s="18" t="inlineStr"/>
-    </row>
-    <row r="181" hidden="1">
-      <c r="A181" s="9" t="n"/>
-      <c r="B181" s="9" t="n"/>
-      <c r="C181" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="D181" s="17" t="inlineStr">
+      <c r="I183" s="18" t="inlineStr"/>
+    </row>
+    <row r="184" hidden="1">
+      <c r="A184" s="9" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="16" t="n">
+        <v>183</v>
+      </c>
+      <c r="D184" s="17" t="inlineStr">
         <is>
           <t>이 고객 디폴트옵션 설정돼 있어?</t>
         </is>
       </c>
-      <c r="E181" s="18" t="inlineStr">
+      <c r="E184" s="18" t="inlineStr">
         <is>
           <t>● 박정호
 박정호 고객님은 현재 디폴트옵션 설정이 되어 있어요. 다만 이미 디폴트옵션(초저위험)을 등록·보유한 고객은 ⓐ 사전지정운용제도 등록/변경 → ⓑ 보유상품 변경(기존 매도 + 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요. 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 «현재 보유중이신 디폴트옵션(초저위험)은 정기예금만으로 구성되어 있습니다»라고 짚어 주세요.
@@ -7344,35 +7552,35 @@
 이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
         </is>
       </c>
-      <c r="F181" s="23" t="inlineStr">
+      <c r="F184" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G181" s="18" t="inlineStr">
+      <c r="G184" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H181" s="18" t="inlineStr">
+      <c r="H184" s="18" t="inlineStr">
         <is>
           <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
-      <c r="I181" s="18" t="inlineStr"/>
-    </row>
-    <row r="182" hidden="1">
-      <c r="A182" s="9" t="n"/>
-      <c r="B182" s="9" t="n"/>
-      <c r="C182" s="16" t="n">
-        <v>181</v>
-      </c>
-      <c r="D182" s="17" t="inlineStr">
+      <c r="I184" s="18" t="inlineStr"/>
+    </row>
+    <row r="185" hidden="1">
+      <c r="A185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="16" t="n">
+        <v>184</v>
+      </c>
+      <c r="D185" s="17" t="inlineStr">
         <is>
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E182" s="18" t="inlineStr">
+      <c r="E185" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 만기 도래 항목을 묻는 질문에 대해, 현재 2026년 10월 9일에 만기가 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품이 있어요. 그리고 2027년 1-10에 만기가 도래하는 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 3,550만원 상품이 있습니다.
@@ -7383,35 +7591,35 @@
 송도윤 고객님의 만기 내역은 2026년 9월 20일에 만기가 경과한 ISA 만기자금(IRP 외부) 1억 2,000만원이 있어요. 원장에 등록된 만기 항목은 해당 건이 전부이며, 다른 만기 건은 자료에 없어요.</t>
         </is>
       </c>
-      <c r="F182" s="23" t="inlineStr">
+      <c r="F185" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G182" s="18" t="inlineStr">
+      <c r="G185" s="18" t="inlineStr">
         <is>
           <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H182" s="18" t="inlineStr">
+      <c r="H185" s="18" t="inlineStr">
         <is>
           <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
         </is>
       </c>
-      <c r="I182" s="18" t="inlineStr"/>
-    </row>
-    <row r="183" hidden="1">
-      <c r="A183" s="9" t="n"/>
-      <c r="B183" s="9" t="n"/>
-      <c r="C183" s="16" t="n">
-        <v>182</v>
-      </c>
-      <c r="D183" s="17" t="inlineStr">
+      <c r="I185" s="18" t="inlineStr"/>
+    </row>
+    <row r="186" hidden="1">
+      <c r="A186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="16" t="n">
+        <v>185</v>
+      </c>
+      <c r="D186" s="17" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E186" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 및 환매추천 펀드인 KB 퇴직연금 배당 (주식)을 보유하고 계시고, 미운용 현금성자산이 있으며, 디폴트옵션이 미설정 상태이고, ISA 만기자금 보유와 운용변경이 12개월 이상 없었기 때문이에요. 추가로 관리 사각지대 고객이자 당해 납입이 없는 고객에 해당하며, 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시고 운용수익률은 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 계세요. 다만 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있는 상태예요.
@@ -7419,35 +7627,35 @@
 적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
         </is>
       </c>
-      <c r="F183" s="19" t="inlineStr">
+      <c r="F186" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G183" s="18" t="inlineStr">
+      <c r="G186" s="18" t="inlineStr">
         <is>
           <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
-      <c r="H183" s="18" t="inlineStr">
+      <c r="H186" s="18" t="inlineStr">
         <is>
           <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
-      <c r="I183" s="18" t="inlineStr"/>
-    </row>
-    <row r="184" hidden="1">
-      <c r="A184" s="9" t="n"/>
-      <c r="B184" s="9" t="n"/>
-      <c r="C184" s="16" t="n">
-        <v>183</v>
-      </c>
-      <c r="D184" s="17" t="inlineStr">
+      <c r="I186" s="18" t="inlineStr"/>
+    </row>
+    <row r="187" hidden="1">
+      <c r="A187" s="9" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="16" t="n">
+        <v>186</v>
+      </c>
+      <c r="D187" s="17" t="inlineStr">
         <is>
           <t>지난 상담에서 무슨 얘기 했지?</t>
         </is>
       </c>
-      <c r="E184" s="18" t="inlineStr">
+      <c r="E187" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 ※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담 기록에 따르면, 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 있어요.
@@ -7455,35 +7663,35 @@
 고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
         </is>
       </c>
-      <c r="F184" s="19" t="inlineStr">
+      <c r="F187" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G184" s="18" t="inlineStr">
+      <c r="G187" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
-      <c r="H184" s="18" t="inlineStr">
+      <c r="H187" s="18" t="inlineStr">
         <is>
           <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="I184" s="18" t="inlineStr"/>
-    </row>
-    <row r="185" hidden="1">
-      <c r="A185" s="9" t="n"/>
-      <c r="B185" s="9" t="n"/>
-      <c r="C185" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="D185" s="17" t="inlineStr">
+      <c r="I187" s="18" t="inlineStr"/>
+    </row>
+    <row r="188" hidden="1">
+      <c r="A188" s="9" t="n"/>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="D188" s="17" t="inlineStr">
         <is>
           <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="E188" s="18" t="inlineStr">
         <is>
           <t>● 이수민
 이수민 고객에게 개인형IRP 계좌에 300만원을 추가 납입할 때 예상되는 세액공제 환급액을 안내할 때는 총급여 구간과 세액공제 한도를 함께 짚어주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 한도 및 잔여한도가 900만원이므로, 300만원을 추가 납입하면 총급여 5,500만원 이하 기준 16.5%의 공제율을 적용하여 495,000원의 환급을 예상할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 이를 바탕으로 안내해 보세요.
@@ -7492,35 +7700,35 @@
 다만 ISA 만기자금을 개인형IRP 계좌로 전환하는 경우라면 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 별개의 축이에요. 300만원을 ISA 만기자금에서 개인형IRP로 전환할 때 적용되는 공제율에 따라 추가 공제 대상과 환급액이 달라질 수 있어요. 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 49,500원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않았으니 단말에서 고객의 총급여 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="F185" s="19" t="inlineStr">
+      <c r="F188" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G185" s="18" t="inlineStr">
+      <c r="G188" s="18" t="inlineStr">
         <is>
           <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H185" s="18" t="inlineStr">
+      <c r="H188" s="18" t="inlineStr">
         <is>
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
-      <c r="I185" s="18" t="inlineStr"/>
-    </row>
-    <row r="186" hidden="1">
-      <c r="A186" s="9" t="n"/>
-      <c r="B186" s="9" t="n"/>
-      <c r="C186" s="16" t="n">
-        <v>185</v>
-      </c>
-      <c r="D186" s="17" t="inlineStr">
+      <c r="I188" s="18" t="inlineStr"/>
+    </row>
+    <row r="189" hidden="1">
+      <c r="A189" s="9" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
         <is>
           <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
         </is>
       </c>
-      <c r="E186" s="18" t="inlineStr">
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>● 박지민
 고객의 소득 수준이나 종합소득금액 값이 자료에 나와 있지 않아 해당 고객의 세액공제율을 바로 확정해 말씀드리기는 어려워요. 2026년 6월 기준 자료에 따르면, 공제율은 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 경우 16.5%, 이를 초과하는 경우 13.2%가 적용돼요. 여기서 5,500만원 '이상'이 아니라 '초과'가 정확한 경계 표현이며, 5,500만원 정확히 일치하는 금액은 16.5% 구간에 해당한다는 점을 참고해 주세요. 단말에서 고객의 소득 조건을 먼저 확인하신 뒤에 안내를 이어가셔야 해요.
@@ -7528,35 +7736,35 @@
 총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
         </is>
       </c>
-      <c r="F186" s="23" t="inlineStr">
+      <c r="F189" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G186" s="18" t="inlineStr">
+      <c r="G189" s="18" t="inlineStr">
         <is>
           <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
         </is>
       </c>
-      <c r="H186" s="18" t="inlineStr">
+      <c r="H189" s="18" t="inlineStr">
         <is>
           <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
         </is>
       </c>
-      <c r="I186" s="18" t="inlineStr"/>
-    </row>
-    <row r="187" hidden="1">
-      <c r="A187" s="9" t="n"/>
-      <c r="B187" s="9" t="n"/>
-      <c r="C187" s="16" t="n">
-        <v>186</v>
-      </c>
-      <c r="D187" s="17" t="inlineStr">
+      <c r="I189" s="18" t="inlineStr"/>
+    </row>
+    <row r="190" hidden="1">
+      <c r="A190" s="9" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="D190" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E187" s="18" t="inlineStr">
+      <c r="E190" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금을 IRP로 옮겨 세액공제 혜택을 확인하는 고객에게는 만기금액의 전환에 따른 추가 공제 구조를 짚어 드리는 게 핵심이에요. 개인형IRP 계좌로 8,000만원을 전환할 때 이 금액은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이라, 8,000만원을 전환하면 추가 공제 대상은 300만원이 돼요. 총급여 5,500만원 이하 16.5% 기준으로 이 전환으로 늘어나는 환급 예상액은 495,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로 서로 다른 한도예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
@@ -7564,35 +7772,35 @@
 ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F187" s="19" t="inlineStr">
+      <c r="F190" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G187" s="18" t="inlineStr">
+      <c r="G190" s="18" t="inlineStr">
         <is>
           <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H187" s="18" t="inlineStr">
+      <c r="H190" s="18" t="inlineStr">
         <is>
           <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
-      <c r="I187" s="18" t="inlineStr"/>
-    </row>
-    <row r="188" hidden="1">
-      <c r="A188" s="9" t="n"/>
-      <c r="B188" s="9" t="n"/>
-      <c r="C188" s="16" t="n">
-        <v>187</v>
-      </c>
-      <c r="D188" s="17" t="inlineStr">
+      <c r="I190" s="18" t="inlineStr"/>
+    </row>
+    <row r="191" hidden="1">
+      <c r="A191" s="9" t="n"/>
+      <c r="B191" s="9" t="n"/>
+      <c r="C191" s="16" t="n">
+        <v>190</v>
+      </c>
+      <c r="D191" s="17" t="inlineStr">
         <is>
           <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
-      <c r="E188" s="18" t="inlineStr">
+      <c r="E191" s="18" t="inlineStr">
         <is>
           <t>● 박정호
 박정호 고객님은 연금개시 요건을 충족하였으나 아직 연금개시를 하지 않은 상태예요. 
@@ -7601,35 +7809,35 @@
 송도윤 고객님은 연금개시요건을 충족하지 않아 현재 연금개시를 하실 수 없어요. 자료에 따르면 연금개시 상태는 미개시이며 연금개시요건도 충족되지 않은 상태로 확인돼요.</t>
         </is>
       </c>
-      <c r="F188" s="19" t="inlineStr">
+      <c r="F191" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G188" s="18" t="inlineStr">
+      <c r="G191" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H188" s="18" t="inlineStr">
+      <c r="H191" s="18" t="inlineStr">
         <is>
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
-      <c r="I188" s="18" t="inlineStr"/>
-    </row>
-    <row r="189" hidden="1">
-      <c r="A189" s="9" t="n"/>
-      <c r="B189" s="9" t="n"/>
-      <c r="C189" s="16" t="n">
-        <v>188</v>
-      </c>
-      <c r="D189" s="17" t="inlineStr">
+      <c r="I191" s="18" t="inlineStr"/>
+    </row>
+    <row r="192" hidden="1">
+      <c r="A192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="16" t="n">
+        <v>191</v>
+      </c>
+      <c r="D192" s="17" t="inlineStr">
         <is>
           <t>판매중단된 펀드 뭐 들고 있어?</t>
         </is>
       </c>
-      <c r="E189" s="18" t="inlineStr">
+      <c r="E192" s="18" t="inlineStr">
         <is>
           <t>● 최서윤
 최서윤 고객이 보유하고 있는 판매중단 상품은 KB 코리아밸류업액티브(주식)이다. 해당 상품은 920만원 규모로 보유 중이며 수익률은 -38.7%를 기록하고 있다. 판매중단 상품을 보유하고 있어 관리 공백이 우려되는 상황이므로, 보유 포트폴리오를 점검하고 매도 및 재추천 등의 액션을 안내하는 방향으로 접근해야 한다.
@@ -7637,35 +7845,35 @@
 판매중단된 보유상품은 없어요.</t>
         </is>
       </c>
-      <c r="F189" s="19" t="inlineStr">
+      <c r="F192" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G189" s="18" t="inlineStr">
+      <c r="G192" s="18" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="H189" s="18" t="inlineStr">
+      <c r="H192" s="18" t="inlineStr">
         <is>
           <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
-      <c r="I189" s="18" t="inlineStr"/>
-    </row>
-    <row r="190" hidden="1">
-      <c r="A190" s="9" t="n"/>
-      <c r="B190" s="9" t="n"/>
-      <c r="C190" s="16" t="n">
-        <v>189</v>
-      </c>
-      <c r="D190" s="17" t="inlineStr">
+      <c r="I192" s="18" t="inlineStr"/>
+    </row>
+    <row r="193" hidden="1">
+      <c r="A193" s="9" t="n"/>
+      <c r="B193" s="9" t="n"/>
+      <c r="C193" s="16" t="n">
+        <v>192</v>
+      </c>
+      <c r="D193" s="17" t="inlineStr">
         <is>
           <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E190" s="18" t="inlineStr">
+      <c r="E193" s="18" t="inlineStr">
         <is>
           <t>● 정민석
 현재 보유한 자산이 예금 위주인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가는 게 핵심이에요. 원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 입증해야 하므로, 금리 갈아타기가 곧 관리라는 논리로 대응해 보세요. 다만 사용계획이 있는 자금은 먼저 걸러내고, 고객에게 생소한 고유계정대 같은 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 고객이 예금만 해서 관리가 필요 없다고 반응할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
@@ -7673,35 +7881,35 @@
 예금만 보유하고 있어 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 점을 짚어주는 게 핵심이에요. 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 같은 안전성 안에서 금리를 올려주는 제안으로 들어가야 해요. 고객이 사용계획이 있는 자금인지 먼저 확인하고, 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F190" s="19" t="inlineStr">
+      <c r="F193" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G190" s="18" t="inlineStr">
+      <c r="G193" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H190" s="18" t="inlineStr">
+      <c r="H193" s="18" t="inlineStr">
         <is>
           <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
-      <c r="I190" s="18" t="inlineStr"/>
-    </row>
-    <row r="191" hidden="1">
-      <c r="A191" s="10" t="n"/>
-      <c r="B191" s="10" t="n"/>
-      <c r="C191" s="16" t="n">
-        <v>190</v>
-      </c>
-      <c r="D191" s="17" t="inlineStr">
+      <c r="I193" s="18" t="inlineStr"/>
+    </row>
+    <row r="194" hidden="1">
+      <c r="A194" s="10" t="n"/>
+      <c r="B194" s="10" t="n"/>
+      <c r="C194" s="16" t="n">
+        <v>193</v>
+      </c>
+      <c r="D194" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E191" s="18" t="inlineStr">
+      <c r="E194" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 송도윤 고객에게는 지금 안내할 수 있는 세미나로 11/5(목) 16시에 진행되는 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 온라인 세미나가 있어요. 이 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어, 미운용 자금 및 디폴트옵션 제도를 다루는 해당 세미나를 안내합니다. 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX를 활용하시면 돼요. 고객에게 안내하실 때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 사용계획이 있는 자금이라면 먼저 걸러내고 접근하시는 게 핵심이에요. 참고로 다른 세미나 후보 4건인 연금개시 전 꼭 알아야 할 IRP 수령 방법, 예금만으로 괜찮을까? 퇴직연금 자산배분 전략, 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기, 금리 변화기, 퇴직연금 예금 만기 이후 운용 전략에 대해서는 아직 상세 안내 자료가 없어요.
@@ -7709,60 +7917,60 @@
 이 고객에게는 지금 요건에 맞는 안내 대상 세미나가 없어요. 다만 현재 열려 있는 세미나 중 날짜가 가장 가까운 것은 11/12(목) 17시에 KB국민은행 WM투자부에서 주관하는 «내 투자성향에 맞는 포트폴리오 찾기»예요. 이 콘텐츠는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋으나 이 고객의 요건과는 무관해요. 안내 시 참고할 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요. 다른 이벤트나 세미나 관련해서 다른 후보 콘텐츠들에 대한 상세 요건은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F191" s="19" t="inlineStr">
+      <c r="F194" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G191" s="18" t="inlineStr">
+      <c r="G194" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H191" s="18" t="inlineStr">
+      <c r="H194" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I191" s="18" t="inlineStr"/>
+      <c r="I194" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B141:B146"/>
     <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B183:B194"/>
     <mergeCell ref="B34:B40"/>
-    <mergeCell ref="B129:B140"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A165:A191"/>
     <mergeCell ref="B124:B128"/>
+    <mergeCell ref="B129:B142"/>
     <mergeCell ref="A41:A93"/>
-    <mergeCell ref="B147:B150"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="A143:A167"/>
+    <mergeCell ref="B157:B162"/>
     <mergeCell ref="B41:B54"/>
     <mergeCell ref="B82:B87"/>
-    <mergeCell ref="B160:B162"/>
+    <mergeCell ref="B168:B176"/>
     <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B180:B191"/>
-    <mergeCell ref="A94:A140"/>
-    <mergeCell ref="A141:A164"/>
     <mergeCell ref="B88:B93"/>
     <mergeCell ref="B75:B81"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="A2:A40"/>
-    <mergeCell ref="B174:B179"/>
-    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B143:B148"/>
+    <mergeCell ref="A94:A142"/>
     <mergeCell ref="B118:B123"/>
-    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="B149:B153"/>
+    <mergeCell ref="A168:A194"/>
+    <mergeCell ref="B177:B182"/>
     <mergeCell ref="B18:B26"/>
     <mergeCell ref="B65:B74"/>
-    <mergeCell ref="B165:B173"/>
     <mergeCell ref="B111:B117"/>
     <mergeCell ref="B6:B17"/>
     <mergeCell ref="B55:B64"/>
     <mergeCell ref="B94:B110"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B154:B159"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7776,7 +7984,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
+      <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
+      <c r="A5" s="8" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="8" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14" hidden="1">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
+      <c r="A17" s="8" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
+      <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
+      <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
+      <c r="A24" s="8" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
+      <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="8" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27" hidden="1">
-      <c r="A27" s="9" t="n"/>
+      <c r="A27" s="8" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28" hidden="1">
-      <c r="A28" s="9" t="n"/>
+      <c r="A28" s="8" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
+      <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
+      <c r="A30" s="8" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n"/>
+      <c r="A31" s="8" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
+      <c r="A32" s="8" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n"/>
+      <c r="A33" s="8" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
+      <c r="A34" s="8" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n"/>
+      <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
+      <c r="A36" s="8" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
+      <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="8" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
+      <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1965,7 +1965,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
+      <c r="A40" s="24" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -2049,7 +2049,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
+      <c r="A42" s="8" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2082,7 +2082,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
+      <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2115,7 +2115,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
+      <c r="A44" s="8" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2148,7 +2148,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
+      <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2179,7 +2179,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
+      <c r="A46" s="8" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2213,7 +2213,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
+      <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2248,7 +2248,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
+      <c r="A48" s="8" t="n"/>
       <c r="B48" s="9" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2282,7 +2282,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n"/>
+      <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="4" t="n">
         <v>48</v>
@@ -2315,7 +2315,7 @@
       <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="8" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="4" t="n">
         <v>49</v>
@@ -2348,7 +2348,7 @@
       <c r="I50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n"/>
+      <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="4" t="n">
         <v>50</v>
@@ -2381,7 +2381,7 @@
       <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
+      <c r="A52" s="8" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="4" t="n">
         <v>51</v>
@@ -2414,7 +2414,7 @@
       <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53" hidden="1">
-      <c r="A53" s="9" t="n"/>
+      <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="4" t="n">
         <v>52</v>
@@ -2459,7 +2459,7 @@
       <c r="I53" s="6" t="inlineStr"/>
     </row>
     <row r="54" hidden="1">
-      <c r="A54" s="9" t="n"/>
+      <c r="A54" s="8" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="4" t="n">
         <v>53</v>
@@ -2505,7 +2505,7 @@
       <c r="I54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n"/>
+      <c r="A55" s="8" t="n"/>
       <c r="B55" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2542,7 +2542,7 @@
       <c r="I55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
+      <c r="A56" s="8" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2575,7 +2575,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="n"/>
+      <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2611,7 +2611,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
+      <c r="A58" s="8" t="n"/>
       <c r="B58" s="9" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2682,7 +2682,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n"/>
+      <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="16" t="n">
         <v>58</v>
@@ -2735,7 +2735,7 @@
       <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
+      <c r="A60" s="8" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="16" t="n">
         <v>59</v>
@@ -2782,7 +2782,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n"/>
+      <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="16" t="n">
         <v>60</v>
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
+      <c r="A62" s="8" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="16" t="n">
         <v>61</v>
@@ -2858,7 +2858,7 @@
       <c r="I62" s="18" t="inlineStr"/>
     </row>
     <row r="63" hidden="1">
-      <c r="A63" s="9" t="n"/>
+      <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="16" t="n">
         <v>62</v>
@@ -2891,7 +2891,7 @@
       <c r="I63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
+      <c r="A64" s="8" t="n"/>
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="16" t="n">
         <v>63</v>
@@ -2924,7 +2924,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n"/>
+      <c r="A65" s="8" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2964,7 +2964,7 @@
       <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
+      <c r="A66" s="8" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="4" t="n">
         <v>65</v>
@@ -2999,7 +2999,7 @@
       <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
+      <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="4" t="n">
         <v>66</v>
@@ -3032,7 +3032,7 @@
       <c r="I67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
+      <c r="A68" s="8" t="n"/>
       <c r="B68" s="9" t="n"/>
       <c r="C68" s="4" t="n">
         <v>67</v>
@@ -3068,7 +3068,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="n"/>
+      <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3101,7 +3101,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
+      <c r="A70" s="8" t="n"/>
       <c r="B70" s="9" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3134,7 +3134,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71" hidden="1">
-      <c r="A71" s="9" t="n"/>
+      <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="4" t="n">
         <v>70</v>
@@ -3168,7 +3168,7 @@
       <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
+      <c r="A72" s="8" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="4" t="n">
         <v>71</v>
@@ -3201,7 +3201,7 @@
       <c r="I72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="n"/>
+      <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="4" t="n">
         <v>72</v>
@@ -3234,7 +3234,7 @@
       <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
+      <c r="A74" s="8" t="n"/>
       <c r="B74" s="10" t="n"/>
       <c r="C74" s="4" t="n">
         <v>73</v>
@@ -3267,7 +3267,7 @@
       <c r="I74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n"/>
+      <c r="A75" s="8" t="n"/>
       <c r="B75" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -3304,7 +3304,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n"/>
+      <c r="A76" s="8" t="n"/>
       <c r="B76" s="9" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3342,7 +3342,7 @@
       <c r="I76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n"/>
+      <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="16" t="n">
         <v>76</v>
@@ -3375,7 +3375,7 @@
       <c r="I77" s="18" t="inlineStr"/>
     </row>
     <row r="78" hidden="1">
-      <c r="A78" s="9" t="n"/>
+      <c r="A78" s="8" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="16" t="n">
         <v>77</v>
@@ -3410,7 +3410,7 @@
       <c r="I78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="n"/>
+      <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="16" t="n">
         <v>78</v>
@@ -3443,7 +3443,7 @@
       <c r="I79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n"/>
+      <c r="A80" s="8" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="16" t="n">
         <v>79</v>
@@ -3476,7 +3476,7 @@
       <c r="I80" s="18" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="n"/>
+      <c r="A81" s="8" t="n"/>
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="16" t="n">
         <v>80</v>
@@ -3509,7 +3509,7 @@
       <c r="I81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n"/>
+      <c r="A82" s="8" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3546,7 +3546,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n"/>
+      <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3580,7 +3580,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
+      <c r="A84" s="8" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3613,7 +3613,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="n"/>
+      <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3646,7 +3646,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
+      <c r="A86" s="8" t="n"/>
       <c r="B86" s="9" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3682,7 +3682,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="n"/>
+      <c r="A87" s="8" t="n"/>
       <c r="B87" s="10" t="n"/>
       <c r="C87" s="4" t="n">
         <v>86</v>
@@ -3715,7 +3715,7 @@
       <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n"/>
+      <c r="A88" s="8" t="n"/>
       <c r="B88" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3752,7 +3752,7 @@
       <c r="I88" s="18" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n"/>
+      <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3785,7 +3785,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n"/>
+      <c r="A90" s="8" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3820,7 +3820,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n"/>
+      <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3856,7 +3856,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n"/>
+      <c r="A92" s="8" t="n"/>
       <c r="B92" s="9" t="n"/>
       <c r="C92" s="16" t="n">
         <v>91</v>
@@ -3889,7 +3889,7 @@
       <c r="I92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="n"/>
+      <c r="A93" s="24" t="n"/>
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="16" t="n">
         <v>92</v>
@@ -3963,7 +3963,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n"/>
+      <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -3999,7 +3999,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96" hidden="1">
-      <c r="A96" s="9" t="n"/>
+      <c r="A96" s="8" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4035,7 +4035,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="n"/>
+      <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4074,7 +4074,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n"/>
+      <c r="A98" s="8" t="n"/>
       <c r="B98" s="9" t="n"/>
       <c r="C98" s="4" t="n">
         <v>97</v>
@@ -4109,7 +4109,7 @@
       <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99" hidden="1">
-      <c r="A99" s="9" t="n"/>
+      <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="4" t="n">
         <v>98</v>
@@ -4144,7 +4144,7 @@
       <c r="I99" s="6" t="inlineStr"/>
     </row>
     <row r="100" hidden="1">
-      <c r="A100" s="9" t="n"/>
+      <c r="A100" s="8" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="4" t="n">
         <v>99</v>
@@ -4182,7 +4182,7 @@
       <c r="I100" s="6" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="9" t="n"/>
+      <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="4" t="n">
         <v>100</v>
@@ -4215,7 +4215,7 @@
       <c r="I101" s="6" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
-      <c r="A102" s="9" t="n"/>
+      <c r="A102" s="8" t="n"/>
       <c r="B102" s="9" t="n"/>
       <c r="C102" s="4" t="n">
         <v>101</v>
@@ -4256,7 +4256,7 @@
       <c r="I102" s="6" t="inlineStr"/>
     </row>
     <row r="103" hidden="1">
-      <c r="A103" s="9" t="n"/>
+      <c r="A103" s="8" t="n"/>
       <c r="B103" s="9" t="n"/>
       <c r="C103" s="4" t="n">
         <v>102</v>
@@ -4289,7 +4289,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104" hidden="1">
-      <c r="A104" s="9" t="n"/>
+      <c r="A104" s="8" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4322,7 +4322,7 @@
       <c r="I104" s="6" t="inlineStr"/>
     </row>
     <row r="105" hidden="1">
-      <c r="A105" s="9" t="n"/>
+      <c r="A105" s="8" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4356,7 +4356,7 @@
       <c r="I105" s="6" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
-      <c r="A106" s="9" t="n"/>
+      <c r="A106" s="8" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4389,7 +4389,7 @@
       <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107" hidden="1">
-      <c r="A107" s="9" t="n"/>
+      <c r="A107" s="8" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4424,7 +4424,7 @@
       <c r="I107" s="6" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
-      <c r="A108" s="9" t="n"/>
+      <c r="A108" s="8" t="n"/>
       <c r="B108" s="9" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4461,7 +4461,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109" hidden="1">
-      <c r="A109" s="9" t="n"/>
+      <c r="A109" s="8" t="n"/>
       <c r="B109" s="9" t="n"/>
       <c r="C109" s="4" t="n">
         <v>108</v>
@@ -4497,7 +4497,7 @@
       <c r="I109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="n"/>
+      <c r="A110" s="8" t="n"/>
       <c r="B110" s="10" t="n"/>
       <c r="C110" s="4" t="n">
         <v>109</v>
@@ -4532,7 +4532,7 @@
       <c r="I110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="n"/>
+      <c r="A111" s="8" t="n"/>
       <c r="B111" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -4577,7 +4577,7 @@
       <c r="I111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n"/>
+      <c r="A112" s="8" t="n"/>
       <c r="B112" s="9" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4621,7 +4621,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="n"/>
+      <c r="A113" s="8" t="n"/>
       <c r="B113" s="9" t="n"/>
       <c r="C113" s="16" t="n">
         <v>112</v>
@@ -4667,7 +4667,7 @@
       <c r="I113" s="18" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n"/>
+      <c r="A114" s="8" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="16" t="n">
         <v>113</v>
@@ -4724,7 +4724,7 @@
       <c r="I114" s="18" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n"/>
+      <c r="A115" s="8" t="n"/>
       <c r="B115" s="9" t="n"/>
       <c r="C115" s="16" t="n">
         <v>114</v>
@@ -4784,7 +4784,7 @@
       <c r="I115" s="18" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n"/>
+      <c r="A116" s="8" t="n"/>
       <c r="B116" s="9" t="n"/>
       <c r="C116" s="16" t="n">
         <v>115</v>
@@ -4822,7 +4822,7 @@
       <c r="I116" s="18" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="n"/>
+      <c r="A117" s="8" t="n"/>
       <c r="B117" s="10" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -4870,7 +4870,7 @@
       <c r="I117" s="18" t="inlineStr"/>
     </row>
     <row r="118" hidden="1">
-      <c r="A118" s="9" t="n"/>
+      <c r="A118" s="8" t="n"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4917,7 +4917,7 @@
       <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="n"/>
+      <c r="A119" s="8" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="4" t="n">
         <v>118</v>
@@ -4992,7 +4992,7 @@
       <c r="I119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="n"/>
+      <c r="A120" s="8" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="4" t="n">
         <v>119</v>
@@ -5025,7 +5025,7 @@
       <c r="I120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="n"/>
+      <c r="A121" s="8" t="n"/>
       <c r="B121" s="9" t="n"/>
       <c r="C121" s="4" t="n">
         <v>120</v>
@@ -5097,7 +5097,7 @@
       <c r="I121" s="6" t="inlineStr"/>
     </row>
     <row r="122" hidden="1">
-      <c r="A122" s="9" t="n"/>
+      <c r="A122" s="8" t="n"/>
       <c r="B122" s="9" t="n"/>
       <c r="C122" s="4" t="n">
         <v>121</v>
@@ -5130,7 +5130,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="n"/>
+      <c r="A123" s="8" t="n"/>
       <c r="B123" s="10" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5168,7 +5168,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="n"/>
+      <c r="A124" s="8" t="n"/>
       <c r="B124" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -5205,7 +5205,7 @@
       <c r="I124" s="18" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="n"/>
+      <c r="A125" s="8" t="n"/>
       <c r="B125" s="9" t="n"/>
       <c r="C125" s="16" t="n">
         <v>124</v>
@@ -5244,7 +5244,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="n"/>
+      <c r="A126" s="8" t="n"/>
       <c r="B126" s="9" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5282,7 +5282,7 @@
       <c r="I126" s="18" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="n"/>
+      <c r="A127" s="8" t="n"/>
       <c r="B127" s="9" t="n"/>
       <c r="C127" s="16" t="n">
         <v>126</v>
@@ -5315,7 +5315,7 @@
       <c r="I127" s="18" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="n"/>
+      <c r="A128" s="8" t="n"/>
       <c r="B128" s="10" t="n"/>
       <c r="C128" s="16" t="n">
         <v>127</v>
@@ -5354,7 +5354,7 @@
       <c r="I128" s="18" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
-      <c r="A129" s="9" t="n"/>
+      <c r="A129" s="8" t="n"/>
       <c r="B129" s="3" t="inlineStr">
         <is>
           <t>17. 복합·연쇄 턴</t>
@@ -5394,7 +5394,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="n"/>
+      <c r="A130" s="8" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5431,7 +5431,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="n"/>
+      <c r="A131" s="8" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5470,7 +5470,7 @@
       <c r="I131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="n"/>
+      <c r="A132" s="8" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5503,7 +5503,7 @@
       <c r="I132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="n"/>
+      <c r="A133" s="8" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5544,7 +5544,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="n"/>
+      <c r="A134" s="8" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5581,7 +5581,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="n"/>
+      <c r="A135" s="8" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5622,7 +5622,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="n"/>
+      <c r="A136" s="8" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5661,7 +5661,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="n"/>
+      <c r="A137" s="8" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5700,7 +5700,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="n"/>
+      <c r="A138" s="8" t="n"/>
       <c r="B138" s="9" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5710,7 +5710,12 @@
           <t>(오프너 되묻기 뒤) 중립적 용건으로 열기</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr"/>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>수익률 관리 해피콜의 문을 열 때는 고객에게 문제점을 직접적으로 지적하기보다 전담직원 인사와 정기적 상품관리라는 중립적 명분을 활용하는 것이 좋아요. 통화 초반에는 구체적인 내용을 바로 꺼내기보다 먼저 가볍게 용건을 전하며 상대방의 의사를 확인하는 방식으로 접근해 보세요. 
+고객에게는 "안녕하세요, KB국민은행 000지점 000입니다. 저희 국민은행에 가입하신 퇴직연금 관련해서 안내드릴 사항이 있어 전화드렸습니다! 잠시 통화 가능하세요?"라고 먼저 건네주시고, 이어지는 턴에서 "고객님의 퇴직연금 전담직원으로 안내 인사드리고 정기적인 상품관리를 해 드리고자 연락드렸습니다. 퇴직연금 상품을 운용하시면서 혹시 궁금하시거나 상담하고 싶으신 내용이 있으신지요?"라고 자연스럽게 대화를 이어가며 문의 사항을 여쭤보시면 돼요.</t>
+        </is>
+      </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -5733,7 +5738,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="n"/>
+      <c r="A139" s="8" t="n"/>
       <c r="B139" s="9" t="n"/>
       <c r="C139" s="4" t="n">
         <v>138</v>
@@ -5770,7 +5775,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="n"/>
+      <c r="A140" s="8" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="4" t="n">
         <v>139</v>
@@ -5806,8 +5811,8 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="9" t="n"/>
+    <row r="141" hidden="1">
+      <c r="A141" s="8" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="4" t="n">
         <v>140</v>
@@ -5840,7 +5845,7 @@
       <c r="I141" s="6" t="inlineStr"/>
     </row>
     <row r="142" hidden="1">
-      <c r="A142" s="10" t="n"/>
+      <c r="A142" s="24" t="n"/>
       <c r="B142" s="10" t="n"/>
       <c r="C142" s="4" t="n">
         <v>141</v>
@@ -5916,7 +5921,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="n"/>
+      <c r="A144" s="8" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -5957,7 +5962,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="n"/>
+      <c r="A145" s="8" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -5998,7 +6003,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="n"/>
+      <c r="A146" s="8" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6037,7 +6042,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n"/>
+      <c r="A147" s="8" t="n"/>
       <c r="B147" s="9" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6084,7 +6089,7 @@
       </c>
     </row>
     <row r="148" hidden="1">
-      <c r="A148" s="9" t="n"/>
+      <c r="A148" s="8" t="n"/>
       <c r="B148" s="10" t="n"/>
       <c r="C148" s="16" t="n">
         <v>147</v>
@@ -6117,7 +6122,7 @@
       <c r="I148" s="18" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="n"/>
+      <c r="A149" s="8" t="n"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6163,7 +6168,7 @@
       </c>
     </row>
     <row r="150" hidden="1">
-      <c r="A150" s="9" t="n"/>
+      <c r="A150" s="8" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6200,7 +6205,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="n"/>
+      <c r="A151" s="8" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6237,7 +6242,7 @@
       </c>
     </row>
     <row r="152" hidden="1">
-      <c r="A152" s="9" t="n"/>
+      <c r="A152" s="8" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6269,8 +6274,8 @@
       </c>
       <c r="I152" s="6" t="inlineStr"/>
     </row>
-    <row r="153">
-      <c r="A153" s="9" t="n"/>
+    <row r="153" hidden="1">
+      <c r="A153" s="8" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6280,7 +6285,11 @@
           <t>(쪽지 초안 뒤) 응, 사번 3902172한테 보내줘</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr"/>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
+        </is>
+      </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -6303,7 +6312,7 @@
       </c>
     </row>
     <row r="154" hidden="1">
-      <c r="A154" s="9" t="n"/>
+      <c r="A154" s="8" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>20. 브리핑 수정</t>
@@ -6340,7 +6349,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155" hidden="1">
-      <c r="A155" s="9" t="n"/>
+      <c r="A155" s="8" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6373,7 +6382,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156" hidden="1">
-      <c r="A156" s="9" t="n"/>
+      <c r="A156" s="8" t="n"/>
       <c r="B156" s="10" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6417,7 +6426,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="n"/>
+      <c r="A157" s="8" t="n"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
@@ -6461,7 +6470,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="n"/>
+      <c r="A158" s="8" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="4" t="n">
         <v>157</v>
@@ -6500,7 +6509,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="n"/>
+      <c r="A159" s="8" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="4" t="n">
         <v>158</v>
@@ -6537,7 +6546,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="n"/>
+      <c r="A160" s="8" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="4" t="n">
         <v>159</v>
@@ -6582,7 +6591,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="n"/>
+      <c r="A161" s="8" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="4" t="n">
         <v>160</v>
@@ -6620,8 +6629,8 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="9" t="n"/>
+    <row r="162" hidden="1">
+      <c r="A162" s="8" t="n"/>
       <c r="B162" s="10" t="n"/>
       <c r="C162" s="4" t="n">
         <v>161</v>
@@ -6654,7 +6663,7 @@
       <c r="I162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n"/>
+      <c r="A163" s="8" t="n"/>
       <c r="B163" s="15" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -6706,7 +6715,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="n"/>
+      <c r="A164" s="8" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6756,7 +6765,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n"/>
+      <c r="A165" s="8" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6806,7 +6815,7 @@
       <c r="I165" s="18" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="n"/>
+      <c r="A166" s="8" t="n"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>23. 오늘의 타겟 목록</t>
@@ -6843,7 +6852,7 @@
       <c r="I166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="n"/>
+      <c r="A167" s="24" t="n"/>
       <c r="B167" s="10" t="n"/>
       <c r="C167" s="4" t="n">
         <v>166</v>
@@ -6937,7 +6946,7 @@
       <c r="I168" s="18" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
-      <c r="A169" s="9" t="n"/>
+      <c r="A169" s="8" t="n"/>
       <c r="B169" s="9" t="n"/>
       <c r="C169" s="16" t="n">
         <v>168</v>
@@ -6996,7 +7005,7 @@
       <c r="I169" s="18" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
-      <c r="A170" s="9" t="n"/>
+      <c r="A170" s="8" t="n"/>
       <c r="B170" s="9" t="n"/>
       <c r="C170" s="16" t="n">
         <v>169</v>
@@ -7042,7 +7051,7 @@
       <c r="I170" s="18" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
-      <c r="A171" s="9" t="n"/>
+      <c r="A171" s="8" t="n"/>
       <c r="B171" s="9" t="n"/>
       <c r="C171" s="16" t="n">
         <v>170</v>
@@ -7079,7 +7088,7 @@
       </c>
     </row>
     <row r="172" hidden="1">
-      <c r="A172" s="9" t="n"/>
+      <c r="A172" s="8" t="n"/>
       <c r="B172" s="9" t="n"/>
       <c r="C172" s="16" t="n">
         <v>171</v>
@@ -7112,7 +7121,7 @@
       <c r="I172" s="18" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
-      <c r="A173" s="9" t="n"/>
+      <c r="A173" s="8" t="n"/>
       <c r="B173" s="9" t="n"/>
       <c r="C173" s="16" t="n">
         <v>172</v>
@@ -7146,7 +7155,7 @@
       <c r="I173" s="18" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
-      <c r="A174" s="9" t="n"/>
+      <c r="A174" s="8" t="n"/>
       <c r="B174" s="9" t="n"/>
       <c r="C174" s="16" t="n">
         <v>173</v>
@@ -7179,7 +7188,7 @@
       <c r="I174" s="18" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
-      <c r="A175" s="9" t="n"/>
+      <c r="A175" s="8" t="n"/>
       <c r="B175" s="9" t="n"/>
       <c r="C175" s="16" t="n">
         <v>174</v>
@@ -7216,7 +7225,7 @@
       </c>
     </row>
     <row r="176" hidden="1">
-      <c r="A176" s="9" t="n"/>
+      <c r="A176" s="8" t="n"/>
       <c r="B176" s="10" t="n"/>
       <c r="C176" s="16" t="n">
         <v>175</v>
@@ -7249,7 +7258,7 @@
       <c r="I176" s="18" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
-      <c r="A177" s="9" t="n"/>
+      <c r="A177" s="8" t="n"/>
       <c r="B177" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -7288,7 +7297,7 @@
       <c r="I177" s="6" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
-      <c r="A178" s="9" t="n"/>
+      <c r="A178" s="8" t="n"/>
       <c r="B178" s="9" t="n"/>
       <c r="C178" s="4" t="n">
         <v>177</v>
@@ -7323,7 +7332,7 @@
       <c r="I178" s="6" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
-      <c r="A179" s="9" t="n"/>
+      <c r="A179" s="8" t="n"/>
       <c r="B179" s="9" t="n"/>
       <c r="C179" s="4" t="n">
         <v>178</v>
@@ -7356,7 +7365,7 @@
       <c r="I179" s="6" t="inlineStr"/>
     </row>
     <row r="180" hidden="1">
-      <c r="A180" s="9" t="n"/>
+      <c r="A180" s="8" t="n"/>
       <c r="B180" s="9" t="n"/>
       <c r="C180" s="4" t="n">
         <v>179</v>
@@ -7389,7 +7398,7 @@
       <c r="I180" s="6" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
-      <c r="A181" s="9" t="n"/>
+      <c r="A181" s="8" t="n"/>
       <c r="B181" s="9" t="n"/>
       <c r="C181" s="4" t="n">
         <v>180</v>
@@ -7427,7 +7436,7 @@
       <c r="I181" s="6" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
-      <c r="A182" s="9" t="n"/>
+      <c r="A182" s="8" t="n"/>
       <c r="B182" s="10" t="n"/>
       <c r="C182" s="4" t="n">
         <v>181</v>
@@ -7460,7 +7469,7 @@
       </c>
     </row>
     <row r="183" hidden="1">
-      <c r="A183" s="9" t="n"/>
+      <c r="A183" s="8" t="n"/>
       <c r="B183" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -7534,7 +7543,7 @@
       <c r="I183" s="18" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
-      <c r="A184" s="9" t="n"/>
+      <c r="A184" s="8" t="n"/>
       <c r="B184" s="9" t="n"/>
       <c r="C184" s="16" t="n">
         <v>183</v>
@@ -7570,7 +7579,7 @@
       <c r="I184" s="18" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
-      <c r="A185" s="9" t="n"/>
+      <c r="A185" s="8" t="n"/>
       <c r="B185" s="9" t="n"/>
       <c r="C185" s="16" t="n">
         <v>184</v>
@@ -7609,7 +7618,7 @@
       <c r="I185" s="18" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
-      <c r="A186" s="9" t="n"/>
+      <c r="A186" s="8" t="n"/>
       <c r="B186" s="9" t="n"/>
       <c r="C186" s="16" t="n">
         <v>185</v>
@@ -7645,7 +7654,7 @@
       <c r="I186" s="18" t="inlineStr"/>
     </row>
     <row r="187" hidden="1">
-      <c r="A187" s="9" t="n"/>
+      <c r="A187" s="8" t="n"/>
       <c r="B187" s="9" t="n"/>
       <c r="C187" s="16" t="n">
         <v>186</v>
@@ -7681,7 +7690,7 @@
       <c r="I187" s="18" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
-      <c r="A188" s="9" t="n"/>
+      <c r="A188" s="8" t="n"/>
       <c r="B188" s="9" t="n"/>
       <c r="C188" s="16" t="n">
         <v>187</v>
@@ -7718,7 +7727,7 @@
       <c r="I188" s="18" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
-      <c r="A189" s="9" t="n"/>
+      <c r="A189" s="8" t="n"/>
       <c r="B189" s="9" t="n"/>
       <c r="C189" s="16" t="n">
         <v>188</v>
@@ -7754,7 +7763,7 @@
       <c r="I189" s="18" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
-      <c r="A190" s="9" t="n"/>
+      <c r="A190" s="8" t="n"/>
       <c r="B190" s="9" t="n"/>
       <c r="C190" s="16" t="n">
         <v>189</v>
@@ -7790,7 +7799,7 @@
       <c r="I190" s="18" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
-      <c r="A191" s="9" t="n"/>
+      <c r="A191" s="8" t="n"/>
       <c r="B191" s="9" t="n"/>
       <c r="C191" s="16" t="n">
         <v>190</v>
@@ -7827,7 +7836,7 @@
       <c r="I191" s="18" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
-      <c r="A192" s="9" t="n"/>
+      <c r="A192" s="8" t="n"/>
       <c r="B192" s="9" t="n"/>
       <c r="C192" s="16" t="n">
         <v>191</v>
@@ -7863,7 +7872,7 @@
       <c r="I192" s="18" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
-      <c r="A193" s="9" t="n"/>
+      <c r="A193" s="8" t="n"/>
       <c r="B193" s="9" t="n"/>
       <c r="C193" s="16" t="n">
         <v>192</v>
@@ -7899,7 +7908,7 @@
       <c r="I193" s="18" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
-      <c r="A194" s="10" t="n"/>
+      <c r="A194" s="24" t="n"/>
       <c r="B194" s="10" t="n"/>
       <c r="C194" s="16" t="n">
         <v>193</v>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -675,7 +675,7 @@
       <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n"/>
+      <c r="A3" s="9" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="4" t="n">
         <v>2</v>
@@ -704,7 +704,7 @@
       <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
       <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n"/>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -776,7 +776,7 @@
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2. 고객 현황 확인</t>
@@ -813,7 +813,7 @@
       <c r="I6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="16" t="n">
         <v>6</v>
@@ -849,7 +849,7 @@
       <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="16" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
       <c r="I8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="16" t="n">
         <v>8</v>
@@ -915,7 +915,7 @@
       <c r="I9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="16" t="n">
         <v>9</v>
@@ -951,7 +951,7 @@
       <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="16" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="16" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="16" t="n">
         <v>12</v>
@@ -1060,7 +1060,7 @@
       <c r="I13" s="18" t="inlineStr"/>
     </row>
     <row r="14" hidden="1">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="16" t="n">
         <v>13</v>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="16" t="n">
         <v>14</v>
@@ -1128,7 +1128,7 @@
       <c r="I15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="16" t="n">
         <v>15</v>
@@ -1162,7 +1162,7 @@
       <c r="I16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="16" t="n">
         <v>16</v>
@@ -1198,7 +1198,7 @@
       <c r="I17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>3. 고객 계좌 상태 확인</t>
@@ -1235,7 +1235,7 @@
       <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="4" t="n">
         <v>18</v>
@@ -1265,7 +1265,7 @@
       <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
       <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -1331,7 +1331,7 @@
       <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -1367,7 +1367,7 @@
       <c r="I22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="4" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
       <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="4" t="n">
         <v>23</v>
@@ -1429,7 +1429,7 @@
       <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="4" t="n">
         <v>24</v>
@@ -1462,7 +1462,7 @@
       <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="4" t="n">
         <v>25</v>
@@ -1495,7 +1495,7 @@
       <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27" hidden="1">
-      <c r="A27" s="8" t="n"/>
+      <c r="A27" s="9" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
           <t>4. 상담 이력 조회</t>
@@ -1532,7 +1532,7 @@
       <c r="I27" s="18" t="inlineStr"/>
     </row>
     <row r="28" hidden="1">
-      <c r="A28" s="8" t="n"/>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="16" t="n">
         <v>27</v>
@@ -1566,7 +1566,7 @@
       <c r="I28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
+      <c r="A29" s="9" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="16" t="n">
         <v>28</v>
@@ -1599,7 +1599,7 @@
       <c r="I29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="9" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="16" t="n">
         <v>29</v>
@@ -1632,7 +1632,7 @@
       <c r="I30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5. 상담 준비 자료</t>
@@ -1669,7 +1669,7 @@
       <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
+      <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="4" t="n">
         <v>31</v>
@@ -1702,7 +1702,7 @@
       <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
+      <c r="A33" s="9" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="4" t="n">
         <v>32</v>
@@ -1740,7 +1740,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
+      <c r="A34" s="9" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6. 금지·주의 안내</t>
@@ -1786,7 +1786,7 @@
       <c r="I34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="16" t="n">
         <v>34</v>
@@ -1823,7 +1823,7 @@
       <c r="I35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
+      <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="16" t="n">
         <v>35</v>
@@ -1856,7 +1856,7 @@
       <c r="I36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
+      <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="16" t="n">
         <v>36</v>
@@ -1898,7 +1898,7 @@
       <c r="I37" s="18" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
-      <c r="A38" s="8" t="n"/>
+      <c r="A38" s="9" t="n"/>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="16" t="n">
         <v>37</v>
@@ -1931,7 +1931,7 @@
       <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
+      <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
         <v>38</v>
@@ -1965,7 +1965,7 @@
       <c r="I39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
+      <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="16" t="n">
         <v>39</v>
@@ -2049,7 +2049,7 @@
       <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n"/>
+      <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="4" t="n">
         <v>41</v>
@@ -2082,7 +2082,7 @@
       <c r="I42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="4" t="n">
         <v>42</v>
@@ -2115,7 +2115,7 @@
       <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n"/>
+      <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="4" t="n">
         <v>43</v>
@@ -2148,7 +2148,7 @@
       <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
+      <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="4" t="n">
         <v>44</v>
@@ -2179,7 +2179,7 @@
       <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
+      <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="4" t="n">
         <v>45</v>
@@ -2213,7 +2213,7 @@
       <c r="I46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n"/>
+      <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="4" t="n">
         <v>46</v>
@@ -2248,7 +2248,7 @@
       <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
+      <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="n"/>
       <c r="C48" s="4" t="n">
         <v>47</v>
@@ -2282,7 +2282,7 @@
       <c r="I48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="4" t="n">
         <v>48</v>
@@ -2315,7 +2315,7 @@
       <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
+      <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="4" t="n">
         <v>49</v>
@@ -2348,7 +2348,7 @@
       <c r="I50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
+      <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="4" t="n">
         <v>50</v>
@@ -2381,7 +2381,7 @@
       <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
+      <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="4" t="n">
         <v>51</v>
@@ -2414,7 +2414,7 @@
       <c r="I52" s="6" t="inlineStr"/>
     </row>
     <row r="53" hidden="1">
-      <c r="A53" s="8" t="n"/>
+      <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="4" t="n">
         <v>52</v>
@@ -2459,7 +2459,7 @@
       <c r="I53" s="6" t="inlineStr"/>
     </row>
     <row r="54" hidden="1">
-      <c r="A54" s="8" t="n"/>
+      <c r="A54" s="9" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="4" t="n">
         <v>53</v>
@@ -2505,7 +2505,7 @@
       <c r="I54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
+      <c r="A55" s="9" t="n"/>
       <c r="B55" s="15" t="inlineStr">
         <is>
           <t>8. 세액공제 계산</t>
@@ -2542,7 +2542,7 @@
       <c r="I55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
+      <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
       <c r="C56" s="16" t="n">
         <v>55</v>
@@ -2575,7 +2575,7 @@
       <c r="I56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="16" t="n">
         <v>56</v>
@@ -2611,7 +2611,7 @@
       <c r="I57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
+      <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
       <c r="C58" s="16" t="n">
         <v>57</v>
@@ -2682,7 +2682,7 @@
       <c r="I58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
+      <c r="A59" s="9" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="16" t="n">
         <v>58</v>
@@ -2735,7 +2735,7 @@
       <c r="I59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
       <c r="C60" s="16" t="n">
         <v>59</v>
@@ -2782,7 +2782,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
+      <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="16" t="n">
         <v>60</v>
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
+      <c r="A62" s="9" t="n"/>
       <c r="B62" s="9" t="n"/>
       <c r="C62" s="16" t="n">
         <v>61</v>
@@ -2858,7 +2858,7 @@
       <c r="I62" s="18" t="inlineStr"/>
     </row>
     <row r="63" hidden="1">
-      <c r="A63" s="8" t="n"/>
+      <c r="A63" s="9" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="16" t="n">
         <v>62</v>
@@ -2891,7 +2891,7 @@
       <c r="I63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
+      <c r="A64" s="9" t="n"/>
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="16" t="n">
         <v>63</v>
@@ -2924,7 +2924,7 @@
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
+      <c r="A65" s="9" t="n"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
@@ -2964,7 +2964,7 @@
       <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="9" t="n"/>
       <c r="B66" s="9" t="n"/>
       <c r="C66" s="4" t="n">
         <v>65</v>
@@ -2999,7 +2999,7 @@
       <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
+      <c r="A67" s="9" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="4" t="n">
         <v>66</v>
@@ -3032,7 +3032,7 @@
       <c r="I67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
+      <c r="A68" s="9" t="n"/>
       <c r="B68" s="9" t="n"/>
       <c r="C68" s="4" t="n">
         <v>67</v>
@@ -3068,7 +3068,7 @@
       <c r="I68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
+      <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="4" t="n">
         <v>68</v>
@@ -3101,7 +3101,7 @@
       <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
+      <c r="A70" s="9" t="n"/>
       <c r="B70" s="9" t="n"/>
       <c r="C70" s="4" t="n">
         <v>69</v>
@@ -3134,7 +3134,7 @@
       <c r="I70" s="6" t="inlineStr"/>
     </row>
     <row r="71" hidden="1">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="9" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="4" t="n">
         <v>70</v>
@@ -3168,7 +3168,7 @@
       <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
+      <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="4" t="n">
         <v>71</v>
@@ -3201,7 +3201,7 @@
       <c r="I72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="9" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="4" t="n">
         <v>72</v>
@@ -3234,7 +3234,7 @@
       <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
+      <c r="A74" s="9" t="n"/>
       <c r="B74" s="10" t="n"/>
       <c r="C74" s="4" t="n">
         <v>73</v>
@@ -3267,7 +3267,7 @@
       <c r="I74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="15" t="inlineStr">
         <is>
           <t>10. 단말 화면번호</t>
@@ -3304,7 +3304,7 @@
       <c r="I75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n"/>
+      <c r="A76" s="9" t="n"/>
       <c r="B76" s="9" t="n"/>
       <c r="C76" s="16" t="n">
         <v>75</v>
@@ -3342,7 +3342,7 @@
       <c r="I76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n"/>
+      <c r="A77" s="9" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="16" t="n">
         <v>76</v>
@@ -3375,7 +3375,7 @@
       <c r="I77" s="18" t="inlineStr"/>
     </row>
     <row r="78" hidden="1">
-      <c r="A78" s="8" t="n"/>
+      <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="16" t="n">
         <v>77</v>
@@ -3410,7 +3410,7 @@
       <c r="I78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
+      <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="16" t="n">
         <v>78</v>
@@ -3443,7 +3443,7 @@
       <c r="I79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
+      <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="n"/>
       <c r="C80" s="16" t="n">
         <v>79</v>
@@ -3476,7 +3476,7 @@
       <c r="I80" s="18" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
+      <c r="A81" s="9" t="n"/>
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="16" t="n">
         <v>80</v>
@@ -3509,7 +3509,7 @@
       <c r="I81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
           <t>11. 비대면 채널 경로</t>
@@ -3546,7 +3546,7 @@
       <c r="I82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
+      <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="4" t="n">
         <v>82</v>
@@ -3580,7 +3580,7 @@
       <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
+      <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="n"/>
       <c r="C84" s="4" t="n">
         <v>83</v>
@@ -3613,7 +3613,7 @@
       <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="4" t="n">
         <v>84</v>
@@ -3646,7 +3646,7 @@
       <c r="I85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
+      <c r="A86" s="9" t="n"/>
       <c r="B86" s="9" t="n"/>
       <c r="C86" s="4" t="n">
         <v>85</v>
@@ -3682,7 +3682,7 @@
       <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
+      <c r="A87" s="9" t="n"/>
       <c r="B87" s="10" t="n"/>
       <c r="C87" s="4" t="n">
         <v>86</v>
@@ -3715,7 +3715,7 @@
       <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
+      <c r="A88" s="9" t="n"/>
       <c r="B88" s="15" t="inlineStr">
         <is>
           <t>12. 고객군·관리 기준</t>
@@ -3752,7 +3752,7 @@
       <c r="I88" s="18" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
+      <c r="A89" s="9" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="16" t="n">
         <v>88</v>
@@ -3785,7 +3785,7 @@
       <c r="I89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
+      <c r="A90" s="9" t="n"/>
       <c r="B90" s="9" t="n"/>
       <c r="C90" s="16" t="n">
         <v>89</v>
@@ -3820,7 +3820,7 @@
       <c r="I90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
+      <c r="A91" s="9" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="16" t="n">
         <v>90</v>
@@ -3856,7 +3856,7 @@
       <c r="I91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
+      <c r="A92" s="9" t="n"/>
       <c r="B92" s="9" t="n"/>
       <c r="C92" s="16" t="n">
         <v>91</v>
@@ -3889,7 +3889,7 @@
       <c r="I92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="n"/>
+      <c r="A93" s="10" t="n"/>
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="16" t="n">
         <v>92</v>
@@ -3963,7 +3963,7 @@
       <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
+      <c r="A95" s="9" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
@@ -3999,7 +3999,7 @@
       <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96" hidden="1">
-      <c r="A96" s="8" t="n"/>
+      <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
       <c r="C96" s="4" t="n">
         <v>95</v>
@@ -4035,7 +4035,7 @@
       <c r="I96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
+      <c r="A97" s="9" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="4" t="n">
         <v>96</v>
@@ -4074,7 +4074,7 @@
       <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
+      <c r="A98" s="9" t="n"/>
       <c r="B98" s="9" t="n"/>
       <c r="C98" s="4" t="n">
         <v>97</v>
@@ -4109,7 +4109,7 @@
       <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99" hidden="1">
-      <c r="A99" s="8" t="n"/>
+      <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="4" t="n">
         <v>98</v>
@@ -4144,7 +4144,7 @@
       <c r="I99" s="6" t="inlineStr"/>
     </row>
     <row r="100" hidden="1">
-      <c r="A100" s="8" t="n"/>
+      <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
       <c r="C100" s="4" t="n">
         <v>99</v>
@@ -4182,7 +4182,7 @@
       <c r="I100" s="6" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="8" t="n"/>
+      <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="4" t="n">
         <v>100</v>
@@ -4215,7 +4215,7 @@
       <c r="I101" s="6" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
-      <c r="A102" s="8" t="n"/>
+      <c r="A102" s="9" t="n"/>
       <c r="B102" s="9" t="n"/>
       <c r="C102" s="4" t="n">
         <v>101</v>
@@ -4256,7 +4256,7 @@
       <c r="I102" s="6" t="inlineStr"/>
     </row>
     <row r="103" hidden="1">
-      <c r="A103" s="8" t="n"/>
+      <c r="A103" s="9" t="n"/>
       <c r="B103" s="9" t="n"/>
       <c r="C103" s="4" t="n">
         <v>102</v>
@@ -4289,7 +4289,7 @@
       <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104" hidden="1">
-      <c r="A104" s="8" t="n"/>
+      <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
       <c r="C104" s="4" t="n">
         <v>103</v>
@@ -4322,7 +4322,7 @@
       <c r="I104" s="6" t="inlineStr"/>
     </row>
     <row r="105" hidden="1">
-      <c r="A105" s="8" t="n"/>
+      <c r="A105" s="9" t="n"/>
       <c r="B105" s="9" t="n"/>
       <c r="C105" s="4" t="n">
         <v>104</v>
@@ -4356,7 +4356,7 @@
       <c r="I105" s="6" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
-      <c r="A106" s="8" t="n"/>
+      <c r="A106" s="9" t="n"/>
       <c r="B106" s="9" t="n"/>
       <c r="C106" s="4" t="n">
         <v>105</v>
@@ -4389,7 +4389,7 @@
       <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107" hidden="1">
-      <c r="A107" s="8" t="n"/>
+      <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
       <c r="C107" s="4" t="n">
         <v>106</v>
@@ -4424,7 +4424,7 @@
       <c r="I107" s="6" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
-      <c r="A108" s="8" t="n"/>
+      <c r="A108" s="9" t="n"/>
       <c r="B108" s="9" t="n"/>
       <c r="C108" s="4" t="n">
         <v>107</v>
@@ -4461,7 +4461,7 @@
       <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109" hidden="1">
-      <c r="A109" s="8" t="n"/>
+      <c r="A109" s="9" t="n"/>
       <c r="B109" s="9" t="n"/>
       <c r="C109" s="4" t="n">
         <v>108</v>
@@ -4497,7 +4497,7 @@
       <c r="I109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
+      <c r="A110" s="9" t="n"/>
       <c r="B110" s="10" t="n"/>
       <c r="C110" s="4" t="n">
         <v>109</v>
@@ -4532,7 +4532,7 @@
       <c r="I110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
+      <c r="A111" s="9" t="n"/>
       <c r="B111" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
@@ -4577,7 +4577,7 @@
       <c r="I111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
+      <c r="A112" s="9" t="n"/>
       <c r="B112" s="9" t="n"/>
       <c r="C112" s="16" t="n">
         <v>111</v>
@@ -4621,7 +4621,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
+      <c r="A113" s="9" t="n"/>
       <c r="B113" s="9" t="n"/>
       <c r="C113" s="16" t="n">
         <v>112</v>
@@ -4667,7 +4667,7 @@
       <c r="I113" s="18" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
+      <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
       <c r="C114" s="16" t="n">
         <v>113</v>
@@ -4724,7 +4724,7 @@
       <c r="I114" s="18" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
+      <c r="A115" s="9" t="n"/>
       <c r="B115" s="9" t="n"/>
       <c r="C115" s="16" t="n">
         <v>114</v>
@@ -4784,7 +4784,7 @@
       <c r="I115" s="18" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
+      <c r="A116" s="9" t="n"/>
       <c r="B116" s="9" t="n"/>
       <c r="C116" s="16" t="n">
         <v>115</v>
@@ -4822,7 +4822,7 @@
       <c r="I116" s="18" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
+      <c r="A117" s="9" t="n"/>
       <c r="B117" s="10" t="n"/>
       <c r="C117" s="16" t="n">
         <v>116</v>
@@ -4870,7 +4870,7 @@
       <c r="I117" s="18" t="inlineStr"/>
     </row>
     <row r="118" hidden="1">
-      <c r="A118" s="8" t="n"/>
+      <c r="A118" s="9" t="n"/>
       <c r="B118" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4917,7 +4917,7 @@
       <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
+      <c r="A119" s="9" t="n"/>
       <c r="B119" s="9" t="n"/>
       <c r="C119" s="4" t="n">
         <v>118</v>
@@ -4992,7 +4992,7 @@
       <c r="I119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
+      <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
       <c r="C120" s="4" t="n">
         <v>119</v>
@@ -5025,7 +5025,7 @@
       <c r="I120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
+      <c r="A121" s="9" t="n"/>
       <c r="B121" s="9" t="n"/>
       <c r="C121" s="4" t="n">
         <v>120</v>
@@ -5097,7 +5097,7 @@
       <c r="I121" s="6" t="inlineStr"/>
     </row>
     <row r="122" hidden="1">
-      <c r="A122" s="8" t="n"/>
+      <c r="A122" s="9" t="n"/>
       <c r="B122" s="9" t="n"/>
       <c r="C122" s="4" t="n">
         <v>121</v>
@@ -5130,7 +5130,7 @@
       <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
+      <c r="A123" s="9" t="n"/>
       <c r="B123" s="10" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
@@ -5168,7 +5168,7 @@
       <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
+      <c r="A124" s="9" t="n"/>
       <c r="B124" s="15" t="inlineStr">
         <is>
           <t>16. 시황 — 상담에 쓰는 만큼</t>
@@ -5205,7 +5205,7 @@
       <c r="I124" s="18" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
+      <c r="A125" s="9" t="n"/>
       <c r="B125" s="9" t="n"/>
       <c r="C125" s="16" t="n">
         <v>124</v>
@@ -5244,7 +5244,7 @@
       <c r="I125" s="18" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="n"/>
+      <c r="A126" s="9" t="n"/>
       <c r="B126" s="9" t="n"/>
       <c r="C126" s="16" t="n">
         <v>125</v>
@@ -5282,7 +5282,7 @@
       <c r="I126" s="18" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="n"/>
+      <c r="A127" s="9" t="n"/>
       <c r="B127" s="9" t="n"/>
       <c r="C127" s="16" t="n">
         <v>126</v>
@@ -5315,7 +5315,7 @@
       <c r="I127" s="18" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
+      <c r="A128" s="9" t="n"/>
       <c r="B128" s="10" t="n"/>
       <c r="C128" s="16" t="n">
         <v>127</v>
@@ -5354,7 +5354,7 @@
       <c r="I128" s="18" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
-      <c r="A129" s="8" t="n"/>
+      <c r="A129" s="9" t="n"/>
       <c r="B129" s="3" t="inlineStr">
         <is>
           <t>17. 복합·연쇄 턴</t>
@@ -5394,7 +5394,7 @@
       <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="n"/>
+      <c r="A130" s="9" t="n"/>
       <c r="B130" s="9" t="n"/>
       <c r="C130" s="4" t="n">
         <v>129</v>
@@ -5431,7 +5431,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
+      <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -5470,7 +5470,7 @@
       <c r="I131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
+      <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
       <c r="C132" s="4" t="n">
         <v>131</v>
@@ -5503,7 +5503,7 @@
       <c r="I132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
+      <c r="A133" s="9" t="n"/>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="4" t="n">
         <v>132</v>
@@ -5544,7 +5544,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
+      <c r="A134" s="9" t="n"/>
       <c r="B134" s="9" t="n"/>
       <c r="C134" s="4" t="n">
         <v>133</v>
@@ -5581,7 +5581,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
+      <c r="A135" s="9" t="n"/>
       <c r="B135" s="9" t="n"/>
       <c r="C135" s="4" t="n">
         <v>134</v>
@@ -5622,7 +5622,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
+      <c r="A136" s="9" t="n"/>
       <c r="B136" s="9" t="n"/>
       <c r="C136" s="4" t="n">
         <v>135</v>
@@ -5661,7 +5661,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
+      <c r="A137" s="9" t="n"/>
       <c r="B137" s="9" t="n"/>
       <c r="C137" s="4" t="n">
         <v>136</v>
@@ -5673,9 +5673,7 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>어느 채널에서 조회하는 경로를 안내해 드릴까요?
-· KB스타뱅킹
-· 인터넷뱅킹</t>
+          <t>고객이 퇴직연금 ETF 상품을 직접 찾아보실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 확인해 드릴게요. KB스타뱅킹을 이용하신다면 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, 나의 ETF · ETF 상품 조회 순으로 이동하시면 되어요. 인터넷뱅킹을 이용하실 경우에는 KB퇴직연금, 개인고객, 퇴직연금 ETF, 나의 ETF · ETF 상품조회 메뉴를 통해 조회하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
@@ -5700,7 +5698,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
+      <c r="A138" s="9" t="n"/>
       <c r="B138" s="9" t="n"/>
       <c r="C138" s="4" t="n">
         <v>137</v>
@@ -5738,7 +5736,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
+      <c r="A139" s="9" t="n"/>
       <c r="B139" s="9" t="n"/>
       <c r="C139" s="4" t="n">
         <v>138</v>
@@ -5775,7 +5773,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
+      <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
       <c r="C140" s="4" t="n">
         <v>139</v>
@@ -5812,7 +5810,7 @@
       </c>
     </row>
     <row r="141" hidden="1">
-      <c r="A141" s="8" t="n"/>
+      <c r="A141" s="9" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="4" t="n">
         <v>140</v>
@@ -5845,7 +5843,7 @@
       <c r="I141" s="6" t="inlineStr"/>
     </row>
     <row r="142" hidden="1">
-      <c r="A142" s="24" t="n"/>
+      <c r="A142" s="10" t="n"/>
       <c r="B142" s="10" t="n"/>
       <c r="C142" s="4" t="n">
         <v>141</v>
@@ -5921,7 +5919,7 @@
       <c r="I143" s="18" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
+      <c r="A144" s="9" t="n"/>
       <c r="B144" s="9" t="n"/>
       <c r="C144" s="16" t="n">
         <v>143</v>
@@ -5962,7 +5960,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
+      <c r="A145" s="9" t="n"/>
       <c r="B145" s="9" t="n"/>
       <c r="C145" s="16" t="n">
         <v>144</v>
@@ -6003,7 +6001,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
+      <c r="A146" s="9" t="n"/>
       <c r="B146" s="9" t="n"/>
       <c r="C146" s="16" t="n">
         <v>145</v>
@@ -6042,7 +6040,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
+      <c r="A147" s="9" t="n"/>
       <c r="B147" s="9" t="n"/>
       <c r="C147" s="16" t="n">
         <v>146</v>
@@ -6089,7 +6087,7 @@
       </c>
     </row>
     <row r="148" hidden="1">
-      <c r="A148" s="8" t="n"/>
+      <c r="A148" s="9" t="n"/>
       <c r="B148" s="10" t="n"/>
       <c r="C148" s="16" t="n">
         <v>147</v>
@@ -6122,7 +6120,7 @@
       <c r="I148" s="18" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="n"/>
+      <c r="A149" s="9" t="n"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6168,7 +6166,7 @@
       </c>
     </row>
     <row r="150" hidden="1">
-      <c r="A150" s="8" t="n"/>
+      <c r="A150" s="9" t="n"/>
       <c r="B150" s="9" t="n"/>
       <c r="C150" s="4" t="n">
         <v>149</v>
@@ -6205,7 +6203,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="n"/>
+      <c r="A151" s="9" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
         <v>150</v>
@@ -6242,7 +6240,7 @@
       </c>
     </row>
     <row r="152" hidden="1">
-      <c r="A152" s="8" t="n"/>
+      <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
         <v>151</v>
@@ -6275,7 +6273,7 @@
       <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153" hidden="1">
-      <c r="A153" s="8" t="n"/>
+      <c r="A153" s="9" t="n"/>
       <c r="B153" s="10" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
@@ -6312,7 +6310,7 @@
       </c>
     </row>
     <row r="154" hidden="1">
-      <c r="A154" s="8" t="n"/>
+      <c r="A154" s="9" t="n"/>
       <c r="B154" s="15" t="inlineStr">
         <is>
           <t>20. 브리핑 수정</t>
@@ -6349,7 +6347,7 @@
       <c r="I154" s="18" t="inlineStr"/>
     </row>
     <row r="155" hidden="1">
-      <c r="A155" s="8" t="n"/>
+      <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
       <c r="C155" s="16" t="n">
         <v>154</v>
@@ -6382,7 +6380,7 @@
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156" hidden="1">
-      <c r="A156" s="8" t="n"/>
+      <c r="A156" s="9" t="n"/>
       <c r="B156" s="10" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
@@ -6426,7 +6424,7 @@
       <c r="I156" s="18" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="n"/>
+      <c r="A157" s="9" t="n"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
@@ -6470,7 +6468,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="n"/>
+      <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
       <c r="C158" s="4" t="n">
         <v>157</v>
@@ -6509,7 +6507,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="n"/>
+      <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
       <c r="C159" s="4" t="n">
         <v>158</v>
@@ -6546,7 +6544,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="n"/>
+      <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
       <c r="C160" s="4" t="n">
         <v>159</v>
@@ -6591,7 +6589,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="n"/>
+      <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
       <c r="C161" s="4" t="n">
         <v>160</v>
@@ -6630,7 +6628,7 @@
       </c>
     </row>
     <row r="162" hidden="1">
-      <c r="A162" s="8" t="n"/>
+      <c r="A162" s="9" t="n"/>
       <c r="B162" s="10" t="n"/>
       <c r="C162" s="4" t="n">
         <v>161</v>
@@ -6663,7 +6661,7 @@
       <c r="I162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="n"/>
+      <c r="A163" s="9" t="n"/>
       <c r="B163" s="15" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -6715,7 +6713,7 @@
       <c r="I163" s="18" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="n"/>
+      <c r="A164" s="9" t="n"/>
       <c r="B164" s="9" t="n"/>
       <c r="C164" s="16" t="n">
         <v>163</v>
@@ -6765,7 +6763,7 @@
       <c r="I164" s="18" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="8" t="n"/>
+      <c r="A165" s="9" t="n"/>
       <c r="B165" s="10" t="n"/>
       <c r="C165" s="16" t="n">
         <v>164</v>
@@ -6815,7 +6813,7 @@
       <c r="I165" s="18" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="8" t="n"/>
+      <c r="A166" s="9" t="n"/>
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>23. 오늘의 타겟 목록</t>
@@ -6852,7 +6850,7 @@
       <c r="I166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="24" t="n"/>
+      <c r="A167" s="10" t="n"/>
       <c r="B167" s="10" t="n"/>
       <c r="C167" s="4" t="n">
         <v>166</v>
@@ -6946,7 +6944,7 @@
       <c r="I168" s="18" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
-      <c r="A169" s="8" t="n"/>
+      <c r="A169" s="9" t="n"/>
       <c r="B169" s="9" t="n"/>
       <c r="C169" s="16" t="n">
         <v>168</v>
@@ -7005,7 +7003,7 @@
       <c r="I169" s="18" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
-      <c r="A170" s="8" t="n"/>
+      <c r="A170" s="9" t="n"/>
       <c r="B170" s="9" t="n"/>
       <c r="C170" s="16" t="n">
         <v>169</v>
@@ -7051,7 +7049,7 @@
       <c r="I170" s="18" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
-      <c r="A171" s="8" t="n"/>
+      <c r="A171" s="9" t="n"/>
       <c r="B171" s="9" t="n"/>
       <c r="C171" s="16" t="n">
         <v>170</v>
@@ -7088,7 +7086,7 @@
       </c>
     </row>
     <row r="172" hidden="1">
-      <c r="A172" s="8" t="n"/>
+      <c r="A172" s="9" t="n"/>
       <c r="B172" s="9" t="n"/>
       <c r="C172" s="16" t="n">
         <v>171</v>
@@ -7121,7 +7119,7 @@
       <c r="I172" s="18" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
-      <c r="A173" s="8" t="n"/>
+      <c r="A173" s="9" t="n"/>
       <c r="B173" s="9" t="n"/>
       <c r="C173" s="16" t="n">
         <v>172</v>
@@ -7155,7 +7153,7 @@
       <c r="I173" s="18" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
-      <c r="A174" s="8" t="n"/>
+      <c r="A174" s="9" t="n"/>
       <c r="B174" s="9" t="n"/>
       <c r="C174" s="16" t="n">
         <v>173</v>
@@ -7188,7 +7186,7 @@
       <c r="I174" s="18" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
-      <c r="A175" s="8" t="n"/>
+      <c r="A175" s="9" t="n"/>
       <c r="B175" s="9" t="n"/>
       <c r="C175" s="16" t="n">
         <v>174</v>
@@ -7225,7 +7223,7 @@
       </c>
     </row>
     <row r="176" hidden="1">
-      <c r="A176" s="8" t="n"/>
+      <c r="A176" s="9" t="n"/>
       <c r="B176" s="10" t="n"/>
       <c r="C176" s="16" t="n">
         <v>175</v>
@@ -7258,7 +7256,7 @@
       <c r="I176" s="18" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
-      <c r="A177" s="8" t="n"/>
+      <c r="A177" s="9" t="n"/>
       <c r="B177" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -7297,7 +7295,7 @@
       <c r="I177" s="6" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
-      <c r="A178" s="8" t="n"/>
+      <c r="A178" s="9" t="n"/>
       <c r="B178" s="9" t="n"/>
       <c r="C178" s="4" t="n">
         <v>177</v>
@@ -7332,7 +7330,7 @@
       <c r="I178" s="6" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
-      <c r="A179" s="8" t="n"/>
+      <c r="A179" s="9" t="n"/>
       <c r="B179" s="9" t="n"/>
       <c r="C179" s="4" t="n">
         <v>178</v>
@@ -7365,7 +7363,7 @@
       <c r="I179" s="6" t="inlineStr"/>
     </row>
     <row r="180" hidden="1">
-      <c r="A180" s="8" t="n"/>
+      <c r="A180" s="9" t="n"/>
       <c r="B180" s="9" t="n"/>
       <c r="C180" s="4" t="n">
         <v>179</v>
@@ -7398,7 +7396,7 @@
       <c r="I180" s="6" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
-      <c r="A181" s="8" t="n"/>
+      <c r="A181" s="9" t="n"/>
       <c r="B181" s="9" t="n"/>
       <c r="C181" s="4" t="n">
         <v>180</v>
@@ -7436,7 +7434,7 @@
       <c r="I181" s="6" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
-      <c r="A182" s="8" t="n"/>
+      <c r="A182" s="9" t="n"/>
       <c r="B182" s="10" t="n"/>
       <c r="C182" s="4" t="n">
         <v>181</v>
@@ -7469,7 +7467,7 @@
       </c>
     </row>
     <row r="183" hidden="1">
-      <c r="A183" s="8" t="n"/>
+      <c r="A183" s="9" t="n"/>
       <c r="B183" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -7543,7 +7541,7 @@
       <c r="I183" s="18" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
-      <c r="A184" s="8" t="n"/>
+      <c r="A184" s="9" t="n"/>
       <c r="B184" s="9" t="n"/>
       <c r="C184" s="16" t="n">
         <v>183</v>
@@ -7579,7 +7577,7 @@
       <c r="I184" s="18" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
-      <c r="A185" s="8" t="n"/>
+      <c r="A185" s="9" t="n"/>
       <c r="B185" s="9" t="n"/>
       <c r="C185" s="16" t="n">
         <v>184</v>
@@ -7618,7 +7616,7 @@
       <c r="I185" s="18" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
-      <c r="A186" s="8" t="n"/>
+      <c r="A186" s="9" t="n"/>
       <c r="B186" s="9" t="n"/>
       <c r="C186" s="16" t="n">
         <v>185</v>
@@ -7654,7 +7652,7 @@
       <c r="I186" s="18" t="inlineStr"/>
     </row>
     <row r="187" hidden="1">
-      <c r="A187" s="8" t="n"/>
+      <c r="A187" s="9" t="n"/>
       <c r="B187" s="9" t="n"/>
       <c r="C187" s="16" t="n">
         <v>186</v>
@@ -7690,7 +7688,7 @@
       <c r="I187" s="18" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
-      <c r="A188" s="8" t="n"/>
+      <c r="A188" s="9" t="n"/>
       <c r="B188" s="9" t="n"/>
       <c r="C188" s="16" t="n">
         <v>187</v>
@@ -7727,7 +7725,7 @@
       <c r="I188" s="18" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
-      <c r="A189" s="8" t="n"/>
+      <c r="A189" s="9" t="n"/>
       <c r="B189" s="9" t="n"/>
       <c r="C189" s="16" t="n">
         <v>188</v>
@@ -7763,7 +7761,7 @@
       <c r="I189" s="18" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
-      <c r="A190" s="8" t="n"/>
+      <c r="A190" s="9" t="n"/>
       <c r="B190" s="9" t="n"/>
       <c r="C190" s="16" t="n">
         <v>189</v>
@@ -7799,7 +7797,7 @@
       <c r="I190" s="18" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
-      <c r="A191" s="8" t="n"/>
+      <c r="A191" s="9" t="n"/>
       <c r="B191" s="9" t="n"/>
       <c r="C191" s="16" t="n">
         <v>190</v>
@@ -7836,7 +7834,7 @@
       <c r="I191" s="18" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
-      <c r="A192" s="8" t="n"/>
+      <c r="A192" s="9" t="n"/>
       <c r="B192" s="9" t="n"/>
       <c r="C192" s="16" t="n">
         <v>191</v>
@@ -7872,7 +7870,7 @@
       <c r="I192" s="18" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
-      <c r="A193" s="8" t="n"/>
+      <c r="A193" s="9" t="n"/>
       <c r="B193" s="9" t="n"/>
       <c r="C193" s="16" t="n">
         <v>192</v>
@@ -7908,7 +7906,7 @@
       <c r="I193" s="18" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
-      <c r="A194" s="24" t="n"/>
+      <c r="A194" s="10" t="n"/>
       <c r="B194" s="10" t="n"/>
       <c r="C194" s="16" t="n">
         <v>193</v>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="I38" s="18" t="inlineStr"/>
     </row>
-    <row r="39">
+    <row r="39" hidden="1">
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="16" t="n">
@@ -1938,89 +1938,138 @@
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
+          <t>이 고객 대출이 많은데 추가납입 권해도 돼?</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>대출 및 추가납입 가능 여부와 관련된 내용은 제가 가진 자료로는 확인이 어려워요. 다만 해당 고객의 투자성향 적합성 확인 결과에 따른 안내 가능 상품 정보를 정리해 드릴게요. 
+이 고객은 안정추구형 성향이며 적합성 허용 상한은 낮은위험으로, 이 등급까지의 상품만 안내할 수 있어요. 
+안내할 수 있는 상품은 다음과 같아요.
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+- KB 안정형 MP — 낮은위험 · 최근 1년 3.9% · MP
+- KB GIC 확정금리 — 매우낮은위험 · 최근 1년 3.65% · GIC
+- KB ELB 지수연계 — 낮은위험 · 최근 1년 4.1% · ELB
+- KB 정기예금(1년) — 매우낮은위험 · 최근 1년 3.1% · 예금
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험 · 최근 1년 3.3% · MP
+안내할 수 없는 상품들의 허용 상한 초과 사유는 동일하며, 각 상품의 위험등급은 다음과 같아요.
+- KB 글로벌채권인덱스 C-P — 보통위험
+- KB 온국민TDF2035 C-P — 다소높은위험
+- KB 온국민TDF2040 C-P — 다소높은위험
+- KB 중립형 MP — 보통위험
+- KB 성장형 MP — 다소높은위험
+- KB 글로벌리츠 ETF — 높은위험
+이 내용은 어디까지나 적합성 확인 결과이며, 특정 상품에 대한 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>한도 남은 고객 — 예: 박정호 168450-7293815</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>없는 축은 이름을 대고, 아는 것(잔여한도)과 가드(m.1-1 사용계획 자금)를 엮어 답한다 ↔ 첫 문장만 맞고 적합성 상품 목록으로 비켜간다</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
           <t>이 고객 디폴트옵션 등록됐어?</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객님은 디폴트옵션이 미설정 상태예요. 
 디폴트옵션 미지정 고객에게는 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 이렇게 말해 보세요. "여기서의 위험은 '데인저러스'가 아니고 '리스크'입니다. 리스크가 곧 변동성이거든요"라고 설명하며 용어에 대한 부담을 없애고, 연금사업자가 자기 이름을 걸고 운용하므로 관리에 신경 쓴다는 점을 함께 안내해 주세요. 고유계정대 2억 8,000만원을 보유하고 계시므로, 현금성자산 운용지시나 리밸런싱을 권유할 때 디폴트옵션 가입을 함께 유도하는 방향으로 활용할 수 있어요.</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>한 줄 답에 근거 한 건 ↔ 답에 안 쓴 ⑥⑦⑧ 카드까지 근거가 여섯 건 선다</t>
         </is>
       </c>
-      <c r="I39" s="18" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>(더미 문구로 LMS 요청한 뒤) 응, 열어줘</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>연계하지 않았어요. 더미 콘텐츠는 발송 화면에 채울 수 없습니다 — 실제 콘텐츠로 교체한 뒤(자산의 dummy 표시 제거) 다시 시도하세요</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>더미 자산 문구는 발송 화면에 안 채운다 ↔ 게이트가 조용히 열린다</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>"[KB국민은행] 고객님의 개인형IRP 운용 상태를 점검해 안내드릴 예정입니다. 자세한 내용은 https://obank.kbstar.com/pending/irp-checkup-draft 에서 확인해 주세요." 로 LMS 보내줘</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Ⅱ. 상담 중 — 지식 질의응답</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>7. 제도·수치 확인</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="C42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>IRP 세액공제 한도가 얼마야?</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>IRP를 포함한 세액공제 한도는 연간 납입액 최대 900만원이에요. 2026년 6월 기준 자료에 따르면, 연금저축만으로는 한도가 연 600만원이지만 IRP를 포함하면 900만원까지 확대돼요.
 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 고객님은 16.5%, 초과하는 고객님은 13.2%(지방소득세 포함)의 공제율이 적용돼요. 이에 따라 900만원을 모두 채우면 각각 1,485,000원과 1,188,000원을 환급받을 수 있어요.
@@ -2031,52 +2080,19 @@
 · 고객이 앱에서 직접 할 수 있어?</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>900만원 + 연금저축과 공유하는 한도라는 단서 ↔ 되묻는다 · 「IRP에만 900만원」으로 읽힌다</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>고객이 중도해지나 중도인출 시 적용되는 세금을 물을 때에는 2026년 6월 기준 자료를 바탕으로 정확한 과세 방식을 짚어주어야 해요. 중도인출은 일시금 수령과 동일하게 기타소득세 16.5%(지방소득세 포함) 가 부과되고, 중도해지 시에도 세액공제 받은 납입원금·운용수익에 기타소득세 16.5%만 분리과세된다. 이 부담은 납입 시 세액공제(16.5%)와 크거나 같아, 공제받은 고객이 중도인출하면 혜택이 상쇄된다. 연금수령한도 초과 인출분도 소득원천별(퇴직소득세·기타소득세)로 과세된다. 기준시점 2026.06 (KBthink 01 일치) 내용을 안내해 드려요. 과세 대상은 세액공제 받은 원금과 운용수익에 한정되며, 세액공제를 받지 않은 과세제외분은 제외된다는 점을 함께 확인해 주세요.</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2089,17 +2105,17 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
+          <t>고객이 중간에 깨면 세금 얼마나 떼냐고 묻는데 정확히 알려줘</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>IRP 중도인출은 법정 사유에 한해 가능하다. 2026년 6월 기준으로 무주택자 주택구입(매매계약 체결일~소유권 이전 등기 접수일 후 1개월 이내 신청), 무주택자 전세금·임차보증금(계약 체결일~잔금 지급일 후 1개월 이내, 하나의 사업장 근무 중 1회 한정), 본인·배우자·부양가족의 6개월 이상 요양(연간 임금총액의 12.5% 초과 의료비 부담 시), 자연재난·특별재난지역 사회재난 피해, 5년 이내 개인회생절차 개시 결정, 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 최대 90%까지 일부 인출할 수 있으며 횟수 제한은 없다. 다만 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다.</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 시연본</t>
+          <t>고객이 중도해지나 중도인출 시 적용되는 세금을 물을 때에는 2026년 6월 기준 자료를 바탕으로 정확한 과세 방식을 짚어주어야 해요. 중도인출은 일시금 수령과 동일하게 기타소득세 16.5%(지방소득세 포함) 가 부과되고, 중도해지 시에도 세액공제 받은 납입원금·운용수익에 기타소득세 16.5%만 분리과세된다. 이 부담은 납입 시 세액공제(16.5%)와 크거나 같아, 공제받은 고객이 중도인출하면 혜택이 상쇄된다. 연금수령한도 초과 인출분도 소득원천별(퇴직소득세·기타소득세)로 과세된다. 기준시점 2026.06 (KBthink 01 일치) 내용을 안내해 드려요. 과세 대상은 세액공제 받은 원금과 운용수익에 한정되며, 세액공제를 받지 않은 과세제외분은 제외된다는 점을 함께 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2109,7 +2125,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
+          <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -2120,29 +2136,29 @@
       <c r="C44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>수수료 얼마야?</t>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>IRP 중도인출 되는 법정 사유가 뭐뭐 있는지 기한·한도·횟수까지 알려줘</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>사용자부담금 대면 계좌 기준으로 안내드리면, 2026년 3월 기준 개인형IRP 수수료율은 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%가 적용돼요. 단일 수치로 안내하면 오답이 될 수 있으므로 단말에서 부담금 종류와 채널, 금액 구간을 먼저 확인하고 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본</t>
+          <t>IRP 중도인출은 법정 사유에 한해 가능하다. 2026년 6월 기준으로 무주택자 주택구입(매매계약 체결일~소유권 이전 등기 접수일 후 1개월 이내 신청), 무주택자 전세금·임차보증금(계약 체결일~잔금 지급일 후 1개월 이내, 하나의 사업장 근무 중 1회 한정), 본인·배우자·부양가족의 6개월 이상 요양(연간 임금총액의 12.5% 초과 의료비 부담 시), 자연재난·특별재난지역 사회재난 피해, 5년 이내 개인회생절차 개시 결정, 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 최대 90%까지 일부 인출할 수 있으며 횟수 제한은 없다. 다만 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
+          <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -2153,27 +2169,29 @@
       <c r="C45" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="D45" s="10" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>수수료 얼마야?</t>
+        </is>
+      </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>어느 부담금인가요?
-· 사용자부담금
-· 가입자부담금</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
+          <t>사용자부담금 대면 계좌 기준으로 안내드리면, 2026년 3월 기준 개인형IRP 수수료율은 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%가 적용돼요. 단일 수치로 안내하면 오답이 될 수 있으므로 단말에서 부담금 종류와 채널, 금액 구간을 먼저 확인하고 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
+          <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
@@ -2184,20 +2202,17 @@
       <c r="C46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>타행 IRP 수수료는 우리보다 싼가?</t>
-        </is>
-      </c>
+      <c r="D46" s="10" t="n"/>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>타행 IRP 수수료는 제가 가진 자료로는 확인이 어려워요. 다만 당행의 개인형IRP 수수료율에 대한 안내는 드릴 수 있으니 참고해 주세요. 
-2026년 3월 기준 개인형IRP 수수료율은 부담금 종류와 채널, 구간에 따라 다르게 적용돼요. 사용자부담금(퇴직금)은 대면 채널에서 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%이며, 비대면 채널에서는 5천만원 미만인 경우 0.20%, 5천만원 이상인 경우 면제로 적용돼요. 가입자부담금은 대면 채널에서 1억원 미만인 경우 0.28%, 1억원 이상인 경우 0.25%이고, 비대면 채널에서는 1억원 미만인 경우 0.23%, 1억원 이상인 경우 0.21%로 적용되니 안내해 드릴 때 이 점을 함께 확인해 주세요.</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 대본</t>
+          <t>어느 부담금인가요?
+· 사용자부담금
+· 가입자부담금</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2207,7 +2222,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
+          <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr"/>
@@ -2220,29 +2235,28 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>퇴직금을 통장으로 받은 걸 IRP에 다시 넣으면 세액공제도 받을 수 있어?</t>
+          <t>타행 IRP 수수료는 우리보다 싼가?</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>고객의 총급여 수준이 어떻게 되나요?
-· 5,500만원 이하
-· 5,500만원 초과</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
+          <t>타행 IRP 수수료는 제가 가진 자료로는 확인이 어려워요. 다만 당행의 개인형IRP 수수료율에 대한 안내는 드릴 수 있으니 참고해 주세요. 
+2026년 3월 기준 개인형IRP 수수료율은 부담금 종류와 채널, 구간에 따라 다르게 적용돼요. 사용자부담금(퇴직금)은 대면 채널에서 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%이며, 비대면 채널에서는 5천만원 미만인 경우 0.20%, 5천만원 이상인 경우 면제로 적용돼요. 가입자부담금은 대면 채널에서 1억원 미만인 경우 0.28%, 1억원 이상인 경우 0.25%이고, 비대면 채널에서는 1억원 미만인 경우 0.23%, 1억원 이상인 경우 0.21%로 적용되니 안내해 드릴 때 이 점을 함께 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 대본</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>박정호 168450-7293815</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
+          <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -2255,28 +2269,29 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
+          <t>퇴직금을 통장으로 받은 걸 IRP에 다시 넣으면 세액공제도 받을 수 있어?</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>총급여 5,500만원 이하 공제율 16.5%, 적금 이율 3.50% 가정, 이자소득세 15.4% 원천징수 전이라는 전제를 함께 짚어주면서 세액공제 환급액을 적금 이자와 같은 단위로 환산하는 방식을 활용하는 것이 좋아요. 
-"월 75만원 적립 = 적금 월 790만원" 비유를 사용해 세액공제 환급액을 적금 이자와 같은 단위로 환산하면 적금보다 10배 이상 차이 난다는 점을 쉽게 체감시킬 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>고객의 총급여 수준이 어떻게 되나요?
+· 5,500만원 이하
+· 5,500만원 초과</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>박정호 168450-7293815</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
+          <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2289,17 +2304,18 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>연간 납입한도가 얼마고 연금저축이랑 어떻게 나눠 쓰는 거야?</t>
+          <t>연말정산 얼마나 돌려받는지 고객한테 설명하려는데 근거 자료 좀 찾아줘</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2026년 3월부터 적용되는 개인형IRP의 연간 납입한도는 연금저축과 DC형 및 기업형IRP의 개인부담금을 모두 합산하여 1,800만원이에요. IRP 단독이 아니라 타행과 타사의 연금저축 납입액까지 포함되므로 실제 납입 여력은 [06-12-151] 화면의 개인부담금 연합회 한도 조회로 확인하고 안내해 드려야 해요. 세액공제 한도의 경우 연금저축만 보유하면 연 600만원이지만 개인형IRP를 포함하면 연 900만원까지 확대되므로, 연금저축만 가진 고객이라면 개인형IRP로 300만원의 추가 공제 여력을 활용하실 수 있어요. 세액공제 한도 900만원과 전체 납입한도 1,800만원은 혼동하기 쉬우니 구분해서 살펴볼 필요가 있어요.</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>총급여 5,500만원 이하 공제율 16.5%, 적금 이율 3.50% 가정, 이자소득세 15.4% 원천징수 전이라는 전제를 함께 짚어주면서 세액공제 환급액을 적금 이자와 같은 단위로 환산하는 방식을 활용하는 것이 좋아요. 
+"월 75만원 적립 = 적금 월 790만원" 비유를 사용해 세액공제 환급액을 적금 이자와 같은 단위로 환산하면 적금보다 10배 이상 차이 난다는 점을 쉽게 체감시킬 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -2309,7 +2325,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>1,800만원 + 연금저축·DC 개인부담금 합산 ↔ IRP 단독 한도로 답한다</t>
+          <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -2322,17 +2338,17 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>900만원 넘게 넣으면 그 초과분은 어떻게 돼?</t>
+          <t>연간 납입한도가 얼마고 연금저축이랑 어떻게 나눠 쓰는 거야?</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>2026년 3월 기준으로 세액공제 한도인 900만원을 초과해 납입한 금액은 세제 혜택과 인출 시 유리한 구조로 활용할 수 있어요. 900만원 초과분은 운용 기간 동안 과세이연 혜택을 받을 수 있고, 세액공제를 받지 않은 가입자부담금은 연금수령 시 과세제외로 인출할 수 있어요. 또한 올해 초과 납입분을 내년 세액공제분으로 이월 신청하는 이연 공제도 활용할 수 있어요. 다만 세액공제를 받지 않은 금액이 과세제외로 인출되려면 미공제 금액 등록이 선행되어야 하니 단말에서 이 부분을 먼저 챙겨 보셔야 해요. 이연 공제의 구체적인 실무 절차나 서류에 대해서는 제가 가진 자료로는 확인이 어려워요. 고객에게는 "세액공제 한도인 900만원을 초과해서 납입하시는 금액도 운용 기간 동안 과세이연 혜택을 받으실 수 있고, 공제받지 않은 금액은 나중에 연금으로 받으실 때 세금을 내지 않고 먼저 인출하실 수 있어요. 또한 올해 초과 납입하신 분량은 내년 세액공제분으로 이월해서 신청하실 수도 있습니다"라고 안내해 보세요.</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>2026년 3월부터 적용되는 개인형IRP의 연간 납입한도는 연금저축과 DC형 및 기업형IRP의 개인부담금을 모두 합산하여 1,800만원이에요. IRP 단독이 아니라 타행과 타사의 연금저축 납입액까지 포함되므로 실제 납입 여력은 [06-12-151] 화면의 개인부담금 연합회 한도 조회로 확인하고 안내해 드려야 해요. 세액공제 한도의 경우 연금저축만 보유하면 연 600만원이지만 개인형IRP를 포함하면 연 900만원까지 확대되므로, 연금저축만 가진 고객이라면 개인형IRP로 300만원의 추가 공제 여력을 활용하실 수 있어요. 세액공제 한도 900만원과 전체 납입한도 1,800만원은 혼동하기 쉬우니 구분해서 살펴볼 필요가 있어요.</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -2342,7 +2358,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>과세이연 + 인출 시 과세제외 + 이연 공제 신청 ↔ 「공제 안 된다」로만 끝낸다</t>
+          <t>1,800만원 + 연금저축·DC 개인부담금 합산 ↔ IRP 단독 한도로 답한다</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2355,17 +2371,17 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>위험자산 70% 한도가 뭐고 넘으면 어떻게 해?</t>
+          <t>900만원 넘게 넣으면 그 초과분은 어떻게 돼?</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>위험자산 70% 한도는 근로자퇴직급여보장법 시행령에 따라 주식형이나 주식혼합형 펀드 같은 위험자산을 평가금액의 70% 이내에서만 운용할 수 있는 규정이에요. 2026년 6월 기준 자료를 보면 전액 주식형 펀드로만 운용하는 것은 불가능하며, DB형의 경우에는 사용자별 전체 적립금 기준 70% 이내로 제한돼요. 만약 한도를 초과하더라도 별도의 페널티는 없고, 초과된 금액을 정기예금 같은 안전자산으로 교체매매하거나 추가입금을 한 뒤 안전자산으로 운용지시를 내려 해소하면 돼요. 세부적인 위반 현황은 확인 화면 04-12-354의 컴플라이언스 위반점검 현황조회에서 조회구분을 위험자산투자한도위반으로 설정해 확인할 수 있어요. 주식형 ETF의 포함 여부와 관련해서는 영업점 핫팁과 본부 자료의 언급이 달라 법령이나 감독규정 확인 전까지 확정해 안내하기 어려우니 이 점은 참고해 주세요.</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>2026년 3월 기준으로 세액공제 한도인 900만원을 초과해 납입한 금액은 세제 혜택과 인출 시 유리한 구조로 활용할 수 있어요. 900만원 초과분은 운용 기간 동안 과세이연 혜택을 받을 수 있고, 세액공제를 받지 않은 가입자부담금은 연금수령 시 과세제외로 인출할 수 있어요. 또한 올해 초과 납입분을 내년 세액공제분으로 이월 신청하는 이연 공제도 활용할 수 있어요. 다만 세액공제를 받지 않은 금액이 과세제외로 인출되려면 미공제 금액 등록이 선행되어야 하니 단말에서 이 부분을 먼저 챙겨 보셔야 해요. 이연 공제의 구체적인 실무 절차나 서류에 대해서는 제가 가진 자료로는 확인이 어려워요. 고객에게는 "세액공제 한도인 900만원을 초과해서 납입하시는 금액도 운용 기간 동안 과세이연 혜택을 받으실 수 있고, 공제받지 않은 금액은 나중에 연금으로 받으실 때 세금을 내지 않고 먼저 인출하실 수 있어요. 또한 올해 초과 납입하신 분량은 내년 세액공제분으로 이월해서 신청하실 수도 있습니다"라고 안내해 보세요.</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2375,7 +2391,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>한도 범위 + 초과 시 조치 + 확인 화면 ↔ 조치를 빼고 한도만 말한다</t>
+          <t>과세이연 + 인출 시 과세제외 + 이연 공제 신청 ↔ 「공제 안 된다」로만 끝낸다</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2388,17 +2404,17 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>TDF나 디폴트옵션은 70% 한도 예외라던데 맞아?</t>
+          <t>위험자산 70% 한도가 뭐고 넘으면 어떻게 해?</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>TDF나 디폴트옵션은 금감원장이 정한 기준을 충족할 때 위험자산 70% 한도의 예외로 적립금의 100%까지 운용할 수 있어요. 2026년 3~7월 자료를 기준으로 보면, 당행 퇴직연금에서 운용 가능한 TDF는 전부 적격 TDF에 해당해요. 다만 채권형이나 채권혼합형 ETF 100% 예외 같은 범위는 본부 자료에 없어서 지금 확인해 드리기 어려워요.</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>위험자산 70% 한도는 근로자퇴직급여보장법 시행령에 따라 주식형이나 주식혼합형 펀드 같은 위험자산을 평가금액의 70% 이내에서만 운용할 수 있는 규정이에요. 2026년 6월 기준 자료를 보면 전액 주식형 펀드로만 운용하는 것은 불가능하며, DB형의 경우에는 사용자별 전체 적립금 기준 70% 이내로 제한돼요. 만약 한도를 초과하더라도 별도의 페널티는 없고, 초과된 금액을 정기예금 같은 안전자산으로 교체매매하거나 추가입금을 한 뒤 안전자산으로 운용지시를 내려 해소하면 돼요. 세부적인 위반 현황은 확인 화면 04-12-354의 컴플라이언스 위반점검 현황조회에서 조회구분을 위험자산투자한도위반으로 설정해 확인할 수 있어요. 주식형 ETF의 포함 여부와 관련해서는 영업점 핫팁과 본부 자료의 언급이 달라 법령이나 감독규정 확인 전까지 확정해 안내하기 어려우니 이 점은 참고해 주세요.</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -2408,12 +2424,12 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>적격TDF·디폴트옵션 100% 운용 가능 ↔ 채권형 ETF 의 ⚠ 까지 단정한다</t>
+          <t>한도 범위 + 초과 시 조치 + 확인 화면 ↔ 조치를 빼고 한도만 말한다</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="4" t="n">
@@ -2421,10 +2437,43 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
+          <t>TDF나 디폴트옵션은 70% 한도 예외라던데 맞아?</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>TDF나 디폴트옵션은 금감원장이 정한 기준을 충족할 때 위험자산 70% 한도의 예외로 적립금의 100%까지 운용할 수 있어요. 2026년 3~7월 자료를 기준으로 보면, 당행 퇴직연금에서 운용 가능한 TDF는 전부 적격 TDF에 해당해요. 다만 채권형이나 채권혼합형 ETF 100% 예외 같은 범위는 본부 자료에 없어서 지금 확인해 드리기 어려워요.</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>적격TDF·디폴트옵션 100% 운용 가능 ↔ 채권형 ETF 의 ⚠ 까지 단정한다</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" hidden="1">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
           <t>디폴트옵션이 뭔지 고객한테 설명하려는데 위험등급이랑 적용되는 경우 알려줘</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>디폴트옵션 설명 및 적용되는 경우에 대해서는 제가 가진 자료로는 확인이 어려워요. 대신 참고하실 수 있도록 2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션) 목록과 포트폴리오 현황을 안내해 드릴게요.
 - 지켜드림 — 초저위험 / 시중은행 정기예금 중심 포트폴리오 (포트폴리오 1년 수익률 2.13%)
@@ -2441,35 +2490,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>정의 + 위험등급 4단계 + 적용 3케이스 ↔ 등급만 나열한다</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" hidden="1">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" hidden="1">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>IRP에서 살 수 있는 상품이 뭐뭐야?</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>그 부분은 제가 가진 자료로는 확인이 어려워요. 다만 2026년 8월 기준으로 IRP 등 퇴직연금에서 참고할 수 있는 디폴트옵션 추천펀드와 포트폴리오 자료는 다음과 같이 확인할 수 있어요.
 - 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성된 원리금보장형 포트폴리오
@@ -2487,79 +2536,46 @@
 ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>3분류·5종 정의 ↔ 상품명을 나열해 권유처럼 읽힌다(§8)</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>8. 세액공제 계산</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H55" s="18" t="inlineStr">
-        <is>
-          <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
-      <c r="B56" s="9" t="n"/>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>8. 세액공제 계산</t>
+        </is>
+      </c>
       <c r="C56" s="16" t="n">
         <v>55</v>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
+          <t>이 고객 300만원 더 넣으면 얼마 돌려받는지 계산해줘</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr">
         <is>
-          <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
+          <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
@@ -2569,7 +2585,7 @@
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
+          <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr"/>
@@ -2582,30 +2598,27 @@
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
+          <t>이 고객 한도 꽉 채우려면 얼마 더 넣어야 하고, 그러면 얼마 돌려받아?</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>현금을 더 납입하는 경우를 기준으로 안내드리면, 이 고객의 개인형IRP 계좌 추가 납입액 300만원에 대해 더 돌려받는 환급액은 없다. 
-이 고객은 당해 납입액이 0원이고 세액공제 한도 900만원과 잔여한도가 0원이라 추가 공제 대상이 없기 때문이다. 
-세액공제 잔여한도가 0원이라 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않으며, 세액공제 한도 900만원은 연금저축과 함께 쓴다. 단, 납입 자체는 연 납입한도 1,800만원까지 가능하다. 
-단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
         <is>
-          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
+          <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr"/>
@@ -2618,10 +2631,46 @@
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
+          <t>이 고객 300만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>현금을 더 납입하는 경우를 기준으로 안내드리면, 이 고객의 개인형IRP 계좌 추가 납입액 300만원에 대해 더 돌려받는 환급액은 없다. 
+이 고객은 당해 납입액이 0원이고 세액공제 한도 900만원과 잔여한도가 0원이라 추가 공제 대상이 없기 때문이다. 
+세액공제 잔여한도가 0원이라 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않으며, 세액공제 한도 900만원은 연금저축과 함께 쓴다. 단, 납입 자체는 연 납입한도 1,800만원까지 가능하다. 
+단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
@@ -2664,35 +2713,35 @@
 총급여 5,500만원 이하(16.5%) 적용 시, 8천만원 전액을 전환하면 추가 공제 대상 300만원에 대해 최대 495,000원의 환급액이 늘어나게 돼요. 8천만원보다 적은 일부 금액을 옮기더라도 3,000만원까지는 전환액의 10%가 추가 공제 대상에 더해지는 방식으로 계산되니 이 점을 참고해 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G58" s="18" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>ISA 만기자금 8천만원 다 옮기면 세액공제는 얼마나 받는 거야?</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="E60" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금을 8천만원 전부 전환할 때 세액공제 환급 예상액을 묻는 질문에는 개인형IRP 계좌 추가 납입인 현금 납입과 달리 ISA 만기자금 전환은 공제 대상 한도 자체가 늘어나는 축으로 다루는 게 핵심이에요. 
@@ -2717,35 +2766,35 @@
 · 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
         </is>
       </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="F60" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
-      <c r="I59" s="18" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E61" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 총급여 5,500만원 초과 구간인 고객에게는 ISA 만기자금 중 일부를 개인형IRP 계좌로 전환할 때의 세액공제 효과를 금액별로 짚어주는 게 핵심이에요. 앞서 말씀드린 8,000만원 전액 전환 시의 추가 공제 대상 300만원과 늘어나는 환급액 396,000원 외에, 질문하신 일부 금액 전환 시에는 전환액 1,000만원일 때 추가 공제 대상 100만원과 전환액 2,000만원일 때 추가 공제 대상 200만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액들은 현금을 더 납입하는 경우와 별개로 더해지는 몫이니, 두 한도를 같은 안에서 저울질하지 않고 각각 안내해 주세요.
@@ -2760,39 +2809,39 @@
 총급여 5,500만원 초과 구간인 송도윤 고객에게는 ISA 만기자금 1억 2,000만원 중 일부인 1억 2,000만원을 개인형IRP 계좌로 전환할 때 추가 공제 대상 300만원과 적용 공제율 13.2%를 반영한 환급 예상액 396,000원을 안내하는 것이 핵심이에요. 앞서 말씀드린 현금을 더 납입하는 경우와는 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않아야 해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F61" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="G60" s="18" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>원래 질문(300만원)과 고른 갈래를 합쳐 13.2% 로 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>(총급여 구간 되묻기 뒤) 5,500 이하야</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="E62" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 김서연 고객의 총급여가 5,500만원 이하인 경우라면 개인형IRP 계좌 추가 납입과 ISA 만기자금 전환 각각에 따른 세액공제 금액을 나누어 짚어 주는 게 핵심이에요. 현금을 추가 납입할 때는 500만원을 개인형IRP 계좌에 넣으면 총급여 5,500만원 이하 기준 16.5%가 적용되어 825,000원이 늘어난 1,485,000원의 환급을 예상할 수 있어요. ISA 만기자금 8,000만원 중 일부인 1,000만원을 전환할 때는 100만원이 추가 공제 대상이 되고, 2,000만원을 전환하면 200만원, 3,000만원 이상을 전환하면 상한인 300만원이 추가 공제 대상이 되어 총급여 5,500만원 이하 기준 16.5%를 적용하면 495,000원의 환급이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
@@ -2803,61 +2852,28 @@
 만기자금 전환은 기존 현금 추가 납입과 별개의 한도로 운영되는 몫이라 서로 다른 한도 안에서 저울질하지 않고 더해지는 구조예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G61" s="18" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>같은 자리에서 **16.5%** 로 갈린다(300만원이면 495,000원) ↔ 13.2% 로 답하거나 원장 구간이 이긴다고 직원 말을 무시한다</t>
         </is>
       </c>
-      <c r="I61" s="18" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
-        </is>
-      </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>오늘 날짜는 2026년 9월 29일 월요일이고 2026년 연말까지는 오늘을 세지 않고 93일 남았어요. 세액공제를 받으려면 올해 12월 31일까지 납입해야 해요.</t>
-        </is>
-      </c>
-      <c r="F62" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
-        </is>
-      </c>
-      <c r="G62" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H62" s="18" t="inlineStr">
-        <is>
-          <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
-        </is>
-      </c>
-      <c r="I62" s="18" t="inlineStr"/>
-    </row>
-    <row r="63" hidden="1">
+    <row r="63">
       <c r="A63" s="9" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="16" t="n">
@@ -2865,50 +2881,50 @@
       </c>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>이 고객 잔액은 언제 기준 값이야?</t>
+          <t>연말까지 며칠 남았고, 언제까지 넣어야 올해 공제 받는 거야?</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>해당 고객의 잔액 기준 시점에 대한 자료는 아직 준비된 자료가 없어요.</t>
-        </is>
-      </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>오늘 날짜는 2026년 9월 29일 월요일이고 2026년 연말까지는 오늘을 세지 않고 93일 남았어요. 세액공제를 받으려면 올해 12월 31일까지 납입해야 해요.</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
+          <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1">
       <c r="A64" s="9" t="n"/>
-      <c r="B64" s="10" t="n"/>
+      <c r="B64" s="9" t="n"/>
       <c r="C64" s="16" t="n">
         <v>63</v>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>300 넣으면 얼마 받아?</t>
+          <t>이 고객 잔액은 언제 기준 값이야?</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
-          <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 넣으면 적용받는 공제율에 따라 환급액이 달라져요. 총급여 5,500만원 이하인 경우 16.5%를 적용하여 개인형IRP 계좌 추가 납입으로 495,000원의 환급을 받게 되고, 총급여 5,500만원 초과인 경우 13.2%를 적용하여 개인형IRP 계좌 추가 납입으로 396,000원의 환급을 받게 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+          <t>해당 고객의 잔액 기준 시점에 대한 자료는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
@@ -2918,27 +2934,60 @@
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
+          <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n"/>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>300 넣으면 얼마 받아?</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 넣으면 적용받는 공제율에 따라 환급액이 달라져요. 총급여 5,500만원 이하인 경우 16.5%를 적용하여 개인형IRP 계좌 추가 납입으로 495,000원의 환급을 받게 되고, 총급여 5,500만원 초과인 경우 13.2%를 적용하여 개인형IRP 계좌 추가 납입으로 396,000원의 환급을 받게 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>9. 업무 처리 절차</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="C66" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>연금 개시 신청하려면 절차가 어떻게 되고 필요한 서류는 뭐야?</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
 연금 개시 신청 업무는 2단계로 처리해야 하니 [06-12-622] 세액 미공제 한도 등록을 먼저 거친 뒤 [02-12-221] 연금지급 등록을 진행하는 게 핵심이에요. 첫 단계의 준비서류는 연금보험료 등 소득·세액 공제 확인서이며 서류가 없을 때는 국민지갑에서 발급할 수 있어요. 본격적인 개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 먼저 확인해야 하며 연금개시 후에는 이전이 불가능해요. 또한 처리 중에 자동이체 금액이 입금되고 있거나 보유상품변경이 진행 중이면 거래가 불가하니 이 점을 주의해 주세요.
@@ -2946,54 +2995,19 @@
 연금 개시를 신청하는 고객에게는 2단계로 처리하는 것이 핵심이에요. 먼저 [06-12-622] 세액 미공제 한도 등록을 진행하고, 이어서 [02-12-221] 연금지급 등록을 처리해요. 세액 미공제 한도 등록 시에는 「연금보험료 등 소득·세액 공제 확인서」를 준비해야 하며, 서류가 없다면 국민지갑에서 발급할 수 있어요. 연금개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 꼭 확인해야 해요. 아울러 처리 중 자동이체 금액이 입금 중이거나 보유상품변경이 진행 중이면 거래가 불가하다는 점을 미리 안내드릴게요.</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>실물이전 어떻게 처리해?</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>어떤 처리 채널로 진행하시나요?
-· 비대면
-· 전문 송수신(일반)</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr"/>
@@ -3006,17 +3020,19 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
+          <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>과세이연 등록을 처리할 때는 과세이연정보(통산정보) 등록·조회와 과세이연계좌신고서 출력을 할 수 있는 [04-12-648] 과세이연정보관리 화면을 활용하면 돼요. 이어서 [01-12-213] 입금/입금예약 화면에서 거래구분을 과세이연/계약이전입금으로 선택해 입금을 진행하면 과세이연 등록 절차를 처리할 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리</t>
+          <t>어떤 처리 채널로 진행하시나요?
+· 비대면
+· 전문 송수신(일반)</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -3026,7 +3042,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
+          <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -3039,30 +3055,27 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
+          <t>과세이연 등록 절차가 어떻게 되는지 순서대로 알려줘</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>● 오세훈
-만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거친 뒤, [75-08-110] 화면을 통해 예약변경 거래를 처리하면 돼요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 현금성자산에 머무르므로, 저축은행 상품처럼 만기 안내와 예약변경이 중요해요. 특히 만기 후 6주(만기일부터 4주간 지시 없으면 안내 후 2주 뒤 적용)의 유예 구조가 있으나 만기 4주 시점에 본부 안내가 나가기 때문에, 접촉 가능 구간인 만기 1개월 전부터 만기 후 4주 사이에 서둘러 대응해야 해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 하는 방식을 활용할 수 있어요.
-● 이수민
-만기상품 예약변경은 먼저 사용계획이 있는 자금인지 확인하고 처리하는 게 핵심이에요. 정기예금은 만기에 자동 재예치되지 않아 방치되면 현금성자산에 머물게 되니 [75-08-110] 화면에서 만기상품 예약변경으로 처리해야 해요. 처리 순서는 익월 금리가 월 단위로 확정되므로 익월 금리 확인을 선행한 뒤 만기 1개월 전부터 예약변경을 걸고, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하는 방식이에요. 주의할 점은 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 먼저 걸러내야 하며, 디폴트옵션 미등록 고객은 사전지정 등록과 만기 예약변경을 함께 처리해야 한다는 점이에요.</t>
+          <t>과세이연 등록을 처리할 때는 과세이연정보(통산정보) 등록·조회와 과세이연계좌신고서 출력을 할 수 있는 [04-12-648] 과세이연정보관리 화면을 활용하면 돼요. 이어서 [01-12-213] 입금/입금예약 화면에서 거래구분을 과세이연/계약이전입금으로 선택해 입금을 진행하면 과세이연 등록 절차를 처리할 수 있어요.</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA</t>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
+          <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
@@ -3075,12 +3088,15 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
+          <t>만기상품 예약변경 처리 순서랑 주의할 점 알려줘</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 절차와 화면번호는 [75-08-110] 화면을 통해 처리해요. 원리금보장상품 만기가 다가오는데 디폴트옵션 미등록인 고객은 별도 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 디폴트옵션 사전지정 등록과 만기 예약변경으로 나누어 처리할 수 있어요. 만기 예약거래는 만기 한 달 전부터 가능하며, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하면 돼요. 처리는 디폴트옵션(저위험이상) 사전지정 등록과 만기 예약변경 두 갈래로 진행돼요.</t>
+          <t>● 오세훈
+만기상품 예약변경 처리 순서와 주의할 점은 만기 1개월 전부터 예약을 진행하고 매월 첫째 주 만기명세로 관리하는 것이 핵심이에요. 상품 금리는 월 단위로 확정되므로 익월 금리 확인을 먼저 거친 뒤, [75-08-110] 화면을 통해 예약변경 거래를 처리하면 돼요. 디폴트옵션 도입 후 정기예금은 만기에 자동 재예치되지 않고 현금성자산에 머무르므로, 저축은행 상품처럼 만기 안내와 예약변경이 중요해요. 특히 만기 후 6주(만기일부터 4주간 지시 없으면 안내 후 2주 뒤 적용)의 유예 구조가 있으나 만기 4주 시점에 본부 안내가 나가기 때문에, 접촉 가능 구간인 만기 1개월 전부터 만기 후 4주 사이에 서둘러 대응해야 해요. 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 하는 방식을 활용할 수 있어요.
+● 이수민
+만기상품 예약변경은 먼저 사용계획이 있는 자금인지 확인하고 처리하는 게 핵심이에요. 정기예금은 만기에 자동 재예치되지 않아 방치되면 현금성자산에 머물게 되니 [75-08-110] 화면에서 만기상품 예약변경으로 처리해야 해요. 처리 순서는 익월 금리가 월 단위로 확정되므로 익월 금리 확인을 선행한 뒤 만기 1개월 전부터 예약변경을 걸고, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하는 방식이에요. 주의할 점은 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 먼저 걸러내야 하며, 디폴트옵션 미등록 고객은 사전지정 등록과 만기 예약변경을 함께 처리해야 한다는 점이에요.</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -3090,12 +3106,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+          <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
+          <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr"/>
@@ -3108,32 +3124,32 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>추가납입 권유하기 전에 뭘 먼저 확인하고 들어가야 해?</t>
+          <t>디폴트옵션 등록 절차랑 화면번호 같이 알려줘</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>추가납입을 권유하기 전에, 이 고객의 당해 납입액이 0원이며 예상 세액공제액과 세액공제 잔여한도가 모두 0원으로 확인되는지 단말에서 먼저 살펴봐야 해요. 추가납입 여력을 살피는 과정에서는 사용계획이 있는 자금인지 확인하는 단계를 먼저 거쳐야 한다는 점을 염두에 두시면 좋아요.</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>디폴트옵션 등록 절차와 화면번호는 [75-08-110] 화면을 통해 처리해요. 원리금보장상품 만기가 다가오는데 디폴트옵션 미등록인 고객은 별도 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 디폴트옵션 사전지정 등록과 만기 예약변경으로 나누어 처리할 수 있어요. 만기 예약거래는 만기 한 달 전부터 가능하며, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하면 돼요. 처리는 디폴트옵션(저위험이상) 사전지정 등록과 만기 예약변경 두 갈래로 진행돼요.</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>입금이력·한도에 더해 **연금개시 여부**를 먼저 ↔ 연금개시 확인이 빠진다(§8 관리대장)</t>
+          <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
     </row>
-    <row r="71" hidden="1">
+    <row r="71">
       <c r="A71" s="9" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="4" t="n">
@@ -3141,13 +3157,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>수수료 불만 들었는데 상담 전에 뭘 준비해야 해?</t>
+          <t>추가납입 권유하기 전에 뭘 먼저 확인하고 들어가야 해?</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>그 부분은 제가 가진 자료로는 수수료 불만에 대한 구체적인 대응 지침을 확인하기 어려워요. 대신 현재 고객님은 고유계정대 금리가 더 높다던데요 같은 반론이나 디폴트옵션 거부 반응에 대비한 대응 논리를 활용하실 수 있어요. 
-상담을 준비하실 때는 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 설명하는 방향으로 준비해 보세요. 또한 사용계획이 있는 자금인지 먼저 확인하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주시는 것이 좋아요.</t>
+          <t>추가납입을 권유하기 전에, 이 고객의 당해 납입액이 0원이며 예상 세액공제액과 세액공제 잔여한도가 모두 0원으로 확인되는지 단말에서 먼저 살펴봐야 해요. 추가납입 여력을 살피는 과정에서는 사용계획이 있는 자금인지 확인하는 단계를 먼저 거쳐야 한다는 점을 염두에 두시면 좋아요.</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -3162,12 +3177,12 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>[04-12-613] 수수료 예상조회로 현재·전환 후를 숫자로 ↔ 화법만 주고 준비를 뺀다</t>
+          <t>입금이력·한도에 더해 **연금개시 여부**를 먼저 ↔ 연금개시 확인이 빠진다(§8 관리대장)</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
       <c r="C72" s="4" t="n">
@@ -3175,27 +3190,28 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>정기예금 중도해지하면 손실이 얼마인지 어떻게 확인해?</t>
+          <t>수수료 불만 들었는데 상담 전에 뭘 준비해야 해?</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>정기예금 중도해지 예상 손실금액은 「정기예금 중도해지 &amp; 리밸런싱 계산기」를 통해 산출할 수 있어요. 진입 경로는 1번 Info-zone의 연금(퇴직연금) 안 계산기 메뉴를 이용하시거나 [04-12-642] 화면 하단의 연계메뉴에서 바로 클릭하시면 돼요. 계산할 때는 예상이율을 현재 보유상품 이율로 변경한 뒤 조회해야 하며, 그 결과는 참고용이라는 점을 미리 안내해 드릴게요.</t>
-        </is>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>그 부분은 제가 가진 자료로는 수수료 불만에 대한 구체적인 대응 지침을 확인하기 어려워요. 대신 현재 고객님은 고유계정대 금리가 더 높다던데요 같은 반론이나 디폴트옵션 거부 반응에 대비한 대응 논리를 활용하실 수 있어요. 
+상담을 준비하실 때는 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 설명하는 방향으로 준비해 보세요. 또한 사용계획이 있는 자금인지 먼저 확인하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주시는 것이 좋아요.</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>계산기로 사전 산출 + 매도 우선순위 4단계 ↔ 「해지하면 손해」로만 끝낸다</t>
+          <t>[04-12-613] 수수료 예상조회로 현재·전환 후를 숫자로 ↔ 화법만 주고 준비를 뺀다</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -3208,12 +3224,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>퇴직소득세는 어떻게 계산해?</t>
+          <t>정기예금 중도해지하면 손실이 얼마인지 어떻게 확인해?</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>퇴직소득세는 개인형IRP 연금지급 화면인 [02-12-221]에서 입사일자, 중간정산특례 적용 여부, 퇴직일자, 퇴직금액을 입력해 계산하는 것이 핵심이에요. 2026년 기준시점으로, 해당 화면에 나오는 표시 금액은 순수 퇴직소득세이므로 지방소득세 10%를 별도로 더해 고객 안내 총 세액은 표시액의 1.1배로 계산해야 해요. 중간정산특례 적용 여부에 따른 세금 차이도 함께 비교할 수 있으니 참고해 주세요. 근속연수가 짧을수록, 퇴직급여가 많을수록 퇴직소득세가 커진다. 본부 제시 매트릭스(발췌) — 1억·5년 1,036만원(10%) / 1억·10년 426만원(4%) / 2억·10년 1,966만원(10%) / 2억·20년 773만원(4%) / 5억·10년 9,781만원(20%). 원문 각주가 "실제 부과 세액은 다소 상이할 수 있음"을 명시하므로 확정 세액으로 안내하지 말고, 정확한 세액은 홈택스 모의계산 또는 [02-12-221] 시뮬레이션(F46)으로 계산한다. 기준시점 2026</t>
+          <t>정기예금 중도해지 예상 손실금액은 「정기예금 중도해지 &amp; 리밸런싱 계산기」를 통해 산출할 수 있어요. 진입 경로는 1번 Info-zone의 연금(퇴직연금) 안 계산기 메뉴를 이용하시거나 [04-12-642] 화면 하단의 연계메뉴에서 바로 클릭하시면 돼요. 계산할 때는 예상이율을 현재 보유상품 이율로 변경한 뒤 조회해야 하며, 그 결과는 참고용이라는 점을 미리 안내해 드릴게요.</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -3228,25 +3244,25 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>[02-12-221] 「계산」 3단계 + 지방소득세 10% 별도 ↔ 별도분을 뺀다</t>
+          <t>계산기로 사전 산출 + 매도 우선순위 4단계 ↔ 「해지하면 손해」로만 끝낸다</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n"/>
-      <c r="B74" s="10" t="n"/>
+      <c r="B74" s="9" t="n"/>
       <c r="C74" s="4" t="n">
         <v>73</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>타사 연금 납입정보는 어떻게 확인해?</t>
+          <t>퇴직소득세는 어떻게 계산해?</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>타사 연금 납입정보를 파악할 때 활용할 수 있는 두 가지 경로를 안내해 드릴게요. 먼저 고객이 스타뱅킹에서 생활제휴, 국민지갑, 전자증명서 순으로 이동해 「연금보험료 등 소득·세액공제 확인서」를 전송하면, 직원은 [06-7E-001] 화면에서 문서열람번호로 출력할 수 있어요. 또는 [06-10-182] 화면의 연금납입정보 집중 조회 및 정정청구등록(해제) 메뉴를 통해 연금납입정보 현황을 직접 조회하는 방법도 있어요. 이 두 번째 조회 경로를 이용하실 때는 금융거래정보제공요청동의서를 반드시 징구해야 하니 유의해 주세요.</t>
+          <t>퇴직소득세는 개인형IRP 연금지급 화면인 [02-12-221]에서 입사일자, 중간정산특례 적용 여부, 퇴직일자, 퇴직금액을 입력해 계산하는 것이 핵심이에요. 2026년 기준시점으로, 해당 화면에 나오는 표시 금액은 순수 퇴직소득세이므로 지방소득세 10%를 별도로 더해 고객 안내 총 세액은 표시액의 1.1배로 계산해야 해요. 중간정산특례 적용 여부에 따른 세금 차이도 함께 비교할 수 있으니 참고해 주세요. 근속연수가 짧을수록, 퇴직급여가 많을수록 퇴직소득세가 커진다. 본부 제시 매트릭스(발췌) — 1억·5년 1,036만원(10%) / 1억·10년 426만원(4%) / 2억·10년 1,966만원(10%) / 2억·20년 773만원(4%) / 5억·10년 9,781만원(20%). 원문 각주가 "실제 부과 세액은 다소 상이할 수 있음"을 명시하므로 확정 세액으로 안내하지 말고, 정확한 세액은 홈택스 모의계산 또는 [02-12-221] 시뮬레이션(F46)으로 계산한다. 기준시점 2026</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -3261,60 +3277,93 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>전자증명서 출력 또는 집중조회(동의서 징구 필수) ↔ 동의서 징구를 뺀다</t>
+          <t>[02-12-221] 「계산」 3단계 + 지방소득세 10% 별도 ↔ 별도분을 뺀다</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n"/>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>10. 단말 화면번호</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="n">
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>IRP 계좌 해지 업무는 [02-12-220] 퇴직연금 지급 화면에서 진행해요. 해당 화면은 해지, 계좌이체, 미지급금 출금, 지연보상금 지급을 처리하는 화면이에요. 단일 자료에만 등장하는 내용이라 다른 화면 번호는 안내되지 않으니 참고해 주세요.</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스</t>
-        </is>
-      </c>
-      <c r="G75" s="18" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>타사 연금 납입정보는 어떻게 확인해?</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>타사 연금 납입정보를 파악할 때 활용할 수 있는 두 가지 경로를 안내해 드릴게요. 먼저 고객이 스타뱅킹에서 생활제휴, 국민지갑, 전자증명서 순으로 이동해 「연금보험료 등 소득·세액공제 확인서」를 전송하면, 직원은 [06-7E-001] 화면에서 문서열람번호로 출력할 수 있어요. 또는 [06-10-182] 화면의 연금납입정보 집중 조회 및 정정청구등록(해제) 메뉴를 통해 연금납입정보 현황을 직접 조회하는 방법도 있어요. 이 두 번째 조회 경로를 이용하실 때는 금융거래정보제공요청동의서를 반드시 징구해야 하니 유의해 주세요.</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H75" s="18" t="inlineStr">
-        <is>
-          <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>전자증명서 출력 또는 집중조회(동의서 징구 필수) ↔ 동의서 징구를 뺀다</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n"/>
-      <c r="B76" s="9" t="n"/>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>10. 단말 화면번호</t>
+        </is>
+      </c>
       <c r="C76" s="16" t="n">
         <v>75</v>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
+          <t>IRP 계좌 해지는 몇 번 화면에서 하지?</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>IRP 계좌 해지 업무는 [02-12-220] 퇴직연금 지급 화면에서 진행해요. 해당 화면은 해지, 계좌이체, 미지급금 출금, 지연보상금 지급을 처리하는 화면이에요. 단일 자료에만 등장하는 내용이라 다른 화면 번호는 안내되지 않으니 참고해 주세요.</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
           <t>ISA 만기자금 입금은 몇 번 화면에서 처리해?</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E77" s="18" t="inlineStr">
         <is>
           <t>● 김서연
 ISA 만기자금 입금은 입금/입금예약·입금명부 등록 화면인 [01-12-213]번 화면에서 처리하면 돼요. 이 화면은 지급, 과세이연, 연금 관련 업무를 처리하는 곳이며 거래구분에서 ISA 만기자금 입금을 선택할 수 있어요. [01-12-213] 관련 내용은 현재 준비된 자료를 바탕으로 안내해 드렸어요.
@@ -3324,57 +3373,24 @@
 ISA 만기자금 입금은 [01-12-213] 입금/입금예약 화면에서 처리하면 돼요. 이 화면은 입금, 입금예약, 그리고 입금명부 등록을 처리하는 화면이에요. 거래구분을 선택할 때 ISA 만기자금 입금을 고르면 입금가능금액을 자동으로 조회할 수 있어요. 그 외에 과세이연이나 계약이전입금 거래구분도 이 화면에서 함께 다루고 있어요.</t>
         </is>
       </c>
-      <c r="F76" s="21" t="inlineStr">
+      <c r="F77" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>ISA 3명 — 김서연 171203-4815062 · 한지우 176903-5528417 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
         </is>
       </c>
-      <c r="I76" s="18" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="9" t="n"/>
-      <c r="C77" s="16" t="n">
-        <v>76</v>
-      </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="inlineStr">
-        <is>
-          <t>포트폴리오 운용현황 조회를 위한 화면번호는 06-12-604이며, 해당 화면은 연금 로보어드바이저 운용현황 조회를 처리하는 화면이에요. AI투자일임 및 케이봇쌤과 관련된 거래를 확인할 때 활용할 수 있어요. [06-12-604]</t>
-        </is>
-      </c>
-      <c r="F77" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
-        </is>
-      </c>
       <c r="I77" s="18" t="inlineStr"/>
     </row>
-    <row r="78" hidden="1">
+    <row r="78">
       <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
       <c r="C78" s="16" t="n">
@@ -3382,19 +3398,17 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
+          <t>포트폴리오 운용현황 조회는 화면번호가 뭐야?</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
-찾아본 곳: 단말 화면번호 「타행 계좌 잔액 조회」 · 업무 처리 절차 「타행 계좌 잔액 조회 업무 처리 순서」 · 단말 화면번호 「타행 계좌 잔액 조회 화면번호」
-다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+          <t>포트폴리오 운용현황 조회를 위한 화면번호는 06-12-604이며, 해당 화면은 연금 로보어드바이저 운용현황 조회를 처리하는 화면이에요. AI투자일임 및 케이봇쌤과 관련된 거래를 확인할 때 활용할 수 있어요. [06-12-604]</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
@@ -3404,12 +3418,12 @@
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
+          <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr"/>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="16" t="n">
@@ -3417,17 +3431,19 @@
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>적립금이랑 수익률 조회는 몇 번 화면이야?</t>
+          <t>타행 계좌 잔액 조회는 몇 번 화면이야?</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>적립금과 수익률을 조회하실 때는 [04-12-642] 화면을 활용하시면 돼요. 해당 화면은 전일자 보유상품, 평가금액, 수익률 조회 및 고유계정대 이자조회를 하실 수 있는 화면이에요.</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 단말 화면번호 「타행 계좌 잔액 조회」 · 업무 처리 절차 「타행 계좌 잔액 조회 업무 처리 순서」 · 단말 화면번호 「타행 계좌 잔액 조회 화면번호」
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
         </is>
       </c>
       <c r="G79" s="18" t="inlineStr">
@@ -3437,7 +3453,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>[04-12-642] + 그 화면이 무엇을 하는 화면인지 ↔ 번호만 던진다</t>
+          <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr"/>
@@ -3450,17 +3466,17 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>수수료 예상조회 화면번호 알려줘</t>
+          <t>적립금이랑 수익률 조회는 몇 번 화면이야?</t>
         </is>
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>문의하신 수수료 예상조회 화면번호는 [04-12-613]이에요. 해당 화면은 수수료 미납이나 납입 내역 및 예상 조회를 할 수 있고 계좌별 수수료 정보를 확인할 수 있는 화면이에요. 업무에 참고해 주세요.</t>
-        </is>
-      </c>
-      <c r="F80" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>적립금과 수익률을 조회하실 때는 [04-12-642] 화면을 활용하시면 돼요. 해당 화면은 전일자 보유상품, 평가금액, 수익률 조회 및 고유계정대 이자조회를 하실 수 있는 화면이에요.</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
@@ -3470,25 +3486,25 @@
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>[04-12-613] ↔ 수수료율표(제도 수치)로 답해 화면번호를 안 준다</t>
+          <t>[04-12-642] + 그 화면이 무엇을 하는 화면인지 ↔ 번호만 던진다</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n"/>
-      <c r="B81" s="10" t="n"/>
+      <c r="B81" s="9" t="n"/>
       <c r="C81" s="16" t="n">
         <v>80</v>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>고객 거래내역은 어느 화면에서 봐?</t>
+          <t>수수료 예상조회 화면번호 알려줘</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>고객 거래내역은 [04-12-644] 화면에서 확인하실 수 있어요. 해당 화면은 현금성자산 유입사유, 부담금입금내역, 입금내역 등을 조회할 수 있는 거래내역 조회 화면이에요.</t>
+          <t>문의하신 수수료 예상조회 화면번호는 [04-12-613]이에요. 해당 화면은 수수료 미납이나 납입 내역 및 예상 조회를 할 수 있고 계좌별 수수료 정보를 확인할 수 있는 화면이에요. 업무에 참고해 주세요.</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -3503,68 +3519,67 @@
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>거래내역 조회 화면번호 ↔ 적립금 조회 화면을 준다</t>
+          <t>[04-12-613] ↔ 수수료율표(제도 수치)로 답해 화면번호를 안 준다</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n"/>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>11. 비대면 채널 경로</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="n">
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="16" t="n">
         <v>81</v>
       </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>고객이 스타뱅킹에서 직접 추가납입할 때는 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로로 안내해 드려요. 인터넷뱅킹을 이용할 때는 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로로 들어가서 진행할 수 있어요. 이용 시간 예외로 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지 가능하니 이 시간대에 처리하도록 미리 짚어드릴게요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>고객 거래내역은 어느 화면에서 봐?</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>고객 거래내역은 [04-12-644] 화면에서 확인하실 수 있어요. 해당 화면은 현금성자산 유입사유, 부담금입금내역, 입금내역 등을 조회할 수 있는 거래내역 조회 화면이에요.</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr"/>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>거래내역 조회 화면번호 ↔ 적립금 조회 화면을 준다</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n"/>
-      <c r="B83" s="9" t="n"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>11. 비대면 채널 경로</t>
+        </is>
+      </c>
       <c r="C83" s="4" t="n">
         <v>82</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
+          <t>고객이 스타뱅킹에서 직접 추가납입 하려면 어느 메뉴로 들어가?</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>개인형IRP 연금수령 신청은 KB스타뱅킹의 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 수령관리 &gt; 연금 수령관리 – 개인형IRP 연금수령 신청 경로와 인터넷뱅킹의 KB퇴직연금 &gt; 개인고객 &gt; 연금수령신청/조회 &gt; 개인형IRP 연금수령 신청 경로를 통해 고객이 직접 진행할 수 있어요. 
-이용 가능한 채널은 개인형IRP에 한하며, ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>고객이 스타뱅킹에서 직접 추가납입할 때는 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로로 안내해 드려요. 인터넷뱅킹을 이용할 때는 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로로 들어가서 진행할 수 있어요. 이용 시간 예외로 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지 가능하니 이 시간대에 처리하도록 미리 짚어드릴게요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -3574,7 +3589,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
+          <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr"/>
@@ -3587,27 +3602,28 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
+          <t>고객이 앱에서 직접 연금 개시 신청할 수 있어?</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>우리 IRP에서도 ETF 매매를 할 수 있으니 고객이 직접 진행할 때 안내할 경로를 짚어드릴게요. KB스타뱅킹을 이용하는 경우 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, ETF 매매하기 순으로 이동하면 되고, 인터넷뱅킹을 이용하는 경우 KB퇴직연금, 개인고객, 퇴직연금 ETF, ETF 매매하기 경로로 접근하면 돼요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
+          <t>개인형IRP 연금수령 신청은 KB스타뱅킹의 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 수령관리 &gt; 연금 수령관리 – 개인형IRP 연금수령 신청 경로와 인터넷뱅킹의 KB퇴직연금 &gt; 개인고객 &gt; 연금수령신청/조회 &gt; 개인형IRP 연금수령 신청 경로를 통해 고객이 직접 진행할 수 있어요. 
+이용 가능한 채널은 개인형IRP에 한하며, ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>윤가영 162754-9483106</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
+          <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr"/>
@@ -3620,27 +3636,27 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>고객이 앱에서 자기 수익률이랑 보유상품 보려면 어느 메뉴야?</t>
+          <t>우리 IRP에서도 ETF 매매 되는지, 고객이 앱에서 직접 하려면 어디로 가야 하는지 알려줘</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>고객이 앱이나 인터넷으로 직접 수익률과 보유상품을 확인하실 수 있도록 안내할 때는 KB스타뱅킹과 인터넷뱅킹 경로를 활용해 주시면 좋아요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 나의 퇴직연금 순으로 이동해 보유상품 수익률을 점검하실 수 있어요. 인터넷뱅킹을 이용하신다면 KB퇴직연금의 개인고객 메뉴에서 My퇴직연금의 수익률과 평가금액조회 항목을 통해 확인하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>우리 IRP에서도 ETF 매매를 할 수 있으니 고객이 직접 진행할 때 안내할 경로를 짚어드릴게요. KB스타뱅킹을 이용하는 경우 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, ETF 매매하기 순으로 이동하면 되고, 인터넷뱅킹을 이용하는 경우 KB퇴직연금, 개인고객, 퇴직연금 ETF, ETF 매매하기 경로로 접근하면 돼요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>윤가영 162754-9483106</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>채널별 메뉴 경로 ↔ 직원 단말 화면번호를 알려준다(셋을 가른 이유 — §3)</t>
+          <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr"/>
@@ -3653,10 +3669,43 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
+          <t>고객이 앱에서 자기 수익률이랑 보유상품 보려면 어느 메뉴야?</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>고객이 앱이나 인터넷으로 직접 수익률과 보유상품을 확인하실 수 있도록 안내할 때는 KB스타뱅킹과 인터넷뱅킹 경로를 활용해 주시면 좋아요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 나의 퇴직연금 순으로 이동해 보유상품 수익률을 점검하실 수 있어요. 인터넷뱅킹을 이용하신다면 KB퇴직연금의 개인고객 메뉴에서 My퇴직연금의 수익률과 평가금액조회 항목을 통해 확인하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>채널별 메뉴 경로 ↔ 직원 단말 화면번호를 알려준다(셋을 가른 이유 — §3)</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
           <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>어떤 운용상품 종류의 조회 방법을 찾으시는가요?
 · 운용상품 전체 (운용상품 찾기)
@@ -3664,122 +3713,89 @@
 · 디폴트옵션 상품</t>
         </is>
       </c>
-      <c r="F86" s="14" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>운용상품 찾기 경로 + 그 채널에서 되는지 ↔ 상품 목록을 늘어놓는다</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>고객이 추가입금 예약을 직접 걸 수 있어?</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>고객이 추가입금 예약을 직접 진행하실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 짚어드릴 수 있어요. KB스타뱅킹을 이용하신다면 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로를 통해 진행하실 수 있고, 인터넷뱅킹을 이용하신다면 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로를 통해 처리하실 수 있어요. 다만 이용 시간의 경우 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지만 가능하니 이 점을 미리 안내해 드리는 것이 좋아요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F87" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>부담금입금/예약 경로 ↔ 직원이 단말에서 하는 절차를 고객에게 시킨다</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n"/>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>12. 고객군·관리 기준</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="n">
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="D88" s="17" t="inlineStr">
-        <is>
-          <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="inlineStr">
-        <is>
-          <t>적립금이 1천만원 미만이더라도 이 고객은 원리금보장·현금성 자산 비중이 90%로 편중되어 있고 디폴트옵션이 미설정되어 있어 관리 대상에 해당해요. 현재 고유계정대와 예금을 포함한 원리금보장·현금성 자산 비중이 높고 키움 더드림 단기채 수익률이 -6.4%를 기록하면서 전체 운용수익률이 -1.8%에 머물러 있는 상태예요. 이는 동연령 평균 수익률 10.2%와 비교해 저조한 수준이며, 위험자산 한도 70% 중 위험자산 비중이 0%로 나타나 포트폴리오 조정이 필요한 상태예요.</t>
-        </is>
-      </c>
-      <c r="F88" s="20" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · QA</t>
-        </is>
-      </c>
-      <c r="G88" s="18" t="inlineStr">
-        <is>
-          <t>김현수 173544-2074623</t>
-        </is>
-      </c>
-      <c r="H88" s="18" t="inlineStr">
-        <is>
-          <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
-        </is>
-      </c>
-      <c r="I88" s="18" t="inlineStr"/>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>고객이 추가입금 예약을 직접 걸 수 있어?</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>고객이 추가입금 예약을 직접 진행하실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 짚어드릴 수 있어요. KB스타뱅킹을 이용하신다면 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로를 통해 진행하실 수 있고, 인터넷뱅킹을 이용하신다면 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로를 통해 처리하실 수 있어요. 다만 이용 시간의 경우 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지만 가능하니 이 점을 미리 안내해 드리는 것이 좋아요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>부담금입금/예약 경로 ↔ 직원이 단말에서 하는 절차를 고객에게 시킨다</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n"/>
-      <c r="B89" s="9" t="n"/>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>12. 고객군·관리 기준</t>
+        </is>
+      </c>
       <c r="C89" s="16" t="n">
         <v>88</v>
       </c>
       <c r="D89" s="17" t="inlineStr">
         <is>
-          <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
+          <t>적립금이 1천만원도 안 되는데 이런 고객도 관리 대상이야?</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>현금성자산이 많다고 해서 무조건 방치 자금으로 볼 수는 없어요. 현금성자산이 일정기간(1개월 이상) 금액변동 없이 유지 중이고 [04-12-644] 퇴직연금 거래내역조회 시 입금 사유가 '교체매매'나 '연금지급' 사유가 아닌 경우 미운용중인 자산이 있다고 안내해 보세요. 연금지급이나 교체매매 대기 중인 정상 자금일 수도 있으므로, 고객에게 접촉하기 전에 사용계획 자금인지 방치 자금인지 먼저 가르는 것이 판단 기준이에요. 상담 용어: "고유계정대" 대신 "현금성자산", "운용지시가 되지 않는 자산" 사용 (고객에게 생소한 용어 금지).</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>적립금이 1천만원 미만이더라도 이 고객은 원리금보장·현금성 자산 비중이 90%로 편중되어 있고 디폴트옵션이 미설정되어 있어 관리 대상에 해당해요. 현재 고유계정대와 예금을 포함한 원리금보장·현금성 자산 비중이 높고 키움 더드림 단기채 수익률이 -6.4%를 기록하면서 전체 운용수익률이 -1.8%에 머물러 있는 상태예요. 이는 동연령 평균 수익률 10.2%와 비교해 저조한 수준이며, 위험자산 한도 70% 중 위험자산 비중이 0%로 나타나 포트폴리오 조정이 필요한 상태예요.</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · QA</t>
         </is>
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>김현수 173544-2074623</t>
         </is>
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
+          <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
         </is>
       </c>
       <c r="I89" s="18" t="inlineStr"/>
@@ -3792,19 +3808,17 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
+          <t>현금성자산이 많으면 다 방치로 봐도 되는 거야?</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr">
         <is>
-          <t>어떤 이탈 위험 유형을 기준으로 보시겠습니까?
-· 자산 편중형
-· 투자 목적형</t>
-        </is>
-      </c>
-      <c r="F90" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
+          <t>현금성자산이 많다고 해서 무조건 방치 자금으로 볼 수는 없어요. 현금성자산이 일정기간(1개월 이상) 금액변동 없이 유지 중이고 [04-12-644] 퇴직연금 거래내역조회 시 입금 사유가 '교체매매'나 '연금지급' 사유가 아닌 경우 미운용중인 자산이 있다고 안내해 보세요. 연금지급이나 교체매매 대기 중인 정상 자금일 수도 있으므로, 고객에게 접촉하기 전에 사용계획 자금인지 방치 자금인지 먼저 가르는 것이 판단 기준이에요. 상담 용어: "고유계정대" 대신 "현금성자산", "운용지시가 되지 않는 자산" 사용 (고객에게 생소한 용어 금지).</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
@@ -3814,7 +3828,7 @@
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
+          <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
         </is>
       </c>
       <c r="I90" s="18" t="inlineStr"/>
@@ -3827,20 +3841,19 @@
       </c>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
+          <t>이탈 위험 고객은 어떤 기준으로 뽑는 거야?</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>어떤 목적의 대상 선정 기준인가요?
-· TM 콜 대상
-· 매월 안내 LMS 자동발송
-· 이탈위험 선별</t>
-        </is>
-      </c>
-      <c r="F91" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>어떤 이탈 위험 유형을 기준으로 보시겠습니까?
+· 자산 편중형
+· 투자 목적형</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
@@ -3850,7 +3863,7 @@
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
+          <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
         </is>
       </c>
       <c r="I91" s="18" t="inlineStr"/>
@@ -3863,12 +3876,15 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
+          <t>미운용 현금성자산 고객은 몇 퍼센트부터 대상이야?</t>
         </is>
       </c>
       <c r="E92" s="18" t="inlineStr">
         <is>
-          <t>오늘 우선 관리해야 할 대상은 총 11명이며, 각 고객의 현황에 따른 선정 요건 순서대로 확인해야 해요. 윤가영 고객은 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월에 해당해요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월이며, 최서윤 고객은 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원이 확인되며, 이수민 고객은 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원이 선정 요 이에요. 박정호 고객은 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원이며, 김현수는 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시이며, 김서연 고객은 ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원이에요. 한지우 고객은 ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
+          <t>어떤 목적의 대상 선정 기준인가요?
+· TM 콜 대상
+· 매월 안내 LMS 자동발송
+· 이탈위험 선별</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -3883,97 +3899,130 @@
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
+          <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="n"/>
-      <c r="B93" s="10" t="n"/>
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n"/>
       <c r="C93" s="16" t="n">
         <v>92</v>
       </c>
       <c r="D93" s="17" t="inlineStr">
         <is>
+          <t>오늘 여러 명 봐야 하는데 어떤 고객부터 관리하는 게 맞아?</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>오늘 우선 관리해야 할 대상은 총 11명이며, 각 고객의 현황에 따른 선정 요건 순서대로 확인해야 해요. 윤가영 고객은 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월에 해당해요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월이며, 최서윤 고객은 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원이 확인되며, 이수민 고객은 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원이 선정 요 이에요. 박정호 고객은 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원이며, 김현수는 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시이며, 김서연 고객은 ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원이에요. 한지우 고객은 ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
+        </is>
+      </c>
+      <c r="F93" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
           <t>만기 안내 전화할 때 현장에서 잘 먹히는 방법 있어?</t>
         </is>
       </c>
-      <c r="E93" s="18" t="inlineStr">
+      <c r="E94" s="18" t="inlineStr">
         <is>
           <t>만기 안내 전화할 때는 본부 공식 지침은 아니지만 영업점 현장에서 관찰된 방식을 활용할 수 있어요. 비율 대신 원 단위 금액으로 제시하는 것이 반복되는 성공 패턴이며, 계산이 상담의 성패를 가른다는 점을 참고해 보세요. 중도해지이율이 수수료율 합계보다 낮으면 원금에서 차감 지급된다는 점이나 지급까지 3영업일이 소요된다는 사실, 그리고 중도인출 신청액이 세전이라는 점을 미리 안내하지 않으면 민원으로 돌아올 수 있으니 사전에 고지하는 것이 중요해요. 만기 안내 전화 과정에서 수수료로 원금이 깨질 수 있는 부분이나 현금화 지연 가능성 같은 필수 고지 사항을 빠뜨리지 않도록 유의하세요.</t>
         </is>
       </c>
-      <c r="F93" s="19" t="inlineStr">
+      <c r="F94" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G93" s="18" t="inlineStr">
+      <c r="G94" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H93" s="18" t="inlineStr">
+      <c r="H94" s="18" t="inlineStr">
         <is>
           <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
-      <c r="I93" s="18" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="18" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Ⅲ. 상담 중 — 말하기와 이어지는 대화</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>13. 상담 화법·반론 대응</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>손실만 나고 해지하겠다는 고객에게는 보유 포트폴리오 유형으로 화법을 분기하여, 저희가 세심하게 관리를 해드렸어야 했는데 죄송합니다라고 먼저 관리 미흡을 사과하고 그 자리에서 매도와 재추천이라는 액션을 약속하는 방식으로 접근해야 해요. 본부 교육 영상에서는 공시 순위를 앞세우지 않고 이처럼 사과와 원인 규명에 이어 즉시 리밸런싱을 3단으로 밟아나가는 방식을 권하고 있어요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속해서는 안 되며, 근거는 수익률 예측이 아니라 운용 여건의 차이에 두어야 해요. 또한 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 미리 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 상담 용어를 사용해 주세요.</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>해지 만류 화법 — 사과 → 원인 규명 → 리밸런싱 3단 + 고객에게 할 대사 ↔ 절차 카드 한 장으로 「준비된 자료에 없어요」(gap 35 재현)</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="n"/>
-      <c r="B95" s="9" t="n"/>
       <c r="C95" s="4" t="n">
         <v>94</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
+          <t>고객이 '손실만 나는데 그냥 해지하겠다'는데 어떻게 대응하지?</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>손실만 나고 해지하겠다는 고객에게는 보유 포트폴리오 유형으로 화법을 분기하여, 저희가 세심하게 관리를 해드렸어야 했는데 죄송합니다라고 먼저 관리 미흡을 사과하고 그 자리에서 매도와 재추천이라는 액션을 약속하는 방식으로 접근해야 해요. 본부 교육 영상에서는 공시 순위를 앞세우지 않고 이처럼 사과와 원인 규명에 이어 즉시 리밸런싱을 3단으로 밟아나가는 방식을 권하고 있어요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속해서는 안 되며, 근거는 수익률 예측이 아니라 운용 여건의 차이에 두어야 해요. 또한 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 미리 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 상담 용어를 사용해 주세요.</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>해지 만류 화법 — 사과 → 원인 규명 → 리밸런싱 3단 + 고객에게 할 대사 ↔ 절차 카드 한 장으로 「준비된 자료에 없어요」(gap 35 재현)</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>● 이수민
 "예금만 해서 관리 필요 없어요"라는 고객에게는 금리 갈아타기가 곧 관리라는 논리로 접근하는 게 핵심이에요. 예금과 같은 원리금보장상품도 꾸준한 관리가 필요한 대상이라는 점을 짚어주고, 매월 금리가 가장 좋은 상품을 제공하고 있다는 점을 설명해 주세요. 고객에게는 이렇게 안내해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다." 이미 안정적으로 잘 운용하고 있다는 점을 먼저 인정한 뒤, 같은 안전성인 예금자보호 테두리 안에서 금리를 올려주는 제안으로 자연스럽게 대화를 이어가면 됩니다.
@@ -3981,35 +4030,35 @@
 예금만으로도 충분하지 않냐고 묻는 고객에게는 예금 같은 원리금보장상품도 매월 금리가 유리한 상품으로 갈아타는 과정이 곧 관리라는 점을 짚어주는 것이 핵심이에요. 당행은 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있다는 점을 설명해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내하시면 돼요. 이 과정에서 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 '고유계정대' 같은 용어 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 표현을 사용해 주세요. 아울러 연금지급 대기나 교체매매 등으로 사용 계획이 있는 자금인지 먼저 확인하고 접근하시는 것이 안전해요.</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>이수민 175926-3048171·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr"/>
-    </row>
-    <row r="96" hidden="1">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="9" t="n"/>
-      <c r="C96" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97" hidden="1">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>고객이 IRP에 넣으면 55세까지 못 빼는 거 아니냐고 걱정하는데, 중간에 뺄 수 있어?</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>IRP 중도인출 가능 여부를 묻는 고객에게는 무주택자의 주택 구입이나 전세금 및 임차보증금이 필요한 경우 등 법적 요건을 충족하면 언제든 중도인출이 가능하다고 안내하는 것이 핵심이에요. 55세까지 아예 못 뺀다는 고객의 우려를 법정 사유로 먼저 해소해야 해요. 
 그후 고객이 자유로운 입출금을 원하며 가입을 망설일 때는 무조건 돈 전부를 넣으라는 것이 아니라고 요구 수준을 낮추어 짚어 주세요. 한 가지 음식만 먹으면 영양이 부족하듯 자산을 골고루 나누어 안정성과 수익성, 절세 효과를 균형 있게 챙겨야 한다는 점을 설명하는 것이 효과적이에요. 해지에 대한 우려로 큰 혜택을 놓치는 것은 아쉽다는 점을 강조하면서 다음 대사를 활용해 보세요. 
@@ -4017,35 +4066,35 @@
 "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="n"/>
-      <c r="B97" s="9" t="n"/>
-      <c r="C97" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>고객이 '증권사는 수수료 무료라던데요' 하는데 뭐라고 답하지?</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>증권사 수수료 무료 발언으로 이탈을 우려하는 고객에게는 면제 조건을 먼저 제시한 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 
 만 55세 이후 연금개시를 하시면 수수료가 0원이 되며, 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되므로 이 조건을 먼저 짚어주세요. 
@@ -4056,59 +4105,24 @@
 대화 중 "IRP 수수료는 적립금 규모와 가입 방식에 따라 다릅니다. 우리 고객님 조건에서는 오히려 국민은행이 더 저렴한 경우가 많습니다. 실제로 고객님 상황과 적립금 기준으로 한번 같이 비교해드릴게요."라는 멘트를 활용해 고객의 상황을 구체적으로 비교해 보면서 대응을 이어가세요.</t>
         </is>
       </c>
-      <c r="F97" s="14" t="inlineStr">
+      <c r="F98" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="n"/>
-      <c r="B98" s="9" t="n"/>
-      <c r="C98" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>디폴트옵션에 거부반응을 보이는 고객에게는 전량 전환을 밀지 않고 일부만 먼저 전환하고 되돌릴 수 있다는 가역성을 제시하는 게 핵심이에요. 
-전부 바꾸지 않고 일부만 먼저 운용해 보고 원할 때 되돌릴 수 있다는 점을 안내해 심리적 부담을 낮추는 방식으로 접근해야 해요. 
-이용하려는 자금이 연금지급 대기나 교체매매 중에 있는 등 사용계획이 있는 자금이라면 먼저 걸러내야 하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 시연본</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
-        </is>
-      </c>
       <c r="I98" s="6" t="inlineStr"/>
     </row>
-    <row r="99" hidden="1">
+    <row r="99">
       <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="4" t="n">
@@ -4116,29 +4130,29 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
+          <t>고객이 원치 않는 상품에 강제 가입되는 거 아니냐고 하면 뭐라고 설명해?</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>현금성자산 방치 고객이 금액이 적다는 이유로 운용을 미루려 할 때는, 사용계획이 있는 자금인지 먼저 확인하고 수익률 관점에서의 기회비용을 짚어주는 게 핵심이에요. 
-고유계정대 같은 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰고, 연금지급 대기나 교체매매 등 사용계획이 있는 자금인지 먼저 걸러내야 해요. 그런 자금이 아니라면 현재 미운용 중인 자산은 금리가 낮아 방치할수록 손해라는 점을 자연스럽게 설명해 보세요. 
-고객에게는 "고객님, 금액이 작아 보이셔도 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준이라서요. 금리가 높은 저축은행 정기예금이나 펀드 같은 상품으로 운용하시면 향후에 수령하시는 퇴직연금 금액이 달라지니 지금 재정비하시는 게 좋아요"라고 안내해 드릴 수 있어요.</t>
+          <t>디폴트옵션에 거부반응을 보이는 고객에게는 전량 전환을 밀지 않고 일부만 먼저 전환하고 되돌릴 수 있다는 가역성을 제시하는 게 핵심이에요. 
+전부 바꾸지 않고 일부만 먼저 운용해 보고 원할 때 되돌릴 수 있다는 점을 안내해 심리적 부담을 낮추는 방식으로 접근해야 해요. 
+이용하려는 자금이 연금지급 대기나 교체매매 중에 있는 등 사용계획이 있는 자금이라면 먼저 걸러내야 하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>○ 예비 · QA</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>김현수 173544-2074623</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
+          <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr"/>
@@ -4151,10 +4165,45 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
+          <t>고객이 '금액도 얼마 안 되는데 그냥 두면 안 되나요' 하면 뭐라고 하지?</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>현금성자산 방치 고객이 금액이 적다는 이유로 운용을 미루려 할 때는, 사용계획이 있는 자금인지 먼저 확인하고 수익률 관점에서의 기회비용을 짚어주는 게 핵심이에요. 
+고유계정대 같은 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰고, 연금지급 대기나 교체매매 등 사용계획이 있는 자금인지 먼저 걸러내야 해요. 그런 자금이 아니라면 현재 미운용 중인 자산은 금리가 낮아 방치할수록 손해라는 점을 자연스럽게 설명해 보세요. 
+고객에게는 "고객님, 금액이 작아 보이셔도 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준이라서요. 금리가 높은 저축은행 정기예금이나 펀드 같은 상품으로 운용하시면 향후에 수령하시는 퇴직연금 금액이 달라지니 지금 재정비하시는 게 좋아요"라고 안내해 드릴 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>김현수 173544-2074623</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101" hidden="1">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
           <t>고객이 '손실 난 걸 지금 팔라는 거냐'고 하면 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>● 최서윤
 성과저조나 판매중단 펀드를 보유한 고객이 손실 중인 상태에서 교체를 망설일 때는 고객의 속상한 심정을 먼저 인정하는 공감의 자세로 접근해야 해요. 
@@ -4164,52 +4213,19 @@
 성과저조·판매중단 펀드 보유 고객이 손실 상황에서 불만을 제기할 때는 감정 공감을 먼저 건네며 접근하는 것이 핵심이에요. "속상하시겠지만"이라는 감정 인정을 반드시 앞세우고, 판매중단 사유와 그 결과로 운용사 관심도가 하락해 향후 수익률 개선이 어려울 수 있다는 점을 설명한 뒤 교체를 권해야 해요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되고, 수익률 예측이 아니라 운용 여건의 차이를 근거로 다가가야 해요. 고객에게는 "많이 속상하시겠지만, 고객님 안정적인 퇴직연금 자산관리를 위해 최근 수익률 등을 비교해 보시고 상대적으로 성과가 우수한 상품으로 변경해 보시는 건 어떠신가요?"라고 안내해 보세요. 상담 과정에서 사용계획이 있는 자금이라면 먼저 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 해요.</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr"/>
-    </row>
-    <row r="101" hidden="1">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="9" t="n"/>
-      <c r="C101" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>증권사가 ETF 종류가 훨씬 많다는 고객에게는 고객의 반론을 먼저 인정하면서 10~20년 장기 운용을 해야 하는 연금자산에서는 상품의 개수보다 어떤 상품을 선택해서 운용하느냐가 더 중요하다는 점으로 설명을 이끌어가는 게 핵심이에요. 증권사는 8~900개의 다양한 테마형, 섹터형 ETF를 제공하고 있지만, 선택의 폭이 넓어지면 트렌드에 맞춰 관리해야 하고 그에 따른 피로도와 결정장애가 생기기 마련이라는 점을 짚어주세요. 퇴직연금은 중장기 안정적인 성과를 추구해야 하는 장기자산이므로, 국민은행은 이런 자산의 특성과 시장상황 등을 고려해 엄선한 ETF만을 선별 제공하고 있다는 점을 안내할 수 있어요. 현재 당행에서 판매 중인 ETF는 총 193종(국내 90종, 해외 103종)으로 계속 늘려가고 있으며, 고객님의 선택 폭을 넓히기 위해 중복테마 및 거래가 활발하지 않은 ETF를 제외하고 상품 라인업을 최대 400개까지 확대할 예정이라는 사실을 함께 활용해 보세요.</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>윤가영 162754-9483106</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr"/>
@@ -4222,10 +4238,43 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
+          <t>고객이 ETF는 증권사가 편하다고 옮기겠다는데 뭐라고 붙잡지?</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>증권사가 ETF 종류가 훨씬 많다는 고객에게는 고객의 반론을 먼저 인정하면서 10~20년 장기 운용을 해야 하는 연금자산에서는 상품의 개수보다 어떤 상품을 선택해서 운용하느냐가 더 중요하다는 점으로 설명을 이끌어가는 게 핵심이에요. 증권사는 8~900개의 다양한 테마형, 섹터형 ETF를 제공하고 있지만, 선택의 폭이 넓어지면 트렌드에 맞춰 관리해야 하고 그에 따른 피로도와 결정장애가 생기기 마련이라는 점을 짚어주세요. 퇴직연금은 중장기 안정적인 성과를 추구해야 하는 장기자산이므로, 국민은행은 이런 자산의 특성과 시장상황 등을 고려해 엄선한 ETF만을 선별 제공하고 있다는 점을 안내할 수 있어요. 현재 당행에서 판매 중인 ETF는 총 193종(국내 90종, 해외 103종)으로 계속 늘려가고 있으며, 고객님의 선택 폭을 넓히기 위해 중복테마 및 거래가 활발하지 않은 ETF를 제외하고 상품 라인업을 최대 400개까지 확대할 예정이라는 사실을 함께 활용해 보세요.</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>윤가영 162754-9483106</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103" hidden="1">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
           <t>예금만 하겠다는 고객, 뭐라고 설득하지?</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>● 정민석
 예금만 하겠다는 고객에게는 원리금보장상품도 관리가 필요하다는 점을 짚어주고 같은 안전성 안에서 금리를 올려주는 제안으로 접근하는 게 핵심이에요. 
@@ -4238,52 +4287,19 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="F102" s="13" t="inlineStr">
+      <c r="F103" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="inlineStr"/>
-    </row>
-    <row r="103" hidden="1">
-      <c r="A103" s="9" t="n"/>
-      <c r="B103" s="9" t="n"/>
-      <c r="C103" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>원금 손실을 우려하는 고객에게는 연금 자산의 투자 성격과 기간을 들어 위험의 의미를 다시 정의하며 접근하는 것이 핵심이에요. 먼저 주식이 위험하다는 고객의 의견을 수용하면서, 여기서 말하는 위험이 손실이 아니라 기간이 길어질수록 줄어드는 변동성임을 짚어주세요. 당장 1~2년 뒤에 쓸 돈이 아니라 은퇴 후 30년을 운용해야 할 자산이라는 점을 설명하고, 연금이야말로 기간이 길어 30년이면 손실 확률이 0%에 수렴하는 특성을 지닌다는 점을 안내할 수 있어요. 또한 '위험'이라는 단어가 주는 부담감을 줄이기 위해 30년이라는 장기 투자 기간과 소규모 납입금의 특성을 들어 오히려 연금투자가 변동성을 감당할 수 있는 자금 성격임을 설명하는 방식을 활용해 보세요. 다만 사용 계획이 있는 자금이나 연금지급 대기 및 교체매매 중인 자금은 먼저 걸러내야 하며, 고객에게 생소할 수 있는 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>정민석 181245-3097614</t>
-        </is>
-      </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr"/>
@@ -4296,27 +4312,27 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>고객이 '생각 좀 해볼게요' 하고 미루는데 뭐라고 하지?</t>
+          <t>고객이 원금 잃는 건 싫다는데, 그래도 권해야 해?</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>고객이 망설일 때는 즉답을 압박하지 않고 생각할 시간의 정당성을 먼저 인정해 주는 방식으로 접근해야 해요. 당장 결정을 재촉하기보다 고객이 스스로 상품 정보를 찾아볼 수 있도록 안내하는 것이 좋아요. "아무래도 많이 운용해보신 상품이 아니라 생각하실 시간이 필요하실 거에요. 궁금한 점 있으시면 언제든지 연락 주시고, 인터넷뱅킹 또는 스타뱅킹을 통해서도 관련상품에 대한 정보를 찾아보실 수 있으니 참고해주세요"라고 안내해 드려 보세요.</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>원금 손실을 우려하는 고객에게는 연금 자산의 투자 성격과 기간을 들어 위험의 의미를 다시 정의하며 접근하는 것이 핵심이에요. 먼저 주식이 위험하다는 고객의 의견을 수용하면서, 여기서 말하는 위험이 손실이 아니라 기간이 길어질수록 줄어드는 변동성임을 짚어주세요. 당장 1~2년 뒤에 쓸 돈이 아니라 은퇴 후 30년을 운용해야 할 자산이라는 점을 설명하고, 연금이야말로 기간이 길어 30년이면 손실 확률이 0%에 수렴하는 특성을 지닌다는 점을 안내할 수 있어요. 또한 '위험'이라는 단어가 주는 부담감을 줄이기 위해 30년이라는 장기 투자 기간과 소규모 납입금의 특성을 들어 오히려 연금투자가 변동성을 감당할 수 있는 자금 성격임을 설명하는 방식을 활용해 보세요. 다만 사용 계획이 있는 자금이나 연금지급 대기 및 교체매매 중인 자금은 먼저 걸러내야 하며, 고객에게 생소할 수 있는 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>정민석 181245-3097614</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>시간의 정당성 인정 + 자가확인 경로 ↔ 재촉하거나 그냥 끝낸다</t>
+          <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr"/>
@@ -4329,13 +4345,12 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>고객이 '지금 쓸 돈도 없어요' 하는데 뭐라고 해?</t>
+          <t>고객이 '생각 좀 해볼게요' 하고 미루는데 뭐라고 하지?</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>지금 쓸 돈이 없다고 말씀하시는 고객에게는 IRP가 매달 의무적으로 일정 금액을 납입해야 하는 상품이 아니라는 점을 안내하여 부담을 덜어드리는 것이 핵심이에요. 여유가 있는 달에만 넣고 부담되는 달에는 쉬어가면서 원할 때만 입금하면 된다는 점을 설명하면서 큰 금액보다는 '시작하는 습관'을 강조하는 방식으로 접근할 수 있어요. 
-상담 과정에서 고객이 적금을 따로 가입하겠다고 말씀하신다면 "IRP는 매달 무조건 일정 금액을 입금해야하는 상품이 아닙니다. 여유가 있는 달에 넣고, 부담되는 달에는 쉬어가면서 원할때만 입금하시면 됩니다."라고 안내해 보세요. 이어지는 대응으로는 "적금은 만기이자에 이자소득세가 차감되는 반면, IRP는 예금, 펀드 등 운용수익에 대해 세금을 하나도 차감하지 않아요. 또 연말정산, 종합소득세 신고때 세액공제까지 된답니다."라는 내용을 활용하실 수 있어요.</t>
+          <t>고객이 망설일 때는 즉답을 압박하지 않고 생각할 시간의 정당성을 먼저 인정해 주는 방식으로 접근해야 해요. 당장 결정을 재촉하기보다 고객이 스스로 상품 정보를 찾아볼 수 있도록 안내하는 것이 좋아요. "아무래도 많이 운용해보신 상품이 아니라 생각하실 시간이 필요하실 거에요. 궁금한 점 있으시면 언제든지 연락 주시고, 인터넷뱅킹 또는 스타뱅킹을 통해서도 관련상품에 대한 정보를 찾아보실 수 있으니 참고해주세요"라고 안내해 드려 보세요.</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -4350,7 +4365,7 @@
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>자유납입으로 부담 제거 ↔ 한도를 채우라고 밀어붙인다</t>
+          <t>시간의 정당성 인정 + 자가확인 경로 ↔ 재촉하거나 그냥 끝낸다</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr"/>
@@ -4363,17 +4378,18 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>고객이 '나중에 돈 못 빼는 거 아니에요?' 하는데 뭐라고 설명하지?</t>
+          <t>고객이 '지금 쓸 돈도 없어요' 하는데 뭐라고 해?</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>IRP 가입 시 중도인출에 대한 우려를 표하는 고객에게는 법적 요건을 충족하면 언제든 인출이 가능하다는 점을 설명하고, 자산을 균형 있게 나누어 운용하는 방식을 안내하는 것이 좋아요. IRP는 노후 대비를 위한 계좌이지만 무주택자의 주택 구입이나 전세금 및 임차보증금 마련 등 법정 사유가 있을 때 중도인출이 가능하므로, 고객이 가진 자금 유동성에 대한 불안을 먼저 덜어줄 수 있어요. 또한 고객의 전체 자산을 전부 IRP에 넣으라는 것이 아니라는 점을 짚어 주면서, "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."라고 말씀해 보세요. IRP의 절세 혜택과 안정성을 함께 챙길 수 있도록 유도하는 화법이에요.</t>
-        </is>
-      </c>
-      <c r="F106" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>지금 쓸 돈이 없다고 말씀하시는 고객에게는 IRP가 매달 의무적으로 일정 금액을 납입해야 하는 상품이 아니라는 점을 안내하여 부담을 덜어드리는 것이 핵심이에요. 여유가 있는 달에만 넣고 부담되는 달에는 쉬어가면서 원할 때만 입금하면 된다는 점을 설명하면서 큰 금액보다는 '시작하는 습관'을 강조하는 방식으로 접근할 수 있어요. 
+상담 과정에서 고객이 적금을 따로 가입하겠다고 말씀하신다면 "IRP는 매달 무조건 일정 금액을 입금해야하는 상품이 아닙니다. 여유가 있는 달에 넣고, 부담되는 달에는 쉬어가면서 원할때만 입금하시면 됩니다."라고 안내해 보세요. 이어지는 대응으로는 "적금은 만기이자에 이자소득세가 차감되는 반면, IRP는 예금, 펀드 등 운용수익에 대해 세금을 하나도 차감하지 않아요. 또 연말정산, 종합소득세 신고때 세액공제까지 된답니다."라는 내용을 활용하실 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -4383,7 +4399,7 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>법정 사유 + 균형 비유 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
+          <t>자유납입으로 부담 제거 ↔ 한도를 채우라고 밀어붙인다</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr"/>
@@ -4396,14 +4412,12 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>고객이 '회사에서 알아서 해주는 거 아니냐'고 하는데?</t>
+          <t>고객이 '나중에 돈 못 빼는 거 아니에요?' 하는데 뭐라고 설명하지?</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>그 부분은 제가 가진 자료로는 확인이 어려워요. 다만 바쁜 일상 속에서 직접 관리해야 하는 번거로움을 느끼는 고객에게는 자동화 기능을 통해 부담을 덜어드리는 방식을 활용할 수 있어요. 
-「충분히 그렇게 느끼실 수 있습니다. 바쁜 일상에서 운용 중인 상품을 관리해야 하는 일은 보통 일이 아니죠. 정기적으로 보험료 납입하시는 것처럼 IRP로 자동이체와 자동매수 설정을 해놓으시면 편하게 관리 가능합니다.」
-「그 부분은 전혀 걱정하지 않으셔도 됩니다. 기존 상품이 만기가 도래해도 알아서 상품이 매수되는 디폴트옵션 설정도 도와드릴게요. 한번 설정해놓으시면 기존 연금보험처럼 신경 쓰실 필요 없이 알아서 운용될 거에요.」</t>
+          <t>IRP 가입 시 중도인출에 대한 우려를 표하는 고객에게는 법적 요건을 충족하면 언제든 인출이 가능하다는 점을 설명하고, 자산을 균형 있게 나누어 운용하는 방식을 안내하는 것이 좋아요. IRP는 노후 대비를 위한 계좌이지만 무주택자의 주택 구입이나 전세금 및 임차보증금 마련 등 법정 사유가 있을 때 중도인출이 가능하므로, 고객이 가진 자금 유동성에 대한 불안을 먼저 덜어줄 수 있어요. 또한 고객의 전체 자산을 전부 IRP에 넣으라는 것이 아니라는 점을 짚어 주면서, "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."라고 말씀해 보세요. IRP의 절세 혜택과 안정성을 함께 챙길 수 있도록 유도하는 화법이에요.</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
@@ -4418,7 +4432,7 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>「가입보다 관리」로 논점 이동 ↔ 제도 설명만 하고 할 말이 없다</t>
+          <t>법정 사유 + 균형 비유 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr"/>
@@ -4431,10 +4445,45 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
+          <t>고객이 '회사에서 알아서 해주는 거 아니냐'고 하는데?</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>그 부분은 제가 가진 자료로는 확인이 어려워요. 다만 바쁜 일상 속에서 직접 관리해야 하는 번거로움을 느끼는 고객에게는 자동화 기능을 통해 부담을 덜어드리는 방식을 활용할 수 있어요. 
+「충분히 그렇게 느끼실 수 있습니다. 바쁜 일상에서 운용 중인 상품을 관리해야 하는 일은 보통 일이 아니죠. 정기적으로 보험료 납입하시는 것처럼 IRP로 자동이체와 자동매수 설정을 해놓으시면 편하게 관리 가능합니다.」
+「그 부분은 전혀 걱정하지 않으셔도 됩니다. 기존 상품이 만기가 도래해도 알아서 상품이 매수되는 디폴트옵션 설정도 도와드릴게요. 한번 설정해놓으시면 기존 연금보험처럼 신경 쓰실 필요 없이 알아서 운용될 거에요.」</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>「가입보다 관리」로 논점 이동 ↔ 제도 설명만 하고 할 말이 없다</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109" hidden="1">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
           <t>고객이 '직접 관리하기 귀찮다'고 하는데 뭐라고 하지?</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>직접 관리하기 귀찮다는 고객에게는 전문가의 추천이나 자동화된 운용 방식을 제안하여 선택의 부담을 덜어주는 방향으로 접근하는 것이 핵심이에요.
 펀드 선택에 어려움을 겪는 고객에게는 전문가들로 구성된 상품선정 및 자산배분 회의를 거쳐 매월 추천 펀드와 포트폴리오를 제공하고 있다는 점을 안내할 수 있어요. 
@@ -4443,35 +4492,35 @@
 직접 운용이 어려운 고객에게는 디폴트옵션이나 TDF 외의 제3 선택지로 AI투자일임 서비스를 안내해 드릴 수 있어요. KB국민은행 개인형IRP 보유 고객은 제휴 투자일임사 3곳인 디셈버앤컴퍼니, 미래에셋자산운용, 한국투자신탁운용의 로보어드바이저에 운용을 맡길 수 있어요. 다만 이 서비스를 안내하실 때는 1인 1계좌 제한, 연금 수령을 시작한 고객·미성년자·외국인 제외, 전 운용사 합산 연 900만원의 투자 한도, 퇴직연금 수수료 외 별도 일임 보수 발생, 원금 비보장 등의 제약 사항을 함께 확인해 주셔야 해요. 아울러 운용 중에는 타기관 이전, 연금 지급, 중도인출, 해지가 제한되며 일임계약 해지 후에만 가능하다는 점과 투자성향이 안정형이면 진행이 어려울 수 있다는 점도 미리 짚어드릴 필요가 있어요.</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>자동화 3종(자동이체·자동매수·디폴트옵션) ↔ 디폴트옵션 하나만 말한다</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr"/>
-    </row>
-    <row r="109" hidden="1">
-      <c r="A109" s="9" t="n"/>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110" hidden="1">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>고객이 '수익률은 다른 은행이 더 좋던데요' 하면 뭐라고 답해?</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>고객이 수익률 불만을 제기할 때는 2026년 1분기 금융감독원 발표 공시 자료를 근거로 내세워 단기 성과 중심의 비교에서 장기 관리의 중요성으로 설명을 유도하는 게 핵심이에요. 
 수익률 반론에는 금융감독원 공시를 바탕으로 당행의 성과를 객관적으로 짚어드려야 하니, "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀해 보세요. 
@@ -4479,74 +4528,74 @@
 다만 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하거나 예측하는 표현은 쓰지 않도록 주의가 필요해요. 사용 계획이 있는 자금인 경우 사전에 걸러내야 한다는 점도 함께 염두에 두고 상담을 진행해 보세요. 그 외에 추가로 확인이 필요한 사항은 제가 가진 자료로는 확인이 어려워요.</t>
         </is>
       </c>
-      <c r="F109" s="14" t="inlineStr">
+      <c r="F110" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="H110" s="6" t="inlineStr">
         <is>
           <t>공시 근거 + 장기 관리 약속 ↔ 근거 없이 우리가 낫다고 말한다</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="n"/>
-      <c r="B110" s="10" t="n"/>
-      <c r="C110" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="I110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>상담 목적과 오프너 유형 중 어떤 방식을 원하시나요?
 · 중립적 용건으로 열기 (수익률 관리 해피콜)
 · 침묵을 유도하는 질문으로 열기 (IRP 수익률)</t>
         </is>
       </c>
-      <c r="F110" s="14" t="inlineStr">
+      <c r="F111" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>중립적 용건 오프너 ↔ 바로 상품 권유로 들어간다</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="n"/>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="I111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="15" t="inlineStr">
         <is>
           <t>14. 적합성 범위 안내</t>
         </is>
       </c>
-      <c r="C111" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="D111" s="17" t="inlineStr">
+      <c r="C112" s="16" t="n">
+        <v>111</v>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr">
         <is>
           <t>이 고객에게는 적합성 확인 결과 허용된 상품 범위 안에서만 상품을 안내해야 해요. 현재 고객의 투자성향은 안정추구형이며, 적합성 허용 상한은 낮은위험으로 이 등급까지의 상품만 안내할 수 있어요. 
 안내할 수 있는 상품은 다음과 같아요.
@@ -4559,35 +4608,35 @@
 반면 KB 글로벌채권인덱스 C-P, KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 중립형 MP, KB 성장형 MP, KB 글로벌리츠 ETF는 상품 위험등급이 허용 상한인 낮은위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F111" s="20" t="inlineStr">
+      <c r="F112" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G111" s="18" t="inlineStr">
+      <c r="G112" s="18" t="inlineStr">
         <is>
           <t>보수 성향 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H111" s="18" t="inlineStr">
+      <c r="H112" s="18" t="inlineStr">
         <is>
           <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
         </is>
       </c>
-      <c r="I111" s="18" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="n"/>
-      <c r="B112" s="9" t="n"/>
-      <c r="C112" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="D112" s="17" t="inlineStr">
+      <c r="I112" s="18" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="16" t="n">
+        <v>112</v>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
         <is>
           <t>왜 이 상품은 목록에서 빠진 거야?</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr">
+      <c r="E113" s="18" t="inlineStr">
         <is>
           <t>이 고객에게 안내할 수 없는 상품이 목록에서 빠진 이유는 고객의 투자성향이 안정추구형이라 위험등급 허용 상한이 낮은위험으로 정해져 있기 때문이에요. 앞서 말씀드린 안내할 수 없는 상품들은 상품 자체의 위험등급이 고객의 허용 상한보다 높아 제외되었으며, 구체적인 내용은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
@@ -4599,39 +4648,39 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F112" s="23" t="inlineStr">
+      <c r="F113" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G112" s="18" t="inlineStr">
+      <c r="G113" s="18" t="inlineStr">
         <is>
           <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="H112" s="18" t="inlineStr">
+      <c r="H113" s="18" t="inlineStr">
         <is>
           <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
         </is>
       </c>
-      <c r="I112" s="18" t="inlineStr">
+      <c r="I113" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="9" t="n"/>
-      <c r="B113" s="9" t="n"/>
-      <c r="C113" s="16" t="n">
-        <v>112</v>
-      </c>
-      <c r="D113" s="17" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="16" t="n">
+        <v>113</v>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
         <is>
           <t>이 고객한테는 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E113" s="18" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr">
         <is>
           <t>공격투자형인 이 고객에게는 높은위험 등급까지의 상품만 안내할 수 있고, 허용 상한이 높은위험이라 카탈로그 전부가 범위 안이다. 다만 무엇을 권유할지는 직원이 판단해야 하므로, 안내할 수 있는 상품 목록을 확인하고 적합성 확인 결과이지 투자권유가 아니라는 점을 염두에 두어야 해요. 안내할 수 없는 상품은 없어요. 안내할 수 있는 상품 12종은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 보통위험 · 최근 1년 4.8% · 채권형
@@ -4649,35 +4698,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F113" s="21" t="inlineStr">
+      <c r="F114" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · 대본</t>
         </is>
       </c>
-      <c r="G113" s="18" t="inlineStr">
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H113" s="18" t="inlineStr">
+      <c r="H114" s="18" t="inlineStr">
         <is>
           <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
         </is>
       </c>
-      <c r="I113" s="18" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="n"/>
-      <c r="B114" s="9" t="n"/>
-      <c r="C114" s="16" t="n">
-        <v>113</v>
-      </c>
-      <c r="D114" s="17" t="inlineStr">
+      <c r="I114" s="18" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
         <is>
           <t>고객이 주식형 펀드 넣어달라는데 이 고객 성향으로 가능해?</t>
         </is>
       </c>
-      <c r="E114" s="18" t="inlineStr">
+      <c r="E115" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 이 고객의 투자성향과 위험등급 상한을 고려할 때 주식형 펀드는 안내할 수 없어요. 현재 고객의 투자성향은 안정추구형이고 적합성 허용 상한은 낮은위험이라서, 이 등급보다 높은 상품은 가입 대상이 아니에요. 따라서 위험등급이 보통위험 이상인 주식형 펀드는 안내가 제한돼요. 지금 고객에게 안내할 수 있는 상품은 위험등급이 낮은위험과 매우낮은위험에 해당하는 다음의 6종이에요.
@@ -4706,35 +4755,35 @@
 반면에 글로벌채권인덱스 C-P, 온국민TDF2035 C-P, 온국민TDF2040 C-P, 중립형 MP, 성장형 MP, 글로벌리츠 ETF 같은 상품들은 상품 위험등급이 보통위험에서 높은위험까지로 고객의 허용 상한인 낮은위험을 초과하기 때문에 안내할 수 없어요. 이는 어디까지나 적합성 확인 결과에 따른 안내이며 특정 상품에 대한 투자권유가 아니라는 점을 염두에 두셔야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F114" s="19" t="inlineStr">
+      <c r="F115" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G114" s="18" t="inlineStr">
+      <c r="G115" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H114" s="18" t="inlineStr">
+      <c r="H115" s="18" t="inlineStr">
         <is>
           <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
-      <c r="I114" s="18" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="n"/>
-      <c r="B115" s="9" t="n"/>
-      <c r="C115" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="D115" s="17" t="inlineStr">
+      <c r="I115" s="18" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="16" t="n">
+        <v>115</v>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
         <is>
           <t>만기 자금 실적배당으로 돌리면 이 고객 성향으로 뭘 안내할 수 있어?</t>
         </is>
       </c>
-      <c r="E115" s="18" t="inlineStr">
+      <c r="E116" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 안정추구형인 이 고객에게는 적합성 허용 상한이 낮은위험으로 설정되어 있어 그에 맞는 상품만 안내할 수 있어요. 
@@ -4766,35 +4815,35 @@
 이외에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험보다 높아 안내할 수 없으며, KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이라 안내할 수 없어요. 이 안내는 적합성 확인 결과이며 투자권유가 아니라는 점을 염두에 두시고, 사용계획이 있는 자금이라면 먼저 걸러내어 현금성자산이나 운용지시가 되지 않는 자산으로 다루어 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F115" s="21" t="inlineStr">
+      <c r="F116" s="21" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="G115" s="18" t="inlineStr">
+      <c r="G116" s="18" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H115" s="18" t="inlineStr">
+      <c r="H116" s="18" t="inlineStr">
         <is>
           <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
         </is>
       </c>
-      <c r="I115" s="18" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="n"/>
-      <c r="B116" s="9" t="n"/>
-      <c r="C116" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="D116" s="17" t="inlineStr">
+      <c r="I116" s="18" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
         <is>
           <t>이 고객 성향으로 안내 못 하는 건 뭐고 왜 그런 거야?</t>
         </is>
       </c>
-      <c r="E116" s="18" t="inlineStr">
+      <c r="E117" s="18" t="inlineStr">
         <is>
           <t>위험중립형 성향인 이 고객에게 안내할 수 있는 상품 위험등급 상한은 보통위험이에요. 안내할 수 없는 상품들은 모두 허용 상한을 초과하여 다음의 상품들이 해당돼요.
 - KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험
@@ -4804,35 +4853,35 @@
 이 안내는 고객의 투자성향에 따른 적합성 확인 결과이며 특정 상품에 대한 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F116" s="23" t="inlineStr">
+      <c r="F117" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G116" s="18" t="inlineStr">
+      <c r="G117" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H116" s="18" t="inlineStr">
+      <c r="H117" s="18" t="inlineStr">
         <is>
           <t>제외된 상품 + 사유 ↔ 「없다」로 끝내거나 사유를 지어낸다(§5 — 0건일 때 침묵하지 않는다)</t>
         </is>
       </c>
-      <c r="I116" s="18" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="n"/>
-      <c r="B117" s="10" t="n"/>
-      <c r="C117" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="D117" s="17" t="inlineStr">
+      <c r="I117" s="18" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
         <is>
           <t>이 고객 위험등급 상한이 어디까지야?</t>
         </is>
       </c>
-      <c r="E117" s="18" t="inlineStr">
+      <c r="E118" s="18" t="inlineStr">
         <is>
           <t>이 고객에게 안내할 수 있는 투자성향 허용 상한은 보통위험까지예요. 적합성 확인 결과 이 등급까지의 상품만 안내할 수 있으니 참고해 주세요. 
 안내할 수 있는 상품은 다음과 같아요.
@@ -4852,39 +4901,39 @@
 이 안내는 적합성 확인 결과이며 투자권유가 아니에요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F117" s="19" t="inlineStr">
+      <c r="F118" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G117" s="18" t="inlineStr">
+      <c r="G118" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H117" s="18" t="inlineStr">
+      <c r="H118" s="18" t="inlineStr">
         <is>
           <t>허용 위험등급 상한 + 투자권유가 아니라는 표시 ↔ 상한만 던진다</t>
         </is>
       </c>
-      <c r="I117" s="18" t="inlineStr"/>
-    </row>
-    <row r="118" hidden="1">
-      <c r="A118" s="9" t="n"/>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="I118" s="18" t="inlineStr"/>
+    </row>
+    <row r="119" hidden="1">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
         </is>
       </c>
-      <c r="C118" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="D118" s="12" t="inlineStr">
+      <c r="C119" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>이 고객 1975년생인데 TDF 몇 년짜리가 맞고 위험자산 비중이 얼마야?</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>고객이 문의한 TDF 추천 연도 및 위험자산 비중 정보는 현재 준비된 자료가 없어 안내하기 어려워요. 대신 현재 등록된 투자성향을 기준으로 안내할 수 있는 상품 범위와 적합성 확인 결과를 짚어 드릴게요. 이 고객은 위험중립형 성향으로 위험등급 보통위험까지 허용되므로, 해당 등급 이내의 상품만 안내할 수 있어요. 
 안내할 수 있는 상품은 다음과 같아요.
@@ -4899,35 +4948,35 @@
 반면에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하며, KB 글로벌리츠 ETF는 높은위험으로 역시 허용 상한을 초과하여 목록에 포함되지 않아요. 이 목록은 고객의 적합성 확인 결과에 따른 안내 가능 범위이며 특정 상품의 가입을 권유하는 것이 아니니 유의해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F118" s="11" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
+      <c r="G119" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H118" s="6" t="inlineStr">
+      <c r="H119" s="6" t="inlineStr">
         <is>
           <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="n"/>
-      <c r="B119" s="9" t="n"/>
-      <c r="C119" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="D119" s="12" t="inlineStr">
+      <c r="I119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>8월 퇴직연금 추천펀드에 뭐뭐 올라와 있는지 구분별로 알려줘</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>8월 퇴직연금 추천펀드(디폴트옵션)에 올라와 있는 상품은 위험도별로 구분되어 있으며, 2026년 8월 기준(수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준)으로 안내할 수 있다. 시장 변동과 상품 개편에 따라 빠르게 달라질 수 있으므로 인용 전 기준시점을 확인해야 한다. 
 초저위험 지켜드림 포트폴리오는 비중 100이며 1년 수익률 2.13%로 구성되어 있다. 편입상품은 다음과 같다.
@@ -4974,52 +5023,19 @@
   ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
+      <c r="G120" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="H120" s="6" t="inlineStr">
         <is>
           <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="n"/>
-      <c r="B120" s="9" t="n"/>
-      <c r="C120" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="D120" s="12" t="inlineStr">
-        <is>
-          <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>수익률 비교 질문을 하는 고객에게는 금융감독원 공시와 디폴트옵션 실적을 근거로 제시하면서 장기적인 관점의 관리를 약속하는 방식으로 접근해야 해요. 다른 은행과 비교하는 고객에게는 단기 성과보다 장기 관리가 중요하다는 점을 짚어주는 것이 핵심이에요. IRP 실적배당형 부문 전 구간 1위와 디폴트옵션 수익률 순위를 안내할 수 있도록 "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀드려 보세요. 또한 디폴트옵션 고위험 포트폴리오의 실적을 바탕으로 "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요.</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr"/>
@@ -5032,10 +5048,43 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
+          <t>고객이 다른 은행 대비 국민은행 개인형 IRP 수익률 얼마냐고 물어보시는데</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>수익률 비교 질문을 하는 고객에게는 금융감독원 공시와 디폴트옵션 실적을 근거로 제시하면서 장기적인 관점의 관리를 약속하는 방식으로 접근해야 해요. 다른 은행과 비교하는 고객에게는 단기 성과보다 장기 관리가 중요하다는 점을 짚어주는 것이 핵심이에요. IRP 실적배당형 부문 전 구간 1위와 디폴트옵션 수익률 순위를 안내할 수 있도록 "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀드려 보세요. 또한 디폴트옵션 고위험 포트폴리오의 실적을 바탕으로 "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요.</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
           <t>디폴트옵션 포트폴리오 구성상품이랑 비중, 금리까지 알려줘</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>디폴트옵션 포트폴리오의 구성상품과 비중, 금리 정보는 2026년 8월 기준(수익률은 2026년 7월 30일, 원리금보장 금리는 2026년 8월 기준)으로 안내할 수 있는 상품들이 있다. 위험도별 포트폴리오의 구체적인 구성과 비중, 금리는 다음과 같이 확인된다.
 초저위험 '지켜드림' 포트폴리오
@@ -5079,68 +5128,68 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F121" s="14" t="inlineStr">
+      <c r="F122" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G121" s="6" t="inlineStr">
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H121" s="6" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
         </is>
       </c>
-      <c r="I121" s="6" t="inlineStr"/>
-    </row>
-    <row r="122" hidden="1">
-      <c r="A122" s="9" t="n"/>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>직원이 물어본 TDF 수익률 및 위험등급에 대해서는 현재 준비된 자료가 없어요. 다만 2026년 3월에 작성된 연금사업본부 연금컨설팅부 자료를 기준으로 2025년 10월 기준 당행 라인업의 개념과 선택 공식에 관한 내용은 확인할 수 있어요. TDF는 은퇴 시점에 맞춰 주식→채권 비중을 자동 조정하는 자산배분 펀드다(전략 명칭 글라이드 패스). 상품명 숫자 = 목표 은퇴연도, 5년 단위 빈티지. 선택 공식 출생연도 + 예상 은퇴연령 = Target Date(예: 1990+60=2050). 당행 라인업 총 18종(2025.10 기준). 환헤지 여부로 H(헤지) / UH(언헤지) 상품이 구분된다 — H는 환율 변동 영향 축소, UH는 환차익·환차손 반영. 관련 내용은 기준시점 2025.10 (KBthink 04) 기준으로 안내해 드릴 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F122" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
-        </is>
-      </c>
       <c r="I122" s="6" t="inlineStr"/>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123" s="9" t="n"/>
-      <c r="B123" s="10" t="n"/>
+      <c r="B123" s="9" t="n"/>
       <c r="C123" s="4" t="n">
         <v>122</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
+          <t>KB 온국민 TDF 시리즈 수익률이랑 위험등급 알려줘</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>직원이 물어본 TDF 수익률 및 위험등급에 대해서는 현재 준비된 자료가 없어요. 다만 2026년 3월에 작성된 연금사업본부 연금컨설팅부 자료를 기준으로 2025년 10월 기준 당행 라인업의 개념과 선택 공식에 관한 내용은 확인할 수 있어요. TDF는 은퇴 시점에 맞춰 주식→채권 비중을 자동 조정하는 자산배분 펀드다(전략 명칭 글라이드 패스). 상품명 숫자 = 목표 은퇴연도, 5년 단위 빈티지. 선택 공식 출생연도 + 예상 은퇴연령 = Target Date(예: 1990+60=2050). 당행 라인업 총 18종(2025.10 기준). 환헤지 여부로 H(헤지) / UH(언헤지) 상품이 구분된다 — H는 환율 변동 영향 축소, UH는 환차익·환차손 반영. 관련 내용은 기준시점 2025.10 (KBthink 04) 기준으로 안내해 드릴 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
           <t>투자성향별 포트폴리오에서 위험중립형은 어떻게 짜여 있어?</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>위험중립형 포트폴리오는 2026년 8월 기준 국내채권 60%, 해외채권 15%, 해외혼합 25%의 자산배분으로 구성되어 있어요. 이 유형의 기대수익은 5.4%, 변동성은 4.9%로 산정되어 있으며, 활용할 수 있는 상품은 다음과 같아요.
 - 하나 파워e단기채 (합성총보수 연0.1834%) — 단기 회사채 및 기업어음에 주로 투자하여 시중금리 대비 초과수익을 추구
@@ -5150,72 +5199,72 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F123" s="14" t="inlineStr">
+      <c r="F124" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G124" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="n"/>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>16. 시황 — 상담에 쓰는 만큼</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="n">
-        <v>123</v>
-      </c>
-      <c r="D124" s="17" t="inlineStr">
-        <is>
-          <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
-        </is>
-      </c>
-      <c r="E124" s="18" t="inlineStr">
-        <is>
-          <t>시장 불안을 이유로 실적배당형 상품 전환을 고민하는 고객에게는 연금의 자금 성격과 운용 기간의 특성을 활용해 접근하는 것이 핵심이에요. 연금은 일반 투자와 달리 30년 이상이라는 장기 기간을 가지며 투입되는 규모도 상대적으로 작아 마이너스 50%를 맞아도 실제 체감하는 타격이 크지 않다는 점을 짚어주세요. 일반 투자는 금액이 크고 기간이 짧아 저변동성이 맞지만, 연금은 오히려 변동성을 지향해도 된다는 논리로 고객의 통념을 전환해 줄 수 있어요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 연금지급 대기나 교체매매 중으로 사용계획이 있는 자금은 먼저 걸러내야 해요. 또한 고객에게 설명할 때는 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 시장 상황에 대한 불안을 해소할 때는 우리나라 사람들이 실거주 부동산을 30~50년씩 보유하는 것처럼 30년 이상의 기간에는 이미 익숙하다는 점을 함께 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="F124" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
-        </is>
-      </c>
-      <c r="G124" s="18" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H124" s="18" t="inlineStr">
-        <is>
-          <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
-        </is>
-      </c>
-      <c r="I124" s="18" t="inlineStr"/>
+      <c r="I124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="9" t="n"/>
-      <c r="B125" s="9" t="n"/>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>16. 시황 — 상담에 쓰는 만큼</t>
+        </is>
+      </c>
       <c r="C125" s="16" t="n">
         <v>124</v>
       </c>
       <c r="D125" s="17" t="inlineStr">
         <is>
+          <t>고객이 지금 시장 불안한데 실적배당으로 옮겨도 되겠냐고 묻는데 뭐라고 설명하지?</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>시장 불안을 이유로 실적배당형 상품 전환을 고민하는 고객에게는 연금의 자금 성격과 운용 기간의 특성을 활용해 접근하는 것이 핵심이에요. 연금은 일반 투자와 달리 30년 이상이라는 장기 기간을 가지며 투입되는 규모도 상대적으로 작아 마이너스 50%를 맞아도 실제 체감하는 타격이 크지 않다는 점을 짚어주세요. 일반 투자는 금액이 크고 기간이 짧아 저변동성이 맞지만, 연금은 오히려 변동성을 지향해도 된다는 논리로 고객의 통념을 전환해 줄 수 있어요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 연금지급 대기나 교체매매 중으로 사용계획이 있는 자금은 먼저 걸러내야 해요. 또한 고객에게 설명할 때는 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 시장 상황에 대한 불안을 해소할 때는 우리나라 사람들이 실거주 부동산을 30~50년씩 보유하는 것처럼 30년 이상의 기간에는 이미 익숙하다는 점을 함께 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
           <t>이번 주 금융시장에 영향 줄 만한 일정 뭐 있어?</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차(2026년 8월 14일 종가 기준) 금융시장에 영향을 줄 수 있는 주요 일정은 국가별로 지정되어 있어요.
 - 17일 월요일 — 1~20일 수출/입
@@ -5226,35 +5275,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F125" s="19" t="inlineStr">
+      <c r="F126" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G125" s="18" t="inlineStr">
+      <c r="G126" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H125" s="18" t="inlineStr">
+      <c r="H126" s="18" t="inlineStr">
         <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「이번 주」에 8월 3주차 일정이 나온다(시효 표시는 붙는다). 봐야 할 것은 기준시점이 빠지지 않는가</t>
         </is>
       </c>
-      <c r="I125" s="18" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="n"/>
-      <c r="B126" s="9" t="n"/>
-      <c r="C126" s="16" t="n">
-        <v>125</v>
-      </c>
-      <c r="D126" s="17" t="inlineStr">
+      <c r="I126" s="18" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
         <is>
           <t>이번 달 FOMC 어떻게 보고 있는지 시나리오별로 알려줘</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr">
+      <c r="E127" s="18" t="inlineStr">
         <is>
           <t>2026년 9월 자료 기준으로 9월 미국 FOMC는 기준금리를 동결할 가능성이 가장 높은 기본 시나리오로 보고 있어요.
 당시 기준으로 연준의 9월 기준금리 동결 가능성은 시장에 이미 선반영되었고, 포워드 가이던스를 주지 않으려는 워시 의장의 태도로 인해 시장 영향력은 제한적일 것으로 보았어요. 기본 시나리오에서는 미국초단기 국채 ETF신탁 같은 미국초단기채 상품을 고려해 볼 수 있어요.
@@ -5264,68 +5313,68 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F126" s="19" t="inlineStr">
+      <c r="F127" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G126" s="18" t="inlineStr">
+      <c r="G127" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H126" s="18" t="inlineStr">
+      <c r="H127" s="18" t="inlineStr">
         <is>
           <t>긍정·기본·부정 + 기준시점(26.09 — 시연일과 같은 달) ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
-        </is>
-      </c>
-      <c r="I126" s="18" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="n"/>
-      <c r="B127" s="9" t="n"/>
-      <c r="C127" s="16" t="n">
-        <v>126</v>
-      </c>
-      <c r="D127" s="17" t="inlineStr">
-        <is>
-          <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
-        </is>
-      </c>
-      <c r="E127" s="18" t="inlineStr">
-        <is>
-          <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
-        </is>
-      </c>
-      <c r="F127" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
-        </is>
-      </c>
-      <c r="G127" s="18" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H127" s="18" t="inlineStr">
-        <is>
-          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="n"/>
-      <c r="B128" s="10" t="n"/>
+      <c r="B128" s="9" t="n"/>
       <c r="C128" s="16" t="n">
         <v>127</v>
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
+          <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="inlineStr">
+        <is>
+          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
+        </is>
+      </c>
+      <c r="I128" s="18" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
           <t>요즘 시황 근거로 이 고객 원리금보장 그대로 둬도 되는지 판단 근거 알려줘</t>
         </is>
       </c>
-      <c r="E128" s="18" t="inlineStr">
+      <c r="E129" s="18" t="inlineStr">
         <is>
           <t>● 정민석
 질문하신 고객의 원리금보장 상품 유지 여부를 판단할 때 시장 상황과 자금의 성격을 함께 고려해야 해요. 2026년 8월 3주차 기준으로 미국 증시는 소비자물가 예상 부합과 생산자물가 예상 하회, 연준 금리 인상 우려 완화 속에 AI 반도체 및 기술주 중심의 상승세로 S&amp;P500지수가 사상 최고치를 경신했으나, 미국-이란 긴장으로 인한 국제유가 상승, 미국 재정 적자 우려, 하이퍼스케일러들의 AI 인프라 투자 자금 채권시장 조달에 따른 미국 국채 금리 상승 등이 증시 상승세를 제약하는 요인으로 작용하고 있습니다. 2026년 9월 기준으로는 미국 FOMC와 일본 BOJ 등 주요 경제 이벤트와 점도표 변화, 엔 캐리 청산 우려 등 변동성 확대 요인이 있으므로 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. 또한 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라진니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.
@@ -5336,39 +5385,39 @@
 요즘 시황 근거로 원리금보장 자산을 그대로 두어도 되는지 판단할 때는 2026년 8월 3주차와 2026년 9월 자료에서 다루는 시장 상황과 기준시점을 확인해야 해요. 미국 7월 소비자물가가 예상에 부합하고 생산자물가는 예상을 하회하여 연준 금리 인상 우려가 완화된 반면, 미·이런 긴장에 따른 국제유가 상승과 미국 국채 금리 상승 요인이 함께 작용하고 있어요. 또한 9월에는 기준금리 동결 후 데이터 의존 입장을 반복할 것으로 예상되는 미국 FOMC와 기준금리 인상이 예상되는 일본 BOJ 금융정책결정회의 등 중요 이벤트가 예정되어 있어요. 미국 재정적자 확대와 장기국채 수요 감소를 감안해 장기금리 하락은 비중 축소 기회로 활용할 수 있으며, BOJ의 기준금리 인상과 엔 캐리 청산 우려가 있으나 인상이 예상된 이벤트라 2024년 8월과 같은 증시 폭락 가능성은 낮다고 판단하고 있어요. 다만 사용계획이 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내어 판단해야 해요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="F128" s="19" t="inlineStr">
+      <c r="F129" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G128" s="18" t="inlineStr">
+      <c r="G129" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H128" s="18" t="inlineStr">
+      <c r="H129" s="18" t="inlineStr">
         <is>
           <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
         </is>
       </c>
-      <c r="I128" s="18" t="inlineStr"/>
-    </row>
-    <row r="129" hidden="1">
-      <c r="A129" s="9" t="n"/>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="I129" s="18" t="inlineStr"/>
+    </row>
+    <row r="130" hidden="1">
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>17. 복합·연쇄 턴</t>
         </is>
       </c>
-      <c r="C129" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="C130" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
         <is>
           <t>우리 수수료가 얼마고, 증권사는 무료라는데 뭐라고 답하지?</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>증권사 수수료 무료를 이유로 이탈하려는 고객에게는 면제 조건을 먼저 짚어준 뒤 운용과 관리 가치로 설명의 초점을 옮겨야 해요. 증권사의 수수료 면제가 고객을 모아 펀드 판매로 수익을 내는 전략이라는 점과 장기할인 소멸 및 수시인출 면제 구조를 염두에 두고 대응 논리를 펼치세요. 만 55세 이후 연금개시 시 수수료가 0원이 되며 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제되는 조건을 먼저 확인해 주세요. 
 고객에게는 "국민은행도 만 55세 이후 연금개시를 하시면 수수료가 0원입니다^^ 만 55세가 안되셨더라도 퇴직금 5천만원 이상 입금된 경우라면 퇴직금 전액 수수료가 면제됩니다"라고 안내해 보세요. 
@@ -5376,59 +5425,22 @@
 아울러 당행 구체적인 수수료율이나 우리 수수료가 얼마인지에 대한 상세한 수치는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H129" s="6" t="inlineStr">
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="n"/>
-      <c r="B130" s="9" t="n"/>
-      <c r="C130" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 라이브러리</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
-        </is>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
+      <c r="I130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="n"/>
@@ -5438,10 +5450,47 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
+          <t>(제안 뒤) 그건 됐고, 이 고객 만기 언제야?</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 라이브러리</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
           <t>이 고객 예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>● 정민석
 현재 보유하신 자산이 모두 원리금보장상품으로만 운용 중인 고객에게는 정기예금 대신 디폴트옵션 저위험 이상으로 운용해 보시는 방법을 제안해 볼 수 있어요. 다만 해당 고객이 이미 디폴트옵션 초저위험을 등록해 보유하고 계신 상태라면 사전지정운용제도 등록 및 변경과 보유상품 변경인 기존 매도 및 신규 매수의 2단계 거래가 필요하다는 점을 반드시 함께 안내해 드려야 해요. 또한 고객에게 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 쉽게 설명해 주시는 것이 좋아요. 사용 계획이 있는 자금이나 반대 케이스에 해당하는지 먼저 확인하고 접근하는 점도 잊지 마세요.
@@ -5452,52 +5501,19 @@
 이미 디폴트옵션 초저위험을 등록·보유한 고객이라면 사전지정운용제도 등록 및 변경과 보유상품 변경(기존 매도 후 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요.</t>
         </is>
       </c>
-      <c r="F131" s="13" t="inlineStr">
+      <c r="F132" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G132" s="6" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="H132" s="6" t="inlineStr">
         <is>
           <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
-        </is>
-      </c>
-      <c r="I131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="n"/>
-      <c r="B132" s="9" t="n"/>
-      <c r="C132" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F132" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr"/>
@@ -5510,10 +5526,43 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
+          <t>올해 얼마 넣었고 세액공제 더 받을 수 있는지 계산까지 해줘</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · QA</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
           <t>(만기 질문 뒤) 그냥 두면 어떻게 돼?</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>● 오세훈
 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 안내하는 것이 핵심이에요. 1개월 내 만기도래 원리금보장상품을 보유하고 디폴트옵션이 미등록된 상태라면 이러한 제도 변경 내용을 짚어주면서 디폴트옵션 사전지정 등록이나 만기 예약변경을 권유하는 방법을 활용할 수 있어요.
@@ -5522,61 +5571,24 @@
 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 만기 전 운용 방향을 확정해야 해요. 만기 임박 + 디폴트옵션 미등록 고객에게는 "정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기 자금이 현금성자산으로 상환되니 디폴트옵션 사전지정 등록이나 만기 예약을 하시는 것이 좋아요"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F133" s="13" t="inlineStr">
+      <c r="F134" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
+      <c r="G134" s="6" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>이 고객 만기 언제고 금액은 얼마야?</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="9" t="n"/>
-      <c r="B134" s="9" t="n"/>
-      <c r="C134" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="D134" s="12" t="inlineStr">
-        <is>
-          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
-        </is>
-      </c>
-      <c r="F134" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
-        </is>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
@@ -5588,10 +5600,47 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
+          <t>(적합성 목록 뒤) 1번꺼 좀 더 설명해줘</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
           <t>(되묻기 뒤) 2번째꺼</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>■ [06-AD-080] 개인형IRP 계좌이체 전입/전출  (계약이전)
 · 무슨 화면인지: 계좌이체 전입/전출 조회, 전출취소(해제), 이전 진행상황 수시 조회 → 관련 지식항목 33·34
@@ -5600,58 +5649,19 @@
 · 출처 퇴직연금 주요거래 화면번호 안내 (KB StarLearn 직원교육)</t>
         </is>
       </c>
-      <c r="F135" s="13" t="inlineStr">
+      <c r="F136" s="13" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="G136" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
-        </is>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>실물이전 어떻게 처리해?</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="n"/>
-      <c r="B136" s="9" t="n"/>
-      <c r="C136" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="D136" s="12" t="inlineStr">
-        <is>
-          <t>(되묻기 뒤) 잘 모르겠는데</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>어느 방향으로 이전하는 건가요?
-· 전출
-· 전입</t>
-        </is>
-      </c>
-      <c r="F136" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
@@ -5668,32 +5678,34 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>(채널 되묻기 뒤) ETF 상품</t>
+          <t>(되묻기 뒤) 잘 모르겠는데</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>고객이 퇴직연금 ETF 상품을 직접 찾아보실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 확인해 드릴게요. KB스타뱅킹을 이용하신다면 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, 나의 ETF · ETF 상품 조회 순으로 이동하시면 되어요. 인터넷뱅킹을 이용하실 경우에는 KB퇴직연금, 개인고객, 퇴직연금 ETF, 나의 ETF · ETF 상품조회 메뉴를 통해 조회하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
-        </is>
-      </c>
-      <c r="F137" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>어느 방향으로 이전하는 건가요?
+· 전출
+· 전입</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>고른 갈래의 채널 경로만 ↔ 세 갈래를 다 쏟거나 되묻기를 또 한다</t>
+          <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
+          <t>실물이전 어떻게 처리해?</t>
         </is>
       </c>
     </row>
@@ -5705,13 +5717,12 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>(오프너 되묻기 뒤) 중립적 용건으로 열기</t>
+          <t>(채널 되묻기 뒤) ETF 상품</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>수익률 관리 해피콜의 문을 열 때는 고객에게 문제점을 직접적으로 지적하기보다 전담직원 인사와 정기적 상품관리라는 중립적 명분을 활용하는 것이 좋아요. 통화 초반에는 구체적인 내용을 바로 꺼내기보다 먼저 가볍게 용건을 전하며 상대방의 의사를 확인하는 방식으로 접근해 보세요. 
-고객에게는 "안녕하세요, KB국민은행 000지점 000입니다. 저희 국민은행에 가입하신 퇴직연금 관련해서 안내드릴 사항이 있어 전화드렸습니다! 잠시 통화 가능하세요?"라고 먼저 건네주시고, 이어지는 턴에서 "고객님의 퇴직연금 전담직원으로 안내 인사드리고 정기적인 상품관리를 해 드리고자 연락드렸습니다. 퇴직연금 상품을 운용하시면서 혹시 궁금하시거나 상담하고 싶으신 내용이 있으신지요?"라고 자연스럽게 대화를 이어가며 문의 사항을 여쭤보시면 돼요.</t>
+          <t>고객이 퇴직연금 ETF 상품을 직접 찾아보실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 확인해 드릴게요. KB스타뱅킹을 이용하신다면 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, 나의 ETF · ETF 상품 조회 순으로 이동하시면 되어요. 인터넷뱅킹을 이용하실 경우에는 KB퇴직연금, 개인고객, 퇴직연금 ETF, 나의 ETF · ETF 상품조회 메뉴를 통해 조회하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -5721,17 +5732,17 @@
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>고른 오프너의 첫 마디 대사 ↔ 고르지 않은 쪽을 답하거나 일반론으로 돌아간다</t>
+          <t>고른 갈래의 채널 경로만 ↔ 세 갈래를 다 쏟거나 되묻기를 또 한다</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
+          <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
         </is>
       </c>
     </row>
@@ -5743,17 +5754,18 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>(제안 뒤) 아니, 됐어</t>
+          <t>(오프너 되묻기 뒤) 중립적 용건으로 열기</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
-        </is>
-      </c>
-      <c r="F139" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>수익률 관리 해피콜의 문을 열 때는 고객에게 문제점을 직접적으로 지적하기보다 전담직원 인사와 정기적 상품관리라는 중립적 명분을 활용하는 것이 좋아요. 통화 초반에는 구체적인 내용을 바로 꺼내기보다 먼저 가볍게 용건을 전하며 상대방의 의사를 확인하는 방식으로 접근해 보세요. 
+고객에게는 "안녕하세요, KB국민은행 000지점 000입니다. 저희 국민은행에 가입하신 퇴직연금 관련해서 안내드릴 사항이 있어 전화드렸습니다! 잠시 통화 가능하세요?"라고 먼저 건네주시고, 이어지는 턴에서 "고객님의 퇴직연금 전담직원으로 안내 인사드리고 정기적인 상품관리를 해 드리고자 연락드렸습니다. 퇴직연금 상품을 운용하시면서 혹시 궁금하시거나 상담하고 싶으신 내용이 있으신지요?"라고 자연스럽게 대화를 이어가며 문의 사항을 여쭤보시면 돼요.</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
@@ -5763,12 +5775,12 @@
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
+          <t>고른 오프너의 첫 마디 대사 ↔ 고르지 않은 쪽을 답하거나 일반론으로 돌아간다</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+          <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
         </is>
       </c>
     </row>
@@ -5780,17 +5792,17 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
+          <t>(제안 뒤) 아니, 됐어</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
+          <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
         </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -5800,16 +5812,16 @@
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
+          <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" hidden="1">
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
       <c r="A141" s="9" t="n"/>
       <c r="B141" s="9" t="n"/>
       <c r="C141" s="4" t="n">
@@ -5817,12 +5829,12 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>(첫 턴) 네</t>
+          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+          <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
         </is>
       </c>
       <c r="F141" s="14" t="inlineStr">
@@ -5832,104 +5844,141 @@
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>고객 없이</t>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="inlineStr"/>
+          <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
+        </is>
+      </c>
     </row>
     <row r="142" hidden="1">
-      <c r="A142" s="10" t="n"/>
-      <c r="B142" s="10" t="n"/>
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
       <c r="C142" s="4" t="n">
         <v>141</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
+          <t>(첫 턴) 네</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143" hidden="1">
+      <c r="A143" s="10" t="n"/>
+      <c r="B143" s="10" t="n"/>
+      <c r="C143" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
           <t>(10턴쯤 뒤) 처음에 물어본 거 다시 정리해줘</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr"/>
-      <c r="F142" s="14" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr"/>
+      <c r="F143" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G142" s="6" t="inlineStr">
+      <c r="G143" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H143" s="6" t="inlineStr">
         <is>
           <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
         </is>
       </c>
-      <c r="I142" s="6" t="inlineStr">
+      <c r="I143" s="6" t="inlineStr">
         <is>
           <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Ⅳ. 상담 후 · 그 밖</t>
         </is>
       </c>
-      <c r="B143" s="15" t="inlineStr">
+      <c r="B144" s="15" t="inlineStr">
         <is>
           <t>18. 안내 콘텐츠·발송</t>
         </is>
       </c>
-      <c r="C143" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="D143" s="17" t="inlineStr">
+      <c r="C144" s="16" t="n">
+        <v>143</v>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
-      <c r="E143" s="18" t="inlineStr">
+      <c r="E144" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 안내할 만한 이벤트와 세미나는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있고 디폴트옵션이 미설정된 상태이므로 잠자는 IRP 자금 깨우기 운용 이벤트와 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나를 안내하는 것이 핵심이에요.
 잠자는 IRP 자금 깨우기 운용 이벤트는 12/30까지 KB스타뱅킹에서 진행되며, 고객이 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 상태이므로 참고하시기 좋고 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX를 활용할 수 있어요.
 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나는 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 온라인 세미나로, 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어 추천하며 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX로 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="F143" s="20" t="inlineStr">
+      <c r="F144" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G143" s="18" t="inlineStr">
+      <c r="G144" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H143" s="18" t="inlineStr">
+      <c r="H144" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
-      <c r="I143" s="18" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="9" t="n"/>
-      <c r="B144" s="9" t="n"/>
-      <c r="C144" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="I144" s="18" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="16" t="n">
+        <v>144</v>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>왜 이 이벤트를 고른 거야?</t>
         </is>
       </c>
-      <c r="E144" s="18" t="inlineStr">
+      <c r="E145" s="18" t="inlineStr">
         <is>
           <t>송도윤 고객에게 잠자는 IRP 자금 깨우기 운용 이벤트를 안내하는 이유는 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 성립 요건을 충족하기 때문이에요. 고객이 최종 운용변경 이후 장기간 운용되지 않은 자금을 보유하고 있어 운용상품을 선택하거나 변경할 수 있도록 이벤트를 권유할 수 있어요. 안내 시 참고할 발송 문구는 다음과 같아요.
 (광고) 송도윤 고객님, KB국민은행입니다.
@@ -5938,39 +5987,39 @@
 무료수신거부 080-XXX-XXXX</t>
         </is>
       </c>
-      <c r="F144" s="23" t="inlineStr">
+      <c r="F145" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G144" s="18" t="inlineStr">
+      <c r="G145" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H144" s="18" t="inlineStr">
+      <c r="H145" s="18" t="inlineStr">
         <is>
           <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
         </is>
       </c>
-      <c r="I144" s="18" t="inlineStr">
+      <c r="I145" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="9" t="n"/>
-      <c r="B145" s="9" t="n"/>
-      <c r="C145" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="D145" s="17" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>(이벤트 답변 뒤) 응, 발송 화면 열어줘</t>
         </is>
       </c>
-      <c r="E145" s="18" t="inlineStr">
+      <c r="E146" s="18" t="inlineStr">
         <is>
           <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기
 화면이 열리면 이 문구를 넣어 주세요 — "(광고) 송도윤 고객님, KB국민은행입니다.
@@ -5979,58 +6028,19 @@
 무료수신거부 080-XXX-XXXX"</t>
         </is>
       </c>
-      <c r="F145" s="20" t="inlineStr">
+      <c r="F146" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G145" s="18" t="inlineStr">
+      <c r="G146" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H145" s="18" t="inlineStr">
+      <c r="H146" s="18" t="inlineStr">
         <is>
           <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
-        </is>
-      </c>
-      <c r="I145" s="18" t="inlineStr">
-        <is>
-          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="n"/>
-      <c r="B146" s="9" t="n"/>
-      <c r="C146" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="D146" s="17" t="inlineStr">
-        <is>
-          <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
-        </is>
-      </c>
-      <c r="E146" s="18" t="inlineStr">
-        <is>
-          <t>이 고객에게 안내할 이벤트와 세미나의 발송 문구는 자료에 있는 문구를 그대로 활용하는 게 핵심이에요. 
-잠자는 IRP 자금 깨우기 운용 이벤트 발송 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX"를 그대로 사용해 주세요.
-온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
-        </is>
-      </c>
-      <c r="F146" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G146" s="18" t="inlineStr">
-        <is>
-          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H146" s="18" t="inlineStr">
-        <is>
-          <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
         </is>
       </c>
       <c r="I146" s="18" t="inlineStr">
@@ -6047,10 +6057,49 @@
       </c>
       <c r="D147" s="17" t="inlineStr">
         <is>
+          <t>문자로 뭐라고 보내면 좋을지 문구 좀 다듬어줘</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>이 고객에게 안내할 이벤트와 세미나의 발송 문구는 자료에 있는 문구를 그대로 활용하는 게 핵심이에요. 
+잠자는 IRP 자금 깨우기 운용 이벤트 발송 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. KB스타뱅킹에서 12/30까지 진행하는 잠자는 IRP 자금 깨우기 운용 이벤트를 안내해 드려요. 최종 운용변경 이후 14.4개월이 경과하여 미운용 현금성자산이 있는 고객님께서 참고하시기 좋아요. ▶ https://obank.kbstar.com/demo/event/irp-004 무료수신거부 080-XXX-XXXX"를 그대로 사용해 주세요.
+온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
+        </is>
+      </c>
+      <c r="F147" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="16" t="n">
+        <v>147</v>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
           <t>다른 건 없어? 열려 있는 거 전부 보여줘</t>
         </is>
       </c>
-      <c r="E147" s="18" t="inlineStr">
+      <c r="E148" s="18" t="inlineStr">
         <is>
           <t>앞서 말씀드린 2건 외에 잠재적 안내 후보로 열려 있는 이벤트 3건과 세미나 4건이 더 있어요.
 이벤트 3건은 다음과 같아요.
@@ -6065,76 +6114,76 @@
 고객에게 안내할 때는 사용계획이 있는 자금인지 먼저 확인하고 활용할 수 있는 방법을 살펴보세요. 세부적인 발송 문구나 링크가 필요한 항목이 있다면 이어서 말씀해 드릴게요.</t>
         </is>
       </c>
-      <c r="F147" s="19" t="inlineStr">
+      <c r="F148" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G147" s="18" t="inlineStr">
+      <c r="G148" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H147" s="18" t="inlineStr">
+      <c r="H148" s="18" t="inlineStr">
         <is>
           <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
         </is>
       </c>
-      <c r="I147" s="18" t="inlineStr">
+      <c r="I148" s="18" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="148" hidden="1">
-      <c r="A148" s="9" t="n"/>
-      <c r="B148" s="10" t="n"/>
-      <c r="C148" s="16" t="n">
-        <v>147</v>
-      </c>
-      <c r="D148" s="17" t="inlineStr">
+    <row r="149" hidden="1">
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="10" t="n"/>
+      <c r="C149" s="16" t="n">
+        <v>148</v>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E148" s="18" t="inlineStr">
+      <c r="E149" s="18" t="inlineStr">
         <is>
           <t>현재 이 고객의 요건에 맞는 세미나는 아직 준비된 자료가 없어요. 다만 열려 있는 콘텐츠 중 날짜가 가까운 세미나로는 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 세미나가 11/12(목) 17시에 KB국민은행 WM투자부 주관으로 예정되어 있어요. 이 세미나는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋은 내용이에요. 안내할 때 참고할 수 있는 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요.</t>
         </is>
       </c>
-      <c r="F148" s="19" t="inlineStr">
+      <c r="F149" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G148" s="18" t="inlineStr">
+      <c r="G149" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H148" s="18" t="inlineStr">
+      <c r="H149" s="18" t="inlineStr">
         <is>
           <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I148" s="18" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="n"/>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="I149" s="18" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="n"/>
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="D149" s="12" t="inlineStr">
+      <c r="C150" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>[제목] 송도윤 고객 관리 대상 사유 및 대응 방향
 송도윤 고객은 최근 358일간 접촉 이력이 없어 타사 비교 견적 노출 가능성이 있습니다.
@@ -6144,65 +6193,28 @@
 (아래에 이 고객의 연령·투자성향·평가금액·수익률·연금개시·세액공제 잔여한도·관리 사유 표가 붙습니다)</t>
         </is>
       </c>
-      <c r="F149" s="7" t="inlineStr">
+      <c r="F150" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="G149" s="6" t="inlineStr">
+      <c r="G150" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H149" s="6" t="inlineStr">
+      <c r="H150" s="6" t="inlineStr">
         <is>
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="I149" s="6" t="inlineStr">
+      <c r="I150" s="6" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="150" hidden="1">
-      <c r="A150" s="9" t="n"/>
-      <c r="B150" s="9" t="n"/>
-      <c r="C150" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="D150" s="12" t="inlineStr">
-        <is>
-          <t>(쪽지 초안 뒤) 응, 보내줘</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 시연본</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
-        </is>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
+    <row r="151" hidden="1">
       <c r="A151" s="9" t="n"/>
       <c r="B151" s="9" t="n"/>
       <c r="C151" s="4" t="n">
@@ -6210,17 +6222,17 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>지금까지 얘기한 거 정리해줘</t>
+          <t>(쪽지 초안 뒤) 응, 보내줘</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
-        </is>
-      </c>
-      <c r="F151" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
@@ -6230,16 +6242,16 @@
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
+          <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" hidden="1">
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
       <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
       <c r="C152" s="4" t="n">
@@ -6247,12 +6259,12 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
+          <t>지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
+          <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
         </is>
       </c>
       <c r="F152" s="14" t="inlineStr">
@@ -6267,30 +6279,34 @@
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
-        </is>
-      </c>
-      <c r="I152" s="6" t="inlineStr"/>
+          <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="153" hidden="1">
       <c r="A153" s="9" t="n"/>
-      <c r="B153" s="10" t="n"/>
+      <c r="B153" s="9" t="n"/>
       <c r="C153" s="4" t="n">
         <v>152</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>(쪽지 초안 뒤) 응, 사번 3902172한테 보내줘</t>
+          <t>(첫 턴) 지금까지 얘기한 거 정리해줘</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
-        </is>
-      </c>
-      <c r="F153" s="11" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
+          <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
@@ -6300,71 +6316,71 @@
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>받는 사람이 본인이 아니라 그 사번으로 바뀌고 화면에 밝힌다 ↔ 사번을 금액으로 읽어 본인에게 보낸다 · 사번을 못 읽었는데 「보냈다」고 답한다</t>
-        </is>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
-        </is>
-      </c>
+          <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr"/>
     </row>
     <row r="154" hidden="1">
       <c r="A154" s="9" t="n"/>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>20. 브리핑 수정</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="n">
+      <c r="B154" s="10" t="n"/>
+      <c r="C154" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="D154" s="17" t="inlineStr">
-        <is>
-          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
-        </is>
-      </c>
-      <c r="E154" s="18" t="inlineStr">
-        <is>
-          <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="F154" s="23" t="inlineStr">
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>(쪽지 초안 뒤) 응, 사번 3902172한테 보내줘</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G154" s="18" t="inlineStr">
+      <c r="G154" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H154" s="18" t="inlineStr">
-        <is>
-          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
-        </is>
-      </c>
-      <c r="I154" s="18" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>받는 사람이 본인이 아니라 그 사번으로 바뀌고 화면에 밝힌다 ↔ 사번을 금액으로 읽어 본인에게 보낸다 · 사번을 못 읽었는데 「보냈다」고 답한다</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
+        </is>
+      </c>
     </row>
     <row r="155" hidden="1">
       <c r="A155" s="9" t="n"/>
-      <c r="B155" s="9" t="n"/>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>20. 브리핑 수정</t>
+        </is>
+      </c>
       <c r="C155" s="16" t="n">
         <v>154</v>
       </c>
       <c r="D155" s="17" t="inlineStr">
         <is>
-          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
+          <t>화면에 뜬 평가금액을 5억으로 바꿔줘</t>
         </is>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="F155" s="19" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G155" s="18" t="inlineStr">
@@ -6374,23 +6390,56 @@
       </c>
       <c r="H155" s="18" t="inlineStr">
         <is>
-          <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
+          <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
         </is>
       </c>
       <c r="I155" s="18" t="inlineStr"/>
     </row>
     <row r="156" hidden="1">
       <c r="A156" s="9" t="n"/>
-      <c r="B156" s="10" t="n"/>
+      <c r="B156" s="9" t="n"/>
       <c r="C156" s="16" t="n">
         <v>155</v>
       </c>
       <c r="D156" s="17" t="inlineStr">
         <is>
+          <t>화면 제안 문장에서 '적극적으로'라는 표현 빼줘</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr"/>
+    </row>
+    <row r="157" hidden="1">
+      <c r="A157" s="9" t="n"/>
+      <c r="B157" s="10" t="n"/>
+      <c r="C157" s="16" t="n">
+        <v>156</v>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
           <t>추천 상품을 다른 걸로 바꿔줘</t>
         </is>
       </c>
-      <c r="E156" s="18" t="inlineStr">
+      <c r="E157" s="18" t="inlineStr">
         <is>
           <t>추천 상품을 다른 걸로 바꿔 달라는 요청에 대해서는 직접적인 변경 사유나 추가 상품을 안내해 드릴 자료가 아직 준비된 사유가 없어요. 다만 현재 등록된 투자성향 기준으로는 안내할 수 있는 위험등급 상한이 보통위험까지예요. 
 이 고객은 위험중립형 성향이라 보통위험 등급까지만 상품을 안내할 수 있어서, 현재 기준으로 안내 가능한 상품 목록은 다음과 같아요.
@@ -6406,39 +6455,39 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F156" s="19" t="inlineStr">
+      <c r="F157" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G156" s="18" t="inlineStr">
+      <c r="G157" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H156" s="18" t="inlineStr">
+      <c r="H157" s="18" t="inlineStr">
         <is>
           <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
         </is>
       </c>
-      <c r="I156" s="18" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="9" t="n"/>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="I157" s="18" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
+      <c r="C158" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>고객에게 해야 할 말 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E158" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 내용을 바탕으로 고객에게 바로 전달할 수 있는 핵심 대사만 짧게 줄여서 정리해 드릴게요. 
 연금지급 대기 자금이나 교체매매 중인 자금이 아닌지 먼저 확인한 뒤에 이렇게 안내해 보세요.
@@ -6446,63 +6495,24 @@
 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정해 약속하지 않도록 주의하고, 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용하여 고객이 쉽게 이해할 수 있도록 설명해 주세요.</t>
         </is>
       </c>
-      <c r="F157" s="7" t="inlineStr">
+      <c r="F158" s="7" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G157" s="6" t="inlineStr">
+      <c r="G158" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H157" s="6" t="inlineStr">
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="I157" s="6" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="n"/>
-      <c r="B158" s="9" t="n"/>
-      <c r="C158" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="D158" s="12" t="inlineStr">
-        <is>
-          <t>그 중 두 번째 상품만 자세히 설명해줘</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>앞서 안내드린 상품 중 두 번째 상품인 KB 국내채권형 C-P에 대해 자세히 설명해 드릴게요.
-- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
-위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 케이스</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
-        </is>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
@@ -6514,17 +6524,19 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
+          <t>그 중 두 번째 상품만 자세히 설명해줘</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
-        </is>
-      </c>
-      <c r="F159" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>앞서 안내드린 상품 중 두 번째 상품인 KB 국내채권형 C-P에 대해 자세히 설명해 드릴게요.
+- KB 국내채권형 C-P — 낮은위험 · 최근 1년 3.8% · 채권형
+위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
@@ -6534,12 +6546,12 @@
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
+          <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+          <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
       </c>
     </row>
@@ -6551,10 +6563,47 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
+          <t>방금 답변에서 고객한테 그대로 읽어줄 대사만 뽑아줘</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
           <t>아까 수수료 설명한 거 요약해줘</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E161" s="6" t="inlineStr">
         <is>
           <t>앞서 안내드린 개인형IRP 수수료는 부담금 종류와 채널 및 구간에 따라 차등 적용되니 단말에서 먼저 확인한 뒤 안내해 주세요. 상세 수수료율은 다음과 같이 대면 및 비대면 채널별 구간에 따라 적용돼요.
 - 사용자부담금(퇴직금) 대면 5천만원 미만 — 0.45%
@@ -6567,115 +6616,115 @@
 - 가입자부담금 비대면 1억원 이상 — 0.21%</t>
         </is>
       </c>
-      <c r="F160" s="14" t="inlineStr">
+      <c r="F161" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G160" s="6" t="inlineStr">
+      <c r="G161" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="9" t="n"/>
-      <c r="B161" s="9" t="n"/>
-      <c r="C161" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="D161" s="12" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>아까 그 답변에 수수료 얘기도 넣어서 다시 써줘</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E162" s="6" t="inlineStr">
         <is>
           <t>예금만으로 자산을 보유해 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 자산관리라는 논리로 접근하는 게 핵심이에요. 앞서 안내드린 내용에 수수료 관련 내용은 자료에 없어 추가하지 못했어요. 이미 안전하게 잘 운용하고 계신 점을 먼저 인정한 뒤, 원리금보장 상품도 매월 최고금리 상품 제공과 비대면 거래를 통해 꾸준히 관리해야 한다는 점을 짚어주세요. 
 고객에게는 이렇게 말씀해 보세요.
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="F161" s="14" t="inlineStr">
+      <c r="F162" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G161" s="6" t="inlineStr">
+      <c r="G162" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="162" hidden="1">
-      <c r="A162" s="9" t="n"/>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="4" t="n">
-        <v>161</v>
-      </c>
-      <c r="D162" s="12" t="inlineStr">
+    <row r="163" hidden="1">
+      <c r="A163" s="9" t="n"/>
+      <c r="B163" s="10" t="n"/>
+      <c r="C163" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>(첫 턴) 좀 더 짧게 줄여줘</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>이번 상담에서 오간 대화 기록은 없습니다.</t>
         </is>
       </c>
-      <c r="F162" s="14" t="inlineStr">
+      <c r="F163" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G162" s="6" t="inlineStr">
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="15" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="15" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
         </is>
       </c>
-      <c r="C163" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="D163" s="17" t="inlineStr">
+      <c r="C164" s="16" t="n">
+        <v>163</v>
+      </c>
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>너 뭐 할 수 있는지 알려줘</t>
         </is>
       </c>
-      <c r="E163" s="18" t="inlineStr">
+      <c r="E164" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6695,35 +6744,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F163" s="23" t="inlineStr">
+      <c r="F164" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G163" s="18" t="inlineStr">
+      <c r="G164" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H163" s="18" t="inlineStr">
+      <c r="H164" s="18" t="inlineStr">
         <is>
           <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
         </is>
       </c>
-      <c r="I163" s="18" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="9" t="n"/>
-      <c r="B164" s="9" t="n"/>
-      <c r="C164" s="16" t="n">
-        <v>163</v>
-      </c>
-      <c r="D164" s="17" t="inlineStr">
+      <c r="I164" s="18" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="n"/>
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="16" t="n">
+        <v>164</v>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
         <is>
           <t>너 이전 대화 기억해?</t>
         </is>
       </c>
-      <c r="E164" s="18" t="inlineStr">
+      <c r="E165" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6745,35 +6794,35 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F164" s="19" t="inlineStr">
+      <c r="F165" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G164" s="18" t="inlineStr">
+      <c r="G165" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H164" s="18" t="inlineStr">
+      <c r="H165" s="18" t="inlineStr">
         <is>
           <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
         </is>
       </c>
-      <c r="I164" s="18" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="9" t="n"/>
-      <c r="B165" s="10" t="n"/>
-      <c r="C165" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="I165" s="18" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="n"/>
+      <c r="B166" s="10" t="n"/>
+      <c r="C166" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D166" s="17" t="inlineStr">
         <is>
           <t>고객한테 문자 직접 보내줄 수 있어?</t>
         </is>
       </c>
-      <c r="E165" s="18" t="inlineStr">
+      <c r="E166" s="18" t="inlineStr">
         <is>
           <t>■ 제가 도와드릴 수 있는 것
 IRP(개인형 퇴직연금) 상담 화법을 안내해 드려요. 예를 들면:
@@ -6795,72 +6844,72 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F165" s="19" t="inlineStr">
+      <c r="F166" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G165" s="18" t="inlineStr">
+      <c r="G166" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H165" s="18" t="inlineStr">
+      <c r="H166" s="18" t="inlineStr">
         <is>
           <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
         </is>
       </c>
-      <c r="I165" s="18" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="9" t="n"/>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="I166" s="18" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="n"/>
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>23. 오늘의 타겟 목록</t>
         </is>
       </c>
-      <c r="C166" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="D166" s="12" t="inlineStr">
-        <is>
-          <t>오늘 누구부터 봐야 해?</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
-        </is>
-      </c>
-      <c r="F166" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G166" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
-        </is>
-      </c>
-      <c r="I166" s="6" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="10" t="n"/>
-      <c r="B167" s="10" t="n"/>
       <c r="C167" s="4" t="n">
         <v>166</v>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
+          <t>오늘 누구부터 봐야 해?</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
+        </is>
+      </c>
+      <c r="F167" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="n"/>
+      <c r="B168" s="10" t="n"/>
+      <c r="C168" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
           <t>타겟 목록에 고객번호도 같이 넣어줘</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E168" s="6" t="inlineStr">
         <is>
           <t>요청하신 타겟 목록의 고객번호는 현재 자료에 없어요. 2026년 9월 29일 기준 타겟 목록에 있는 고객들의 선정 사유와 순서를 안내해 드릴게요.
 - 윤가영 — 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원, 디폴트옵션 미설정
@@ -6876,43 +6925,43 @@
 - 한지우 — ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원</t>
         </is>
       </c>
-      <c r="F167" s="14" t="inlineStr">
+      <c r="F168" s="14" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G167" s="6" t="inlineStr">
+      <c r="G168" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H167" s="6" t="inlineStr">
+      <c r="H168" s="6" t="inlineStr">
         <is>
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
-      <c r="I167" s="6" t="inlineStr"/>
-    </row>
-    <row r="168" hidden="1">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" hidden="1">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Ⅴ. 품질 — 시연엔 안 올려도 보는 것</t>
         </is>
       </c>
-      <c r="B168" s="15" t="inlineStr">
+      <c r="B169" s="15" t="inlineStr">
         <is>
           <t>24. 도구 경계 혼동</t>
         </is>
       </c>
-      <c r="C168" s="16" t="n">
-        <v>167</v>
-      </c>
-      <c r="D168" s="17" t="inlineStr">
+      <c r="C169" s="16" t="n">
+        <v>168</v>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 무슨 상품 추천해주지?</t>
         </is>
       </c>
-      <c r="E168" s="18" t="inlineStr">
+      <c r="E169" s="18" t="inlineStr">
         <is>
           <t>투자성향이 위험중립형인 이 고객에게는 적합성 허용 상한이 보통위험까지이므로, 그에 맞는 상품들을 확인하고 안내해 드리는 것이 핵심이에요. 이 고객의 적합성 허용 상한은 보통위험이며, 안내할 수 있는 상품 목록은 다음과 같아요.
 - KB 글로벌채권인덱스 C-P — 보통위험, 최근 1년 4.8%, 채권형
@@ -6926,35 +6975,35 @@
 안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 허용 상한을 초과하여 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F168" s="20" t="inlineStr">
+      <c r="F169" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="G168" s="18" t="inlineStr">
+      <c r="G169" s="18" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H168" s="18" t="inlineStr">
+      <c r="H169" s="18" t="inlineStr">
         <is>
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
-      <c r="I168" s="18" t="inlineStr"/>
-    </row>
-    <row r="169" hidden="1">
-      <c r="A169" s="9" t="n"/>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="D169" s="17" t="inlineStr">
+      <c r="I169" s="18" t="inlineStr"/>
+    </row>
+    <row r="170" hidden="1">
+      <c r="A170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="16" t="n">
+        <v>169</v>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
         <is>
           <t>국고채 금리 어때?</t>
         </is>
       </c>
-      <c r="E169" s="18" t="inlineStr">
+      <c r="E170" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 3주차 기준 국고채 금리는 국고채3년물과 국고채10년물의 변동 추이를 살펴보아야 해요. 2026년 8월 14일 종가 기준으로 국고채3년물은 3.795, 국고채10년물은 4.31로 나타나 있어요. 
 - KOSPI — 6977.94 (+11.5%)
@@ -6985,35 +7034,35 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F169" s="19" t="inlineStr">
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G169" s="18" t="inlineStr">
+      <c r="G170" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H169" s="18" t="inlineStr">
+      <c r="H170" s="18" t="inlineStr">
         <is>
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I169" s="18" t="inlineStr"/>
-    </row>
-    <row r="170" hidden="1">
-      <c r="A170" s="9" t="n"/>
-      <c r="B170" s="9" t="n"/>
-      <c r="C170" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="D170" s="17" t="inlineStr">
+      <c r="I170" s="18" t="inlineStr"/>
+    </row>
+    <row r="171" hidden="1">
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="16" t="n">
+        <v>170</v>
+      </c>
+      <c r="D171" s="17" t="inlineStr">
         <is>
           <t>8월 추천펀드 뭐야?</t>
         </is>
       </c>
-      <c r="E170" s="18" t="inlineStr">
+      <c r="E171" s="18" t="inlineStr">
         <is>
           <t>2026년 8월 기준 퇴직연금 추천펀드(디폴트옵션)로는 위험도에 따라 초저위험 지켜드림, 저위험 알파드림·알파드림 II·알파드림 III, 중위험 뿔려드림·뿔려드림 II·뿔려드림 III, 고위험 모두드림·모두드림 II·모두드림 III 같은 상품들이 있어요. 2026년 8월 기준(수익률은 2026년 7월 30일 기준, 원리금보장 금리는 2026년 8월 기준)으로 각 포트폴리오의 구성과 1년 수익률을 살펴보면 다음과 같아요.
 - 지켜드림 — 초저위험, 신한·기업·하나은행 정기예금(3년) 등으로 구성, 1년 수익률 미표시
@@ -7031,59 +7080,22 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="F170" s="19" t="inlineStr">
+      <c r="F171" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G170" s="18" t="inlineStr">
+      <c r="G171" s="18" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H170" s="18" t="inlineStr">
+      <c r="H171" s="18" t="inlineStr">
         <is>
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="I170" s="18" t="inlineStr"/>
-    </row>
-    <row r="171" hidden="1">
-      <c r="A171" s="9" t="n"/>
-      <c r="B171" s="9" t="n"/>
-      <c r="C171" s="16" t="n">
-        <v>170</v>
-      </c>
-      <c r="D171" s="17" t="inlineStr">
-        <is>
-          <t>대화 내용 요약해줘</t>
-        </is>
-      </c>
-      <c r="E171" s="18" t="inlineStr">
-        <is>
-          <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
-        </is>
-      </c>
-      <c r="F171" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · 시연본</t>
-        </is>
-      </c>
-      <c r="G171" s="18" t="inlineStr">
-        <is>
-          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H171" s="18" t="inlineStr">
-        <is>
-          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
-        </is>
-      </c>
-      <c r="I171" s="18" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상으로 떴어?</t>
-        </is>
-      </c>
+      <c r="I171" s="18" t="inlineStr"/>
     </row>
     <row r="172" hidden="1">
       <c r="A172" s="9" t="n"/>
@@ -7093,17 +7105,17 @@
       </c>
       <c r="D172" s="17" t="inlineStr">
         <is>
-          <t>지난번엔 무슨 얘기 했지?</t>
+          <t>대화 내용 요약해줘</t>
         </is>
       </c>
       <c r="E172" s="18" t="inlineStr">
         <is>
-          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
+          <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
         </is>
       </c>
       <c r="F172" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 대본</t>
+          <t>○ 예비 · 시연본</t>
         </is>
       </c>
       <c r="G172" s="18" t="inlineStr">
@@ -7113,10 +7125,14 @@
       </c>
       <c r="H172" s="18" t="inlineStr">
         <is>
-          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
-        </is>
-      </c>
-      <c r="I172" s="18" t="inlineStr"/>
+          <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
+        </is>
+      </c>
+      <c r="I172" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 왜 관리 대상으로 떴어?</t>
+        </is>
+      </c>
     </row>
     <row r="173" hidden="1">
       <c r="A173" s="9" t="n"/>
@@ -7126,28 +7142,27 @@
       </c>
       <c r="D173" s="17" t="inlineStr">
         <is>
-          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
+          <t>지난번엔 무슨 얘기 했지?</t>
         </is>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
-자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
-        </is>
-      </c>
-      <c r="F173" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 대본</t>
         </is>
       </c>
       <c r="G173" s="18" t="inlineStr">
         <is>
-          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
+          <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
       <c r="H173" s="18" t="inlineStr">
         <is>
-          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
+          <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
       <c r="I173" s="18" t="inlineStr"/>
@@ -7160,27 +7175,28 @@
       </c>
       <c r="D174" s="17" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
+          <t>세액공제 한도가 얼마고, 이 고객 300만원 더 넣으면 얼마 받아?</t>
         </is>
       </c>
       <c r="E174" s="18" t="inlineStr">
         <is>
-          <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
-        </is>
-      </c>
-      <c r="F174" s="21" t="inlineStr">
-        <is>
-          <t>○ 예비 · QA</t>
+          <t>이수민 고객의 개인형IRP 계좌에 300만원을 추가 납입할 때 받을 수 있는 세액공제 환급 예상액은 원장의 총급여 구간에 따라 달라져요. 
+자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
+        </is>
+      </c>
+      <c r="F174" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G174" s="18" t="inlineStr">
         <is>
-          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
+          <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
       <c r="H174" s="18" t="inlineStr">
         <is>
-          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
+          <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
       <c r="I174" s="18" t="inlineStr"/>
@@ -7193,49 +7209,45 @@
       </c>
       <c r="D175" s="17" t="inlineStr">
         <is>
-          <t>좀 더 짧게 줄여줘</t>
+          <t>디폴트옵션 등록 어떻게 하는지랑 화면번호, 고객이 앱에서 할 수 있는지 다 알려줘</t>
         </is>
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
+          <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
       <c r="F175" s="21" t="inlineStr">
         <is>
-          <t>○ 예비 · 케이스</t>
+          <t>○ 예비 · QA</t>
         </is>
       </c>
       <c r="G175" s="18" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
       <c r="H175" s="18" t="inlineStr">
         <is>
-          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
-        </is>
-      </c>
-      <c r="I175" s="18" t="inlineStr">
-        <is>
-          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
-        </is>
-      </c>
+          <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="inlineStr"/>
     </row>
     <row r="176" hidden="1">
       <c r="A176" s="9" t="n"/>
-      <c r="B176" s="10" t="n"/>
+      <c r="B176" s="9" t="n"/>
       <c r="C176" s="16" t="n">
         <v>175</v>
       </c>
       <c r="D176" s="17" t="inlineStr">
         <is>
-          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
+          <t>좀 더 짧게 줄여줘</t>
         </is>
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
+          <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
       <c r="F176" s="21" t="inlineStr">
@@ -7250,81 +7262,83 @@
       </c>
       <c r="H176" s="18" t="inlineStr">
         <is>
-          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
-        </is>
-      </c>
-      <c r="I176" s="18" t="inlineStr"/>
+          <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
+        </is>
+      </c>
+      <c r="I176" s="18" t="inlineStr">
+        <is>
+          <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
+        </is>
+      </c>
     </row>
     <row r="177" hidden="1">
       <c r="A177" s="9" t="n"/>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B177" s="10" t="n"/>
+      <c r="C177" s="16" t="n">
+        <v>176</v>
+      </c>
+      <c r="D177" s="17" t="inlineStr">
+        <is>
+          <t>이 고객은 왜 관리 대상으로 뜬 거야?</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
+        </is>
+      </c>
+      <c r="F177" s="21" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="inlineStr">
+        <is>
+          <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
+        </is>
+      </c>
+      <c r="I177" s="18" t="inlineStr"/>
+    </row>
+    <row r="178" hidden="1">
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="D177" s="12" t="inlineStr">
+      <c r="C178" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
         <is>
           <t>퇴직연금이랑 부동산 투자 중에 뭐가 나은지 비교해줘</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E178" s="6" t="inlineStr">
         <is>
           <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
 찾아본 곳: 상담 화법 「퇴직연금과 부동산 투자 비교 설명 및 설득 화법」 · 시황 자료 「퇴직연금과 부동산 투자 시장 현황 및 비교」 · 운용 상품 자료 「퇴직연금과 부동산 투자 비교」 · 관리 방법론 「퇴직연금과 부동산 투자 비교 판단 기준 및 장단점」
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="F177" s="11" t="inlineStr">
+      <c r="F178" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr">
+      <c r="G178" s="6" t="inlineStr">
         <is>
           <t>고객 없이</t>
         </is>
       </c>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
-        </is>
-      </c>
-      <c r="I177" s="6" t="inlineStr"/>
-    </row>
-    <row r="178" hidden="1">
-      <c r="A178" s="9" t="n"/>
-      <c r="B178" s="9" t="n"/>
-      <c r="C178" s="4" t="n">
-        <v>177</v>
-      </c>
-      <c r="D178" s="12" t="inlineStr">
-        <is>
-          <t>이 고객 평가금액 얼마야?</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
-찾아본 곳: 제도·상품 수치 「고객 평가금액」
-다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
-        </is>
-      </c>
-      <c r="F178" s="14" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
         </is>
       </c>
       <c r="I178" s="6" t="inlineStr"/>
@@ -7337,17 +7351,19 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>IRP 중도인출 사유가 뭐야?</t>
+          <t>이 고객 평가금액 얼마야?</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
-        </is>
-      </c>
-      <c r="F179" s="13" t="inlineStr">
-        <is>
-          <t>○ 예비 · 케이스</t>
+          <t>죄송해요, 그 질문에 쓸 근거는 제가 가진 지식베이스에서 찾지 못했어요. 제가 가진 자료는 화법·제도 수치·업무 절차·단말 화면번호·비대면 채널 경로·고객군 정의·관리 방법론·현장 관찰이고, 고객 개별 정보와 지난 상담 기록은 브리핑 화면이 열려 있을 때만 볼 수 있어요.
+찾아본 곳: 제도·상품 수치 「고객 평가금액」
+다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
+        </is>
+      </c>
+      <c r="F179" s="14" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr">
@@ -7357,7 +7373,7 @@
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
+          <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr"/>
@@ -7370,12 +7386,12 @@
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>이 고객은 왜 타겟이 됐지?</t>
+          <t>IRP 중도인출 사유가 뭐야?</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
+          <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
         </is>
       </c>
       <c r="F180" s="13" t="inlineStr">
@@ -7385,12 +7401,12 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
+          <t>고객 없이</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
+          <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
         </is>
       </c>
       <c r="I180" s="6" t="inlineStr"/>
@@ -7403,10 +7419,43 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
+          <t>이 고객은 왜 타겟이 됐지?</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
+        </is>
+      </c>
+      <c r="F181" s="13" t="inlineStr">
+        <is>
+          <t>○ 예비 · 케이스</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182" hidden="1">
+      <c r="A182" s="9" t="n"/>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
           <t>이 고객 전반적으로 다 정리해서 알려줘</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>송도윤 고객님은 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 크게 상회하고 있지만, 6개월 이상 장기 미접촉 상태인 관리 사각지대 고객이에요. 현재 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식을 보유하고 계시며, 고유계정대 2억 8,000만원의 현금성자산이 방치되어 있고, 디폴트옵션 미설정 및 ISA 만기자금 1억 2,000만원을 보유하고 계셔요.
 - 고유계정대 — 2억 8,000만원 (수익률 0.0%)
@@ -7416,72 +7465,72 @@
 장기간 접촉 이력이 없어 타사 비교에 노출될 가능성이 있으므로, 유선 접촉을 통해 관계를 회복해야 합니다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 사용계획이 있는 자금은 먼저 걸러내며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="F181" s="14" t="inlineStr">
+      <c r="F182" s="14" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="G181" s="6" t="inlineStr">
+      <c r="G182" s="6" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H181" s="6" t="inlineStr">
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr"/>
-    </row>
-    <row r="182" hidden="1">
-      <c r="A182" s="9" t="n"/>
-      <c r="B182" s="10" t="n"/>
-      <c r="C182" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="D182" s="12" t="inlineStr">
-        <is>
-          <t>(고객 연 직후 첫 질문)</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr"/>
-      <c r="F182" s="14" t="inlineStr">
-        <is>
-          <t>– 디버깅용 · 신규</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr">
-        <is>
-          <t>누구나 — 예: 송도윤 188406-7352194</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
-        </is>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
-        </is>
-      </c>
+      <c r="I182" s="6" t="inlineStr"/>
     </row>
     <row r="183" hidden="1">
       <c r="A183" s="9" t="n"/>
-      <c r="B183" s="15" t="inlineStr">
+      <c r="B183" s="10" t="n"/>
+      <c r="C183" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>(고객 연 직후 첫 질문)</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr"/>
+      <c r="F183" s="14" t="inlineStr">
+        <is>
+          <t>– 디버깅용 · 신규</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>누구나 — 예: 송도윤 188406-7352194</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" hidden="1">
+      <c r="A184" s="9" t="n"/>
+      <c r="B184" s="15" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
         </is>
       </c>
-      <c r="C183" s="16" t="n">
-        <v>182</v>
-      </c>
-      <c r="D183" s="17" t="inlineStr">
+      <c r="C184" s="16" t="n">
+        <v>183</v>
+      </c>
+      <c r="D184" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 권할 수 있어?</t>
         </is>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E184" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 ■ 제가 도와드릴 수 있는 것
@@ -7523,55 +7572,19 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
+      <c r="F184" s="20" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="G183" s="18" t="inlineStr">
+      <c r="G184" s="18" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="H183" s="18" t="inlineStr">
+      <c r="H184" s="18" t="inlineStr">
         <is>
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
-        </is>
-      </c>
-      <c r="I183" s="18" t="inlineStr"/>
-    </row>
-    <row r="184" hidden="1">
-      <c r="A184" s="9" t="n"/>
-      <c r="B184" s="9" t="n"/>
-      <c r="C184" s="16" t="n">
-        <v>183</v>
-      </c>
-      <c r="D184" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 디폴트옵션 설정돼 있어?</t>
-        </is>
-      </c>
-      <c r="E184" s="18" t="inlineStr">
-        <is>
-          <t>● 박정호
-박정호 고객님은 현재 디폴트옵션 설정이 되어 있어요. 다만 이미 디폴트옵션(초저위험)을 등록·보유한 고객은 ⓐ 사전지정운용제도 등록/변경 → ⓑ 보유상품 변경(기존 매도 + 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요. 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 «현재 보유중이신 디폴트옵션(초저위험)은 정기예금만으로 구성되어 있습니다»라고 짚어 주세요.
-● 이수민
-이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
-        </is>
-      </c>
-      <c r="F184" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
-        </is>
-      </c>
-      <c r="G184" s="18" t="inlineStr">
-        <is>
-          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
-        </is>
-      </c>
-      <c r="H184" s="18" t="inlineStr">
-        <is>
-          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
       <c r="I184" s="18" t="inlineStr"/>
@@ -7584,10 +7597,46 @@
       </c>
       <c r="D185" s="17" t="inlineStr">
         <is>
+          <t>이 고객 디폴트옵션 설정돼 있어?</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>● 박정호
+박정호 고객님은 현재 디폴트옵션 설정이 되어 있어요. 다만 이미 디폴트옵션(초저위험)을 등록·보유한 고객은 ⓐ 사전지정운용제도 등록/변경 → ⓑ 보유상품 변경(기존 매도 + 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요. 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 «현재 보유중이신 디폴트옵션(초저위험)은 정기예금만으로 구성되어 있습니다»라고 짚어 주세요.
+● 이수민
+이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
+        </is>
+      </c>
+      <c r="F185" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
+        </is>
+      </c>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
+        </is>
+      </c>
+      <c r="H185" s="18" t="inlineStr">
+        <is>
+          <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
+        </is>
+      </c>
+      <c r="I185" s="18" t="inlineStr"/>
+    </row>
+    <row r="186" hidden="1">
+      <c r="A186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="16" t="n">
+        <v>185</v>
+      </c>
+      <c r="D186" s="17" t="inlineStr">
+        <is>
           <t>이 고객 만기 뭐뭐 있어?</t>
         </is>
       </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="E186" s="18" t="inlineStr">
         <is>
           <t>● 오세훈
 만기 도래 항목을 묻는 질문에 대해, 현재 2026년 10월 9일에 만기가 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품이 있어요. 그리고 2027년 1-10에 만기가 도래하는 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 3,550만원 상품이 있습니다.
@@ -7598,55 +7647,19 @@
 송도윤 고객님의 만기 내역은 2026년 9월 20일에 만기가 경과한 ISA 만기자금(IRP 외부) 1억 2,000만원이 있어요. 원장에 등록된 만기 항목은 해당 건이 전부이며, 다른 만기 건은 자료에 없어요.</t>
         </is>
       </c>
-      <c r="F185" s="23" t="inlineStr">
+      <c r="F186" s="23" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="G185" s="18" t="inlineStr">
+      <c r="G186" s="18" t="inlineStr">
         <is>
           <t>오세훈2 193482-6012375 ↔ 이수민1 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H185" s="18" t="inlineStr">
+      <c r="H186" s="18" t="inlineStr">
         <is>
           <t>0건은 「없다」, 2건은 둘 다 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
-        </is>
-      </c>
-      <c r="I185" s="18" t="inlineStr"/>
-    </row>
-    <row r="186" hidden="1">
-      <c r="A186" s="9" t="n"/>
-      <c r="B186" s="9" t="n"/>
-      <c r="C186" s="16" t="n">
-        <v>185</v>
-      </c>
-      <c r="D186" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 왜 관리 대상이야?</t>
-        </is>
-      </c>
-      <c r="E186" s="18" t="inlineStr">
-        <is>
-          <t>● 송도윤
-송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 및 환매추천 펀드인 KB 퇴직연금 배당 (주식)을 보유하고 계시고, 미운용 현금성자산이 있으며, 디폴트옵션이 미설정 상태이고, ISA 만기자금 보유와 운용변경이 12개월 이상 없었기 때문이에요. 추가로 관리 사각지대 고객이자 당해 납입이 없는 고객에 해당하며, 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시고 운용수익률은 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 계세요. 다만 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있는 상태예요.
-● 이준호
-적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
-        </is>
-      </c>
-      <c r="F186" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G186" s="18" t="inlineStr">
-        <is>
-          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
-        </is>
-      </c>
-      <c r="H186" s="18" t="inlineStr">
-        <is>
-          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
       <c r="I186" s="18" t="inlineStr"/>
@@ -7659,15 +7672,15 @@
       </c>
       <c r="D187" s="17" t="inlineStr">
         <is>
-          <t>지난 상담에서 무슨 얘기 했지?</t>
+          <t>이 고객 왜 관리 대상이야?</t>
         </is>
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
-※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담 기록에 따르면, 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 있어요.
-● 김서연
-고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
+송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 및 환매추천 펀드인 KB 퇴직연금 배당 (주식)을 보유하고 계시고, 미운용 현금성자산이 있으며, 디폴트옵션이 미설정 상태이고, ISA 만기자금 보유와 운용변경이 12개월 이상 없었기 때문이에요. 추가로 관리 사각지대 고객이자 당해 납입이 없는 고객에 해당하며, 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시고 운용수익률은 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 계세요. 다만 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있는 상태예요.
+● 이준호
+적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
         </is>
       </c>
       <c r="F187" s="19" t="inlineStr">
@@ -7677,12 +7690,12 @@
       </c>
       <c r="G187" s="18" t="inlineStr">
         <is>
-          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
+          <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
       <c r="H187" s="18" t="inlineStr">
         <is>
-          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
+          <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
       <c r="I187" s="18" t="inlineStr"/>
@@ -7695,10 +7708,46 @@
       </c>
       <c r="D188" s="17" t="inlineStr">
         <is>
+          <t>지난 상담에서 무슨 얘기 했지?</t>
+        </is>
+      </c>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>● 송도윤
+※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담 기록에 따르면, 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 있어요.
+● 김서연
+고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
+        </is>
+      </c>
+      <c r="H188" s="18" t="inlineStr">
+        <is>
+          <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
+        </is>
+      </c>
+      <c r="I188" s="18" t="inlineStr"/>
+    </row>
+    <row r="189" hidden="1">
+      <c r="A189" s="9" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
+        <is>
           <t>300만원 더 넣으면 얼마 돌려받아?</t>
         </is>
       </c>
-      <c r="E188" s="18" t="inlineStr">
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>● 이수민
 이수민 고객에게 개인형IRP 계좌에 300만원을 추가 납입할 때 예상되는 세액공제 환급액을 안내할 때는 총급여 구간과 세액공제 한도를 함께 짚어주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 한도 및 잔여한도가 900만원이므로, 300만원을 추가 납입하면 총급여 5,500만원 이하 기준 16.5%의 공제율을 적용하여 495,000원의 환급을 예상할 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 이를 바탕으로 안내해 보세요.
@@ -7707,55 +7756,19 @@
 다만 ISA 만기자금을 개인형IRP 계좌로 전환하는 경우라면 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 별개의 축이에요. 300만원을 ISA 만기자금에서 개인형IRP로 전환할 때 적용되는 공제율에 따라 추가 공제 대상과 환급액이 달라질 수 있어요. 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 49,500원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않았으니 단말에서 고객의 총급여 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="F188" s="19" t="inlineStr">
+      <c r="F189" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G188" s="18" t="inlineStr">
+      <c r="G189" s="18" t="inlineStr">
         <is>
           <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="H188" s="18" t="inlineStr">
+      <c r="H189" s="18" t="inlineStr">
         <is>
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
-        </is>
-      </c>
-      <c r="I188" s="18" t="inlineStr"/>
-    </row>
-    <row r="189" hidden="1">
-      <c r="A189" s="9" t="n"/>
-      <c r="B189" s="9" t="n"/>
-      <c r="C189" s="16" t="n">
-        <v>188</v>
-      </c>
-      <c r="D189" s="17" t="inlineStr">
-        <is>
-          <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
-        </is>
-      </c>
-      <c r="E189" s="18" t="inlineStr">
-        <is>
-          <t>● 박지민
-고객의 소득 수준이나 종합소득금액 값이 자료에 나와 있지 않아 해당 고객의 세액공제율을 바로 확정해 말씀드리기는 어려워요. 2026년 6월 기준 자료에 따르면, 공제율은 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 경우 16.5%, 이를 초과하는 경우 13.2%가 적용돼요. 여기서 5,500만원 '이상'이 아니라 '초과'가 정확한 경계 표현이며, 5,500만원 정확히 일치하는 금액은 16.5% 구간에 해당한다는 점을 참고해 주세요. 단말에서 고객의 소득 조건을 먼저 확인하신 뒤에 안내를 이어가셔야 해요.
-● 한지우
-총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
-        </is>
-      </c>
-      <c r="F189" s="23" t="inlineStr">
-        <is>
-          <t>◎ 1순위 · 신규</t>
-        </is>
-      </c>
-      <c r="G189" s="18" t="inlineStr">
-        <is>
-          <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
-        </is>
-      </c>
-      <c r="H189" s="18" t="inlineStr">
-        <is>
-          <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
         </is>
       </c>
       <c r="I189" s="18" t="inlineStr"/>
@@ -7768,30 +7781,30 @@
       </c>
       <c r="D190" s="17" t="inlineStr">
         <is>
-          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
+          <t>이 고객 세액공제율 몇 퍼센트 적용돼?</t>
         </is>
       </c>
       <c r="E190" s="18" t="inlineStr">
         <is>
-          <t>● 김서연
-ISA 만기자금을 IRP로 옮겨 세액공제 혜택을 확인하는 고객에게는 만기금액의 전환에 따른 추가 공제 구조를 짚어 드리는 게 핵심이에요. 개인형IRP 계좌로 8,000만원을 전환할 때 이 금액은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이라, 8,000만원을 전환하면 추가 공제 대상은 300만원이 돼요. 총급여 5,500만원 이하 16.5% 기준으로 이 전환으로 늘어나는 환급 예상액은 495,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로 서로 다른 한도예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
-● 박지민
-ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
-        </is>
-      </c>
-      <c r="F190" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
+          <t>● 박지민
+고객의 소득 수준이나 종합소득금액 값이 자료에 나와 있지 않아 해당 고객의 세액공제율을 바로 확정해 말씀드리기는 어려워요. 2026년 6월 기준 자료에 따르면, 공제율은 총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 경우 16.5%, 이를 초과하는 경우 13.2%가 적용돼요. 여기서 5,500만원 '이상'이 아니라 '초과'가 정확한 경계 표현이며, 5,500만원 정확히 일치하는 금액은 16.5% 구간에 해당한다는 점을 참고해 주세요. 단말에서 고객의 소득 조건을 먼저 확인하신 뒤에 안내를 이어가셔야 해요.
+● 한지우
+총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
+        </is>
+      </c>
+      <c r="F190" s="23" t="inlineStr">
+        <is>
+          <t>◎ 1순위 · 신규</t>
         </is>
       </c>
       <c r="G190" s="18" t="inlineStr">
         <is>
-          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
+          <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
         </is>
       </c>
       <c r="H190" s="18" t="inlineStr">
         <is>
-          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
+          <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
         </is>
       </c>
       <c r="I190" s="18" t="inlineStr"/>
@@ -7804,10 +7817,46 @@
       </c>
       <c r="D191" s="17" t="inlineStr">
         <is>
+          <t>ISA 만기자금 IRP로 옮기면 세액공제 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="E191" s="18" t="inlineStr">
+        <is>
+          <t>● 김서연
+ISA 만기자금을 IRP로 옮겨 세액공제 혜택을 확인하는 고객에게는 만기금액의 전환에 따른 추가 공제 구조를 짚어 드리는 게 핵심이에요. 개인형IRP 계좌로 8,000만원을 전환할 때 이 금액은 연 납입한도 1,800만원과 무관하게 만기일로부터 60일 이내에 넣을 수 있어요. 전환액의 10%가 세액공제 대상에 더해지는데 상한이 300만원이라, 8,000만원을 전환하면 추가 공제 대상은 300만원이 돼요. 총급여 5,500만원 이하 16.5% 기준으로 이 전환으로 늘어나는 환급 예상액은 495,000원이에요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫으로 서로 다른 한도예요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 박지민
+ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
+        </is>
+      </c>
+      <c r="F191" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G191" s="18" t="inlineStr">
+        <is>
+          <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
+        </is>
+      </c>
+      <c r="H191" s="18" t="inlineStr">
+        <is>
+          <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
+        </is>
+      </c>
+      <c r="I191" s="18" t="inlineStr"/>
+    </row>
+    <row r="192" hidden="1">
+      <c r="A192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="16" t="n">
+        <v>191</v>
+      </c>
+      <c r="D192" s="17" t="inlineStr">
+        <is>
           <t>이 고객 연금개시 할 수 있어?</t>
         </is>
       </c>
-      <c r="E191" s="18" t="inlineStr">
+      <c r="E192" s="18" t="inlineStr">
         <is>
           <t>● 박정호
 박정호 고객님은 연금개시 요건을 충족하였으나 아직 연금개시를 하지 않은 상태예요. 
@@ -7816,55 +7865,19 @@
 송도윤 고객님은 연금개시요건을 충족하지 않아 현재 연금개시를 하실 수 없어요. 자료에 따르면 연금개시 상태는 미개시이며 연금개시요건도 충족되지 않은 상태로 확인돼요.</t>
         </is>
       </c>
-      <c r="F191" s="19" t="inlineStr">
+      <c r="F192" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G191" s="18" t="inlineStr">
+      <c r="G192" s="18" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="H191" s="18" t="inlineStr">
+      <c r="H192" s="18" t="inlineStr">
         <is>
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
-        </is>
-      </c>
-      <c r="I191" s="18" t="inlineStr"/>
-    </row>
-    <row r="192" hidden="1">
-      <c r="A192" s="9" t="n"/>
-      <c r="B192" s="9" t="n"/>
-      <c r="C192" s="16" t="n">
-        <v>191</v>
-      </c>
-      <c r="D192" s="17" t="inlineStr">
-        <is>
-          <t>판매중단된 펀드 뭐 들고 있어?</t>
-        </is>
-      </c>
-      <c r="E192" s="18" t="inlineStr">
-        <is>
-          <t>● 최서윤
-최서윤 고객이 보유하고 있는 판매중단 상품은 KB 코리아밸류업액티브(주식)이다. 해당 상품은 920만원 규모로 보유 중이며 수익률은 -38.7%를 기록하고 있다. 판매중단 상품을 보유하고 있어 관리 공백이 우려되는 상황이므로, 보유 포트폴리오를 점검하고 매도 및 재추천 등의 액션을 안내하는 방향으로 접근해야 한다.
-● 박지민
-판매중단된 보유상품은 없어요.</t>
-        </is>
-      </c>
-      <c r="F192" s="19" t="inlineStr">
-        <is>
-          <t>○ 예비 · 신규</t>
-        </is>
-      </c>
-      <c r="G192" s="18" t="inlineStr">
-        <is>
-          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
-        </is>
-      </c>
-      <c r="H192" s="18" t="inlineStr">
-        <is>
-          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
       <c r="I192" s="18" t="inlineStr"/>
@@ -7877,10 +7890,46 @@
       </c>
       <c r="D193" s="17" t="inlineStr">
         <is>
+          <t>판매중단된 펀드 뭐 들고 있어?</t>
+        </is>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>● 최서윤
+최서윤 고객이 보유하고 있는 판매중단 상품은 KB 코리아밸류업액티브(주식)이다. 해당 상품은 920만원 규모로 보유 중이며 수익률은 -38.7%를 기록하고 있다. 판매중단 상품을 보유하고 있어 관리 공백이 우려되는 상황이므로, 보유 포트폴리오를 점검하고 매도 및 재추천 등의 액션을 안내하는 방향으로 접근해야 한다.
+● 박지민
+판매중단된 보유상품은 없어요.</t>
+        </is>
+      </c>
+      <c r="F193" s="19" t="inlineStr">
+        <is>
+          <t>○ 예비 · 신규</t>
+        </is>
+      </c>
+      <c r="G193" s="18" t="inlineStr">
+        <is>
+          <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
+        </is>
+      </c>
+      <c r="H193" s="18" t="inlineStr">
+        <is>
+          <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
+        </is>
+      </c>
+      <c r="I193" s="18" t="inlineStr"/>
+    </row>
+    <row r="194" hidden="1">
+      <c r="A194" s="9" t="n"/>
+      <c r="B194" s="9" t="n"/>
+      <c r="C194" s="16" t="n">
+        <v>193</v>
+      </c>
+      <c r="D194" s="17" t="inlineStr">
+        <is>
           <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
         </is>
       </c>
-      <c r="E193" s="18" t="inlineStr">
+      <c r="E194" s="18" t="inlineStr">
         <is>
           <t>● 정민석
 현재 보유한 자산이 예금 위주인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가는 게 핵심이에요. 원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 입증해야 하므로, 금리 갈아타기가 곧 관리라는 논리로 대응해 보세요. 다만 사용계획이 있는 자금은 먼저 걸러내고, 고객에게 생소한 고유계정대 같은 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 고객이 예금만 해서 관리가 필요 없다고 반응할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
@@ -7888,35 +7937,35 @@
 예금만 보유하고 있어 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 점을 짚어주는 게 핵심이에요. 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 같은 안전성 안에서 금리를 올려주는 제안으로 들어가야 해요. 고객이 사용계획이 있는 자금인지 먼저 확인하고, 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="F193" s="19" t="inlineStr">
+      <c r="F194" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G193" s="18" t="inlineStr">
+      <c r="G194" s="18" t="inlineStr">
         <is>
           <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="H193" s="18" t="inlineStr">
+      <c r="H194" s="18" t="inlineStr">
         <is>
           <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
         </is>
       </c>
-      <c r="I193" s="18" t="inlineStr"/>
-    </row>
-    <row r="194" hidden="1">
-      <c r="A194" s="10" t="n"/>
-      <c r="B194" s="10" t="n"/>
-      <c r="C194" s="16" t="n">
-        <v>193</v>
-      </c>
-      <c r="D194" s="17" t="inlineStr">
+      <c r="I194" s="18" t="inlineStr"/>
+    </row>
+    <row r="195" hidden="1">
+      <c r="A195" s="10" t="n"/>
+      <c r="B195" s="10" t="n"/>
+      <c r="C195" s="16" t="n">
+        <v>194</v>
+      </c>
+      <c r="D195" s="17" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 세미나 있어?</t>
         </is>
       </c>
-      <c r="E194" s="18" t="inlineStr">
+      <c r="E195" s="18" t="inlineStr">
         <is>
           <t>● 송도윤
 송도윤 고객에게는 지금 안내할 수 있는 세미나로 11/5(목) 16시에 진행되는 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 온라인 세미나가 있어요. 이 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어, 미운용 자금 및 디폴트옵션 제도를 다루는 해당 세미나를 안내합니다. 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX를 활용하시면 돼요. 고객에게 안내하실 때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 사용계획이 있는 자금이라면 먼저 걸러내고 접근하시는 게 핵심이에요. 참고로 다른 세미나 후보 4건인 연금개시 전 꼭 알아야 할 IRP 수령 방법, 예금만으로 괜찮을까? 퇴직연금 자산배분 전략, 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기, 금리 변화기, 퇴직연금 예금 만기 이후 운용 전략에 대해서는 아직 상세 안내 자료가 없어요.
@@ -7924,60 +7973,60 @@
 이 고객에게는 지금 요건에 맞는 안내 대상 세미나가 없어요. 다만 현재 열려 있는 세미나 중 날짜가 가장 가까운 것은 11/12(목) 17시에 KB국민은행 WM투자부에서 주관하는 «내 투자성향에 맞는 포트폴리오 찾기»예요. 이 콘텐츠는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋으나 이 고객의 요건과는 무관해요. 안내 시 참고할 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요. 다른 이벤트나 세미나 관련해서 다른 후보 콘텐츠들에 대한 상세 요건은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="F194" s="19" t="inlineStr">
+      <c r="F195" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="G194" s="18" t="inlineStr">
+      <c r="G195" s="18" t="inlineStr">
         <is>
           <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="H194" s="18" t="inlineStr">
+      <c r="H195" s="18" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="I194" s="18" t="inlineStr"/>
+      <c r="I195" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B183:B194"/>
-    <mergeCell ref="B34:B40"/>
+    <mergeCell ref="A144:A168"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="A2:A41"/>
+    <mergeCell ref="B164:B166"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B112:B118"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B124:B128"/>
-    <mergeCell ref="B129:B142"/>
-    <mergeCell ref="A41:A93"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="A143:A167"/>
-    <mergeCell ref="B157:B162"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="B168:B176"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="B184:B195"/>
+    <mergeCell ref="A42:A94"/>
+    <mergeCell ref="B76:B82"/>
+    <mergeCell ref="B125:B129"/>
     <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="B75:B81"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A2:A40"/>
-    <mergeCell ref="B143:B148"/>
-    <mergeCell ref="A94:A142"/>
-    <mergeCell ref="B118:B123"/>
-    <mergeCell ref="B149:B153"/>
-    <mergeCell ref="A168:A194"/>
-    <mergeCell ref="B177:B182"/>
+    <mergeCell ref="B169:B177"/>
+    <mergeCell ref="B178:B183"/>
+    <mergeCell ref="B130:B143"/>
+    <mergeCell ref="B119:B124"/>
+    <mergeCell ref="B150:B154"/>
+    <mergeCell ref="B155:B157"/>
+    <mergeCell ref="A169:A195"/>
+    <mergeCell ref="B89:B94"/>
+    <mergeCell ref="B158:B163"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B83:B88"/>
     <mergeCell ref="B18:B26"/>
-    <mergeCell ref="B65:B74"/>
-    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B42:B55"/>
+    <mergeCell ref="B95:B111"/>
     <mergeCell ref="B6:B17"/>
-    <mergeCell ref="B55:B64"/>
-    <mergeCell ref="B94:B110"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A95:A143"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -97,11 +97,18 @@
         <color rgb="00BFA55A"/>
       </top>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00BFA55A"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +542,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J198"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -614,7 +624,7 @@
       </c>
     </row>
     <row r="5" ht="135" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ⅰ. 대상 선정 — 오늘 누구를 보고, 왜 그 사람인가</t>
         </is>
@@ -666,7 +676,6 @@
       <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="11" t="n"/>
       <c r="C6" s="12" t="n">
         <v>2</v>
       </c>
@@ -698,7 +707,6 @@
       <c r="J6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="11" t="n"/>
       <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
@@ -735,7 +743,6 @@
       <c r="J7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="135" customHeight="1">
-      <c r="A8" s="11" t="n"/>
       <c r="C8" s="12" t="n">
         <v>4</v>
       </c>
@@ -778,7 +785,6 @@
       <c r="J8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="11" t="n"/>
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t>2. 고객군·관리 기준</t>
@@ -820,7 +826,6 @@
       <c r="J9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="11" t="n"/>
       <c r="C10" s="12" t="n">
         <v>6</v>
       </c>
@@ -857,7 +862,6 @@
       <c r="J10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="11" t="n"/>
       <c r="C11" s="12" t="n">
         <v>7</v>
       </c>
@@ -896,7 +900,6 @@
       <c r="J11" s="14" t="inlineStr"/>
     </row>
     <row r="12" hidden="1">
-      <c r="A12" s="11" t="n"/>
       <c r="C12" s="12" t="n">
         <v>8</v>
       </c>
@@ -936,7 +939,6 @@
       <c r="J12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="135" customHeight="1">
-      <c r="A13" s="11" t="n"/>
       <c r="C13" s="12" t="n">
         <v>9</v>
       </c>
@@ -973,7 +975,6 @@
       <c r="J13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="11" t="n"/>
       <c r="C14" s="12" t="n">
         <v>10</v>
       </c>
@@ -1010,7 +1011,6 @@
       <c r="J14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="135" customHeight="1">
-      <c r="A15" s="11" t="n"/>
       <c r="B15" s="18" t="inlineStr">
         <is>
           <t>3. 오늘의 타겟 목록</t>
@@ -1052,7 +1052,6 @@
       <c r="J15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="135" customHeight="1">
-      <c r="A16" s="11" t="n"/>
       <c r="C16" s="12" t="n">
         <v>12</v>
       </c>
@@ -1100,7 +1099,7 @@
       <c r="J16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Ⅱ. 고객 상태 — 이 고객이 지금 어떤 상태이고, 조심할 것은 무엇인가</t>
         </is>
@@ -1146,7 +1145,6 @@
       <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="94.5" customHeight="1">
-      <c r="A18" s="11" t="n"/>
       <c r="C18" s="12" t="n">
         <v>14</v>
       </c>
@@ -1186,7 +1184,6 @@
       <c r="J18" s="14" t="inlineStr"/>
     </row>
     <row r="19" hidden="1">
-      <c r="A19" s="11" t="n"/>
       <c r="C19" s="12" t="n">
         <v>15</v>
       </c>
@@ -1223,7 +1220,6 @@
       <c r="J19" s="14" t="inlineStr"/>
     </row>
     <row r="20" hidden="1">
-      <c r="A20" s="11" t="n"/>
       <c r="C20" s="12" t="n">
         <v>16</v>
       </c>
@@ -1260,7 +1256,6 @@
       <c r="J20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="94.5" customHeight="1">
-      <c r="A21" s="11" t="n"/>
       <c r="C21" s="12" t="n">
         <v>17</v>
       </c>
@@ -1300,7 +1295,6 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="81" customHeight="1">
-      <c r="A22" s="11" t="n"/>
       <c r="C22" s="12" t="n">
         <v>18</v>
       </c>
@@ -1340,7 +1334,6 @@
       <c r="J22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="11" t="n"/>
       <c r="C23" s="12" t="n">
         <v>19</v>
       </c>
@@ -1377,7 +1370,6 @@
       <c r="J23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="135" customHeight="1">
-      <c r="A24" s="11" t="n"/>
       <c r="C24" s="12" t="n">
         <v>20</v>
       </c>
@@ -1419,7 +1411,6 @@
       <c r="J24" s="14" t="inlineStr"/>
     </row>
     <row r="25" hidden="1">
-      <c r="A25" s="11" t="n"/>
       <c r="C25" s="12" t="n">
         <v>21</v>
       </c>
@@ -1458,7 +1449,6 @@
       <c r="J25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="11" t="n"/>
       <c r="C26" s="12" t="n">
         <v>22</v>
       </c>
@@ -1495,7 +1485,6 @@
       <c r="J26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="94.5" customHeight="1">
-      <c r="A27" s="11" t="n"/>
       <c r="C27" s="12" t="n">
         <v>23</v>
       </c>
@@ -1533,7 +1522,6 @@
       <c r="J27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="94.5" customHeight="1">
-      <c r="A28" s="11" t="n"/>
       <c r="C28" s="12" t="n">
         <v>24</v>
       </c>
@@ -1573,7 +1561,6 @@
       <c r="J28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="11" t="n"/>
       <c r="B29" s="18" t="inlineStr">
         <is>
           <t>5. 고객 계좌 상태 확인</t>
@@ -1615,7 +1602,6 @@
       <c r="J29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="67.5" customHeight="1">
-      <c r="A30" s="11" t="n"/>
       <c r="C30" s="12" t="n">
         <v>26</v>
       </c>
@@ -1648,7 +1634,6 @@
       <c r="J30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="11" t="n"/>
       <c r="C31" s="12" t="n">
         <v>27</v>
       </c>
@@ -1685,7 +1670,6 @@
       <c r="J31" s="14" t="inlineStr"/>
     </row>
     <row r="32" hidden="1">
-      <c r="A32" s="11" t="n"/>
       <c r="C32" s="12" t="n">
         <v>28</v>
       </c>
@@ -1722,7 +1706,6 @@
       <c r="J32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="121.5" customHeight="1">
-      <c r="A33" s="11" t="n"/>
       <c r="C33" s="12" t="n">
         <v>29</v>
       </c>
@@ -1762,7 +1745,6 @@
       <c r="J33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="11" t="n"/>
       <c r="C34" s="12" t="n">
         <v>30</v>
       </c>
@@ -1794,7 +1776,6 @@
       <c r="J34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="11" t="n"/>
       <c r="C35" s="12" t="n">
         <v>31</v>
       </c>
@@ -1831,7 +1812,6 @@
       <c r="J35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="11" t="n"/>
       <c r="C36" s="12" t="n">
         <v>32</v>
       </c>
@@ -1868,7 +1848,6 @@
       <c r="J36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="11" t="n"/>
       <c r="C37" s="12" t="n">
         <v>33</v>
       </c>
@@ -1905,7 +1884,6 @@
       <c r="J37" s="14" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
-      <c r="A38" s="11" t="n"/>
       <c r="B38" s="18" t="inlineStr">
         <is>
           <t>6. 상담 이력 조회</t>
@@ -1947,7 +1925,6 @@
       <c r="J38" s="14" t="inlineStr"/>
     </row>
     <row r="39" hidden="1">
-      <c r="A39" s="11" t="n"/>
       <c r="C39" s="12" t="n">
         <v>35</v>
       </c>
@@ -1975,7 +1952,6 @@
       <c r="J39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="40.5" customHeight="1">
-      <c r="A40" s="11" t="n"/>
       <c r="C40" s="12" t="n">
         <v>36</v>
       </c>
@@ -2012,7 +1988,6 @@
       <c r="J40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="40.5" customHeight="1">
-      <c r="A41" s="11" t="n"/>
       <c r="C41" s="12" t="n">
         <v>37</v>
       </c>
@@ -2049,7 +2024,6 @@
       <c r="J41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="135" customHeight="1">
-      <c r="A42" s="11" t="n"/>
       <c r="B42" s="18" t="inlineStr">
         <is>
           <t>7. 금지·주의 안내</t>
@@ -2100,7 +2074,6 @@
       <c r="J42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="135" customHeight="1">
-      <c r="A43" s="11" t="n"/>
       <c r="C43" s="12" t="n">
         <v>39</v>
       </c>
@@ -2141,7 +2114,6 @@
       <c r="J43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="54" customHeight="1">
-      <c r="A44" s="11" t="n"/>
       <c r="C44" s="12" t="n">
         <v>40</v>
       </c>
@@ -2178,7 +2150,6 @@
       <c r="J44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="135" customHeight="1">
-      <c r="A45" s="11" t="n"/>
       <c r="C45" s="12" t="n">
         <v>41</v>
       </c>
@@ -2224,7 +2195,6 @@
       <c r="J45" s="14" t="inlineStr"/>
     </row>
     <row r="46" hidden="1">
-      <c r="A46" s="11" t="n"/>
       <c r="C46" s="12" t="n">
         <v>42</v>
       </c>
@@ -2261,7 +2231,6 @@
       <c r="J46" s="14" t="inlineStr"/>
     </row>
     <row r="47" hidden="1">
-      <c r="A47" s="11" t="n"/>
       <c r="C47" s="12" t="n">
         <v>43</v>
       </c>
@@ -2314,7 +2283,6 @@
       <c r="J47" s="14" t="inlineStr"/>
     </row>
     <row r="48" hidden="1">
-      <c r="A48" s="11" t="n"/>
       <c r="C48" s="12" t="n">
         <v>44</v>
       </c>
@@ -2352,7 +2320,6 @@
       <c r="J48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="40.5" customHeight="1">
-      <c r="A49" s="11" t="n"/>
       <c r="C49" s="12" t="n">
         <v>45</v>
       </c>
@@ -2394,7 +2361,6 @@
       </c>
     </row>
     <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="11" t="n"/>
       <c r="B50" s="18" t="inlineStr">
         <is>
           <t>8. 상담 준비 자료</t>
@@ -2436,7 +2402,6 @@
       <c r="J50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="67.5" customHeight="1">
-      <c r="A51" s="11" t="n"/>
       <c r="C51" s="12" t="n">
         <v>47</v>
       </c>
@@ -2473,7 +2438,6 @@
       <c r="J51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="108" customHeight="1">
-      <c r="A52" s="11" t="n"/>
       <c r="C52" s="12" t="n">
         <v>48</v>
       </c>
@@ -2515,7 +2479,7 @@
       </c>
     </row>
     <row r="53" ht="135" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>Ⅲ. 업무 확인 — 제도는 어떻고, 어떻게 처리하고, 몇 번 화면이고, 시장은 어떤가</t>
         </is>
@@ -2567,7 +2531,6 @@
       <c r="J53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="67.5" customHeight="1">
-      <c r="A54" s="11" t="n"/>
       <c r="C54" s="12" t="n">
         <v>50</v>
       </c>
@@ -2604,7 +2567,6 @@
       <c r="J54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="67.5" customHeight="1">
-      <c r="A55" s="11" t="n"/>
       <c r="C55" s="12" t="n">
         <v>51</v>
       </c>
@@ -2641,7 +2603,6 @@
       <c r="J55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="11" t="n"/>
       <c r="C56" s="12" t="n">
         <v>52</v>
       </c>
@@ -2678,7 +2639,6 @@
       <c r="J56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="54" customHeight="1">
-      <c r="A57" s="11" t="n"/>
       <c r="C57" s="12" t="n">
         <v>53</v>
       </c>
@@ -2712,7 +2672,6 @@
       <c r="J57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="81" customHeight="1">
-      <c r="A58" s="11" t="n"/>
       <c r="C58" s="12" t="n">
         <v>54</v>
       </c>
@@ -2750,7 +2709,6 @@
       <c r="J58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="54" customHeight="1">
-      <c r="A59" s="11" t="n"/>
       <c r="C59" s="12" t="n">
         <v>55</v>
       </c>
@@ -2789,7 +2747,6 @@
       <c r="J59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="67.5" customHeight="1">
-      <c r="A60" s="11" t="n"/>
       <c r="C60" s="12" t="n">
         <v>56</v>
       </c>
@@ -2827,7 +2784,6 @@
       <c r="J60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="67.5" customHeight="1">
-      <c r="A61" s="11" t="n"/>
       <c r="C61" s="12" t="n">
         <v>57</v>
       </c>
@@ -2864,7 +2820,6 @@
       <c r="J61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="94.5" customHeight="1">
-      <c r="A62" s="11" t="n"/>
       <c r="C62" s="12" t="n">
         <v>58</v>
       </c>
@@ -2901,7 +2856,6 @@
       <c r="J62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="81" customHeight="1">
-      <c r="A63" s="11" t="n"/>
       <c r="C63" s="12" t="n">
         <v>59</v>
       </c>
@@ -2938,7 +2892,6 @@
       <c r="J63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="40.5" customHeight="1">
-      <c r="A64" s="11" t="n"/>
       <c r="C64" s="12" t="n">
         <v>60</v>
       </c>
@@ -2975,7 +2928,6 @@
       <c r="J64" s="14" t="inlineStr"/>
     </row>
     <row r="65" hidden="1">
-      <c r="A65" s="11" t="n"/>
       <c r="C65" s="12" t="n">
         <v>61</v>
       </c>
@@ -3024,7 +2976,6 @@
       <c r="J65" s="14" t="inlineStr"/>
     </row>
     <row r="66" hidden="1">
-      <c r="A66" s="11" t="n"/>
       <c r="C66" s="12" t="n">
         <v>62</v>
       </c>
@@ -3074,7 +3025,6 @@
       <c r="J66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="135" customHeight="1">
-      <c r="A67" s="11" t="n"/>
       <c r="B67" s="18" t="inlineStr">
         <is>
           <t>10. 업무 처리 절차</t>
@@ -3119,7 +3069,6 @@
       <c r="J67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="54" customHeight="1">
-      <c r="A68" s="11" t="n"/>
       <c r="C68" s="12" t="n">
         <v>64</v>
       </c>
@@ -3158,7 +3107,6 @@
       <c r="J68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="40.5" customHeight="1">
-      <c r="A69" s="11" t="n"/>
       <c r="C69" s="12" t="n">
         <v>65</v>
       </c>
@@ -3195,7 +3143,6 @@
       <c r="J69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="135" customHeight="1">
-      <c r="A70" s="11" t="n"/>
       <c r="C70" s="12" t="n">
         <v>66</v>
       </c>
@@ -3235,7 +3182,6 @@
       <c r="J70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="54" customHeight="1">
-      <c r="A71" s="11" t="n"/>
       <c r="C71" s="12" t="n">
         <v>67</v>
       </c>
@@ -3272,7 +3218,6 @@
       <c r="J71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="11" t="n"/>
       <c r="C72" s="12" t="n">
         <v>68</v>
       </c>
@@ -3309,7 +3254,6 @@
       <c r="J72" s="14" t="inlineStr"/>
     </row>
     <row r="73" hidden="1">
-      <c r="A73" s="11" t="n"/>
       <c r="C73" s="12" t="n">
         <v>69</v>
       </c>
@@ -3347,7 +3291,6 @@
       <c r="J73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="40.5" customHeight="1">
-      <c r="A74" s="11" t="n"/>
       <c r="C74" s="12" t="n">
         <v>70</v>
       </c>
@@ -3384,7 +3327,6 @@
       <c r="J74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="81" customHeight="1">
-      <c r="A75" s="11" t="n"/>
       <c r="C75" s="12" t="n">
         <v>71</v>
       </c>
@@ -3421,7 +3363,6 @@
       <c r="J75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="54" customHeight="1">
-      <c r="A76" s="11" t="n"/>
       <c r="C76" s="12" t="n">
         <v>72</v>
       </c>
@@ -3458,7 +3399,6 @@
       <c r="J76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="27" customHeight="1">
-      <c r="A77" s="11" t="n"/>
       <c r="B77" s="18" t="inlineStr">
         <is>
           <t>11. 단말 화면번호</t>
@@ -3500,7 +3440,6 @@
       <c r="J77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="121.5" customHeight="1">
-      <c r="A78" s="11" t="n"/>
       <c r="C78" s="12" t="n">
         <v>74</v>
       </c>
@@ -3540,7 +3479,6 @@
       <c r="J78" s="14" t="inlineStr"/>
     </row>
     <row r="79" hidden="1">
-      <c r="A79" s="11" t="n"/>
       <c r="C79" s="12" t="n">
         <v>75</v>
       </c>
@@ -3577,7 +3515,6 @@
       <c r="J79" s="14" t="inlineStr"/>
     </row>
     <row r="80" hidden="1">
-      <c r="A80" s="11" t="n"/>
       <c r="C80" s="12" t="n">
         <v>76</v>
       </c>
@@ -3616,7 +3553,6 @@
       <c r="J80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="27" customHeight="1">
-      <c r="A81" s="11" t="n"/>
       <c r="C81" s="12" t="n">
         <v>77</v>
       </c>
@@ -3653,7 +3589,6 @@
       <c r="J81" s="14" t="inlineStr"/>
     </row>
     <row r="82" hidden="1">
-      <c r="A82" s="11" t="n"/>
       <c r="C82" s="12" t="n">
         <v>78</v>
       </c>
@@ -3690,7 +3625,6 @@
       <c r="J82" s="14" t="inlineStr"/>
     </row>
     <row r="83" hidden="1">
-      <c r="A83" s="11" t="n"/>
       <c r="C83" s="12" t="n">
         <v>79</v>
       </c>
@@ -3727,7 +3661,6 @@
       <c r="J83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="54" customHeight="1">
-      <c r="A84" s="11" t="n"/>
       <c r="B84" s="18" t="inlineStr">
         <is>
           <t>12. 비대면 채널 경로</t>
@@ -3769,7 +3702,6 @@
       <c r="J84" s="14" t="inlineStr"/>
     </row>
     <row r="85" ht="54" customHeight="1">
-      <c r="A85" s="11" t="n"/>
       <c r="C85" s="12" t="n">
         <v>81</v>
       </c>
@@ -3807,7 +3739,6 @@
       <c r="J85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="40.5" customHeight="1">
-      <c r="A86" s="11" t="n"/>
       <c r="C86" s="12" t="n">
         <v>82</v>
       </c>
@@ -3844,7 +3775,6 @@
       <c r="J86" s="14" t="inlineStr"/>
     </row>
     <row r="87" ht="54" customHeight="1">
-      <c r="A87" s="11" t="n"/>
       <c r="C87" s="12" t="n">
         <v>83</v>
       </c>
@@ -3881,7 +3811,6 @@
       <c r="J87" s="14" t="inlineStr"/>
     </row>
     <row r="88" hidden="1">
-      <c r="A88" s="11" t="n"/>
       <c r="C88" s="12" t="n">
         <v>84</v>
       </c>
@@ -3921,7 +3850,6 @@
       <c r="J88" s="14" t="inlineStr"/>
     </row>
     <row r="89" hidden="1">
-      <c r="A89" s="11" t="n"/>
       <c r="C89" s="12" t="n">
         <v>85</v>
       </c>
@@ -3958,7 +3886,6 @@
       <c r="J89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="81" customHeight="1">
-      <c r="A90" s="11" t="n"/>
       <c r="B90" s="18" t="inlineStr">
         <is>
           <t>13. 시황 — 상담에 쓰는 만큼</t>
@@ -4000,7 +3927,6 @@
       <c r="J90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="135" customHeight="1">
-      <c r="A91" s="11" t="n"/>
       <c r="C91" s="12" t="n">
         <v>87</v>
       </c>
@@ -4043,7 +3969,6 @@
       <c r="J91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="135" customHeight="1">
-      <c r="A92" s="11" t="n"/>
       <c r="C92" s="12" t="n">
         <v>88</v>
       </c>
@@ -4085,7 +4010,6 @@
       <c r="J92" s="14" t="inlineStr"/>
     </row>
     <row r="93" ht="94.5" customHeight="1">
-      <c r="A93" s="11" t="n"/>
       <c r="C93" s="12" t="n">
         <v>89</v>
       </c>
@@ -4122,7 +4046,6 @@
       <c r="J93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="135" customHeight="1">
-      <c r="A94" s="11" t="n"/>
       <c r="C94" s="12" t="n">
         <v>90</v>
       </c>
@@ -4165,7 +4088,7 @@
       <c r="J94" s="14" t="inlineStr"/>
     </row>
     <row r="95" ht="135" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="24" t="inlineStr">
         <is>
           <t>Ⅳ. 고객 응대 — 이 고객에게 무엇을 권할 수 있고, 어떻게 말할 것인가</t>
         </is>
@@ -4219,7 +4142,6 @@
       <c r="J95" s="9" t="inlineStr"/>
     </row>
     <row r="96" ht="135" customHeight="1">
-      <c r="A96" s="11" t="n"/>
       <c r="C96" s="12" t="n">
         <v>92</v>
       </c>
@@ -4267,7 +4189,6 @@
       </c>
     </row>
     <row r="97" hidden="1">
-      <c r="A97" s="11" t="n"/>
       <c r="C97" s="12" t="n">
         <v>93</v>
       </c>
@@ -4317,7 +4238,6 @@
       <c r="J97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="135" customHeight="1">
-      <c r="A98" s="11" t="n"/>
       <c r="C98" s="12" t="n">
         <v>94</v>
       </c>
@@ -4378,7 +4298,6 @@
       <c r="J98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="135" customHeight="1">
-      <c r="A99" s="11" t="n"/>
       <c r="C99" s="12" t="n">
         <v>95</v>
       </c>
@@ -4442,7 +4361,6 @@
       <c r="J99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="135" customHeight="1">
-      <c r="A100" s="11" t="n"/>
       <c r="C100" s="12" t="n">
         <v>96</v>
       </c>
@@ -4484,7 +4402,6 @@
       <c r="J100" s="14" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="11" t="n"/>
       <c r="C101" s="12" t="n">
         <v>97</v>
       </c>
@@ -4536,7 +4453,6 @@
       <c r="J101" s="14" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
-      <c r="A102" s="11" t="n"/>
       <c r="B102" s="18" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4588,7 +4504,6 @@
       <c r="J102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="135" customHeight="1">
-      <c r="A103" s="11" t="n"/>
       <c r="C103" s="12" t="n">
         <v>99</v>
       </c>
@@ -4667,7 +4582,6 @@
       <c r="J103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="94.5" customHeight="1">
-      <c r="A104" s="11" t="n"/>
       <c r="C104" s="12" t="n">
         <v>100</v>
       </c>
@@ -4704,7 +4618,6 @@
       <c r="J104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="135" customHeight="1">
-      <c r="A105" s="11" t="n"/>
       <c r="C105" s="12" t="n">
         <v>101</v>
       </c>
@@ -4780,7 +4693,6 @@
       <c r="J105" s="14" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
-      <c r="A106" s="11" t="n"/>
       <c r="C106" s="12" t="n">
         <v>102</v>
       </c>
@@ -4817,7 +4729,6 @@
       <c r="J106" s="14" t="inlineStr"/>
     </row>
     <row r="107" ht="135" customHeight="1">
-      <c r="A107" s="11" t="n"/>
       <c r="C107" s="12" t="n">
         <v>103</v>
       </c>
@@ -4859,7 +4770,6 @@
       <c r="J107" s="14" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
-      <c r="A108" s="11" t="n"/>
       <c r="B108" s="18" t="inlineStr">
         <is>
           <t>16. 세액공제 계산</t>
@@ -4901,7 +4811,6 @@
       <c r="J108" s="14" t="inlineStr"/>
     </row>
     <row r="109" ht="67.5" customHeight="1">
-      <c r="A109" s="11" t="n"/>
       <c r="C109" s="12" t="n">
         <v>105</v>
       </c>
@@ -4938,7 +4847,6 @@
       <c r="J109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="121.5" customHeight="1">
-      <c r="A110" s="11" t="n"/>
       <c r="C110" s="12" t="n">
         <v>106</v>
       </c>
@@ -4978,7 +4886,6 @@
       <c r="J110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="135" customHeight="1">
-      <c r="A111" s="11" t="n"/>
       <c r="C111" s="12" t="n">
         <v>107</v>
       </c>
@@ -5048,7 +4955,6 @@
       <c r="J111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="135" customHeight="1">
-      <c r="A112" s="11" t="n"/>
       <c r="C112" s="12" t="n">
         <v>108</v>
       </c>
@@ -5090,7 +4996,6 @@
       <c r="J112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="135" customHeight="1">
-      <c r="A113" s="11" t="n"/>
       <c r="C113" s="12" t="n">
         <v>109</v>
       </c>
@@ -5139,7 +5044,6 @@
       </c>
     </row>
     <row r="114" hidden="1">
-      <c r="A114" s="11" t="n"/>
       <c r="C114" s="12" t="n">
         <v>110</v>
       </c>
@@ -5183,7 +5087,6 @@
       </c>
     </row>
     <row r="115" ht="27" customHeight="1">
-      <c r="A115" s="11" t="n"/>
       <c r="C115" s="12" t="n">
         <v>111</v>
       </c>
@@ -5220,7 +5123,6 @@
       <c r="J115" s="14" t="inlineStr"/>
     </row>
     <row r="116" hidden="1">
-      <c r="A116" s="11" t="n"/>
       <c r="C116" s="12" t="n">
         <v>112</v>
       </c>
@@ -5257,7 +5159,6 @@
       <c r="J116" s="14" t="inlineStr"/>
     </row>
     <row r="117" hidden="1">
-      <c r="A117" s="11" t="n"/>
       <c r="C117" s="12" t="n">
         <v>113</v>
       </c>
@@ -5294,7 +5195,6 @@
       <c r="J117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="67.5" customHeight="1">
-      <c r="A118" s="11" t="n"/>
       <c r="B118" s="18" t="inlineStr">
         <is>
           <t>17. 상담 화법·반론 대응</t>
@@ -5336,7 +5236,6 @@
       <c r="J118" s="14" t="inlineStr"/>
     </row>
     <row r="119" ht="135" customHeight="1">
-      <c r="A119" s="11" t="n"/>
       <c r="C119" s="12" t="n">
         <v>115</v>
       </c>
@@ -5353,9 +5252,16 @@
       <c r="F119" s="14" t="inlineStr">
         <is>
           <t>● 이수민
-"예금만 해서 관리 필요 없어요"라는 고객에게는 금리 갈아타기가 곧 관리라는 논리로 접근하는 게 핵심이에요. 예금과 같은 원리금보장상품도 꾸준한 관리가 필요한 대상이라는 점을 짚어주고, 매월 금리가 가장 좋은 상품을 제공하고 있다는 점을 설명해 주세요. 고객에게는 이렇게 안내해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다." 이미 안정적으로 잘 운용하고 있다는 점을 먼저 인정한 뒤, 같은 안전성인 예금자보호 테두리 안에서 금리를 올려주는 제안으로 자연스럽게 대화를 이어가면 됩니다.
+예금으로 충분하다는 고객에게는 원리금보장상품도 꾸준한 관리가 필요하다는 점을 짚어주는 것이 핵심이에요. 
+매월 금리가 가장 좋은 상품을 계속 제공하고 있고 GIC 같은 고금리 원리금보장상품을 비대면으로 손쉽게 거래할 수 있다는 점을 활용해 금리 갈아타기가 곧 자산 관리라는 점을 설명해야 해요. 
+다만 사용 계획이 있는 자금이라면 먼저 걸러내야 하고 고객에게 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 써야 해요.
+고객에게는 이렇게 말씀해 보세요.
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."
 ● 송도윤
-예금만으로도 충분하지 않냐고 묻는 고객에게는 예금 같은 원리금보장상품도 매월 금리가 유리한 상품으로 갈아타는 과정이 곧 관리라는 점을 짚어주는 것이 핵심이에요. 당행은 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있다는 점을 설명해 보세요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내하시면 돼요. 이 과정에서 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 '고유계정대' 같은 용어 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 표현을 사용해 주세요. 아울러 연금지급 대기나 교체매매 등으로 사용 계획이 있는 자금인지 먼저 확인하고 접근하시는 것이 안전해요.</t>
+예금만 해서 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 논리로 접근하는 게 핵심이에요. 
+원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 짚어 드려야 해요. 
+고객에게는 이렇게 말씀해 보세요.
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
       <c r="G119" s="19" t="inlineStr">
@@ -5376,7 +5282,6 @@
       <c r="J119" s="14" t="inlineStr"/>
     </row>
     <row r="120" hidden="1">
-      <c r="A120" s="11" t="n"/>
       <c r="C120" s="12" t="n">
         <v>116</v>
       </c>
@@ -5416,7 +5321,6 @@
       <c r="J120" s="14" t="inlineStr"/>
     </row>
     <row r="121" ht="135" customHeight="1">
-      <c r="A121" s="11" t="n"/>
       <c r="C121" s="12" t="n">
         <v>117</v>
       </c>
@@ -5459,7 +5363,6 @@
       <c r="J121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="81" customHeight="1">
-      <c r="A122" s="11" t="n"/>
       <c r="C122" s="12" t="n">
         <v>118</v>
       </c>
@@ -5498,7 +5401,6 @@
       <c r="J122" s="14" t="inlineStr"/>
     </row>
     <row r="123" hidden="1">
-      <c r="A123" s="11" t="n"/>
       <c r="C123" s="12" t="n">
         <v>119</v>
       </c>
@@ -5537,7 +5439,6 @@
       <c r="J123" s="14" t="inlineStr"/>
     </row>
     <row r="124" hidden="1">
-      <c r="A124" s="11" t="n"/>
       <c r="C124" s="12" t="n">
         <v>120</v>
       </c>
@@ -5579,7 +5480,6 @@
       <c r="J124" s="14" t="inlineStr"/>
     </row>
     <row r="125" hidden="1">
-      <c r="A125" s="11" t="n"/>
       <c r="C125" s="12" t="n">
         <v>121</v>
       </c>
@@ -5616,7 +5516,6 @@
       <c r="J125" s="14" t="inlineStr"/>
     </row>
     <row r="126" hidden="1">
-      <c r="A126" s="11" t="n"/>
       <c r="C126" s="12" t="n">
         <v>122</v>
       </c>
@@ -5661,7 +5560,6 @@
       <c r="J126" s="14" t="inlineStr"/>
     </row>
     <row r="127" hidden="1">
-      <c r="A127" s="11" t="n"/>
       <c r="C127" s="12" t="n">
         <v>123</v>
       </c>
@@ -5698,7 +5596,6 @@
       <c r="J127" s="14" t="inlineStr"/>
     </row>
     <row r="128" hidden="1">
-      <c r="A128" s="11" t="n"/>
       <c r="C128" s="12" t="n">
         <v>124</v>
       </c>
@@ -5735,7 +5632,6 @@
       <c r="J128" s="14" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
-      <c r="A129" s="11" t="n"/>
       <c r="C129" s="12" t="n">
         <v>125</v>
       </c>
@@ -5773,7 +5669,6 @@
       <c r="J129" s="14" t="inlineStr"/>
     </row>
     <row r="130" hidden="1">
-      <c r="A130" s="11" t="n"/>
       <c r="C130" s="12" t="n">
         <v>126</v>
       </c>
@@ -5810,7 +5705,6 @@
       <c r="J130" s="14" t="inlineStr"/>
     </row>
     <row r="131" hidden="1">
-      <c r="A131" s="11" t="n"/>
       <c r="C131" s="12" t="n">
         <v>127</v>
       </c>
@@ -5849,7 +5743,6 @@
       <c r="J131" s="14" t="inlineStr"/>
     </row>
     <row r="132" hidden="1">
-      <c r="A132" s="11" t="n"/>
       <c r="C132" s="12" t="n">
         <v>128</v>
       </c>
@@ -5890,7 +5783,6 @@
       <c r="J132" s="14" t="inlineStr"/>
     </row>
     <row r="133" hidden="1">
-      <c r="A133" s="11" t="n"/>
       <c r="C133" s="12" t="n">
         <v>129</v>
       </c>
@@ -5930,7 +5822,6 @@
       <c r="J133" s="14" t="inlineStr"/>
     </row>
     <row r="134" ht="54" customHeight="1">
-      <c r="A134" s="11" t="n"/>
       <c r="C134" s="12" t="n">
         <v>130</v>
       </c>
@@ -5969,7 +5860,7 @@
       <c r="J134" s="14" t="inlineStr"/>
     </row>
     <row r="135" ht="135" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="24" t="inlineStr">
         <is>
           <t>Ⅴ. 발송·화면 연계 — 문자·쪽지 문구를 만들고 발송 화면을 연다</t>
         </is>
@@ -6017,7 +5908,6 @@
       <c r="J135" s="9" t="inlineStr"/>
     </row>
     <row r="136" ht="121.5" customHeight="1">
-      <c r="A136" s="11" t="n"/>
       <c r="C136" s="12" t="n">
         <v>132</v>
       </c>
@@ -6062,7 +5952,6 @@
       </c>
     </row>
     <row r="137" ht="81" customHeight="1">
-      <c r="A137" s="11" t="n"/>
       <c r="C137" s="12" t="n">
         <v>133</v>
       </c>
@@ -6107,7 +5996,6 @@
       </c>
     </row>
     <row r="138" ht="135" customHeight="1">
-      <c r="A138" s="11" t="n"/>
       <c r="C138" s="12" t="n">
         <v>134</v>
       </c>
@@ -6150,7 +6038,6 @@
       </c>
     </row>
     <row r="139" ht="135" customHeight="1">
-      <c r="A139" s="11" t="n"/>
       <c r="C139" s="12" t="n">
         <v>135</v>
       </c>
@@ -6201,7 +6088,6 @@
       </c>
     </row>
     <row r="140" hidden="1">
-      <c r="A140" s="11" t="n"/>
       <c r="C140" s="12" t="n">
         <v>136</v>
       </c>
@@ -6238,7 +6124,6 @@
       <c r="J140" s="14" t="inlineStr"/>
     </row>
     <row r="141" ht="121.5" customHeight="1">
-      <c r="A141" s="11" t="n"/>
       <c r="B141" s="18" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6289,7 +6174,6 @@
       </c>
     </row>
     <row r="142" hidden="1">
-      <c r="A142" s="11" t="n"/>
       <c r="C142" s="12" t="n">
         <v>138</v>
       </c>
@@ -6330,7 +6214,6 @@
       </c>
     </row>
     <row r="143" ht="67.5" customHeight="1">
-      <c r="A143" s="11" t="n"/>
       <c r="C143" s="12" t="n">
         <v>139</v>
       </c>
@@ -6371,7 +6254,6 @@
       </c>
     </row>
     <row r="144" hidden="1">
-      <c r="A144" s="11" t="n"/>
       <c r="C144" s="12" t="n">
         <v>140</v>
       </c>
@@ -6408,7 +6290,6 @@
       <c r="J144" s="14" t="inlineStr"/>
     </row>
     <row r="145" hidden="1">
-      <c r="A145" s="11" t="n"/>
       <c r="C145" s="12" t="n">
         <v>141</v>
       </c>
@@ -6449,7 +6330,7 @@
       </c>
     </row>
     <row r="146" hidden="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="A146" s="24" t="inlineStr">
         <is>
           <t>Ⅵ. 대화 이어가기 — 앞서 물은 것을 이어받고, 방금 답을 고쳐 쓴다</t>
         </is>
@@ -6498,7 +6379,6 @@
       <c r="J146" s="9" t="inlineStr"/>
     </row>
     <row r="147" ht="27" customHeight="1">
-      <c r="A147" s="11" t="n"/>
       <c r="C147" s="12" t="n">
         <v>143</v>
       </c>
@@ -6539,7 +6419,6 @@
       </c>
     </row>
     <row r="148" ht="135" customHeight="1">
-      <c r="A148" s="11" t="n"/>
       <c r="C148" s="12" t="n">
         <v>144</v>
       </c>
@@ -6556,12 +6435,14 @@
       <c r="F148" s="14" t="inlineStr">
         <is>
           <t>● 정민석
-현재 보유하신 자산이 모두 원리금보장상품으로만 운용 중인 고객에게는 정기예금 대신 디폴트옵션 저위험 이상으로 운용해 보시는 방법을 제안해 볼 수 있어요. 다만 해당 고객이 이미 디폴트옵션 초저위험을 등록해 보유하고 계신 상태라면 사전지정운용제도 등록 및 변경과 보유상품 변경인 기존 매도 및 신규 매수의 2단계 거래가 필요하다는 점을 반드시 함께 안내해 드려야 해요. 또한 고객에게 생소한 고유계정대라는 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 쉽게 설명해 주시는 것이 좋아요. 사용 계획이 있는 자금이나 반대 케이스에 해당하는지 먼저 확인하고 접근하는 점도 잊지 마세요.
+투자성향이 공격투자형이신 정민석 고객님은 현재 원리금보장 및 현금성 자산이 100%를 차지하여 운용수익률이 3.1%에 머물고 있으므로, 예금 중심 운용에 대해 디폴트옵션 활용을 제안해 보세요.
+적립금 300만원 이상이면서 원리금보장상품을 100%로 운용 중인 고객에게는 "정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용"하시는 방안을 제안할 수 있어요.
+다만 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 "현재 보유중이신 디폴트옵션은 정기예금만으로 구성되어 있습니다"라고 짚어 주실 수 있어요.
+고객이 "예금만 해서 관리 필요 없어요"라고 말씀하신다면 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
+또한 "노후 자금을 주식에 투자하는 건 위험하지 않나요"라고 하시는 경우라면 "주식이 위험한 건 맞지만 여기서 말하는 위험은 변동성을 뜻하며, 변동성은 기간이 길어지면 줄어듭니다"라고 설명해 주실 수 있어요.
 ● 박정호
-원리금보장상품 100% 운용 고객에게는 적립금 300만원 이상인 경우 정기예금 대신 디폴트옵션 저위험 이상으로 운용을 제안할 수 있어요. 
-상담을 진행할 때 사용계획 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내야 한다는 점을 유념해 주세요. 
-또한 고객에게 안내할 때는 생소한 '고유계정대'라는 표현 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요. 
-이미 디폴트옵션 초저위험을 등록·보유한 고객이라면 사전지정운용제도 등록 및 변경과 보유상품 변경(기존 매도 후 신규 매수)의 2단계 거래가 필요하다는 점을 반드시 안내해야 해요.</t>
+박정호 고객님은 평가금액 2,000만원 전액이 정기예금으로만 구성되어 있어 원리금보장상품 편중 상태예요. 안정적인 자산 운용 중인 고객에게는 같은 안전성 안에서 금리를 올려주는 제안으로 접근해야 해요. 
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
       <c r="G148" s="14" t="inlineStr">
@@ -6576,13 +6457,12 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>고객 재료(불일치) + 그에 맞는 화법 ↔ 성향 무시하고 일반 화법만</t>
+          <t>고객 재료(불일치·펀드 경험) + 그에 맞는 화법 ↔ 재료를 무시하고 일반 화법만</t>
         </is>
       </c>
       <c r="J148" s="14" t="inlineStr"/>
     </row>
     <row r="149" ht="81" customHeight="1">
-      <c r="A149" s="11" t="n"/>
       <c r="C149" s="12" t="n">
         <v>145</v>
       </c>
@@ -6619,7 +6499,6 @@
       <c r="J149" s="14" t="inlineStr"/>
     </row>
     <row r="150" ht="135" customHeight="1">
-      <c r="A150" s="11" t="n"/>
       <c r="C150" s="12" t="n">
         <v>146</v>
       </c>
@@ -6664,7 +6543,6 @@
       </c>
     </row>
     <row r="151" ht="27" customHeight="1">
-      <c r="A151" s="11" t="n"/>
       <c r="C151" s="12" t="n">
         <v>147</v>
       </c>
@@ -6705,7 +6583,6 @@
       </c>
     </row>
     <row r="152" hidden="1">
-      <c r="A152" s="11" t="n"/>
       <c r="C152" s="12" t="n">
         <v>148</v>
       </c>
@@ -6750,7 +6627,6 @@
       </c>
     </row>
     <row r="153" ht="54" customHeight="1">
-      <c r="A153" s="11" t="n"/>
       <c r="C153" s="12" t="n">
         <v>149</v>
       </c>
@@ -6793,7 +6669,6 @@
       </c>
     </row>
     <row r="154" hidden="1">
-      <c r="A154" s="11" t="n"/>
       <c r="C154" s="12" t="n">
         <v>150</v>
       </c>
@@ -6834,7 +6709,6 @@
       </c>
     </row>
     <row r="155" ht="81" customHeight="1">
-      <c r="A155" s="11" t="n"/>
       <c r="C155" s="12" t="n">
         <v>151</v>
       </c>
@@ -6876,7 +6750,6 @@
       </c>
     </row>
     <row r="156" hidden="1">
-      <c r="A156" s="11" t="n"/>
       <c r="C156" s="12" t="n">
         <v>152</v>
       </c>
@@ -6917,7 +6790,6 @@
       </c>
     </row>
     <row r="157" ht="54" customHeight="1">
-      <c r="A157" s="11" t="n"/>
       <c r="C157" s="12" t="n">
         <v>153</v>
       </c>
@@ -6958,7 +6830,6 @@
       </c>
     </row>
     <row r="158" hidden="1">
-      <c r="A158" s="11" t="n"/>
       <c r="C158" s="12" t="n">
         <v>154</v>
       </c>
@@ -6995,7 +6866,6 @@
       <c r="J158" s="14" t="inlineStr"/>
     </row>
     <row r="159" hidden="1">
-      <c r="A159" s="11" t="n"/>
       <c r="C159" s="12" t="n">
         <v>155</v>
       </c>
@@ -7032,7 +6902,6 @@
       </c>
     </row>
     <row r="160" ht="121.5" customHeight="1">
-      <c r="A160" s="11" t="n"/>
       <c r="B160" s="18" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
@@ -7081,7 +6950,6 @@
       </c>
     </row>
     <row r="161" ht="81" customHeight="1">
-      <c r="A161" s="11" t="n"/>
       <c r="C161" s="12" t="n">
         <v>157</v>
       </c>
@@ -7124,7 +6992,6 @@
       </c>
     </row>
     <row r="162" hidden="1">
-      <c r="A162" s="11" t="n"/>
       <c r="C162" s="12" t="n">
         <v>158</v>
       </c>
@@ -7165,7 +7032,6 @@
       </c>
     </row>
     <row r="163" ht="135" customHeight="1">
-      <c r="A163" s="11" t="n"/>
       <c r="C163" s="12" t="n">
         <v>159</v>
       </c>
@@ -7214,7 +7080,6 @@
       </c>
     </row>
     <row r="164" hidden="1">
-      <c r="A164" s="11" t="n"/>
       <c r="C164" s="12" t="n">
         <v>160</v>
       </c>
@@ -7257,7 +7122,6 @@
       </c>
     </row>
     <row r="165" hidden="1">
-      <c r="A165" s="11" t="n"/>
       <c r="C165" s="12" t="n">
         <v>161</v>
       </c>
@@ -7294,7 +7158,6 @@
       <c r="J165" s="14" t="inlineStr"/>
     </row>
     <row r="166" ht="135" customHeight="1">
-      <c r="A166" s="11" t="n"/>
       <c r="B166" s="18" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -7351,7 +7214,6 @@
       <c r="J166" s="14" t="inlineStr"/>
     </row>
     <row r="167" ht="135" customHeight="1">
-      <c r="A167" s="11" t="n"/>
       <c r="C167" s="12" t="n">
         <v>163</v>
       </c>
@@ -7405,7 +7267,6 @@
       <c r="J167" s="14" t="inlineStr"/>
     </row>
     <row r="168" ht="135" customHeight="1">
-      <c r="A168" s="11" t="n"/>
       <c r="C168" s="12" t="n">
         <v>164</v>
       </c>
@@ -7459,7 +7320,6 @@
       <c r="J168" s="14" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
-      <c r="A169" s="11" t="n"/>
       <c r="B169" s="18" t="inlineStr">
         <is>
           <t>23. 브리핑 수정</t>
@@ -7501,7 +7361,6 @@
       <c r="J169" s="14" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
-      <c r="A170" s="11" t="n"/>
       <c r="C170" s="12" t="n">
         <v>166</v>
       </c>
@@ -7538,7 +7397,6 @@
       <c r="J170" s="14" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
-      <c r="A171" s="11" t="n"/>
       <c r="C171" s="12" t="n">
         <v>167</v>
       </c>
@@ -7586,7 +7444,7 @@
       <c r="J171" s="14" t="inlineStr"/>
     </row>
     <row r="172" hidden="1">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="A172" s="24" t="inlineStr">
         <is>
           <t>Ⅶ. 개발 회귀 — 도구 선택 · 실패 처리 · 고객별 대조</t>
         </is>
@@ -7641,7 +7499,6 @@
       <c r="J172" s="9" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
-      <c r="A173" s="11" t="n"/>
       <c r="C173" s="12" t="n">
         <v>169</v>
       </c>
@@ -7704,7 +7561,6 @@
       <c r="J173" s="14" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
-      <c r="A174" s="11" t="n"/>
       <c r="C174" s="12" t="n">
         <v>170</v>
       </c>
@@ -7754,7 +7610,6 @@
       <c r="J174" s="14" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
-      <c r="A175" s="11" t="n"/>
       <c r="C175" s="12" t="n">
         <v>171</v>
       </c>
@@ -7795,7 +7650,6 @@
       </c>
     </row>
     <row r="176" hidden="1">
-      <c r="A176" s="11" t="n"/>
       <c r="C176" s="12" t="n">
         <v>172</v>
       </c>
@@ -7832,7 +7686,6 @@
       <c r="J176" s="14" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
-      <c r="A177" s="11" t="n"/>
       <c r="C177" s="12" t="n">
         <v>173</v>
       </c>
@@ -7870,7 +7723,6 @@
       <c r="J177" s="14" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
-      <c r="A178" s="11" t="n"/>
       <c r="C178" s="12" t="n">
         <v>174</v>
       </c>
@@ -7907,7 +7759,6 @@
       <c r="J178" s="14" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
-      <c r="A179" s="11" t="n"/>
       <c r="C179" s="12" t="n">
         <v>175</v>
       </c>
@@ -7948,7 +7799,6 @@
       </c>
     </row>
     <row r="180" hidden="1">
-      <c r="A180" s="11" t="n"/>
       <c r="C180" s="12" t="n">
         <v>176</v>
       </c>
@@ -7985,7 +7835,6 @@
       <c r="J180" s="14" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
-      <c r="A181" s="11" t="n"/>
       <c r="B181" s="18" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -8029,7 +7878,6 @@
       <c r="J181" s="14" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
-      <c r="A182" s="11" t="n"/>
       <c r="C182" s="12" t="n">
         <v>178</v>
       </c>
@@ -8068,7 +7916,6 @@
       <c r="J182" s="14" t="inlineStr"/>
     </row>
     <row r="183" hidden="1">
-      <c r="A183" s="11" t="n"/>
       <c r="C183" s="12" t="n">
         <v>179</v>
       </c>
@@ -8105,7 +7952,6 @@
       <c r="J183" s="14" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
-      <c r="A184" s="11" t="n"/>
       <c r="C184" s="12" t="n">
         <v>180</v>
       </c>
@@ -8142,7 +7988,6 @@
       <c r="J184" s="14" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
-      <c r="A185" s="11" t="n"/>
       <c r="C185" s="12" t="n">
         <v>181</v>
       </c>
@@ -8184,7 +8029,6 @@
       <c r="J185" s="14" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
-      <c r="A186" s="11" t="n"/>
       <c r="C186" s="12" t="n">
         <v>182</v>
       </c>
@@ -8221,7 +8065,6 @@
       </c>
     </row>
     <row r="187" hidden="1">
-      <c r="A187" s="11" t="n"/>
       <c r="B187" s="18" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -8300,7 +8143,6 @@
       <c r="J187" s="14" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
-      <c r="A188" s="11" t="n"/>
       <c r="C188" s="12" t="n">
         <v>184</v>
       </c>
@@ -8340,7 +8182,6 @@
       <c r="J188" s="14" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
-      <c r="A189" s="11" t="n"/>
       <c r="C189" s="12" t="n">
         <v>185</v>
       </c>
@@ -8380,7 +8221,6 @@
       <c r="J189" s="14" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
-      <c r="A190" s="11" t="n"/>
       <c r="C190" s="12" t="n">
         <v>186</v>
       </c>
@@ -8420,7 +8260,6 @@
       <c r="J190" s="14" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
-      <c r="A191" s="11" t="n"/>
       <c r="C191" s="12" t="n">
         <v>187</v>
       </c>
@@ -8460,7 +8299,6 @@
       <c r="J191" s="14" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
-      <c r="A192" s="11" t="n"/>
       <c r="C192" s="12" t="n">
         <v>188</v>
       </c>
@@ -8501,7 +8339,6 @@
       <c r="J192" s="14" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
-      <c r="A193" s="11" t="n"/>
       <c r="C193" s="12" t="n">
         <v>189</v>
       </c>
@@ -8541,7 +8378,6 @@
       <c r="J193" s="14" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
-      <c r="A194" s="11" t="n"/>
       <c r="C194" s="12" t="n">
         <v>190</v>
       </c>
@@ -8581,7 +8417,6 @@
       <c r="J194" s="14" t="inlineStr"/>
     </row>
     <row r="195" hidden="1">
-      <c r="A195" s="11" t="n"/>
       <c r="C195" s="12" t="n">
         <v>191</v>
       </c>
@@ -8622,7 +8457,6 @@
       <c r="J195" s="14" t="inlineStr"/>
     </row>
     <row r="196" hidden="1">
-      <c r="A196" s="11" t="n"/>
       <c r="C196" s="12" t="n">
         <v>192</v>
       </c>
@@ -8662,7 +8496,6 @@
       <c r="J196" s="14" t="inlineStr"/>
     </row>
     <row r="197" hidden="1">
-      <c r="A197" s="11" t="n"/>
       <c r="C197" s="12" t="n">
         <v>193</v>
       </c>
@@ -8673,17 +8506,10 @@
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>정민석 ↔ 김현수</t>
-        </is>
-      </c>
-      <c r="F197" s="14" t="inlineStr">
-        <is>
-          <t>● 정민석
-현재 보유한 자산이 예금 위주인 고객에게는 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤 같은 안전성 안에서 금리를 올려주는 제안으로 들어가는 게 핵심이에요. 원리금보장상품도 관리가 중요하다는 점을 매월 최고금리 상품 제공과 GIC 비대면 거래 가능으로 입증해야 하므로, 금리 갈아타기가 곧 관리라는 논리로 대응해 보세요. 다만 사용계획이 있는 자금은 먼저 걸러내고, 고객에게 생소한 고유계정대 같은 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 고객이 예금만 해서 관리가 필요 없다고 반응할 때는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."라고 안내해 보세요.
-● 김현수
-예금만 보유하고 있어 관리가 필요 없다는 고객에게는 금리 갈아타기가 곧 관리라는 점을 짚어주는 게 핵심이에요. 이미 안정적으로 잘 운용하고 계신다고 인정한 뒤, 같은 안전성 안에서 금리를 올려주는 제안으로 들어가야 해요. 고객이 사용계획이 있는 자금인지 먼저 확인하고, 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
-        </is>
-      </c>
+          <t>박정호(펀드 경험 없음) ↔ 김현수(펀드 보유)</t>
+        </is>
+      </c>
+      <c r="F197" s="14" t="inlineStr"/>
       <c r="G197" s="17" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -8691,18 +8517,17 @@
       </c>
       <c r="H197" s="14" t="inlineStr">
         <is>
-          <t>정민석 181245-3097614 ↔ 김현수 173544-2074623</t>
+          <t>박정호 168450-7293815(펀드 경험 없음) ↔ 김현수 173544-2074623(펀드 보유)</t>
         </is>
       </c>
       <c r="I197" s="14" t="inlineStr">
         <is>
-          <t>같은 문제라도 성향 다르면 화법이 갈린다 ↔ 같은 화법이 나온다</t>
+          <t>경험 없는 쪽은 원금보장 유지 + 금리만 올리는 제안, 있는 쪽은 일부 금액 운용 ↔ 둘에게 같은 화법이 나온다</t>
         </is>
       </c>
       <c r="J197" s="14" t="inlineStr"/>
     </row>
     <row r="198" hidden="1">
-      <c r="A198" s="11" t="n"/>
       <c r="C198" s="12" t="n">
         <v>194</v>
       </c>
@@ -8794,7 +8619,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -97,18 +97,11 @@
         <color rgb="00BFA55A"/>
       </top>
     </border>
-    <border>
-      <right/>
-      <top style="medium">
-        <color rgb="00BFA55A"/>
-      </top>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,9 +165,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +532,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J198"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -624,7 +614,7 @@
       </c>
     </row>
     <row r="5" ht="135" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Ⅰ. 대상 선정 — 오늘 누구를 보고, 왜 그 사람인가</t>
         </is>
@@ -676,6 +666,7 @@
       <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="11" t="n"/>
       <c r="C6" s="12" t="n">
         <v>2</v>
       </c>
@@ -707,6 +698,7 @@
       <c r="J6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="11" t="n"/>
       <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
@@ -743,6 +735,7 @@
       <c r="J7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="135" customHeight="1">
+      <c r="A8" s="11" t="n"/>
       <c r="C8" s="12" t="n">
         <v>4</v>
       </c>
@@ -785,6 +778,7 @@
       <c r="J8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="11" t="n"/>
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t>2. 고객군·관리 기준</t>
@@ -826,6 +820,7 @@
       <c r="J9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="11" t="n"/>
       <c r="C10" s="12" t="n">
         <v>6</v>
       </c>
@@ -862,6 +857,7 @@
       <c r="J10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="11" t="n"/>
       <c r="C11" s="12" t="n">
         <v>7</v>
       </c>
@@ -900,6 +896,7 @@
       <c r="J11" s="14" t="inlineStr"/>
     </row>
     <row r="12" hidden="1">
+      <c r="A12" s="11" t="n"/>
       <c r="C12" s="12" t="n">
         <v>8</v>
       </c>
@@ -939,6 +936,7 @@
       <c r="J12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="11" t="n"/>
       <c r="C13" s="12" t="n">
         <v>9</v>
       </c>
@@ -975,6 +973,7 @@
       <c r="J13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="11" t="n"/>
       <c r="C14" s="12" t="n">
         <v>10</v>
       </c>
@@ -1011,6 +1010,7 @@
       <c r="J14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="135" customHeight="1">
+      <c r="A15" s="11" t="n"/>
       <c r="B15" s="18" t="inlineStr">
         <is>
           <t>3. 오늘의 타겟 목록</t>
@@ -1052,6 +1052,7 @@
       <c r="J15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="135" customHeight="1">
+      <c r="A16" s="11" t="n"/>
       <c r="C16" s="12" t="n">
         <v>12</v>
       </c>
@@ -1099,7 +1100,7 @@
       <c r="J16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Ⅱ. 고객 상태 — 이 고객이 지금 어떤 상태이고, 조심할 것은 무엇인가</t>
         </is>
@@ -1145,6 +1146,7 @@
       <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="94.5" customHeight="1">
+      <c r="A18" s="11" t="n"/>
       <c r="C18" s="12" t="n">
         <v>14</v>
       </c>
@@ -1184,6 +1186,7 @@
       <c r="J18" s="14" t="inlineStr"/>
     </row>
     <row r="19" hidden="1">
+      <c r="A19" s="11" t="n"/>
       <c r="C19" s="12" t="n">
         <v>15</v>
       </c>
@@ -1220,6 +1223,7 @@
       <c r="J19" s="14" t="inlineStr"/>
     </row>
     <row r="20" hidden="1">
+      <c r="A20" s="11" t="n"/>
       <c r="C20" s="12" t="n">
         <v>16</v>
       </c>
@@ -1256,6 +1260,7 @@
       <c r="J20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="94.5" customHeight="1">
+      <c r="A21" s="11" t="n"/>
       <c r="C21" s="12" t="n">
         <v>17</v>
       </c>
@@ -1295,6 +1300,7 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="81" customHeight="1">
+      <c r="A22" s="11" t="n"/>
       <c r="C22" s="12" t="n">
         <v>18</v>
       </c>
@@ -1334,6 +1340,7 @@
       <c r="J22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="40.5" customHeight="1">
+      <c r="A23" s="11" t="n"/>
       <c r="C23" s="12" t="n">
         <v>19</v>
       </c>
@@ -1370,6 +1377,7 @@
       <c r="J23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="135" customHeight="1">
+      <c r="A24" s="11" t="n"/>
       <c r="C24" s="12" t="n">
         <v>20</v>
       </c>
@@ -1411,6 +1419,7 @@
       <c r="J24" s="14" t="inlineStr"/>
     </row>
     <row r="25" hidden="1">
+      <c r="A25" s="11" t="n"/>
       <c r="C25" s="12" t="n">
         <v>21</v>
       </c>
@@ -1449,6 +1458,7 @@
       <c r="J25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="11" t="n"/>
       <c r="C26" s="12" t="n">
         <v>22</v>
       </c>
@@ -1485,6 +1495,7 @@
       <c r="J26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="94.5" customHeight="1">
+      <c r="A27" s="11" t="n"/>
       <c r="C27" s="12" t="n">
         <v>23</v>
       </c>
@@ -1522,6 +1533,7 @@
       <c r="J27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="94.5" customHeight="1">
+      <c r="A28" s="11" t="n"/>
       <c r="C28" s="12" t="n">
         <v>24</v>
       </c>
@@ -1561,6 +1573,7 @@
       <c r="J28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="11" t="n"/>
       <c r="B29" s="18" t="inlineStr">
         <is>
           <t>5. 고객 계좌 상태 확인</t>
@@ -1602,6 +1615,7 @@
       <c r="J29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="67.5" customHeight="1">
+      <c r="A30" s="11" t="n"/>
       <c r="C30" s="12" t="n">
         <v>26</v>
       </c>
@@ -1634,6 +1648,7 @@
       <c r="J30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="27" customHeight="1">
+      <c r="A31" s="11" t="n"/>
       <c r="C31" s="12" t="n">
         <v>27</v>
       </c>
@@ -1670,6 +1685,7 @@
       <c r="J31" s="14" t="inlineStr"/>
     </row>
     <row r="32" hidden="1">
+      <c r="A32" s="11" t="n"/>
       <c r="C32" s="12" t="n">
         <v>28</v>
       </c>
@@ -1706,6 +1722,7 @@
       <c r="J32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="121.5" customHeight="1">
+      <c r="A33" s="11" t="n"/>
       <c r="C33" s="12" t="n">
         <v>29</v>
       </c>
@@ -1745,6 +1762,7 @@
       <c r="J33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="11" t="n"/>
       <c r="C34" s="12" t="n">
         <v>30</v>
       </c>
@@ -1776,6 +1794,7 @@
       <c r="J34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="27" customHeight="1">
+      <c r="A35" s="11" t="n"/>
       <c r="C35" s="12" t="n">
         <v>31</v>
       </c>
@@ -1812,6 +1831,7 @@
       <c r="J35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="27" customHeight="1">
+      <c r="A36" s="11" t="n"/>
       <c r="C36" s="12" t="n">
         <v>32</v>
       </c>
@@ -1848,6 +1868,7 @@
       <c r="J36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="27" customHeight="1">
+      <c r="A37" s="11" t="n"/>
       <c r="C37" s="12" t="n">
         <v>33</v>
       </c>
@@ -1884,6 +1905,7 @@
       <c r="J37" s="14" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
+      <c r="A38" s="11" t="n"/>
       <c r="B38" s="18" t="inlineStr">
         <is>
           <t>6. 상담 이력 조회</t>
@@ -1925,6 +1947,7 @@
       <c r="J38" s="14" t="inlineStr"/>
     </row>
     <row r="39" hidden="1">
+      <c r="A39" s="11" t="n"/>
       <c r="C39" s="12" t="n">
         <v>35</v>
       </c>
@@ -1952,6 +1975,7 @@
       <c r="J39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="40.5" customHeight="1">
+      <c r="A40" s="11" t="n"/>
       <c r="C40" s="12" t="n">
         <v>36</v>
       </c>
@@ -1988,6 +2012,7 @@
       <c r="J40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="40.5" customHeight="1">
+      <c r="A41" s="11" t="n"/>
       <c r="C41" s="12" t="n">
         <v>37</v>
       </c>
@@ -2024,6 +2049,7 @@
       <c r="J41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="135" customHeight="1">
+      <c r="A42" s="11" t="n"/>
       <c r="B42" s="18" t="inlineStr">
         <is>
           <t>7. 금지·주의 안내</t>
@@ -2074,6 +2100,7 @@
       <c r="J42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="135" customHeight="1">
+      <c r="A43" s="11" t="n"/>
       <c r="C43" s="12" t="n">
         <v>39</v>
       </c>
@@ -2114,6 +2141,7 @@
       <c r="J43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="54" customHeight="1">
+      <c r="A44" s="11" t="n"/>
       <c r="C44" s="12" t="n">
         <v>40</v>
       </c>
@@ -2150,6 +2178,7 @@
       <c r="J44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="135" customHeight="1">
+      <c r="A45" s="11" t="n"/>
       <c r="C45" s="12" t="n">
         <v>41</v>
       </c>
@@ -2195,6 +2224,7 @@
       <c r="J45" s="14" t="inlineStr"/>
     </row>
     <row r="46" hidden="1">
+      <c r="A46" s="11" t="n"/>
       <c r="C46" s="12" t="n">
         <v>42</v>
       </c>
@@ -2231,6 +2261,7 @@
       <c r="J46" s="14" t="inlineStr"/>
     </row>
     <row r="47" hidden="1">
+      <c r="A47" s="11" t="n"/>
       <c r="C47" s="12" t="n">
         <v>43</v>
       </c>
@@ -2283,6 +2314,7 @@
       <c r="J47" s="14" t="inlineStr"/>
     </row>
     <row r="48" hidden="1">
+      <c r="A48" s="11" t="n"/>
       <c r="C48" s="12" t="n">
         <v>44</v>
       </c>
@@ -2320,6 +2352,7 @@
       <c r="J48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="40.5" customHeight="1">
+      <c r="A49" s="11" t="n"/>
       <c r="C49" s="12" t="n">
         <v>45</v>
       </c>
@@ -2361,6 +2394,7 @@
       </c>
     </row>
     <row r="50" ht="40.5" customHeight="1">
+      <c r="A50" s="11" t="n"/>
       <c r="B50" s="18" t="inlineStr">
         <is>
           <t>8. 상담 준비 자료</t>
@@ -2402,6 +2436,7 @@
       <c r="J50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="67.5" customHeight="1">
+      <c r="A51" s="11" t="n"/>
       <c r="C51" s="12" t="n">
         <v>47</v>
       </c>
@@ -2438,6 +2473,7 @@
       <c r="J51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="108" customHeight="1">
+      <c r="A52" s="11" t="n"/>
       <c r="C52" s="12" t="n">
         <v>48</v>
       </c>
@@ -2479,7 +2515,7 @@
       </c>
     </row>
     <row r="53" ht="135" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Ⅲ. 업무 확인 — 제도는 어떻고, 어떻게 처리하고, 몇 번 화면이고, 시장은 어떤가</t>
         </is>
@@ -2531,6 +2567,7 @@
       <c r="J53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="67.5" customHeight="1">
+      <c r="A54" s="11" t="n"/>
       <c r="C54" s="12" t="n">
         <v>50</v>
       </c>
@@ -2567,6 +2604,7 @@
       <c r="J54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="67.5" customHeight="1">
+      <c r="A55" s="11" t="n"/>
       <c r="C55" s="12" t="n">
         <v>51</v>
       </c>
@@ -2603,6 +2641,7 @@
       <c r="J55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="11" t="n"/>
       <c r="C56" s="12" t="n">
         <v>52</v>
       </c>
@@ -2639,6 +2678,7 @@
       <c r="J56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="54" customHeight="1">
+      <c r="A57" s="11" t="n"/>
       <c r="C57" s="12" t="n">
         <v>53</v>
       </c>
@@ -2672,6 +2712,7 @@
       <c r="J57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="81" customHeight="1">
+      <c r="A58" s="11" t="n"/>
       <c r="C58" s="12" t="n">
         <v>54</v>
       </c>
@@ -2709,6 +2750,7 @@
       <c r="J58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="54" customHeight="1">
+      <c r="A59" s="11" t="n"/>
       <c r="C59" s="12" t="n">
         <v>55</v>
       </c>
@@ -2747,6 +2789,7 @@
       <c r="J59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="67.5" customHeight="1">
+      <c r="A60" s="11" t="n"/>
       <c r="C60" s="12" t="n">
         <v>56</v>
       </c>
@@ -2784,6 +2827,7 @@
       <c r="J60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="67.5" customHeight="1">
+      <c r="A61" s="11" t="n"/>
       <c r="C61" s="12" t="n">
         <v>57</v>
       </c>
@@ -2820,6 +2864,7 @@
       <c r="J61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="94.5" customHeight="1">
+      <c r="A62" s="11" t="n"/>
       <c r="C62" s="12" t="n">
         <v>58</v>
       </c>
@@ -2856,6 +2901,7 @@
       <c r="J62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="81" customHeight="1">
+      <c r="A63" s="11" t="n"/>
       <c r="C63" s="12" t="n">
         <v>59</v>
       </c>
@@ -2892,6 +2938,7 @@
       <c r="J63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="40.5" customHeight="1">
+      <c r="A64" s="11" t="n"/>
       <c r="C64" s="12" t="n">
         <v>60</v>
       </c>
@@ -2928,6 +2975,7 @@
       <c r="J64" s="14" t="inlineStr"/>
     </row>
     <row r="65" hidden="1">
+      <c r="A65" s="11" t="n"/>
       <c r="C65" s="12" t="n">
         <v>61</v>
       </c>
@@ -2976,6 +3024,7 @@
       <c r="J65" s="14" t="inlineStr"/>
     </row>
     <row r="66" hidden="1">
+      <c r="A66" s="11" t="n"/>
       <c r="C66" s="12" t="n">
         <v>62</v>
       </c>
@@ -3025,6 +3074,7 @@
       <c r="J66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="135" customHeight="1">
+      <c r="A67" s="11" t="n"/>
       <c r="B67" s="18" t="inlineStr">
         <is>
           <t>10. 업무 처리 절차</t>
@@ -3069,6 +3119,7 @@
       <c r="J67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="54" customHeight="1">
+      <c r="A68" s="11" t="n"/>
       <c r="C68" s="12" t="n">
         <v>64</v>
       </c>
@@ -3107,6 +3158,7 @@
       <c r="J68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="40.5" customHeight="1">
+      <c r="A69" s="11" t="n"/>
       <c r="C69" s="12" t="n">
         <v>65</v>
       </c>
@@ -3143,6 +3195,7 @@
       <c r="J69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="135" customHeight="1">
+      <c r="A70" s="11" t="n"/>
       <c r="C70" s="12" t="n">
         <v>66</v>
       </c>
@@ -3182,6 +3235,7 @@
       <c r="J70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="54" customHeight="1">
+      <c r="A71" s="11" t="n"/>
       <c r="C71" s="12" t="n">
         <v>67</v>
       </c>
@@ -3218,6 +3272,7 @@
       <c r="J71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="27" customHeight="1">
+      <c r="A72" s="11" t="n"/>
       <c r="C72" s="12" t="n">
         <v>68</v>
       </c>
@@ -3254,6 +3309,7 @@
       <c r="J72" s="14" t="inlineStr"/>
     </row>
     <row r="73" hidden="1">
+      <c r="A73" s="11" t="n"/>
       <c r="C73" s="12" t="n">
         <v>69</v>
       </c>
@@ -3291,6 +3347,7 @@
       <c r="J73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="40.5" customHeight="1">
+      <c r="A74" s="11" t="n"/>
       <c r="C74" s="12" t="n">
         <v>70</v>
       </c>
@@ -3327,6 +3384,7 @@
       <c r="J74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="81" customHeight="1">
+      <c r="A75" s="11" t="n"/>
       <c r="C75" s="12" t="n">
         <v>71</v>
       </c>
@@ -3363,6 +3421,7 @@
       <c r="J75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="54" customHeight="1">
+      <c r="A76" s="11" t="n"/>
       <c r="C76" s="12" t="n">
         <v>72</v>
       </c>
@@ -3399,6 +3458,7 @@
       <c r="J76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="27" customHeight="1">
+      <c r="A77" s="11" t="n"/>
       <c r="B77" s="18" t="inlineStr">
         <is>
           <t>11. 단말 화면번호</t>
@@ -3440,6 +3500,7 @@
       <c r="J77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="121.5" customHeight="1">
+      <c r="A78" s="11" t="n"/>
       <c r="C78" s="12" t="n">
         <v>74</v>
       </c>
@@ -3479,6 +3540,7 @@
       <c r="J78" s="14" t="inlineStr"/>
     </row>
     <row r="79" hidden="1">
+      <c r="A79" s="11" t="n"/>
       <c r="C79" s="12" t="n">
         <v>75</v>
       </c>
@@ -3515,6 +3577,7 @@
       <c r="J79" s="14" t="inlineStr"/>
     </row>
     <row r="80" hidden="1">
+      <c r="A80" s="11" t="n"/>
       <c r="C80" s="12" t="n">
         <v>76</v>
       </c>
@@ -3553,6 +3616,7 @@
       <c r="J80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="11" t="n"/>
       <c r="C81" s="12" t="n">
         <v>77</v>
       </c>
@@ -3589,6 +3653,7 @@
       <c r="J81" s="14" t="inlineStr"/>
     </row>
     <row r="82" hidden="1">
+      <c r="A82" s="11" t="n"/>
       <c r="C82" s="12" t="n">
         <v>78</v>
       </c>
@@ -3625,6 +3690,7 @@
       <c r="J82" s="14" t="inlineStr"/>
     </row>
     <row r="83" hidden="1">
+      <c r="A83" s="11" t="n"/>
       <c r="C83" s="12" t="n">
         <v>79</v>
       </c>
@@ -3661,6 +3727,7 @@
       <c r="J83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="54" customHeight="1">
+      <c r="A84" s="11" t="n"/>
       <c r="B84" s="18" t="inlineStr">
         <is>
           <t>12. 비대면 채널 경로</t>
@@ -3702,6 +3769,7 @@
       <c r="J84" s="14" t="inlineStr"/>
     </row>
     <row r="85" ht="54" customHeight="1">
+      <c r="A85" s="11" t="n"/>
       <c r="C85" s="12" t="n">
         <v>81</v>
       </c>
@@ -3739,6 +3807,7 @@
       <c r="J85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="40.5" customHeight="1">
+      <c r="A86" s="11" t="n"/>
       <c r="C86" s="12" t="n">
         <v>82</v>
       </c>
@@ -3775,6 +3844,7 @@
       <c r="J86" s="14" t="inlineStr"/>
     </row>
     <row r="87" ht="54" customHeight="1">
+      <c r="A87" s="11" t="n"/>
       <c r="C87" s="12" t="n">
         <v>83</v>
       </c>
@@ -3811,6 +3881,7 @@
       <c r="J87" s="14" t="inlineStr"/>
     </row>
     <row r="88" hidden="1">
+      <c r="A88" s="11" t="n"/>
       <c r="C88" s="12" t="n">
         <v>84</v>
       </c>
@@ -3850,6 +3921,7 @@
       <c r="J88" s="14" t="inlineStr"/>
     </row>
     <row r="89" hidden="1">
+      <c r="A89" s="11" t="n"/>
       <c r="C89" s="12" t="n">
         <v>85</v>
       </c>
@@ -3886,6 +3958,7 @@
       <c r="J89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="81" customHeight="1">
+      <c r="A90" s="11" t="n"/>
       <c r="B90" s="18" t="inlineStr">
         <is>
           <t>13. 시황 — 상담에 쓰는 만큼</t>
@@ -3927,6 +4000,7 @@
       <c r="J90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="135" customHeight="1">
+      <c r="A91" s="11" t="n"/>
       <c r="C91" s="12" t="n">
         <v>87</v>
       </c>
@@ -3969,6 +4043,7 @@
       <c r="J91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="135" customHeight="1">
+      <c r="A92" s="11" t="n"/>
       <c r="C92" s="12" t="n">
         <v>88</v>
       </c>
@@ -4010,6 +4085,7 @@
       <c r="J92" s="14" t="inlineStr"/>
     </row>
     <row r="93" ht="94.5" customHeight="1">
+      <c r="A93" s="11" t="n"/>
       <c r="C93" s="12" t="n">
         <v>89</v>
       </c>
@@ -4046,6 +4122,7 @@
       <c r="J93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="135" customHeight="1">
+      <c r="A94" s="11" t="n"/>
       <c r="C94" s="12" t="n">
         <v>90</v>
       </c>
@@ -4088,7 +4165,7 @@
       <c r="J94" s="14" t="inlineStr"/>
     </row>
     <row r="95" ht="135" customHeight="1">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Ⅳ. 고객 응대 — 이 고객에게 무엇을 권할 수 있고, 어떻게 말할 것인가</t>
         </is>
@@ -4142,6 +4219,7 @@
       <c r="J95" s="9" t="inlineStr"/>
     </row>
     <row r="96" ht="135" customHeight="1">
+      <c r="A96" s="11" t="n"/>
       <c r="C96" s="12" t="n">
         <v>92</v>
       </c>
@@ -4189,6 +4267,7 @@
       </c>
     </row>
     <row r="97" hidden="1">
+      <c r="A97" s="11" t="n"/>
       <c r="C97" s="12" t="n">
         <v>93</v>
       </c>
@@ -4238,6 +4317,7 @@
       <c r="J97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="135" customHeight="1">
+      <c r="A98" s="11" t="n"/>
       <c r="C98" s="12" t="n">
         <v>94</v>
       </c>
@@ -4298,6 +4378,7 @@
       <c r="J98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="135" customHeight="1">
+      <c r="A99" s="11" t="n"/>
       <c r="C99" s="12" t="n">
         <v>95</v>
       </c>
@@ -4361,6 +4442,7 @@
       <c r="J99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="135" customHeight="1">
+      <c r="A100" s="11" t="n"/>
       <c r="C100" s="12" t="n">
         <v>96</v>
       </c>
@@ -4402,6 +4484,7 @@
       <c r="J100" s="14" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
+      <c r="A101" s="11" t="n"/>
       <c r="C101" s="12" t="n">
         <v>97</v>
       </c>
@@ -4453,6 +4536,7 @@
       <c r="J101" s="14" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
+      <c r="A102" s="11" t="n"/>
       <c r="B102" s="18" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4504,6 +4588,7 @@
       <c r="J102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="135" customHeight="1">
+      <c r="A103" s="11" t="n"/>
       <c r="C103" s="12" t="n">
         <v>99</v>
       </c>
@@ -4582,6 +4667,7 @@
       <c r="J103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="94.5" customHeight="1">
+      <c r="A104" s="11" t="n"/>
       <c r="C104" s="12" t="n">
         <v>100</v>
       </c>
@@ -4618,6 +4704,7 @@
       <c r="J104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="135" customHeight="1">
+      <c r="A105" s="11" t="n"/>
       <c r="C105" s="12" t="n">
         <v>101</v>
       </c>
@@ -4693,6 +4780,7 @@
       <c r="J105" s="14" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
+      <c r="A106" s="11" t="n"/>
       <c r="C106" s="12" t="n">
         <v>102</v>
       </c>
@@ -4729,6 +4817,7 @@
       <c r="J106" s="14" t="inlineStr"/>
     </row>
     <row r="107" ht="135" customHeight="1">
+      <c r="A107" s="11" t="n"/>
       <c r="C107" s="12" t="n">
         <v>103</v>
       </c>
@@ -4770,6 +4859,7 @@
       <c r="J107" s="14" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
+      <c r="A108" s="11" t="n"/>
       <c r="B108" s="18" t="inlineStr">
         <is>
           <t>16. 세액공제 계산</t>
@@ -4811,6 +4901,7 @@
       <c r="J108" s="14" t="inlineStr"/>
     </row>
     <row r="109" ht="67.5" customHeight="1">
+      <c r="A109" s="11" t="n"/>
       <c r="C109" s="12" t="n">
         <v>105</v>
       </c>
@@ -4847,6 +4938,7 @@
       <c r="J109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="121.5" customHeight="1">
+      <c r="A110" s="11" t="n"/>
       <c r="C110" s="12" t="n">
         <v>106</v>
       </c>
@@ -4886,6 +4978,7 @@
       <c r="J110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="135" customHeight="1">
+      <c r="A111" s="11" t="n"/>
       <c r="C111" s="12" t="n">
         <v>107</v>
       </c>
@@ -4955,6 +5048,7 @@
       <c r="J111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="135" customHeight="1">
+      <c r="A112" s="11" t="n"/>
       <c r="C112" s="12" t="n">
         <v>108</v>
       </c>
@@ -4996,6 +5090,7 @@
       <c r="J112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="135" customHeight="1">
+      <c r="A113" s="11" t="n"/>
       <c r="C113" s="12" t="n">
         <v>109</v>
       </c>
@@ -5044,6 +5139,7 @@
       </c>
     </row>
     <row r="114" hidden="1">
+      <c r="A114" s="11" t="n"/>
       <c r="C114" s="12" t="n">
         <v>110</v>
       </c>
@@ -5087,6 +5183,7 @@
       </c>
     </row>
     <row r="115" ht="27" customHeight="1">
+      <c r="A115" s="11" t="n"/>
       <c r="C115" s="12" t="n">
         <v>111</v>
       </c>
@@ -5123,6 +5220,7 @@
       <c r="J115" s="14" t="inlineStr"/>
     </row>
     <row r="116" hidden="1">
+      <c r="A116" s="11" t="n"/>
       <c r="C116" s="12" t="n">
         <v>112</v>
       </c>
@@ -5159,6 +5257,7 @@
       <c r="J116" s="14" t="inlineStr"/>
     </row>
     <row r="117" hidden="1">
+      <c r="A117" s="11" t="n"/>
       <c r="C117" s="12" t="n">
         <v>113</v>
       </c>
@@ -5195,6 +5294,7 @@
       <c r="J117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="67.5" customHeight="1">
+      <c r="A118" s="11" t="n"/>
       <c r="B118" s="18" t="inlineStr">
         <is>
           <t>17. 상담 화법·반론 대응</t>
@@ -5236,6 +5336,7 @@
       <c r="J118" s="14" t="inlineStr"/>
     </row>
     <row r="119" ht="135" customHeight="1">
+      <c r="A119" s="11" t="n"/>
       <c r="C119" s="12" t="n">
         <v>115</v>
       </c>
@@ -5282,6 +5383,7 @@
       <c r="J119" s="14" t="inlineStr"/>
     </row>
     <row r="120" hidden="1">
+      <c r="A120" s="11" t="n"/>
       <c r="C120" s="12" t="n">
         <v>116</v>
       </c>
@@ -5321,6 +5423,7 @@
       <c r="J120" s="14" t="inlineStr"/>
     </row>
     <row r="121" ht="135" customHeight="1">
+      <c r="A121" s="11" t="n"/>
       <c r="C121" s="12" t="n">
         <v>117</v>
       </c>
@@ -5363,6 +5466,7 @@
       <c r="J121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="81" customHeight="1">
+      <c r="A122" s="11" t="n"/>
       <c r="C122" s="12" t="n">
         <v>118</v>
       </c>
@@ -5401,6 +5505,7 @@
       <c r="J122" s="14" t="inlineStr"/>
     </row>
     <row r="123" hidden="1">
+      <c r="A123" s="11" t="n"/>
       <c r="C123" s="12" t="n">
         <v>119</v>
       </c>
@@ -5439,6 +5544,7 @@
       <c r="J123" s="14" t="inlineStr"/>
     </row>
     <row r="124" hidden="1">
+      <c r="A124" s="11" t="n"/>
       <c r="C124" s="12" t="n">
         <v>120</v>
       </c>
@@ -5480,6 +5586,7 @@
       <c r="J124" s="14" t="inlineStr"/>
     </row>
     <row r="125" hidden="1">
+      <c r="A125" s="11" t="n"/>
       <c r="C125" s="12" t="n">
         <v>121</v>
       </c>
@@ -5516,6 +5623,7 @@
       <c r="J125" s="14" t="inlineStr"/>
     </row>
     <row r="126" hidden="1">
+      <c r="A126" s="11" t="n"/>
       <c r="C126" s="12" t="n">
         <v>122</v>
       </c>
@@ -5560,6 +5668,7 @@
       <c r="J126" s="14" t="inlineStr"/>
     </row>
     <row r="127" hidden="1">
+      <c r="A127" s="11" t="n"/>
       <c r="C127" s="12" t="n">
         <v>123</v>
       </c>
@@ -5596,6 +5705,7 @@
       <c r="J127" s="14" t="inlineStr"/>
     </row>
     <row r="128" hidden="1">
+      <c r="A128" s="11" t="n"/>
       <c r="C128" s="12" t="n">
         <v>124</v>
       </c>
@@ -5632,6 +5742,7 @@
       <c r="J128" s="14" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
+      <c r="A129" s="11" t="n"/>
       <c r="C129" s="12" t="n">
         <v>125</v>
       </c>
@@ -5669,6 +5780,7 @@
       <c r="J129" s="14" t="inlineStr"/>
     </row>
     <row r="130" hidden="1">
+      <c r="A130" s="11" t="n"/>
       <c r="C130" s="12" t="n">
         <v>126</v>
       </c>
@@ -5705,6 +5817,7 @@
       <c r="J130" s="14" t="inlineStr"/>
     </row>
     <row r="131" hidden="1">
+      <c r="A131" s="11" t="n"/>
       <c r="C131" s="12" t="n">
         <v>127</v>
       </c>
@@ -5743,6 +5856,7 @@
       <c r="J131" s="14" t="inlineStr"/>
     </row>
     <row r="132" hidden="1">
+      <c r="A132" s="11" t="n"/>
       <c r="C132" s="12" t="n">
         <v>128</v>
       </c>
@@ -5783,6 +5897,7 @@
       <c r="J132" s="14" t="inlineStr"/>
     </row>
     <row r="133" hidden="1">
+      <c r="A133" s="11" t="n"/>
       <c r="C133" s="12" t="n">
         <v>129</v>
       </c>
@@ -5822,6 +5937,7 @@
       <c r="J133" s="14" t="inlineStr"/>
     </row>
     <row r="134" ht="54" customHeight="1">
+      <c r="A134" s="11" t="n"/>
       <c r="C134" s="12" t="n">
         <v>130</v>
       </c>
@@ -5860,7 +5976,7 @@
       <c r="J134" s="14" t="inlineStr"/>
     </row>
     <row r="135" ht="135" customHeight="1">
-      <c r="A135" s="24" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>Ⅴ. 발송·화면 연계 — 문자·쪽지 문구를 만들고 발송 화면을 연다</t>
         </is>
@@ -5908,6 +6024,7 @@
       <c r="J135" s="9" t="inlineStr"/>
     </row>
     <row r="136" ht="121.5" customHeight="1">
+      <c r="A136" s="11" t="n"/>
       <c r="C136" s="12" t="n">
         <v>132</v>
       </c>
@@ -5952,6 +6069,7 @@
       </c>
     </row>
     <row r="137" ht="81" customHeight="1">
+      <c r="A137" s="11" t="n"/>
       <c r="C137" s="12" t="n">
         <v>133</v>
       </c>
@@ -5996,6 +6114,7 @@
       </c>
     </row>
     <row r="138" ht="135" customHeight="1">
+      <c r="A138" s="11" t="n"/>
       <c r="C138" s="12" t="n">
         <v>134</v>
       </c>
@@ -6038,6 +6157,7 @@
       </c>
     </row>
     <row r="139" ht="135" customHeight="1">
+      <c r="A139" s="11" t="n"/>
       <c r="C139" s="12" t="n">
         <v>135</v>
       </c>
@@ -6088,6 +6208,7 @@
       </c>
     </row>
     <row r="140" hidden="1">
+      <c r="A140" s="11" t="n"/>
       <c r="C140" s="12" t="n">
         <v>136</v>
       </c>
@@ -6124,6 +6245,7 @@
       <c r="J140" s="14" t="inlineStr"/>
     </row>
     <row r="141" ht="121.5" customHeight="1">
+      <c r="A141" s="11" t="n"/>
       <c r="B141" s="18" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6174,6 +6296,7 @@
       </c>
     </row>
     <row r="142" hidden="1">
+      <c r="A142" s="11" t="n"/>
       <c r="C142" s="12" t="n">
         <v>138</v>
       </c>
@@ -6214,6 +6337,7 @@
       </c>
     </row>
     <row r="143" ht="67.5" customHeight="1">
+      <c r="A143" s="11" t="n"/>
       <c r="C143" s="12" t="n">
         <v>139</v>
       </c>
@@ -6254,6 +6378,7 @@
       </c>
     </row>
     <row r="144" hidden="1">
+      <c r="A144" s="11" t="n"/>
       <c r="C144" s="12" t="n">
         <v>140</v>
       </c>
@@ -6290,6 +6415,7 @@
       <c r="J144" s="14" t="inlineStr"/>
     </row>
     <row r="145" hidden="1">
+      <c r="A145" s="11" t="n"/>
       <c r="C145" s="12" t="n">
         <v>141</v>
       </c>
@@ -6330,7 +6456,7 @@
       </c>
     </row>
     <row r="146" hidden="1">
-      <c r="A146" s="24" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>Ⅵ. 대화 이어가기 — 앞서 물은 것을 이어받고, 방금 답을 고쳐 쓴다</t>
         </is>
@@ -6379,6 +6505,7 @@
       <c r="J146" s="9" t="inlineStr"/>
     </row>
     <row r="147" ht="27" customHeight="1">
+      <c r="A147" s="11" t="n"/>
       <c r="C147" s="12" t="n">
         <v>143</v>
       </c>
@@ -6419,6 +6546,7 @@
       </c>
     </row>
     <row r="148" ht="135" customHeight="1">
+      <c r="A148" s="11" t="n"/>
       <c r="C148" s="12" t="n">
         <v>144</v>
       </c>
@@ -6463,6 +6591,7 @@
       <c r="J148" s="14" t="inlineStr"/>
     </row>
     <row r="149" ht="81" customHeight="1">
+      <c r="A149" s="11" t="n"/>
       <c r="C149" s="12" t="n">
         <v>145</v>
       </c>
@@ -6499,6 +6628,7 @@
       <c r="J149" s="14" t="inlineStr"/>
     </row>
     <row r="150" ht="135" customHeight="1">
+      <c r="A150" s="11" t="n"/>
       <c r="C150" s="12" t="n">
         <v>146</v>
       </c>
@@ -6543,6 +6673,7 @@
       </c>
     </row>
     <row r="151" ht="27" customHeight="1">
+      <c r="A151" s="11" t="n"/>
       <c r="C151" s="12" t="n">
         <v>147</v>
       </c>
@@ -6583,6 +6714,7 @@
       </c>
     </row>
     <row r="152" hidden="1">
+      <c r="A152" s="11" t="n"/>
       <c r="C152" s="12" t="n">
         <v>148</v>
       </c>
@@ -6627,6 +6759,7 @@
       </c>
     </row>
     <row r="153" ht="54" customHeight="1">
+      <c r="A153" s="11" t="n"/>
       <c r="C153" s="12" t="n">
         <v>149</v>
       </c>
@@ -6669,6 +6802,7 @@
       </c>
     </row>
     <row r="154" hidden="1">
+      <c r="A154" s="11" t="n"/>
       <c r="C154" s="12" t="n">
         <v>150</v>
       </c>
@@ -6709,6 +6843,7 @@
       </c>
     </row>
     <row r="155" ht="81" customHeight="1">
+      <c r="A155" s="11" t="n"/>
       <c r="C155" s="12" t="n">
         <v>151</v>
       </c>
@@ -6750,6 +6885,7 @@
       </c>
     </row>
     <row r="156" hidden="1">
+      <c r="A156" s="11" t="n"/>
       <c r="C156" s="12" t="n">
         <v>152</v>
       </c>
@@ -6790,6 +6926,7 @@
       </c>
     </row>
     <row r="157" ht="54" customHeight="1">
+      <c r="A157" s="11" t="n"/>
       <c r="C157" s="12" t="n">
         <v>153</v>
       </c>
@@ -6830,6 +6967,7 @@
       </c>
     </row>
     <row r="158" hidden="1">
+      <c r="A158" s="11" t="n"/>
       <c r="C158" s="12" t="n">
         <v>154</v>
       </c>
@@ -6866,6 +7004,7 @@
       <c r="J158" s="14" t="inlineStr"/>
     </row>
     <row r="159" hidden="1">
+      <c r="A159" s="11" t="n"/>
       <c r="C159" s="12" t="n">
         <v>155</v>
       </c>
@@ -6902,6 +7041,7 @@
       </c>
     </row>
     <row r="160" ht="121.5" customHeight="1">
+      <c r="A160" s="11" t="n"/>
       <c r="B160" s="18" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
@@ -6950,6 +7090,7 @@
       </c>
     </row>
     <row r="161" ht="81" customHeight="1">
+      <c r="A161" s="11" t="n"/>
       <c r="C161" s="12" t="n">
         <v>157</v>
       </c>
@@ -6992,6 +7133,7 @@
       </c>
     </row>
     <row r="162" hidden="1">
+      <c r="A162" s="11" t="n"/>
       <c r="C162" s="12" t="n">
         <v>158</v>
       </c>
@@ -7032,6 +7174,7 @@
       </c>
     </row>
     <row r="163" ht="135" customHeight="1">
+      <c r="A163" s="11" t="n"/>
       <c r="C163" s="12" t="n">
         <v>159</v>
       </c>
@@ -7080,6 +7223,7 @@
       </c>
     </row>
     <row r="164" hidden="1">
+      <c r="A164" s="11" t="n"/>
       <c r="C164" s="12" t="n">
         <v>160</v>
       </c>
@@ -7122,6 +7266,7 @@
       </c>
     </row>
     <row r="165" hidden="1">
+      <c r="A165" s="11" t="n"/>
       <c r="C165" s="12" t="n">
         <v>161</v>
       </c>
@@ -7158,6 +7303,7 @@
       <c r="J165" s="14" t="inlineStr"/>
     </row>
     <row r="166" ht="135" customHeight="1">
+      <c r="A166" s="11" t="n"/>
       <c r="B166" s="18" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -7214,6 +7360,7 @@
       <c r="J166" s="14" t="inlineStr"/>
     </row>
     <row r="167" ht="135" customHeight="1">
+      <c r="A167" s="11" t="n"/>
       <c r="C167" s="12" t="n">
         <v>163</v>
       </c>
@@ -7267,6 +7414,7 @@
       <c r="J167" s="14" t="inlineStr"/>
     </row>
     <row r="168" ht="135" customHeight="1">
+      <c r="A168" s="11" t="n"/>
       <c r="C168" s="12" t="n">
         <v>164</v>
       </c>
@@ -7320,6 +7468,7 @@
       <c r="J168" s="14" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
+      <c r="A169" s="11" t="n"/>
       <c r="B169" s="18" t="inlineStr">
         <is>
           <t>23. 브리핑 수정</t>
@@ -7361,6 +7510,7 @@
       <c r="J169" s="14" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
+      <c r="A170" s="11" t="n"/>
       <c r="C170" s="12" t="n">
         <v>166</v>
       </c>
@@ -7397,6 +7547,7 @@
       <c r="J170" s="14" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
+      <c r="A171" s="11" t="n"/>
       <c r="C171" s="12" t="n">
         <v>167</v>
       </c>
@@ -7444,7 +7595,7 @@
       <c r="J171" s="14" t="inlineStr"/>
     </row>
     <row r="172" hidden="1">
-      <c r="A172" s="24" t="inlineStr">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>Ⅶ. 개발 회귀 — 도구 선택 · 실패 처리 · 고객별 대조</t>
         </is>
@@ -7499,6 +7650,7 @@
       <c r="J172" s="9" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
+      <c r="A173" s="11" t="n"/>
       <c r="C173" s="12" t="n">
         <v>169</v>
       </c>
@@ -7561,6 +7713,7 @@
       <c r="J173" s="14" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
+      <c r="A174" s="11" t="n"/>
       <c r="C174" s="12" t="n">
         <v>170</v>
       </c>
@@ -7610,6 +7763,7 @@
       <c r="J174" s="14" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
+      <c r="A175" s="11" t="n"/>
       <c r="C175" s="12" t="n">
         <v>171</v>
       </c>
@@ -7650,6 +7804,7 @@
       </c>
     </row>
     <row r="176" hidden="1">
+      <c r="A176" s="11" t="n"/>
       <c r="C176" s="12" t="n">
         <v>172</v>
       </c>
@@ -7686,6 +7841,7 @@
       <c r="J176" s="14" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
+      <c r="A177" s="11" t="n"/>
       <c r="C177" s="12" t="n">
         <v>173</v>
       </c>
@@ -7723,6 +7879,7 @@
       <c r="J177" s="14" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
+      <c r="A178" s="11" t="n"/>
       <c r="C178" s="12" t="n">
         <v>174</v>
       </c>
@@ -7759,6 +7916,7 @@
       <c r="J178" s="14" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
+      <c r="A179" s="11" t="n"/>
       <c r="C179" s="12" t="n">
         <v>175</v>
       </c>
@@ -7799,6 +7957,7 @@
       </c>
     </row>
     <row r="180" hidden="1">
+      <c r="A180" s="11" t="n"/>
       <c r="C180" s="12" t="n">
         <v>176</v>
       </c>
@@ -7835,6 +7994,7 @@
       <c r="J180" s="14" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
+      <c r="A181" s="11" t="n"/>
       <c r="B181" s="18" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -7878,6 +8038,7 @@
       <c r="J181" s="14" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
+      <c r="A182" s="11" t="n"/>
       <c r="C182" s="12" t="n">
         <v>178</v>
       </c>
@@ -7916,6 +8077,7 @@
       <c r="J182" s="14" t="inlineStr"/>
     </row>
     <row r="183" hidden="1">
+      <c r="A183" s="11" t="n"/>
       <c r="C183" s="12" t="n">
         <v>179</v>
       </c>
@@ -7952,6 +8114,7 @@
       <c r="J183" s="14" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
+      <c r="A184" s="11" t="n"/>
       <c r="C184" s="12" t="n">
         <v>180</v>
       </c>
@@ -7988,6 +8151,7 @@
       <c r="J184" s="14" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
+      <c r="A185" s="11" t="n"/>
       <c r="C185" s="12" t="n">
         <v>181</v>
       </c>
@@ -8029,6 +8193,7 @@
       <c r="J185" s="14" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
+      <c r="A186" s="11" t="n"/>
       <c r="C186" s="12" t="n">
         <v>182</v>
       </c>
@@ -8065,6 +8230,7 @@
       </c>
     </row>
     <row r="187" hidden="1">
+      <c r="A187" s="11" t="n"/>
       <c r="B187" s="18" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -8143,6 +8309,7 @@
       <c r="J187" s="14" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
+      <c r="A188" s="11" t="n"/>
       <c r="C188" s="12" t="n">
         <v>184</v>
       </c>
@@ -8182,6 +8349,7 @@
       <c r="J188" s="14" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
+      <c r="A189" s="11" t="n"/>
       <c r="C189" s="12" t="n">
         <v>185</v>
       </c>
@@ -8221,6 +8389,7 @@
       <c r="J189" s="14" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
+      <c r="A190" s="11" t="n"/>
       <c r="C190" s="12" t="n">
         <v>186</v>
       </c>
@@ -8260,6 +8429,7 @@
       <c r="J190" s="14" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
+      <c r="A191" s="11" t="n"/>
       <c r="C191" s="12" t="n">
         <v>187</v>
       </c>
@@ -8299,6 +8469,7 @@
       <c r="J191" s="14" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
+      <c r="A192" s="11" t="n"/>
       <c r="C192" s="12" t="n">
         <v>188</v>
       </c>
@@ -8339,6 +8510,7 @@
       <c r="J192" s="14" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
+      <c r="A193" s="11" t="n"/>
       <c r="C193" s="12" t="n">
         <v>189</v>
       </c>
@@ -8378,6 +8550,7 @@
       <c r="J193" s="14" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
+      <c r="A194" s="11" t="n"/>
       <c r="C194" s="12" t="n">
         <v>190</v>
       </c>
@@ -8417,6 +8590,7 @@
       <c r="J194" s="14" t="inlineStr"/>
     </row>
     <row r="195" hidden="1">
+      <c r="A195" s="11" t="n"/>
       <c r="C195" s="12" t="n">
         <v>191</v>
       </c>
@@ -8457,6 +8631,7 @@
       <c r="J195" s="14" t="inlineStr"/>
     </row>
     <row r="196" hidden="1">
+      <c r="A196" s="11" t="n"/>
       <c r="C196" s="12" t="n">
         <v>192</v>
       </c>
@@ -8496,12 +8671,13 @@
       <c r="J196" s="14" t="inlineStr"/>
     </row>
     <row r="197" hidden="1">
+      <c r="A197" s="11" t="n"/>
       <c r="C197" s="12" t="n">
         <v>193</v>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>예금만 들고 있는데 뭐라고 말해야 하지?</t>
+          <t>이 고객 정기예금 만기인데 뭐라고 안내하지?</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
@@ -8522,12 +8698,13 @@
       </c>
       <c r="I197" s="14" t="inlineStr">
         <is>
-          <t>경험 없는 쪽은 원금보장 유지 + 금리만 올리는 제안, 있는 쪽은 일부 금액 운용 ↔ 둘에게 같은 화법이 나온다</t>
+          <t>경험 없는 쪽은 원금보장 유지 + 금리만 올리는 제안(저축은행 정기예금), 있는 쪽은 일부 금액만 추천펀드·TDF ↔ 둘에게 같은 화법이 나온다 · 두 카드를 섞어 답한다</t>
         </is>
       </c>
       <c r="J197" s="14" t="inlineStr"/>
     </row>
     <row r="198" hidden="1">
+      <c r="A198" s="11" t="n"/>
       <c r="C198" s="12" t="n">
         <v>194</v>
       </c>
@@ -8619,7 +8796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -97,11 +97,18 @@
         <color rgb="00BFA55A"/>
       </top>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00BFA55A"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,7 +624,7 @@
       </c>
     </row>
     <row r="5" ht="135" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ⅰ. 대상 선정 — 오늘 누구를 보고, 왜 그 사람인가</t>
         </is>
@@ -666,7 +676,6 @@
       <c r="J5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="11" t="n"/>
       <c r="C6" s="12" t="n">
         <v>2</v>
       </c>
@@ -698,7 +707,6 @@
       <c r="J6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="11" t="n"/>
       <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
@@ -735,7 +743,6 @@
       <c r="J7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="135" customHeight="1">
-      <c r="A8" s="11" t="n"/>
       <c r="C8" s="12" t="n">
         <v>4</v>
       </c>
@@ -778,7 +785,6 @@
       <c r="J8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="11" t="n"/>
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t>2. 고객군·관리 기준</t>
@@ -820,7 +826,6 @@
       <c r="J9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="11" t="n"/>
       <c r="C10" s="12" t="n">
         <v>6</v>
       </c>
@@ -857,7 +862,6 @@
       <c r="J10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="11" t="n"/>
       <c r="C11" s="12" t="n">
         <v>7</v>
       </c>
@@ -896,7 +900,6 @@
       <c r="J11" s="14" t="inlineStr"/>
     </row>
     <row r="12" hidden="1">
-      <c r="A12" s="11" t="n"/>
       <c r="C12" s="12" t="n">
         <v>8</v>
       </c>
@@ -936,7 +939,6 @@
       <c r="J12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="135" customHeight="1">
-      <c r="A13" s="11" t="n"/>
       <c r="C13" s="12" t="n">
         <v>9</v>
       </c>
@@ -973,7 +975,6 @@
       <c r="J13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="11" t="n"/>
       <c r="C14" s="12" t="n">
         <v>10</v>
       </c>
@@ -1010,7 +1011,6 @@
       <c r="J14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="135" customHeight="1">
-      <c r="A15" s="11" t="n"/>
       <c r="B15" s="18" t="inlineStr">
         <is>
           <t>3. 오늘의 타겟 목록</t>
@@ -1052,7 +1052,6 @@
       <c r="J15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="135" customHeight="1">
-      <c r="A16" s="11" t="n"/>
       <c r="C16" s="12" t="n">
         <v>12</v>
       </c>
@@ -1100,7 +1099,7 @@
       <c r="J16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Ⅱ. 고객 상태 — 이 고객이 지금 어떤 상태이고, 조심할 것은 무엇인가</t>
         </is>
@@ -1146,7 +1145,6 @@
       <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="94.5" customHeight="1">
-      <c r="A18" s="11" t="n"/>
       <c r="C18" s="12" t="n">
         <v>14</v>
       </c>
@@ -1186,7 +1184,6 @@
       <c r="J18" s="14" t="inlineStr"/>
     </row>
     <row r="19" hidden="1">
-      <c r="A19" s="11" t="n"/>
       <c r="C19" s="12" t="n">
         <v>15</v>
       </c>
@@ -1223,7 +1220,6 @@
       <c r="J19" s="14" t="inlineStr"/>
     </row>
     <row r="20" hidden="1">
-      <c r="A20" s="11" t="n"/>
       <c r="C20" s="12" t="n">
         <v>16</v>
       </c>
@@ -1260,7 +1256,6 @@
       <c r="J20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="94.5" customHeight="1">
-      <c r="A21" s="11" t="n"/>
       <c r="C21" s="12" t="n">
         <v>17</v>
       </c>
@@ -1300,7 +1295,6 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="81" customHeight="1">
-      <c r="A22" s="11" t="n"/>
       <c r="C22" s="12" t="n">
         <v>18</v>
       </c>
@@ -1340,7 +1334,6 @@
       <c r="J22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="11" t="n"/>
       <c r="C23" s="12" t="n">
         <v>19</v>
       </c>
@@ -1377,7 +1370,6 @@
       <c r="J23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="135" customHeight="1">
-      <c r="A24" s="11" t="n"/>
       <c r="C24" s="12" t="n">
         <v>20</v>
       </c>
@@ -1419,7 +1411,6 @@
       <c r="J24" s="14" t="inlineStr"/>
     </row>
     <row r="25" hidden="1">
-      <c r="A25" s="11" t="n"/>
       <c r="C25" s="12" t="n">
         <v>21</v>
       </c>
@@ -1458,7 +1449,6 @@
       <c r="J25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="11" t="n"/>
       <c r="C26" s="12" t="n">
         <v>22</v>
       </c>
@@ -1495,7 +1485,6 @@
       <c r="J26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="94.5" customHeight="1">
-      <c r="A27" s="11" t="n"/>
       <c r="C27" s="12" t="n">
         <v>23</v>
       </c>
@@ -1533,7 +1522,6 @@
       <c r="J27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="94.5" customHeight="1">
-      <c r="A28" s="11" t="n"/>
       <c r="C28" s="12" t="n">
         <v>24</v>
       </c>
@@ -1573,7 +1561,6 @@
       <c r="J28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="11" t="n"/>
       <c r="B29" s="18" t="inlineStr">
         <is>
           <t>5. 고객 계좌 상태 확인</t>
@@ -1615,7 +1602,6 @@
       <c r="J29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="67.5" customHeight="1">
-      <c r="A30" s="11" t="n"/>
       <c r="C30" s="12" t="n">
         <v>26</v>
       </c>
@@ -1648,7 +1634,6 @@
       <c r="J30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="11" t="n"/>
       <c r="C31" s="12" t="n">
         <v>27</v>
       </c>
@@ -1685,7 +1670,6 @@
       <c r="J31" s="14" t="inlineStr"/>
     </row>
     <row r="32" hidden="1">
-      <c r="A32" s="11" t="n"/>
       <c r="C32" s="12" t="n">
         <v>28</v>
       </c>
@@ -1722,7 +1706,6 @@
       <c r="J32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="121.5" customHeight="1">
-      <c r="A33" s="11" t="n"/>
       <c r="C33" s="12" t="n">
         <v>29</v>
       </c>
@@ -1762,7 +1745,6 @@
       <c r="J33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="11" t="n"/>
       <c r="C34" s="12" t="n">
         <v>30</v>
       </c>
@@ -1794,7 +1776,6 @@
       <c r="J34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="11" t="n"/>
       <c r="C35" s="12" t="n">
         <v>31</v>
       </c>
@@ -1831,7 +1812,6 @@
       <c r="J35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="11" t="n"/>
       <c r="C36" s="12" t="n">
         <v>32</v>
       </c>
@@ -1868,7 +1848,6 @@
       <c r="J36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="11" t="n"/>
       <c r="C37" s="12" t="n">
         <v>33</v>
       </c>
@@ -1905,7 +1884,6 @@
       <c r="J37" s="14" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
-      <c r="A38" s="11" t="n"/>
       <c r="B38" s="18" t="inlineStr">
         <is>
           <t>6. 상담 이력 조회</t>
@@ -1947,7 +1925,6 @@
       <c r="J38" s="14" t="inlineStr"/>
     </row>
     <row r="39" hidden="1">
-      <c r="A39" s="11" t="n"/>
       <c r="C39" s="12" t="n">
         <v>35</v>
       </c>
@@ -1975,7 +1952,6 @@
       <c r="J39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="40.5" customHeight="1">
-      <c r="A40" s="11" t="n"/>
       <c r="C40" s="12" t="n">
         <v>36</v>
       </c>
@@ -2012,7 +1988,6 @@
       <c r="J40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="40.5" customHeight="1">
-      <c r="A41" s="11" t="n"/>
       <c r="C41" s="12" t="n">
         <v>37</v>
       </c>
@@ -2049,7 +2024,6 @@
       <c r="J41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="135" customHeight="1">
-      <c r="A42" s="11" t="n"/>
       <c r="B42" s="18" t="inlineStr">
         <is>
           <t>7. 금지·주의 안내</t>
@@ -2100,7 +2074,6 @@
       <c r="J42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="135" customHeight="1">
-      <c r="A43" s="11" t="n"/>
       <c r="C43" s="12" t="n">
         <v>39</v>
       </c>
@@ -2141,7 +2114,6 @@
       <c r="J43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="54" customHeight="1">
-      <c r="A44" s="11" t="n"/>
       <c r="C44" s="12" t="n">
         <v>40</v>
       </c>
@@ -2178,7 +2150,6 @@
       <c r="J44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="135" customHeight="1">
-      <c r="A45" s="11" t="n"/>
       <c r="C45" s="12" t="n">
         <v>41</v>
       </c>
@@ -2224,7 +2195,6 @@
       <c r="J45" s="14" t="inlineStr"/>
     </row>
     <row r="46" hidden="1">
-      <c r="A46" s="11" t="n"/>
       <c r="C46" s="12" t="n">
         <v>42</v>
       </c>
@@ -2261,7 +2231,6 @@
       <c r="J46" s="14" t="inlineStr"/>
     </row>
     <row r="47" hidden="1">
-      <c r="A47" s="11" t="n"/>
       <c r="C47" s="12" t="n">
         <v>43</v>
       </c>
@@ -2314,7 +2283,6 @@
       <c r="J47" s="14" t="inlineStr"/>
     </row>
     <row r="48" hidden="1">
-      <c r="A48" s="11" t="n"/>
       <c r="C48" s="12" t="n">
         <v>44</v>
       </c>
@@ -2352,7 +2320,6 @@
       <c r="J48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="40.5" customHeight="1">
-      <c r="A49" s="11" t="n"/>
       <c r="C49" s="12" t="n">
         <v>45</v>
       </c>
@@ -2394,7 +2361,6 @@
       </c>
     </row>
     <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="11" t="n"/>
       <c r="B50" s="18" t="inlineStr">
         <is>
           <t>8. 상담 준비 자료</t>
@@ -2436,7 +2402,6 @@
       <c r="J50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="67.5" customHeight="1">
-      <c r="A51" s="11" t="n"/>
       <c r="C51" s="12" t="n">
         <v>47</v>
       </c>
@@ -2473,7 +2438,6 @@
       <c r="J51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="108" customHeight="1">
-      <c r="A52" s="11" t="n"/>
       <c r="C52" s="12" t="n">
         <v>48</v>
       </c>
@@ -2515,7 +2479,7 @@
       </c>
     </row>
     <row r="53" ht="135" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>Ⅲ. 업무 확인 — 제도는 어떻고, 어떻게 처리하고, 몇 번 화면이고, 시장은 어떤가</t>
         </is>
@@ -2567,7 +2531,6 @@
       <c r="J53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="67.5" customHeight="1">
-      <c r="A54" s="11" t="n"/>
       <c r="C54" s="12" t="n">
         <v>50</v>
       </c>
@@ -2604,7 +2567,6 @@
       <c r="J54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="67.5" customHeight="1">
-      <c r="A55" s="11" t="n"/>
       <c r="C55" s="12" t="n">
         <v>51</v>
       </c>
@@ -2641,7 +2603,6 @@
       <c r="J55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="11" t="n"/>
       <c r="C56" s="12" t="n">
         <v>52</v>
       </c>
@@ -2678,7 +2639,6 @@
       <c r="J56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="54" customHeight="1">
-      <c r="A57" s="11" t="n"/>
       <c r="C57" s="12" t="n">
         <v>53</v>
       </c>
@@ -2712,7 +2672,6 @@
       <c r="J57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="81" customHeight="1">
-      <c r="A58" s="11" t="n"/>
       <c r="C58" s="12" t="n">
         <v>54</v>
       </c>
@@ -2750,7 +2709,6 @@
       <c r="J58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="54" customHeight="1">
-      <c r="A59" s="11" t="n"/>
       <c r="C59" s="12" t="n">
         <v>55</v>
       </c>
@@ -2789,7 +2747,6 @@
       <c r="J59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="67.5" customHeight="1">
-      <c r="A60" s="11" t="n"/>
       <c r="C60" s="12" t="n">
         <v>56</v>
       </c>
@@ -2827,7 +2784,6 @@
       <c r="J60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="67.5" customHeight="1">
-      <c r="A61" s="11" t="n"/>
       <c r="C61" s="12" t="n">
         <v>57</v>
       </c>
@@ -2864,7 +2820,6 @@
       <c r="J61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="94.5" customHeight="1">
-      <c r="A62" s="11" t="n"/>
       <c r="C62" s="12" t="n">
         <v>58</v>
       </c>
@@ -2901,7 +2856,6 @@
       <c r="J62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="81" customHeight="1">
-      <c r="A63" s="11" t="n"/>
       <c r="C63" s="12" t="n">
         <v>59</v>
       </c>
@@ -2938,7 +2892,6 @@
       <c r="J63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="40.5" customHeight="1">
-      <c r="A64" s="11" t="n"/>
       <c r="C64" s="12" t="n">
         <v>60</v>
       </c>
@@ -2975,7 +2928,6 @@
       <c r="J64" s="14" t="inlineStr"/>
     </row>
     <row r="65" hidden="1">
-      <c r="A65" s="11" t="n"/>
       <c r="C65" s="12" t="n">
         <v>61</v>
       </c>
@@ -3024,7 +2976,6 @@
       <c r="J65" s="14" t="inlineStr"/>
     </row>
     <row r="66" hidden="1">
-      <c r="A66" s="11" t="n"/>
       <c r="C66" s="12" t="n">
         <v>62</v>
       </c>
@@ -3074,7 +3025,6 @@
       <c r="J66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="135" customHeight="1">
-      <c r="A67" s="11" t="n"/>
       <c r="B67" s="18" t="inlineStr">
         <is>
           <t>10. 업무 처리 절차</t>
@@ -3119,7 +3069,6 @@
       <c r="J67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="54" customHeight="1">
-      <c r="A68" s="11" t="n"/>
       <c r="C68" s="12" t="n">
         <v>64</v>
       </c>
@@ -3158,7 +3107,6 @@
       <c r="J68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="40.5" customHeight="1">
-      <c r="A69" s="11" t="n"/>
       <c r="C69" s="12" t="n">
         <v>65</v>
       </c>
@@ -3195,7 +3143,6 @@
       <c r="J69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="135" customHeight="1">
-      <c r="A70" s="11" t="n"/>
       <c r="C70" s="12" t="n">
         <v>66</v>
       </c>
@@ -3235,7 +3182,6 @@
       <c r="J70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="54" customHeight="1">
-      <c r="A71" s="11" t="n"/>
       <c r="C71" s="12" t="n">
         <v>67</v>
       </c>
@@ -3272,7 +3218,6 @@
       <c r="J71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="11" t="n"/>
       <c r="C72" s="12" t="n">
         <v>68</v>
       </c>
@@ -3309,7 +3254,6 @@
       <c r="J72" s="14" t="inlineStr"/>
     </row>
     <row r="73" hidden="1">
-      <c r="A73" s="11" t="n"/>
       <c r="C73" s="12" t="n">
         <v>69</v>
       </c>
@@ -3347,7 +3291,6 @@
       <c r="J73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="40.5" customHeight="1">
-      <c r="A74" s="11" t="n"/>
       <c r="C74" s="12" t="n">
         <v>70</v>
       </c>
@@ -3384,7 +3327,6 @@
       <c r="J74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="81" customHeight="1">
-      <c r="A75" s="11" t="n"/>
       <c r="C75" s="12" t="n">
         <v>71</v>
       </c>
@@ -3421,7 +3363,6 @@
       <c r="J75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="54" customHeight="1">
-      <c r="A76" s="11" t="n"/>
       <c r="C76" s="12" t="n">
         <v>72</v>
       </c>
@@ -3458,7 +3399,6 @@
       <c r="J76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="27" customHeight="1">
-      <c r="A77" s="11" t="n"/>
       <c r="B77" s="18" t="inlineStr">
         <is>
           <t>11. 단말 화면번호</t>
@@ -3500,7 +3440,6 @@
       <c r="J77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="121.5" customHeight="1">
-      <c r="A78" s="11" t="n"/>
       <c r="C78" s="12" t="n">
         <v>74</v>
       </c>
@@ -3540,7 +3479,6 @@
       <c r="J78" s="14" t="inlineStr"/>
     </row>
     <row r="79" hidden="1">
-      <c r="A79" s="11" t="n"/>
       <c r="C79" s="12" t="n">
         <v>75</v>
       </c>
@@ -3577,7 +3515,6 @@
       <c r="J79" s="14" t="inlineStr"/>
     </row>
     <row r="80" hidden="1">
-      <c r="A80" s="11" t="n"/>
       <c r="C80" s="12" t="n">
         <v>76</v>
       </c>
@@ -3616,7 +3553,6 @@
       <c r="J80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="27" customHeight="1">
-      <c r="A81" s="11" t="n"/>
       <c r="C81" s="12" t="n">
         <v>77</v>
       </c>
@@ -3653,7 +3589,6 @@
       <c r="J81" s="14" t="inlineStr"/>
     </row>
     <row r="82" hidden="1">
-      <c r="A82" s="11" t="n"/>
       <c r="C82" s="12" t="n">
         <v>78</v>
       </c>
@@ -3690,7 +3625,6 @@
       <c r="J82" s="14" t="inlineStr"/>
     </row>
     <row r="83" hidden="1">
-      <c r="A83" s="11" t="n"/>
       <c r="C83" s="12" t="n">
         <v>79</v>
       </c>
@@ -3727,7 +3661,6 @@
       <c r="J83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="54" customHeight="1">
-      <c r="A84" s="11" t="n"/>
       <c r="B84" s="18" t="inlineStr">
         <is>
           <t>12. 비대면 채널 경로</t>
@@ -3769,7 +3702,6 @@
       <c r="J84" s="14" t="inlineStr"/>
     </row>
     <row r="85" ht="54" customHeight="1">
-      <c r="A85" s="11" t="n"/>
       <c r="C85" s="12" t="n">
         <v>81</v>
       </c>
@@ -3807,7 +3739,6 @@
       <c r="J85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="40.5" customHeight="1">
-      <c r="A86" s="11" t="n"/>
       <c r="C86" s="12" t="n">
         <v>82</v>
       </c>
@@ -3844,7 +3775,6 @@
       <c r="J86" s="14" t="inlineStr"/>
     </row>
     <row r="87" ht="54" customHeight="1">
-      <c r="A87" s="11" t="n"/>
       <c r="C87" s="12" t="n">
         <v>83</v>
       </c>
@@ -3881,7 +3811,6 @@
       <c r="J87" s="14" t="inlineStr"/>
     </row>
     <row r="88" hidden="1">
-      <c r="A88" s="11" t="n"/>
       <c r="C88" s="12" t="n">
         <v>84</v>
       </c>
@@ -3921,7 +3850,6 @@
       <c r="J88" s="14" t="inlineStr"/>
     </row>
     <row r="89" hidden="1">
-      <c r="A89" s="11" t="n"/>
       <c r="C89" s="12" t="n">
         <v>85</v>
       </c>
@@ -3958,7 +3886,6 @@
       <c r="J89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="81" customHeight="1">
-      <c r="A90" s="11" t="n"/>
       <c r="B90" s="18" t="inlineStr">
         <is>
           <t>13. 시황 — 상담에 쓰는 만큼</t>
@@ -4000,7 +3927,6 @@
       <c r="J90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="135" customHeight="1">
-      <c r="A91" s="11" t="n"/>
       <c r="C91" s="12" t="n">
         <v>87</v>
       </c>
@@ -4043,7 +3969,6 @@
       <c r="J91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="135" customHeight="1">
-      <c r="A92" s="11" t="n"/>
       <c r="C92" s="12" t="n">
         <v>88</v>
       </c>
@@ -4085,7 +4010,6 @@
       <c r="J92" s="14" t="inlineStr"/>
     </row>
     <row r="93" ht="94.5" customHeight="1">
-      <c r="A93" s="11" t="n"/>
       <c r="C93" s="12" t="n">
         <v>89</v>
       </c>
@@ -4122,7 +4046,6 @@
       <c r="J93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="135" customHeight="1">
-      <c r="A94" s="11" t="n"/>
       <c r="C94" s="12" t="n">
         <v>90</v>
       </c>
@@ -4165,7 +4088,7 @@
       <c r="J94" s="14" t="inlineStr"/>
     </row>
     <row r="95" ht="135" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="24" t="inlineStr">
         <is>
           <t>Ⅳ. 고객 응대 — 이 고객에게 무엇을 권할 수 있고, 어떻게 말할 것인가</t>
         </is>
@@ -4219,7 +4142,6 @@
       <c r="J95" s="9" t="inlineStr"/>
     </row>
     <row r="96" ht="135" customHeight="1">
-      <c r="A96" s="11" t="n"/>
       <c r="C96" s="12" t="n">
         <v>92</v>
       </c>
@@ -4267,7 +4189,6 @@
       </c>
     </row>
     <row r="97" hidden="1">
-      <c r="A97" s="11" t="n"/>
       <c r="C97" s="12" t="n">
         <v>93</v>
       </c>
@@ -4317,7 +4238,6 @@
       <c r="J97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="135" customHeight="1">
-      <c r="A98" s="11" t="n"/>
       <c r="C98" s="12" t="n">
         <v>94</v>
       </c>
@@ -4378,7 +4298,6 @@
       <c r="J98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="135" customHeight="1">
-      <c r="A99" s="11" t="n"/>
       <c r="C99" s="12" t="n">
         <v>95</v>
       </c>
@@ -4442,7 +4361,6 @@
       <c r="J99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="135" customHeight="1">
-      <c r="A100" s="11" t="n"/>
       <c r="C100" s="12" t="n">
         <v>96</v>
       </c>
@@ -4484,7 +4402,6 @@
       <c r="J100" s="14" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="11" t="n"/>
       <c r="C101" s="12" t="n">
         <v>97</v>
       </c>
@@ -4536,7 +4453,6 @@
       <c r="J101" s="14" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
-      <c r="A102" s="11" t="n"/>
       <c r="B102" s="18" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4588,7 +4504,6 @@
       <c r="J102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="135" customHeight="1">
-      <c r="A103" s="11" t="n"/>
       <c r="C103" s="12" t="n">
         <v>99</v>
       </c>
@@ -4667,7 +4582,6 @@
       <c r="J103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="94.5" customHeight="1">
-      <c r="A104" s="11" t="n"/>
       <c r="C104" s="12" t="n">
         <v>100</v>
       </c>
@@ -4704,7 +4618,6 @@
       <c r="J104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="135" customHeight="1">
-      <c r="A105" s="11" t="n"/>
       <c r="C105" s="12" t="n">
         <v>101</v>
       </c>
@@ -4780,7 +4693,6 @@
       <c r="J105" s="14" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
-      <c r="A106" s="11" t="n"/>
       <c r="C106" s="12" t="n">
         <v>102</v>
       </c>
@@ -4817,7 +4729,6 @@
       <c r="J106" s="14" t="inlineStr"/>
     </row>
     <row r="107" ht="135" customHeight="1">
-      <c r="A107" s="11" t="n"/>
       <c r="C107" s="12" t="n">
         <v>103</v>
       </c>
@@ -4859,7 +4770,6 @@
       <c r="J107" s="14" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
-      <c r="A108" s="11" t="n"/>
       <c r="B108" s="18" t="inlineStr">
         <is>
           <t>16. 세액공제 계산</t>
@@ -4901,7 +4811,6 @@
       <c r="J108" s="14" t="inlineStr"/>
     </row>
     <row r="109" ht="67.5" customHeight="1">
-      <c r="A109" s="11" t="n"/>
       <c r="C109" s="12" t="n">
         <v>105</v>
       </c>
@@ -4938,7 +4847,6 @@
       <c r="J109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="121.5" customHeight="1">
-      <c r="A110" s="11" t="n"/>
       <c r="C110" s="12" t="n">
         <v>106</v>
       </c>
@@ -4978,7 +4886,6 @@
       <c r="J110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="135" customHeight="1">
-      <c r="A111" s="11" t="n"/>
       <c r="C111" s="12" t="n">
         <v>107</v>
       </c>
@@ -5048,7 +4955,6 @@
       <c r="J111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="135" customHeight="1">
-      <c r="A112" s="11" t="n"/>
       <c r="C112" s="12" t="n">
         <v>108</v>
       </c>
@@ -5090,7 +4996,6 @@
       <c r="J112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="135" customHeight="1">
-      <c r="A113" s="11" t="n"/>
       <c r="C113" s="12" t="n">
         <v>109</v>
       </c>
@@ -5139,7 +5044,6 @@
       </c>
     </row>
     <row r="114" hidden="1">
-      <c r="A114" s="11" t="n"/>
       <c r="C114" s="12" t="n">
         <v>110</v>
       </c>
@@ -5183,7 +5087,6 @@
       </c>
     </row>
     <row r="115" ht="27" customHeight="1">
-      <c r="A115" s="11" t="n"/>
       <c r="C115" s="12" t="n">
         <v>111</v>
       </c>
@@ -5220,7 +5123,6 @@
       <c r="J115" s="14" t="inlineStr"/>
     </row>
     <row r="116" hidden="1">
-      <c r="A116" s="11" t="n"/>
       <c r="C116" s="12" t="n">
         <v>112</v>
       </c>
@@ -5257,7 +5159,6 @@
       <c r="J116" s="14" t="inlineStr"/>
     </row>
     <row r="117" hidden="1">
-      <c r="A117" s="11" t="n"/>
       <c r="C117" s="12" t="n">
         <v>113</v>
       </c>
@@ -5294,7 +5195,6 @@
       <c r="J117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="67.5" customHeight="1">
-      <c r="A118" s="11" t="n"/>
       <c r="B118" s="18" t="inlineStr">
         <is>
           <t>17. 상담 화법·반론 대응</t>
@@ -5336,7 +5236,6 @@
       <c r="J118" s="14" t="inlineStr"/>
     </row>
     <row r="119" ht="135" customHeight="1">
-      <c r="A119" s="11" t="n"/>
       <c r="C119" s="12" t="n">
         <v>115</v>
       </c>
@@ -5383,7 +5282,6 @@
       <c r="J119" s="14" t="inlineStr"/>
     </row>
     <row r="120" hidden="1">
-      <c r="A120" s="11" t="n"/>
       <c r="C120" s="12" t="n">
         <v>116</v>
       </c>
@@ -5423,7 +5321,6 @@
       <c r="J120" s="14" t="inlineStr"/>
     </row>
     <row r="121" ht="135" customHeight="1">
-      <c r="A121" s="11" t="n"/>
       <c r="C121" s="12" t="n">
         <v>117</v>
       </c>
@@ -5466,7 +5363,6 @@
       <c r="J121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="81" customHeight="1">
-      <c r="A122" s="11" t="n"/>
       <c r="C122" s="12" t="n">
         <v>118</v>
       </c>
@@ -5505,7 +5401,6 @@
       <c r="J122" s="14" t="inlineStr"/>
     </row>
     <row r="123" hidden="1">
-      <c r="A123" s="11" t="n"/>
       <c r="C123" s="12" t="n">
         <v>119</v>
       </c>
@@ -5544,7 +5439,6 @@
       <c r="J123" s="14" t="inlineStr"/>
     </row>
     <row r="124" hidden="1">
-      <c r="A124" s="11" t="n"/>
       <c r="C124" s="12" t="n">
         <v>120</v>
       </c>
@@ -5586,7 +5480,6 @@
       <c r="J124" s="14" t="inlineStr"/>
     </row>
     <row r="125" hidden="1">
-      <c r="A125" s="11" t="n"/>
       <c r="C125" s="12" t="n">
         <v>121</v>
       </c>
@@ -5623,7 +5516,6 @@
       <c r="J125" s="14" t="inlineStr"/>
     </row>
     <row r="126" hidden="1">
-      <c r="A126" s="11" t="n"/>
       <c r="C126" s="12" t="n">
         <v>122</v>
       </c>
@@ -5668,7 +5560,6 @@
       <c r="J126" s="14" t="inlineStr"/>
     </row>
     <row r="127" hidden="1">
-      <c r="A127" s="11" t="n"/>
       <c r="C127" s="12" t="n">
         <v>123</v>
       </c>
@@ -5705,7 +5596,6 @@
       <c r="J127" s="14" t="inlineStr"/>
     </row>
     <row r="128" hidden="1">
-      <c r="A128" s="11" t="n"/>
       <c r="C128" s="12" t="n">
         <v>124</v>
       </c>
@@ -5742,7 +5632,6 @@
       <c r="J128" s="14" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
-      <c r="A129" s="11" t="n"/>
       <c r="C129" s="12" t="n">
         <v>125</v>
       </c>
@@ -5780,7 +5669,6 @@
       <c r="J129" s="14" t="inlineStr"/>
     </row>
     <row r="130" hidden="1">
-      <c r="A130" s="11" t="n"/>
       <c r="C130" s="12" t="n">
         <v>126</v>
       </c>
@@ -5817,7 +5705,6 @@
       <c r="J130" s="14" t="inlineStr"/>
     </row>
     <row r="131" hidden="1">
-      <c r="A131" s="11" t="n"/>
       <c r="C131" s="12" t="n">
         <v>127</v>
       </c>
@@ -5856,7 +5743,6 @@
       <c r="J131" s="14" t="inlineStr"/>
     </row>
     <row r="132" hidden="1">
-      <c r="A132" s="11" t="n"/>
       <c r="C132" s="12" t="n">
         <v>128</v>
       </c>
@@ -5897,7 +5783,6 @@
       <c r="J132" s="14" t="inlineStr"/>
     </row>
     <row r="133" hidden="1">
-      <c r="A133" s="11" t="n"/>
       <c r="C133" s="12" t="n">
         <v>129</v>
       </c>
@@ -5937,7 +5822,6 @@
       <c r="J133" s="14" t="inlineStr"/>
     </row>
     <row r="134" ht="54" customHeight="1">
-      <c r="A134" s="11" t="n"/>
       <c r="C134" s="12" t="n">
         <v>130</v>
       </c>
@@ -5976,7 +5860,7 @@
       <c r="J134" s="14" t="inlineStr"/>
     </row>
     <row r="135" ht="135" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="24" t="inlineStr">
         <is>
           <t>Ⅴ. 발송·화면 연계 — 문자·쪽지 문구를 만들고 발송 화면을 연다</t>
         </is>
@@ -6024,7 +5908,6 @@
       <c r="J135" s="9" t="inlineStr"/>
     </row>
     <row r="136" ht="121.5" customHeight="1">
-      <c r="A136" s="11" t="n"/>
       <c r="C136" s="12" t="n">
         <v>132</v>
       </c>
@@ -6069,7 +5952,6 @@
       </c>
     </row>
     <row r="137" ht="81" customHeight="1">
-      <c r="A137" s="11" t="n"/>
       <c r="C137" s="12" t="n">
         <v>133</v>
       </c>
@@ -6114,7 +5996,6 @@
       </c>
     </row>
     <row r="138" ht="135" customHeight="1">
-      <c r="A138" s="11" t="n"/>
       <c r="C138" s="12" t="n">
         <v>134</v>
       </c>
@@ -6157,7 +6038,6 @@
       </c>
     </row>
     <row r="139" ht="135" customHeight="1">
-      <c r="A139" s="11" t="n"/>
       <c r="C139" s="12" t="n">
         <v>135</v>
       </c>
@@ -6208,7 +6088,6 @@
       </c>
     </row>
     <row r="140" hidden="1">
-      <c r="A140" s="11" t="n"/>
       <c r="C140" s="12" t="n">
         <v>136</v>
       </c>
@@ -6245,7 +6124,6 @@
       <c r="J140" s="14" t="inlineStr"/>
     </row>
     <row r="141" ht="121.5" customHeight="1">
-      <c r="A141" s="11" t="n"/>
       <c r="B141" s="18" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6296,7 +6174,6 @@
       </c>
     </row>
     <row r="142" hidden="1">
-      <c r="A142" s="11" t="n"/>
       <c r="C142" s="12" t="n">
         <v>138</v>
       </c>
@@ -6337,7 +6214,6 @@
       </c>
     </row>
     <row r="143" ht="67.5" customHeight="1">
-      <c r="A143" s="11" t="n"/>
       <c r="C143" s="12" t="n">
         <v>139</v>
       </c>
@@ -6378,7 +6254,6 @@
       </c>
     </row>
     <row r="144" hidden="1">
-      <c r="A144" s="11" t="n"/>
       <c r="C144" s="12" t="n">
         <v>140</v>
       </c>
@@ -6415,7 +6290,6 @@
       <c r="J144" s="14" t="inlineStr"/>
     </row>
     <row r="145" hidden="1">
-      <c r="A145" s="11" t="n"/>
       <c r="C145" s="12" t="n">
         <v>141</v>
       </c>
@@ -6456,7 +6330,7 @@
       </c>
     </row>
     <row r="146" hidden="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="A146" s="24" t="inlineStr">
         <is>
           <t>Ⅵ. 대화 이어가기 — 앞서 물은 것을 이어받고, 방금 답을 고쳐 쓴다</t>
         </is>
@@ -6505,7 +6379,6 @@
       <c r="J146" s="9" t="inlineStr"/>
     </row>
     <row r="147" ht="27" customHeight="1">
-      <c r="A147" s="11" t="n"/>
       <c r="C147" s="12" t="n">
         <v>143</v>
       </c>
@@ -6546,7 +6419,6 @@
       </c>
     </row>
     <row r="148" ht="135" customHeight="1">
-      <c r="A148" s="11" t="n"/>
       <c r="C148" s="12" t="n">
         <v>144</v>
       </c>
@@ -6591,7 +6463,6 @@
       <c r="J148" s="14" t="inlineStr"/>
     </row>
     <row r="149" ht="81" customHeight="1">
-      <c r="A149" s="11" t="n"/>
       <c r="C149" s="12" t="n">
         <v>145</v>
       </c>
@@ -6628,7 +6499,6 @@
       <c r="J149" s="14" t="inlineStr"/>
     </row>
     <row r="150" ht="135" customHeight="1">
-      <c r="A150" s="11" t="n"/>
       <c r="C150" s="12" t="n">
         <v>146</v>
       </c>
@@ -6673,7 +6543,6 @@
       </c>
     </row>
     <row r="151" ht="27" customHeight="1">
-      <c r="A151" s="11" t="n"/>
       <c r="C151" s="12" t="n">
         <v>147</v>
       </c>
@@ -6714,7 +6583,6 @@
       </c>
     </row>
     <row r="152" hidden="1">
-      <c r="A152" s="11" t="n"/>
       <c r="C152" s="12" t="n">
         <v>148</v>
       </c>
@@ -6759,7 +6627,6 @@
       </c>
     </row>
     <row r="153" ht="54" customHeight="1">
-      <c r="A153" s="11" t="n"/>
       <c r="C153" s="12" t="n">
         <v>149</v>
       </c>
@@ -6802,7 +6669,6 @@
       </c>
     </row>
     <row r="154" hidden="1">
-      <c r="A154" s="11" t="n"/>
       <c r="C154" s="12" t="n">
         <v>150</v>
       </c>
@@ -6843,7 +6709,6 @@
       </c>
     </row>
     <row r="155" ht="81" customHeight="1">
-      <c r="A155" s="11" t="n"/>
       <c r="C155" s="12" t="n">
         <v>151</v>
       </c>
@@ -6885,7 +6750,6 @@
       </c>
     </row>
     <row r="156" hidden="1">
-      <c r="A156" s="11" t="n"/>
       <c r="C156" s="12" t="n">
         <v>152</v>
       </c>
@@ -6926,7 +6790,6 @@
       </c>
     </row>
     <row r="157" ht="54" customHeight="1">
-      <c r="A157" s="11" t="n"/>
       <c r="C157" s="12" t="n">
         <v>153</v>
       </c>
@@ -6967,7 +6830,6 @@
       </c>
     </row>
     <row r="158" hidden="1">
-      <c r="A158" s="11" t="n"/>
       <c r="C158" s="12" t="n">
         <v>154</v>
       </c>
@@ -7004,7 +6866,6 @@
       <c r="J158" s="14" t="inlineStr"/>
     </row>
     <row r="159" hidden="1">
-      <c r="A159" s="11" t="n"/>
       <c r="C159" s="12" t="n">
         <v>155</v>
       </c>
@@ -7041,7 +6902,6 @@
       </c>
     </row>
     <row r="160" ht="121.5" customHeight="1">
-      <c r="A160" s="11" t="n"/>
       <c r="B160" s="18" t="inlineStr">
         <is>
           <t>21. 답변 다듬기·되짚기</t>
@@ -7090,7 +6950,6 @@
       </c>
     </row>
     <row r="161" ht="81" customHeight="1">
-      <c r="A161" s="11" t="n"/>
       <c r="C161" s="12" t="n">
         <v>157</v>
       </c>
@@ -7133,7 +6992,6 @@
       </c>
     </row>
     <row r="162" hidden="1">
-      <c r="A162" s="11" t="n"/>
       <c r="C162" s="12" t="n">
         <v>158</v>
       </c>
@@ -7174,7 +7032,6 @@
       </c>
     </row>
     <row r="163" ht="135" customHeight="1">
-      <c r="A163" s="11" t="n"/>
       <c r="C163" s="12" t="n">
         <v>159</v>
       </c>
@@ -7223,7 +7080,6 @@
       </c>
     </row>
     <row r="164" hidden="1">
-      <c r="A164" s="11" t="n"/>
       <c r="C164" s="12" t="n">
         <v>160</v>
       </c>
@@ -7266,7 +7122,6 @@
       </c>
     </row>
     <row r="165" hidden="1">
-      <c r="A165" s="11" t="n"/>
       <c r="C165" s="12" t="n">
         <v>161</v>
       </c>
@@ -7303,7 +7158,6 @@
       <c r="J165" s="14" t="inlineStr"/>
     </row>
     <row r="166" ht="135" customHeight="1">
-      <c r="A166" s="11" t="n"/>
       <c r="B166" s="18" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -7360,7 +7214,6 @@
       <c r="J166" s="14" t="inlineStr"/>
     </row>
     <row r="167" ht="135" customHeight="1">
-      <c r="A167" s="11" t="n"/>
       <c r="C167" s="12" t="n">
         <v>163</v>
       </c>
@@ -7414,7 +7267,6 @@
       <c r="J167" s="14" t="inlineStr"/>
     </row>
     <row r="168" ht="135" customHeight="1">
-      <c r="A168" s="11" t="n"/>
       <c r="C168" s="12" t="n">
         <v>164</v>
       </c>
@@ -7468,7 +7320,6 @@
       <c r="J168" s="14" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
-      <c r="A169" s="11" t="n"/>
       <c r="B169" s="18" t="inlineStr">
         <is>
           <t>23. 브리핑 수정</t>
@@ -7510,7 +7361,6 @@
       <c r="J169" s="14" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
-      <c r="A170" s="11" t="n"/>
       <c r="C170" s="12" t="n">
         <v>166</v>
       </c>
@@ -7547,7 +7397,6 @@
       <c r="J170" s="14" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
-      <c r="A171" s="11" t="n"/>
       <c r="C171" s="12" t="n">
         <v>167</v>
       </c>
@@ -7595,7 +7444,7 @@
       <c r="J171" s="14" t="inlineStr"/>
     </row>
     <row r="172" hidden="1">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="A172" s="24" t="inlineStr">
         <is>
           <t>Ⅶ. 개발 회귀 — 도구 선택 · 실패 처리 · 고객별 대조</t>
         </is>
@@ -7650,7 +7499,6 @@
       <c r="J172" s="9" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
-      <c r="A173" s="11" t="n"/>
       <c r="C173" s="12" t="n">
         <v>169</v>
       </c>
@@ -7713,7 +7561,6 @@
       <c r="J173" s="14" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
-      <c r="A174" s="11" t="n"/>
       <c r="C174" s="12" t="n">
         <v>170</v>
       </c>
@@ -7763,7 +7610,6 @@
       <c r="J174" s="14" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
-      <c r="A175" s="11" t="n"/>
       <c r="C175" s="12" t="n">
         <v>171</v>
       </c>
@@ -7804,7 +7650,6 @@
       </c>
     </row>
     <row r="176" hidden="1">
-      <c r="A176" s="11" t="n"/>
       <c r="C176" s="12" t="n">
         <v>172</v>
       </c>
@@ -7841,7 +7686,6 @@
       <c r="J176" s="14" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
-      <c r="A177" s="11" t="n"/>
       <c r="C177" s="12" t="n">
         <v>173</v>
       </c>
@@ -7879,7 +7723,6 @@
       <c r="J177" s="14" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
-      <c r="A178" s="11" t="n"/>
       <c r="C178" s="12" t="n">
         <v>174</v>
       </c>
@@ -7916,7 +7759,6 @@
       <c r="J178" s="14" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
-      <c r="A179" s="11" t="n"/>
       <c r="C179" s="12" t="n">
         <v>175</v>
       </c>
@@ -7957,7 +7799,6 @@
       </c>
     </row>
     <row r="180" hidden="1">
-      <c r="A180" s="11" t="n"/>
       <c r="C180" s="12" t="n">
         <v>176</v>
       </c>
@@ -7994,7 +7835,6 @@
       <c r="J180" s="14" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
-      <c r="A181" s="11" t="n"/>
       <c r="B181" s="18" t="inlineStr">
         <is>
           <t>25. 실패·경계 처리</t>
@@ -8038,7 +7878,6 @@
       <c r="J181" s="14" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
-      <c r="A182" s="11" t="n"/>
       <c r="C182" s="12" t="n">
         <v>178</v>
       </c>
@@ -8077,7 +7916,6 @@
       <c r="J182" s="14" t="inlineStr"/>
     </row>
     <row r="183" hidden="1">
-      <c r="A183" s="11" t="n"/>
       <c r="C183" s="12" t="n">
         <v>179</v>
       </c>
@@ -8114,7 +7952,6 @@
       <c r="J183" s="14" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
-      <c r="A184" s="11" t="n"/>
       <c r="C184" s="12" t="n">
         <v>180</v>
       </c>
@@ -8151,7 +7988,6 @@
       <c r="J184" s="14" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
-      <c r="A185" s="11" t="n"/>
       <c r="C185" s="12" t="n">
         <v>181</v>
       </c>
@@ -8193,7 +8029,6 @@
       <c r="J185" s="14" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
-      <c r="A186" s="11" t="n"/>
       <c r="C186" s="12" t="n">
         <v>182</v>
       </c>
@@ -8230,7 +8065,6 @@
       </c>
     </row>
     <row r="187" hidden="1">
-      <c r="A187" s="11" t="n"/>
       <c r="B187" s="18" t="inlineStr">
         <is>
           <t>26. 고객별 대조</t>
@@ -8309,7 +8143,6 @@
       <c r="J187" s="14" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
-      <c r="A188" s="11" t="n"/>
       <c r="C188" s="12" t="n">
         <v>184</v>
       </c>
@@ -8349,7 +8182,6 @@
       <c r="J188" s="14" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
-      <c r="A189" s="11" t="n"/>
       <c r="C189" s="12" t="n">
         <v>185</v>
       </c>
@@ -8389,7 +8221,6 @@
       <c r="J189" s="14" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
-      <c r="A190" s="11" t="n"/>
       <c r="C190" s="12" t="n">
         <v>186</v>
       </c>
@@ -8429,7 +8260,6 @@
       <c r="J190" s="14" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
-      <c r="A191" s="11" t="n"/>
       <c r="C191" s="12" t="n">
         <v>187</v>
       </c>
@@ -8469,7 +8299,6 @@
       <c r="J191" s="14" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
-      <c r="A192" s="11" t="n"/>
       <c r="C192" s="12" t="n">
         <v>188</v>
       </c>
@@ -8510,7 +8339,6 @@
       <c r="J192" s="14" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
-      <c r="A193" s="11" t="n"/>
       <c r="C193" s="12" t="n">
         <v>189</v>
       </c>
@@ -8550,7 +8378,6 @@
       <c r="J193" s="14" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
-      <c r="A194" s="11" t="n"/>
       <c r="C194" s="12" t="n">
         <v>190</v>
       </c>
@@ -8590,7 +8417,6 @@
       <c r="J194" s="14" t="inlineStr"/>
     </row>
     <row r="195" hidden="1">
-      <c r="A195" s="11" t="n"/>
       <c r="C195" s="12" t="n">
         <v>191</v>
       </c>
@@ -8631,7 +8457,6 @@
       <c r="J195" s="14" t="inlineStr"/>
     </row>
     <row r="196" hidden="1">
-      <c r="A196" s="11" t="n"/>
       <c r="C196" s="12" t="n">
         <v>192</v>
       </c>
@@ -8671,7 +8496,6 @@
       <c r="J196" s="14" t="inlineStr"/>
     </row>
     <row r="197" hidden="1">
-      <c r="A197" s="11" t="n"/>
       <c r="C197" s="12" t="n">
         <v>193</v>
       </c>
@@ -8685,7 +8509,21 @@
           <t>박정호(펀드 경험 없음) ↔ 김현수(펀드 보유)</t>
         </is>
       </c>
-      <c r="F197" s="14" t="inlineStr"/>
+      <c r="F197" s="14" t="inlineStr">
+        <is>
+          <t>● 박정호
+정기예금 만기를 앞둔 안전자산 선호 성향의 고객에게는 원금 보장을 유지하면서 더 높은 금리의 상품으로 재예치하도록 안내하는 것이 핵심이에요.
+펀드 경험이 전무하고 원금 손실을 우려하는 성향인 만큼 "원금손실 걱정 때문이시죠?"라고 고객의 이유를 먼저 공감하며 짚어주는 방식으로 접근해야 해요.
+"저축은행 정기예금 상품은 은행별 차이가 있지만 일반은행 정기예금 대비 금리가 약 0.7~0.8% 높고 예금자보호도 5천만원까지 가능하여 자산관리에 관심있는 고객분들은 정기예금 운용시 저축은행 상품으로 주로 운용하고 계세요. 안전자산을 선호하시는 고객님께 딱 맞는 상품이니 이번 기회에 저축은행 정기예금으로 재예치 해보시는건 어떠세요?"
+통화 종료 후 스타뱅킹 URL을 통해 만기 한 달 전부터 예약변경 거래가 가능하다는 점을 함께 안내해 주세요.
+그 부분은 제가 가진 자료로는 확인이 어려워요.
+● 김현수
+원리금보장·현금성 자산 비중이 90%로 편중되어 있고 펀드 경험이 있는 고객에게는 만기 후 일부 금액의 포트폴리오 운용을 권유하는 방식으로 접근하는 게 핵심이에요.
+퇴직연금은 미래 은퇴 후 사용할 자산이니 좀더 길게 보시고 포트폴리오로 운용해 보시는 것이 좋다고 설명하면서, 지금 시장이 불안정하고 손실 날 가능성도 있지만 일부금액을 포트폴리오 차원으로 운용하시면 정기예금으로만 운용하실 때보다 높은 수익률을 기대하실 수 있다는 점을 안내해 보세요.
+통화 종료 후에 고객님께 문자메시지로 만기상품 예약변경 거래를 하실 수 있는 스타뱅킹 URL 링크를 보내드리고, 만기 한 달 전부터 예약거래가 가능하시니 URL로 접속하셔서 지금 예약거래를 하실 수 있다는 점을 함께 짚어 주세요.
+퇴직연금 상품 검색 시 'TDF상품'이나 '추천상품' 테마에 접속하시면 관련 상품을 찾으실 수 있을 거라고 안내해 주시면 돼요.</t>
+        </is>
+      </c>
       <c r="G197" s="17" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
@@ -8704,7 +8542,6 @@
       <c r="J197" s="14" t="inlineStr"/>
     </row>
     <row r="198" hidden="1">
-      <c r="A198" s="11" t="n"/>
       <c r="C198" s="12" t="n">
         <v>194</v>
       </c>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="질문리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="고객축_20260929" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="더미 고객 상세정보" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'질문리스트'!$A$4:$K$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'질문리스트'!$A$4:$L$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -547,20 +547,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:L198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="74" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="20" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="34" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="72" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="40" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="20" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="34" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="72" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -601,7 +602,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>앞 턴</t>
+          <t>앞 질문과 답</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -611,31 +612,36 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>실측 답변</t>
+          <t>AI 답변</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>시연</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대상 고객</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>확인 포인트</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>선행 질문</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1">
+    <row r="5" ht="202.5" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ⅰ. 대상 선정 — 오늘 누구를 보고, 왜 그 사람인가</t>
@@ -671,22 +677,23 @@
 최근 6개월 이상 접촉이 없고 12개월 이상 운용변경 이력이 없어서 포트폴리오 점검이 필요한 상태예요.</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194(요건 6개) ↔ 정민석 181245-3097614(요건 2개)</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>〔송도윤(요건 6개) ↔ 정민석(요건 2개)〕 성립 요건 **전부** + 왜 문제인지 ↔ 요건 하나만 말하거나 고객군 일반 정의로 샌다</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="C6" s="13" t="n">
@@ -703,24 +710,25 @@
           <t>이준호 고객님이 관리 대상으로 뜬 이유는 평가금액 1억 2,500만원, 운용수익률 13.7%로 동연령 평균 수익률 12.1%를 상회하고 있으나, 2026년 9월 10일 만기가 경과한 예금 4,050만원이 포함되어 있어 체계적인 포트폴리오 재점검이 필요하기 때문이에요.</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>〔이준호〕 9/29 기준 요건 0개 — 「타겟이 아니다」 ↔ 요건을 지어내거나 지난 만기를 「곧 만기」로 말한다</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="54" customHeight="1">
+      <c r="L6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7" ht="67.5" customHeight="1">
       <c r="C7" s="13" t="n">
         <v>3</v>
       </c>
@@ -740,24 +748,25 @@
           <t>박지민 고객님은 적극투자형 성향이지만 위험자산 비중이 75%로 DC·개인형IRP 투자한도인 70%를 초과하여 컴플라이언스 위반 점검 대상이 되었습니다. 이 규정 사항은 고객의 투자성향과 무관하게 한도 내로 조정해야 하므로 다른 위험자산 조정 전략에 흡수시키지 않고 우선적으로 해소해야 합니다. 위험자산 한도를 초과한 계좌를 해소하는 방법은 초과 금액을 정기예금 등 안전자산으로 교체매매하거나, 추가입금 후 안전자산으로 운용지시하여 분모를 늘려 비율을 해소하는 두 가지 방법이 있습니다.</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>요건의 뜻 + 임계값 + 할 일 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="135" customHeight="1">
+      <c r="L7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8" ht="229.5" customHeight="1">
       <c r="C8" s="13" t="n">
         <v>4</v>
       </c>
@@ -783,24 +792,25 @@
 고객에게 안내할 때는 고유계정대라는 생소한 용어 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 쓰도록 하세요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지는 말고, 운용 여건의 차이를 중심으로 설명해야 해요.</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>불일치 요건의 조건 + 이 고객 값 ↔ 조건을 지어낸다</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="54" customHeight="1">
+      <c r="L8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1">
       <c r="B9" s="20" t="inlineStr">
         <is>
           <t>2. 고객군·관리 기준</t>
@@ -825,22 +835,23 @@
           <t>적립금이 1천만원 미만이더라도 이 고객은 원리금보장·현금성 자산 비중이 90%로 편중되어 있고 디폴트옵션이 미설정되어 있어 관리 대상에 해당해요. 현재 고유계정대와 예금을 포함한 원리금보장·현금성 자산 비중이 높고 키움 더드림 단기채 수익률이 -6.4%를 기록하면서 전체 운용수익률이 -1.8%에 머물러 있는 상태예요. 이는 동연령 평균 수익률 10.2%와 비교해 저조한 수준이며, 위험자산 한도 70% 중 위험자산 비중이 0%로 나타나 포트폴리오 조정이 필요한 상태예요.</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>제외 안 함 — 「별도 요청 리스트」 구분일 뿐(룰베이스 원문) ↔ 대상에서 빼라고 답한다</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="67.5" customHeight="1">
       <c r="C10" s="13" t="n">
@@ -862,22 +873,23 @@
           <t>현금성자산이 많다고 해서 무조건 방치 자금으로 볼 수는 없어요. 현금성자산이 일정기간(1개월 이상) 금액변동 없이 유지 중이고 [04-12-644] 퇴직연금 거래내역조회 시 입금 사유가 '교체매매'나 '연금지급' 사유가 아닌 경우 미운용중인 자산이 있다고 안내해 보세요. 연금지급이나 교체매매 대기 중인 정상 자금일 수도 있으므로, 고객에게 접촉하기 전에 사용계획 자금인지 방치 자금인지 먼저 가르는 것이 판단 기준이에요. 상담 용어: "고유계정대" 대신 "현금성자산", "운용지시가 되지 않는 자산" 사용 (고객에게 생소한 용어 금지).</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr"/>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
           <t>1개월 변동 없으면 방치, 유입 있으면 이탈관찰 ↔ 비중 하나로 방치라고 단정한다</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="C11" s="13" t="n">
@@ -901,22 +913,23 @@
 · 투자 목적형</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
           <t>선정 조건 + 왜 문제인지(고객군 일반) ↔ 열려 있는 고객 값으로 답한다</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
     </row>
     <row r="12" hidden="1">
       <c r="C12" s="13" t="n">
@@ -941,24 +954,25 @@
 · 이탈위험 선별</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
           <t>임계값 + 세그먼트 원문 조건 ↔ 임계값을 지어낸다</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="135" customHeight="1">
+      <c r="L12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13" ht="216" customHeight="1">
       <c r="C13" s="13" t="n">
         <v>9</v>
       </c>
@@ -978,24 +992,25 @@
           <t>오늘 우선 관리해야 할 대상은 총 11명이며, 각 고객의 현황에 따른 선정 요건 순서대로 확인해야 해요. 윤가영 고객은 이탈위험 관찰(현금화 신호) 최근 1개월 +1억 7,000만원과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원 · 만기 경과 9일 · 당행, 운용변경 없음(12개월+) 14.4개월에 해당해요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 · 원리금보장 100%, 원리금보장상품 편중(80% 이상) 100%, 운용변경 없음(12개월+) 13.9개월이며, 최서윤 고객은 장기 미접촉 288일, 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원이 확인되며, 이수민 고객은 원리금보장상품 편중(80% 이상) 100%, 디폴트옵션 미설정, 만기예금 보유 D-18 · 7,000만원, 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원이 선정 요 이에요. 박정호 고객은 원리금보장상품 편중(80% 이상) 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원이며, 김현수는 원리금보장상품 편중(80% 이상) 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10 · 7,040만원, 연금개시 요건충족 후 미개시이며, 김서연 고객은 ISA 만기자금 보유 8,000만원 · D-1 · 타행, 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원이에요. 한지우 고객은 ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
           <t>판단 기준 + 도출 근거 ↔ 일반론으로 넘어간다</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="67.5" customHeight="1">
+      <c r="L13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14" ht="81" customHeight="1">
       <c r="C14" s="13" t="n">
         <v>10</v>
       </c>
@@ -1015,24 +1030,25 @@
           <t>만기 안내 전화할 때는 본부 공식 지침은 아니지만 영업점 현장에서 관찰된 방식을 활용할 수 있어요. 비율 대신 원 단위 금액으로 제시하는 것이 반복되는 성공 패턴이며, 계산이 상담의 성패를 가른다는 점을 참고해 보세요. 중도해지이율이 수수료율 합계보다 낮으면 원금에서 차감 지급된다는 점이나 지급까지 3영업일이 소요된다는 사실, 그리고 중도인출 신청액이 세전이라는 점을 미리 안내하지 않으면 민원으로 돌아올 수 있으니 사전에 고지하는 것이 중요해요. 만기 안내 전화 과정에서 수수료로 원금이 깨질 수 있는 부분이나 현금화 지연 가능성 같은 필수 고지 사항을 빠뜨리지 않도록 유의하세요.</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr"/>
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
           <t>현장 관찰 + 「본부 지침 아님」 표시 ↔ 본부 지침처럼 단정한다</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="135" customHeight="1">
+      <c r="L14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15" ht="202.5" customHeight="1">
       <c r="B15" s="20" t="inlineStr">
         <is>
           <t>3. 오늘의 타겟 목록</t>
@@ -1057,22 +1073,23 @@
           <t>오늘 집중해서 봐야 할 타겟 고객은 총 11명이에요. 순서대로 윤가영 고객은 최근 1개월 이탈위험 관찰(현금화 신호)과 디폴트옵션 미설정으로 선정되었고, 송도윤 고객은 장기 미접촉 358일, 판매중단·환매추천 펀드 보유 1건, 미운용 현금성자산 2억 8,000만원(53.8%), 디폴트옵션 미설정, ISA 만기자금 보유 1억 2,000만원(만기 경과 9일, 당행), 운용변경 없음 14.4개월로 선정되었어요. 정민석 고객은 장기 미접촉 221일, 투자성향 불일치 공격투자형 및 원리금보장 100%, 원리금보장상품 편중 100%, 운용변경 없음 13.9개월로 선정되었고, 최서윤 고객은 장기 미접촉 288일과 판매중단·환매추천 펀드 보유 1건으로 선정되었어요. 박지민 고객은 위험자산 한도 초과 위험자산 75%, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었고, 이수민 고객은 원리금보장상품 편중 100%, 디폴트옵션 미설정, 만기예금 보유 D-18(7,000만원), 세액공제 활용 가능 900만원, 추가입금 여력 보유 900만원으로 선정되었어요. 박정호 고객은 원리금보장상품 편중 100%, 연금개시 요건충족 후 미개시, 세액공제 활용 가능 600만원, 추가입금 여력 보유 600만원으로 선정되었고, 김현수 고객은 원리금보장상품 편중 90%, 미운용 현금성자산 600만원(75.0%), 디폴트옵션 미설정으로 선정되었어요. 오세훈 고객은 만기예금 보유 D-10(7,040만원), 연금개시 요건충족 후 미개시로 선정되었고, 김서연 고객은 ISA 만기자금 보유 8,000만원(D-1, 타행), 세액공제 활용 가능 500만원, 추가입금 여력 보유 500만원으로 선정되었으며, 한지우 고객은 ISA 만기자금 보유 8,000만원(만기 경과 24일, 타행), 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원으로 선정되었어요.</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
           <t>이름 + 순번 + 선정 요건 ↔ 「고객 화면을 먼저 열어달라」고 답하거나 브리핑과 다른 순서를 말한다</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
     </row>
     <row r="16" hidden="1">
       <c r="C16" s="13" t="n">
@@ -1105,22 +1122,23 @@
 - 한지우 — ISA 만기자금 보유 8,000만원 · 만기 경과 24일 · 타행, 세액공제 활용 가능 300만원, 추가입금 여력 보유 300만원</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr"/>
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
           <t>식별번호는 재료에 없다 — 이름·순번으로 ↔ 고객 식별번호를 답에 싣는다</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -1152,22 +1170,23 @@
           <t>송도윤 고객님의 평가금액은 5억 2,000만원이에요. 자료에 따르면 이 고객은 평가금액 5억 2,000만원의 대규모 자산을 보유하고 계시며, 운용수익률 32.6%를 기록하고 있어요.</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr"/>
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>물어본 값 하나 ↔ 화법·문제상황이 따라 나온다</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18" ht="94.5" customHeight="1">
       <c r="C18" s="13" t="n">
@@ -1192,22 +1211,23 @@
 송도윤 고객님의 고유계정대는 2억 8,000만원이며, 자산군별 비중은 53.8%예요. 고객에게 안내할 때는 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 표현을 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>김현수 173544-2074623·송도윤 188406-7352194 등</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>600만원 · 75% 둘 다 ↔ 「비중만 있고 금액은 없다」 · 반올림값과 원장값이 두 값이 된다</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
     </row>
     <row r="19" hidden="1">
       <c r="C19" s="13" t="n">
@@ -1229,22 +1249,23 @@
           <t>이 고객의 만기 예정 자산은 2026년 10월 9일에 도래하는 7,040만원 규모의 SBI저축은행 퇴직연금 정기예금 1년 상품과, 2027년 1-10에 도래하는 3,550만원 규모의 KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) 상품이 있어요. 만기 1개월 전 원리금보장상품을 보유하고 있어 정기예금 자동 재예치 제도가 폐지됨에 따라 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로 만기 전 운용 방향 확정이 필요해요.</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>만기 2건 3명 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>예금·GIC **전부** ↔ 가장 가까운 한 건만 답해 나머지가 없는 것이 된다</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
     </row>
     <row r="20" hidden="1">
       <c r="C20" s="13" t="n">
@@ -1266,22 +1287,23 @@
           <t>송도윤 고객님의 만기 일자는 2026년 9월 20일인 1억 2,000만원 규모의 당행 ISA 만기자금이 있다. 해당 자금은 만기가 경과한 상태이다.</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>만기 0건 2명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>만기 자산 없음 ↔ ISA 만기를 IRP 만기로 답한다</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="94.5" customHeight="1">
       <c r="C21" s="13" t="n">
@@ -1306,22 +1328,23 @@
 이수민 고객님의 만기일은 2026년 10월 17일이며, 해당 예금 금액은 7,000만원이다. 만기가 18일 앞으로 다가온 상태이니 만기 전 운용 방향을 확정할 수 있도록 안내해야 한다.</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>날짜와 금액을 재료 그대로 ↔ 잔여일수로 날짜를 계산해 지어낸다(수치 검사에 안 걸린다)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="81" customHeight="1">
       <c r="C22" s="13" t="n">
@@ -1346,24 +1369,25 @@
 한지우 고객님의 ISA 만기일은 2026년 9월 5일이고, 금액은 8,000만원이에요. 이 자금은 타행 ISA 만기자금이며 만기가 경과한 지 24일이 되었어요.</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr"/>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>ISA 는 **IRP 밖의 돈**이라 갈라 적는다 ↔ IRP 잔액에 합산해 부풀린다</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="40.5" customHeight="1">
+      <c r="L22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
       <c r="C23" s="13" t="n">
         <v>19</v>
       </c>
@@ -1383,24 +1407,25 @@
           <t>당해 납입액은 0원이고 세액공제 잔여한도는 900만원이 남았어요. 연 납입한도 1,800만원 중 당해 납입액이 없어 1,800만원의 납입 여력이 있는 상태예요. 세액공제 한도 900만원에 미달하는 고객인 만큼, 세액공제 잔여한도 900만원을 확인한 뒤 자동이체 금액 증액을 제안하거나 여유자금 발생 시점의 추가입금으로 예약을 남기는 순서로 설계해 보세요.</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="K23" s="16" t="inlineStr">
         <is>
           <t>당해 납입액 + 잔여한도 ↔ 화법 카드의 숫자(300)를 잔여한도로 붙인다</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="135" customHeight="1">
+      <c r="L23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24" ht="175.5" customHeight="1">
       <c r="C24" s="13" t="n">
         <v>20</v>
       </c>
@@ -1425,22 +1450,23 @@
 참고로 이 고객은 사용자부담금(퇴직급여) 5억 2,000만원 전액이 고유계정대(현금성자산)로 2억 8,000만원, 수익증권 1억 2,400만원, ETF 1억 1,600만원으로 구성되어 있어요. 판매중단 펀드인 KB 퇴직연금 배당 (주식) 외에 RISE 미국나스닥100 ETF(수익률 65.7%), 하나 파이팅 코리아 (주식)(수익률 46.7%)도 함께 보유 중이에요.</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr"/>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>종목 + **고객 보유수익률** ↔ 상품의 1년 수익률을 고객 손익으로 말한다</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr"/>
+      <c r="L24" s="16" t="inlineStr"/>
     </row>
     <row r="25" hidden="1">
       <c r="C25" s="13" t="n">
@@ -1464,22 +1490,23 @@
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr"/>
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="K25" s="16" t="inlineStr">
         <is>
           <t>+1.7억 ↔ 「활동 기록이 없다」로 끝난다</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="C26" s="13" t="n">
@@ -1501,24 +1528,25 @@
           <t>송도윤 고객님의 퇴직급여와 개인부담금은 사용자부담금(퇴직급여) 5억 2,000만원, 가입자부담금(개인부담금) 0원이에요.</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr"/>
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>둘을 갈라 답한다 ↔ 「원장에 없다」고 답한다(실은 있는 값)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="108" customHeight="1">
+      <c r="L26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27" ht="121.5" customHeight="1">
       <c r="C27" s="13" t="n">
         <v>23</v>
       </c>
@@ -1539,24 +1567,25 @@
 비교그룹 운용현황은 [06-12-631] 고객포털에서, 추천 포트폴리오는 WiseNet에서 준비해 상담 근거자료를 만들어 활용할 수 있어요. 수익률 하위 고객에게 "같은 연령대는 이렇게 운용한다"는 비교 상담을 하려면 [06-12-631] 퇴직연금 고객포털의 '퇴직연금 컨설팅'에서 비교그룹 상품운용현황을 조회하면 돼요. 제안할 상품은 KB-WiseNet/Info-zone의 실적배당상품 메뉴인 펀드정보와 추천펀드 및 포트폴리오에서 준비할 수 있어요. 단말의 고객 현황과 WiseNet의 제안 상품, 고객포털의 비교군까지 3개 소스를 상담 전에 묶는 구조로 준비해 보세요.</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr"/>
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>peer 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>peer 값 ↔ peer 없는 3명에게 지어낸 평균을 말한다</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="94.5" customHeight="1">
+      <c r="L27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28" ht="121.5" customHeight="1">
       <c r="C28" s="13" t="n">
         <v>24</v>
       </c>
@@ -1579,22 +1608,23 @@
 송도윤 고객이 운용변경을 하지 않은 기간은 12개월 이상이에요. 358일간 접촉 이력이 없으며 최근 운용지시는 2025년 7월 18일에 이루어졌어요. 장기간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으니, 유선 접촉을 통해 관계를 회복해야 해요. 만일 현금성자산(고유계정대)을 방치 중인 상황이라면 운용지시나 리밸런싱을 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="K28" s="16" t="inlineStr">
         <is>
           <t>경과 개월 + 왜 요건인지 ↔ 값이 없다고 답한다</t>
         </is>
       </c>
-      <c r="K28" s="16" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr"/>
     </row>
     <row r="29" ht="40.5" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
@@ -1621,22 +1651,23 @@
           <t>박정호 고객님은 디폴트옵션 설정이 되어 있어요. IRP 안에서 이미 디폴트옵션이 등록되어 있는 고객이므로, 만약 보유상품을 변경하시거나 사전지정운용제도를 다시 등록하실 경우에는 사전지정운용제도 등록 및 변경과 기존 매도 후 신규 매수로 이어지는 2단계 거래가 필요하다는 점을 안내해 드릴 수 있어요.</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>설정된 8명 — 예: 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="K29" s="16" t="inlineStr">
         <is>
           <t>〔설정된 8명〕 「네, 설정돼 있습니다」 ↔ 「준비된 자료가 없습니다」(문제일 때만 싣는 필터가 넘어옴 — 실제 사고)</t>
         </is>
       </c>
-      <c r="K29" s="16" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr"/>
     </row>
     <row r="30" ht="81" customHeight="1">
       <c r="C30" s="13" t="n">
@@ -1654,22 +1685,23 @@
 이수민 고객님은 현재 원리금보장·현금성 자산이 100%를 차지하고 있으며, 7,000만원 규모의 정기예금 만기가 2026년 10월 17일(D-18) 도래를 앞두고 있어요. 만기 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태이므로, 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 디폴트옵션 사전지정 등록 또는 만기 예약변경을 권유해 보세요.</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="K30" s="16" t="inlineStr">
         <is>
           <t>〔미설정 4명〕 「미설정」 + 왜 요건인지 ↔ 설정돼 있다고 답한다</t>
         </is>
       </c>
-      <c r="K30" s="16" t="inlineStr"/>
+      <c r="L30" s="16" t="inlineStr"/>
     </row>
     <row r="31" ht="40.5" customHeight="1">
       <c r="C31" s="13" t="n">
@@ -1691,22 +1723,23 @@
           <t>이수민 고객의 세액공제 잔여한도는 900만원이에요. 세액공제 한도 900만원에 미달하여 납입하고 있는 상태이므로, 당행과 타행의 합산 잔여한도를 먼저 확인하고 자동이체 금액 증액을 제안해 보세요. 거절할 경우 여유자금 발생 시점의 추가입금으로 예약을 남기는 순서로 설계해 주시면 돼요.</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr"/>
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="K31" s="16" t="inlineStr">
         <is>
           <t>금액 + 연금저축과 함께 쓰는 한도라는 단서 ↔ 「IRP에 900만원까지」로 읽히게 쓴다</t>
         </is>
       </c>
-      <c r="K31" s="16" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr"/>
     </row>
     <row r="32" hidden="1">
       <c r="C32" s="13" t="n">
@@ -1728,24 +1761,25 @@
           <t>송도윤 고객이 세액공제를 더 받을 수 있는지 묻는 질문에는 총급여 구간에 따른 세액공제 환급액 기준으로 안내드리면 돼요. 현재 이 고객의 개인형IRP 계좌 추가 납입분은 세액공제 잔여한도가 0원이어서 더 납입해도 올해 세액공제로 돌아오는 금액은 늘지 않아요. 다만 ISA 만기자금을 개인형IRP로 전환하는 경우라면 전환액의 10%가 세액공제 대상에 더해져 상한 300만원까지 공제 대상 한도가 늘어나요. 총급여 5,500만원 이하인 경우 16.5% 공제율을 적용하면 전환액 1억 2,000만원 전액을 전환할 때 추가 공제 대상 300만원에 대해 495,000원의 환급액이 늘어나요. 총급여 5,500만원 초과인 경우 13.2% 공제율을 적용하면 추가 공제 대상 300만원에 대해 396,000원의 환급액이 늘어나요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이므로 둘을 같은 한도 안에서 저울질하지 않아요.</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr"/>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
         <is>
           <t>「올해 한도를 이미 채웠다」 ↔ 「자료가 없습니다」로 끝나거나 한도가 있는 듯 계산한다</t>
         </is>
       </c>
-      <c r="K32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="121.5" customHeight="1">
+      <c r="L32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33" ht="135" customHeight="1">
       <c r="C33" s="13" t="n">
         <v>29</v>
       </c>
@@ -1768,22 +1802,23 @@
 박정호 고객님은 연금개시 요건을 충족했으나 아직 연금개시를 하지 않은 상태예요. 연금개시를 미루는 고객에게는 "고객님. 지금은 퇴직금을 꺼내 쓰시기보다, 자산을 늘려나가야 하는 시기입니다. IRP 안에서 운용수익에 대해선 과세가 되지 않는 만큼 계속 운용하면서 복리효과를 더 누리시는 게 좋습니다"라고 예상 반론 대응을 활용해 안내해 보세요.</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="K33" s="16" t="inlineStr">
         <is>
           <t>〔오세훈 · 박정호〕 요건 충족 + 무엇이 충족됐는지 ↔ 미충족으로 답한다</t>
         </is>
       </c>
-      <c r="K33" s="16" t="inlineStr"/>
+      <c r="L33" s="16" t="inlineStr"/>
     </row>
     <row r="34" ht="27" customHeight="1">
       <c r="C34" s="13" t="n">
@@ -1800,22 +1835,23 @@
           <t>송도윤 고객님은 아직 연금개시요건을 충족하지 못해 연금개시를 할 수 있는 상태가 아니에요. 현재 연금개시가 미개시 상태로 등록되어 있으니 이 점을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>미충족 10명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="K34" s="16" t="inlineStr">
         <is>
           <t>〔미충족 10명〕 무엇이 모자란지까지 ↔ 「자료 없음」으로 끝난다</t>
         </is>
       </c>
-      <c r="K34" s="16" t="inlineStr"/>
+      <c r="L34" s="16" t="inlineStr"/>
     </row>
     <row r="35" ht="27" customHeight="1">
       <c r="C35" s="13" t="n">
@@ -1837,22 +1873,23 @@
           <t>박지민 고객님은 ISA 만기자금 보유 내역이 없어요.</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr"/>
+      <c r="I35" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>ISA 없는 9명 — 예: 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="K35" s="16" t="inlineStr">
         <is>
           <t>없다고 답한다 ↔ ISA 전환을 안내한다</t>
         </is>
       </c>
-      <c r="K35" s="16" t="inlineStr"/>
+      <c r="L35" s="16" t="inlineStr"/>
     </row>
     <row r="36" ht="27" customHeight="1">
       <c r="C36" s="13" t="n">
@@ -1874,22 +1911,23 @@
           <t>판매중단 보유상품은 없어요.</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr"/>
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>보유 없는 10명 — 예: 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="K36" s="16" t="inlineStr">
         <is>
           <t>없다고 답한다 ↔ 종목을 지어낸다</t>
         </is>
       </c>
-      <c r="K36" s="16" t="inlineStr"/>
+      <c r="L36" s="16" t="inlineStr"/>
     </row>
     <row r="37" ht="27" customHeight="1">
       <c r="C37" s="13" t="n">
@@ -1911,22 +1949,23 @@
           <t>그 고객의 IRP 가입일은 2023년 10월 2일이고, 가입 후 2년 11개월이 지났어요.</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr"/>
+      <c r="I37" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="K37" s="16" t="inlineStr">
         <is>
           <t>가입일 + 경과 ↔ 「자료가 없습니다」로 끝난다(같은 필터 문제)</t>
         </is>
       </c>
-      <c r="K37" s="16" t="inlineStr"/>
+      <c r="L37" s="16" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
       <c r="B38" s="20" t="inlineStr">
@@ -1953,22 +1992,23 @@
           <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서 고객은 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 밝혔어요. 지난 기록인 만큼 지금의 상황과는 다를 수 있으니 참고해서 상담을 진행해 주세요.</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr"/>
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="K38" s="16" t="inlineStr">
         <is>
           <t>〔기록 있는 9명〕 날짜 + 요지 + **시효 표시** ↔ 30초 전 자기 답변이 「지난 상담」으로 나온다</t>
         </is>
       </c>
-      <c r="K38" s="16" t="inlineStr"/>
+      <c r="L38" s="16" t="inlineStr"/>
     </row>
     <row r="39" hidden="1">
       <c r="C39" s="13" t="n">
@@ -1981,24 +2021,25 @@
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr"/>
-      <c r="H39" s="21" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr"/>
+      <c r="I39" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I39" s="16" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>기록 없는 쪽 — 김현수 173544-2074623 ↔ 기록 있는 쪽 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="K39" s="16" t="inlineStr">
         <is>
           <t>〔기록 없는 쪽〕 「기록이 없다」 한 줄 ↔ 계획이 세 바퀴 돌고 무관한 화법 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="K39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="40.5" customHeight="1">
+      <c r="L39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40" ht="54" customHeight="1">
       <c r="C40" s="13" t="n">
         <v>36</v>
       </c>
@@ -2018,24 +2059,25 @@
           <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶어 하셨어요. 그때 나눈 이야기인 만큼 오늘 대화에서는 지금 고객의 자산 상황이나 투자 의향이 그때와 같은지 단말에서 먼저 확인해 보고 말씀을 이어가야 해요.</t>
         </is>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr"/>
+      <c r="I40" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="K40" s="16" t="inlineStr">
         <is>
           <t>지난 기록 → 오늘 제안으로 잇는다 ↔ 지난 안내 수치를 지금 값으로 단정한다</t>
         </is>
       </c>
-      <c r="K40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="40.5" customHeight="1">
+      <c r="L40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41" ht="54" customHeight="1">
       <c r="C41" s="13" t="n">
         <v>37</v>
       </c>
@@ -2055,24 +2097,25 @@
           <t>원리금보장상품 금리는 매월 변경되므로 어떤 자료의 수치도 고정 팩트로 쓸 수 없다. 상담 전 [04-12-17A] New퇴직연금상품조회와 월별 특별제공상품 자료에서 당월 상품·금리·잔여한도를 확인하는 것이 유일하게 정확한 안내다. "일반은행 → 저축은행/GIC 갈아타기로 금리 상향"이라는 논리 구조만 시점 무관하게 유효하다. 기준시점 상시. 이 내용은 고객에게 그대로 안내하지는 마세요.</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr"/>
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="K41" s="16" t="inlineStr">
         <is>
           <t>기록에 시효 표시, 최신값은 따로 부른다 ↔ 지난 금리를 지금 값으로 답한다</t>
         </is>
       </c>
-      <c r="K41" s="16" t="inlineStr"/>
-    </row>
-    <row r="42" ht="135" customHeight="1">
+      <c r="L41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42" ht="229.5" customHeight="1">
       <c r="B42" s="20" t="inlineStr">
         <is>
           <t>7. 금지·주의 안내</t>
@@ -2106,24 +2149,25 @@
 다소높은위험 등급인 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP와 높은위험 등급인 KB 글로벌리츠 ETF는 상품 위험등급이 고객의 허용 상한인 보통위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이지 투자권유가 아니라는 점을 유의해야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H42" s="21" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr"/>
+      <c r="I42" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본</t>
         </is>
       </c>
-      <c r="I42" s="16" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>가드 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="K42" s="16" t="inlineStr">
         <is>
           <t>지식베이스 근거의 금지 + **대안 화법** ↔ 금지만 주고 대안이 없다 · 가드가 안 붙는다</t>
         </is>
       </c>
-      <c r="K42" s="16" t="inlineStr"/>
-    </row>
-    <row r="43" ht="135" customHeight="1">
+      <c r="L42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43" ht="162" customHeight="1">
       <c r="C43" s="13" t="n">
         <v>39</v>
       </c>
@@ -2147,24 +2191,25 @@
 전년도 세액공제 한도 미소진 사실을 확인해 알려주고 자동이체 금액 증액을 제안할 때는 이렇게 말씀해 보세요. "세액공제 한도 납입 — 전년도 세액공제 한도 미소진 사실을 확인해 알려주고 자동이체 금액 증액을 제안한다." 거절 시에도 여지를 남기는 짧은 클로징이 원문에 같이 붙어 있습니다.</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr"/>
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I43" s="16" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="K43" s="16" t="inlineStr">
         <is>
           <t>권유하지 않는다(개시 계좌) ↔ 추가납입을 권한다</t>
         </is>
       </c>
-      <c r="K43" s="16" t="inlineStr"/>
-    </row>
-    <row r="44" ht="67.5" customHeight="1">
+      <c r="L43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44" ht="81" customHeight="1">
       <c r="C44" s="13" t="n">
         <v>40</v>
       </c>
@@ -2184,24 +2229,25 @@
           <t>박정호 고객님은 연금개시 요건을 충족하고 있으나 연금개시가 미개시 상태인 고객으로, 연금개시 진행 시 만 55세 아직 멀었어요 같은 반론이 나올 수 있음에 유의해야 한다. 연금개시를 안내할 때는 "고객님. 지금은 퇴직금을 꺼내 쓰시기보다, 자산을 늘려나가야 하는 시기입니다. IRP 안에서 운용수익에 대해선 과세가 되지 않는 만큼 계속 운용하면서 복리효과를 더 누리시는 게 좋습니다."라는 대응 논리를 활용할 수 있다. 사용계획 있는 자금은 먼저 걸러내야 하며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 한다.</t>
         </is>
       </c>
-      <c r="H44" s="21" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr"/>
+      <c r="I44" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I44" s="16" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J44" s="16" t="inlineStr">
+      <c r="K44" s="16" t="inlineStr">
         <is>
           <t>환급 완료 전 제한을 **먼저** 세운다 ↔ 화법 축으로만 가서 순서 경고를 못 한다</t>
         </is>
       </c>
-      <c r="K44" s="16" t="inlineStr"/>
-    </row>
-    <row r="45" ht="135" customHeight="1">
+      <c r="L44" s="16" t="inlineStr"/>
+    </row>
+    <row r="45" ht="256.5" customHeight="1">
       <c r="C45" s="13" t="n">
         <v>41</v>
       </c>
@@ -2230,22 +2276,23 @@
 안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 안내 대상에서 제외돼요. 이 안내는 적합성 확인 결과에 따른 것이며 특정 상품에 대한 투자권유를 의미하지 않아요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr"/>
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I45" s="16" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="K45" s="16" t="inlineStr">
         <is>
           <t>「이런 상품이 있습니다」 톤까지 ↔ 「추천드립니다」·「가입시키세요」를 쓴다</t>
         </is>
       </c>
-      <c r="K45" s="16" t="inlineStr"/>
+      <c r="L45" s="16" t="inlineStr"/>
     </row>
     <row r="46" hidden="1">
       <c r="C46" s="13" t="n">
@@ -2267,22 +2314,23 @@
           <t>송도윤 고객님의 재취업 여부나 고용 상태에 대해서는 현재 보유하신 자료에 확인되는 내용이 없어요. 재취업 관련 사항은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="H46" s="19" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr"/>
+      <c r="I46" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I46" s="16" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="K46" s="16" t="inlineStr">
         <is>
           <t>확인이 필요하다고 답한다 ↔ 「아마 될 것 같다」로 추정한다</t>
         </is>
       </c>
-      <c r="K46" s="16" t="inlineStr"/>
+      <c r="L46" s="16" t="inlineStr"/>
     </row>
     <row r="47" hidden="1">
       <c r="C47" s="13" t="n">
@@ -2320,22 +2368,23 @@
 이 내용은 어디까지나 적합성 확인 결과이며, 특정 상품에 대한 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H47" s="19" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr"/>
+      <c r="I47" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I47" s="16" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>한도 남은 고객 — 예: 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J47" s="16" t="inlineStr">
+      <c r="K47" s="16" t="inlineStr">
         <is>
           <t>없는 축은 이름을 대고, 아는 것(잔여한도)과 가드(m.1-1 사용계획 자금)를 엮어 답한다 ↔ 첫 문장만 맞고 적합성 상품 목록으로 비켜간다</t>
         </is>
       </c>
-      <c r="K47" s="16" t="inlineStr"/>
+      <c r="L47" s="16" t="inlineStr"/>
     </row>
     <row r="48" hidden="1">
       <c r="C48" s="13" t="n">
@@ -2358,24 +2407,25 @@
 디폴트옵션 미지정 고객에게는 투자성향이 등록하신 디폴트 옵션 위험등급보다 높은 경우라면 이렇게 말해 보세요. "여기서의 위험은 '데인저러스'가 아니고 '리스크'입니다. 리스크가 곧 변동성이거든요"라고 설명하며 용어에 대한 부담을 없애고, 연금사업자가 자기 이름을 걸고 운용하므로 관리에 신경 쓴다는 점을 함께 안내해 주세요. 고유계정대 2억 8,000만원을 보유하고 계시므로, 현금성자산 운용지시나 리밸런싱을 권유할 때 디폴트옵션 가입을 함께 유도하는 방향으로 활용할 수 있어요.</t>
         </is>
       </c>
-      <c r="H48" s="19" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr"/>
+      <c r="I48" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J48" s="16" t="inlineStr">
+      <c r="K48" s="16" t="inlineStr">
         <is>
           <t>한 줄 답에 근거 한 건 ↔ 답에 안 쓴 ⑥⑦⑧ 카드까지 근거가 여섯 건 선다</t>
         </is>
       </c>
-      <c r="K48" s="16" t="inlineStr"/>
-    </row>
-    <row r="49" ht="40.5" customHeight="1">
+      <c r="L48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49" ht="94.5" customHeight="1">
       <c r="C49" s="13" t="n">
         <v>45</v>
       </c>
@@ -2402,28 +2452,29 @@
 화면이 열리면 이 문구를 넣어 주세요 — "[KB국민은행] 고객님의 개인형IRP 운용 상태를 점검해 안내드릴 예정입니다. 자세한 내용은 https://obank.kbstar.com/pending/irp-checkup-draft 에서 확인해 주세요."</t>
         </is>
       </c>
-      <c r="H49" s="19" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr"/>
+      <c r="I49" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I49" s="16" t="inlineStr">
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J49" s="16" t="inlineStr">
+      <c r="K49" s="16" t="inlineStr">
         <is>
           <t>발송 화면 딥링크 + 그 문구를 그대로 건넨다 ↔ 문구를 되묻거나 「연계하지 않았다」로 끝난다</t>
         </is>
       </c>
-      <c r="K49" s="16" t="inlineStr">
+      <c r="L49" s="16" t="inlineStr">
         <is>
           <t>"[KB국민은행] 고객님의 개인형IRP 운용 상태를 점검해 안내드릴 예정입니다. 자세한 내용은 https://obank.kbstar.com/pending/irp-checkup-draft 에서 확인해 주세요." 로 LMS 보내줘</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="54" customHeight="1">
+    <row r="50" ht="67.5" customHeight="1">
       <c r="B50" s="20" t="inlineStr">
         <is>
           <t>8. 상담 준비 자료</t>
@@ -2448,24 +2499,25 @@
           <t>송도윤 고객님과의 상담을 시작하기 전에 단말에서 확인된 고객 현황과 제안 근거 자료를 미리 준비해 두어야 해요. 비교그룹 운용현황은 고객포털에서, 추천 포트폴리오는 WiseNet에서 준비해 상담 근거자료를 만드세요. 구체적으로는 단말에서 확인한 고객 현황과 WiseNet의 제안 상품, 그리고 고객포털의 비교군 정보를 사전에 묶어두는 것이 필요해요. 관리 사각지대 고객이자 장기간 접촉 이력이 없는 상태이므로, 유선 접촉을 통해 관계를 회복해야 해요.</t>
         </is>
       </c>
-      <c r="H50" s="17" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr"/>
+      <c r="I50" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I50" s="16" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J50" s="16" t="inlineStr">
+      <c r="K50" s="16" t="inlineStr">
         <is>
           <t>브리핑 ⑥⑦⑧ 과 같은 후보군에서 ↔ 화면이 고른 걸 다르게 요약하거나 저작 메모가 노출된다</t>
         </is>
       </c>
-      <c r="K50" s="16" t="inlineStr"/>
-    </row>
-    <row r="51" ht="67.5" customHeight="1">
+      <c r="L50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51" ht="81" customHeight="1">
       <c r="C51" s="13" t="n">
         <v>47</v>
       </c>
@@ -2485,24 +2537,25 @@
           <t>송도윤 고객님의 상태에 걸려 있는 참고 자료는 대기 현금성자산 보유 고객(금액 기준), 디폴트옵션 미지정(미동의) 고객(만기 조건 없는 전수 대상), 성과저조(환매추천) 펀드 보유 고객, 관리 사각지대 고객(무권유 비대면 신규 / 전담직원 관리 미비), 전년 납입 있었으나 당해 미납인 고객(납입 중단 신호), ISA 만기(예정)·만기해지 자금 보유 고객까지 총 6건이에요. 자료에 따르면 358일간 접촉 이력이 없어 관리 사각지대 및 장기 미접촉 상태에 해당하며, 8,000만원 규모의 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 계시고 고유계정대 2억 8,000만원의 현금성자산을 보유 중인 점 등이 함께 확인돼요.</t>
         </is>
       </c>
-      <c r="H51" s="19" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr"/>
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J51" s="16" t="inlineStr">
+      <c r="K51" s="16" t="inlineStr">
         <is>
           <t>그 고객 상태에 걸린 것만 ↔ 상태에 안 걸린 자료가 나온다</t>
         </is>
       </c>
-      <c r="K51" s="16" t="inlineStr"/>
-    </row>
-    <row r="52" ht="121.5" customHeight="1">
+      <c r="L51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52" ht="243" customHeight="1">
       <c r="C52" s="13" t="n">
         <v>48</v>
       </c>
@@ -2511,7 +2564,14 @@
           <t>(화법 제안 뒤) 네, 보여줘</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr"/>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>1. 고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?
+→ 예금만으로도 충분하지 않냐고 묻는 고객에게는 원리금보장상품 역시 정기적인 관리가 필요하다는 점을 짚어주는 것이 핵심이에요.
+사후관리의 핵심은 금리 갈아타기에 있다는 논리로 접근해야 해요.
+"예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
+        </is>
+      </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
           <t>누구나</t>
@@ -2519,32 +2579,36 @@
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>보유하신 퇴직연금 DC, 기업형 IRP, 개인형 IRP 계좌에 운용지시가 안 된 현금성자산이 000만원 있는데 알고 계신가요? 하고 물어볼 수 있도록 현금성자산 운용지시와 리밸런싱을 권유하는 첫 번째 화법을 활용할 수 있어요. 고객이 어떻게 하면 되냐고 물어보면 은행에 내점하실 필요 없이, 스타뱅킹에서 운용지시를 하실 수 있습니다. 고객님, 스타뱅킹이나 인터넷뱅킹은 사용하고 계시죠? 라고 안내해 드릴 수 있어요. 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속하지 않도록 주의하고, 고객에게 생소한 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.
-만기 1개월 내 원리금보장상품을 보유하고 디폴트옵션에 등록하지 않은 고객이라면 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 사전지정 등록을 권유하는 두 번째 화법을 쓸 수 있어요. 사용계획이 있는 자금인지 먼저 확인하고 접근하는 것이 중요해요.</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
+          <t>현금성자산을 방치 중인 고객에게는 운용지시와 리밸런싱을 권유하는 방법을 활용할 수 있어요. 
+"보유하신 퇴직연금 DC/기업형IRP/개인형IRP 계좌에 운용지시가 안된 현금성자산이 000만원 있는데 알고 계신가요?"
+"고객님께서 가입하신 퇴직연금 제도는 정기예금이나 펀드 등의 상품으로 자유롭게 운용하실 수 있고, 여기서 발생하는 운용수익에 따라서 향후에 수령하시는 퇴직연금 금액이 달라집니다. 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준으로 빨리 금리가 높은 저축은행 정기예금이나 펀드같은 상품으로 운용하시면 좋을거 같아요."
+"은행에 내점하실 필요 없이, 스타뱅킹에서 운용지시를 하실 수 있습니다. 고객님, 스타뱅킹이나 인터넷뱅킹은 사용하고 계시죠?"
+만기가 임박한 원리금보장상품을 보유하고 디폴트옵션이 미등록된 고객에게는 재예치 제도가 폐지되었다는 점을 안내할 수 있어요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환된다는 제도 변화를 근거로 디폴트옵션 사전지정 등록 또는 만기 예약변경을 권유해 보세요. 갈아탄 상품이 더 좋을 것이라고 단정적으로 약속하지 않도록 주의하시고, 연금지급 대기나 교체매매 등으로 사용계획이 있는 자금인지 먼저 확인해 주세요. 고객에게 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주시는 것이 좋아요.</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr"/>
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I52" s="16" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J52" s="16" t="inlineStr">
+      <c r="K52" s="16" t="inlineStr">
         <is>
           <t>⑥⑦⑧ 의 나머지 후보를 보여준다 ↔ 「직전에 제안드린 작업이 없어요」로 끝난다</t>
         </is>
       </c>
-      <c r="K52" s="16" t="inlineStr">
+      <c r="L52" s="16" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="135" customHeight="1">
+    <row r="53" ht="189" customHeight="1">
       <c r="A53" s="26" t="inlineStr">
         <is>
           <t>Ⅲ. 업무 확인 — 제도는 어떻고, 어떻게 처리하고, 몇 번 화면이고, 시장은 어떤가</t>
@@ -2571,33 +2635,37 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>IRP를 포함한 세액공제 한도는 연간 납입액 최대 900만원이에요. 2026년 6월 기준 자료에 따르면, 연금저축만으로는 한도가 연 600만원이지만 IRP를 포함하면 900만원까지 확대돼요.
-총급여 5,500만원 이하(종합소득금액 4,500만원 이하)인 고객님은 16.5%, 초과하는 고객님은 13.2%(지방소득세 포함)의 공제율이 적용돼요. 이에 따라 900만원을 모두 채우면 각각 1,485,000원과 1,188,000원을 환급받을 수 있어요.
-다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못할 수 있다는 점을 유의해서 안내해 주세요.
-── 참고한 자료
-· 본부 공식 자료
-── 이어서 물어보실 수 있어요
-· 고객이 앱에서 직접 할 수 있어?</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
+          <t>어떤 상품으로 가입되어 있나요?
+· 연금저축 단독
+· IRP 포함</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 개인형IRP 마케팅 보물지도 Vol.1 (연금사업본부 연금컨설팅부, 2026-03)
+     — 세액공제 — 한도 900만원 · 5,500만원 이하 16.5% / 초과 13.2% · 최대 148.5만원 [fact.k04.f2 · 관련도 2.0]
+   · 개인형IRP 마케팅 보물지도 Vol.1 (연금사업본부 연금컨설팅부, 2026-03)
+     — 연금저축 단독 600만원 vs IRP 포함 900만원 [fact.k04.f3 · 관련도 2.0]</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
           <t>900만원 + 연금저축과 공유하는 한도라는 단서 ↔ 되묻는다 · 「IRP에만 900만원」으로 읽힌다</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr"/>
-    </row>
-    <row r="54" ht="81" customHeight="1">
+      <c r="L53" s="10" t="inlineStr"/>
+    </row>
+    <row r="54" ht="94.5" customHeight="1">
       <c r="C54" s="13" t="n">
         <v>50</v>
       </c>
@@ -2617,24 +2685,25 @@
           <t>고객이 중도해지나 중도인출 시 적용되는 세금을 물을 때에는 2026년 6월 기준 자료를 바탕으로 정확한 과세 방식을 짚어주어야 해요. 중도인출은 일시금 수령과 동일하게 기타소득세 16.5%(지방소득세 포함) 가 부과되고, 중도해지 시에도 세액공제 받은 납입원금·운용수익에 기타소득세 16.5%만 분리과세된다. 이 부담은 납입 시 세액공제(16.5%)와 크거나 같아, 공제받은 고객이 중도인출하면 혜택이 상쇄된다. 연금수령한도 초과 인출분도 소득원천별(퇴직소득세·기타소득세)로 과세된다. 기준시점 2026.06 (KBthink 01 일치) 내용을 안내해 드려요. 과세 대상은 세액공제 받은 원금과 운용수익에 한정되며, 세액공제를 받지 않은 과세제외분은 제외된다는 점을 함께 확인해 주세요.</t>
         </is>
       </c>
-      <c r="H54" s="21" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr"/>
+      <c r="I54" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
           <t>16.5% + 붙는 조건 ↔ 값과 조건의 짝이 뒤집힌다</t>
         </is>
       </c>
-      <c r="K54" s="16" t="inlineStr"/>
-    </row>
-    <row r="55" ht="67.5" customHeight="1">
+      <c r="L54" s="16" t="inlineStr"/>
+    </row>
+    <row r="55" ht="81" customHeight="1">
       <c r="C55" s="13" t="n">
         <v>51</v>
       </c>
@@ -2654,22 +2723,23 @@
           <t>IRP 중도인출은 법정 사유에 한해 가능하다. 2026년 6월 기준으로 무주택자 주택구입(매매계약 체결일~소유권 이전 등기 접수일 후 1개월 이내 신청), 무주택자 전세금·임차보증금(계약 체결일~잔금 지급일 후 1개월 이내, 하나의 사업장 근무 중 1회 한정), 본인·배우자·부양가족의 6개월 이상 요양(연간 임금총액의 12.5% 초과 의료비 부담 시), 자연재난·특별재난지역 사회재난 피해, 5년 이내 개인회생절차 개시 결정, 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 최대 90%까지 일부 인출할 수 있으며 횟수 제한은 없다. 다만 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다.</t>
         </is>
       </c>
-      <c r="H55" s="16" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr"/>
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본</t>
         </is>
       </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
           <t>사유 6가지 + 각각의 조건 ↔ 사유를 빠뜨리거나 조건을 뭉갠다</t>
         </is>
       </c>
-      <c r="K55" s="16" t="inlineStr"/>
+      <c r="L55" s="16" t="inlineStr"/>
     </row>
     <row r="56" ht="40.5" customHeight="1">
       <c r="C56" s="13" t="n">
@@ -2691,22 +2761,23 @@
           <t>사용자부담금 대면 계좌 기준으로 안내드리면, 2026년 3월 기준 개인형IRP 수수료율은 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%가 적용돼요. 단일 수치로 안내하면 오답이 될 수 있으므로 단말에서 부담금 종류와 채널, 금액 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H56" s="21" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr"/>
+      <c r="I56" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본</t>
         </is>
       </c>
-      <c r="I56" s="16" t="inlineStr">
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J56" s="16" t="inlineStr">
+      <c r="K56" s="16" t="inlineStr">
         <is>
           <t>〔누구나〕 원장이 축을 아니까 「사용자부담금·대면 기준으로」 전제를 밝히고 답한다 ↔ 되묻는다</t>
         </is>
       </c>
-      <c r="K56" s="16" t="inlineStr"/>
+      <c r="L56" s="16" t="inlineStr"/>
     </row>
     <row r="57" ht="54" customHeight="1">
       <c r="C57" s="13" t="n">
@@ -2725,22 +2796,23 @@
 · 가입자부담금</t>
         </is>
       </c>
-      <c r="H57" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr"/>
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
           <t>〔고객 없이〕 축을 모르니 되묻는다(출처도 붙는다) ↔ 한쪽을 골라 답하거나 출처가 「없음」이다</t>
         </is>
       </c>
-      <c r="K57" s="16" t="inlineStr"/>
+      <c r="L57" s="16" t="inlineStr"/>
     </row>
     <row r="58" hidden="1">
       <c r="C58" s="13" t="n">
@@ -2763,22 +2835,23 @@
 2026년 3월 기준 개인형IRP 수수료율은 부담금 종류와 채널, 구간에 따라 다르게 적용돼요. 사용자부담금(퇴직금)은 대면 채널에서 5천만원 미만인 경우 0.45%, 5천만원 이상인 경우 0.38%이며, 비대면 채널에서는 5천만원 미만인 경우 0.20%, 5천만원 이상인 경우 면제로 적용돼요. 가입자부담금은 대면 채널에서 1억원 미만인 경우 0.28%, 1억원 이상인 경우 0.25%이고, 비대면 채널에서는 1억원 미만인 경우 0.23%, 1억원 이상인 경우 0.21%로 적용되니 안내해 드릴 때 이 점을 함께 확인해 주세요.</t>
         </is>
       </c>
-      <c r="H58" s="21" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr"/>
+      <c r="I58" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본</t>
         </is>
       </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
           <t>첫 문장에서 「자료 없음」, 그 뒤 비교 화법 ↔ 당행 수수료표를 펴 놓고 끝낸다</t>
         </is>
       </c>
-      <c r="K58" s="16" t="inlineStr"/>
+      <c r="L58" s="16" t="inlineStr"/>
     </row>
     <row r="59" ht="54" customHeight="1">
       <c r="C59" s="13" t="n">
@@ -2802,22 +2875,23 @@
 · 5,500만원 초과</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr"/>
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J59" s="16" t="inlineStr">
+      <c r="K59" s="16" t="inlineStr">
         <is>
           <t>가능 여부 + 60일 기한 + 조건 ↔ 조건을 떼고 「받는다」로만 답한다</t>
         </is>
       </c>
-      <c r="K59" s="16" t="inlineStr"/>
+      <c r="L59" s="16" t="inlineStr"/>
     </row>
     <row r="60" ht="67.5" customHeight="1">
       <c r="C60" s="13" t="n">
@@ -2840,24 +2914,25 @@
 "월 75만원 적립 = 적금 월 790만원" 비유를 사용해 세액공제 환급액을 적금 이자와 같은 단위로 환산하면 적금보다 10배 이상 차이 난다는 점을 쉽게 체감시킬 수 있어요.</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr"/>
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K60" s="16" t="inlineStr">
+        <is>
           <t>세액공제 카드를 찾아낸다 ↔ 0건으로 끝난다(직원 말투와 카드 말이 달라서)</t>
         </is>
       </c>
-      <c r="K60" s="16" t="inlineStr"/>
-    </row>
-    <row r="61" ht="67.5" customHeight="1">
+      <c r="L60" s="16" t="inlineStr"/>
+    </row>
+    <row r="61" ht="81" customHeight="1">
       <c r="C61" s="13" t="n">
         <v>57</v>
       </c>
@@ -2877,24 +2952,25 @@
           <t>2026년 3월부터 적용되는 개인형IRP의 연간 납입한도는 연금저축과 DC형 및 기업형IRP의 개인부담금을 모두 합산하여 1,800만원이에요. IRP 단독이 아니라 타행과 타사의 연금저축 납입액까지 포함되므로 실제 납입 여력은 [06-12-151] 화면의 개인부담금 연합회 한도 조회로 확인하고 안내해 드려야 해요. 세액공제 한도의 경우 연금저축만 보유하면 연 600만원이지만 개인형IRP를 포함하면 연 900만원까지 확대되므로, 연금저축만 가진 고객이라면 개인형IRP로 300만원의 추가 공제 여력을 활용하실 수 있어요. 세액공제 한도 900만원과 전체 납입한도 1,800만원은 혼동하기 쉬우니 구분해서 살펴볼 필요가 있어요.</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr"/>
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
           <t>1,800만원 + 연금저축·DC 개인부담금 합산 ↔ IRP 단독 한도로 답한다</t>
         </is>
       </c>
-      <c r="K61" s="16" t="inlineStr"/>
-    </row>
-    <row r="62" ht="94.5" customHeight="1">
+      <c r="L61" s="16" t="inlineStr"/>
+    </row>
+    <row r="62" ht="121.5" customHeight="1">
       <c r="C62" s="13" t="n">
         <v>58</v>
       </c>
@@ -2914,24 +2990,25 @@
           <t>2026년 3월 기준으로 세액공제 한도인 900만원을 초과해 납입한 금액은 세제 혜택과 인출 시 유리한 구조로 활용할 수 있어요. 900만원 초과분은 운용 기간 동안 과세이연 혜택을 받을 수 있고, 세액공제를 받지 않은 가입자부담금은 연금수령 시 과세제외로 인출할 수 있어요. 또한 올해 초과 납입분을 내년 세액공제분으로 이월 신청하는 이연 공제도 활용할 수 있어요. 다만 세액공제를 받지 않은 금액이 과세제외로 인출되려면 미공제 금액 등록이 선행되어야 하니 단말에서 이 부분을 먼저 챙겨 보셔야 해요. 이연 공제의 구체적인 실무 절차나 서류에 대해서는 제가 가진 자료로는 확인이 어려워요. 고객에게는 "세액공제 한도인 900만원을 초과해서 납입하시는 금액도 운용 기간 동안 과세이연 혜택을 받으실 수 있고, 공제받지 않은 금액은 나중에 연금으로 받으실 때 세금을 내지 않고 먼저 인출하실 수 있어요. 또한 올해 초과 납입하신 분량은 내년 세액공제분으로 이월해서 신청하실 수도 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="H62" s="19" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr"/>
+      <c r="I62" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
           <t>과세이연 + 인출 시 과세제외 + 이연 공제 신청 ↔ 「공제 안 된다」로만 끝낸다</t>
         </is>
       </c>
-      <c r="K62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63" ht="81" customHeight="1">
+      <c r="L62" s="16" t="inlineStr"/>
+    </row>
+    <row r="63" ht="108" customHeight="1">
       <c r="C63" s="13" t="n">
         <v>59</v>
       </c>
@@ -2951,24 +3028,25 @@
           <t>위험자산 70% 한도는 근로자퇴직급여보장법 시행령에 따라 주식형이나 주식혼합형 펀드 같은 위험자산을 평가금액의 70% 이내에서만 운용할 수 있는 규정이에요. 2026년 6월 기준 자료를 보면 전액 주식형 펀드로만 운용하는 것은 불가능하며, DB형의 경우에는 사용자별 전체 적립금 기준 70% 이내로 제한돼요. 만약 한도를 초과하더라도 별도의 페널티는 없고, 초과된 금액을 정기예금 같은 안전자산으로 교체매매하거나 추가입금을 한 뒤 안전자산으로 운용지시를 내려 해소하면 돼요. 세부적인 위반 현황은 확인 화면 04-12-354의 컴플라이언스 위반점검 현황조회에서 조회구분을 위험자산투자한도위반으로 설정해 확인할 수 있어요. 주식형 ETF의 포함 여부와 관련해서는 영업점 핫팁과 본부 자료의 언급이 달라 법령이나 감독규정 확인 전까지 확정해 안내하기 어려우니 이 점은 참고해 주세요.</t>
         </is>
       </c>
-      <c r="H63" s="17" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr"/>
+      <c r="I63" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
           <t>한도 범위 + 초과 시 조치 + 확인 화면 ↔ 조치를 빼고 한도만 말한다</t>
         </is>
       </c>
-      <c r="K63" s="16" t="inlineStr"/>
-    </row>
-    <row r="64" ht="40.5" customHeight="1">
+      <c r="L63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64" ht="54" customHeight="1">
       <c r="C64" s="13" t="n">
         <v>60</v>
       </c>
@@ -2988,22 +3066,23 @@
           <t>TDF나 디폴트옵션은 금감원장이 정한 기준을 충족할 때 위험자산 70% 한도의 예외로 적립금의 100%까지 운용할 수 있어요. 2026년 3~7월 자료를 기준으로 보면, 당행 퇴직연금에서 운용 가능한 TDF는 전부 적격 TDF에 해당해요. 다만 채권형이나 채권혼합형 ETF 100% 예외 같은 범위는 본부 자료에 없어서 지금 확인해 드리기 어려워요.</t>
         </is>
       </c>
-      <c r="H64" s="19" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr"/>
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
           <t>적격TDF·디폴트옵션 100% 운용 가능 ↔ 채권형 ETF 의 ⚠ 까지 단정한다</t>
         </is>
       </c>
-      <c r="K64" s="16" t="inlineStr"/>
+      <c r="L64" s="16" t="inlineStr"/>
     </row>
     <row r="65" hidden="1">
       <c r="C65" s="13" t="n">
@@ -3037,22 +3116,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H65" s="17" t="inlineStr">
+      <c r="H65" s="16" t="inlineStr"/>
+      <c r="I65" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
           <t>정의 + 위험등급 4단계 + 적용 3케이스 ↔ 등급만 나열한다</t>
         </is>
       </c>
-      <c r="K65" s="16" t="inlineStr"/>
+      <c r="L65" s="16" t="inlineStr"/>
     </row>
     <row r="66" hidden="1">
       <c r="C66" s="13" t="n">
@@ -3087,24 +3167,25 @@
 ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H66" s="16" t="inlineStr"/>
+      <c r="I66" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
           <t>3분류·5종 정의 ↔ 상품명을 나열해 권유처럼 읽힌다(§8)</t>
         </is>
       </c>
-      <c r="K66" s="16" t="inlineStr"/>
-    </row>
-    <row r="67" ht="135" customHeight="1">
+      <c r="L66" s="16" t="inlineStr"/>
+    </row>
+    <row r="67" ht="175.5" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
         <is>
           <t>10. 업무 처리 절차</t>
@@ -3132,22 +3213,23 @@
 연금 개시를 신청하는 고객에게는 2단계로 처리하는 것이 핵심이에요. 먼저 [06-12-622] 세액 미공제 한도 등록을 진행하고, 이어서 [02-12-221] 연금지급 등록을 처리해요. 세액 미공제 한도 등록 시에는 「연금보험료 등 소득·세액 공제 확인서」를 준비해야 하며, 서류가 없다면 국민지갑에서 발급할 수 있어요. 연금개시 전에는 [04-10-099] 세금우대 조회로 이전 가능한 상품이 있는지 꼭 확인해야 해요. 아울러 처리 중 자동이체 금액이 입금 중이거나 보유상품변경이 진행 중이면 거래가 불가하다는 점을 미리 안내드릴게요.</t>
         </is>
       </c>
-      <c r="H67" s="21" t="inlineStr">
+      <c r="H67" s="16" t="inlineStr"/>
+      <c r="I67" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · QA</t>
         </is>
       </c>
-      <c r="I67" s="16" t="inlineStr">
+      <c r="J67" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J67" s="16" t="inlineStr">
+      <c r="K67" s="16" t="inlineStr">
         <is>
           <t>순서 + 서류 + 화면번호 ↔ 서류나 화면번호를 빠뜨린다</t>
         </is>
       </c>
-      <c r="K67" s="16" t="inlineStr"/>
+      <c r="L67" s="16" t="inlineStr"/>
     </row>
     <row r="68" ht="54" customHeight="1">
       <c r="C68" s="13" t="n">
@@ -3171,22 +3253,23 @@
 · 전문 송수신(일반)</t>
         </is>
       </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="H68" s="16" t="inlineStr"/>
+      <c r="I68" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K68" s="16" t="inlineStr">
+        <is>
           <t>타행→당행인지 되묻는다 ↔ 아무 쪽이나 답한다(직원은 다른 절차인 줄도 모른다)</t>
         </is>
       </c>
-      <c r="K68" s="16" t="inlineStr"/>
+      <c r="L68" s="16" t="inlineStr"/>
     </row>
     <row r="69" ht="40.5" customHeight="1">
       <c r="C69" s="13" t="n">
@@ -3208,24 +3291,25 @@
           <t>과세이연 등록을 처리할 때는 과세이연정보(통산정보) 등록·조회와 과세이연계좌신고서 출력을 할 수 있는 [04-12-648] 과세이연정보관리 화면을 활용하면 돼요. 이어서 [01-12-213] 입금/입금예약 화면에서 거래구분을 과세이연/계약이전입금으로 선택해 입금을 진행하면 과세이연 등록 절차를 처리할 수 있어요.</t>
         </is>
       </c>
-      <c r="H69" s="16" t="inlineStr">
+      <c r="H69" s="16" t="inlineStr"/>
+      <c r="I69" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
           <t>순서 + 화면번호 + 주의 ↔ 화면번호를 일부만 인용했다고 답이 폐기돼 원문 덤프가 나간다</t>
         </is>
       </c>
-      <c r="K69" s="16" t="inlineStr"/>
-    </row>
-    <row r="70" ht="135" customHeight="1">
+      <c r="L69" s="16" t="inlineStr"/>
+    </row>
+    <row r="70" ht="216" customHeight="1">
       <c r="C70" s="13" t="n">
         <v>66</v>
       </c>
@@ -3248,24 +3332,25 @@
 만기상품 예약변경은 먼저 사용계획이 있는 자금인지 확인하고 처리하는 게 핵심이에요. 정기예금은 만기에 자동 재예치되지 않아 방치되면 현금성자산에 머물게 되니 [75-08-110] 화면에서 만기상품 예약변경으로 처리해야 해요. 처리 순서는 익월 금리가 월 단위로 확정되므로 익월 금리 확인을 선행한 뒤 만기 1개월 전부터 예약변경을 걸고, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하는 방식이에요. 주의할 점은 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 먼저 걸러내야 하며, 디폴트옵션 미등록 고객은 사전지정 등록과 만기 예약변경을 함께 처리해야 한다는 점이에요.</t>
         </is>
       </c>
-      <c r="H70" s="16" t="inlineStr">
+      <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I70" s="16" t="inlineStr">
+      <c r="J70" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J70" s="16" t="inlineStr">
+      <c r="K70" s="16" t="inlineStr">
         <is>
           <t>순서 + 화면번호 + 주의 ↔ 저작 메모(「팀 논의 필요」)가 직원 답변에 노출된다</t>
         </is>
       </c>
-      <c r="K70" s="16" t="inlineStr"/>
-    </row>
-    <row r="71" ht="54" customHeight="1">
+      <c r="L70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71" ht="67.5" customHeight="1">
       <c r="C71" s="13" t="n">
         <v>67</v>
       </c>
@@ -3285,22 +3370,23 @@
           <t>디폴트옵션 등록 절차와 화면번호는 [75-08-110] 화면을 통해 처리해요. 원리금보장상품 만기가 다가오는데 디폴트옵션 미등록인 고객은 별도 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 디폴트옵션 사전지정 등록과 만기 예약변경으로 나누어 처리할 수 있어요. 만기 예약거래는 만기 한 달 전부터 가능하며, 통화 후 스타뱅킹 URL 링크를 문자로 보내 고객이 직접 처리하게 안내하면 돼요. 처리는 디폴트옵션(저위험이상) 사전지정 등록과 만기 예약변경 두 갈래로 진행돼요.</t>
         </is>
       </c>
-      <c r="H71" s="16" t="inlineStr">
+      <c r="H71" s="16" t="inlineStr"/>
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I71" s="16" t="inlineStr">
+      <c r="J71" s="16" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J71" s="16" t="inlineStr">
+      <c r="K71" s="16" t="inlineStr">
         <is>
           <t>절차 + 화면번호 ↔ 직원 단말 절차를 고객 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="K71" s="16" t="inlineStr"/>
+      <c r="L71" s="16" t="inlineStr"/>
     </row>
     <row r="72" ht="40.5" customHeight="1">
       <c r="C72" s="13" t="n">
@@ -3322,22 +3408,23 @@
           <t>추가납입을 권유하기 전에, 이 고객의 당해 납입액이 0원이며 예상 세액공제액과 세액공제 잔여한도가 모두 0원으로 확인되는지 단말에서 먼저 살펴봐야 해요. 추가납입 여력을 살피는 과정에서는 사용계획이 있는 자금인지 확인하는 단계를 먼저 거쳐야 한다는 점을 염두에 두시면 좋아요.</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="H72" s="16" t="inlineStr"/>
+      <c r="I72" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I72" s="16" t="inlineStr">
+      <c r="J72" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J72" s="16" t="inlineStr">
+      <c r="K72" s="16" t="inlineStr">
         <is>
           <t>입금이력·한도에 더해 **연금개시 여부**를 먼저 ↔ 연금개시 확인이 빠진다(§8 관리대장)</t>
         </is>
       </c>
-      <c r="K72" s="16" t="inlineStr"/>
+      <c r="L72" s="16" t="inlineStr"/>
     </row>
     <row r="73" hidden="1">
       <c r="C73" s="13" t="n">
@@ -3360,24 +3447,25 @@
 상담을 준비하실 때는 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 운용 여건의 차이를 설명하는 방향으로 준비해 보세요. 또한 사용계획이 있는 자금인지 먼저 확인하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주시는 것이 좋아요.</t>
         </is>
       </c>
-      <c r="H73" s="17" t="inlineStr">
+      <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I73" s="16" t="inlineStr">
+      <c r="J73" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J73" s="16" t="inlineStr">
+      <c r="K73" s="16" t="inlineStr">
         <is>
           <t>[04-12-613] 수수료 예상조회로 현재·전환 후를 숫자로 ↔ 화법만 주고 준비를 뺀다</t>
         </is>
       </c>
-      <c r="K73" s="16" t="inlineStr"/>
-    </row>
-    <row r="74" ht="40.5" customHeight="1">
+      <c r="L73" s="16" t="inlineStr"/>
+    </row>
+    <row r="74" ht="54" customHeight="1">
       <c r="C74" s="13" t="n">
         <v>70</v>
       </c>
@@ -3397,24 +3485,25 @@
           <t>정기예금 중도해지 예상 손실금액은 「정기예금 중도해지 &amp; 리밸런싱 계산기」를 통해 산출할 수 있어요. 진입 경로는 1번 Info-zone의 연금(퇴직연금) 안 계산기 메뉴를 이용하시거나 [04-12-642] 화면 하단의 연계메뉴에서 바로 클릭하시면 돼요. 계산할 때는 예상이율을 현재 보유상품 이율로 변경한 뒤 조회해야 하며, 그 결과는 참고용이라는 점을 미리 안내해 드릴게요.</t>
         </is>
       </c>
-      <c r="H74" s="19" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
           <t>계산기로 사전 산출 + 매도 우선순위 4단계 ↔ 「해지하면 손해」로만 끝낸다</t>
         </is>
       </c>
-      <c r="K74" s="16" t="inlineStr"/>
-    </row>
-    <row r="75" ht="94.5" customHeight="1">
+      <c r="L74" s="16" t="inlineStr"/>
+    </row>
+    <row r="75" ht="121.5" customHeight="1">
       <c r="C75" s="13" t="n">
         <v>71</v>
       </c>
@@ -3434,24 +3523,25 @@
           <t>퇴직소득세는 개인형IRP 연금지급 화면인 [02-12-221]에서 입사일자, 중간정산특례 적용 여부, 퇴직일자, 퇴직금액을 입력해 계산하는 것이 핵심이에요. 2026년 기준시점으로, 해당 화면에 나오는 표시 금액은 순수 퇴직소득세이므로 지방소득세 10%를 별도로 더해 고객 안내 총 세액은 표시액의 1.1배로 계산해야 해요. 중간정산특례 적용 여부에 따른 세금 차이도 함께 비교할 수 있으니 참고해 주세요. 근속연수가 짧을수록, 퇴직급여가 많을수록 퇴직소득세가 커진다. 본부 제시 매트릭스(발췌) — 1억·5년 1,036만원(10%) / 1억·10년 426만원(4%) / 2억·10년 1,966만원(10%) / 2억·20년 773만원(4%) / 5억·10년 9,781만원(20%). 원문 각주가 "실제 부과 세액은 다소 상이할 수 있음"을 명시하므로 확정 세액으로 안내하지 말고, 정확한 세액은 홈택스 모의계산 또는 [02-12-221] 시뮬레이션(F46)으로 계산한다. 기준시점 2026</t>
         </is>
       </c>
-      <c r="H75" s="19" t="inlineStr">
+      <c r="H75" s="16" t="inlineStr"/>
+      <c r="I75" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
           <t>[02-12-221] 「계산」 3단계 + 지방소득세 10% 별도 ↔ 별도분을 뺀다</t>
         </is>
       </c>
-      <c r="K75" s="16" t="inlineStr"/>
-    </row>
-    <row r="76" ht="54" customHeight="1">
+      <c r="L75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76" ht="67.5" customHeight="1">
       <c r="C76" s="13" t="n">
         <v>72</v>
       </c>
@@ -3471,24 +3561,25 @@
           <t>타사 연금 납입정보를 파악할 때 활용할 수 있는 두 가지 경로를 안내해 드릴게요. 먼저 고객이 스타뱅킹에서 생활제휴, 국민지갑, 전자증명서 순으로 이동해 「연금보험료 등 소득·세액공제 확인서」를 전송하면, 직원은 [06-7E-001] 화면에서 문서열람번호로 출력할 수 있어요. 또는 [06-10-182] 화면의 연금납입정보 집중 조회 및 정정청구등록(해제) 메뉴를 통해 연금납입정보 현황을 직접 조회하는 방법도 있어요. 이 두 번째 조회 경로를 이용하실 때는 금융거래정보제공요청동의서를 반드시 징구해야 하니 유의해 주세요.</t>
         </is>
       </c>
-      <c r="H76" s="19" t="inlineStr">
+      <c r="H76" s="16" t="inlineStr"/>
+      <c r="I76" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K76" s="16" t="inlineStr">
+        <is>
           <t>전자증명서 출력 또는 집중조회(동의서 징구 필수) ↔ 동의서 징구를 뺀다</t>
         </is>
       </c>
-      <c r="K76" s="16" t="inlineStr"/>
-    </row>
-    <row r="77" ht="27" customHeight="1">
+      <c r="L76" s="16" t="inlineStr"/>
+    </row>
+    <row r="77" ht="40.5" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
         <is>
           <t>11. 단말 화면번호</t>
@@ -3513,24 +3604,25 @@
           <t>IRP 계좌 해지 업무는 [02-12-220] 퇴직연금 지급 화면에서 진행해요. 해당 화면은 해지, 계좌이체, 미지급금 출금, 지연보상금 지급을 처리하는 화면이에요. 단일 자료에만 등장하는 내용이라 다른 화면 번호는 안내되지 않으니 참고해 주세요.</t>
         </is>
       </c>
-      <c r="H77" s="21" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr"/>
+      <c r="I77" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K77" s="16" t="inlineStr">
+        <is>
           <t>번호 + 화면명, 본문 번호가 곧 딥링크 ↔ 「연계해드릴까요?」가 붙는다(조회는 링크가 대체)</t>
         </is>
       </c>
-      <c r="K77" s="16" t="inlineStr"/>
-    </row>
-    <row r="78" ht="121.5" customHeight="1">
+      <c r="L77" s="16" t="inlineStr"/>
+    </row>
+    <row r="78" ht="135" customHeight="1">
       <c r="C78" s="13" t="n">
         <v>74</v>
       </c>
@@ -3553,22 +3645,23 @@
 ISA 만기자금 입금은 입금·입금예약·입금명부 등록을 처리하는 01-12-213 화면에서 처리해요. 해당 화면에서는 거래구분을 과세이연·계약이전입금이나 ISA 만기자금 입금으로 선택해 진행할 수 있어요. [01-12-213] ISA 만기자금 입금 거래구분을 선택하면 입금가능금액을 자동으로 조회할 수 있다는 점을 함께 참고해서 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H78" s="16" t="inlineStr">
+      <c r="H78" s="16" t="inlineStr"/>
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I78" s="16" t="inlineStr">
+      <c r="J78" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J78" s="16" t="inlineStr">
+      <c r="K78" s="16" t="inlineStr">
         <is>
           <t>번호 + 화면명 → 딥링크 ↔ 지어낸 번호로 링크를 만든다</t>
         </is>
       </c>
-      <c r="K78" s="16" t="inlineStr"/>
+      <c r="L78" s="16" t="inlineStr"/>
     </row>
     <row r="79" hidden="1">
       <c r="C79" s="13" t="n">
@@ -3590,22 +3683,23 @@
           <t>포트폴리오 운용현황 조회를 위한 화면번호는 06-12-604이며, 해당 화면은 연금 로보어드바이저 운용현황 조회를 처리하는 화면이에요. AI투자일임 및 케이봇쌤과 관련된 거래를 확인할 때 활용할 수 있어요. [06-12-604]</t>
         </is>
       </c>
-      <c r="H79" s="19" t="inlineStr">
+      <c r="H79" s="16" t="inlineStr"/>
+      <c r="I79" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
           <t>번호 + 「낡았을 수 있다」 시효 표시(데이터가 정한다) ↔ 확인 필요 아닌 화면에도 문구가 붙는다</t>
         </is>
       </c>
-      <c r="K79" s="16" t="inlineStr"/>
+      <c r="L79" s="16" t="inlineStr"/>
     </row>
     <row r="80" hidden="1">
       <c r="C80" s="13" t="n">
@@ -3629,22 +3723,23 @@
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="H80" s="19" t="inlineStr">
+      <c r="H80" s="16" t="inlineStr"/>
+      <c r="I80" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K80" s="16" t="inlineStr">
+        <is>
           <t>없다고 답한다 ↔ 그럴듯한 번호를 지어내고 딥링크까지 붙는다</t>
         </is>
       </c>
-      <c r="K80" s="16" t="inlineStr"/>
+      <c r="L80" s="16" t="inlineStr"/>
     </row>
     <row r="81" ht="27" customHeight="1">
       <c r="C81" s="13" t="n">
@@ -3666,22 +3761,23 @@
           <t>적립금과 수익률을 조회하실 때는 [04-12-642] 화면을 활용하시면 돼요. 해당 화면은 전일자 보유상품, 평가금액, 수익률 조회 및 고유계정대 이자조회를 하실 수 있는 화면이에요.</t>
         </is>
       </c>
-      <c r="H81" s="17" t="inlineStr">
+      <c r="H81" s="16" t="inlineStr"/>
+      <c r="I81" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K81" s="16" t="inlineStr">
+        <is>
           <t>[04-12-642] + 그 화면이 무엇을 하는 화면인지 ↔ 번호만 던진다</t>
         </is>
       </c>
-      <c r="K81" s="16" t="inlineStr"/>
+      <c r="L81" s="16" t="inlineStr"/>
     </row>
     <row r="82" hidden="1">
       <c r="C82" s="13" t="n">
@@ -3703,22 +3799,23 @@
           <t>문의하신 수수료 예상조회 화면번호는 [04-12-613]이에요. 해당 화면은 수수료 미납이나 납입 내역 및 예상 조회를 할 수 있고 계좌별 수수료 정보를 확인할 수 있는 화면이에요. 업무에 참고해 주세요.</t>
         </is>
       </c>
-      <c r="H82" s="19" t="inlineStr">
+      <c r="H82" s="16" t="inlineStr"/>
+      <c r="I82" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K82" s="16" t="inlineStr">
+        <is>
           <t>[04-12-613] ↔ 수수료율표(제도 수치)로 답해 화면번호를 안 준다</t>
         </is>
       </c>
-      <c r="K82" s="16" t="inlineStr"/>
+      <c r="L82" s="16" t="inlineStr"/>
     </row>
     <row r="83" hidden="1">
       <c r="C83" s="13" t="n">
@@ -3740,22 +3837,23 @@
           <t>고객 거래내역은 [04-12-644] 화면에서 확인하실 수 있어요. 해당 화면은 현금성자산 유입사유, 부담금입금내역, 입금내역 등을 조회할 수 있는 거래내역 조회 화면이에요.</t>
         </is>
       </c>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="H83" s="16" t="inlineStr"/>
+      <c r="I83" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K83" s="16" t="inlineStr">
+        <is>
           <t>거래내역 조회 화면번호 ↔ 적립금 조회 화면을 준다</t>
         </is>
       </c>
-      <c r="K83" s="16" t="inlineStr"/>
+      <c r="L83" s="16" t="inlineStr"/>
     </row>
     <row r="84" ht="67.5" customHeight="1">
       <c r="B84" s="20" t="inlineStr">
@@ -3782,24 +3880,25 @@
           <t>고객이 스타뱅킹에서 직접 추가납입할 때는 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로로 안내해 드려요. 인터넷뱅킹을 이용할 때는 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로로 들어가서 진행할 수 있어요. 이용 시간 예외로 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지 가능하니 이 시간대에 처리하도록 미리 짚어드릴게요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H84" s="21" t="inlineStr">
+      <c r="H84" s="16" t="inlineStr"/>
+      <c r="I84" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K84" s="16" t="inlineStr">
+        <is>
           <t>앱 메뉴 경로 ↔ 직원이 단말에서 할 일을 고객에게 시킨다</t>
         </is>
       </c>
-      <c r="K84" s="16" t="inlineStr"/>
-    </row>
-    <row r="85" ht="67.5" customHeight="1">
+      <c r="L84" s="16" t="inlineStr"/>
+    </row>
+    <row r="85" ht="81" customHeight="1">
       <c r="C85" s="13" t="n">
         <v>81</v>
       </c>
@@ -3820,22 +3919,23 @@
 이용 가능한 채널은 개인형IRP에 한하며, ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H85" s="19" t="inlineStr">
+      <c r="H85" s="16" t="inlineStr"/>
+      <c r="I85" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K85" s="16" t="inlineStr">
+        <is>
           <t>「안 된다」도 답이다 + 대면 경로 ↔ 「없다」로만 끝내거나 되는 것처럼 답한다</t>
         </is>
       </c>
-      <c r="K85" s="16" t="inlineStr"/>
+      <c r="L85" s="16" t="inlineStr"/>
     </row>
     <row r="86" ht="54" customHeight="1">
       <c r="C86" s="13" t="n">
@@ -3857,24 +3957,25 @@
           <t>우리 IRP에서도 ETF 매매를 할 수 있으니 고객이 직접 진행할 때 안내할 경로를 짚어드릴게요. KB스타뱅킹을 이용하는 경우 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, ETF 매매하기 순으로 이동하면 되고, 인터넷뱅킹을 이용하는 경우 KB퇴직연금, 개인고객, 퇴직연금 ETF, ETF 매매하기 경로로 접근하면 돼요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H86" s="16" t="inlineStr">
+      <c r="H86" s="16" t="inlineStr"/>
+      <c r="I86" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I86" s="16" t="inlineStr">
+      <c r="J86" s="16" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="J86" s="16" t="inlineStr">
+      <c r="K86" s="16" t="inlineStr">
         <is>
           <t>가능 여부 + 앱 경로 ↔ 단말 화면번호를 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="K86" s="16" t="inlineStr"/>
-    </row>
-    <row r="87" ht="54" customHeight="1">
+      <c r="L86" s="16" t="inlineStr"/>
+    </row>
+    <row r="87" ht="67.5" customHeight="1">
       <c r="C87" s="13" t="n">
         <v>83</v>
       </c>
@@ -3894,22 +3995,23 @@
           <t>고객이 앱이나 인터넷으로 직접 수익률과 보유상품을 확인하실 수 있도록 안내할 때는 KB스타뱅킹과 인터넷뱅킹 경로를 활용해 주시면 좋아요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 나의 퇴직연금 순으로 이동해 보유상품 수익률을 점검하실 수 있어요. 인터넷뱅킹을 이용하신다면 KB퇴직연금의 개인고객 메뉴에서 My퇴직연금의 수익률과 평가금액조회 항목을 통해 확인하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H87" s="17" t="inlineStr">
+      <c r="H87" s="16" t="inlineStr"/>
+      <c r="I87" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K87" s="16" t="inlineStr">
+        <is>
           <t>채널별 메뉴 경로 ↔ 직원 단말 화면번호를 알려준다(셋을 가른 이유 — §3)</t>
         </is>
       </c>
-      <c r="K87" s="16" t="inlineStr"/>
+      <c r="L87" s="16" t="inlineStr"/>
     </row>
     <row r="88" hidden="1">
       <c r="C88" s="13" t="n">
@@ -3934,22 +4036,23 @@
 · 디폴트옵션 상품</t>
         </is>
       </c>
-      <c r="H88" s="19" t="inlineStr">
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K88" s="16" t="inlineStr">
+        <is>
           <t>운용상품 찾기 경로 + 그 채널에서 되는지 ↔ 상품 목록을 늘어놓는다</t>
         </is>
       </c>
-      <c r="K88" s="16" t="inlineStr"/>
+      <c r="L88" s="16" t="inlineStr"/>
     </row>
     <row r="89" hidden="1">
       <c r="C89" s="13" t="n">
@@ -3971,27 +4074,28 @@
           <t>고객이 추가입금 예약을 직접 진행하실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 짚어드릴 수 있어요. KB스타뱅킹을 이용하신다면 전체메뉴 &gt; 뱅킹 &gt; 가입상품관리 &gt; 퇴직연금 &gt; 납입관리&gt;퇴직연금 입금/자동이체 – 퇴직연금 입금 경로를 통해 진행하실 수 있고, 인터넷뱅킹을 이용하신다면 KB퇴직연금 &gt; 개인고객 &gt; 입금/자동이체/해지&gt;입금(DC/기업형IRP) 경로를 통해 처리하실 수 있어요. 다만 이용 시간의 경우 부담금입금 및 예약은 09:00부터 19:00까지, 가상계좌입금은 09:00부터 18:00까지만 가능하니 이 점을 미리 안내해 드리는 것이 좋아요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H89" s="19" t="inlineStr">
+      <c r="H89" s="16" t="inlineStr"/>
+      <c r="I89" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K89" s="16" t="inlineStr">
+        <is>
           <t>부담금입금/예약 경로 ↔ 직원이 단말에서 하는 절차를 고객에게 시킨다</t>
         </is>
       </c>
-      <c r="K89" s="16" t="inlineStr"/>
-    </row>
-    <row r="90" ht="94.5" customHeight="1">
+      <c r="L89" s="16" t="inlineStr"/>
+    </row>
+    <row r="90" ht="121.5" customHeight="1">
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>13. 시황 — 상담에 쓰는 만큼</t>
+          <t>13. 시황</t>
         </is>
       </c>
       <c r="C90" s="13" t="n">
@@ -4013,24 +4117,25 @@
           <t>시장 불안을 이유로 실적배당형 상품 전환을 고민하는 고객에게는 연금의 자금 성격과 운용 기간의 특성을 활용해 접근하는 것이 핵심이에요. 연금은 일반 투자와 달리 30년 이상이라는 장기 기간을 가지며 투입되는 규모도 상대적으로 작아 마이너스 50%를 맞아도 실제 체감하는 타격이 크지 않다는 점을 짚어주세요. 일반 투자는 금액이 크고 기간이 짧아 저변동성이 맞지만, 연금은 오히려 변동성을 지향해도 된다는 논리로 고객의 통념을 전환해 줄 수 있어요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되며, 연금지급 대기나 교체매매 중으로 사용계획이 있는 자금은 먼저 걸러내야 해요. 또한 고객에게 설명할 때는 생소한 고유계정대라는 표현 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 써야 해요. 시장 상황에 대한 불안을 해소할 때는 우리나라 사람들이 실거주 부동산을 30~50년씩 보유하는 것처럼 30년 이상의 기간에는 이미 익숙하다는 점을 함께 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H90" s="17" t="inlineStr">
+      <c r="H90" s="16" t="inlineStr"/>
+      <c r="I90" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I90" s="16" t="inlineStr">
+      <c r="J90" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J90" s="16" t="inlineStr">
+      <c r="K90" s="16" t="inlineStr">
         <is>
           <t>시황 + 그걸 고객에게 옮기는 화법 ↔ 수익을 약속하거나 시황만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="K90" s="16" t="inlineStr"/>
-    </row>
-    <row r="91" ht="135" customHeight="1">
+      <c r="L90" s="16" t="inlineStr"/>
+    </row>
+    <row r="91" ht="189" customHeight="1">
       <c r="C91" s="13" t="n">
         <v>87</v>
       </c>
@@ -4056,24 +4161,25 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H91" s="19" t="inlineStr">
+      <c r="H91" s="16" t="inlineStr"/>
+      <c r="I91" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K91" s="16" t="inlineStr">
+        <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「이번 주」에 8월 3주차 일정이 나온다(시효 표시는 붙는다). 봐야 할 것은 기준시점이 빠지지 않는가</t>
         </is>
       </c>
-      <c r="K91" s="16" t="inlineStr"/>
-    </row>
-    <row r="92" ht="135" customHeight="1">
+      <c r="L91" s="16" t="inlineStr"/>
+    </row>
+    <row r="92" ht="283.5" customHeight="1">
       <c r="C92" s="13" t="n">
         <v>88</v>
       </c>
@@ -4098,24 +4204,25 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H92" s="19" t="inlineStr">
+      <c r="H92" s="16" t="inlineStr"/>
+      <c r="I92" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K92" s="16" t="inlineStr">
+        <is>
           <t>긍정·기본·부정 + 기준시점(26.09 — 시연일과 같은 달) ↔ 하나로 접어 단정 · 없는 추천상품을 지어낸다</t>
         </is>
       </c>
-      <c r="K92" s="16" t="inlineStr"/>
-    </row>
-    <row r="93" ht="108" customHeight="1">
+      <c r="L92" s="16" t="inlineStr"/>
+    </row>
+    <row r="93" ht="121.5" customHeight="1">
       <c r="C93" s="13" t="n">
         <v>89</v>
       </c>
@@ -4135,24 +4242,25 @@
           <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H93" s="19" t="inlineStr">
+      <c r="H93" s="16" t="inlineStr"/>
+      <c r="I93" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K93" s="16" t="inlineStr">
+        <is>
           <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
         </is>
       </c>
-      <c r="K93" s="16" t="inlineStr"/>
-    </row>
-    <row r="94" ht="135" customHeight="1">
+      <c r="L93" s="16" t="inlineStr"/>
+    </row>
+    <row r="94" ht="499.5" customHeight="1">
       <c r="C94" s="13" t="n">
         <v>90</v>
       </c>
@@ -4178,24 +4286,25 @@
 요즘 시황 근거로 원리금보장 자산을 그대로 두어도 되는지 판단할 때는 2026년 8월 3주차와 2026년 9월 자료에서 다루는 시장 상황과 기준시점을 확인해야 해요. 미국 7월 소비자물가가 예상에 부합하고 생산자물가는 예상을 하회하여 연준 금리 인상 우려가 완화된 반면, 미·이런 긴장에 따른 국제유가 상승과 미국 국채 금리 상승 요인이 함께 작용하고 있어요. 또한 9월에는 기준금리 동결 후 데이터 의존 입장을 반복할 것으로 예상되는 미국 FOMC와 기준금리 인상이 예상되는 일본 BOJ 금융정책결정회의 등 중요 이벤트가 예정되어 있어요. 미국 재정적자 확대와 장기국채 수요 감소를 감안해 장기금리 하락은 비중 축소 기회로 활용할 수 있으며, BOJ의 기준금리 인상과 엔 캐리 청산 우려가 있으나 인상이 예상된 이벤트라 2024년 8월과 같은 증시 폭락 가능성은 낮다고 판단하고 있어요. 다만 사용계획이 있는 자금인 연금지급 대기나 교체매매 중인 자금은 먼저 걸러내어 판단해야 해요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.09 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H94" s="19" t="inlineStr">
+      <c r="H94" s="16" t="inlineStr"/>
+      <c r="I94" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I94" s="16" t="inlineStr">
+      <c r="J94" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J94" s="16" t="inlineStr">
+      <c r="K94" s="16" t="inlineStr">
         <is>
           <t>시황 + 이 고객 상태 ↔ 근거 없이 「지금은 예금이 유리」식 판단을 지어낸다</t>
         </is>
       </c>
-      <c r="K94" s="16" t="inlineStr"/>
-    </row>
-    <row r="95" ht="135" customHeight="1">
+      <c r="L94" s="16" t="inlineStr"/>
+    </row>
+    <row r="95" ht="216" customHeight="1">
       <c r="A95" s="26" t="inlineStr">
         <is>
           <t>Ⅳ. 고객 응대 — 이 고객에게 무엇을 권할 수 있고, 어떻게 말할 것인가</t>
@@ -4233,24 +4342,25 @@
 반면 KB 글로벌채권인덱스 C-P, KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 중립형 MP, KB 성장형 MP, KB 글로벌리츠 ETF는 상품 위험등급이 허용 상한인 낮은위험보다 높아 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr"/>
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
+      <c r="J95" s="10" t="inlineStr">
         <is>
           <t>보수 성향 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="J95" s="10" t="inlineStr">
+      <c r="K95" s="10" t="inlineStr">
         <is>
           <t>위험등급 상한 + 통과 목록 + **제외 상품과 사유** + 권유 아님 표시 ↔ 권유 표현을 쓴다</t>
         </is>
       </c>
-      <c r="K95" s="10" t="inlineStr"/>
-    </row>
-    <row r="96" ht="135" customHeight="1">
+      <c r="L95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96" ht="364.5" customHeight="1">
       <c r="C96" s="13" t="n">
         <v>92</v>
       </c>
@@ -4259,7 +4369,28 @@
           <t>왜 이 상품은 목록에서 빠진 거야?</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr"/>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>1. 이 고객한테 뭘 추천해주면 좋을까?
+→ 이 고객의 투자성향 적합성 허용 상한은 낮은위험이에요. 
+이 고객에게 안내할 수 있는 상품은 아래와 같아요.
+- KB 국내채권형 C-P — 낮은위험
+- KB 안정형 MP — 낮은위험
+- KB GIC 확정금리 — 매우낮은위험
+- KB ELB 지수연계 — 낮은위험
+- KB 정기예금(1년) — 매우낮은위험
+- KB 원리금보장 안정 포트폴리오 — 매우낮은위험
+아래 상품들은 고객의 허용 상한을 초과하여 안내할 수 없어요.
+- KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험
+- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험
+- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험
+- KB 중립형 MP — 상품 위험등급 보통위험
+- KB 성장형 MP — 상품 위험등급 다소높은위험
+- KB 글로벌리츠 ETF — 상품 위험등급 높은위험
+이 목록은 고객의 적합성 확인 결과이며 특정 상품을 권유하는 것은 아니에요.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
           <t>제외 있는 고객</t>
@@ -4267,32 +4398,35 @@
       </c>
       <c r="G96" s="16" t="inlineStr">
         <is>
-          <t>이 고객에게 안내할 수 없는 상품이 목록에서 빠진 이유는 고객의 투자성향이 안정추구형이라 위험등급 허용 상한이 낮은위험으로 정해져 있기 때문이에요. 앞서 말씀드린 안내할 수 없는 상품들은 상품 자체의 위험등급이 고객의 허용 상한보다 높아 제외되었으며, 구체적인 내용은 다음과 같아요.
-- KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
-- KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
-- KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
-- KB 중립형 MP —상품 위험등급 보통위험 &gt; 허용 상한 낮은위험
-- KB 성장형 MP — 상품 위험등급 다소높은위험 &gt; 허용 상한 낮은위험
-- KB 글로벌리츠 ETF — 상품 위험등급 높은위험 &gt; 허용 상한 낮은위험
+          <t>오세훈 고객에게 안내할 수 없는 상품들이 목록에서 빠진 이유는 고객님의 적합성 허용 상한인 낮은위험 등급을 초과했기 때문이에요. 
+안내할 수 없는 상품들의 구체적인 등급은 다음과 같아요.
+· KB 글로벌채권인덱스 C-P — 상품 위험등급 보통위험
+· KB 온국민TDF2035 C-P — 상품 위험등급 다소높은위험
+· KB 온국민TDF2040 C-P — 상품 위험등급 다소높은위험
+· KB 중립형 MP — 상품 위험등급 보통위험
+· KB 성장형 MP — 상품 위험등급 다소높은위험
+· KB 글로벌리츠 ETF — 상품 위험등급 높은위험
+이 목록은 고객의 적합성 확인 결과에 따른 안내 가능 여부를 정리한 것이며, 특정 상품에 대한 투자권유를 의미하는 것은 아니에요.
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H96" s="17" t="inlineStr">
+      <c r="H96" s="16" t="inlineStr"/>
+      <c r="I96" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I96" s="16" t="inlineStr">
+      <c r="J96" s="16" t="inlineStr">
         <is>
           <t>제외 있는 고객 — 예: 오세훈 193482-6012375</t>
         </is>
       </c>
-      <c r="J96" s="16" t="inlineStr">
+      <c r="K96" s="16" t="inlineStr">
         <is>
           <t>제외 사유 ↔ 사유를 지어낸다(답 못 하면 직원은 목록을 안 믿는다)</t>
         </is>
       </c>
-      <c r="K96" s="16" t="inlineStr">
+      <c r="L96" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
@@ -4331,24 +4465,25 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H97" s="16" t="inlineStr">
+      <c r="H97" s="16" t="inlineStr"/>
+      <c r="I97" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 대본</t>
         </is>
       </c>
-      <c r="I97" s="16" t="inlineStr">
+      <c r="J97" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="J97" s="16" t="inlineStr">
+      <c r="K97" s="16" t="inlineStr">
         <is>
           <t>제외 0건이면 「제외 없음」을 명시 ↔ 통과 목록에서 하나 빼고 사유를 지어낸다(실측 사고)</t>
         </is>
       </c>
-      <c r="K97" s="16" t="inlineStr"/>
-    </row>
-    <row r="98" ht="135" customHeight="1">
+      <c r="L97" s="16" t="inlineStr"/>
+    </row>
+    <row r="98" ht="607.5" customHeight="1">
       <c r="C98" s="13" t="n">
         <v>94</v>
       </c>
@@ -4392,24 +4527,25 @@
 반면에 글로벌채권인덱스 C-P, 온국민TDF2035 C-P, 온국민TDF2040 C-P, 중립형 MP, 성장형 MP, 글로벌리츠 ETF 같은 상품들은 상품 위험등급이 보통위험에서 높은위험까지로 고객의 허용 상한인 낮은위험을 초과하기 때문에 안내할 수 없어요. 이는 어디까지나 적합성 확인 결과에 따른 안내이며 특정 상품에 대한 투자권유가 아니라는 점을 염두에 두셔야 해요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H98" s="19" t="inlineStr">
+      <c r="H98" s="16" t="inlineStr"/>
+      <c r="I98" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I98" s="16" t="inlineStr">
+      <c r="J98" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J98" s="16" t="inlineStr">
+      <c r="K98" s="16" t="inlineStr">
         <is>
           <t>범위 밖은 안내 안 한다 ↔ 범위 밖 상품을 안내하거나 판정을 새로 한다</t>
         </is>
       </c>
-      <c r="K98" s="16" t="inlineStr"/>
-    </row>
-    <row r="99" ht="135" customHeight="1">
+      <c r="L98" s="16" t="inlineStr"/>
+    </row>
+    <row r="99" ht="594" customHeight="1">
       <c r="C99" s="13" t="n">
         <v>95</v>
       </c>
@@ -4456,24 +4592,25 @@
 이외에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험보다 높아 안내할 수 없으며, KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이라 안내할 수 없어요. 이 안내는 적합성 확인 결과이며 투자권유가 아니라는 점을 염두에 두시고, 사용계획이 있는 자금이라면 먼저 걸러내어 현금성자산이나 운용지시가 되지 않는 자산으로 다루어 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H99" s="16" t="inlineStr">
+      <c r="H99" s="16" t="inlineStr"/>
+      <c r="I99" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I99" s="16" t="inlineStr">
+      <c r="J99" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J99" s="16" t="inlineStr">
+      <c r="K99" s="16" t="inlineStr">
         <is>
           <t>그 성향 범위 안에서 ↔ 범위 밖 상품을 안내한다</t>
         </is>
       </c>
-      <c r="K99" s="16" t="inlineStr"/>
-    </row>
-    <row r="100" ht="135" customHeight="1">
+      <c r="L99" s="16" t="inlineStr"/>
+    </row>
+    <row r="100" ht="148.5" customHeight="1">
       <c r="C100" s="13" t="n">
         <v>96</v>
       </c>
@@ -4498,22 +4635,23 @@
 이 안내는 고객의 투자성향에 따른 적합성 확인 결과이며 특정 상품에 대한 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H100" s="17" t="inlineStr">
+      <c r="H100" s="16" t="inlineStr"/>
+      <c r="I100" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I100" s="16" t="inlineStr">
+      <c r="J100" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J100" s="16" t="inlineStr">
+      <c r="K100" s="16" t="inlineStr">
         <is>
           <t>제외된 상품 + 사유 ↔ 「없다」로 끝내거나 사유를 지어낸다(§5 — 0건일 때 침묵하지 않는다)</t>
         </is>
       </c>
-      <c r="K100" s="16" t="inlineStr"/>
+      <c r="L100" s="16" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
       <c r="C101" s="13" t="n">
@@ -4550,22 +4688,23 @@
 이 안내는 적합성 확인 결과이며 투자권유가 아니에요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H101" s="19" t="inlineStr">
+      <c r="H101" s="16" t="inlineStr"/>
+      <c r="I101" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I101" s="16" t="inlineStr">
+      <c r="J101" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J101" s="16" t="inlineStr">
+      <c r="K101" s="16" t="inlineStr">
         <is>
           <t>허용 위험등급 상한 + 투자권유가 아니라는 표시 ↔ 상한만 던진다</t>
         </is>
       </c>
-      <c r="K101" s="16" t="inlineStr"/>
+      <c r="L101" s="16" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
       <c r="B102" s="20" t="inlineStr">
@@ -4602,24 +4741,25 @@
 반면에 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP는 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하며, KB 글로벌리츠 ETF는 높은위험으로 역시 허용 상한을 초과하여 목록에 포함되지 않아요. 이 목록은 고객의 적합성 확인 결과에 따른 안내 가능 범위이며 특정 상품의 가입을 권유하는 것이 아니니 유의해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H102" s="17" t="inlineStr">
+      <c r="H102" s="16" t="inlineStr"/>
+      <c r="I102" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I102" s="16" t="inlineStr">
+      <c r="J102" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J102" s="16" t="inlineStr">
+      <c r="K102" s="16" t="inlineStr">
         <is>
           <t>출생연도 → TDF 2035 매핑 + 운용사별 비중 + 기준시점 ↔ 빈티지를 잘못 매핑하거나 비중을 섞는다</t>
         </is>
       </c>
-      <c r="K102" s="16" t="inlineStr"/>
-    </row>
-    <row r="103" ht="135" customHeight="1">
+      <c r="L102" s="16" t="inlineStr"/>
+    </row>
+    <row r="103" ht="850.5" customHeight="1">
       <c r="C103" s="13" t="n">
         <v>99</v>
       </c>
@@ -4681,24 +4821,25 @@
   ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H103" s="17" t="inlineStr">
+      <c r="H103" s="16" t="inlineStr"/>
+      <c r="I103" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K103" s="16" t="inlineStr">
+        <is>
           <t>구분별 상품 + 위험등급 + 기준시점 ↔ 기준시점 없이 단정 · 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="K103" s="16" t="inlineStr"/>
-    </row>
-    <row r="104" ht="108" customHeight="1">
+      <c r="L103" s="16" t="inlineStr"/>
+    </row>
+    <row r="104" ht="121.5" customHeight="1">
       <c r="C104" s="13" t="n">
         <v>100</v>
       </c>
@@ -4718,24 +4859,25 @@
           <t>수익률 비교 질문을 하는 고객에게는 금융감독원 공시와 디폴트옵션 실적을 근거로 제시하면서 장기적인 관점의 관리를 약속하는 방식으로 접근해야 해요. 다른 은행과 비교하는 고객에게는 단기 성과보다 장기 관리가 중요하다는 점을 짚어주는 것이 핵심이에요. IRP 실적배당형 부문 전 구간 1위와 디폴트옵션 수익률 순위를 안내할 수 있도록 "2026년 1분기 금융감독원 발표에 따르면, KB국민은행이 IRP 실적배당형 부문에서 최근 1년, 3년, 5년, 7년 수익률 모두 주요 시중은행 가운데 가장 높은 수익률을 기록했습니다. 이는 꾸준한 고객관리로 만들어낸 결과물이죠^^"라고 말씀드려 보세요. 또한 디폴트옵션 고위험 포트폴리오의 실적을 바탕으로 "고객님, 저희 퇴직연금 디폴트옵션 고위험 포트폴리오 2025년 4분기 기준 개인형IRP 수익률 1위입니다. 전체 42개 사업자 중 2위예요. 퇴직연금은 단기 성과보다는 장기적으로 꾸준히 관리하는 게 더 중요한 상품입니다. 지속적인 관리가 핵심으로 앞으로는 제가 꾸준히 관리해 드리겠습니다."라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="H104" s="21" t="inlineStr">
+      <c r="H104" s="16" t="inlineStr"/>
+      <c r="I104" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K104" s="16" t="inlineStr">
+        <is>
           <t>타행 대비 수익률 카드 + 기준시점 ↔ 상품 표 9종을 받고 위험등급을 되물으며 끝난다</t>
         </is>
       </c>
-      <c r="K104" s="16" t="inlineStr"/>
-    </row>
-    <row r="105" ht="135" customHeight="1">
+      <c r="L104" s="16" t="inlineStr"/>
+    </row>
+    <row r="105" ht="769.5" customHeight="1">
       <c r="C105" s="13" t="n">
         <v>101</v>
       </c>
@@ -4794,22 +4936,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H105" s="19" t="inlineStr">
+      <c r="H105" s="16" t="inlineStr"/>
+      <c r="I105" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K105" s="16" t="inlineStr">
+        <is>
           <t>구성상품·비중·금리 + 기준시점 ↔ 상품명을 지어내거나 다른 포트폴리오를 섞는다</t>
         </is>
       </c>
-      <c r="K105" s="16" t="inlineStr"/>
+      <c r="L105" s="16" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
       <c r="C106" s="13" t="n">
@@ -4831,24 +4974,25 @@
           <t>직원이 물어본 TDF 수익률 및 위험등급에 대해서는 현재 준비된 자료가 없어요. 다만 2026년 3월에 작성된 연금사업본부 연금컨설팅부 자료를 기준으로 2025년 10월 기준 당행 라인업의 개념과 선택 공식에 관한 내용은 확인할 수 있어요. TDF는 은퇴 시점에 맞춰 주식→채권 비중을 자동 조정하는 자산배분 펀드다(전략 명칭 글라이드 패스). 상품명 숫자 = 목표 은퇴연도, 5년 단위 빈티지. 선택 공식 출생연도 + 예상 은퇴연령 = Target Date(예: 1990+60=2050). 당행 라인업 총 18종(2025.10 기준). 환헤지 여부로 H(헤지) / UH(언헤지) 상품이 구분된다 — H는 환율 변동 영향 축소, UH는 환차익·환차손 반영. 관련 내용은 기준시점 2025.10 (KBthink 04) 기준으로 안내해 드릴 수 있어요.</t>
         </is>
       </c>
-      <c r="H106" s="19" t="inlineStr">
+      <c r="H106" s="16" t="inlineStr"/>
+      <c r="I106" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K106" s="16" t="inlineStr">
+        <is>
           <t>기간별 수익률 + 위험등급 + 기준시점 ↔ 실재 상품인데 「미등록」으로 폐기 · 과거 수익률을 기대수익으로 단정</t>
         </is>
       </c>
-      <c r="K106" s="16" t="inlineStr"/>
-    </row>
-    <row r="107" ht="135" customHeight="1">
+      <c r="L106" s="16" t="inlineStr"/>
+    </row>
+    <row r="107" ht="202.5" customHeight="1">
       <c r="C107" s="13" t="n">
         <v>103</v>
       </c>
@@ -4873,22 +5017,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H107" s="19" t="inlineStr">
+      <c r="H107" s="16" t="inlineStr"/>
+      <c r="I107" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K107" s="16" t="inlineStr">
+        <is>
           <t>그 성향 구성 + 기준시점 ↔ 고객 특정 질문으로 읽혀 일반 자료가 전멸한다</t>
         </is>
       </c>
-      <c r="K107" s="16" t="inlineStr"/>
+      <c r="L107" s="16" t="inlineStr"/>
     </row>
     <row r="108" hidden="1">
       <c r="B108" s="20" t="inlineStr">
@@ -4915,24 +5060,25 @@
           <t>이수민 고객이 개인형IRP 계좌에 300만 원을 추가 납입할 때의 환급 예상액을 안내할 때는 개인형IRP 계좌 추가 납입액 300만 원을 기준으로 총급여 구간에 따른 환급액을 짚어 주어야 해요. 이 고객의 당해 납입액은 0원이고 세액공제 잔여한도는 900만 원이라 추가 납입하는 300만 원 전액이 공제 대상이 돼요. 공제율은 원장의 총급여 구간에서 확인된 값에 따르므로, 총급여 5,500만 원 이하로 16.5%가 적용되는 경우라면 "개인형IRP 계좌에 300만 원을 추가 납입하시면 총급여 5,500만 원 이하 기준 16.5% 공제율이 적용되어 495,000원을 환급받으실 수 있어요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 또한 사용계획이 있는 자금인지는 먼저 걸러내고, 고객에게 생소한 "고유계정대" 같은 용어 대신 "현금성자산"이나 "운용지시가 되지 않는 자산"이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H108" s="21" t="inlineStr">
+      <c r="H108" s="16" t="inlineStr"/>
+      <c r="I108" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I108" s="16" t="inlineStr">
+      <c r="J108" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J108" s="16" t="inlineStr">
+      <c r="K108" s="16" t="inlineStr">
         <is>
           <t>**되묻지 않는다** — 원장의 총급여 구간으로 계산한다(박지민 16.5% · 한지우 13.2%). 환급액 + 어느 계좌인지 + 결정세액 단서 ↔ 총급여를 되묻거나 정해진 걸 「가정하면」으로 적는다</t>
         </is>
       </c>
-      <c r="K108" s="16" t="inlineStr"/>
-    </row>
-    <row r="109" ht="67.5" customHeight="1">
+      <c r="L108" s="16" t="inlineStr"/>
+    </row>
+    <row r="109" ht="81" customHeight="1">
       <c r="C109" s="13" t="n">
         <v>105</v>
       </c>
@@ -4952,24 +5098,25 @@
           <t>이수민 고객의 추가 납입 한도를 채울 때는 개인형IRP 계좌에 900만원을 더 넣어야 해요. 총급여 5,500만원 이하인 고객이라면 16.5% 공제율을 적용해 1,485,000원을 돌려받을 수 있고, 총급여 5,500만원 초과 고객이라면 13.2% 공제율을 적용해 1,188,000원을 돌려받을 수 있어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 고객의 정확한 총급여 구간은 아직 단말 원장에 나타나지 않아 두 경우를 다 실었으니, 고객의 소득 구간을 먼저 확인한 뒤에 해당하는 금액으로 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H109" s="16" t="inlineStr">
+      <c r="H109" s="16" t="inlineStr"/>
+      <c r="I109" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I109" s="16" t="inlineStr">
+      <c r="J109" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J109" s="16" t="inlineStr">
+      <c r="K109" s="16" t="inlineStr">
         <is>
           <t>원장의 잔여한도 + 원장의 구간으로 계산 ↔ 총급여를 되묻거나, IRP 납입액만으로 한도를 다시 계산한다(연금저축과 공유하는 한도다)</t>
         </is>
       </c>
-      <c r="K109" s="16" t="inlineStr"/>
-    </row>
-    <row r="110" ht="135" customHeight="1">
+      <c r="L109" s="16" t="inlineStr"/>
+    </row>
+    <row r="110" ht="148.5" customHeight="1">
       <c r="C110" s="13" t="n">
         <v>106</v>
       </c>
@@ -4992,24 +5139,25 @@
 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H110" s="17" t="inlineStr">
+      <c r="H110" s="16" t="inlineStr"/>
+      <c r="I110" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I110" s="16" t="inlineStr">
+      <c r="J110" s="16" t="inlineStr">
         <is>
           <t>한도 0인 7명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J110" s="16" t="inlineStr">
+      <c r="K110" s="16" t="inlineStr">
         <is>
           <t>「추가 공제 없음」 + 결정세액 단서는 **안 붙인다** ↔ 환급액을 만들거나 무관한 경고가 붙는다</t>
         </is>
       </c>
-      <c r="K110" s="16" t="inlineStr"/>
-    </row>
-    <row r="111" ht="135" customHeight="1">
+      <c r="L110" s="16" t="inlineStr"/>
+    </row>
+    <row r="111" ht="661.5" customHeight="1">
       <c r="C111" s="13" t="n">
         <v>107</v>
       </c>
@@ -5062,24 +5210,25 @@
 · 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
         </is>
       </c>
-      <c r="H111" s="21" t="inlineStr">
+      <c r="H111" s="16" t="inlineStr"/>
+      <c r="I111" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I111" s="16" t="inlineStr">
+      <c r="J111" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J111" s="16" t="inlineStr">
+      <c r="K111" s="16" t="inlineStr">
         <is>
           <t>총급여 구간을 되묻거나 전환 특례 축을 한도와 **갈라** 답한다 ↔ 잔여한도를 상한처럼 말한다</t>
         </is>
       </c>
-      <c r="K111" s="16" t="inlineStr"/>
-    </row>
-    <row r="112" ht="135" customHeight="1">
+      <c r="L111" s="16" t="inlineStr"/>
+    </row>
+    <row r="112" ht="256.5" customHeight="1">
       <c r="C112" s="13" t="n">
         <v>108</v>
       </c>
@@ -5104,24 +5253,25 @@
 ISA 만기자금 8,000만원을 개인형IRP 계좌로 전환하면 세액공제 대상 한도가 늘어나 환급액을 더 받을 수 있어요. 한지우 고객의 총급여 5,500만원 초과(13.2%) 기준으로 전환액 8,000만원에 대해 추가 공제 대상 300만원이 적용되어 396,000원의 환급액이 늘어나요. 이 금액은 현금을 더 납입하는 경우와 별개로 더해지는 몫이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H112" s="16" t="inlineStr">
+      <c r="H112" s="16" t="inlineStr"/>
+      <c r="I112" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I112" s="16" t="inlineStr">
+      <c r="J112" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J112" s="16" t="inlineStr">
+      <c r="K112" s="16" t="inlineStr">
         <is>
           <t>전환 특례(최대 1,200만원)와 연 납입한도를 갈라 답한다 ↔ 「전액이 공제 대상」 · 가장 작은 숫자가 상한이 된다</t>
         </is>
       </c>
-      <c r="K112" s="16" t="inlineStr"/>
-    </row>
-    <row r="113" ht="135" customHeight="1">
+      <c r="L112" s="16" t="inlineStr"/>
+    </row>
+    <row r="113" ht="850.5" customHeight="1">
       <c r="C113" s="13" t="n">
         <v>109</v>
       </c>
@@ -5130,7 +5280,41 @@
           <t>(총급여 구간 되묻기 뒤) 초과야</t>
         </is>
       </c>
-      <c r="E113" s="14" t="inlineStr"/>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>● 김서연
+1. 고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?
+→ 김서연 고객의 ISA 만기자금 8천만원 중 일부만 IRP 계좌로 전환할 때의 세액공제는 전환하신 금액에 따라 달라집니다. 
+전환금액의 10%가 세액공제 대상에 더해지며 상한은 300만원입니다. 
+총급여 5,500만원 이하 구간을 기준으로 전환액에 따른 추가 공제 대상과 환급액은 다음과 같이 달라집니다.
+- 1,000만원 — 추가 공제 대상 100만원
+- 2,000만원 — 추가 공제 대상 200만원
+- 3,000만원 — 추가 공제 대상 300만원(상한)
+- 8,000만원 — 추가 공제 대상 300만원(상한)
+이 금액은 현금을 직접 더 납입하는 경우와 별개로 더해지는 몫입니다.
+※ 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.
+● 한지우
+1. 고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?
+→ 답변 문장이 근거 검증을 통과하지 못해서, 찾은 근거를 원문 그대로 보여드려요 — 아래는 제가 쓴 문장이 아니라 자료 원문입니다.
+(자료에 없는 수치·상품명)
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 8,000만원
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 공제율은 **원장의 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 더해지는 것은 전환액의 10%뿐이고 전환액 자체가 공제 대상이 되지는 않는다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 10%는 800만원이지만 상한에서 잘려 추가 공제 대상 300만원
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
+        </is>
+      </c>
       <c r="F113" s="15" t="inlineStr">
         <is>
           <t>김서연(5500이하) ↔ 한지우(5500초과)</t>
@@ -5139,32 +5323,62 @@
       <c r="G113" s="16" t="inlineStr">
         <is>
           <t>● 김서연
-총급여 5,500만원 초과 구간인 고객에게는 ISA 만기자금 중 일부를 개인형IRP 계좌로 전환할 때의 세액공제 효과를 금액별로 짚어주는 게 핵심이에요. 앞서 말씀드린 8,000만원 전액 전환 시의 추가 공제 대상 300만원과 늘어나는 환급액 396,000원 외에, 질문하신 일부 금액 전환 시에는 전환액 1,000만원일 때 추가 공제 대상 100만원과 전환액 2,000만원일 때 추가 공제 대상 200만원이 적용돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 이 금액들은 현금을 더 납입하는 경우와 별개로 더해지는 몫이니, 두 한도를 같은 안에서 저울질하지 않고 각각 안내해 주세요.
+답변 문장이 근거 검증을 통과하지 못해서, 찾은 근거를 원문 그대로 보여드려요 — 아래는 제가 쓴 문장이 아니라 자료 원문입니다.
+(자료에 없는 수치·상품명)
+■ 세액공제 환급 예상액 — 김서연 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 400만원 · 세액공제 한도 900만원 · 잔여한도 500만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 500만원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 공제 대상 400만원 → 900만원 (잔여한도 500만원까지)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 528,000원 → 1,188,000원 (늘어나는 금액 660,000원)
+· 공제율은 **직원이 이번 턴에 말한 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-30 (D-1) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 더해지는 것은 전환액의 10%뿐이고 전환액 자체가 공제 대상이 되지는 않는다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 10%는 800만원이지만 상한에서 잘려 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다
 ● 한지우
-ISA 만기자금 중 일부를 IRP 계좌로 전환할 때는 전환액의 10%가 세액공제 대상에 더해져 공제 한도가 최대 1,200만원까지 늘어나요. 
-고객이 8천만원 중 일부만 전환하는 경우, 전환액별로 추가되는 공제 대상 금액은 다음과 같이 달라져요.
-- 1,000만원 전환 — 추가 공제 대상 100만원
-- 2,000만원 전환 — 추가 공제 대상 200만원
-- 3,000만원 이상 전환 — 추가 공제 대상 300만원(상한)
-총급여가 5,500만원을 초과해 13.2%의 공제율이 적용되는 경우, 전환액 3,000만원 이상을 넣으면 늘어나는 환급액은 396,000원이 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 앞서 말씀드린 현금 추가 납입분과 ISA 전환분은 서로 다른 한도이므로 같은 한도 안에서 저울질하지 않도록 안내해 주세요.</t>
-        </is>
-      </c>
-      <c r="H113" s="21" t="inlineStr">
+답변 문장이 근거 검증을 통과하지 못해서, 찾은 근거를 원문 그대로 보여드려요 — 아래는 제가 쓴 문장이 아니라 자료 원문입니다.
+(자료에 없는 수치·상품명)
+■ 세액공제 환급 예상액 — 한지우 고객 · 현금을 더 납입하는 경우 (시스템 계산 — 검색 결과가 아니다)
+· 어디에 넣는 금액인가: 이 고객의 **개인형IRP 계좌 추가 납입**이다
+· 당해 납입액 600만원 · 세액공제 한도 900만원 · 잔여한도 300만원 — 한도와 잔여한도는 연금저축 납입분까지 합산한 값이다(원장 값)
+· 계산에 쓴 추가 납입액 300만원 (질문에 금액이 없어 잔여한도로 계산했다)
+· 공제 대상 600만원 → 900만원 (잔여한도 300만원까지)
+· 총급여 5,500만원 초과(13.2%): 환급 예상 792,000원 → 1,188,000원 (늘어나는 금액 396,000원)
+· 공제율은 **직원이 이번 턴에 말한 총급여 구간**에서 나온 값이다 — 되물을 것이 없다
+■ ISA 만기자금을 전환하는 경우 — 위 계산과 **다른 축**이다 (잔여한도 안에서 나눠 쓰는 것이 아니라, 공제 대상 한도 자체가 늘어난다)
+· ISA 만기자금 8,000만원 · 만기 2026-09-05 (만기 24일 경과 · 전환 기한 36일 남음) · 타행 — 만기일로부터 60일 이내에 전환한다
+· 전환금은 연 납입한도 1,800만원과 무관하다 — 만기금액의 전부 또는 일부를 넣을 수 있다
+· 전환액의 10%가 세액공제 대상에 **더해진다**(상한 300만원) — 전환액 3,000만원에서 상한에 닿는다. 더해지는 것은 전환액의 10%뿐이고 전환액 자체가 공제 대상이 되지는 않는다
+· 그래서 공제 대상 한도가 900만원에서 최대 1,200만원으로 늘어난다
+· 전환액별 추가 공제 대상: 1,000만원 → 100만원 · 2,000만원 → 200만원 · 3,000만원 → 300만원(상한) · 8,000만원 → 300만원(상한)
+· 계산에 쓴 전환액 8,000만원 → 10%는 800만원이지만 상한에서 잘려 추가 공제 대상 300만원 (질문에 금액이 없어 만기금액 전부로 계산했다)
+· 총급여 5,500만원 초과(13.2%): 이 전환으로 늘어나는 환급 396,000원
+· 이 금액은 위의 «현금을 더 납입하는 경우»와 별개로 더해지는 몫이다 — 둘을 같은 한도 안에서 저울질하지 않는다</t>
+        </is>
+      </c>
+      <c r="H113" s="16" t="inlineStr"/>
+      <c r="I113" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I113" s="16" t="inlineStr">
+      <c r="J113" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J113" s="16" t="inlineStr">
+      <c r="K113" s="16" t="inlineStr">
         <is>
           <t>원래 질문(300만원)과 고른 갈래를 합쳐 13.2% 로 ↔ 「5,500만원」을 납입액으로 읽어 틀린 환급액</t>
         </is>
       </c>
-      <c r="K113" s="16" t="inlineStr">
+      <c r="L113" s="16" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
@@ -5193,22 +5407,23 @@
 총급여가 5,500만원 이하인 고객에게는 개인형IRP 계좌로 ISA 만기자금을 일부 전환할 때 전환액에 따라 추가 공제 대상이 달라진다는 점을 짚어주는 게 핵심이에요. 앞서 말씀드린 대로 전환액의 10%가 세액공제 대상에 더해지며 상한은 300만원이에요. 전환액별 추가 공제 대상은 1,000만원이면 100만원, 2,000만원이면 200만원, 3,000만원 이상이면 상한인 300만원이 적용되어요. 총급여 5,500만원 이하 구간에서는 16.5%의 공제율이 적용되어 전환액 3,000만원 이상일 때 늘어나는 환급액은 495,000원이 되어요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H114" s="19" t="inlineStr">
+      <c r="H114" s="16" t="inlineStr"/>
+      <c r="I114" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I114" s="16" t="inlineStr">
+      <c r="J114" s="16" t="inlineStr">
         <is>
           <t>ISA 보유 — 김서연 171203-4815062(5500이하) ↔ 한지우 176903-5528417(5500초과)</t>
         </is>
       </c>
-      <c r="J114" s="16" t="inlineStr">
+      <c r="K114" s="16" t="inlineStr">
         <is>
           <t>같은 자리에서 **16.5%** 로 갈린다(300만원이면 495,000원) ↔ 13.2% 로 답하거나 원장 구간이 이긴다고 직원 말을 무시한다</t>
         </is>
       </c>
-      <c r="K114" s="16" t="inlineStr">
+      <c r="L114" s="16" t="inlineStr">
         <is>
           <t>고객이 8천만원 전부는 부담스럽다는데, 일부만 옮기면 세액공제는 어떻게 돼?</t>
         </is>
@@ -5234,22 +5449,23 @@
           <t>오늘 날짜는 2026년 9월 29일 월요일이고 2026년 연말까지는 오늘을 세지 않고 93일 남았어요. 세액공제를 받으려면 올해 12월 31일까지 납입해야 해요.</t>
         </is>
       </c>
-      <c r="H115" s="16" t="inlineStr">
+      <c r="H115" s="16" t="inlineStr"/>
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K115" s="16" t="inlineStr">
+        <is>
           <t>오늘 + 남은 일수 + 마감 ↔ 학습 시점 감각으로 틀린 날짜를 말하거나 문장이 잘린다</t>
         </is>
       </c>
-      <c r="K115" s="16" t="inlineStr"/>
+      <c r="L115" s="16" t="inlineStr"/>
     </row>
     <row r="116" hidden="1">
       <c r="C116" s="13" t="n">
@@ -5271,22 +5487,23 @@
           <t>해당 고객의 잔액 기준 시점에 대한 자료는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="H116" s="19" t="inlineStr">
+      <c r="H116" s="16" t="inlineStr"/>
+      <c r="I116" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I116" s="16" t="inlineStr">
+      <c r="J116" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J116" s="16" t="inlineStr">
+      <c r="K116" s="16" t="inlineStr">
         <is>
           <t>잔액은 원장일(8/24), 잔여일수는 오늘 ↔ 두 시간축을 섞는다</t>
         </is>
       </c>
-      <c r="K116" s="16" t="inlineStr"/>
+      <c r="L116" s="16" t="inlineStr"/>
     </row>
     <row r="117" hidden="1">
       <c r="C117" s="13" t="n">
@@ -5308,24 +5525,25 @@
           <t>ISA 만기자금을 개인형IRP 계좌로 전환할 때 300만원을 넣으면 적용받는 공제율에 따라 환급액이 달라져요. 총급여 5,500만원 이하인 경우 16.5%를 적용하여 개인형IRP 계좌 추가 납입으로 495,000원의 환급을 받게 되고, 총급여 5,500만원 초과인 경우 13.2%를 적용하여 개인형IRP 계좌 추가 납입으로 396,000원의 환급을 받게 돼요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H117" s="19" t="inlineStr">
+      <c r="H117" s="16" t="inlineStr"/>
+      <c r="I117" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I117" s="16" t="inlineStr">
+      <c r="J117" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J117" s="16" t="inlineStr">
+      <c r="K117" s="16" t="inlineStr">
         <is>
           <t>단위 없는 맨숫자는 금액으로 안 읽는다 ↔ 임의로 정해 계산한다(틀린 입력이 승인된 숫자가 된다)</t>
         </is>
       </c>
-      <c r="K117" s="16" t="inlineStr"/>
-    </row>
-    <row r="118" ht="81" customHeight="1">
+      <c r="L117" s="16" t="inlineStr"/>
+    </row>
+    <row r="118" ht="94.5" customHeight="1">
       <c r="B118" s="20" t="inlineStr">
         <is>
           <t>17. 상담 화법·반론 대응</t>
@@ -5350,24 +5568,25 @@
           <t>손실만 나고 해지하겠다는 고객에게는 보유 포트폴리오 유형으로 화법을 분기하여, 저희가 세심하게 관리를 해드렸어야 했는데 죄송합니다라고 먼저 관리 미흡을 사과하고 그 자리에서 매도와 재추천이라는 액션을 약속하는 방식으로 접근해야 해요. 본부 교육 영상에서는 공시 순위를 앞세우지 않고 이처럼 사과와 원인 규명에 이어 즉시 리밸런싱을 3단으로 밟아나가는 방식을 권하고 있어요. 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속해서는 안 되며, 근거는 수익률 예측이 아니라 운용 여건의 차이에 두어야 해요. 또한 연금지급 대기나 교체매매 중인 자금처럼 사용계획이 있는 자금은 미리 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 상담 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H118" s="21" t="inlineStr">
+      <c r="H118" s="16" t="inlineStr"/>
+      <c r="I118" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I118" s="16" t="inlineStr">
+      <c r="J118" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J118" s="16" t="inlineStr">
+      <c r="K118" s="16" t="inlineStr">
         <is>
           <t>해지 만류 화법 — 사과 → 원인 규명 → 리밸런싱 3단 + 고객에게 할 대사 ↔ 절차 카드 한 장으로 「준비된 자료에 없어요」(gap 35 재현)</t>
         </is>
       </c>
-      <c r="K118" s="16" t="inlineStr"/>
-    </row>
-    <row r="119" ht="135" customHeight="1">
+      <c r="L118" s="16" t="inlineStr"/>
+    </row>
+    <row r="119" ht="324" customHeight="1">
       <c r="C119" s="13" t="n">
         <v>115</v>
       </c>
@@ -5397,22 +5616,23 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="H119" s="21" t="inlineStr">
+      <c r="H119" s="16" t="inlineStr"/>
+      <c r="I119" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I119" s="16" t="inlineStr">
+      <c r="J119" s="16" t="inlineStr">
         <is>
           <t>이수민 175926-3048171·송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J119" s="16" t="inlineStr">
+      <c r="K119" s="16" t="inlineStr">
         <is>
           <t>예금 편중 대비 운용 화법 + 이 고객 값 ↔ 무엇을 두겠다는 건지 몰라 일반론으로 답한다</t>
         </is>
       </c>
-      <c r="K119" s="16" t="inlineStr"/>
+      <c r="L119" s="16" t="inlineStr"/>
     </row>
     <row r="120" hidden="1">
       <c r="C120" s="13" t="n">
@@ -5437,24 +5657,25 @@
 "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."</t>
         </is>
       </c>
-      <c r="H120" s="21" t="inlineStr">
+      <c r="H120" s="16" t="inlineStr"/>
+      <c r="I120" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I120" s="16" t="inlineStr">
+      <c r="J120" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J120" s="16" t="inlineStr">
+      <c r="K120" s="16" t="inlineStr">
         <is>
           <t>중도인출 사유 + 세금으로 혜택이 상쇄된다는 것까지 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
-      <c r="K120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121" ht="135" customHeight="1">
+      <c r="L120" s="16" t="inlineStr"/>
+    </row>
+    <row r="121" ht="324" customHeight="1">
       <c r="C121" s="13" t="n">
         <v>117</v>
       </c>
@@ -5480,24 +5701,25 @@
 대화 중 "IRP 수수료는 적립금 규모와 가입 방식에 따라 다릅니다. 우리 고객님 조건에서는 오히려 국민은행이 더 저렴한 경우가 많습니다. 실제로 고객님 상황과 적립금 기준으로 한번 같이 비교해드릴게요."라는 멘트를 활용해 고객의 상황을 구체적으로 비교해 보면서 대응을 이어가세요.</t>
         </is>
       </c>
-      <c r="H121" s="19" t="inlineStr">
+      <c r="H121" s="16" t="inlineStr"/>
+      <c r="I121" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K121" s="16" t="inlineStr">
+        <is>
           <t>고객에게 할 말 + 접근 이유 ↔ 제도 설명만 나오고 할 말이 없다</t>
         </is>
       </c>
-      <c r="K121" s="16" t="inlineStr"/>
-    </row>
-    <row r="122" ht="94.5" customHeight="1">
+      <c r="L121" s="16" t="inlineStr"/>
+    </row>
+    <row r="122" ht="121.5" customHeight="1">
       <c r="C122" s="13" t="n">
         <v>118</v>
       </c>
@@ -5519,22 +5741,23 @@
 이용하려는 자금이 연금지급 대기나 교체매매 중에 있는 등 사용계획이 있는 자금이라면 먼저 걸러내야 하고, 고객에게 생소한 용어인 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H122" s="16" t="inlineStr">
+      <c r="H122" s="16" t="inlineStr"/>
+      <c r="I122" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본</t>
         </is>
       </c>
-      <c r="I122" s="16" t="inlineStr">
+      <c r="J122" s="16" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J122" s="16" t="inlineStr">
+      <c r="K122" s="16" t="inlineStr">
         <is>
           <t>그 반론에 맞는 화법 ↔ 주제어만 겹치는 카드로 답한다</t>
         </is>
       </c>
-      <c r="K122" s="16" t="inlineStr"/>
+      <c r="L122" s="16" t="inlineStr"/>
     </row>
     <row r="123" hidden="1">
       <c r="C123" s="13" t="n">
@@ -5558,22 +5781,23 @@
 고객에게는 "고객님, 금액이 작아 보이셔도 현재 미운용 중인 현금성자산의 적용금리는 2.42% 수준이라서요. 금리가 높은 저축은행 정기예금이나 펀드 같은 상품으로 운용하시면 향후에 수령하시는 퇴직연금 금액이 달라지니 지금 재정비하시는 게 좋아요"라고 안내해 드릴 수 있어요.</t>
         </is>
       </c>
-      <c r="H123" s="16" t="inlineStr">
+      <c r="H123" s="16" t="inlineStr"/>
+      <c r="I123" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I123" s="16" t="inlineStr">
+      <c r="J123" s="16" t="inlineStr">
         <is>
           <t>김현수 173544-2074623</t>
         </is>
       </c>
-      <c r="J123" s="16" t="inlineStr">
+      <c r="K123" s="16" t="inlineStr">
         <is>
           <t>그 반론 화법 + 이 고객 값 ↔ 일반론만 나온다</t>
         </is>
       </c>
-      <c r="K123" s="16" t="inlineStr"/>
+      <c r="L123" s="16" t="inlineStr"/>
     </row>
     <row r="124" hidden="1">
       <c r="C124" s="13" t="n">
@@ -5600,22 +5824,23 @@
 성과저조·판매중단 펀드 보유 고객이 손실 상황에서 불만을 제기할 때는 감정 공감을 먼저 건네며 접근하는 것이 핵심이에요. "속상하시겠지만"이라는 감정 인정을 반드시 앞세우고, 판매중단 사유와 그 결과로 운용사 관심도가 하락해 향후 수익률 개선이 어려울 수 있다는 점을 설명한 뒤 교체를 권해야 해요. 다만 갈아탄 상품이 더 좋을 것이라고 수익을 확정적으로 약속해서는 안 되고, 수익률 예측이 아니라 운용 여건의 차이를 근거로 다가가야 해요. 고객에게는 "많이 속상하시겠지만, 고객님 안정적인 퇴직연금 자산관리를 위해 최근 수익률 등을 비교해 보시고 상대적으로 성과가 우수한 상품으로 변경해 보시는 건 어떠신가요?"라고 안내해 보세요. 상담 과정에서 사용계획이 있는 자금이라면 먼저 걸러내야 하며, 고객에게 생소한 용어인 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해야 해요.</t>
         </is>
       </c>
-      <c r="H124" s="16" t="inlineStr">
+      <c r="H124" s="16" t="inlineStr"/>
+      <c r="I124" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I124" s="16" t="inlineStr">
+      <c r="J124" s="16" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 · 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J124" s="16" t="inlineStr">
+      <c r="K124" s="16" t="inlineStr">
         <is>
           <t>화법 + 「갈아탄 상품이 더 좋다고 약속 안 한다」 가드 ↔ 더 좋다고 약속한다</t>
         </is>
       </c>
-      <c r="K124" s="16" t="inlineStr"/>
+      <c r="L124" s="16" t="inlineStr"/>
     </row>
     <row r="125" hidden="1">
       <c r="C125" s="13" t="n">
@@ -5637,22 +5862,23 @@
           <t>증권사가 ETF 종류가 훨씬 많다는 고객에게는 고객의 반론을 먼저 인정하면서 10~20년 장기 운용을 해야 하는 연금자산에서는 상품의 개수보다 어떤 상품을 선택해서 운용하느냐가 더 중요하다는 점으로 설명을 이끌어가는 게 핵심이에요. 증권사는 8~900개의 다양한 테마형, 섹터형 ETF를 제공하고 있지만, 선택의 폭이 넓어지면 트렌드에 맞춰 관리해야 하고 그에 따른 피로도와 결정장애가 생기기 마련이라는 점을 짚어주세요. 퇴직연금은 중장기 안정적인 성과를 추구해야 하는 장기자산이므로, 국민은행은 이런 자산의 특성과 시장상황 등을 고려해 엄선한 ETF만을 선별 제공하고 있다는 점을 안내할 수 있어요. 현재 당행에서 판매 중인 ETF는 총 193종(국내 90종, 해외 103종)으로 계속 늘려가고 있으며, 고객님의 선택 폭을 넓히기 위해 중복테마 및 거래가 활발하지 않은 ETF를 제외하고 상품 라인업을 최대 400개까지 확대할 예정이라는 사실을 함께 활용해 보세요.</t>
         </is>
       </c>
-      <c r="H125" s="16" t="inlineStr">
+      <c r="H125" s="16" t="inlineStr"/>
+      <c r="I125" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I125" s="16" t="inlineStr">
+      <c r="J125" s="16" t="inlineStr">
         <is>
           <t>윤가영 162754-9483106</t>
         </is>
       </c>
-      <c r="J125" s="16" t="inlineStr">
+      <c r="K125" s="16" t="inlineStr">
         <is>
           <t>이탈 반론 화법 + 우리 채널에서 되는 것 ↔ 일반론으로 답한다</t>
         </is>
       </c>
-      <c r="K125" s="16" t="inlineStr"/>
+      <c r="L125" s="16" t="inlineStr"/>
     </row>
     <row r="126" hidden="1">
       <c r="C126" s="13" t="n">
@@ -5682,22 +5908,23 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="H126" s="16" t="inlineStr">
+      <c r="H126" s="16" t="inlineStr"/>
+      <c r="I126" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I126" s="16" t="inlineStr">
+      <c r="J126" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J126" s="16" t="inlineStr">
+      <c r="K126" s="16" t="inlineStr">
         <is>
           <t>할 말 + 접근 이유 ↔ 「받게 된다」로 수익을 약속한다</t>
         </is>
       </c>
-      <c r="K126" s="16" t="inlineStr"/>
+      <c r="L126" s="16" t="inlineStr"/>
     </row>
     <row r="127" hidden="1">
       <c r="C127" s="13" t="n">
@@ -5719,22 +5946,23 @@
           <t>원금 손실을 우려하는 고객에게는 연금 자산의 투자 성격과 기간을 들어 위험의 의미를 다시 정의하며 접근하는 것이 핵심이에요. 먼저 주식이 위험하다는 고객의 의견을 수용하면서, 여기서 말하는 위험이 손실이 아니라 기간이 길어질수록 줄어드는 변동성임을 짚어주세요. 당장 1~2년 뒤에 쓸 돈이 아니라 은퇴 후 30년을 운용해야 할 자산이라는 점을 설명하고, 연금이야말로 기간이 길어 30년이면 손실 확률이 0%에 수렴하는 특성을 지닌다는 점을 안내할 수 있어요. 또한 '위험'이라는 단어가 주는 부담감을 줄이기 위해 30년이라는 장기 투자 기간과 소규모 납입금의 특성을 들어 오히려 연금투자가 변동성을 감당할 수 있는 자금 성격임을 설명하는 방식을 활용해 보세요. 다만 사용 계획이 있는 자금이나 연금지급 대기 및 교체매매 중인 자금은 먼저 걸러내야 하며, 고객에게 생소할 수 있는 '고유계정대' 대신 '현금성자산'이나 '운용지시가 되지 않는 자산'이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H127" s="16" t="inlineStr">
+      <c r="H127" s="16" t="inlineStr"/>
+      <c r="I127" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I127" s="16" t="inlineStr">
+      <c r="J127" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="J127" s="16" t="inlineStr">
+      <c r="K127" s="16" t="inlineStr">
         <is>
           <t>「어디까지 안내할 수 있나」로 답한다(판단은 직원) ↔ 권유하라고 지시한다</t>
         </is>
       </c>
-      <c r="K127" s="16" t="inlineStr"/>
+      <c r="L127" s="16" t="inlineStr"/>
     </row>
     <row r="128" hidden="1">
       <c r="C128" s="13" t="n">
@@ -5756,22 +5984,23 @@
           <t>고객이 망설일 때는 즉답을 압박하지 않고 생각할 시간의 정당성을 먼저 인정해 주는 방식으로 접근해야 해요. 당장 결정을 재촉하기보다 고객이 스스로 상품 정보를 찾아볼 수 있도록 안내하는 것이 좋아요. "아무래도 많이 운용해보신 상품이 아니라 생각하실 시간이 필요하실 거에요. 궁금한 점 있으시면 언제든지 연락 주시고, 인터넷뱅킹 또는 스타뱅킹을 통해서도 관련상품에 대한 정보를 찾아보실 수 있으니 참고해주세요"라고 안내해 드려 보세요.</t>
         </is>
       </c>
-      <c r="H128" s="17" t="inlineStr">
+      <c r="H128" s="16" t="inlineStr"/>
+      <c r="I128" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I128" s="16" t="inlineStr">
+      <c r="J128" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J128" s="16" t="inlineStr">
+      <c r="K128" s="16" t="inlineStr">
         <is>
           <t>시간의 정당성 인정 + 자가확인 경로 ↔ 재촉하거나 그냥 끝낸다</t>
         </is>
       </c>
-      <c r="K128" s="16" t="inlineStr"/>
+      <c r="L128" s="16" t="inlineStr"/>
     </row>
     <row r="129" hidden="1">
       <c r="C129" s="13" t="n">
@@ -5794,22 +6023,23 @@
 상담 과정에서 고객이 적금을 따로 가입하겠다고 말씀하신다면 "IRP는 매달 무조건 일정 금액을 입금해야하는 상품이 아닙니다. 여유가 있는 달에 넣고, 부담되는 달에는 쉬어가면서 원할때만 입금하시면 됩니다."라고 안내해 보세요. 이어지는 대응으로는 "적금은 만기이자에 이자소득세가 차감되는 반면, IRP는 예금, 펀드 등 운용수익에 대해 세금을 하나도 차감하지 않아요. 또 연말정산, 종합소득세 신고때 세액공제까지 된답니다."라는 내용을 활용하실 수 있어요.</t>
         </is>
       </c>
-      <c r="H129" s="17" t="inlineStr">
+      <c r="H129" s="16" t="inlineStr"/>
+      <c r="I129" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I129" s="16" t="inlineStr">
+      <c r="J129" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J129" s="16" t="inlineStr">
+      <c r="K129" s="16" t="inlineStr">
         <is>
           <t>자유납입으로 부담 제거 ↔ 한도를 채우라고 밀어붙인다</t>
         </is>
       </c>
-      <c r="K129" s="16" t="inlineStr"/>
+      <c r="L129" s="16" t="inlineStr"/>
     </row>
     <row r="130" hidden="1">
       <c r="C130" s="13" t="n">
@@ -5831,22 +6061,23 @@
           <t>IRP 가입 시 중도인출에 대한 우려를 표하는 고객에게는 법적 요건을 충족하면 언제든 인출이 가능하다는 점을 설명하고, 자산을 균형 있게 나누어 운용하는 방식을 안내하는 것이 좋아요. IRP는 노후 대비를 위한 계좌이지만 무주택자의 주택 구입이나 전세금 및 임차보증금 마련 등 법정 사유가 있을 때 중도인출이 가능하므로, 고객이 가진 자금 유동성에 대한 불안을 먼저 덜어줄 수 있어요. 또한 고객의 전체 자산을 전부 IRP에 넣으라는 것이 아니라는 점을 짚어 주면서, "그래서 고객님 돈 대부분을 IRP에 넣으라고 말씀드리지 않아요. 우리가 한가지 음식만 먹으면 영양이 부족하듯, 고객님의 자산도 골고루 나눠야 안정성과, 수익성, 절세효과까지 균형있게 챙기실 수 있어요. 해지에 대한 우려로 이 엄청난 혜택을 시작조차 안하시는 건 너무 아쉽습니다."라고 말씀해 보세요. IRP의 절세 혜택과 안정성을 함께 챙길 수 있도록 유도하는 화법이에요.</t>
         </is>
       </c>
-      <c r="H130" s="19" t="inlineStr">
+      <c r="H130" s="16" t="inlineStr"/>
+      <c r="I130" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="J130" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J130" s="16" t="inlineStr">
+      <c r="K130" s="16" t="inlineStr">
         <is>
           <t>법정 사유 + 균형 비유 ↔ 「뺄 수 있다」만 답하고 조건을 뗀다</t>
         </is>
       </c>
-      <c r="K130" s="16" t="inlineStr"/>
+      <c r="L130" s="16" t="inlineStr"/>
     </row>
     <row r="131" hidden="1">
       <c r="C131" s="13" t="n">
@@ -5870,22 +6101,23 @@
 「그 부분은 전혀 걱정하지 않으셔도 됩니다. 기존 상품이 만기가 도래해도 알아서 상품이 매수되는 디폴트옵션 설정도 도와드릴게요. 한번 설정해놓으시면 기존 연금보험처럼 신경 쓰실 필요 없이 알아서 운용될 거에요.」</t>
         </is>
       </c>
-      <c r="H131" s="19" t="inlineStr">
+      <c r="H131" s="16" t="inlineStr"/>
+      <c r="I131" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I131" s="16" t="inlineStr">
+      <c r="J131" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J131" s="16" t="inlineStr">
+      <c r="K131" s="16" t="inlineStr">
         <is>
           <t>「가입보다 관리」로 논점 이동 ↔ 제도 설명만 하고 할 말이 없다</t>
         </is>
       </c>
-      <c r="K131" s="16" t="inlineStr"/>
+      <c r="L131" s="16" t="inlineStr"/>
     </row>
     <row r="132" hidden="1">
       <c r="C132" s="13" t="n">
@@ -5911,22 +6143,23 @@
 직접 운용이 어려운 고객에게는 디폴트옵션이나 TDF 외의 제3 선택지로 AI투자일임 서비스를 안내해 드릴 수 있어요. KB국민은행 개인형IRP 보유 고객은 제휴 투자일임사 3곳인 디셈버앤컴퍼니, 미래에셋자산운용, 한국투자신탁운용의 로보어드바이저에 운용을 맡길 수 있어요. 다만 이 서비스를 안내하실 때는 1인 1계좌 제한, 연금 수령을 시작한 고객·미성년자·외국인 제외, 전 운용사 합산 연 900만원의 투자 한도, 퇴직연금 수수료 외 별도 일임 보수 발생, 원금 비보장 등의 제약 사항을 함께 확인해 주셔야 해요. 아울러 운용 중에는 타기관 이전, 연금 지급, 중도인출, 해지가 제한되며 일임계약 해지 후에만 가능하다는 점과 투자성향이 안정형이면 진행이 어려울 수 있다는 점도 미리 짚어드릴 필요가 있어요.</t>
         </is>
       </c>
-      <c r="H132" s="17" t="inlineStr">
+      <c r="H132" s="16" t="inlineStr"/>
+      <c r="I132" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I132" s="16" t="inlineStr">
+      <c r="J132" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J132" s="16" t="inlineStr">
+      <c r="K132" s="16" t="inlineStr">
         <is>
           <t>자동화 3종(자동이체·자동매수·디폴트옵션) ↔ 디폴트옵션 하나만 말한다</t>
         </is>
       </c>
-      <c r="K132" s="16" t="inlineStr"/>
+      <c r="L132" s="16" t="inlineStr"/>
     </row>
     <row r="133" hidden="1">
       <c r="C133" s="13" t="n">
@@ -5951,22 +6184,23 @@
 다만 갈아탄 상품이 더 좋을 것이라고 수익률을 확정적으로 약속하거나 예측하는 표현은 쓰지 않도록 주의가 필요해요. 사용 계획이 있는 자금인 경우 사전에 걸러내야 한다는 점도 함께 염두에 두고 상담을 진행해 보세요. 그 외에 추가로 확인이 필요한 사항은 제가 가진 자료로는 확인이 어려워요.</t>
         </is>
       </c>
-      <c r="H133" s="19" t="inlineStr">
+      <c r="H133" s="16" t="inlineStr"/>
+      <c r="I133" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I133" s="16" t="inlineStr">
+      <c r="J133" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J133" s="16" t="inlineStr">
+      <c r="K133" s="16" t="inlineStr">
         <is>
           <t>공시 근거 + 장기 관리 약속 ↔ 근거 없이 우리가 낫다고 말한다</t>
         </is>
       </c>
-      <c r="K133" s="16" t="inlineStr"/>
+      <c r="L133" s="16" t="inlineStr"/>
     </row>
     <row r="134" ht="54" customHeight="1">
       <c r="C134" s="13" t="n">
@@ -5990,24 +6224,25 @@
 · 침묵을 유도하는 질문으로 열기 (IRP 수익률)</t>
         </is>
       </c>
-      <c r="H134" s="19" t="inlineStr">
+      <c r="H134" s="16" t="inlineStr"/>
+      <c r="I134" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I134" s="16" t="inlineStr">
+      <c r="J134" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J134" s="16" t="inlineStr">
+      <c r="K134" s="16" t="inlineStr">
         <is>
           <t>중립적 용건 오프너 ↔ 바로 상품 권유로 들어간다</t>
         </is>
       </c>
-      <c r="K134" s="16" t="inlineStr"/>
-    </row>
-    <row r="135" ht="135" customHeight="1">
+      <c r="L134" s="16" t="inlineStr"/>
+    </row>
+    <row r="135" ht="229.5" customHeight="1">
       <c r="A135" s="26" t="inlineStr">
         <is>
           <t>Ⅴ. 발송·화면 연계 — 문자·쪽지 문구를 만들고 발송 화면을 연다</t>
@@ -6039,24 +6274,25 @@
 퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까? 세미나는 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 온라인 세미나로, 고객의 성립 요건에 미운용 현금성자산과 디폴트옵션 미설정이 포함되어 있어 추천하며 발송 문구는 (광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX로 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr">
+      <c r="H135" s="10" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I135" s="10" t="inlineStr">
+      <c r="J135" s="10" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J135" s="10" t="inlineStr">
+      <c r="K135" s="10" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 **같은** 콘텐츠(다시 고르지 않는다) ↔ 화면과 다른 세미나를 말하거나 상품 자료로 가서 재료 0건</t>
         </is>
       </c>
-      <c r="K135" s="10" t="inlineStr"/>
-    </row>
-    <row r="136" ht="121.5" customHeight="1">
+      <c r="L135" s="10" t="inlineStr"/>
+    </row>
+    <row r="136" ht="135" customHeight="1">
       <c r="C136" s="13" t="n">
         <v>132</v>
       </c>
@@ -6080,22 +6316,23 @@
 무료수신거부 080-XXX-XXXX</t>
         </is>
       </c>
-      <c r="H136" s="17" t="inlineStr">
+      <c r="H136" s="16" t="inlineStr"/>
+      <c r="I136" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="J136" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J136" s="16" t="inlineStr">
+      <c r="K136" s="16" t="inlineStr">
         <is>
           <t>고객 상태와 콘텐츠의 연결 근거 ↔ 선정을 다시 해서 화면과 다른 답을 낸다</t>
         </is>
       </c>
-      <c r="K136" s="16" t="inlineStr">
+      <c r="L136" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
@@ -6125,28 +6362,29 @@
 무료수신거부 080-XXX-XXXX"</t>
         </is>
       </c>
-      <c r="H137" s="21" t="inlineStr">
+      <c r="H137" s="16" t="inlineStr"/>
+      <c r="I137" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I137" s="16" t="inlineStr">
+      <c r="J137" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J137" s="16" t="inlineStr">
+      <c r="K137" s="16" t="inlineStr">
         <is>
           <t>발송 화면 + 넣을 문구(보낼지는 직원이) ↔ 에이전트가 발송까지 하거나 승낙 없이 건넨다</t>
         </is>
       </c>
-      <c r="K137" s="16" t="inlineStr">
+      <c r="L137" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="135" customHeight="1">
+    <row r="138" ht="189" customHeight="1">
       <c r="C138" s="13" t="n">
         <v>134</v>
       </c>
@@ -6168,28 +6406,29 @@
 온라인 세미나 안내 문구는 "(광고) 송도윤 고객님, KB국민은행입니다. 11/5(목) 16시에 KB국민은행 연금사업부가 주관하는 '퇴직연금 디폴트옵션, 내 계좌도 점검이 필요할까?' 온라인 세미나가 진행됩니다. 현재 고객님의 계좌 상태를 점검하고 미운용 자금 관리 방법을 확인하실 수 있도록 추천해 드립니다. ▶ https://obank.kbstar.com/demo/seminar/irp-002 무료수신거부 080-XXX-XXXX"로 안내해 주시면 돼요. 문구에 포함된 링크는 각각 https://obank.kbstar.com/demo/event/irp-004와 https://obank.kbstar.com/demo/seminar/irp-002를 그대로 적어 주시면 돼요.</t>
         </is>
       </c>
-      <c r="H138" s="19" t="inlineStr">
+      <c r="H138" s="16" t="inlineStr"/>
+      <c r="I138" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I138" s="16" t="inlineStr">
+      <c r="J138" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J138" s="16" t="inlineStr">
+      <c r="K138" s="16" t="inlineStr">
         <is>
           <t>브리핑이 만든 문구를 옮기거나 다듬는다 ↔ 일정·링크가 잘려 규칙 폴백 문구가 뜬다</t>
         </is>
       </c>
-      <c r="K138" s="16" t="inlineStr">
+      <c r="L138" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="135" customHeight="1">
+    <row r="139" ht="202.5" customHeight="1">
       <c r="C139" s="13" t="n">
         <v>135</v>
       </c>
@@ -6219,22 +6458,23 @@
 고객에게 안내할 때는 사용계획이 있는 자금인지 먼저 확인하고 활용할 수 있는 방법을 살펴보세요. 세부적인 발송 문구나 링크가 필요한 항목이 있다면 이어서 말씀해 드릴게요.</t>
         </is>
       </c>
-      <c r="H139" s="19" t="inlineStr">
+      <c r="H139" s="16" t="inlineStr"/>
+      <c r="I139" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I139" s="16" t="inlineStr">
+      <c r="J139" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 걸린 고객 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J139" s="16" t="inlineStr">
+      <c r="K139" s="16" t="inlineStr">
         <is>
           <t>열려 있는 나머지 ↔ 지어낸 세미나를 만든다</t>
         </is>
       </c>
-      <c r="K139" s="16" t="inlineStr">
+      <c r="L139" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
@@ -6260,24 +6500,25 @@
           <t>현재 이 고객의 요건에 맞는 세미나는 아직 준비된 자료가 없어요. 다만 열려 있는 콘텐츠 중 날짜가 가까운 세미나로는 내 투자성향에 맞는 퇴직연금 포트폴리오 찾기 세미나가 11/12(목) 17시에 KB국민은행 WM투자부 주관으로 예정되어 있어요. 이 세미나는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋은 내용이에요. 안내할 때 참고할 수 있는 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요.</t>
         </is>
       </c>
-      <c r="H140" s="19" t="inlineStr">
+      <c r="H140" s="16" t="inlineStr"/>
+      <c r="I140" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="J140" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 없는 고객 — 예: 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="J140" s="16" t="inlineStr">
+      <c r="K140" s="16" t="inlineStr">
         <is>
           <t>「지금 걸린 콘텐츠가 없다」 ↔ 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="K140" s="16" t="inlineStr"/>
-    </row>
-    <row r="141" ht="135" customHeight="1">
+      <c r="L140" s="16" t="inlineStr"/>
+    </row>
+    <row r="141" ht="148.5" customHeight="1">
       <c r="B141" s="20" t="inlineStr">
         <is>
           <t>19. 이번 상담 요약·쪽지</t>
@@ -6307,22 +6548,23 @@
 (아래에 이 고객의 연령·투자성향·평가금액·수익률·연금개시·세액공제 잔여한도·관리 사유 표가 붙습니다)</t>
         </is>
       </c>
-      <c r="H141" s="21" t="inlineStr">
+      <c r="H141" s="16" t="inlineStr"/>
+      <c r="I141" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I141" s="16" t="inlineStr">
+      <c r="J141" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J141" s="16" t="inlineStr">
+      <c r="K141" s="16" t="inlineStr">
         <is>
           <t>요약 + 「이대로 보낼까요?」 ↔ 확인 없이 보낸다 · 신뢰등급 표시가 쪽지에 안 붙는다(**미해결**)</t>
         </is>
       </c>
-      <c r="K141" s="16" t="inlineStr">
+      <c r="L141" s="16" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -6348,28 +6590,29 @@
           <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
         </is>
       </c>
-      <c r="H142" s="21" t="inlineStr">
+      <c r="H142" s="16" t="inlineStr"/>
+      <c r="I142" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 시연본</t>
         </is>
       </c>
-      <c r="I142" s="16" t="inlineStr">
+      <c r="J142" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J142" s="16" t="inlineStr">
+      <c r="K142" s="16" t="inlineStr">
         <is>
           <t>직원 본인 쪽지함으로, 미연결이면 「미연결」 ↔ 미연결인데 「보냈다」고 접는다</t>
         </is>
       </c>
-      <c r="K142" s="16" t="inlineStr">
+      <c r="L142" s="16" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="67.5" customHeight="1">
+    <row r="143" ht="81" customHeight="1">
       <c r="C143" s="13" t="n">
         <v>139</v>
       </c>
@@ -6389,22 +6632,23 @@
           <t>- 직원 — 이 고객 왜 관리 대상으로 떴어? — 에이전트 — 송도윤 고객이 관리 대상으로 선정된 사유는 장기 미접촉, 판매중단·환매추천 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 확인되었기 때문이에요. 세부적으로는 최근 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있고, 수익률이 저조한 판매중단 상품인 KB 퇴직연금 배당 (주식)을 보유하고 있어요. 또한 고유계정대인 현금성자산이 방치되어 있으며 디폴트옵션도 설정되지 않았고, 만기가 경과한 ISA 만기자금 1억 2,000만원이 있으며 12개월 이상 운용변경 이력이 없는 상태예요.</t>
         </is>
       </c>
-      <c r="H143" s="19" t="inlineStr">
+      <c r="H143" s="16" t="inlineStr"/>
+      <c r="I143" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I143" s="16" t="inlineStr">
+      <c r="J143" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J143" s="16" t="inlineStr">
+      <c r="K143" s="16" t="inlineStr">
         <is>
           <t>이번 세션 대화만 ↔ 지난 상담을 요약하거나 「기록 없음」으로 끝난다</t>
         </is>
       </c>
-      <c r="K143" s="16" t="inlineStr">
+      <c r="L143" s="16" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -6430,22 +6674,23 @@
           <t>이번 상담에서 아직 오간 대화가 없습니다.</t>
         </is>
       </c>
-      <c r="H144" s="19" t="inlineStr">
+      <c r="H144" s="16" t="inlineStr"/>
+      <c r="I144" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I144" s="16" t="inlineStr">
+      <c r="J144" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J144" s="16" t="inlineStr">
+      <c r="K144" s="16" t="inlineStr">
         <is>
           <t>「아직 오간 대화가 없다」 ↔ 지난 상담을 요약해 놓고 「이번 상담」이라 말한다</t>
         </is>
       </c>
-      <c r="K144" s="16" t="inlineStr"/>
+      <c r="L144" s="16" t="inlineStr"/>
     </row>
     <row r="145" hidden="1">
       <c r="C145" s="13" t="n">
@@ -6467,22 +6712,23 @@
           <t>쪽지를 보내지 못했어요. WorkB 클라이언트가 주입되지 않았습니다 — 본문만 생성했습니다</t>
         </is>
       </c>
-      <c r="H145" s="17" t="inlineStr">
+      <c r="H145" s="16" t="inlineStr"/>
+      <c r="I145" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I145" s="16" t="inlineStr">
+      <c r="J145" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J145" s="16" t="inlineStr">
+      <c r="K145" s="16" t="inlineStr">
         <is>
           <t>받는 사람이 본인이 아니라 그 사번으로 바뀌고 화면에 밝힌다 ↔ 사번을 금액으로 읽어 본인에게 보낸다 · 사번을 못 읽었는데 「보냈다」고 답한다</t>
         </is>
       </c>
-      <c r="K145" s="16" t="inlineStr">
+      <c r="L145" s="16" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어? → 대화 내용 요약해서 쪽지로 보내줘</t>
         </is>
@@ -6496,7 +6742,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>20. 복합·연쇄 턴</t>
+          <t>20. 복합 질문·앞 말 이어받기</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
@@ -6521,22 +6767,23 @@
 아울러 당행 구체적인 수수료율이나 우리 수수료가 얼마인지에 대한 상세한 수치는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="H146" s="11" t="inlineStr">
+      <c r="H146" s="10" t="inlineStr"/>
+      <c r="I146" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 대본</t>
         </is>
       </c>
-      <c r="I146" s="10" t="inlineStr">
+      <c r="J146" s="10" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J146" s="10" t="inlineStr">
+      <c r="K146" s="10" t="inlineStr">
         <is>
           <t>값 + 고객 재료 + 화법이 한 답에 ↔ 도구 하나로 끝내고 질문의 절반만 답한다</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr"/>
+      <c r="L146" s="10" t="inlineStr"/>
     </row>
     <row r="147" ht="27" customHeight="1">
       <c r="C147" s="13" t="n">
@@ -6558,28 +6805,29 @@
           <t>송도윤 고객님의 ISA 만기자금(IRP 외부) 만기일은 2026년 9월 20일이에요. 현재 만기 경과 9일인 상태예요.</t>
         </is>
       </c>
-      <c r="H147" s="21" t="inlineStr">
+      <c r="H147" s="16" t="inlineStr"/>
+      <c r="I147" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I147" s="16" t="inlineStr">
+      <c r="J147" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J147" s="16" t="inlineStr">
+      <c r="K147" s="16" t="inlineStr">
         <is>
           <t>제안이 무효가 되고 새 질문으로 ↔ 새 질문을 승낙으로 읽는다</t>
         </is>
       </c>
-      <c r="K147" s="16" t="inlineStr">
+      <c r="L147" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="135" customHeight="1">
+    <row r="148" ht="310.5" customHeight="1">
       <c r="C148" s="13" t="n">
         <v>144</v>
       </c>
@@ -6607,24 +6855,25 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="H148" s="16" t="inlineStr">
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I148" s="16" t="inlineStr">
+      <c r="J148" s="16" t="inlineStr">
         <is>
           <t>정민석 181245-3097614·박정호 168450-7293815</t>
         </is>
       </c>
-      <c r="J148" s="16" t="inlineStr">
+      <c r="K148" s="16" t="inlineStr">
         <is>
           <t>고객 재료(불일치·펀드 경험) + 그에 맞는 화법 ↔ 재료를 무시하고 일반 화법만</t>
         </is>
       </c>
-      <c r="K148" s="16" t="inlineStr"/>
-    </row>
-    <row r="149" ht="94.5" customHeight="1">
+      <c r="L148" s="16" t="inlineStr"/>
+    </row>
+    <row r="149" ht="108" customHeight="1">
       <c r="C149" s="13" t="n">
         <v>145</v>
       </c>
@@ -6644,24 +6893,25 @@
           <t>이수민 고객의 세액공제 환급 예상액을 안내할 때는 개인형IRP 계좌의 추가 납입을 기준으로 짚어주는 게 핵심이에요. 당해 납입액이 0원이고 세액공제 한도와 잔여한도는 연금저축 납입분을 합산해 900만원으로 확인돼요. 질문에 금액이 없어 잔여한도인 900만원을 추가 납입하는 상황으로 계산하면, 공제 대상은 0원에서 900만원으로 늘어나요. 총급여 5,500만원 이하(16.5% 공제율)인 경우 환급 예상액은 1,485,000원이 늘어나요. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요 없이 바로 활용하시면 돼요. "개인형IRP 계좌에 900만원을 추가 납입하시면, 총급여 5,500만원 이하 기준 세액공제 환급 예상액이 1,485,000원 늘어나요"라고 안내해 보세요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H149" s="16" t="inlineStr">
+      <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I149" s="16" t="inlineStr">
+      <c r="J149" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J149" s="16" t="inlineStr">
+      <c r="K149" s="16" t="inlineStr">
         <is>
           <t>납입액 + 잔여한도 + 환급 계산 ↔ 한쪽만 답한다</t>
         </is>
       </c>
-      <c r="K149" s="16" t="inlineStr"/>
-    </row>
-    <row r="150" ht="135" customHeight="1">
+      <c r="L149" s="16" t="inlineStr"/>
+    </row>
+    <row r="150" ht="175.5" customHeight="1">
       <c r="C150" s="13" t="n">
         <v>146</v>
       </c>
@@ -6685,22 +6935,23 @@
 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 만기 전 운용 방향을 확정해야 해요. 만기 임박 + 디폴트옵션 미등록 고객에게는 "정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기 자금이 현금성자산으로 상환되니 디폴트옵션 사전지정 등록이나 만기 예약을 하시는 것이 좋아요"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="H150" s="16" t="inlineStr">
+      <c r="H150" s="16" t="inlineStr"/>
+      <c r="I150" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I150" s="16" t="inlineStr">
+      <c r="J150" s="16" t="inlineStr">
         <is>
           <t>오세훈 193482-6012375 · 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J150" s="16" t="inlineStr">
+      <c r="K150" s="16" t="inlineStr">
         <is>
           <t>이전 턴 대상을 이어받는다 ↔ 무엇을 두는지 몰라 되묻거나 일반론</t>
         </is>
       </c>
-      <c r="K150" s="16" t="inlineStr">
+      <c r="L150" s="16" t="inlineStr">
         <is>
           <t>이 고객 만기 언제고 금액은 얼마야?</t>
         </is>
@@ -6726,22 +6977,23 @@
           <t>앞서 안내드린 내용 중 첫 번째 상품인 KB 글로벌채권인덱스 C-P에 대해 더 자세히 설명해 드릴게요. 해당 상품은 보통위험 등급의 채권형 상품이며 최근 1년 기준 4.8%의 수익률을 보여요. 위험중립형 고객의 적합성 허용 상한인 보통위험 등급에 부합하여 안내할 수 있어요.</t>
         </is>
       </c>
-      <c r="H151" s="19" t="inlineStr">
+      <c r="H151" s="16" t="inlineStr"/>
+      <c r="I151" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I151" s="16" t="inlineStr">
+      <c r="J151" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J151" s="16" t="inlineStr">
+      <c r="K151" s="16" t="inlineStr">
         <is>
           <t>맥락으로 무엇인지 정한 뒤 판정 ↔ 제대로 찾은 카드까지 전멸하고 「근거를 못 찾았다」</t>
         </is>
       </c>
-      <c r="K151" s="16" t="inlineStr">
+      <c r="L151" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
@@ -6771,22 +7023,23 @@
 · 출처 퇴직연금 주요거래 화면번호 안내 (KB StarLearn 직원교육)</t>
         </is>
       </c>
-      <c r="H152" s="16" t="inlineStr">
+      <c r="H152" s="16" t="inlineStr"/>
+      <c r="I152" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 라이브러리</t>
         </is>
       </c>
-      <c r="I152" s="16" t="inlineStr">
+      <c r="J152" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J152" s="16" t="inlineStr">
+      <c r="K152" s="16" t="inlineStr">
         <is>
           <t>원래 질문 + 고른 갈래를 합쳐 답한다 ↔ 승낙으로 읽어 「제안드린 작업이 없어요」</t>
         </is>
       </c>
-      <c r="K152" s="16" t="inlineStr">
+      <c r="L152" s="16" t="inlineStr">
         <is>
           <t>실물이전 어떻게 처리해?</t>
         </is>
@@ -6814,22 +7067,23 @@
 · 전입</t>
         </is>
       </c>
-      <c r="H153" s="19" t="inlineStr">
+      <c r="H153" s="16" t="inlineStr"/>
+      <c r="I153" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I153" s="16" t="inlineStr">
+      <c r="J153" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J153" s="16" t="inlineStr">
+      <c r="K153" s="16" t="inlineStr">
         <is>
           <t>전제를 밝히고 답한다(연속 되묻기 금지) ↔ 또 되묻는다</t>
         </is>
       </c>
-      <c r="K153" s="16" t="inlineStr">
+      <c r="L153" s="16" t="inlineStr">
         <is>
           <t>실물이전 어떻게 처리해?</t>
         </is>
@@ -6855,28 +7109,29 @@
           <t>고객이 퇴직연금 ETF 상품을 직접 찾아보실 수 있도록 안내해 드릴 때는 채널별 메뉴 경로를 확인해 드릴게요. KB스타뱅킹을 이용하신다면 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 ETF, 나의 ETF · ETF 상품 조회 순으로 이동하시면 되어요. 인터넷뱅킹을 이용하실 경우에는 KB퇴직연금, 개인고객, 퇴직연금 ETF, 나의 ETF · ETF 상품조회 메뉴를 통해 조회하실 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다.</t>
         </is>
       </c>
-      <c r="H154" s="17" t="inlineStr">
+      <c r="H154" s="16" t="inlineStr"/>
+      <c r="I154" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J154" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K154" s="16" t="inlineStr">
+        <is>
           <t>고른 갈래의 채널 경로만 ↔ 세 갈래를 다 쏟거나 되묻기를 또 한다</t>
         </is>
       </c>
-      <c r="K154" s="16" t="inlineStr">
+      <c r="L154" s="16" t="inlineStr">
         <is>
           <t>고객이 앱에서 운용상품을 직접 찾아볼 수 있어?</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="108" customHeight="1">
+    <row r="155" ht="121.5" customHeight="1">
       <c r="C155" s="13" t="n">
         <v>151</v>
       </c>
@@ -6897,22 +7152,23 @@
 고객에게는 "안녕하세요, KB국민은행 000지점 000입니다. 저희 국민은행에 가입하신 퇴직연금 관련해서 안내드릴 사항이 있어 전화드렸습니다! 잠시 통화 가능하세요?"라고 먼저 건네주시고, 이어지는 턴에서 "고객님의 퇴직연금 전담직원으로 안내 인사드리고 정기적인 상품관리를 해 드리고자 연락드렸습니다. 퇴직연금 상품을 운용하시면서 혹시 궁금하시거나 상담하고 싶으신 내용이 있으신지요?"라고 자연스럽게 대화를 이어가며 문의 사항을 여쭤보시면 돼요.</t>
         </is>
       </c>
-      <c r="H155" s="17" t="inlineStr">
+      <c r="H155" s="16" t="inlineStr"/>
+      <c r="I155" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I155" s="16" t="inlineStr">
+      <c r="J155" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J155" s="16" t="inlineStr">
+      <c r="K155" s="16" t="inlineStr">
         <is>
           <t>고른 오프너의 첫 마디 대사 ↔ 고르지 않은 쪽을 답하거나 일반론으로 돌아간다</t>
         </is>
       </c>
-      <c r="K155" s="16" t="inlineStr">
+      <c r="L155" s="16" t="inlineStr">
         <is>
           <t>상담 문을 어떻게 열어야 할지 모르겠는데 첫 마디 좀 알려줘</t>
         </is>
@@ -6938,34 +7194,35 @@
           <t>«잠자는 IRP 자금 깨우기 운용 이벤트» 안내 문구로 75-08-110 발송 화면 열기를 취소했어요.</t>
         </is>
       </c>
-      <c r="H156" s="19" t="inlineStr">
+      <c r="H156" s="16" t="inlineStr"/>
+      <c r="I156" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I156" s="16" t="inlineStr">
+      <c r="J156" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J156" s="16" t="inlineStr">
+      <c r="K156" s="16" t="inlineStr">
         <is>
           <t>제안을 취소한다 ↔ 그래도 화면을 열거나 문구를 건넨다</t>
         </is>
       </c>
-      <c r="K156" s="16" t="inlineStr">
+      <c r="L156" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 안내할 만한 이벤트나 세미나 있어?</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="54" customHeight="1">
+    <row r="157" ht="67.5" customHeight="1">
       <c r="C157" s="13" t="n">
         <v>153</v>
       </c>
       <c r="D157" s="18" t="inlineStr">
         <is>
-          <t>(앞 턴에서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
+          <t>(앞서 3,000만원 언급) 말씀하신 3,000만원은 어떻게 돼?</t>
         </is>
       </c>
       <c r="E157" s="14" t="inlineStr"/>
@@ -6979,22 +7236,23 @@
           <t>앞서 안내드린 ISA 만기자금의 개인형IRP 전환 건은 전환금 3,000만원을 넣었을 때 추가 공제 대상 300만원이 적용되어 총급여 5,500만원 이하 기준 16.5%인 495,000원의 환급액을 늘릴 수 있는 것이 핵심이에요. ISA 만기일로부터 60일 이내인 2026년 9월 20일 기준 전환 기한이 51일 남았으니, 고객의 총급여 구간과 세액공제 전 결정세액이 공제액보다 적지 않은지 먼저 확인하고 안내해 보세요. 전환금은 연 납입한도 1,800만원과 무관하게 만기금액의 전부 또는 일부를 넣을 수 있어요.</t>
         </is>
       </c>
-      <c r="H157" s="19" t="inlineStr">
+      <c r="H157" s="16" t="inlineStr"/>
+      <c r="I157" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I157" s="16" t="inlineStr">
+      <c r="J157" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J157" s="16" t="inlineStr">
+      <c r="K157" s="16" t="inlineStr">
         <is>
           <t>앞 턴 수치를 되받아 적는다 ↔ 「수치 '3,000'」으로 폐기된다(gap 34). **이 수치로는 판정이 안 선다** — 3,000만원은 ISA 전환 상한이라 이번 턴 재료에도 있다</t>
         </is>
       </c>
-      <c r="K157" s="16" t="inlineStr">
+      <c r="L157" s="16" t="inlineStr">
         <is>
           <t>3,000만원 더 넣으면 얼마 돌려받아?</t>
         </is>
@@ -7020,22 +7278,23 @@
           <t>직전에 제안드린 작업이 없어요. 무엇을 도와드릴까요?</t>
         </is>
       </c>
-      <c r="H158" s="19" t="inlineStr">
+      <c r="H158" s="16" t="inlineStr"/>
+      <c r="I158" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K158" s="16" t="inlineStr">
+        <is>
           <t>「제안드린 작업이 없다」 ↔ 아무 화면이나 연다</t>
         </is>
       </c>
-      <c r="K158" s="16" t="inlineStr"/>
+      <c r="L158" s="16" t="inlineStr"/>
     </row>
     <row r="159" hidden="1">
       <c r="C159" s="13" t="n">
@@ -7053,22 +7312,23 @@
         </is>
       </c>
       <c r="G159" s="16" t="inlineStr"/>
-      <c r="H159" s="19" t="inlineStr">
+      <c r="H159" s="16" t="inlineStr"/>
+      <c r="I159" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I159" s="16" t="inlineStr">
+      <c r="J159" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J159" s="16" t="inlineStr">
+      <c r="K159" s="16" t="inlineStr">
         <is>
           <t>12턴 창 안이면 그 턴을 고른다 ↔ 엉뚱한 턴을 싣거나 없는 턴을 지어낸다</t>
         </is>
       </c>
-      <c r="K159" s="16" t="inlineStr">
+      <c r="L159" s="16" t="inlineStr">
         <is>
           <t>[12턴 맥락 창을 채워야 성립 — 손으로 돌린다]</t>
         </is>
@@ -7102,22 +7362,23 @@
 이때 갈아탄 상품이 더 좋을 것이라고 수익을 확정해 약속하지 않도록 주의하고, 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용하여 고객이 쉽게 이해할 수 있도록 설명해 주세요.</t>
         </is>
       </c>
-      <c r="H160" s="21" t="inlineStr">
+      <c r="H160" s="16" t="inlineStr"/>
+      <c r="I160" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I160" s="16" t="inlineStr">
+      <c r="J160" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J160" s="16" t="inlineStr">
+      <c r="K160" s="16" t="inlineStr">
         <is>
           <t>직전 답변을 재료로 다시 쓴다 ↔ 화법과 무관한 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="K160" s="16" t="inlineStr">
+      <c r="L160" s="16" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -7145,22 +7406,23 @@
 위 상품은 이 고객의 적합성 허용 상한인 보통위험 등급 이하의 상품 범위에 포함되며, 낮은위험 등급의 채권형 상품이에요. 지난 1년 수익률은 3.8%예요.</t>
         </is>
       </c>
-      <c r="H161" s="21" t="inlineStr">
+      <c r="H161" s="16" t="inlineStr"/>
+      <c r="I161" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I161" s="16" t="inlineStr">
+      <c r="J161" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J161" s="16" t="inlineStr">
+      <c r="K161" s="16" t="inlineStr">
         <is>
           <t>좁힌 부분만 + 그 턴 근거 카드를 되싣는다 ↔ 목록을 통째로 다시 세우거나 새로 검색한다</t>
         </is>
       </c>
-      <c r="K161" s="16" t="inlineStr">
+      <c r="L161" s="16" t="inlineStr">
         <is>
           <t>이 고객한테 뭘 추천해주면 좋을까?</t>
         </is>
@@ -7186,28 +7448,29 @@
           <t>앞서 안내드린 대사 중에서 고객에게 그대로 읽어드릴 수 있는 부분만 줄여서 안내해 드릴게요. "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 말씀해 보세요.</t>
         </is>
       </c>
-      <c r="H162" s="19" t="inlineStr">
+      <c r="H162" s="16" t="inlineStr"/>
+      <c r="I162" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I162" s="16" t="inlineStr">
+      <c r="J162" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J162" s="16" t="inlineStr">
+      <c r="K162" s="16" t="inlineStr">
         <is>
           <t>그 답변에 있던 대사만 ↔ 없던 대사를 지어내거나 되묻는다</t>
         </is>
       </c>
-      <c r="K162" s="16" t="inlineStr">
+      <c r="L162" s="16" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="135" customHeight="1">
+    <row r="163" ht="148.5" customHeight="1">
       <c r="C163" s="13" t="n">
         <v>159</v>
       </c>
@@ -7235,22 +7498,23 @@
 - 가입자부담금 비대면 1억원 이상 — 0.21%</t>
         </is>
       </c>
-      <c r="H163" s="19" t="inlineStr">
+      <c r="H163" s="16" t="inlineStr"/>
+      <c r="I163" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I163" s="16" t="inlineStr">
+      <c r="J163" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J163" s="16" t="inlineStr">
+      <c r="K163" s="16" t="inlineStr">
         <is>
           <t>그 턴 **하나만** 싣는다 ↔ 대화 전체가 인용 허용이 되어 옛 수치가 근거로 통과한다</t>
         </is>
       </c>
-      <c r="K163" s="16" t="inlineStr">
+      <c r="L163" s="16" t="inlineStr">
         <is>
           <t>수수료 얼마야? → 이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -7278,22 +7542,23 @@
 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 고객님들을 위해 매월 금리가 가장 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다."</t>
         </is>
       </c>
-      <c r="H164" s="19" t="inlineStr">
+      <c r="H164" s="16" t="inlineStr"/>
+      <c r="I164" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I164" s="16" t="inlineStr">
+      <c r="J164" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J164" s="16" t="inlineStr">
+      <c r="K164" s="16" t="inlineStr">
         <is>
           <t>그 재료의 도구를 함께 부른다 ↔ 없던 내용을 지어내 더한다</t>
         </is>
       </c>
-      <c r="K164" s="16" t="inlineStr">
+      <c r="L164" s="16" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -7319,24 +7584,25 @@
           <t>이번 상담에서 오간 대화 기록은 없습니다.</t>
         </is>
       </c>
-      <c r="H165" s="19" t="inlineStr">
+      <c r="H165" s="16" t="inlineStr"/>
+      <c r="I165" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I165" s="16" t="inlineStr">
+      <c r="J165" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J165" s="16" t="inlineStr">
+      <c r="K165" s="16" t="inlineStr">
         <is>
           <t>「다시 쓸 답이 없다」 ↔ 직전 답변이 없는데 도구를 골라 한 바퀴 버린다</t>
         </is>
       </c>
-      <c r="K165" s="16" t="inlineStr"/>
-    </row>
-    <row r="166" ht="135" customHeight="1">
+      <c r="L165" s="16" t="inlineStr"/>
+    </row>
+    <row r="166" ht="256.5" customHeight="1">
       <c r="B166" s="20" t="inlineStr">
         <is>
           <t>22. 에이전트 능력 안내</t>
@@ -7376,24 +7642,25 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="H166" s="17" t="inlineStr">
+      <c r="H166" s="16" t="inlineStr"/>
+      <c r="I166" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J166" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K166" s="16" t="inlineStr">
+        <is>
           <t>도울 수 있는 일을 스스로 답한다 ↔ 지식베이스를 검색해 엉뚱한 카드로 답한다</t>
         </is>
       </c>
-      <c r="K166" s="16" t="inlineStr"/>
-    </row>
-    <row r="167" ht="135" customHeight="1">
+      <c r="L166" s="16" t="inlineStr"/>
+    </row>
+    <row r="167" ht="283.5" customHeight="1">
       <c r="C167" s="13" t="n">
         <v>163</v>
       </c>
@@ -7430,24 +7697,25 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="H167" s="19" t="inlineStr">
+      <c r="H167" s="16" t="inlineStr"/>
+      <c r="I167" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I167" s="16" t="inlineStr">
+      <c r="J167" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J167" s="16" t="inlineStr">
+      <c r="K167" s="16" t="inlineStr">
         <is>
           <t>기억한다(맥락 12턴 + 지난 상담) ↔ 「기억하지 못해요」 — 사실이 아닌 문장</t>
         </is>
       </c>
-      <c r="K167" s="16" t="inlineStr"/>
-    </row>
-    <row r="168" ht="135" customHeight="1">
+      <c r="L167" s="16" t="inlineStr"/>
+    </row>
+    <row r="168" ht="283.5" customHeight="1">
       <c r="C168" s="13" t="n">
         <v>164</v>
       </c>
@@ -7484,22 +7752,23 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="H168" s="19" t="inlineStr">
+      <c r="H168" s="16" t="inlineStr"/>
+      <c r="I168" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I168" s="16" t="inlineStr">
+      <c r="J168" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J168" s="16" t="inlineStr">
+      <c r="K168" s="16" t="inlineStr">
         <is>
           <t>대외 행위는 안 한다, 화면을 열어주는 데까지 ↔ 보낼 수 있다고 답한다</t>
         </is>
       </c>
-      <c r="K168" s="16" t="inlineStr"/>
+      <c r="L168" s="16" t="inlineStr"/>
     </row>
     <row r="169" hidden="1">
       <c r="B169" s="20" t="inlineStr">
@@ -7526,22 +7795,23 @@
           <t>평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없습니다.</t>
         </is>
       </c>
-      <c r="H169" s="17" t="inlineStr">
+      <c r="H169" s="16" t="inlineStr"/>
+      <c r="I169" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I169" s="16" t="inlineStr">
+      <c r="J169" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J169" s="16" t="inlineStr">
+      <c r="K169" s="16" t="inlineStr">
         <is>
           <t>거절 + **왜 대화로 못 고치는지** ↔ 고쳤다고 답한다</t>
         </is>
       </c>
-      <c r="K169" s="16" t="inlineStr"/>
+      <c r="L169" s="16" t="inlineStr"/>
     </row>
     <row r="170" hidden="1">
       <c r="C170" s="13" t="n">
@@ -7563,22 +7833,23 @@
           <t>요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있지 않아 수정할 수 없습니다.</t>
         </is>
       </c>
-      <c r="H170" s="19" t="inlineStr">
+      <c r="H170" s="16" t="inlineStr"/>
+      <c r="I170" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I170" s="16" t="inlineStr">
+      <c r="J170" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J170" s="16" t="inlineStr">
+      <c r="K170" s="16" t="inlineStr">
         <is>
           <t>**시연 금지 — 재적용 루프 미구현.** 다만 이 문구로는 안 드러난다(화면에 그 표현이 없어 정당하게 거절된다) — 화면에 실제로 있는 낱말로 바꿔 물어야 「반영할게요」가 나오고 화면은 그대로다(correction.py 머리말)</t>
         </is>
       </c>
-      <c r="K170" s="16" t="inlineStr"/>
+      <c r="L170" s="16" t="inlineStr"/>
     </row>
     <row r="171" hidden="1">
       <c r="C171" s="13" t="n">
@@ -7611,22 +7882,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H171" s="19" t="inlineStr">
+      <c r="H171" s="16" t="inlineStr"/>
+      <c r="I171" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I171" s="16" t="inlineStr">
+      <c r="J171" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J171" s="16" t="inlineStr">
+      <c r="K171" s="16" t="inlineStr">
         <is>
           <t>거절(결정론 계산) ↔ 바꿨다고 답한다</t>
         </is>
       </c>
-      <c r="K171" s="16" t="inlineStr"/>
+      <c r="L171" s="16" t="inlineStr"/>
     </row>
     <row r="172" hidden="1">
       <c r="A172" s="26" t="inlineStr">
@@ -7667,22 +7939,23 @@
 안내할 수 없는 상품으로는 KB 온국민TDF2035 C-P, KB 온국민TDF2040 C-P, KB 성장형 MP가 있는데, 이들은 상품 위험등급이 다소높은위험으로 허용 상한인 보통위험을 초과하기 때문이에요. 또한 KB 글로벌리츠 ETF는 상품 위험등급이 높은위험이어서 허용 상한을 초과하여 안내할 수 없어요. 이는 적합성 확인 결과이며 투자권유가 아니라는 점을 참고해 주세요. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H172" s="11" t="inlineStr">
+      <c r="H172" s="10" t="inlineStr"/>
+      <c r="I172" s="11" t="inlineStr">
         <is>
           <t>◎ 1순위 · 케이스</t>
         </is>
       </c>
-      <c r="I172" s="10" t="inlineStr">
+      <c r="J172" s="10" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J172" s="10" t="inlineStr">
+      <c r="K172" s="10" t="inlineStr">
         <is>
           <t>적합성 범위로 간다 ↔ 상품 자료만 세 바퀴 돌다 재료 0건으로 끝난다</t>
         </is>
       </c>
-      <c r="K172" s="10" t="inlineStr"/>
+      <c r="L172" s="10" t="inlineStr"/>
     </row>
     <row r="173" hidden="1">
       <c r="C173" s="13" t="n">
@@ -7730,22 +8003,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H173" s="19" t="inlineStr">
+      <c r="H173" s="16" t="inlineStr"/>
+      <c r="I173" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I173" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K173" s="16" t="inlineStr">
+        <is>
           <t>시황만 ↔ 추천펀드가 따라 나온다</t>
         </is>
       </c>
-      <c r="K173" s="16" t="inlineStr"/>
+      <c r="L173" s="16" t="inlineStr"/>
     </row>
     <row r="174" hidden="1">
       <c r="C174" s="13" t="n">
@@ -7780,22 +8054,23 @@
 ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
         </is>
       </c>
-      <c r="H174" s="19" t="inlineStr">
+      <c r="H174" s="16" t="inlineStr"/>
+      <c r="I174" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I174" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J174" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K174" s="16" t="inlineStr">
+        <is>
           <t>상품만 ↔ 월간 투자전략 시황 카드가 따라 나온다</t>
         </is>
       </c>
-      <c r="K174" s="16" t="inlineStr"/>
+      <c r="L174" s="16" t="inlineStr"/>
     </row>
     <row r="175" hidden="1">
       <c r="C175" s="13" t="n">
@@ -7817,22 +8092,23 @@
           <t>- 직원: 이 고객 왜 관리 대상으로 떴어? — 송도윤 고객님이 관리 대상으로 뜬 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 운용변경 없음 상태가 겹쳤기 때문이에요. 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있고, 8,000만원 규모의 판매중단 상품인 'KB 퇴직연금 배당 (주식)'을 보유하고 계세요. 또한 2억 8,000만원의 고유계정대 현금성자산을 보유하고 있으며 디폴트옵션도 미설정 상태예요. 여기에 ISA 만기자금 1억 2,000만원을 보유하고 있고 12개월 이상 운용변경이 없으며 당해 납입액이 없는 상태라서 관리 대상에 올랐어요.</t>
         </is>
       </c>
-      <c r="H175" s="16" t="inlineStr">
+      <c r="H175" s="16" t="inlineStr"/>
+      <c r="I175" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 시연본</t>
         </is>
       </c>
-      <c r="I175" s="16" t="inlineStr">
+      <c r="J175" s="16" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J175" s="16" t="inlineStr">
+      <c r="K175" s="16" t="inlineStr">
         <is>
           <t>이번 세션 ↔ 지난 상담을 요약하거나 「기록 없음」</t>
         </is>
       </c>
-      <c r="K175" s="16" t="inlineStr">
+      <c r="L175" s="16" t="inlineStr">
         <is>
           <t>이 고객 왜 관리 대상으로 떴어?</t>
         </is>
@@ -7858,22 +8134,23 @@
           <t>※ 지난 상담 기록입니다 — 그때 나눈 이야기이지 지금 기준 값이 아닐 수 있습니다. 2025년 10월 6일 상담에서는 수익이 난 투자상품은 유지하되 현금성자산은 시장 상황을 보면서 단계적으로 재투자하고 싶다는 의사를 나눈 기록이 남아 있어요. 이어서 2026년 9월 20일에는 평가금액은 시스템이 계산한 값이므로 대화로 변경할 수 없다는 점과 요청하신 문구에 '적극적으로'라는 표현은 현재 AI 브리핑 화면의 문장에 포함되어 있어 수정할 수 없다는 수정요청을 나눈 기록이 있습니다. 지난 상담 기록이니 지금 기준 값과는 다를 수 있다는 점을 염두에 두고 상담을 이어가 보세요.</t>
         </is>
       </c>
-      <c r="H176" s="16" t="inlineStr">
+      <c r="H176" s="16" t="inlineStr"/>
+      <c r="I176" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 대본</t>
         </is>
       </c>
-      <c r="I176" s="16" t="inlineStr">
+      <c r="J176" s="16" t="inlineStr">
         <is>
           <t>기록 있는 9명 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J176" s="16" t="inlineStr">
+      <c r="K176" s="16" t="inlineStr">
         <is>
           <t>이번 세션은 빠진다 ↔ 방금 한 턴이 「지난 상담」으로 나온다</t>
         </is>
       </c>
-      <c r="K176" s="16" t="inlineStr"/>
+      <c r="L176" s="16" t="inlineStr"/>
     </row>
     <row r="177" hidden="1">
       <c r="C177" s="13" t="n">
@@ -7896,22 +8173,23 @@
 자료에 따르면 이 고객의 총급여가 5,500만원 이하(16.5%)인 경우 개인형IRP 계좌에 추가 납입액 300만원을 넣으면 환급 예상액은 495,000원이 돼요. 이때 연금저축 납입분을 합산한 세액공제 한도와 잔여한도는 각각 900만원이며, 당해 납입액은 0원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 공제율은 원장의 총급여 구간에서 나온 값이니 되물을 필요가 없어요.</t>
         </is>
       </c>
-      <c r="H177" s="19" t="inlineStr">
+      <c r="H177" s="16" t="inlineStr"/>
+      <c r="I177" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I177" s="16" t="inlineStr">
+      <c r="J177" s="16" t="inlineStr">
         <is>
           <t>한도 남은 5명 — 예: 이수민 175926-3048171(900만)</t>
         </is>
       </c>
-      <c r="J177" s="16" t="inlineStr">
+      <c r="K177" s="16" t="inlineStr">
         <is>
           <t>제도값 + 이 고객 계산 둘 다 ↔ 한도만 답하거나 재료 밖 계산으로 잘린다</t>
         </is>
       </c>
-      <c r="K177" s="16" t="inlineStr"/>
+      <c r="L177" s="16" t="inlineStr"/>
     </row>
     <row r="178" hidden="1">
       <c r="C178" s="13" t="n">
@@ -7933,22 +8211,23 @@
           <t>디폴트옵션 등록 및 변경 방법은 KB스타뱅킹과 인터넷뱅킹을 통해 진행할 수 있어요. KB스타뱅킹에서는 전체메뉴, 뱅킹, 가입상품관리, 퇴직연금, 변경관리, 퇴직연금 디폴트옵션, 등록/변경 순서로 이동하면 되고, 인터넷뱅킹에서는 KB퇴직연금, 개인고객, 사전지정운용(디폴트옵션), 등록/변경 메뉴를 이용하면 고객이 직접 처리할 수 있어요. ※ 앱 개편으로 메뉴명이 바뀔 수 있음 — 2025.03.31 기준 표기입니다. 화면번호 관련 자료나 영업점 단말기 화면번호에 대해서는 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="H178" s="16" t="inlineStr">
+      <c r="H178" s="16" t="inlineStr"/>
+      <c r="I178" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · QA</t>
         </is>
       </c>
-      <c r="I178" s="16" t="inlineStr">
+      <c r="J178" s="16" t="inlineStr">
         <is>
           <t>미설정 4명 — 예: 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J178" s="16" t="inlineStr">
+      <c r="K178" s="16" t="inlineStr">
         <is>
           <t>절차·화면·앱 경로를 **갈라** 답한다 ↔ 단말 절차를 앱 경로로 답한다</t>
         </is>
       </c>
-      <c r="K178" s="16" t="inlineStr"/>
+      <c r="L178" s="16" t="inlineStr"/>
     </row>
     <row r="179" hidden="1">
       <c r="C179" s="13" t="n">
@@ -7970,22 +8249,23 @@
           <t>앞서 안내드린 내용은 금리 갈아타기를 통해 원리금보장상품의 관리가 중요하다는 점을 짧게 짚어주는 게 핵심이에요. 연금지급 대기나 교체매매 중인 사용계획 자금이 아닌지 먼저 확인하시고, 갈아탄 상품이 더 좋을 것이라고 수익률을 확정해 약속해서는 안 돼요. 고객에게는 "예금과 같은 원리금보장상품도 관리가 중요합니다. 국민은행은 매월 금리가 좋은 상품을 지속적으로 제공하고 있고, GIC 등 고금리 원리금보장상품도 비대면으로 손쉽게 거래하실 수 있습니다"라고 안내해 보세요.</t>
         </is>
       </c>
-      <c r="H179" s="16" t="inlineStr">
+      <c r="H179" s="16" t="inlineStr"/>
+      <c r="I179" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I179" s="16" t="inlineStr">
+      <c r="J179" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J179" s="16" t="inlineStr">
+      <c r="K179" s="16" t="inlineStr">
         <is>
           <t>직전 답변을 다시 쓴다 ↔ 화면 문장을 고치고 「반영했다」로 끝낸다</t>
         </is>
       </c>
-      <c r="K179" s="16" t="inlineStr">
+      <c r="L179" s="16" t="inlineStr">
         <is>
           <t>고객이 '그 돈 그냥 예금으로 둬도 되지 않나요?' 하는데 뭐라고 하지?</t>
         </is>
@@ -8011,22 +8291,23 @@
           <t>송도윤 고객님이 관리 대상인 사유는 장기 미접촉 상태인 가운데 판매중단 펀드 보유, 미운용 현금성자산 보유, 디폴트옵션 미설정, ISA 만기자금 보유, 12개월 이상 운용변경 없음 상태이기 때문이에요. 현재 358일간 접촉 이력이 없어 타사 비교 견적에 노출되었을 가능성이 있으며, 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계세요. 또한 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있어요.</t>
         </is>
       </c>
-      <c r="H180" s="16" t="inlineStr">
+      <c r="H180" s="16" t="inlineStr"/>
+      <c r="I180" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I180" s="16" t="inlineStr">
+      <c r="J180" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J180" s="16" t="inlineStr">
+      <c r="K180" s="16" t="inlineStr">
         <is>
           <t>이 고객 요건·값 ↔ 고객군 일반 정의로 빗나간 채 끝난다</t>
         </is>
       </c>
-      <c r="K180" s="16" t="inlineStr"/>
+      <c r="L180" s="16" t="inlineStr"/>
     </row>
     <row r="181" hidden="1">
       <c r="B181" s="20" t="inlineStr">
@@ -8055,22 +8336,23 @@
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="H181" s="17" t="inlineStr">
+      <c r="H181" s="16" t="inlineStr"/>
+      <c r="I181" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I181" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K181" s="16" t="inlineStr">
+        <is>
           <t>정직하게 「없다」 ↔ 없는 재료를 지어내 답한다</t>
         </is>
       </c>
-      <c r="K181" s="16" t="inlineStr"/>
+      <c r="L181" s="16" t="inlineStr"/>
     </row>
     <row r="182" hidden="1">
       <c r="C182" s="13" t="n">
@@ -8094,22 +8376,23 @@
 다른 말로 다시 물어보시면 찾을 수도 있어요.</t>
         </is>
       </c>
-      <c r="H182" s="19" t="inlineStr">
+      <c r="H182" s="16" t="inlineStr"/>
+      <c r="I182" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I182" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J182" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K182" s="16" t="inlineStr">
+        <is>
           <t>「고객 화면을 먼저 열어달라」 ↔ 아무 고객 값을 말하거나 일반론으로 넘어간다</t>
         </is>
       </c>
-      <c r="K182" s="16" t="inlineStr"/>
+      <c r="L182" s="16" t="inlineStr"/>
     </row>
     <row r="183" hidden="1">
       <c r="C183" s="13" t="n">
@@ -8131,22 +8414,23 @@
           <t>개인형IRP 중도인출은 원칙적으로 불가하며 2026년 6월 자료 기준으로 법정 사유 6가지에 한해서만 가능하다. 연금수령 중에는 중도인출이 아니라 해지만 가능하다는 점을 미리 안내해 드려야 한다. 첫째는 무주택자의 주택구입으로 매매계약 체결일로부터 소유권 이전 등기 접수일 후 1개월 이내에 신청해야 한다. 둘째는 무주택자의 전세금 및 임차보증금으로 계약 체결일부터 잔금 지급일 후 1개월 이내에 가능하며 하나의 사업장 근무 중 1회로 한정된다. 셋째는 본인과 배우자 및 부양가족의 6개월 이상 요양이며 연간 임금총액의 12.5%를 초과하는 의료비를 부담할 때 신청할 수 있다. 넷째는 자연재난이나 특별재난지역의 사회재난 피해이며, 다섯째는 5년 이내 개인회생절차 개시 결정, 여섯째는 5년 이내 파산선고가 해당된다. 인출 가능금액은 전액 또는 일부로 최대 90%까지 가능하며 횟수 제한은 없다.</t>
         </is>
       </c>
-      <c r="H183" s="16" t="inlineStr">
+      <c r="H183" s="16" t="inlineStr"/>
+      <c r="I183" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I183" s="16" t="inlineStr">
-        <is>
-          <t>고객 없이</t>
-        </is>
-      </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
+          <t>고객 없이</t>
+        </is>
+      </c>
+      <c r="K183" s="16" t="inlineStr">
+        <is>
           <t>고객 없이도 답한다 ↔ 고객을 열라고 답한다</t>
         </is>
       </c>
-      <c r="K183" s="16" t="inlineStr"/>
+      <c r="L183" s="16" t="inlineStr"/>
     </row>
     <row r="184" hidden="1">
       <c r="C184" s="13" t="n">
@@ -8168,22 +8452,23 @@
           <t>송도윤 고객님이 관리 대상이 된 이유는 평가금액 5억 2,000만원 규모의 자산을 보유하고 계시며 운용수익률 32.6%로 동연령 평균 4.7% 및 상위1% 평균 15.3%를 상회하고 있으나, 6개월 이상 장기 미접촉 상태인 가운데 현재 8,000만원 규모의 'KB 퇴직연금 배당 (주식)' 판매중단 상품을 보유하고 계시기 때문이에요. 또한 358일간 접촉 이력이 없어 타사 비교 견적에 노출됐을 가능성이 있으며, 대기 현금성자산 보유, 디폴트옵션 미지정, 성과저조(환매추천) 펀드 보유, 관리 사각지대, 전년 납입 있었으나 당해 미납, ISA 만기자금 보유 항목에도 해당하기 때문이에요.</t>
         </is>
       </c>
-      <c r="H184" s="16" t="inlineStr">
+      <c r="H184" s="16" t="inlineStr"/>
+      <c r="I184" s="16" t="inlineStr">
         <is>
           <t>○ 예비 · 케이스</t>
         </is>
       </c>
-      <c r="I184" s="16" t="inlineStr">
+      <c r="J184" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J184" s="16" t="inlineStr">
+      <c r="K184" s="16" t="inlineStr">
         <is>
           <t>0건이면 안 써 본 도구로 한 번 재계획 ↔ 같은 호출을 반복하다 「근거 없음」</t>
         </is>
       </c>
-      <c r="K184" s="16" t="inlineStr"/>
+      <c r="L184" s="16" t="inlineStr"/>
     </row>
     <row r="185" hidden="1">
       <c r="C185" s="13" t="n">
@@ -8210,22 +8495,23 @@
 장기간 접촉 이력이 없어 타사 비교에 노출될 가능성이 있으므로, 유선 접촉을 통해 관계를 회복해야 합니다. 갈아탄 상품이 더 좋을 것이라고 약속하지 않도록 주의하고, 사용계획이 있는 자금은 먼저 걸러내며, 고객에게 설명할 때는 고유계정대 대신 현금성자산이나 운용지시가 되지 않는 자산이라는 용어를 사용해 주세요.</t>
         </is>
       </c>
-      <c r="H185" s="19" t="inlineStr">
+      <c r="H185" s="16" t="inlineStr"/>
+      <c r="I185" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I185" s="16" t="inlineStr">
+      <c r="J185" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J185" s="16" t="inlineStr">
+      <c r="K185" s="16" t="inlineStr">
         <is>
           <t>상한 안에서 모은 만큼 답한다 ↔ 상한에 걸려 「근거 없음」</t>
         </is>
       </c>
-      <c r="K185" s="16" t="inlineStr"/>
+      <c r="L185" s="16" t="inlineStr"/>
     </row>
     <row r="186" hidden="1">
       <c r="C186" s="13" t="n">
@@ -8243,22 +8529,23 @@
         </is>
       </c>
       <c r="G186" s="16" t="inlineStr"/>
-      <c r="H186" s="19" t="inlineStr">
+      <c r="H186" s="16" t="inlineStr"/>
+      <c r="I186" s="19" t="inlineStr">
         <is>
           <t>– 디버깅용 · 신규</t>
         </is>
       </c>
-      <c r="I186" s="16" t="inlineStr">
+      <c r="J186" s="16" t="inlineStr">
         <is>
           <t>누구나 — 예: 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J186" s="16" t="inlineStr">
+      <c r="K186" s="16" t="inlineStr">
         <is>
           <t>브리핑 캐시를 읽어 쓴다 ↔ 429 로 답변 작성이 죽고 「LLM 호출 실패」</t>
         </is>
       </c>
-      <c r="K186" s="16" t="inlineStr">
+      <c r="L186" s="16" t="inlineStr">
         <is>
           <t>[질문이 아니라 상황 표기 — 손으로 고른다]</t>
         </is>
@@ -8326,22 +8613,23 @@
 "세액공제 한도 얼마야?"·"디폴트옵션 변경 화면번호"처럼 값이나 절차만 물어보셔도 됩니다.</t>
         </is>
       </c>
-      <c r="H187" s="21" t="inlineStr">
+      <c r="H187" s="16" t="inlineStr"/>
+      <c r="I187" s="21" t="inlineStr">
         <is>
           <t>◎ 1순위 · 라이브러리</t>
         </is>
       </c>
-      <c r="I187" s="16" t="inlineStr">
+      <c r="J187" s="16" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 정민석 181245-3097614</t>
         </is>
       </c>
-      <c r="J187" s="16" t="inlineStr">
+      <c r="K187" s="16" t="inlineStr">
         <is>
           <t>성향이 다르면 상한·목록·제외가 다르다 ↔ 두 고객에게 같은 목록</t>
         </is>
       </c>
-      <c r="K187" s="16" t="inlineStr"/>
+      <c r="L187" s="16" t="inlineStr"/>
     </row>
     <row r="188" hidden="1">
       <c r="C188" s="13" t="n">
@@ -8366,22 +8654,23 @@
 이수민 고객님께는 디폴트옵션이 설정되어 있지 않아요. 현재 원리금보장상품 100% 운용 고객이자 1개월 내 만기도래 원리금보장상품을 보유하고 있으면서 디폴트옵션이 미등록된 상태예요. 정기예금 자동 재예치 제도가 폐지되어 운용지시가 없으면 만기자금이 현금성자산으로 상환되므로, 재예치 폐지를 근거로 사전지정 등록을 권유하는 화법을 활용할 수 있어요. 투자성향이 등록하신 디폴트옵션 위험등급보다 높은 경우라면 “정기예금(GIC,ELB) 대신 디폴트옵션(저위험이상)으로 운용”을 제안하는 방식을 검토해 보세요.</t>
         </is>
       </c>
-      <c r="H188" s="17" t="inlineStr">
+      <c r="H188" s="16" t="inlineStr"/>
+      <c r="I188" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I188" s="16" t="inlineStr">
+      <c r="J188" s="16" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 이수민 175926-3048171</t>
         </is>
       </c>
-      <c r="J188" s="16" t="inlineStr">
+      <c r="K188" s="16" t="inlineStr">
         <is>
           <t>설정/미설정 **양쪽 다** 답이 나온다 ↔ 설정된 쪽이 「자료가 없습니다」</t>
         </is>
       </c>
-      <c r="K188" s="16" t="inlineStr"/>
+      <c r="L188" s="16" t="inlineStr"/>
     </row>
     <row r="189" hidden="1">
       <c r="C189" s="13" t="n">
@@ -8406,22 +8695,23 @@
 송도윤 고객님의 만기 내역은 2026년 9월 20일에 만기가 경과한 ISA 만기자금(IRP 외부) 1억 2,000만원이 있어요. 원장에 등록된 만기 항목은 해당 건이 전부이며, 다른 만기 건은 자료에 없어요.</t>
         </is>
       </c>
-      <c r="H189" s="17" t="inlineStr">
+      <c r="H189" s="16" t="inlineStr"/>
+      <c r="I189" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I189" s="16" t="inlineStr">
+      <c r="J189" s="16" t="inlineStr">
         <is>
           <t>오세훈2 193482-6012375 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="J189" s="16" t="inlineStr">
+      <c r="K189" s="16" t="inlineStr">
         <is>
           <t>2건은 둘 다, 0건은 「없다」 ↔ 2건에 한 건만 · 0건에 ISA 만기를 답한다</t>
         </is>
       </c>
-      <c r="K189" s="16" t="inlineStr"/>
+      <c r="L189" s="16" t="inlineStr"/>
     </row>
     <row r="190" hidden="1">
       <c r="C190" s="13" t="n">
@@ -8446,22 +8736,23 @@
 적극투자형 성향임에도 원리금보장·현금성 자산이 36%를 차지하고 있어 포트폴리오 재정비가 필요한 시점이고, 현재 수익률은 13.7%로 동연령 평균 12.1%를 상회하고 있으나 2026년 9월 10일 만기가 경과된 기업은행 퇴직연금 정기예금 4,050만원이 대기 중이기 때문에 관리 대상이에요.</t>
         </is>
       </c>
-      <c r="H190" s="19" t="inlineStr">
+      <c r="H190" s="16" t="inlineStr"/>
+      <c r="I190" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I190" s="16" t="inlineStr">
+      <c r="J190" s="16" t="inlineStr">
         <is>
           <t>송도윤6 188406-7352194 ↔ 이준호0 198734-1205842</t>
         </is>
       </c>
-      <c r="J190" s="16" t="inlineStr">
+      <c r="K190" s="16" t="inlineStr">
         <is>
           <t>요건 6개 ↔ 「오늘 기준 타겟 아님」 · 0개 고객에게 요건을 지어낸다</t>
         </is>
       </c>
-      <c r="K190" s="16" t="inlineStr"/>
+      <c r="L190" s="16" t="inlineStr"/>
     </row>
     <row r="191" hidden="1">
       <c r="C191" s="13" t="n">
@@ -8486,22 +8777,23 @@
 고객과의 지난 상담 기록은 확인되지 않아요. 이 고객과의 지난 상담 기록은 0건으로 조회되므로, 이번 상담이 첫 기록이에요.</t>
         </is>
       </c>
-      <c r="H191" s="19" t="inlineStr">
+      <c r="H191" s="16" t="inlineStr"/>
+      <c r="I191" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I191" s="16" t="inlineStr">
+      <c r="J191" s="16" t="inlineStr">
         <is>
           <t>송도윤 188406-7352194 ↔ 김서연 171203-4815062</t>
         </is>
       </c>
-      <c r="J191" s="16" t="inlineStr">
+      <c r="K191" s="16" t="inlineStr">
         <is>
           <t>기록/무기록 양쪽 ↔ 없는 쪽에서 무관한 카드가 근거로 선다</t>
         </is>
       </c>
-      <c r="K191" s="16" t="inlineStr"/>
+      <c r="L191" s="16" t="inlineStr"/>
     </row>
     <row r="192" hidden="1">
       <c r="C192" s="13" t="n">
@@ -8527,22 +8819,23 @@
 다만 ISA 만기자금을 개인형IRP 계좌로 전환하는 경우라면 잔여한도 안에서 나눠 쓰는 것이 아니라 공제 대상 한도 자체가 늘어나는 별개의 축이에요. 300만원을 ISA 만기자금에서 개인형IRP로 전환할 때 적용되는 공제율에 따라 추가 공제 대상과 환급액이 달라질 수 있어요. 총급여 5,500만원 이하(16.5%)인 경우 이 전환으로 늘어나는 환급액은 49,500원이에요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다. 총급여 구간이 확인되지 않았으니 단말에서 고객의 총급여 구간을 먼저 확인하고 안내해 주세요.</t>
         </is>
       </c>
-      <c r="H192" s="19" t="inlineStr">
+      <c r="H192" s="16" t="inlineStr"/>
+      <c r="I192" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I192" s="16" t="inlineStr">
+      <c r="J192" s="16" t="inlineStr">
         <is>
           <t>이수민900 175926-3048171 ↔ 송도윤0 188406-7352194</t>
         </is>
       </c>
-      <c r="J192" s="16" t="inlineStr">
+      <c r="K192" s="16" t="inlineStr">
         <is>
           <t>환급액 ↔ 「추가 공제 없음」 · 없는 쪽에도 금액을 만든다</t>
         </is>
       </c>
-      <c r="K192" s="16" t="inlineStr"/>
+      <c r="L192" s="16" t="inlineStr"/>
     </row>
     <row r="193" hidden="1">
       <c r="C193" s="13" t="n">
@@ -8567,22 +8860,23 @@
 총급여 기준을 적용하는 경우 5,500만원 이하 고객에게는 16.5%, 초과 고객에게는 13.2%의 세액공제율이 적용돼요. 세액공제 한도는 연간 납입액 최대 900만원이고, 공제율은 지방소득세 포함 기준이며 5,500만원 정확히 일치하는 경우에도 16.5% 구간에 해당해요. 다만 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못하므로 이 점을 유의해야 하며, 해당 내용은 2026년 6월 기준의 자료를 바탕으로 안내드려요.</t>
         </is>
       </c>
-      <c r="H193" s="17" t="inlineStr">
+      <c r="H193" s="16" t="inlineStr"/>
+      <c r="I193" s="17" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
         </is>
       </c>
-      <c r="I193" s="16" t="inlineStr">
+      <c r="J193" s="16" t="inlineStr">
         <is>
           <t>박지민16.5 154821-4938201 ↔ 한지우13.2 176903-5528417</t>
         </is>
       </c>
-      <c r="J193" s="16" t="inlineStr">
+      <c r="K193" s="16" t="inlineStr">
         <is>
           <t>원장 구간대로 갈린다 ↔ 둘 다 13.2% (구간을 안 읽고 낮은 쪽으로 떨어진다) · 되묻는다</t>
         </is>
       </c>
-      <c r="K193" s="16" t="inlineStr"/>
+      <c r="L193" s="16" t="inlineStr"/>
     </row>
     <row r="194" hidden="1">
       <c r="C194" s="13" t="n">
@@ -8607,22 +8901,23 @@
 ISA 만기자금을 IRP로 옮겼을 때의 세액공제 관련 자료는 아직 준비된 것이 없어요. 박지민 고객의 개인형IRP 계좌 추가 납입에 대해서는, 잔여한도 300만원을 채워 총 900만원을 납입할 경우 총급여 5,500만원 이하(16.5%) 기준으로 환급 예상액이 990,000원에서 1,485,000원으로 늘어나 495,000원이 증가해요. 단, 세액공제 전 결정세액이 공제액보다 적으면 최대 환급액을 받지 못한다 — 소득이 낮은 고객에게 "900만원 넣으면 무조건 148.5만원"이라고 안내하면 오안내다.</t>
         </is>
       </c>
-      <c r="H194" s="19" t="inlineStr">
+      <c r="H194" s="16" t="inlineStr"/>
+      <c r="I194" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I194" s="16" t="inlineStr">
+      <c r="J194" s="16" t="inlineStr">
         <is>
           <t>김서연 171203-4815062 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="J194" s="16" t="inlineStr">
+      <c r="K194" s="16" t="inlineStr">
         <is>
           <t>전환 특례 계산 ↔ 「ISA 가 없다」 · 없는 고객에게 전환을 안내한다</t>
         </is>
       </c>
-      <c r="K194" s="16" t="inlineStr"/>
+      <c r="L194" s="16" t="inlineStr"/>
     </row>
     <row r="195" hidden="1">
       <c r="C195" s="13" t="n">
@@ -8648,22 +8943,23 @@
 송도윤 고객님은 연금개시요건을 충족하지 않아 현재 연금개시를 하실 수 없어요. 자료에 따르면 연금개시 상태는 미개시이며 연금개시요건도 충족되지 않은 상태로 확인돼요.</t>
         </is>
       </c>
-      <c r="H195" s="19" t="inlineStr">
+      <c r="H195" s="16" t="inlineStr"/>
+      <c r="I195" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I195" s="16" t="inlineStr">
+      <c r="J195" s="16" t="inlineStr">
         <is>
           <t>박정호 168450-7293815 ↔ 송도윤 188406-7352194</t>
         </is>
       </c>
-      <c r="J195" s="16" t="inlineStr">
+      <c r="K195" s="16" t="inlineStr">
         <is>
           <t>충족/미충족 양쪽 ↔ 미충족 쪽이 「자료 없음」</t>
         </is>
       </c>
-      <c r="K195" s="16" t="inlineStr"/>
+      <c r="L195" s="16" t="inlineStr"/>
     </row>
     <row r="196" hidden="1">
       <c r="C196" s="13" t="n">
@@ -8688,22 +8984,23 @@
 판매중단된 보유상품은 없어요.</t>
         </is>
       </c>
-      <c r="H196" s="19" t="inlineStr">
+      <c r="H196" s="16" t="inlineStr"/>
+      <c r="I196" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I196" s="16" t="inlineStr">
+      <c r="J196" s="16" t="inlineStr">
         <is>
           <t>최서윤 165932-8741205 ↔ 박지민 154821-4938201</t>
         </is>
       </c>
-      <c r="J196" s="16" t="inlineStr">
+      <c r="K196" s="16" t="inlineStr">
         <is>
           <t>보유 종목 ↔ 「없다」 · 미보유에 종목을 지어낸다</t>
         </is>
       </c>
-      <c r="K196" s="16" t="inlineStr"/>
+      <c r="L196" s="16" t="inlineStr"/>
     </row>
     <row r="197" hidden="1">
       <c r="C197" s="13" t="n">
@@ -8735,22 +9032,23 @@
 퇴직연금 상품 검색 시 'TDF상품'이나 '추천상품' 테마에 접속하시면 관련 상품을 찾으실 수 있을 거라고 안내해 주시면 돼요.</t>
         </is>
       </c>
-      <c r="H197" s="19" t="inlineStr">
+      <c r="H197" s="16" t="inlineStr"/>
+      <c r="I197" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I197" s="16" t="inlineStr">
+      <c r="J197" s="16" t="inlineStr">
         <is>
           <t>박정호 168450-7293815(펀드 경험 없음) ↔ 김현수 173544-2074623(펀드 보유)</t>
         </is>
       </c>
-      <c r="J197" s="16" t="inlineStr">
+      <c r="K197" s="16" t="inlineStr">
         <is>
           <t>경험 없는 쪽은 원금보장 유지 + 금리만 올리는 제안(저축은행 정기예금), 있는 쪽은 일부 금액만 추천펀드·TDF ↔ 둘에게 같은 화법이 나온다 · 두 카드를 섞어 답한다</t>
         </is>
       </c>
-      <c r="K197" s="16" t="inlineStr"/>
+      <c r="L197" s="16" t="inlineStr"/>
     </row>
     <row r="198" hidden="1">
       <c r="C198" s="13" t="n">
@@ -8775,25 +9073,26 @@
 이 고객에게는 지금 요건에 맞는 안내 대상 세미나가 없어요. 다만 현재 열려 있는 세미나 중 날짜가 가장 가까운 것은 11/12(목) 17시에 KB국민은행 WM투자부에서 주관하는 «내 투자성향에 맞는 포트폴리오 찾기»예요. 이 콘텐츠는 적극투자형 성향에 비해 원리금보장·현금성 자산 비중이 높아, 포트폴리오를 점검하고 리밸런싱할 때 참고하시기 좋으나 이 고객의 요건과는 무관해요. 안내 시 참고할 링크는 https://obank.kbstar.com/demo/seminar/irp-004 에요. 다른 이벤트나 세미나 관련해서 다른 후보 콘텐츠들에 대한 상세 요건은 아직 준비된 자료가 없어요.</t>
         </is>
       </c>
-      <c r="H198" s="19" t="inlineStr">
+      <c r="H198" s="16" t="inlineStr"/>
+      <c r="I198" s="19" t="inlineStr">
         <is>
           <t>○ 예비 · 신규</t>
         </is>
       </c>
-      <c r="I198" s="16" t="inlineStr">
+      <c r="J198" s="16" t="inlineStr">
         <is>
           <t>콘텐츠 있음 송도윤 188406-7352194 ↔ 없음 이준호 198734-1205842</t>
         </is>
       </c>
-      <c r="J198" s="16" t="inlineStr">
+      <c r="K198" s="16" t="inlineStr">
         <is>
           <t>브리핑 ⑨ 와 같은 콘텐츠 ↔ 「걸린 게 없다」 · 다른 고객 콘텐츠를 말한다</t>
         </is>
       </c>
-      <c r="K198" s="16" t="inlineStr"/>
+      <c r="L198" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K198"/>
+  <autoFilter ref="A4:L198"/>
   <mergeCells count="38">
     <mergeCell ref="B53:B66"/>
     <mergeCell ref="A95:A134"/>

--- a/docs/QUESTION_MAP.xlsx
+++ b/docs/QUESTION_MAP.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -97,11 +97,18 @@
         <color rgb="00BFA55A"/>
       </top>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00BFA55A"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +542,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K198"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -620,7 +630,7 @@
       </c>
     </row>
     <row r="5" ht="202.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ⅰ. 대상 선정 — 오늘 누구를 보고, 왜 그 사람인가</t>
         </is>
@@ -673,7 +683,6 @@
       <c r="K5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="11" t="n"/>
       <c r="C6" s="12" t="n">
         <v>2</v>
       </c>
@@ -706,7 +715,6 @@
       <c r="K6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="67.5" customHeight="1">
-      <c r="A7" s="11" t="n"/>
       <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
@@ -744,7 +752,6 @@
       <c r="K7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="229.5" customHeight="1">
-      <c r="A8" s="11" t="n"/>
       <c r="C8" s="12" t="n">
         <v>4</v>
       </c>
@@ -788,7 +795,6 @@
       <c r="K8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="11" t="n"/>
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t>2. 고객군·관리 기준</t>
@@ -831,7 +837,6 @@
       <c r="K9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="67.5" customHeight="1">
-      <c r="A10" s="11" t="n"/>
       <c r="C10" s="12" t="n">
         <v>6</v>
       </c>
@@ -869,7 +874,6 @@
       <c r="K10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="11" t="n"/>
       <c r="C11" s="12" t="n">
         <v>7</v>
       </c>
@@ -909,7 +913,6 @@
       <c r="K11" s="14" t="inlineStr"/>
     </row>
     <row r="12" hidden="1">
-      <c r="A12" s="11" t="n"/>
       <c r="C12" s="12" t="n">
         <v>8</v>
       </c>
@@ -950,7 +953,6 @@
       <c r="K12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="202.5" customHeight="1">
-      <c r="A13" s="11" t="n"/>
       <c r="C13" s="12" t="n">
         <v>9</v>
       </c>
@@ -988,7 +990,6 @@
       <c r="K13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="67.5" customHeight="1">
-      <c r="A14" s="11" t="n"/>
       <c r="C14" s="12" t="n">
         <v>10</v>
       </c>
@@ -1026,7 +1027,6 @@
       <c r="K14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="202.5" customHeight="1">
-      <c r="A15" s="11" t="n"/>
       <c r="B15" s="18" t="inlineStr">
         <is>
           <t>3. 오늘의 타겟 목록</t>
@@ -1069,7 +1069,6 @@
       <c r="K15" s="14" t="inlineStr"/>
     </row>
     <row r="16" hidden="1">
-      <c r="A16" s="11" t="n"/>
       <c r="C16" s="12" t="n">
         <v>12</v>
       </c>
@@ -1118,7 +1117,7 @@
       <c r="K16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Ⅱ. 고객 상태 — 이 고객이 지금 어떤 상태이고, 조심할 것은 무엇인가</t>
         </is>
@@ -1165,7 +1164,6 @@
       <c r="K17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="94.5" customHeight="1">
-      <c r="A18" s="11" t="n"/>
       <c r="C18" s="12" t="n">
         <v>14</v>
       </c>
@@ -1206,7 +1204,6 @@
       <c r="K18" s="14" t="inlineStr"/>
     </row>
     <row r="19" hidden="1">
-      <c r="A19" s="11" t="n"/>
       <c r="C19" s="12" t="n">
         <v>15</v>
       </c>
@@ -1244,7 +1241,6 @@
       <c r="K19" s="14" t="inlineStr"/>
     </row>
     <row r="20" hidden="1">
-      <c r="A20" s="11" t="n"/>
       <c r="C20" s="12" t="n">
         <v>16</v>
       </c>
@@ -1282,7 +1278,6 @@
       <c r="K20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="94.5" customHeight="1">
-      <c r="A21" s="11" t="n"/>
       <c r="C21" s="12" t="n">
         <v>17</v>
       </c>
@@ -1323,7 +1318,6 @@
       <c r="K21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="81" customHeight="1">
-      <c r="A22" s="11" t="n"/>
       <c r="C22" s="12" t="n">
         <v>18</v>
       </c>
@@ -1364,7 +1358,6 @@
       <c r="K22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="40.5" customHeight="1">
-      <c r="A23" s="11" t="n"/>
       <c r="C23" s="12" t="n">
         <v>19</v>
       </c>
@@ -1402,7 +1395,6 @@
       <c r="K23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="175.5" customHeight="1">
-      <c r="A24" s="11" t="n"/>
       <c r="C24" s="12" t="n">
         <v>20</v>
       </c>
@@ -1445,7 +1437,6 @@
       <c r="K24" s="14" t="inlineStr"/>
     </row>
     <row r="25" hidden="1">
-      <c r="A25" s="11" t="n"/>
       <c r="C25" s="12" t="n">
         <v>21</v>
       </c>
@@ -1485,7 +1476,6 @@
       <c r="K25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="11" t="n"/>
       <c r="C26" s="12" t="n">
         <v>22</v>
       </c>
@@ -1523,7 +1513,6 @@
       <c r="K26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="108" customHeight="1">
-      <c r="A27" s="11" t="n"/>
       <c r="C27" s="12" t="n">
         <v>23</v>
       </c>
@@ -1562,7 +1551,6 @@
       <c r="K27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="108" customHeight="1">
-      <c r="A28" s="11" t="n"/>
       <c r="C28" s="12" t="n">
         <v>24</v>
       </c>
@@ -1603,7 +1591,6 @@
       <c r="K28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="40.5" customHeight="1">
-      <c r="A29" s="11" t="n"/>
       <c r="B29" s="18" t="inlineStr">
         <is>
           <t>5. 고객 계좌 상태 확인</t>
@@ -1646,7 +1633,6 @@
       <c r="K29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="11" t="n"/>
       <c r="C30" s="12" t="n">
         <v>26</v>
       </c>
@@ -1680,7 +1666,6 @@
       <c r="K30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="40.5" customHeight="1">
-      <c r="A31" s="11" t="n"/>
       <c r="C31" s="12" t="n">
         <v>27</v>
       </c>
@@ -1718,7 +1703,6 @@
       <c r="K31" s="14" t="inlineStr"/>
     </row>
     <row r="32" hidden="1">
-      <c r="A32" s="11" t="n"/>
       <c r="C32" s="12" t="n">
         <v>28</v>
       </c>
@@ -1756,7 +1740,6 @@
       <c r="K32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="121.5" customHeight="1">
-      <c r="A33" s="11" t="n"/>
       <c r="C33" s="12" t="n">
         <v>29</v>
       </c>
@@ -1797,7 +1780,6 @@
       <c r="K33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="11" t="n"/>
       <c r="C34" s="12" t="n">
         <v>30</v>
       </c>
@@ -1830,7 +1812,6 @@
       <c r="K34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="11" t="n"/>
       <c r="C35" s="12" t="n">
         <v>31</v>
       </c>
@@ -1868,7 +1849,6 @@
       <c r="K35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="11" t="n"/>
       <c r="C36" s="12" t="n">
         <v>32</v>
       </c>
@@ -1906,7 +1886,6 @@
       <c r="K36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="11" t="n"/>
       <c r="C37" s="12" t="n">
         <v>33</v>
       </c>
@@ -1944,7 +1923,6 @@
       <c r="K37" s="14" t="inlineStr"/>
     </row>
     <row r="38" hidden="1">
-      <c r="A38" s="11" t="n"/>
       <c r="B38" s="18" t="inlineStr">
         <is>
           <t>6. 상담 이력 조회</t>
@@ -1987,7 +1965,6 @@
       <c r="K38" s="14" t="inlineStr"/>
     </row>
     <row r="39" hidden="1">
-      <c r="A39" s="11" t="n"/>
       <c r="C39" s="12" t="n">
         <v>35</v>
       </c>
@@ -2016,7 +1993,6 @@
       <c r="K39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="11" t="n"/>
       <c r="C40" s="12" t="n">
         <v>36</v>
       </c>
@@ -2054,7 +2030,6 @@
       <c r="K40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="11" t="n"/>
       <c r="C41" s="12" t="n">
         <v>37</v>
       </c>
@@ -2092,7 +2067,6 @@
       <c r="K41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="216" customHeight="1">
-      <c r="A42" s="11" t="n"/>
       <c r="B42" s="18" t="inlineStr">
         <is>
           <t>7. 금지·주의 안내</t>
@@ -2144,7 +2118,6 @@
       <c r="K42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="162" customHeight="1">
-      <c r="A43" s="11" t="n"/>
       <c r="C43" s="12" t="n">
         <v>39</v>
       </c>
@@ -2186,7 +2159,6 @@
       <c r="K43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="67.5" customHeight="1">
-      <c r="A44" s="11" t="n"/>
       <c r="C44" s="12" t="n">
         <v>40</v>
       </c>
@@ -2224,7 +2196,6 @@
       <c r="K44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="243" customHeight="1">
-      <c r="A45" s="11" t="n"/>
       <c r="C45" s="12" t="n">
         <v>41</v>
       </c>
@@ -2271,7 +2242,6 @@
       <c r="K45" s="14" t="inlineStr"/>
     </row>
     <row r="46" hidden="1">
-      <c r="A46" s="11" t="n"/>
       <c r="C46" s="12" t="n">
         <v>42</v>
       </c>
@@ -2309,7 +2279,6 @@
       <c r="K46" s="14" t="inlineStr"/>
     </row>
     <row r="47" hidden="1">
-      <c r="A47" s="11" t="n"/>
       <c r="C47" s="12" t="n">
         <v>43</v>
       </c>
@@ -2363,7 +2332,6 @@
       <c r="K47" s="14" t="inlineStr"/>
     </row>
     <row r="48" hidden="1">
-      <c r="A48" s="11" t="n"/>
       <c r="C48" s="12" t="n">
         <v>44</v>
       </c>
@@ -2402,7 +2370,6 @@
       <c r="K48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="148.5" customHeight="1">
-      <c r="A49" s="11" t="n"/>
       <c r="C49" s="12" t="n">
         <v>45</v>
       </c>
@@ -2449,7 +2416,6 @@
       </c>
     </row>
     <row r="50" ht="54" customHeight="1">
-      <c r="A50" s="11" t="n"/>
       <c r="B50" s="18" t="inlineStr">
         <is>
           <t>8. 상담 준비 자료</t>
@@ -2492,7 +2458,6 @@
       <c r="K50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="81" customHeight="1">
-      <c r="A51" s="11" t="n"/>
       <c r="C51" s="12" t="n">
         <v>47</v>
       </c>
@@ -2530,7 +2495,6 @@
       <c r="K51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="229.5" customHeight="1">
-      <c r="A52" s="11" t="n"/>
       <c r="C52" s="12" t="n">
         <v>48</v>
       </c>
@@ -2581,7 +2545,7 @@
       </c>
     </row>
     <row r="53" ht="148.5" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>Ⅲ. 업무 확인 — 제도는 어떻고, 어떻게 처리하고, 몇 번 화면이고, 시장은 어떤가</t>
         </is>
@@ -2637,7 +2601,6 @@
       <c r="K53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="81" customHeight="1">
-      <c r="A54" s="11" t="n"/>
       <c r="C54" s="12" t="n">
         <v>50</v>
       </c>
@@ -2675,7 +2638,6 @@
       <c r="K54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="81" customHeight="1">
-      <c r="A55" s="11" t="n"/>
       <c r="C55" s="12" t="n">
         <v>51</v>
       </c>
@@ -2713,7 +2675,6 @@
       <c r="K55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="40.5" customHeight="1">
-      <c r="A56" s="11" t="n"/>
       <c r="C56" s="12" t="n">
         <v>52</v>
       </c>
@@ -2751,7 +2712,6 @@
       <c r="K56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="54" customHeight="1">
-      <c r="A57" s="11" t="n"/>
       <c r="C57" s="12" t="n">
         <v>53</v>
       </c>
@@ -2786,7 +2746,6 @@
       <c r="K57" s="14" t="inlineStr"/>
     </row>
     <row r="58" hidden="1">
-      <c r="A58" s="11" t="n"/>
       <c r="C58" s="12" t="n">
         <v>54</v>
       </c>
@@ -2825,7 +2784,6 @@
       <c r="K58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="54" customHeight="1">
-      <c r="A59" s="11" t="n"/>
       <c r="C59" s="12" t="n">
         <v>55</v>
       </c>
@@ -2865,7 +2823,6 @@
       <c r="K59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="67.5" customHeight="1">
-      <c r="A60" s="11" t="n"/>
       <c r="C60" s="12" t="n">
         <v>56</v>
       </c>
@@ -2904,7 +2861,6 @@
       <c r="K60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="81" customHeight="1">
-      <c r="A61" s="11" t="n"/>
       <c r="C61" s="12" t="n">
         <v>57</v>
       </c>
@@ -2942,7 +2898,6 @@
       <c r="K61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="108" customHeight="1">
-      <c r="A62" s="11" t="n"/>
       <c r="C62" s="12" t="n">
         <v>58</v>
       </c>
@@ -2980,7 +2935,6 @@
       <c r="K62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="94.5" customHeight="1">
-      <c r="A63" s="11" t="n"/>
       <c r="C63" s="12" t="n">
         <v>59</v>
       </c>
@@ -3018,7 +2972,6 @@
       <c r="K63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="40.5" customHeight="1">
-      <c r="A64" s="11" t="n"/>
       <c r="C64" s="12" t="n">
         <v>60</v>
       </c>
@@ -3056,7 +3009,6 @@
       <c r="K64" s="14" t="inlineStr"/>
     </row>
     <row r="65" hidden="1">
-      <c r="A65" s="11" t="n"/>
       <c r="C65" s="12" t="n">
         <v>61</v>
       </c>
@@ -3106,7 +3058,6 @@
       <c r="K65" s="14" t="inlineStr"/>
     </row>
     <row r="66" hidden="1">
-      <c r="A66" s="11" t="n"/>
       <c r="C66" s="12" t="n">
         <v>62</v>
       </c>
@@ -3157,7 +3108,6 @@
       <c r="K66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="175.5" customHeight="1">
-      <c r="A67" s="11" t="n"/>
       <c r="B67" s="18" t="inlineStr">
         <is>
           <t>10. 업무 처리 절차</t>
@@ -3203,7 +3153,6 @@
       <c r="K67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="54" customHeight="1">
-      <c r="A68" s="11" t="n"/>
       <c r="C68" s="12" t="n">
         <v>64</v>
       </c>
@@ -3243,7 +3192,6 @@
       <c r="K68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="40.5" customHeight="1">
-      <c r="A69" s="11" t="n"/>
       <c r="C69" s="12" t="n">
         <v>65</v>
       </c>
@@ -3281,7 +3229,6 @@
       <c r="K69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="216" customHeight="1">
-      <c r="A70" s="11" t="n"/>
       <c r="C70" s="12" t="n">
         <v>66</v>
       </c>
@@ -3322,7 +3269,6 @@
       <c r="K70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="67.5" customHeight="1">
-      <c r="A71" s="11" t="n"/>
       <c r="C71" s="12" t="n">
         <v>67</v>
       </c>
@@ -3360,7 +3306,6 @@
       <c r="K71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="40.5" customHeight="1">
-      <c r="A72" s="11" t="n"/>
       <c r="C72" s="12" t="n">
         <v>68</v>
       </c>
@@ -3398,7 +3343,6 @@
       <c r="K72" s="14" t="inlineStr"/>
     </row>
     <row r="73" hidden="1">
-      <c r="A73" s="11" t="n"/>
       <c r="C73" s="12" t="n">
         <v>69</v>
       </c>
@@ -3437,7 +3381,6 @@
       <c r="K73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="54" customHeight="1">
-      <c r="A74" s="11" t="n"/>
       <c r="C74" s="12" t="n">
         <v>70</v>
       </c>
@@ -3475,7 +3418,6 @@
       <c r="K74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="108" customHeight="1">
-      <c r="A75" s="11" t="n"/>
       <c r="C75" s="12" t="n">
         <v>71</v>
       </c>
@@ -3513,7 +3455,6 @@
       <c r="K75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="67.5" customHeight="1">
-      <c r="A76" s="11" t="n"/>
       <c r="C76" s="12" t="n">
         <v>72</v>
       </c>
@@ -3551,7 +3492,6 @@
       <c r="K76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="40.5" customHeight="1">
-      <c r="A77" s="11" t="n"/>
       <c r="B77" s="18" t="inlineStr">
         <is>
           <t>11. 단말 화면번호</t>
@@ -3594,7 +3534,6 @@
       <c r="K77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="121.5" customHeight="1">
-      <c r="A78" s="11" t="n"/>
       <c r="C78" s="12" t="n">
         <v>74</v>
       </c>
@@ -3635,7 +3574,6 @@
       <c r="K78" s="14" t="inlineStr"/>
     </row>
     <row r="79" hidden="1">
-      <c r="A79" s="11" t="n"/>
       <c r="C79" s="12" t="n">
         <v>75</v>
       </c>
@@ -3673,7 +3611,6 @@
       <c r="K79" s="14" t="inlineStr"/>
     </row>
     <row r="80" hidden="1">
-      <c r="A80" s="11" t="n"/>
       <c r="C80" s="12" t="n">
         <v>76</v>
       </c>
@@ -3713,7 +3650,6 @@
       <c r="K80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="27" customHeight="1">
-      <c r="A81" s="11" t="n"/>
       <c r="C81" s="12" t="n">
         <v>77</v>
       </c>
@@ -3751,7 +3687,6 @@
       <c r="K81" s="14" t="inlineStr"/>
     </row>
     <row r="82" hidden="1">
-      <c r="A82" s="11" t="n"/>
       <c r="C82" s="12" t="n">
         <v>78</v>
       </c>
@@ -3789,7 +3724,6 @@
       <c r="K82" s="14" t="inlineStr"/>
     </row>
     <row r="83" hidden="1">
-      <c r="A83" s="11" t="n"/>
       <c r="C83" s="12" t="n">
         <v>79</v>
       </c>
@@ -3827,7 +3761,6 @@
       <c r="K83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="67.5" customHeight="1">
-      <c r="A84" s="11" t="n"/>
       <c r="B84" s="18" t="inlineStr">
         <is>
           <t>12. 비대면 채널 경로</t>
@@ -3870,7 +3803,6 @@
       <c r="K84" s="14" t="inlineStr"/>
     </row>
     <row r="85" ht="81" customHeight="1">
-      <c r="A85" s="11" t="n"/>
       <c r="C85" s="12" t="n">
         <v>81</v>
       </c>
@@ -3909,7 +3841,6 @@
       <c r="K85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="54" customHeight="1">
-      <c r="A86" s="11" t="n"/>
       <c r="C86" s="12" t="n">
         <v>82</v>
       </c>
@@ -3947,7 +3878,6 @@
       <c r="K86" s="14" t="inlineStr"/>
     </row>
     <row r="87" ht="54" customHeight="1">
-      <c r="A87" s="11" t="n"/>
       <c r="C87" s="12" t="n">
         <v>83</v>
       </c>
@@ -3985,7 +3915,6 @@
       <c r="K87" s="14" t="inlineStr"/>
     </row>
     <row r="88" hidden="1">
-      <c r="A88" s="11" t="n"/>
       <c r="C88" s="12" t="n">
         <v>84</v>
       </c>
@@ -4026,7 +3955,6 @@
       <c r="K88" s="14" t="inlineStr"/>
     </row>
     <row r="89" hidden="1">
-      <c r="A89" s="11" t="n"/>
       <c r="C89" s="12" t="n">
         <v>85</v>
       </c>
@@ -4064,7 +3992,6 @@
       <c r="K89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="108" customHeight="1">
-      <c r="A90" s="11" t="n"/>
       <c r="B90" s="18" t="inlineStr">
         <is>
           <t>13. 시황</t>
@@ -4107,7 +4034,6 @@
       <c r="K90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="189" customHeight="1">
-      <c r="A91" s="11" t="n"/>
       <c r="C91" s="12" t="n">
         <v>87</v>
       </c>
@@ -4151,7 +4077,6 @@
       <c r="K91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="243" customHeight="1">
-      <c r="A92" s="11" t="n"/>
       <c r="C92" s="12" t="n">
         <v>88</v>
       </c>
@@ -4193,14 +4118,13 @@
       </c>
       <c r="K92" s="14" t="inlineStr"/>
     </row>
-    <row r="93" ht="108" customHeight="1">
-      <c r="A93" s="11" t="n"/>
+    <row r="93" ht="27" customHeight="1">
       <c r="C93" s="12" t="n">
         <v>89</v>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>지금 환율 예상 범위 얼마로 보고 있어?</t>
+          <t>환율 월간 예상 범위 얼마로 보고 있어?</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
@@ -4210,13 +4134,25 @@
       </c>
       <c r="F93" s="14" t="inlineStr">
         <is>
-          <t>2026년 8월 3주차 주간 금융시장 동향에 따른 주요 통화별 주간 예상 범위는 USDKRW 1,400~1,430, USDJPY 157.5~160.5, EURUSD 1.150~1.160, USDCNY 6.730~6.750이며, 월간 예상 범위는 USDKRW 1,400~1,460, USDJPY 155.0~163.0, EURUSD 1.135~1.165, USDCNY 6.730~6.790으로 보고 있어요. 해당 수치는 2026.08.14 종가 기준으로 작성된 2026년 8월 3주차 자료예요. ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다. ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr"/>
+          <t>2026년 8월 3주차 자료를 기준으로, 2026년 8월 월간 환율 예상 범위는 통화별로 다르게 보고 있어요.
+- USDKRW — 1,400~1,460
+- USDJPY — 155.0~163.0
+- EURUSD — 1.135~1.165
+- USDCNY — 6.730~6.790
+시황과 상품 정보는 시장 변동이나 상품 개편에 따라 빠르게 달라질 수 있으니 참고해 주세요.
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 기준시점이 지난 수치는 최신 자료로 확인하세요. — 2026.08.14 종가 기준 (2026년 8월 3주차) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 주간 금융시장 동향 — 2026년 8월 3주차 (WM고객그룹 WM투자상품부, 2026-08)
+     — 6. 주요 차트 및 환율 예상 범위 [mkt.주간금융시장동향_2026-08_3주차.06 · 관련도 2.0]</t>
+        </is>
+      </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>– 디버깅용 · 신규</t>
+          <t>○ 예비 · 신규</t>
         </is>
       </c>
       <c r="I93" s="14" t="inlineStr">
@@ -4226,13 +4162,12 @@
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>**시연 보류 — 주간 재료가 6주 낡음.** 「지금」에 8월 3주차 1,410원대가 나온다. 봐야 할 것은 범위의 양 끝과 기준시점이 함께 나오는가</t>
+          <t>월간 범위의 양 끝 + 기준시점을 함께 ↔ 기준시점 없이 숫자만 말해 오늘 값처럼 읽힌다 · 묻지 않은 주간 범위로 답한다</t>
         </is>
       </c>
       <c r="K93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="486" customHeight="1">
-      <c r="A94" s="11" t="n"/>
       <c r="C94" s="12" t="n">
         <v>90</v>
       </c>
@@ -4276,7 +4211,7 @@
       <c r="K94" s="14" t="inlineStr"/>
     </row>
     <row r="95" ht="216" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="24" t="inlineStr">
         <is>
           <t>Ⅳ. 고객 응대 — 이 고객에게 무엇을 권할 수 있고, 어떻게 말할 것인가</t>
         </is>
@@ -4331,7 +4266,6 @@
       <c r="K95" s="9" t="inlineStr"/>
     </row>
     <row r="96" ht="391.5" customHeight="1">
-      <c r="A96" s="11" t="n"/>
       <c r="C96" s="12" t="n">
         <v>92</v>
       </c>
@@ -4401,7 +4335,6 @@
       </c>
     </row>
     <row r="97" hidden="1">
-      <c r="A97" s="11" t="n"/>
       <c r="C97" s="12" t="n">
         <v>93</v>
       </c>
@@ -4452,7 +4385,6 @@
       <c r="K97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="580.5" customHeight="1">
-      <c r="A98" s="11" t="n"/>
       <c r="C98" s="12" t="n">
         <v>94</v>
       </c>
@@ -4514,7 +4446,6 @@
       <c r="K98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="567" customHeight="1">
-      <c r="A99" s="11" t="n"/>
       <c r="C99" s="12" t="n">
         <v>95</v>
       </c>
@@ -4579,7 +4510,6 @@
       <c r="K99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="148.5" customHeight="1">
-      <c r="A100" s="11" t="n"/>
       <c r="C100" s="12" t="n">
         <v>96</v>
       </c>
@@ -4622,7 +4552,6 @@
       <c r="K100" s="14" t="inlineStr"/>
     </row>
     <row r="101" hidden="1">
-      <c r="A101" s="11" t="n"/>
       <c r="C101" s="12" t="n">
         <v>97</v>
       </c>
@@ -4675,7 +4604,6 @@
       <c r="K101" s="14" t="inlineStr"/>
     </row>
     <row r="102" hidden="1">
-      <c r="A102" s="11" t="n"/>
       <c r="B102" s="18" t="inlineStr">
         <is>
           <t>15. 퇴직연금 운용 상품</t>
@@ -4728,7 +4656,6 @@
       <c r="K102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="850.5" customHeight="1">
-      <c r="A103" s="11" t="n"/>
       <c r="C103" s="12" t="n">
         <v>99</v>
       </c>
@@ -4744,52 +4671,27 @@
       </c>
       <c r="F103" s="14" t="inlineStr">
         <is>
-          <t>8월 퇴직연금 추천펀드(디폴트옵션)에 올라와 있는 상품은 위험도별로 구분되어 있으며, 2026년 8월 기준(수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준)으로 안내할 수 있다. 시장 변동과 상품 개편에 따라 빠르게 달라질 수 있으므로 인용 전 기준시점을 확인해야 한다. 
-초저위험 지켜드림 포트폴리오는 비중 100이며 1년 수익률 2.13%로 구성되어 있다. 편입상품은 다음과 같다.
-- 지켜드림 — 신한은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 35, 금리 3.40%)
-- 지켜드림 — 기업은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 35, 금리 3.25%)
-- 지켜드림 — 하나은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 30, 금리 3.32%)
-저위험 알파드림 포트폴리오는 비중 100이며 1년 수익률 4.23%이다. 편입상품은 다음과 같다.
-- 알파드림 — 수협은행 노후보장 정기예금 디폴트옵션용(3년) (비중 70, 금리 3.27%)
-- 알파드림 — 키움키워드림적격TDF2030 (비중 20)
-- 알파드림 — 삼성글로벌EMP적격TDF2035 (비중 10)
-저위험 알파드림 II 포트폴리오는 비중 100이며 1년 수익률 8.56%이다. 편입상품은 다음과 같다.
-- 알파드림 II — 기업은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 50, 금리 3.25%)
-- 알파드림 II — KB다이나믹적격TDF2030 (비중 40)
-- 알파드림 II — NH하나로적격TDF2035 (비중 10)
-저위험 알파드림 III 포트폴리오는 비중 100이며 1년 수익률 5.86%이다. 편입상품은 다음과 같다.
-- 알파드림 III — 농협은행 디폴트옵션 퇴직연금 정기예금(3년) (비중 35, 금리 3.40%)
-- 알파드림 III — DB손해보험 퇴직연금 디폴트옵션 이율보증형보험(3년) (비중 35, 금리 4.41%)
-- 알파드림 III — KB온국민적격TDF2035(H) (비중 30)
-중위험 뿔려드림 포트폴리오는 비중 100이며 1년 수익률 13.95%이다. 편입상품은 다음과 같다.
-- 뿔려드림 — 하나은행 퇴직연금 디폴트옵션 정기예금(3년) (비중 30, 금리 3.32%)
-- 뿔려드림 — KB다이나믹적격TDF2040 (비중 50)
-- 뿔려드림 — 한화Lifeplus적격TDF2040 (비중 20)
-중위험 뿔려드림 II 포트폴리오는 비중 100이며 1년 수익률 15.04%이다. 편입상품은 다음과 같다.
-- 뿔려드림 II — 미래에셋평생소득 TIF (비중 70)
-- 뿔려드림 II — 키움불리온글로벌멀티에셋EMP(UH) (비중 20)
-- 뿔려드림 II — IBK플레인바닐라EMP (비중 10)
-중위험 뿔려드림 III 포트폴리오는 비중 100이며 1년 수익률 10.59%이다. 편입상품은 다음과 같다.
-- 뿔려드림 III — KB라이프생명 퇴직연금 디폴트옵션 이율보증형보험(3년) (비중 20, 금리 4.25%)
-- 뿔려드림 III — KB드림스타자산배분안정형 (비중 80)
-고위험 모두드림 포트폴리오는 비중 100이며 1년 수익률 20.63%이다. 편입상품은 다음과 같다.
-- 모두드림 — KB온국민적격TDF2055(UH) (비중 60)
-- 모두드림 — 한국투자적격TDF알아서2050(UH) (비중 20)
-- 모두드림 — 한화Lifeplus적격TDF2045 (비중 20)
-고위험 모두드림 II 포트폴리오는 비중 100이며 1년 수익률 19.19%이다. 편입상품은 다음과 같다.
-- 모두드림 II — KB다이나믹적격TDF2050 (비중 50)
-- 모두드림 II — 한국투자적격TDF알아서2055(UH) (비중 40)
-- 모두드림 II — 미래에셋전략배분적격TDF2050 (비중 10)
-고위험 모두드림 III 포트폴리오는 비중 100이며 1년 수익률 15.19%이다. 편입상품은 다음과 같다.
-- 모두드림 III — 미래에셋디폴트전략배분성장형 (비중 100)
-※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기
-── 빠뜨리면 안 되는 표시
-· 8월 퇴직연금 추천펀드(디폴트옵션)
-  ※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 인용 전 as_of 기준시점을 확인하고, 시효가 지난 수치는 갱신하거나 ⏳ 시효 민감 표기와 함께 사용하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
-  ⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
-        </is>
-      </c>
-      <c r="G103" s="14" t="inlineStr"/>
+          <t>8월 퇴직연금 추천펀드 목록은 위험도 구분별로 다음과 같이 구성되어 있어요. 2026년 8월 자료 기준으로, 수익률은 2026년 7월 30일 기준이며 원리금보장 금리는 2026년 8월 기준이에요. 시황과 상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라질 수 있으니 최신 자료로 확인해 보세요.
+- 초저위험 — 지켜드림 (신한·기업·하나은행 정기예금, 포트폴리오 1년 수익률 2.13%)
+- 저위험 — 알파드림 (수협은행 정기예금 및 TDF, 포트폴리오 1년 수익률 4.23%)
+- 저위험 — 알파드림 II (기업은행 정기예금 및 TDF, 포트폴리오 1년 수익률 8.56%)
+- 저위험 — 알파드림 III (농협은행 정기예금, DB손해보험 이율보증형보험 및 TDF, 포트폴리오 1년 수익률 5.86%)
+- 중위험 — 뿔려드림 (하나은행 정기예금 및 TDF, 포트폴리오 1년 수익률 13.95%)
+- 중위험 — 뿔려드림 II (미래에셋 TIF 및 EMP 자산배분형 펀드, 포트폴리오 1년 수익률 15.04%)
+- 중위험 — 뿔려드림 III (KB라이프생명 이율보증형보험 및 자산배분안정형 펀드, 포트폴리오 1년 수익률 10.59%)
+- 고위험 — 모두드림 (TDF 100 투자 포트폴리오, 포트폴리오 1년 수익률 20.63%)
+- 고위험 — 모두드림 II (액티브 TDF 100 포트폴리오, 포트폴리오 1년 수익률 19.19%)
+- 고위험 — 모두드림 III (자산배분형 BF, BF 1년 수익률 15.19%)
+※ 시황·상품 정보는 시장 변동과 상품 개편에 따라 빠르게 달라집니다. 기준시점이 지난 수치는 최신 자료로 확인하세요. — 2026.08 (수익률 2026.07.30 기준 / 원리금보장 금리 2026년 8월 기준) 기준 표기입니다.
+⚖ 본 자료는 정보 제공을 목적으로 합니다. 당행 직원은 투자권유 또는 투자관련 고객 상담 시 「자본시장과 금융투자업에 관한 법률」 및 당행 규정업무 프로세스를 준수할 의무가 있습니다.</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 8월 퇴직연금 추천펀드 (2026-08)
+     — 8월 퇴직연금 추천펀드(디폴트옵션) [lnp.퇴직연금_추천펀드_2026-08.01 · 관련도 2.0]</t>
+        </is>
+      </c>
       <c r="H103" s="15" t="inlineStr">
         <is>
           <t>◎ 1순위 · 신규</t>
@@ -4808,7 +4710,6 @@
       <c r="K103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="121.5" customHeight="1">
-      <c r="A104" s="11" t="n"/>
       <c r="C104" s="12" t="n">
         <v>100</v>
       </c>
@@ -4846,7 +4747,6 @@
       <c r="K104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="769.5" customHeight="1">
-      <c r="A105" s="11" t="n"/>
       <c r="C105" s="12" t="n">
         <v>101</v>
       </c>
@@ -4923,7 +4823,6 @@
       <c r="K105" s="14" t="inlineStr"/>
     </row>
     <row r="106" hidden="1">
-      <c r="A106" s="11" t="n"/>
       <c r="C106" s="12" t="n">
         <v>102</v>
       </c>
@@ -4961,7 +4860,6 @@
       <c r="K106" s="14" t="inlineStr"/>
     </row>
     <